--- a/output/lstm_results/lstm_data_for_cnn.xlsx
+++ b/output/lstm_results/lstm_data_for_cnn.xlsx
@@ -1093,10 +1093,10 @@
         <v>114.8469000678166</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2316407252489419</v>
+        <v>0.1925688695539132</v>
       </c>
       <c r="K17" t="n">
-        <v>2.272597634866488</v>
+        <v>1.946494139388905</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1131,10 +1131,10 @@
         <v>121.7140396574449</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05485432698210912</v>
+        <v>0.1905665222358762</v>
       </c>
       <c r="K18" t="n">
-        <v>0.787186729151895</v>
+        <v>1.929481341763332</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>89.62398589490867</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1032483839981409</v>
+        <v>0.2360938010258965</v>
       </c>
       <c r="K19" t="n">
-        <v>1.193807717916469</v>
+        <v>2.31630053817379</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1207,10 +1207,10 @@
         <v>33.54426885605007</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1047391856533133</v>
+        <v>0.05701234694615651</v>
       </c>
       <c r="K20" t="n">
-        <v>1.206333868449318</v>
+        <v>0.794748053593358</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>82.94462674435562</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0488521441161452</v>
+        <v>0.05245233461809251</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7367546372341722</v>
+        <v>0.756004242163316</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1283,10 +1283,10 @@
         <v>23.47033001498375</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04222428827033076</v>
+        <v>0.05796888564407363</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6810654583641027</v>
+        <v>0.8028752147217519</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1321,10 +1321,10 @@
         <v>32.71524464985964</v>
       </c>
       <c r="J23" t="n">
-        <v>0.07381110992376212</v>
+        <v>0.07487962711095554</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9464671511462076</v>
+        <v>0.9465560934998213</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1359,10 +1359,10 @@
         <v>113.7463477350483</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03267522789902302</v>
+        <v>0.0397574331278687</v>
       </c>
       <c r="K24" t="n">
-        <v>0.600831466643436</v>
+        <v>0.6481429395889411</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1397,10 +1397,10 @@
         <v>81.75279556005768</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06493302358485026</v>
+        <v>0.1181214719597936</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8718708790405296</v>
+        <v>1.313957267483446</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>62.21109375611755</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1132926868762488</v>
+        <v>0.08474754956698828</v>
       </c>
       <c r="K26" t="n">
-        <v>1.278202881694412</v>
+        <v>1.030398175349001</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>28.06236322373248</v>
       </c>
       <c r="J27" t="n">
-        <v>0.04735134644359038</v>
+        <v>0.04264998204503379</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7241444972463705</v>
+        <v>0.6727192700319765</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1511,10 +1511,10 @@
         <v>178.9689372272236</v>
       </c>
       <c r="J28" t="n">
-        <v>0.07887168408307506</v>
+        <v>0.07111572514984059</v>
       </c>
       <c r="K28" t="n">
-        <v>0.9889875719428067</v>
+        <v>0.9145763756106559</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1549,10 +1549,10 @@
         <v>84.11208605333923</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5912174973696124</v>
+        <v>0.7815287466041109</v>
       </c>
       <c r="K29" t="n">
-        <v>5.293866601178711</v>
+        <v>6.950548684561913</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>66.36956275509391</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0817809682692516</v>
+        <v>0.1415566423340512</v>
       </c>
       <c r="K30" t="n">
-        <v>1.013432226624028</v>
+        <v>1.51307247956811</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1625,10 +1625,10 @@
         <v>23.40047239476943</v>
       </c>
       <c r="J31" t="n">
-        <v>0.1376186785488715</v>
+        <v>0.1759279571810698</v>
       </c>
       <c r="K31" t="n">
-        <v>1.482596962218057</v>
+        <v>1.805105843785103</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -1663,10 +1663,10 @@
         <v>36.12062232917751</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05928884968812677</v>
+        <v>0.06804379461858087</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8244468829518236</v>
+        <v>0.8884759423954136</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1701,10 +1701,10 @@
         <v>67.72668745095386</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1124034626348028</v>
+        <v>0.1048645098562135</v>
       </c>
       <c r="K33" t="n">
-        <v>1.270731360136085</v>
+        <v>1.201320457991665</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1739,10 +1739,10 @@
         <v>66.6799118919286</v>
       </c>
       <c r="J34" t="n">
-        <v>0.04722770236632537</v>
+        <v>0.08611848777488625</v>
       </c>
       <c r="K34" t="n">
-        <v>0.723105603629005</v>
+        <v>1.042046251623301</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -1777,10 +1777,10 @@
         <v>23.13933709366622</v>
       </c>
       <c r="J35" t="n">
-        <v>0.1033989645944937</v>
+        <v>0.1579109550289008</v>
       </c>
       <c r="K35" t="n">
-        <v>1.195072940027471</v>
+        <v>1.65202570195692</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1815,10 +1815,10 @@
         <v>106.0058085639172</v>
       </c>
       <c r="J36" t="n">
-        <v>0.08117218242414471</v>
+        <v>0.1006895892114787</v>
       </c>
       <c r="K36" t="n">
-        <v>1.008317030305579</v>
+        <v>1.165848549900647</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -1853,10 +1853,10 @@
         <v>111.0797348091605</v>
       </c>
       <c r="J37" t="n">
-        <v>0.1486504804076339</v>
+        <v>0.1081707527181829</v>
       </c>
       <c r="K37" t="n">
-        <v>1.575289380590396</v>
+        <v>1.229411708797657</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>87.29390324232857</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1278125071293396</v>
+        <v>0.1539742499000445</v>
       </c>
       <c r="K38" t="n">
-        <v>1.400202648443453</v>
+        <v>1.618577774584136</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>83.81767290214503</v>
       </c>
       <c r="J39" t="n">
-        <v>0.04596416474788325</v>
+        <v>0.06965420834600257</v>
       </c>
       <c r="K39" t="n">
-        <v>0.7124889918499602</v>
+        <v>0.9021587049168183</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -1967,10 +1967,10 @@
         <v>123.6619279845129</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1629874121429683</v>
+        <v>0.1692094752537167</v>
       </c>
       <c r="K40" t="n">
-        <v>1.695752464645131</v>
+        <v>1.748022753178629</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2005,10 +2005,10 @@
         <v>72.37302001879915</v>
       </c>
       <c r="J41" t="n">
-        <v>0.08050736148951604</v>
+        <v>0.1630267762381067</v>
       </c>
       <c r="K41" t="n">
-        <v>1.002731010813546</v>
+        <v>1.695491902918582</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>25.18680930590299</v>
       </c>
       <c r="J42" t="n">
-        <v>0.05725280131785473</v>
+        <v>0.1020123989237283</v>
       </c>
       <c r="K42" t="n">
-        <v>0.807339410411998</v>
+        <v>1.177087705929636</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         <v>26.08296014960563</v>
       </c>
       <c r="J43" t="n">
-        <v>0.05717175776637236</v>
+        <v>0.05409404948526979</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8066584588433821</v>
+        <v>0.7699529525306885</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>35.47804767394748</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07154675615362602</v>
+        <v>0.03471981784077675</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9274413900156515</v>
+        <v>0.6053412095280375</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2157,10 +2157,10 @@
         <v>39.6555224279732</v>
       </c>
       <c r="J45" t="n">
-        <v>0.0457471723795109</v>
+        <v>0.08645046900855807</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7106657586510428</v>
+        <v>1.044866905908934</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>121.5997448837984</v>
       </c>
       <c r="J46" t="n">
-        <v>0.133482973576013</v>
+        <v>0.1141262458867649</v>
       </c>
       <c r="K46" t="n">
-        <v>1.447847562209184</v>
+        <v>1.280012121186106</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2233,10 +2233,10 @@
         <v>29.34622241644798</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05916139908491252</v>
+        <v>0.186762093940394</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8233760057926622</v>
+        <v>1.897157294836498</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -2271,10 +2271,10 @@
         <v>25.88280985124668</v>
       </c>
       <c r="J48" t="n">
-        <v>0.01808969251353029</v>
+        <v>0.0266274941842466</v>
       </c>
       <c r="K48" t="n">
-        <v>0.47827954217583</v>
+        <v>0.5365853730909497</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2309,10 +2309,10 @@
         <v>71.84021847365975</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1215854862649806</v>
+        <v>0.08313714525477334</v>
       </c>
       <c r="K49" t="n">
-        <v>1.347881402053954</v>
+        <v>1.016715492823212</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2347,10 +2347,10 @@
         <v>26.31970097007814</v>
       </c>
       <c r="J50" t="n">
-        <v>0.04783269637789879</v>
+        <v>0.08242402530595418</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7281889398556234</v>
+        <v>1.010656521303769</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>109.8994831034783</v>
       </c>
       <c r="J51" t="n">
-        <v>0.09135474934027876</v>
+        <v>0.05240531444659309</v>
       </c>
       <c r="K51" t="n">
-        <v>1.093873928877406</v>
+        <v>0.7556047387131235</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2423,10 +2423,10 @@
         <v>115.5930553014347</v>
       </c>
       <c r="J52" t="n">
-        <v>0.1394623463415794</v>
+        <v>0.08088031154924248</v>
       </c>
       <c r="K52" t="n">
-        <v>1.498087997007224</v>
+        <v>0.9975404702080489</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2461,10 +2461,10 @@
         <v>27.53483451710818</v>
       </c>
       <c r="J53" t="n">
-        <v>0.05624009696318586</v>
+        <v>0.1335894103379344</v>
       </c>
       <c r="K53" t="n">
-        <v>0.798830372910033</v>
+        <v>1.445379475280115</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2499,10 +2499,10 @@
         <v>92.81163954514967</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04325582656786238</v>
+        <v>0.02130485608554347</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6897327441498735</v>
+        <v>0.4913619675450124</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -2537,10 +2537,10 @@
         <v>68.64758615761735</v>
       </c>
       <c r="J55" t="n">
-        <v>0.1417615878903824</v>
+        <v>0.1235334600947901</v>
       </c>
       <c r="K55" t="n">
-        <v>1.517406895434631</v>
+        <v>1.359939829081685</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2575,10 +2575,10 @@
         <v>32.10072468819907</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1109294868476956</v>
+        <v>0.07785075540776157</v>
       </c>
       <c r="K56" t="n">
-        <v>1.258346585456623</v>
+        <v>0.9718000678981946</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -2613,10 +2613,10 @@
         <v>88.17425718751845</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0516763120862097</v>
+        <v>0.01745413919346912</v>
       </c>
       <c r="K57" t="n">
-        <v>0.760484120630128</v>
+        <v>0.4586446329407117</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2651,10 +2651,10 @@
         <v>33.64864409743456</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1165349541814101</v>
+        <v>0.05722416420351612</v>
       </c>
       <c r="K58" t="n">
-        <v>1.305445357708089</v>
+        <v>0.7965477434376733</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -2689,10 +2689,10 @@
         <v>104.1398557364249</v>
       </c>
       <c r="J59" t="n">
-        <v>0.06082231104575582</v>
+        <v>0.08192360295829193</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8373314727531049</v>
+        <v>1.006404719405365</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>35.82186992468936</v>
       </c>
       <c r="J60" t="n">
-        <v>0.03002908622149717</v>
+        <v>0.06424737291371233</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5785978121066762</v>
+        <v>0.8562199228804854</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2765,10 +2765,10 @@
         <v>105.0936929976162</v>
       </c>
       <c r="J61" t="n">
-        <v>0.05341688180436658</v>
+        <v>0.07432303546427563</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7751088953121963</v>
+        <v>0.9418270532580246</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2803,10 +2803,10 @@
         <v>15.95273410077372</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1164399744870036</v>
+        <v>0.01973248957865294</v>
       </c>
       <c r="K62" t="n">
-        <v>1.304647310599963</v>
+        <v>0.4780024704517788</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -2841,10 +2841,10 @@
         <v>14.44056525502462</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1270480649853807</v>
+        <v>0.1356521616816735</v>
       </c>
       <c r="K63" t="n">
-        <v>1.39377958248048</v>
+        <v>1.462905491294818</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>124.6923600882982</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1682783132110496</v>
+        <v>0.1660646975434473</v>
       </c>
       <c r="K64" t="n">
-        <v>1.740208159340165</v>
+        <v>1.721303379231716</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -2917,10 +2917,10 @@
         <v>73.9138887471542</v>
       </c>
       <c r="J65" t="n">
-        <v>0.04969682707962546</v>
+        <v>0.03557915525352755</v>
       </c>
       <c r="K65" t="n">
-        <v>0.7438519099775827</v>
+        <v>0.6126425070419704</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -2955,10 +2955,10 @@
         <v>33.29099889520067</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1817306317517525</v>
+        <v>0.1724114086071316</v>
       </c>
       <c r="K66" t="n">
-        <v>1.853238465197443</v>
+        <v>1.775227745869721</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -2993,10 +2993,10 @@
         <v>36.12473419365777</v>
       </c>
       <c r="J67" t="n">
-        <v>0.1216449209002296</v>
+        <v>0.06507320674808981</v>
       </c>
       <c r="K67" t="n">
-        <v>1.348380789202748</v>
+        <v>0.8632365596897227</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3031,10 +3031,10 @@
         <v>35.50586425445584</v>
       </c>
       <c r="J68" t="n">
-        <v>0.02770859077818551</v>
+        <v>0.07878124263604053</v>
       </c>
       <c r="K68" t="n">
-        <v>0.5591003322555759</v>
+        <v>0.9797058846190472</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -3069,10 +3069,10 @@
         <v>88.72976512269027</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1116239552662209</v>
+        <v>0.05205412143596317</v>
       </c>
       <c r="K69" t="n">
-        <v>1.264181711759694</v>
+        <v>0.7526208529688559</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3107,10 +3107,10 @@
         <v>33.49739262809233</v>
       </c>
       <c r="J70" t="n">
-        <v>0.1873106368098888</v>
+        <v>0.2332757641635142</v>
       </c>
       <c r="K70" t="n">
-        <v>1.900123295979434</v>
+        <v>2.292357293957737</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3145,10 +3145,10 @@
         <v>106.9492435594261</v>
       </c>
       <c r="J71" t="n">
-        <v>0.04684510921462098</v>
+        <v>0.04594907232511902</v>
       </c>
       <c r="K71" t="n">
-        <v>0.7198909443250938</v>
+        <v>0.7007497494488104</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -3183,10 +3183,10 @@
         <v>23.12531551755875</v>
       </c>
       <c r="J72" t="n">
-        <v>0.09323783954564498</v>
+        <v>0.09687013937000252</v>
       </c>
       <c r="K72" t="n">
-        <v>1.109696202281458</v>
+        <v>1.13339687350628</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -3221,10 +3221,10 @@
         <v>117.4502470876525</v>
       </c>
       <c r="J73" t="n">
-        <v>0.04372017811278468</v>
+        <v>0.09106621404616959</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6936343613312583</v>
+        <v>1.084084246231849</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -3259,10 +3259,10 @@
         <v>25.48816953315677</v>
       </c>
       <c r="J74" t="n">
-        <v>0.1877569535745373</v>
+        <v>0.2142756859137332</v>
       </c>
       <c r="K74" t="n">
-        <v>1.903873379674287</v>
+        <v>2.130924517924412</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3297,10 +3297,10 @@
         <v>57.89955282364862</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05868755690688515</v>
+        <v>0.1057310337176447</v>
       </c>
       <c r="K75" t="n">
-        <v>0.8193946455424972</v>
+        <v>1.208682814641515</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3335,10 +3335,10 @@
         <v>60.76219120513985</v>
       </c>
       <c r="J76" t="n">
-        <v>0.2560602437503157</v>
+        <v>0.3177006168867587</v>
       </c>
       <c r="K76" t="n">
-        <v>2.477777555097066</v>
+        <v>3.009666884062983</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3373,10 +3373,10 @@
         <v>20.96210697934295</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1145799998831253</v>
+        <v>0.2420302074538876</v>
       </c>
       <c r="K77" t="n">
-        <v>1.289019261224903</v>
+        <v>2.366738781465958</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3411,10 +3411,10 @@
         <v>28.48467465157554</v>
       </c>
       <c r="J78" t="n">
-        <v>0.08109232624465894</v>
+        <v>0.1204900649068309</v>
       </c>
       <c r="K78" t="n">
-        <v>1.007646055382962</v>
+        <v>1.334081844324997</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         <v>64.61049376040711</v>
       </c>
       <c r="J79" t="n">
-        <v>0.05136818446911432</v>
+        <v>0.03848444140713767</v>
       </c>
       <c r="K79" t="n">
-        <v>0.7578951424775526</v>
+        <v>0.6373270584834293</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -3487,10 +3487,10 @@
         <v>122.4383516905176</v>
       </c>
       <c r="J80" t="n">
-        <v>0.2379591619414113</v>
+        <v>0.2583422669276106</v>
       </c>
       <c r="K80" t="n">
-        <v>2.325686983719534</v>
+        <v>2.505333002449977</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>38.68579695731702</v>
       </c>
       <c r="J81" t="n">
-        <v>0.07672985798262491</v>
+        <v>0.06744890716079943</v>
       </c>
       <c r="K81" t="n">
-        <v>0.9709913240473617</v>
+        <v>0.8834215245938357</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -3563,10 +3563,10 @@
         <v>109.3671888960649</v>
       </c>
       <c r="J82" t="n">
-        <v>0.06279556925567271</v>
+        <v>0.03344644394929262</v>
       </c>
       <c r="K82" t="n">
-        <v>0.8539113640430296</v>
+        <v>0.594522081336657</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3601,10 +3601,10 @@
         <v>91.0271668826406</v>
       </c>
       <c r="J83" t="n">
-        <v>0.1618491469703704</v>
+        <v>0.1666223103729249</v>
       </c>
       <c r="K83" t="n">
-        <v>1.686188428511423</v>
+        <v>1.726041095878509</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -3639,10 +3639,10 @@
         <v>95.33092216736178</v>
       </c>
       <c r="J84" t="n">
-        <v>0.2573287122580685</v>
+        <v>0.1680658352603595</v>
       </c>
       <c r="K84" t="n">
-        <v>2.488435597646966</v>
+        <v>1.738305899569749</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3677,10 +3677,10 @@
         <v>64.82338270846122</v>
       </c>
       <c r="J85" t="n">
-        <v>0.1518729364350132</v>
+        <v>0.09132628287558688</v>
       </c>
       <c r="K85" t="n">
-        <v>1.602365396467082</v>
+        <v>1.08629390203119</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3715,10 +3715,10 @@
         <v>84.98224840494723</v>
       </c>
       <c r="J86" t="n">
-        <v>0.1312910065149329</v>
+        <v>0.07569551730006013</v>
       </c>
       <c r="K86" t="n">
-        <v>1.429430015331051</v>
+        <v>0.9534882448538309</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>42.84487154692216</v>
       </c>
       <c r="J87" t="n">
-        <v>0.06280575698473986</v>
+        <v>0.05382452405998766</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8539969643155005</v>
+        <v>0.7676629494558139</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -3791,10 +3791,10 @@
         <v>120.2882694055234</v>
       </c>
       <c r="J88" t="n">
-        <v>0.06002416568512538</v>
+        <v>0.01569302601631524</v>
       </c>
       <c r="K88" t="n">
-        <v>0.8306252225288285</v>
+        <v>0.4436814635600753</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -3829,10 +3829,10 @@
         <v>32.79197701173295</v>
       </c>
       <c r="J89" t="n">
-        <v>0.05188999012685597</v>
+        <v>0.2250497321451624</v>
       </c>
       <c r="K89" t="n">
-        <v>0.7622795058803475</v>
+        <v>2.222465414197881</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -3867,10 +3867,10 @@
         <v>39.23217192460997</v>
       </c>
       <c r="J90" t="n">
-        <v>0.04964334104928272</v>
+        <v>0.05052913795359089</v>
       </c>
       <c r="K90" t="n">
-        <v>0.7434025047430546</v>
+        <v>0.7396639422799665</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -3905,10 +3905,10 @@
         <v>80.8818945812928</v>
       </c>
       <c r="J91" t="n">
-        <v>0.02895202868095463</v>
+        <v>0.08472638262288597</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5695480603583021</v>
+        <v>1.030218331955639</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -3943,10 +3943,10 @@
         <v>68.6924200009226</v>
       </c>
       <c r="J92" t="n">
-        <v>0.1706683411958944</v>
+        <v>0.1462484096882001</v>
       </c>
       <c r="K92" t="n">
-        <v>1.760289871895296</v>
+        <v>1.552935737946613</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -3981,10 +3981,10 @@
         <v>173.9483675996963</v>
       </c>
       <c r="J93" t="n">
-        <v>0.05200276713450238</v>
+        <v>0.1206399512443185</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7632270912076926</v>
+        <v>1.335355342635477</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4019,10 +4019,10 @@
         <v>84.91187413383388</v>
       </c>
       <c r="J94" t="n">
-        <v>0.687983943555829</v>
+        <v>0.7698238241908597</v>
       </c>
       <c r="K94" t="n">
-        <v>6.106926519144229</v>
+        <v>6.851098666852243</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>25.35443363328814</v>
       </c>
       <c r="J95" t="n">
-        <v>0.2328252927832088</v>
+        <v>0.2671226474265916</v>
       </c>
       <c r="K95" t="n">
-        <v>2.282550716954283</v>
+        <v>2.579934863555245</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -4095,10 +4095,10 @@
         <v>20.72750508428866</v>
       </c>
       <c r="J96" t="n">
-        <v>0.02335411640163046</v>
+        <v>0.05747529079676747</v>
       </c>
       <c r="K96" t="n">
-        <v>0.5225127678784406</v>
+        <v>0.7986814221810661</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4133,10 +4133,10 @@
         <v>119.9965664792726</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0440580036471459</v>
+        <v>0.06840956173924234</v>
       </c>
       <c r="K97" t="n">
-        <v>0.6964728700507561</v>
+        <v>0.8915836560002657</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -4171,10 +4171,10 @@
         <v>113.9334376356151</v>
       </c>
       <c r="J98" t="n">
-        <v>0.08431821887834411</v>
+        <v>0.1332571932311445</v>
       </c>
       <c r="K98" t="n">
-        <v>1.034750946628655</v>
+        <v>1.442556816915775</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -4209,10 +4209,10 @@
         <v>14.31034497073012</v>
       </c>
       <c r="J99" t="n">
-        <v>0.07390193554762449</v>
+        <v>0.07456716239422292</v>
       </c>
       <c r="K99" t="n">
-        <v>0.9472302945414357</v>
+        <v>0.9439012598737968</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -4247,10 +4247,10 @@
         <v>89.85987267633391</v>
       </c>
       <c r="J100" t="n">
-        <v>0.107554195735074</v>
+        <v>0.1413525495374986</v>
       </c>
       <c r="K100" t="n">
-        <v>1.229986404595411</v>
+        <v>1.51133842004042</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -4285,10 +4285,10 @@
         <v>19.47897198073991</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1315838216767257</v>
+        <v>0.1272152905848346</v>
       </c>
       <c r="K101" t="n">
-        <v>1.431890333765896</v>
+        <v>1.391222232715936</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4323,10 +4323,10 @@
         <v>40.90389467653109</v>
       </c>
       <c r="J102" t="n">
-        <v>0.06652366815812931</v>
+        <v>0.130722756539854</v>
       </c>
       <c r="K102" t="n">
-        <v>0.8852359389061546</v>
+        <v>1.421023160823572</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4361,10 +4361,10 @@
         <v>33.58115805626418</v>
       </c>
       <c r="J103" t="n">
-        <v>0.01885444078156811</v>
+        <v>0.03209762695177764</v>
       </c>
       <c r="K103" t="n">
-        <v>0.4847051802826438</v>
+        <v>0.5830619563094199</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>73.345403061364</v>
       </c>
       <c r="J104" t="n">
-        <v>0.03442889336832976</v>
+        <v>0.09050659121151436</v>
       </c>
       <c r="K104" t="n">
-        <v>0.6155662756480949</v>
+        <v>1.079329451722986</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -4437,10 +4437,10 @@
         <v>72.39286302507902</v>
       </c>
       <c r="J105" t="n">
-        <v>0.05065637611354864</v>
+        <v>0.2944913654518761</v>
       </c>
       <c r="K105" t="n">
-        <v>0.7519143209635573</v>
+        <v>2.812471175733112</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4475,10 +4475,10 @@
         <v>76.64311227969927</v>
       </c>
       <c r="J106" t="n">
-        <v>0.1839067999557193</v>
+        <v>0.3114163466433322</v>
       </c>
       <c r="K106" t="n">
-        <v>1.871523265467895</v>
+        <v>2.956273041290169</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -4513,10 +4513,10 @@
         <v>42.81076421019374</v>
       </c>
       <c r="J107" t="n">
-        <v>0.2367134824797775</v>
+        <v>0.274515837220954</v>
       </c>
       <c r="K107" t="n">
-        <v>2.315220421385124</v>
+        <v>2.642750560235806</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4551,10 +4551,10 @@
         <v>119.293274760407</v>
       </c>
       <c r="J108" t="n">
-        <v>0.05727342179173957</v>
+        <v>0.06151129104276987</v>
       </c>
       <c r="K108" t="n">
-        <v>0.8075126696507733</v>
+        <v>0.8329730032586788</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>61.94308497251904</v>
       </c>
       <c r="J109" t="n">
-        <v>0.1222991711712613</v>
+        <v>0.02991799215497839</v>
       </c>
       <c r="K109" t="n">
-        <v>1.353877990894647</v>
+        <v>0.5645428485794193</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4627,10 +4627,10 @@
         <v>34.24069623645856</v>
       </c>
       <c r="J110" t="n">
-        <v>0.1183388659253758</v>
+        <v>0.2232657343227732</v>
       </c>
       <c r="K110" t="n">
-        <v>1.320602350574638</v>
+        <v>2.207307807101762</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4665,10 +4665,10 @@
         <v>19.02167673066241</v>
       </c>
       <c r="J111" t="n">
-        <v>0.07410995273420991</v>
+        <v>0.08828305809851086</v>
       </c>
       <c r="K111" t="n">
-        <v>0.9489781156439601</v>
+        <v>1.060437365158115</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -4703,10 +4703,10 @@
         <v>28.47111355015264</v>
       </c>
       <c r="J112" t="n">
-        <v>0.07723211555023327</v>
+        <v>0.1242862525429093</v>
       </c>
       <c r="K112" t="n">
-        <v>0.9752114386925905</v>
+        <v>1.366335875091559</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4741,10 +4741,10 @@
         <v>101.302456852818</v>
       </c>
       <c r="J113" t="n">
-        <v>0.03108650214518104</v>
+        <v>0.04217915027234887</v>
       </c>
       <c r="K113" t="n">
-        <v>0.5874825292586459</v>
+        <v>0.6687188822909369</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4779,10 +4779,10 @@
         <v>109.4984290196294</v>
       </c>
       <c r="J114" t="n">
-        <v>0.1856950301116169</v>
+        <v>0.2992587560415825</v>
       </c>
       <c r="K114" t="n">
-        <v>1.886548497055502</v>
+        <v>2.852976961404828</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -4817,10 +4817,10 @@
         <v>67.4631464787651</v>
       </c>
       <c r="J115" t="n">
-        <v>0.08396853903084429</v>
+        <v>0.08151094925463091</v>
       </c>
       <c r="K115" t="n">
-        <v>1.031812834510997</v>
+        <v>1.002898637375245</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -4855,10 +4855,10 @@
         <v>23.95297092332126</v>
       </c>
       <c r="J116" t="n">
-        <v>0.1236784844882521</v>
+        <v>0.1480972163422118</v>
       </c>
       <c r="K116" t="n">
-        <v>1.365467383877036</v>
+        <v>1.568643988543393</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -4893,10 +4893,10 @@
         <v>122.1683816138133</v>
       </c>
       <c r="J117" t="n">
-        <v>0.05826267030509389</v>
+        <v>0.1072765317739502</v>
       </c>
       <c r="K117" t="n">
-        <v>0.815824624329439</v>
+        <v>1.221814025908309</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -4931,10 +4931,10 @@
         <v>62.60808024303017</v>
       </c>
       <c r="J118" t="n">
-        <v>0.1261436761752676</v>
+        <v>0.1608255856656485</v>
       </c>
       <c r="K118" t="n">
-        <v>1.386180643791087</v>
+        <v>1.67678964811632</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -4969,10 +4969,10 @@
         <v>92.46182913504053</v>
       </c>
       <c r="J119" t="n">
-        <v>0.1114332848448975</v>
+        <v>0.0942364738303178</v>
       </c>
       <c r="K119" t="n">
-        <v>1.262579643240805</v>
+        <v>1.111020126756854</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -5007,10 +5007,10 @@
         <v>86.5508806686784</v>
       </c>
       <c r="J120" t="n">
-        <v>0.1015178778836529</v>
+        <v>0.112537079328458</v>
       </c>
       <c r="K120" t="n">
-        <v>1.179267500569055</v>
+        <v>1.266509883684016</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5045,10 +5045,10 @@
         <v>28.85152497254391</v>
       </c>
       <c r="J121" t="n">
-        <v>0.06177570886125396</v>
+        <v>0.1044929949791969</v>
       </c>
       <c r="K121" t="n">
-        <v>0.8453421994069048</v>
+        <v>1.198163908995075</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -5083,10 +5083,10 @@
         <v>35.86365758570292</v>
       </c>
       <c r="J122" t="n">
-        <v>0.05271989446192732</v>
+        <v>0.04621299923983416</v>
       </c>
       <c r="K122" t="n">
-        <v>0.7692526042753618</v>
+        <v>0.7029921851878773</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -5121,10 +5121,10 @@
         <v>20.59121683496781</v>
       </c>
       <c r="J123" t="n">
-        <v>0.08799689261428364</v>
+        <v>0.09635663130952234</v>
       </c>
       <c r="K123" t="n">
-        <v>1.065660236820103</v>
+        <v>1.129033889805422</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -5159,10 +5159,10 @@
         <v>104.4714017654278</v>
       </c>
       <c r="J124" t="n">
-        <v>0.07205028286433539</v>
+        <v>0.08871357277177076</v>
       </c>
       <c r="K124" t="n">
-        <v>0.9316721683715598</v>
+        <v>1.06409520161088</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -5197,10 +5197,10 @@
         <v>122.8532782011974</v>
       </c>
       <c r="J125" t="n">
-        <v>0.082160413948959</v>
+        <v>0.04891149629422316</v>
       </c>
       <c r="K125" t="n">
-        <v>1.016620439949767</v>
+        <v>0.72591976816311</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -5235,10 +5235,10 @@
         <v>33.39893216510407</v>
       </c>
       <c r="J126" t="n">
-        <v>0.1245585368967112</v>
+        <v>0.1492333677940109</v>
       </c>
       <c r="K126" t="n">
-        <v>1.372861841018205</v>
+        <v>1.578297216306301</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -5273,10 +5273,10 @@
         <v>194.5544584781439</v>
       </c>
       <c r="J127" t="n">
-        <v>0.01381819776179194</v>
+        <v>0.050714663219363</v>
       </c>
       <c r="K127" t="n">
-        <v>0.4423891968204251</v>
+        <v>0.7412402441395789</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
@@ -5311,10 +5311,10 @@
         <v>115.7097251581039</v>
       </c>
       <c r="J128" t="n">
-        <v>0.7086490820287286</v>
+        <v>0.7277640962272081</v>
       </c>
       <c r="K128" t="n">
-        <v>6.28056104282187</v>
+        <v>6.493741262576447</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>105.9910297556414</v>
       </c>
       <c r="J129" t="n">
-        <v>0.1905509434090683</v>
+        <v>0.2091809813939853</v>
       </c>
       <c r="K129" t="n">
-        <v>1.927349297569304</v>
+        <v>2.0876377333712</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -5387,10 +5387,10 @@
         <v>26.5434821081493</v>
       </c>
       <c r="J130" t="n">
-        <v>0.04634493545939958</v>
+        <v>0.09951716693374135</v>
       </c>
       <c r="K130" t="n">
-        <v>0.7156883384796108</v>
+        <v>1.15588714971638</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -5425,10 +5425,10 @@
         <v>111.3785682303266</v>
       </c>
       <c r="J131" t="n">
-        <v>0.02346251829008703</v>
+        <v>0.05190777419101923</v>
       </c>
       <c r="K131" t="n">
-        <v>0.523423592177663</v>
+        <v>0.7513774242994818</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -5463,10 +5463,10 @@
         <v>26.52294025040914</v>
       </c>
       <c r="J132" t="n">
-        <v>0.1211325307192015</v>
+        <v>0.139084116871679</v>
       </c>
       <c r="K132" t="n">
-        <v>1.3440755373828</v>
+        <v>1.492064847706992</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -5501,10 +5501,10 @@
         <v>37.67704602233532</v>
       </c>
       <c r="J133" t="n">
-        <v>0.02138914065237886</v>
+        <v>0.02000543188667737</v>
       </c>
       <c r="K133" t="n">
-        <v>0.5060024682399042</v>
+        <v>0.4803215048211155</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -5539,10 +5539,10 @@
         <v>112.1712897611939</v>
       </c>
       <c r="J134" t="n">
-        <v>0.04139841441143732</v>
+        <v>0.09823570137253831</v>
       </c>
       <c r="K134" t="n">
-        <v>0.6741262252060557</v>
+        <v>1.144999271244695</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -5577,10 +5577,10 @@
         <v>60.88529823360503</v>
       </c>
       <c r="J135" t="n">
-        <v>0.05898050009829231</v>
+        <v>0.06488564583347077</v>
       </c>
       <c r="K135" t="n">
-        <v>0.8218560397195213</v>
+        <v>0.8616429620884787</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -5615,10 +5615,10 @@
         <v>29.18651920249006</v>
       </c>
       <c r="J136" t="n">
-        <v>0.1265782419286085</v>
+        <v>0.1070971299944843</v>
       </c>
       <c r="K136" t="n">
-        <v>1.389831992059908</v>
+        <v>1.2202897518025</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -5653,10 +5653,10 @@
         <v>102.553626377895</v>
       </c>
       <c r="J137" t="n">
-        <v>0.03604415545313952</v>
+        <v>0.04618754052856461</v>
       </c>
       <c r="K137" t="n">
-        <v>0.6291381790291586</v>
+        <v>0.7027758771084871</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>36.02215449524763</v>
       </c>
       <c r="J138" t="n">
-        <v>0.1384490576322285</v>
+        <v>0.1100343694383196</v>
       </c>
       <c r="K138" t="n">
-        <v>1.489574049586702</v>
+        <v>1.245245792038722</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -5729,10 +5729,10 @@
         <v>76.53600097423418</v>
       </c>
       <c r="J139" t="n">
-        <v>0.07915361280596933</v>
+        <v>0.1227478542520291</v>
       </c>
       <c r="K139" t="n">
-        <v>0.9913564193412885</v>
+        <v>1.353264986462741</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -5767,10 +5767,10 @@
         <v>92.13551398927078</v>
       </c>
       <c r="J140" t="n">
-        <v>0.03081800945514273</v>
+        <v>0.08671024365859806</v>
       </c>
       <c r="K140" t="n">
-        <v>0.585226575328946</v>
+        <v>1.047074062234699</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -5805,10 +5805,10 @@
         <v>54.08938308637882</v>
       </c>
       <c r="J141" t="n">
-        <v>0.1262177089955708</v>
+        <v>0.1032153903043193</v>
       </c>
       <c r="K141" t="n">
-        <v>1.386802689150556</v>
+        <v>1.187308834261842</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -5843,10 +5843,10 @@
         <v>89.77451102997178</v>
       </c>
       <c r="J142" t="n">
-        <v>0.07534487083475429</v>
+        <v>0.1758830549812806</v>
       </c>
       <c r="K142" t="n">
-        <v>0.9593542578822576</v>
+        <v>1.804724335526732</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -5881,10 +5881,10 @@
         <v>21.82943845038909</v>
       </c>
       <c r="J143" t="n">
-        <v>0.07553315792555934</v>
+        <v>0.1291366266868479</v>
       </c>
       <c r="K143" t="n">
-        <v>0.9609363009626588</v>
+        <v>1.407546724466103</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -5919,10 +5919,10 @@
         <v>21.4249744422117</v>
       </c>
       <c r="J144" t="n">
-        <v>0.08161548378543126</v>
+        <v>0.08468280416495882</v>
       </c>
       <c r="K144" t="n">
-        <v>1.012041777701469</v>
+        <v>1.02984807077324</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -5957,10 +5957,10 @@
         <v>118.9327994529359</v>
       </c>
       <c r="J145" t="n">
-        <v>0.0647705083566341</v>
+        <v>0.1139655454435163</v>
       </c>
       <c r="K145" t="n">
-        <v>0.8705053786700055</v>
+        <v>1.278646741616486</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -5995,10 +5995,10 @@
         <v>62.07183825349536</v>
       </c>
       <c r="J146" t="n">
-        <v>0.03309494103942735</v>
+        <v>0.1841440234101028</v>
       </c>
       <c r="K146" t="n">
-        <v>0.6043580189242699</v>
+        <v>1.874913049944464</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -6033,10 +6033,10 @@
         <v>30.46899355097755</v>
       </c>
       <c r="J147" t="n">
-        <v>0.07933837265154114</v>
+        <v>0.0481988925447011</v>
       </c>
       <c r="K147" t="n">
-        <v>0.9929088254779658</v>
+        <v>0.7198651824932626</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -6071,10 +6071,10 @@
         <v>104.6330855262963</v>
       </c>
       <c r="J148" t="n">
-        <v>0.1223071811320787</v>
+        <v>0.0698174491535709</v>
       </c>
       <c r="K148" t="n">
-        <v>1.353945292922796</v>
+        <v>0.903545668506191</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -6109,10 +6109,10 @@
         <v>109.1764783474178</v>
       </c>
       <c r="J149" t="n">
-        <v>0.04400312816861474</v>
+        <v>0.08862847793601289</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6960117902670984</v>
+        <v>1.063372199558893</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -6147,10 +6147,10 @@
         <v>28.66860530453151</v>
       </c>
       <c r="J150" t="n">
-        <v>0.06932945716503812</v>
+        <v>0.06683529694089348</v>
       </c>
       <c r="K150" t="n">
-        <v>0.9088109968905695</v>
+        <v>0.8782080302124124</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -6185,10 +6185,10 @@
         <v>66.72342194373573</v>
       </c>
       <c r="J151" t="n">
-        <v>0.03243431455379053</v>
+        <v>0.03074681913855199</v>
       </c>
       <c r="K151" t="n">
-        <v>0.5988072424166355</v>
+        <v>0.5715849164620164</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -6223,10 +6223,10 @@
         <v>31.76600741280344</v>
       </c>
       <c r="J152" t="n">
-        <v>0.06450036728999295</v>
+        <v>0.04507731753489023</v>
       </c>
       <c r="K152" t="n">
-        <v>0.868235574599081</v>
+        <v>0.6933429485947874</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>37.32853209050136</v>
       </c>
       <c r="J153" t="n">
-        <v>0.05387991363395111</v>
+        <v>0.04583283703221455</v>
       </c>
       <c r="K153" t="n">
-        <v>0.7789994238602111</v>
+        <v>0.6997621647788983</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -6299,10 +6299,10 @@
         <v>78.81023218736155</v>
       </c>
       <c r="J154" t="n">
-        <v>0.08165799214708934</v>
+        <v>0.06949296571128319</v>
       </c>
       <c r="K154" t="n">
-        <v>1.01239894536035</v>
+        <v>0.9007887186569998</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -6337,10 +6337,10 @@
         <v>110.090723850182</v>
       </c>
       <c r="J155" t="n">
-        <v>0.2445406272865316</v>
+        <v>0.1808495584404956</v>
       </c>
       <c r="K155" t="n">
-        <v>2.380986376065706</v>
+        <v>1.846921869140018</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -6375,10 +6375,10 @@
         <v>107.1450817559737</v>
       </c>
       <c r="J156" t="n">
-        <v>0.06618532782352193</v>
+        <v>0.01247238507985443</v>
       </c>
       <c r="K156" t="n">
-        <v>0.8823931046847663</v>
+        <v>0.4163175232570699</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>36.17768345199257</v>
       </c>
       <c r="J157" t="n">
-        <v>0.02900942037479528</v>
+        <v>0.06317233131664034</v>
       </c>
       <c r="K157" t="n">
-        <v>0.5700302821172388</v>
+        <v>0.8470859105314242</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -6451,10 +6451,10 @@
         <v>107.071725210337</v>
       </c>
       <c r="J158" t="n">
-        <v>0.05098967087683243</v>
+        <v>0.05847809702079833</v>
       </c>
       <c r="K158" t="n">
-        <v>0.7547147608223526</v>
+        <v>0.8072016919631479</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -6489,10 +6489,10 @@
         <v>64.03655325042703</v>
       </c>
       <c r="J159" t="n">
-        <v>0.04660262036944481</v>
+        <v>0.08909107902032858</v>
       </c>
       <c r="K159" t="n">
-        <v>0.7178534822880249</v>
+        <v>1.067302655857828</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
@@ -6527,10 +6527,10 @@
         <v>169.4660714685987</v>
       </c>
       <c r="J160" t="n">
-        <v>0.1254402210374406</v>
+        <v>0.2104165646229064</v>
       </c>
       <c r="K160" t="n">
-        <v>1.380270008450058</v>
+        <v>2.098135775960433</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
@@ -6565,10 +6565,10 @@
         <v>68.76769979400528</v>
       </c>
       <c r="J161" t="n">
-        <v>0.5469982488643362</v>
+        <v>0.7045564915272282</v>
       </c>
       <c r="K161" t="n">
-        <v>4.9223235717591</v>
+        <v>6.296559545609308</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
@@ -6603,10 +6603,10 @@
         <v>32.36673308641997</v>
       </c>
       <c r="J162" t="n">
-        <v>0.1570194478003329</v>
+        <v>0.1909550687336595</v>
       </c>
       <c r="K162" t="n">
-        <v>1.645607886745613</v>
+        <v>1.932782598680835</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
@@ -6641,10 +6641,10 @@
         <v>71.96677153280275</v>
       </c>
       <c r="J163" t="n">
-        <v>0.0650955513678588</v>
+        <v>0.07082604158541332</v>
       </c>
       <c r="K163" t="n">
-        <v>0.8732364849000829</v>
+        <v>0.9121151003799992</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
@@ -6679,10 +6679,10 @@
         <v>36.51646156444046</v>
       </c>
       <c r="J164" t="n">
-        <v>0.04711915972808944</v>
+        <v>0.08954081110479438</v>
       </c>
       <c r="K164" t="n">
-        <v>0.7221935967090647</v>
+        <v>1.071123771640202</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -6717,10 +6717,10 @@
         <v>152.5431449027486</v>
       </c>
       <c r="J165" t="n">
-        <v>0.1250040183578073</v>
+        <v>0.09982219269762178</v>
       </c>
       <c r="K165" t="n">
-        <v>1.376604906248862</v>
+        <v>1.158478778823248</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
@@ -6755,10 +6755,10 @@
         <v>30.79702049824873</v>
       </c>
       <c r="J166" t="n">
-        <v>0.2376268749648791</v>
+        <v>0.4551760649062598</v>
       </c>
       <c r="K166" t="n">
-        <v>2.322895011579103</v>
+        <v>4.177716979355037</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
@@ -6793,10 +6793,10 @@
         <v>21.98558474150429</v>
       </c>
       <c r="J167" t="n">
-        <v>0.03328453558659518</v>
+        <v>0.03500129175058925</v>
       </c>
       <c r="K167" t="n">
-        <v>0.6059510476345559</v>
+        <v>0.6077327320283467</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -6831,10 +6831,10 @@
         <v>110.7931624221399</v>
       </c>
       <c r="J168" t="n">
-        <v>0.01463209234272062</v>
+        <v>0.05842476696610284</v>
       </c>
       <c r="K168" t="n">
-        <v>0.4492277765893772</v>
+        <v>0.8067485770516026</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
@@ -6869,10 +6869,10 @@
         <v>66.06452929222047</v>
       </c>
       <c r="J169" t="n">
-        <v>0.01448800643290511</v>
+        <v>0.06866028614637755</v>
       </c>
       <c r="K169" t="n">
-        <v>0.4480171247298561</v>
+        <v>0.8937139175987205</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -6907,10 +6907,10 @@
         <v>117.5517624535058</v>
       </c>
       <c r="J170" t="n">
-        <v>0.07827721026226581</v>
+        <v>0.09880651271794656</v>
       </c>
       <c r="K170" t="n">
-        <v>0.9839926294288522</v>
+        <v>1.149849128117344</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
@@ -6945,10 +6945,10 @@
         <v>29.07496111156684</v>
       </c>
       <c r="J171" t="n">
-        <v>0.04849567826565692</v>
+        <v>0.07239573359749001</v>
       </c>
       <c r="K171" t="n">
-        <v>0.7337595071392035</v>
+        <v>0.9254518738235401</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
@@ -6983,10 +6983,10 @@
         <v>88.92334507514417</v>
       </c>
       <c r="J172" t="n">
-        <v>0.08026600398008515</v>
+        <v>0.06352757732293363</v>
       </c>
       <c r="K172" t="n">
-        <v>1.000703054589541</v>
+        <v>0.8501042322570908</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -7021,10 +7021,10 @@
         <v>17.98506646030868</v>
       </c>
       <c r="J173" t="n">
-        <v>0.1192888531371482</v>
+        <v>0.08927890568206877</v>
       </c>
       <c r="K173" t="n">
-        <v>1.328584420340697</v>
+        <v>1.068898511360062</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -7059,10 +7059,10 @@
         <v>112.8911600102078</v>
       </c>
       <c r="J174" t="n">
-        <v>0.07247937694359428</v>
+        <v>0.1122005739429752</v>
       </c>
       <c r="K174" t="n">
-        <v>0.9352775420380717</v>
+        <v>1.263650790273215</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -7097,10 +7097,10 @@
         <v>65.08135250908313</v>
       </c>
       <c r="J175" t="n">
-        <v>0.07578486457847598</v>
+        <v>0.05748750157453216</v>
       </c>
       <c r="K175" t="n">
-        <v>0.9630512137101823</v>
+        <v>0.7987851701617936</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -7135,10 +7135,10 @@
         <v>30.4156101556041</v>
       </c>
       <c r="J176" t="n">
-        <v>0.02203114699731</v>
+        <v>0.02154834839029065</v>
       </c>
       <c r="K176" t="n">
-        <v>0.5113967928918455</v>
+        <v>0.49343078211416</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -7173,10 +7173,10 @@
         <v>71.17714603620465</v>
       </c>
       <c r="J177" t="n">
-        <v>0.04596685376984659</v>
+        <v>0.05504261455880002</v>
       </c>
       <c r="K177" t="n">
-        <v>0.7125115857971711</v>
+        <v>0.7780123663423135</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -7211,10 +7211,10 @@
         <v>118.0479636452094</v>
       </c>
       <c r="J178" t="n">
-        <v>0.05245052446400275</v>
+        <v>0.1102367770419093</v>
       </c>
       <c r="K178" t="n">
-        <v>0.7669892789487971</v>
+        <v>1.246965533447583</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>25.07744322705548</v>
       </c>
       <c r="J179" t="n">
-        <v>0.1807030746573469</v>
+        <v>0.1592507864894327</v>
       </c>
       <c r="K179" t="n">
-        <v>1.844604630642079</v>
+        <v>1.663409482025981</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>111.3542908689848</v>
       </c>
       <c r="J180" t="n">
-        <v>0.08286023361689078</v>
+        <v>0.0555925416060609</v>
       </c>
       <c r="K180" t="n">
-        <v>1.022500529011882</v>
+        <v>0.782684781302297</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -7325,10 +7325,10 @@
         <v>80.15669710625814</v>
       </c>
       <c r="J181" t="n">
-        <v>0.04640405119271134</v>
+        <v>0.07472311180616235</v>
       </c>
       <c r="K181" t="n">
-        <v>0.7161850461212703</v>
+        <v>0.9452262726531752</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -7363,10 +7363,10 @@
         <v>24.60206255100857</v>
       </c>
       <c r="J182" t="n">
-        <v>0.1125205172581969</v>
+        <v>0.04916788983121513</v>
       </c>
       <c r="K182" t="n">
-        <v>1.271714887239179</v>
+        <v>0.7280981971090063</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -7401,10 +7401,10 @@
         <v>107.2567912056681</v>
       </c>
       <c r="J183" t="n">
-        <v>0.08414595408283508</v>
+        <v>0.06748556581221346</v>
       </c>
       <c r="K183" t="n">
-        <v>1.033303527548746</v>
+        <v>0.8837329921460009</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -7439,10 +7439,10 @@
         <v>34.37877306064453</v>
       </c>
       <c r="J184" t="n">
-        <v>0.08427592156197586</v>
+        <v>0.0957951491969742</v>
       </c>
       <c r="K184" t="n">
-        <v>1.034395552233883</v>
+        <v>1.124263298077846</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -7477,10 +7477,10 @@
         <v>86.52179176185355</v>
       </c>
       <c r="J185" t="n">
-        <v>0.07503889119825849</v>
+        <v>0.06546121668062274</v>
       </c>
       <c r="K185" t="n">
-        <v>0.9567833276894753</v>
+        <v>0.8665332577197962</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
@@ -7515,10 +7515,10 @@
         <v>154.3038375761198</v>
       </c>
       <c r="J186" t="n">
-        <v>0.06261195703410159</v>
+        <v>0.08618529846035286</v>
       </c>
       <c r="K186" t="n">
-        <v>0.8523686005780906</v>
+        <v>1.042613903728823</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -7553,10 +7553,10 @@
         <v>54.00127165820856</v>
       </c>
       <c r="J187" t="n">
-        <v>0.1789352409340405</v>
+        <v>0.2998427506938663</v>
       </c>
       <c r="K187" t="n">
-        <v>1.829750775832922</v>
+        <v>2.857938829280708</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -7591,10 +7591,10 @@
         <v>68.27957939707672</v>
       </c>
       <c r="J188" t="n">
-        <v>0.04608123555230965</v>
+        <v>0.04819139553611359</v>
       </c>
       <c r="K188" t="n">
-        <v>0.7134726549108099</v>
+        <v>0.7198014847077947</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -7629,10 +7629,10 @@
         <v>169.4264043315576</v>
       </c>
       <c r="J189" t="n">
-        <v>0.03166102419572218</v>
+        <v>0.07774724694735378</v>
       </c>
       <c r="K189" t="n">
-        <v>0.5923098311767451</v>
+        <v>0.9709206158303193</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -7667,10 +7667,10 @@
         <v>76.53685059911122</v>
       </c>
       <c r="J190" t="n">
-        <v>0.5768892108710625</v>
+        <v>0.5961439547524904</v>
       </c>
       <c r="K190" t="n">
-        <v>5.173476156926179</v>
+        <v>5.375440351346904</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
@@ -7705,10 +7705,10 @@
         <v>32.80248524512291</v>
       </c>
       <c r="J191" t="n">
-        <v>0.03488246036040607</v>
+        <v>0.1088360188998311</v>
       </c>
       <c r="K191" t="n">
-        <v>0.6193772778694615</v>
+        <v>1.235064094282217</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
@@ -7743,10 +7743,10 @@
         <v>66.89067159300176</v>
       </c>
       <c r="J192" t="n">
-        <v>0.02784093741371864</v>
+        <v>0.05650205039677787</v>
       </c>
       <c r="K192" t="n">
-        <v>0.560212347306976</v>
+        <v>0.7904123562618288</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -7781,10 +7781,10 @@
         <v>19.99557039515501</v>
       </c>
       <c r="J193" t="n">
-        <v>0.07145507045355799</v>
+        <v>0.1200901997053985</v>
       </c>
       <c r="K193" t="n">
-        <v>0.9266710200091673</v>
+        <v>1.330684418869283</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -7819,10 +7819,10 @@
         <v>26.71725451259816</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>0.07099701708656853</v>
       </c>
       <c r="K194" t="n">
-        <v>0.3262846669815048</v>
+        <v>0.9135677812280631</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -7857,10 +7857,10 @@
         <v>120.3160937903825</v>
       </c>
       <c r="J195" t="n">
-        <v>0.05445220993209512</v>
+        <v>0.03886388964466847</v>
       </c>
       <c r="K195" t="n">
-        <v>0.7838080243571799</v>
+        <v>0.6405510126977366</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -7895,10 +7895,10 @@
         <v>85.37585600037754</v>
       </c>
       <c r="J196" t="n">
-        <v>0.005123249520869651</v>
+        <v>0.03003719150176765</v>
       </c>
       <c r="K196" t="n">
-        <v>0.3693317044550014</v>
+        <v>0.5655556171165053</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -7933,10 +7933,10 @@
         <v>74.20460834299267</v>
       </c>
       <c r="J197" t="n">
-        <v>0.1926737390003705</v>
+        <v>0.1561738403191838</v>
       </c>
       <c r="K197" t="n">
-        <v>1.945185645573656</v>
+        <v>1.637266433800687</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -7971,10 +7971,10 @@
         <v>17.19167943207936</v>
       </c>
       <c r="J198" t="n">
-        <v>0.09857101053671419</v>
+        <v>0.01339653198650794</v>
       </c>
       <c r="K198" t="n">
-        <v>1.154507061204088</v>
+        <v>0.4241694698986795</v>
       </c>
       <c r="L198" t="b">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>24.20915289716725</v>
       </c>
       <c r="J199" t="n">
-        <v>0.05821206009799694</v>
+        <v>0.09934708125295344</v>
       </c>
       <c r="K199" t="n">
-        <v>0.8153993826010069</v>
+        <v>1.154442029162025</v>
       </c>
       <c r="L199" t="b">
         <v>0</v>
@@ -8047,10 +8047,10 @@
         <v>90.54095026405273</v>
       </c>
       <c r="J200" t="n">
-        <v>0.08382399785235072</v>
+        <v>0.08431812051606248</v>
       </c>
       <c r="K200" t="n">
-        <v>1.030598357351193</v>
+        <v>1.026749562807044</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8085,10 +8085,10 @@
         <v>35.01823715625947</v>
       </c>
       <c r="J201" t="n">
-        <v>0.1171804769589287</v>
+        <v>0.1790320094459869</v>
       </c>
       <c r="K201" t="n">
-        <v>1.310869228452749</v>
+        <v>1.831479196962418</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -8123,10 +8123,10 @@
         <v>42.04427869408466</v>
       </c>
       <c r="J202" t="n">
-        <v>0.03107980092809004</v>
+        <v>0.04271607065279406</v>
       </c>
       <c r="K202" t="n">
-        <v>0.5874262236771864</v>
+        <v>0.6732807870570467</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -8161,10 +8161,10 @@
         <v>56.26443875030415</v>
       </c>
       <c r="J203" t="n">
-        <v>0.0738961345069343</v>
+        <v>0.04907206958061447</v>
       </c>
       <c r="K203" t="n">
-        <v>0.9471815525047735</v>
+        <v>0.7272840673537853</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -8199,10 +8199,10 @@
         <v>72.07264670031046</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1892086963993666</v>
+        <v>0.2350137228625572</v>
       </c>
       <c r="K204" t="n">
-        <v>1.916071346516959</v>
+        <v>2.307123733007588</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -8237,10 +8237,10 @@
         <v>32.16135634906986</v>
       </c>
       <c r="J205" t="n">
-        <v>0.3031003147237119</v>
+        <v>0.3426063350801419</v>
       </c>
       <c r="K205" t="n">
-        <v>2.873021958029055</v>
+        <v>3.221276498202751</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -8275,10 +8275,10 @@
         <v>23.46562779898933</v>
       </c>
       <c r="J206" t="n">
-        <v>0.1426693579266618</v>
+        <v>0.06332242309089525</v>
       </c>
       <c r="K206" t="n">
-        <v>1.525034244172938</v>
+        <v>0.8483611543203815</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>37.81260860881116</v>
       </c>
       <c r="J207" t="n">
-        <v>0.08566943963622733</v>
+        <v>0.08603314328054416</v>
       </c>
       <c r="K207" t="n">
-        <v>1.046104297731822</v>
+        <v>1.041321128365403</v>
       </c>
       <c r="L207" t="b">
         <v>0</v>
@@ -8351,10 +8351,10 @@
         <v>22.28084895273744</v>
       </c>
       <c r="J208" t="n">
-        <v>0.08158112374135083</v>
+        <v>0.05560765856531992</v>
       </c>
       <c r="K208" t="n">
-        <v>1.01175307458461</v>
+        <v>0.782813221441663</v>
       </c>
       <c r="L208" t="b">
         <v>0</v>
@@ -8389,10 +8389,10 @@
         <v>164.8543394967752</v>
       </c>
       <c r="J209" t="n">
-        <v>0.07301809911090786</v>
+        <v>0.1186666730574493</v>
       </c>
       <c r="K209" t="n">
-        <v>0.9398040428906427</v>
+        <v>1.318589528758054</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -8427,10 +8427,10 @@
         <v>35.79294933954147</v>
       </c>
       <c r="J210" t="n">
-        <v>0.106545115537924</v>
+        <v>0.1704051482388357</v>
       </c>
       <c r="K210" t="n">
-        <v>1.221507818322474</v>
+        <v>1.758181701298648</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8465,10 +8465,10 @@
         <v>37.92407027224739</v>
       </c>
       <c r="J211" t="n">
-        <v>0.05889553645829967</v>
+        <v>0.04017989525064525</v>
       </c>
       <c r="K211" t="n">
-        <v>0.8211421504233335</v>
+        <v>0.6517323581351271</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -8503,10 +8503,10 @@
         <v>219.3877118778974</v>
       </c>
       <c r="J212" t="n">
-        <v>0.05398023353131531</v>
+        <v>0.0766931789741136</v>
       </c>
       <c r="K212" t="n">
-        <v>0.7798423409118954</v>
+        <v>0.961964804343072</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -8541,10 +8541,10 @@
         <v>12.7543992486696</v>
       </c>
       <c r="J213" t="n">
-        <v>0.4845731528077507</v>
+        <v>0.4735890021319494</v>
       </c>
       <c r="K213" t="n">
-        <v>4.397809698622912</v>
+        <v>4.334161154594405</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -8579,10 +8579,10 @@
         <v>176.1972992281623</v>
       </c>
       <c r="J214" t="n">
-        <v>0.1752465126739472</v>
+        <v>0.1766314331967276</v>
       </c>
       <c r="K214" t="n">
-        <v>1.798757004595556</v>
+        <v>1.811082876331367</v>
       </c>
       <c r="L214" t="b">
         <v>0</v>
@@ -8617,10 +8617,10 @@
         <v>111.5272779161666</v>
       </c>
       <c r="J215" t="n">
-        <v>0.124287119701094</v>
+        <v>0.1261322403022037</v>
       </c>
       <c r="K215" t="n">
-        <v>1.37058131453924</v>
+        <v>1.382020175155421</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -8655,10 +8655,10 @@
         <v>33.04623177182928</v>
       </c>
       <c r="J216" t="n">
-        <v>0.08714228478168851</v>
+        <v>0.2386957138110447</v>
       </c>
       <c r="K216" t="n">
-        <v>1.058479572430245</v>
+        <v>2.338407499965272</v>
       </c>
       <c r="L216" t="b">
         <v>0</v>
@@ -8693,10 +8693,10 @@
         <v>109.7568098953646</v>
       </c>
       <c r="J217" t="n">
-        <v>0.01788483971643377</v>
+        <v>0.06425609578644706</v>
       </c>
       <c r="K217" t="n">
-        <v>0.4765583091971818</v>
+        <v>0.8562940361310754</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -8731,10 +8731,10 @@
         <v>34.12132924759686</v>
       </c>
       <c r="J218" t="n">
-        <v>0.00847706490663229</v>
+        <v>0.09087458207358685</v>
       </c>
       <c r="K218" t="n">
-        <v>0.397511439992381</v>
+        <v>1.082456059184191</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -8769,10 +8769,10 @@
         <v>102.4886234060206</v>
       </c>
       <c r="J219" t="n">
-        <v>0.04501157437732306</v>
+        <v>0.05066330000927348</v>
       </c>
       <c r="K219" t="n">
-        <v>0.7044850495841468</v>
+        <v>0.7408038403794612</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -8807,10 +8807,10 @@
         <v>125.0961964683226</v>
       </c>
       <c r="J220" t="n">
-        <v>0.1551812933841095</v>
+        <v>0.2805782405941323</v>
       </c>
       <c r="K220" t="n">
-        <v>1.63016317695451</v>
+        <v>2.694259327362976</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -8845,10 +8845,10 @@
         <v>110.9141993884227</v>
       </c>
       <c r="J221" t="n">
-        <v>0.2274335635253507</v>
+        <v>0.1244370980328358</v>
       </c>
       <c r="K221" t="n">
-        <v>2.237247834386392</v>
+        <v>1.367617522770626</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -8883,10 +8883,10 @@
         <v>26.65908369415094</v>
       </c>
       <c r="J222" t="n">
-        <v>0.09182019087623768</v>
+        <v>0.05435585307608275</v>
       </c>
       <c r="K222" t="n">
-        <v>1.097784704481548</v>
+        <v>0.7721773476034255</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>59.77945856103065</v>
       </c>
       <c r="J223" t="n">
-        <v>0.005425180712269826</v>
+        <v>0.01807578233767812</v>
       </c>
       <c r="K223" t="n">
-        <v>0.3718686184307264</v>
+        <v>0.4639263784763072</v>
       </c>
       <c r="L223" t="b">
         <v>0</v>
@@ -8959,10 +8959,10 @@
         <v>31.42293193182723</v>
       </c>
       <c r="J224" t="n">
-        <v>0.1179015671269088</v>
+        <v>0.1526906356543331</v>
       </c>
       <c r="K224" t="n">
-        <v>1.316928038463146</v>
+        <v>1.607671639971585</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -8997,10 +8997,10 @@
         <v>20.79199558107355</v>
       </c>
       <c r="J225" t="n">
-        <v>0.09801702788924364</v>
+        <v>0.05306503616241371</v>
       </c>
       <c r="K225" t="n">
-        <v>1.149852337344125</v>
+        <v>0.7612100160490534</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -9035,10 +9035,10 @@
         <v>103.7854021329008</v>
       </c>
       <c r="J226" t="n">
-        <v>0.03316891283218969</v>
+        <v>0.07338447642641165</v>
       </c>
       <c r="K226" t="n">
-        <v>0.6049795515125327</v>
+        <v>0.9338526549970441</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -9073,10 +9073,10 @@
         <v>25.10340625405449</v>
       </c>
       <c r="J227" t="n">
-        <v>0.06188092305022199</v>
+        <v>0.04766134646333849</v>
       </c>
       <c r="K227" t="n">
-        <v>0.8462262397248321</v>
+        <v>0.7152979615050437</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -9111,10 +9111,10 @@
         <v>120.488438972897</v>
       </c>
       <c r="J228" t="n">
-        <v>0.02852233248816158</v>
+        <v>0.05641448954099218</v>
       </c>
       <c r="K228" t="n">
-        <v>0.5659376275581753</v>
+        <v>0.7896684018509306</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -9149,10 +9149,10 @@
         <v>116.0246176387348</v>
       </c>
       <c r="J229" t="n">
-        <v>0.1151438149310803</v>
+        <v>0.135911067945694</v>
       </c>
       <c r="K229" t="n">
-        <v>1.293756599782897</v>
+        <v>1.465105269442244</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -9187,10 +9187,10 @@
         <v>66.81089354927215</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1569294494478004</v>
+        <v>0.1882987675053834</v>
       </c>
       <c r="K230" t="n">
-        <v>1.644851694325501</v>
+        <v>1.910213529457854</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -9225,10 +9225,10 @@
         <v>76.02477425267368</v>
       </c>
       <c r="J231" t="n">
-        <v>0.04796539800346465</v>
+        <v>0.06959217058591986</v>
       </c>
       <c r="K231" t="n">
-        <v>0.7293039376368671</v>
+        <v>0.9016316056229428</v>
       </c>
       <c r="L231" t="b">
         <v>0</v>
@@ -9263,10 +9263,10 @@
         <v>73.20213592171007</v>
       </c>
       <c r="J232" t="n">
-        <v>0.02250033258473124</v>
+        <v>0.0489724400855982</v>
       </c>
       <c r="K232" t="n">
-        <v>0.5153390271089129</v>
+        <v>0.7264375726318248</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -9301,10 +9301,10 @@
         <v>31.84387277039228</v>
       </c>
       <c r="J233" t="n">
-        <v>0.131209058708758</v>
+        <v>0.08162145743783954</v>
       </c>
       <c r="K233" t="n">
-        <v>1.428741465950641</v>
+        <v>1.003837562076251</v>
       </c>
       <c r="L233" t="b">
         <v>0</v>
@@ -9339,10 +9339,10 @@
         <v>113.2643780857509</v>
       </c>
       <c r="J234" t="n">
-        <v>0.08708979892481451</v>
+        <v>0.05545174925563268</v>
       </c>
       <c r="K234" t="n">
-        <v>1.058038570945058</v>
+        <v>0.7814885493881392</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -9377,10 +9377,10 @@
         <v>84.1860695441385</v>
       </c>
       <c r="J235" t="n">
-        <v>0.04156699556365728</v>
+        <v>0.1648450393341445</v>
       </c>
       <c r="K235" t="n">
-        <v>0.6755426932401377</v>
+        <v>1.710940642407627</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -9415,10 +9415,10 @@
         <v>32.21266308477222</v>
       </c>
       <c r="J236" t="n">
-        <v>0.2372235942587422</v>
+        <v>0.1141760920962388</v>
       </c>
       <c r="K236" t="n">
-        <v>2.319506529406081</v>
+        <v>1.280435635861378</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9453,10 +9453,10 @@
         <v>18.2660113847979</v>
       </c>
       <c r="J237" t="n">
-        <v>0.08128591705039456</v>
+        <v>0.04087412558706296</v>
       </c>
       <c r="K237" t="n">
-        <v>1.00927266182387</v>
+        <v>0.6576308354435431</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -9491,10 +9491,10 @@
         <v>115.2138444139629</v>
       </c>
       <c r="J238" t="n">
-        <v>0.09262859359574264</v>
+        <v>0.1334350441755801</v>
       </c>
       <c r="K238" t="n">
-        <v>1.104577140028255</v>
+        <v>1.444067914465109</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -9529,10 +9529,10 @@
         <v>91.09277544211677</v>
       </c>
       <c r="J239" t="n">
-        <v>0.06570628981906115</v>
+        <v>0.0287435052564357</v>
       </c>
       <c r="K239" t="n">
-        <v>0.8783680875847302</v>
+        <v>0.5545639064953938</v>
       </c>
       <c r="L239" t="b">
         <v>0</v>
@@ -9567,10 +9567,10 @@
         <v>175.2617340414726</v>
       </c>
       <c r="J240" t="n">
-        <v>0.09073867677966112</v>
+        <v>0.08889083017108267</v>
       </c>
       <c r="K240" t="n">
-        <v>1.088697507448922</v>
+        <v>1.065601256147455</v>
       </c>
       <c r="L240" t="b">
         <v>0</v>
@@ -9605,10 +9605,10 @@
         <v>29.34115344059063</v>
       </c>
       <c r="J241" t="n">
-        <v>0.4522366401625657</v>
+        <v>0.5087902415574903</v>
       </c>
       <c r="K241" t="n">
-        <v>4.126108883363149</v>
+        <v>4.633245912329248</v>
       </c>
       <c r="L241" t="b">
         <v>0</v>
@@ -9643,10 +9643,10 @@
         <v>25.60124944369328</v>
       </c>
       <c r="J242" t="n">
-        <v>0.005538974581210054</v>
+        <v>0.00683278290360227</v>
       </c>
       <c r="K242" t="n">
-        <v>0.3728247477233892</v>
+        <v>0.3684010555948137</v>
       </c>
       <c r="L242" t="b">
         <v>0</v>
@@ -9681,10 +9681,10 @@
         <v>17.57267989449169</v>
       </c>
       <c r="J243" t="n">
-        <v>0.02154583533143141</v>
+        <v>0.01491421346074547</v>
       </c>
       <c r="K243" t="n">
-        <v>0.5073190626578797</v>
+        <v>0.4370643396091944</v>
       </c>
       <c r="L243" t="b">
         <v>0</v>
@@ -9719,10 +9719,10 @@
         <v>91.26914479345537</v>
       </c>
       <c r="J244" t="n">
-        <v>0.06805178487156018</v>
+        <v>0.1043837570640018</v>
       </c>
       <c r="K244" t="n">
-        <v>0.8980756214472791</v>
+        <v>1.197235777033395</v>
       </c>
       <c r="L244" t="b">
         <v>0</v>
@@ -9757,10 +9757,10 @@
         <v>19.71057576972457</v>
       </c>
       <c r="J245" t="n">
-        <v>0.1054216498801602</v>
+        <v>0.1117054486364178</v>
       </c>
       <c r="K245" t="n">
-        <v>1.212068132031001</v>
+        <v>1.259443994297371</v>
       </c>
       <c r="L245" t="b">
         <v>0</v>
@@ -9795,10 +9795,10 @@
         <v>102.540191425305</v>
       </c>
       <c r="J246" t="n">
-        <v>0.06958785463712024</v>
+        <v>0.09311644003208099</v>
       </c>
       <c r="K246" t="n">
-        <v>0.910982127853148</v>
+        <v>1.101503841459313</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -9833,10 +9833,10 @@
         <v>33.94189387693926</v>
       </c>
       <c r="J247" t="n">
-        <v>0.1848432545526971</v>
+        <v>0.2168655576265526</v>
       </c>
       <c r="K247" t="n">
-        <v>1.87939163025554</v>
+        <v>2.152929173624997</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -9871,10 +9871,10 @@
         <v>24.15659066424117</v>
       </c>
       <c r="J248" t="n">
-        <v>0.01856524828233408</v>
+        <v>0.01215869421455872</v>
       </c>
       <c r="K248" t="n">
-        <v>0.482275300515736</v>
+        <v>0.4136522717494049</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -9909,10 +9909,10 @@
         <v>176.3311782301147</v>
       </c>
       <c r="J249" t="n">
-        <v>0.08778792017911416</v>
+        <v>0.07716677705132796</v>
       </c>
       <c r="K249" t="n">
-        <v>1.063904389440227</v>
+        <v>0.9659886957883423</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -9947,10 +9947,10 @@
         <v>88.65975788362667</v>
       </c>
       <c r="J250" t="n">
-        <v>0.1518283578774718</v>
+        <v>0.301551524296655</v>
       </c>
       <c r="K250" t="n">
-        <v>1.601990834418292</v>
+        <v>2.872457299293526</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -9985,10 +9985,10 @@
         <v>30.60042005515762</v>
       </c>
       <c r="J251" t="n">
-        <v>0.2360360663919476</v>
+        <v>0.2203998333888078</v>
       </c>
       <c r="K251" t="n">
-        <v>2.309528573740542</v>
+        <v>2.182957889300141</v>
       </c>
       <c r="L251" t="b">
         <v>0</v>
@@ -10023,10 +10023,10 @@
         <v>122.0366852371933</v>
       </c>
       <c r="J252" t="n">
-        <v>0.08097582552580723</v>
+        <v>0.04331874448683257</v>
       </c>
       <c r="K252" t="n">
-        <v>1.006667182347465</v>
+        <v>0.6784013612353454</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -10061,10 +10061,10 @@
         <v>62.05784407906614</v>
       </c>
       <c r="J253" t="n">
-        <v>0.02098543761676516</v>
+        <v>0.0227917251131098</v>
       </c>
       <c r="K253" t="n">
-        <v>0.5026104375313789</v>
+        <v>0.5039950415546298</v>
       </c>
       <c r="L253" t="b">
         <v>0</v>
@@ -10099,10 +10099,10 @@
         <v>27.50087509078405</v>
       </c>
       <c r="J254" t="n">
-        <v>0.1311562327814016</v>
+        <v>0.1224659047204886</v>
       </c>
       <c r="K254" t="n">
-        <v>1.428297607094027</v>
+        <v>1.350869422877185</v>
       </c>
       <c r="L254" t="b">
         <v>0</v>
@@ -10137,10 +10137,10 @@
         <v>115.3837003660451</v>
       </c>
       <c r="J255" t="n">
-        <v>0.04161845027181647</v>
+        <v>0.05880654477364306</v>
       </c>
       <c r="K255" t="n">
-        <v>0.675975030712926</v>
+        <v>0.8099923242872145</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -10175,10 +10175,10 @@
         <v>124.0365659198359</v>
       </c>
       <c r="J256" t="n">
-        <v>0.09463644331064791</v>
+        <v>0.1326074370146456</v>
       </c>
       <c r="K256" t="n">
-        <v>1.121447679237129</v>
+        <v>1.437036210716402</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -10213,10 +10213,10 @@
         <v>41.49054525958993</v>
       </c>
       <c r="J257" t="n">
-        <v>0.003138030103174275</v>
+        <v>0.03837536771551034</v>
       </c>
       <c r="K257" t="n">
-        <v>0.3526513116069599</v>
+        <v>0.6364003218352892</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -10251,10 +10251,10 @@
         <v>155.5627114501318</v>
       </c>
       <c r="J258" t="n">
-        <v>0.005976250200524738</v>
+        <v>0.02478959964246846</v>
       </c>
       <c r="K258" t="n">
-        <v>0.3764988650768791</v>
+        <v>0.5209698364581381</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -10289,10 +10289,10 @@
         <v>33.30992350911941</v>
       </c>
       <c r="J259" t="n">
-        <v>0.2009179186594785</v>
+        <v>0.3081133150214122</v>
       </c>
       <c r="K259" t="n">
-        <v>2.01445564877733</v>
+        <v>2.92820907455053</v>
       </c>
       <c r="L259" t="b">
         <v>0</v>
@@ -10327,10 +10327,10 @@
         <v>34.22660391073647</v>
       </c>
       <c r="J260" t="n">
-        <v>0.03680474595045725</v>
+        <v>0.05647541878652244</v>
       </c>
       <c r="K260" t="n">
-        <v>0.6355288823331163</v>
+        <v>0.7901860827319385</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -10365,10 +10365,10 @@
         <v>102.8371771209023</v>
       </c>
       <c r="J261" t="n">
-        <v>0.01170962271083647</v>
+        <v>0.05194998621132913</v>
       </c>
       <c r="K261" t="n">
-        <v>0.4246723339457173</v>
+        <v>0.7517360756445457</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -10403,10 +10403,10 @@
         <v>28.176727544604</v>
       </c>
       <c r="J262" t="n">
-        <v>0.07220495832002026</v>
+        <v>0.1074371477788559</v>
       </c>
       <c r="K262" t="n">
-        <v>0.9329717966855768</v>
+        <v>1.22317868805372</v>
       </c>
       <c r="L262" t="b">
         <v>0</v>
@@ -10441,10 +10441,10 @@
         <v>23.67788597379845</v>
       </c>
       <c r="J263" t="n">
-        <v>0.0292963166012499</v>
+        <v>0.03746237373633814</v>
       </c>
       <c r="K263" t="n">
-        <v>0.572440867930186</v>
+        <v>0.6286431352267983</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -10479,10 +10479,10 @@
         <v>65.11104394125033</v>
       </c>
       <c r="J264" t="n">
-        <v>0.05797453190606731</v>
+        <v>0.09527742027969863</v>
       </c>
       <c r="K264" t="n">
-        <v>0.8134036014200678</v>
+        <v>1.119864452175752</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -10517,10 +10517,10 @@
         <v>113.0747159477867</v>
       </c>
       <c r="J265" t="n">
-        <v>0.1000329367951576</v>
+        <v>0.07869092438910395</v>
       </c>
       <c r="K265" t="n">
-        <v>1.166790592227581</v>
+        <v>0.9789385022357877</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -10555,10 +10555,10 @@
         <v>35.53493989199207</v>
       </c>
       <c r="J266" t="n">
-        <v>0.008537826534557457</v>
+        <v>0.02635438979200709</v>
       </c>
       <c r="K266" t="n">
-        <v>0.3980219769208657</v>
+        <v>0.5342649615849273</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -10593,10 +10593,10 @@
         <v>31.63510721690351</v>
       </c>
       <c r="J267" t="n">
-        <v>0.002404349880319978</v>
+        <v>0.0374361368178484</v>
       </c>
       <c r="K267" t="n">
-        <v>0.3464867162816456</v>
+        <v>0.628420215166645</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -10631,10 +10631,10 @@
         <v>125.8710275729972</v>
       </c>
       <c r="J268" t="n">
-        <v>0.04249777330387539</v>
+        <v>0.0381389510802899</v>
       </c>
       <c r="K268" t="n">
-        <v>0.6833633594207427</v>
+        <v>0.6343916251750776</v>
       </c>
       <c r="L268" t="b">
         <v>0</v>
@@ -10669,10 +10669,10 @@
         <v>33.91860427172316</v>
       </c>
       <c r="J269" t="n">
-        <v>0.1015963503833593</v>
+        <v>0.1096023664226732</v>
       </c>
       <c r="K269" t="n">
-        <v>1.179926849410399</v>
+        <v>1.241575309993662</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -10707,10 +10707,10 @@
         <v>78.73700941940552</v>
       </c>
       <c r="J270" t="n">
-        <v>0.005274114338737673</v>
+        <v>0.05256669416470502</v>
       </c>
       <c r="K270" t="n">
-        <v>0.3705993146781112</v>
+        <v>0.7569758896919667</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -10745,10 +10745,10 @@
         <v>25.37746137283139</v>
       </c>
       <c r="J271" t="n">
-        <v>0.1406248659447767</v>
+        <v>0.07033836463075986</v>
       </c>
       <c r="K271" t="n">
-        <v>1.507855825944436</v>
+        <v>0.9079715887816671</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -10783,10 +10783,10 @@
         <v>101.5506041292736</v>
       </c>
       <c r="J272" t="n">
-        <v>0.007953788032691781</v>
+        <v>0.04213714412405244</v>
       </c>
       <c r="K272" t="n">
-        <v>0.3931147150017724</v>
+        <v>0.6683619801223872</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -10821,10 +10821,10 @@
         <v>31.31571995717643</v>
       </c>
       <c r="J273" t="n">
-        <v>0.1052963376008737</v>
+        <v>0.09022456995516549</v>
       </c>
       <c r="K273" t="n">
-        <v>1.211015221693459</v>
+        <v>1.076933278732839</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -10859,10 +10859,10 @@
         <v>24.23961852732564</v>
       </c>
       <c r="J274" t="n">
-        <v>0.05922807242253411</v>
+        <v>0.03053671279515805</v>
       </c>
       <c r="K274" t="n">
-        <v>0.8239362146310935</v>
+        <v>0.5697997632731506</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
@@ -10897,10 +10897,10 @@
         <v>25.9421836907767</v>
       </c>
       <c r="J275" t="n">
-        <v>0.01831521367238281</v>
+        <v>0.06638378666712091</v>
       </c>
       <c r="K275" t="n">
-        <v>0.480174436761121</v>
+        <v>0.8743718061745714</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -10935,10 +10935,10 @@
         <v>30.32516965728715</v>
       </c>
       <c r="J276" t="n">
-        <v>0.04075293505264262</v>
+        <v>0.06294207940093695</v>
       </c>
       <c r="K276" t="n">
-        <v>0.6687027192781837</v>
+        <v>0.8451295919599773</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -10973,10 +10973,10 @@
         <v>34.89829636164806</v>
       </c>
       <c r="J277" t="n">
-        <v>0.02741087902466383</v>
+        <v>0.02070842075020438</v>
       </c>
       <c r="K277" t="n">
-        <v>0.5565988712281666</v>
+        <v>0.4862943983149086</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -11011,10 +11011,10 @@
         <v>124.9534114835613</v>
       </c>
       <c r="J278" t="n">
-        <v>0.1053219035749965</v>
+        <v>0.09567031024921104</v>
       </c>
       <c r="K278" t="n">
-        <v>1.211230034468364</v>
+        <v>1.123202613083314</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11049,10 +11049,10 @@
         <v>107.0527743984536</v>
       </c>
       <c r="J279" t="n">
-        <v>0.06033351881065178</v>
+        <v>0.1105840887524478</v>
       </c>
       <c r="K279" t="n">
-        <v>0.8332244977608532</v>
+        <v>1.249916442009329</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -11087,10 +11087,10 @@
         <v>28.12853563921645</v>
       </c>
       <c r="J280" t="n">
-        <v>0.164772561929052</v>
+        <v>0.03065752914771049</v>
       </c>
       <c r="K280" t="n">
-        <v>1.710751814066688</v>
+        <v>0.5708262705815079</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -11125,10 +11125,10 @@
         <v>37.98242200304831</v>
       </c>
       <c r="J281" t="n">
-        <v>0.05947336727404053</v>
+        <v>0.03275489780998874</v>
       </c>
       <c r="K281" t="n">
-        <v>0.8259972535521609</v>
+        <v>0.5886464101128166</v>
       </c>
       <c r="L281" t="b">
         <v>0</v>
@@ -11163,10 +11163,10 @@
         <v>60.92003271969919</v>
       </c>
       <c r="J282" t="n">
-        <v>0.04990418449128867</v>
+        <v>0.08406835461491839</v>
       </c>
       <c r="K282" t="n">
-        <v>0.7455941874586838</v>
+        <v>1.024627445084681</v>
       </c>
       <c r="L282" t="b">
         <v>0</v>
@@ -11201,10 +11201,10 @@
         <v>88.08224431625337</v>
       </c>
       <c r="J283" t="n">
-        <v>0.07788026865478934</v>
+        <v>0.0468432274559375</v>
       </c>
       <c r="K283" t="n">
-        <v>0.9806574102125668</v>
+        <v>0.7083468731592948</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11239,10 +11239,10 @@
         <v>73.58932195288999</v>
       </c>
       <c r="J284" t="n">
-        <v>0.07549449879769417</v>
+        <v>0.02176988335048191</v>
       </c>
       <c r="K284" t="n">
-        <v>0.9606114756893385</v>
+        <v>0.4953130377102662</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -11277,10 +11277,10 @@
         <v>84.90624866120926</v>
       </c>
       <c r="J285" t="n">
-        <v>0.1720528945033142</v>
+        <v>0.1172086870829781</v>
       </c>
       <c r="K285" t="n">
-        <v>1.771923292806334</v>
+        <v>1.306201857497845</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -11315,10 +11315,10 @@
         <v>40.04217123414976</v>
       </c>
       <c r="J286" t="n">
-        <v>0.1011869733177096</v>
+        <v>0.09205860500108673</v>
       </c>
       <c r="K286" t="n">
-        <v>1.176487143845791</v>
+        <v>1.092516023441213</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -11353,10 +11353,10 @@
         <v>118.3746420990379</v>
       </c>
       <c r="J287" t="n">
-        <v>0.05441508086489608</v>
+        <v>0.09892993343537894</v>
       </c>
       <c r="K287" t="n">
-        <v>0.7834960551000585</v>
+        <v>1.150897763221537</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -11391,10 +11391,10 @@
         <v>104.1345270930894</v>
       </c>
       <c r="J288" t="n">
-        <v>0.04327740978274052</v>
+        <v>0.08131587759602311</v>
       </c>
       <c r="K288" t="n">
-        <v>0.6899140926194089</v>
+        <v>1.001241225286701</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -11429,10 +11429,10 @@
         <v>34.13918459202164</v>
       </c>
       <c r="J289" t="n">
-        <v>0.1543499839945274</v>
+        <v>0.1204703782246339</v>
       </c>
       <c r="K289" t="n">
-        <v>1.623178272881491</v>
+        <v>1.333914577868713</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -11467,10 +11467,10 @@
         <v>183.1021287898644</v>
       </c>
       <c r="J290" t="n">
-        <v>0.05664844391622552</v>
+        <v>0.05792030394179329</v>
       </c>
       <c r="K290" t="n">
-        <v>0.8022614231678979</v>
+        <v>0.8024624438394199</v>
       </c>
       <c r="L290" t="b">
         <v>0</v>
@@ -11505,10 +11505,10 @@
         <v>38.69908310860082</v>
       </c>
       <c r="J291" t="n">
-        <v>0.5987320156534228</v>
+        <v>0.6974869501042115</v>
       </c>
       <c r="K291" t="n">
-        <v>5.357005776586969</v>
+        <v>6.236493703658719</v>
       </c>
       <c r="L291" t="b">
         <v>0</v>
@@ -11543,10 +11543,10 @@
         <v>115.9989429726532</v>
       </c>
       <c r="J292" t="n">
-        <v>0.1223476330299435</v>
+        <v>0.1088527436062234</v>
       </c>
       <c r="K292" t="n">
-        <v>1.354285181572796</v>
+        <v>1.235206194527582</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -11581,10 +11581,10 @@
         <v>110.5192340102021</v>
       </c>
       <c r="J293" t="n">
-        <v>0.1655603165318297</v>
+        <v>0.2477290197375357</v>
       </c>
       <c r="K293" t="n">
-        <v>1.717370758111392</v>
+        <v>2.415158323477725</v>
       </c>
       <c r="L293" t="b">
         <v>0</v>
@@ -11619,10 +11619,10 @@
         <v>191.8713116238582</v>
       </c>
       <c r="J294" t="n">
-        <v>0.2578827647786477</v>
+        <v>0.2748904899551413</v>
       </c>
       <c r="K294" t="n">
-        <v>2.493090908601177</v>
+        <v>2.645933769806484</v>
       </c>
       <c r="L294" t="b">
         <v>0</v>
@@ -11657,10 +11657,10 @@
         <v>30.35291596184192</v>
       </c>
       <c r="J295" t="n">
-        <v>0.875275433640772</v>
+        <v>0.9369945276023238</v>
       </c>
       <c r="K295" t="n">
-        <v>7.680604271772019</v>
+        <v>8.271452328999262</v>
       </c>
       <c r="L295" t="b">
         <v>0</v>
@@ -11695,10 +11695,10 @@
         <v>65.32802165221348</v>
       </c>
       <c r="J296" t="n">
-        <v>0.04808307735898103</v>
+        <v>0.06164180074221275</v>
       </c>
       <c r="K296" t="n">
-        <v>0.7302927139215543</v>
+        <v>0.8340818693803529</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -11733,10 +11733,10 @@
         <v>28.33424565055418</v>
       </c>
       <c r="J297" t="n">
-        <v>0.2918389077128905</v>
+        <v>0.3264070630304559</v>
       </c>
       <c r="K297" t="n">
-        <v>2.778400330168767</v>
+        <v>3.083640567322834</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>106.6254838348628</v>
       </c>
       <c r="J298" t="n">
-        <v>0.0385419100299965</v>
+        <v>0.02585541404958674</v>
       </c>
       <c r="K298" t="n">
-        <v>0.6501250418457306</v>
+        <v>0.5300254506622217</v>
       </c>
       <c r="L298" t="b">
         <v>0</v>
@@ -11809,10 +11809,10 @@
         <v>22.81281055201933</v>
       </c>
       <c r="J299" t="n">
-        <v>0.1984680085910592</v>
+        <v>0.1853039063736686</v>
       </c>
       <c r="K299" t="n">
-        <v>1.993870789482005</v>
+        <v>1.884767910762437</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -11847,10 +11847,10 @@
         <v>113.2173817835335</v>
       </c>
       <c r="J300" t="n">
-        <v>0.02357564973346052</v>
+        <v>0.0938953079150034</v>
       </c>
       <c r="K300" t="n">
-        <v>0.5243741555774137</v>
+        <v>1.108121435495002</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -11885,10 +11885,10 @@
         <v>105.9923178297015</v>
       </c>
       <c r="J301" t="n">
-        <v>0.1525930167560763</v>
+        <v>0.1252532945697668</v>
       </c>
       <c r="K301" t="n">
-        <v>1.608415721449002</v>
+        <v>1.374552276986551</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -11923,10 +11923,10 @@
         <v>63.90708454806359</v>
       </c>
       <c r="J302" t="n">
-        <v>0.198408129884049</v>
+        <v>0.2817275899650334</v>
       </c>
       <c r="K302" t="n">
-        <v>1.99336767111269</v>
+        <v>2.704024690280828</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -11961,10 +11961,10 @@
         <v>63.84805760244783</v>
       </c>
       <c r="J303" t="n">
-        <v>0.197970297389403</v>
+        <v>0.1915384376197787</v>
       </c>
       <c r="K303" t="n">
-        <v>1.989688874730167</v>
+        <v>1.937739149780238</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -11999,10 +11999,10 @@
         <v>34.46188169694703</v>
       </c>
       <c r="J304" t="n">
-        <v>0.270084394554197</v>
+        <v>0.2230942698998958</v>
       </c>
       <c r="K304" t="n">
-        <v>2.595612562494123</v>
+        <v>2.205850972166023</v>
       </c>
       <c r="L304" t="b">
         <v>0</v>
@@ -12037,10 +12037,10 @@
         <v>12.4308486752652</v>
       </c>
       <c r="J305" t="n">
-        <v>0.08219181633155508</v>
+        <v>0.1170563116334886</v>
       </c>
       <c r="K305" t="n">
-        <v>1.016884291931769</v>
+        <v>1.304907210629182</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>36.96798662457154</v>
       </c>
       <c r="J306" t="n">
-        <v>0.0635010348292353</v>
+        <v>0.1248804055206415</v>
       </c>
       <c r="K306" t="n">
-        <v>0.859838891651768</v>
+        <v>1.371384052437085</v>
       </c>
       <c r="L306" t="b">
         <v>0</v>
@@ -12113,10 +12113,10 @@
         <v>158.4106251319052</v>
       </c>
       <c r="J307" t="n">
-        <v>0.09528083908997689</v>
+        <v>0.08799395603444558</v>
       </c>
       <c r="K307" t="n">
-        <v>1.126862080614134</v>
+        <v>1.057981030602779</v>
       </c>
       <c r="L307" t="b">
         <v>0</v>
@@ -12151,10 +12151,10 @@
         <v>57.21718162347668</v>
       </c>
       <c r="J308" t="n">
-        <v>0.2548835684483932</v>
+        <v>0.3013829050172321</v>
       </c>
       <c r="K308" t="n">
-        <v>2.467890785848435</v>
+        <v>2.871024637911182</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>30.79066408123221</v>
       </c>
       <c r="J309" t="n">
-        <v>0.02107044971823092</v>
+        <v>0.05541528821195936</v>
       </c>
       <c r="K309" t="n">
-        <v>0.5033247340150052</v>
+        <v>0.7811787607956988</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -12227,10 +12227,10 @@
         <v>33.38104492461101</v>
       </c>
       <c r="J310" t="n">
-        <v>0.04319609335028518</v>
+        <v>0.03313812601943097</v>
       </c>
       <c r="K310" t="n">
-        <v>0.6892308482252296</v>
+        <v>0.5919024805821713</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -12265,10 +12265,10 @@
         <v>17.20975373591337</v>
       </c>
       <c r="J311" t="n">
-        <v>0.02580889782060314</v>
+        <v>0.04256358494838714</v>
       </c>
       <c r="K311" t="n">
-        <v>0.5431385576826082</v>
+        <v>0.6719852034155378</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -12303,10 +12303,10 @@
         <v>31.99637712838566</v>
       </c>
       <c r="J312" t="n">
-        <v>0.03109571878190467</v>
+        <v>0.07776189960998235</v>
       </c>
       <c r="K312" t="n">
-        <v>0.5875599701298753</v>
+        <v>0.9710451111073025</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12341,10 +12341,10 @@
         <v>62.93117309211515</v>
       </c>
       <c r="J313" t="n">
-        <v>0.03333720538959024</v>
+        <v>0.06733850791052434</v>
       </c>
       <c r="K313" t="n">
-        <v>0.6063935946887281</v>
+        <v>0.882483525433537</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12379,10 +12379,10 @@
         <v>108.0622534196724</v>
       </c>
       <c r="J314" t="n">
-        <v>0.1291673958928032</v>
+        <v>0.2855012375508765</v>
       </c>
       <c r="K314" t="n">
-        <v>1.411586819199856</v>
+        <v>2.736087211158138</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12417,10 +12417,10 @@
         <v>31.37177704380071</v>
       </c>
       <c r="J315" t="n">
-        <v>0.1215684553487628</v>
+        <v>0.1977481122088472</v>
       </c>
       <c r="K315" t="n">
-        <v>1.347738303326155</v>
+        <v>1.990499196028388</v>
       </c>
       <c r="L315" t="b">
         <v>0</v>
@@ -12455,10 +12455,10 @@
         <v>222.6207096485158</v>
       </c>
       <c r="J316" t="n">
-        <v>0.02823018994852813</v>
+        <v>0.01570068663906206</v>
       </c>
       <c r="K316" t="n">
-        <v>0.5634829606909897</v>
+        <v>0.4437465514812883</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -12493,10 +12493,10 @@
         <v>185.5737293923422</v>
       </c>
       <c r="J317" t="n">
-        <v>0.4830048463560693</v>
+        <v>0.5283506537815487</v>
       </c>
       <c r="K317" t="n">
-        <v>4.384632330173367</v>
+        <v>4.799439525017255</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -12531,10 +12531,10 @@
         <v>63.38512461399922</v>
       </c>
       <c r="J318" t="n">
-        <v>0.2997105954126939</v>
+        <v>0.3375237255410258</v>
       </c>
       <c r="K318" t="n">
-        <v>2.844540547234669</v>
+        <v>3.178092477768391</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12569,10 +12569,10 @@
         <v>119.0187792993542</v>
       </c>
       <c r="J319" t="n">
-        <v>0.1324345777795622</v>
+        <v>0.1247600572307578</v>
       </c>
       <c r="K319" t="n">
-        <v>1.439038634798361</v>
+        <v>1.370361521988979</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -12607,10 +12607,10 @@
         <v>121.2670721312614</v>
       </c>
       <c r="J320" t="n">
-        <v>0.07086836800499478</v>
+        <v>0.01640710789920652</v>
       </c>
       <c r="K320" t="n">
-        <v>0.9217413748325636</v>
+        <v>0.4497486080820496</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -12645,10 +12645,10 @@
         <v>29.77274718711185</v>
       </c>
       <c r="J321" t="n">
-        <v>0.1695929631120939</v>
+        <v>0.1441623371213793</v>
       </c>
       <c r="K321" t="n">
-        <v>1.751254231432546</v>
+        <v>1.535211574864667</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -12683,10 +12683,10 @@
         <v>15.35785895954561</v>
       </c>
       <c r="J322" t="n">
-        <v>0.0312811005280387</v>
+        <v>0.04667461496316843</v>
       </c>
       <c r="K322" t="n">
-        <v>0.5891176016565511</v>
+        <v>0.7069142694392588</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -12721,10 +12721,10 @@
         <v>30.97118941678001</v>
       </c>
       <c r="J323" t="n">
-        <v>0.03684166683509545</v>
+        <v>0.149541812738882</v>
       </c>
       <c r="K323" t="n">
-        <v>0.6358391023796124</v>
+        <v>1.580917896234531</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -12759,10 +12759,10 @@
         <v>30.30321725999885</v>
       </c>
       <c r="J324" t="n">
-        <v>0.0595267804481948</v>
+        <v>0.02757237340430488</v>
       </c>
       <c r="K324" t="n">
-        <v>0.8264460466277336</v>
+        <v>0.5446134703179687</v>
       </c>
       <c r="L324" t="b">
         <v>0</v>
@@ -12797,10 +12797,10 @@
         <v>21.76384567448471</v>
       </c>
       <c r="J325" t="n">
-        <v>0.03256333773050307</v>
+        <v>0.03275256531964247</v>
       </c>
       <c r="K325" t="n">
-        <v>0.5998913327972171</v>
+        <v>0.5886265922790835</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>
@@ -12835,10 +12835,10 @@
         <v>28.14172596449839</v>
       </c>
       <c r="J326" t="n">
-        <v>0.09319909336357644</v>
+        <v>0.0996244134651319</v>
       </c>
       <c r="K326" t="n">
-        <v>1.109370645553318</v>
+        <v>1.156798362031125</v>
       </c>
       <c r="L326" t="b">
         <v>0</v>
@@ -12873,10 +12873,10 @@
         <v>18.71654856949598</v>
       </c>
       <c r="J327" t="n">
-        <v>0.01687375004231325</v>
+        <v>0.06250708787374012</v>
       </c>
       <c r="K327" t="n">
-        <v>0.4680628387123588</v>
+        <v>0.8414337182449747</v>
       </c>
       <c r="L327" t="b">
         <v>0</v>
@@ -12911,10 +12911,10 @@
         <v>36.19743089260857</v>
       </c>
       <c r="J328" t="n">
-        <v>0.06946836238917345</v>
+        <v>0.08794887464270834</v>
       </c>
       <c r="K328" t="n">
-        <v>0.9099781191172462</v>
+        <v>1.05759799985312</v>
       </c>
       <c r="L328" t="b">
         <v>0</v>
@@ -12949,10 +12949,10 @@
         <v>74.53465319949539</v>
       </c>
       <c r="J329" t="n">
-        <v>0.02669913158425691</v>
+        <v>0.03897645375258719</v>
       </c>
       <c r="K329" t="n">
-        <v>0.5506185615411107</v>
+        <v>0.6415074054127636</v>
       </c>
       <c r="L329" t="b">
         <v>0</v>
@@ -12987,10 +12987,10 @@
         <v>36.45215118151282</v>
       </c>
       <c r="J330" t="n">
-        <v>0.1516657474892597</v>
+        <v>0.1616314530739727</v>
       </c>
       <c r="K330" t="n">
-        <v>1.600624534485714</v>
+        <v>1.683636641646047</v>
       </c>
       <c r="L330" t="b">
         <v>0</v>
@@ -13025,10 +13025,10 @@
         <v>36.81196255037768</v>
       </c>
       <c r="J331" t="n">
-        <v>0.0226568954231167</v>
+        <v>0.03309449515617641</v>
       </c>
       <c r="K331" t="n">
-        <v>0.5166545137631315</v>
+        <v>0.5915317741417389</v>
       </c>
       <c r="L331" t="b">
         <v>0</v>
@@ -13063,10 +13063,10 @@
         <v>116.1163335164228</v>
       </c>
       <c r="J332" t="n">
-        <v>0.02653213363622665</v>
+        <v>0.0721342656839651</v>
       </c>
       <c r="K332" t="n">
-        <v>0.5492153960506203</v>
+        <v>0.9232303308083445</v>
       </c>
       <c r="L332" t="b">
         <v>0</v>
@@ -13101,10 +13101,10 @@
         <v>120.951572640603</v>
       </c>
       <c r="J333" t="n">
-        <v>0.2623779090258581</v>
+        <v>0.2208021510846493</v>
       </c>
       <c r="K333" t="n">
-        <v>2.530860422279986</v>
+        <v>2.186376152195336</v>
       </c>
       <c r="L333" t="b">
         <v>0</v>
@@ -13139,10 +13139,10 @@
         <v>36.2041653219204</v>
       </c>
       <c r="J334" t="n">
-        <v>0.1193068150795825</v>
+        <v>0.1011698937908879</v>
       </c>
       <c r="K334" t="n">
-        <v>1.328735341822447</v>
+        <v>1.169929422651602</v>
       </c>
       <c r="L334" t="b">
         <v>0</v>
@@ -13177,10 +13177,10 @@
         <v>30.98840386250896</v>
       </c>
       <c r="J335" t="n">
-        <v>0.06536614606216948</v>
+        <v>0.09593689774942167</v>
       </c>
       <c r="K335" t="n">
-        <v>0.8755101004830583</v>
+        <v>1.125467654292567</v>
       </c>
       <c r="L335" t="b">
         <v>0</v>
@@ -13215,10 +13215,10 @@
         <v>24.50584697500355</v>
       </c>
       <c r="J336" t="n">
-        <v>0.08717213309901885</v>
+        <v>0.09689651052334722</v>
       </c>
       <c r="K336" t="n">
-        <v>1.058730366702397</v>
+        <v>1.133620934083066</v>
       </c>
       <c r="L336" t="b">
         <v>0</v>
@@ -13253,10 +13253,10 @@
         <v>27.11868339162558</v>
       </c>
       <c r="J337" t="n">
-        <v>0.03470684152242733</v>
+        <v>0.06739915320342822</v>
       </c>
       <c r="K337" t="n">
-        <v>0.6179016771459895</v>
+        <v>0.8829987937318104</v>
       </c>
       <c r="L337" t="b">
         <v>0</v>
@@ -13291,10 +13291,10 @@
         <v>87.92046479880328</v>
       </c>
       <c r="J338" t="n">
-        <v>0.07122979726704319</v>
+        <v>0.07590076667754163</v>
       </c>
       <c r="K338" t="n">
-        <v>0.9247782089598179</v>
+        <v>0.9552321311868429</v>
       </c>
       <c r="L338" t="b">
         <v>0</v>
@@ -13329,10 +13329,10 @@
         <v>33.81164534663872</v>
       </c>
       <c r="J339" t="n">
-        <v>0.174241040568684</v>
+        <v>0.1663077802908135</v>
       </c>
       <c r="K339" t="n">
-        <v>1.790308734563516</v>
+        <v>1.723368714026513</v>
       </c>
       <c r="L339" t="b">
         <v>0</v>
@@ -13367,10 +13367,10 @@
         <v>177.5258955173807</v>
       </c>
       <c r="J340" t="n">
-        <v>0.09210397117952918</v>
+        <v>0.1151612632961364</v>
       </c>
       <c r="K340" t="n">
-        <v>1.100169109398831</v>
+        <v>1.288806070949948</v>
       </c>
       <c r="L340" t="b">
         <v>0</v>
@@ -13405,10 +13405,10 @@
         <v>27.84573455896668</v>
       </c>
       <c r="J341" t="n">
-        <v>0.2963920265774745</v>
+        <v>0.2041945871538677</v>
       </c>
       <c r="K341" t="n">
-        <v>2.816656963500138</v>
+        <v>2.045271199191897</v>
       </c>
       <c r="L341" t="b">
         <v>0</v>
@@ -13443,10 +13443,10 @@
         <v>87.52923187520246</v>
       </c>
       <c r="J342" t="n">
-        <v>0.003008812568370564</v>
+        <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>0.3515655881729813</v>
+        <v>0.3103468150985003</v>
       </c>
       <c r="L342" t="b">
         <v>0</v>
@@ -13481,10 +13481,10 @@
         <v>17.57109647041198</v>
       </c>
       <c r="J343" t="n">
-        <v>0.03880371742864476</v>
+        <v>0.07180199484025795</v>
       </c>
       <c r="K343" t="n">
-        <v>0.6523248240063577</v>
+        <v>0.9204072158722154</v>
       </c>
       <c r="L343" t="b">
         <v>0</v>
@@ -13519,10 +13519,10 @@
         <v>114.3136463860954</v>
       </c>
       <c r="J344" t="n">
-        <v>0.08558551559525937</v>
+        <v>0.08891640815622917</v>
       </c>
       <c r="K344" t="n">
-        <v>1.045399143450002</v>
+        <v>1.065818577628622</v>
       </c>
       <c r="L344" t="b">
         <v>0</v>
@@ -13557,10 +13557,10 @@
         <v>14.55065210231992</v>
       </c>
       <c r="J345" t="n">
-        <v>0.1097704286528424</v>
+        <v>0.1455004558296157</v>
       </c>
       <c r="K345" t="n">
-        <v>1.248607840282381</v>
+        <v>1.546580802659042</v>
       </c>
       <c r="L345" t="b">
         <v>0</v>
@@ -13595,10 +13595,10 @@
         <v>27.94484649826009</v>
       </c>
       <c r="J346" t="n">
-        <v>0.04390903571594654</v>
+        <v>0.1115391974957013</v>
       </c>
       <c r="K346" t="n">
-        <v>0.6952211980229608</v>
+        <v>1.258031453632446</v>
       </c>
       <c r="L346" t="b">
         <v>0</v>
@@ -13633,10 +13633,10 @@
         <v>135.0214901147274</v>
       </c>
       <c r="J347" t="n">
-        <v>0.04949133432786991</v>
+        <v>0.06315974652451418</v>
       </c>
       <c r="K347" t="n">
-        <v>0.7421252999131461</v>
+        <v>0.8469789847650131</v>
       </c>
       <c r="L347" t="b">
         <v>0</v>
@@ -13671,10 +13671,10 @@
         <v>22.75876730161688</v>
       </c>
       <c r="J348" t="n">
-        <v>0.02812242008234568</v>
+        <v>0.05233417116234471</v>
       </c>
       <c r="K348" t="n">
-        <v>0.5625774468273428</v>
+        <v>0.755000274998745</v>
       </c>
       <c r="L348" t="b">
         <v>0</v>
@@ -13709,10 +13709,10 @@
         <v>43.04401904734274</v>
       </c>
       <c r="J349" t="n">
-        <v>0.09262149928923397</v>
+        <v>0.0673404681484482</v>
       </c>
       <c r="K349" t="n">
-        <v>1.104517531594802</v>
+        <v>0.8825001804517729</v>
       </c>
       <c r="L349" t="b">
         <v>0</v>
@@ -13747,10 +13747,10 @@
         <v>75.27510160932917</v>
       </c>
       <c r="J350" t="n">
-        <v>0.05495588138177206</v>
+        <v>0.1668436157689063</v>
       </c>
       <c r="K350" t="n">
-        <v>0.7880400188521295</v>
+        <v>1.727921400999087</v>
       </c>
       <c r="L350" t="b">
         <v>0</v>
@@ -13785,10 +13785,10 @@
         <v>108.8904327313879</v>
       </c>
       <c r="J351" t="n">
-        <v>0.1695717503046044</v>
+        <v>0.2928345326025137</v>
       </c>
       <c r="K351" t="n">
-        <v>1.751075995233977</v>
+        <v>2.798394016535157</v>
       </c>
       <c r="L351" t="b">
         <v>0</v>
@@ -13823,10 +13823,10 @@
         <v>115.4144567504338</v>
       </c>
       <c r="J352" t="n">
-        <v>0.1941055688188991</v>
+        <v>0.3163991034304343</v>
       </c>
       <c r="K352" t="n">
-        <v>1.957216297526639</v>
+        <v>2.998608670115806</v>
       </c>
       <c r="L352" t="b">
         <v>0</v>
@@ -13861,10 +13861,10 @@
         <v>114.4310840321381</v>
       </c>
       <c r="J353" t="n">
-        <v>0.1264582515714813</v>
+        <v>0.06769544748557844</v>
       </c>
       <c r="K353" t="n">
-        <v>1.388823798065321</v>
+        <v>0.8855162364423879</v>
       </c>
       <c r="L353" t="b">
         <v>0</v>
@@ -13899,10 +13899,10 @@
         <v>50.51158070213913</v>
       </c>
       <c r="J354" t="n">
-        <v>0.05983952443544946</v>
+        <v>0.1106083065096569</v>
       </c>
       <c r="K354" t="n">
-        <v>0.8290738128694756</v>
+        <v>1.250122206413252</v>
       </c>
       <c r="L354" t="b">
         <v>0</v>
@@ -13937,10 +13937,10 @@
         <v>91.84930615961591</v>
       </c>
       <c r="J355" t="n">
-        <v>0.02007705190339254</v>
+        <v>0.02658318490468038</v>
       </c>
       <c r="K355" t="n">
-        <v>0.494977915694476</v>
+        <v>0.5362089025359142</v>
       </c>
       <c r="L355" t="b">
         <v>0</v>
@@ -13975,10 +13975,10 @@
         <v>28.18934767155841</v>
       </c>
       <c r="J356" t="n">
-        <v>0.2021677510247225</v>
+        <v>0.2150571355977063</v>
       </c>
       <c r="K356" t="n">
-        <v>2.024957105019718</v>
+        <v>2.13756404804401</v>
       </c>
       <c r="L356" t="b">
         <v>0</v>
@@ -14013,10 +14013,10 @@
         <v>115.9253931759287</v>
       </c>
       <c r="J357" t="n">
-        <v>0.05521300518773785</v>
+        <v>0.04888201764093887</v>
       </c>
       <c r="K357" t="n">
-        <v>0.7902004481003342</v>
+        <v>0.7256693049402303</v>
       </c>
       <c r="L357" t="b">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>31.26228976959975</v>
       </c>
       <c r="J358" t="n">
-        <v>0.1155729689100014</v>
+        <v>0.07174952696456804</v>
       </c>
       <c r="K358" t="n">
-        <v>1.29736247674385</v>
+        <v>0.91996142640157</v>
       </c>
       <c r="L358" t="b">
         <v>0</v>
@@ -14089,10 +14089,10 @@
         <v>73.59029945000997</v>
       </c>
       <c r="J359" t="n">
-        <v>0.03958553743344607</v>
+        <v>0.0539559652127664</v>
       </c>
       <c r="K359" t="n">
-        <v>0.6588939038271076</v>
+        <v>0.7687797296026713</v>
       </c>
       <c r="L359" t="b">
         <v>0</v>
@@ -14127,10 +14127,10 @@
         <v>25.0541073594561</v>
       </c>
       <c r="J360" t="n">
-        <v>0.03655804498158874</v>
+        <v>0.09980688574824088</v>
       </c>
       <c r="K360" t="n">
-        <v>0.6334560288036579</v>
+        <v>1.158348724446699</v>
       </c>
       <c r="L360" t="b">
         <v>0</v>
@@ -14165,10 +14165,10 @@
         <v>18.56927938530769</v>
       </c>
       <c r="J361" t="n">
-        <v>0.00787620362668553</v>
+        <v>0.03158635521164739</v>
       </c>
       <c r="K361" t="n">
-        <v>0.3924628281828491</v>
+        <v>0.5787179733409515</v>
       </c>
       <c r="L361" t="b">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>27.72703709063884</v>
       </c>
       <c r="J362" t="n">
-        <v>0.0627440933852734</v>
+        <v>0.09740757127949277</v>
       </c>
       <c r="K362" t="n">
-        <v>0.8534788487589244</v>
+        <v>1.13796312444153</v>
       </c>
       <c r="L362" t="b">
         <v>0</v>
@@ -14241,10 +14241,10 @@
         <v>27.44306868271444</v>
       </c>
       <c r="J363" t="n">
-        <v>0.01180416363374425</v>
+        <v>0.02540164716358737</v>
       </c>
       <c r="K363" t="n">
-        <v>0.4254666943676745</v>
+        <v>0.5261700534835433</v>
       </c>
       <c r="L363" t="b">
         <v>0</v>
@@ -14279,10 +14279,10 @@
         <v>76.73860897571544</v>
       </c>
       <c r="J364" t="n">
-        <v>0.04750639265733949</v>
+        <v>0.06251184493002623</v>
       </c>
       <c r="K364" t="n">
-        <v>0.7254472407778332</v>
+        <v>0.8414741362259912</v>
       </c>
       <c r="L364" t="b">
         <v>0</v>
@@ -14317,10 +14317,10 @@
         <v>31.50627494566162</v>
       </c>
       <c r="J365" t="n">
-        <v>0.07380063966515044</v>
+        <v>0.03636138285375808</v>
       </c>
       <c r="K365" t="n">
-        <v>0.9463791769780594</v>
+        <v>0.6192886466701878</v>
       </c>
       <c r="L365" t="b">
         <v>0</v>
@@ -14355,10 +14355,10 @@
         <v>66.49654671964733</v>
       </c>
       <c r="J366" t="n">
-        <v>0.04085308148131795</v>
+        <v>0.0321045297556923</v>
       </c>
       <c r="K366" t="n">
-        <v>0.6695441787953247</v>
+        <v>0.5831206054783185</v>
       </c>
       <c r="L366" t="b">
         <v>0</v>
@@ -14393,10 +14393,10 @@
         <v>101.2586034843393</v>
       </c>
       <c r="J367" t="n">
-        <v>0.02435945312910515</v>
+        <v>0.04812893131445602</v>
       </c>
       <c r="K367" t="n">
-        <v>0.5309599004267962</v>
+        <v>0.7192707620143206</v>
       </c>
       <c r="L367" t="b">
         <v>0</v>
@@ -14431,10 +14431,10 @@
         <v>88.59166440726231</v>
       </c>
       <c r="J368" t="n">
-        <v>0.03345332264628198</v>
+        <v>0.08513958565350307</v>
       </c>
       <c r="K368" t="n">
-        <v>0.6073692457632595</v>
+        <v>1.033729081302088</v>
       </c>
       <c r="L368" t="b">
         <v>0</v>
@@ -14469,10 +14469,10 @@
         <v>96.2458254799941</v>
       </c>
       <c r="J369" t="n">
-        <v>0.08054232647710736</v>
+        <v>0.08220943425448672</v>
       </c>
       <c r="K369" t="n">
-        <v>1.00302479684231</v>
+        <v>1.008833264120567</v>
       </c>
       <c r="L369" t="b">
         <v>0</v>
@@ -14507,10 +14507,10 @@
         <v>21.6990522776749</v>
       </c>
       <c r="J370" t="n">
-        <v>0.1208617633419771</v>
+        <v>0.04613535988218348</v>
       </c>
       <c r="K370" t="n">
-        <v>1.341800470867593</v>
+        <v>0.7023325280606685</v>
       </c>
       <c r="L370" t="b">
         <v>0</v>
@@ -14545,10 +14545,10 @@
         <v>28.9134866701852</v>
       </c>
       <c r="J371" t="n">
-        <v>0.0734298938603431</v>
+        <v>0.08982014643765095</v>
       </c>
       <c r="K371" t="n">
-        <v>0.9432640625399138</v>
+        <v>1.073497123877724</v>
       </c>
       <c r="L371" t="b">
         <v>0</v>
@@ -14583,10 +14583,10 @@
         <v>86.12801420413125</v>
       </c>
       <c r="J372" t="n">
-        <v>0.03111669769579205</v>
+        <v>0.01570817940980184</v>
       </c>
       <c r="K372" t="n">
-        <v>0.5877362410861472</v>
+        <v>0.4438102132601928</v>
       </c>
       <c r="L372" t="b">
         <v>0</v>
@@ -14621,10 +14621,10 @@
         <v>113.5116901430046</v>
       </c>
       <c r="J373" t="n">
-        <v>0.1766170178073082</v>
+        <v>0.1449932494763018</v>
       </c>
       <c r="K373" t="n">
-        <v>1.810272388648799</v>
+        <v>1.542271360952499</v>
       </c>
       <c r="L373" t="b">
         <v>0</v>
@@ -14659,10 +14659,10 @@
         <v>28.20941983612664</v>
       </c>
       <c r="J374" t="n">
-        <v>0.07902289682355368</v>
+        <v>0.07738738309619411</v>
       </c>
       <c r="K374" t="n">
-        <v>0.990258105513217</v>
+        <v>0.9678630589232882</v>
       </c>
       <c r="L374" t="b">
         <v>0</v>
@@ -14697,10 +14697,10 @@
         <v>111.576752548439</v>
       </c>
       <c r="J375" t="n">
-        <v>0.03814942203916092</v>
+        <v>0.04830202463550622</v>
       </c>
       <c r="K375" t="n">
-        <v>0.6468272432160577</v>
+        <v>0.7207414367643198</v>
       </c>
       <c r="L375" t="b">
         <v>0</v>
@@ -14735,10 +14735,10 @@
         <v>119.3964409538112</v>
       </c>
       <c r="J376" t="n">
-        <v>0.1484432300903519</v>
+        <v>0.06363668499512785</v>
       </c>
       <c r="K376" t="n">
-        <v>1.573548002947537</v>
+        <v>0.8510312576186336</v>
       </c>
       <c r="L376" t="b">
         <v>0</v>
@@ -14773,10 +14773,10 @@
         <v>15.96302931080804</v>
       </c>
       <c r="J377" t="n">
-        <v>0.1340401169668149</v>
+        <v>0.2074067656287145</v>
       </c>
       <c r="K377" t="n">
-        <v>1.452528843556942</v>
+        <v>2.072563238808366</v>
       </c>
       <c r="L377" t="b">
         <v>0</v>
@@ -14811,10 +14811,10 @@
         <v>33.97022017553762</v>
       </c>
       <c r="J378" t="n">
-        <v>0.1441976210251753</v>
+        <v>0.1467135739939267</v>
       </c>
       <c r="K378" t="n">
-        <v>1.537875156684243</v>
+        <v>1.556887972468906</v>
       </c>
       <c r="L378" t="b">
         <v>0</v>
@@ -14849,10 +14849,10 @@
         <v>31.87999470172099</v>
       </c>
       <c r="J379" t="n">
-        <v>0.0169736189059006</v>
+        <v>0.09256333790626248</v>
       </c>
       <c r="K379" t="n">
-        <v>0.4689019660466353</v>
+        <v>1.096804449676448</v>
       </c>
       <c r="L379" t="b">
         <v>0</v>
@@ -14887,10 +14887,10 @@
         <v>72.48688012091472</v>
       </c>
       <c r="J380" t="n">
-        <v>0.03696415132790607</v>
+        <v>0.05068252706629479</v>
       </c>
       <c r="K380" t="n">
-        <v>0.6368682528300176</v>
+        <v>0.7409672016640358</v>
       </c>
       <c r="L380" t="b">
         <v>0</v>
@@ -14925,10 +14925,10 @@
         <v>20.33443311749934</v>
       </c>
       <c r="J381" t="n">
-        <v>0.02251073120824273</v>
+        <v>0.02198210945367839</v>
       </c>
       <c r="K381" t="n">
-        <v>0.5154263993780457</v>
+        <v>0.4971162012833499</v>
       </c>
       <c r="L381" t="b">
         <v>0</v>
@@ -14963,10 +14963,10 @@
         <v>116.1171991900592</v>
       </c>
       <c r="J382" t="n">
-        <v>0.09229530597229554</v>
+        <v>0.08188424695696606</v>
       </c>
       <c r="K382" t="n">
-        <v>1.101776760160451</v>
+        <v>1.006070334016838</v>
       </c>
       <c r="L382" t="b">
         <v>0</v>
@@ -15001,10 +15001,10 @@
         <v>28.97558924479167</v>
       </c>
       <c r="J383" t="n">
-        <v>0.03175269157645189</v>
+        <v>0.04739352517031445</v>
       </c>
       <c r="K383" t="n">
-        <v>0.5930800472588029</v>
+        <v>0.7130224374653359</v>
       </c>
       <c r="L383" t="b">
         <v>0</v>
@@ -15039,10 +15039,10 @@
         <v>36.87522104380725</v>
       </c>
       <c r="J384" t="n">
-        <v>0.143954085872678</v>
+        <v>0.1064038883654424</v>
       </c>
       <c r="K384" t="n">
-        <v>1.535828903267742</v>
+        <v>1.214399674974033</v>
       </c>
       <c r="L384" t="b">
         <v>0</v>
@@ -15077,10 +15077,10 @@
         <v>122.3935234424614</v>
       </c>
       <c r="J385" t="n">
-        <v>0.0425652898360632</v>
+        <v>0.05801595057978895</v>
       </c>
       <c r="K385" t="n">
-        <v>0.6839306530259691</v>
+        <v>0.8032750985078327</v>
       </c>
       <c r="L385" t="b">
         <v>0</v>
@@ -15115,10 +15115,10 @@
         <v>37.36931217607049</v>
       </c>
       <c r="J386" t="n">
-        <v>0.05777016414438501</v>
+        <v>0.09400886583491454</v>
       </c>
       <c r="K386" t="n">
-        <v>0.8116864438505065</v>
+        <v>1.10908627206098</v>
       </c>
       <c r="L386" t="b">
         <v>0</v>
@@ -15153,10 +15153,10 @@
         <v>114.1445551177079</v>
       </c>
       <c r="J387" t="n">
-        <v>0.0312638770168506</v>
+        <v>0.1200642775419079</v>
       </c>
       <c r="K387" t="n">
-        <v>0.5889728846896107</v>
+        <v>1.330464173101973</v>
       </c>
       <c r="L387" t="b">
         <v>0</v>
@@ -15191,10 +15191,10 @@
         <v>85.59812606174853</v>
       </c>
       <c r="J388" t="n">
-        <v>0.07106505954808652</v>
+        <v>0.05487504684304577</v>
       </c>
       <c r="K388" t="n">
-        <v>0.9233940345735541</v>
+        <v>0.7765886394938157</v>
       </c>
       <c r="L388" t="b">
         <v>0</v>
@@ -15229,10 +15229,10 @@
         <v>27.7854300477073</v>
       </c>
       <c r="J389" t="n">
-        <v>0.0669015955870982</v>
+        <v>0.04951259965930053</v>
       </c>
       <c r="K389" t="n">
-        <v>0.8884113954461523</v>
+        <v>0.7310269989666742</v>
       </c>
       <c r="L389" t="b">
         <v>0</v>
@@ -15267,10 +15267,10 @@
         <v>36.79245590699077</v>
       </c>
       <c r="J390" t="n">
-        <v>0.02648959386759394</v>
+        <v>0.03474038059536266</v>
       </c>
       <c r="K390" t="n">
-        <v>0.5488579645011736</v>
+        <v>0.6055159194693365</v>
       </c>
       <c r="L390" t="b">
         <v>0</v>
@@ -15305,10 +15305,10 @@
         <v>50.3132081114936</v>
       </c>
       <c r="J391" t="n">
-        <v>0.08013285355037379</v>
+        <v>0.04668434160509277</v>
       </c>
       <c r="K391" t="n">
-        <v>0.9995842858249022</v>
+        <v>0.7069969111413974</v>
       </c>
       <c r="L391" t="b">
         <v>0</v>
@@ -15343,10 +15343,10 @@
         <v>113.0013619677478</v>
       </c>
       <c r="J392" t="n">
-        <v>0.06468440327453115</v>
+        <v>0.1163764607853359</v>
       </c>
       <c r="K392" t="n">
-        <v>0.8697818986441264</v>
+        <v>1.299130907591737</v>
       </c>
       <c r="L392" t="b">
         <v>0</v>
@@ -15381,10 +15381,10 @@
         <v>28.75503351175996</v>
       </c>
       <c r="J393" t="n">
-        <v>0.06793788151551135</v>
+        <v>0.1400803478817251</v>
       </c>
       <c r="K393" t="n">
-        <v>0.8971185722119808</v>
+        <v>1.500529251664069</v>
       </c>
       <c r="L393" t="b">
         <v>0</v>
@@ -15419,10 +15419,10 @@
         <v>21.37182465761164</v>
       </c>
       <c r="J394" t="n">
-        <v>0.05843485542424851</v>
+        <v>0.0344494057640142</v>
       </c>
       <c r="K394" t="n">
-        <v>0.8172713739453682</v>
+        <v>0.6030436730836696</v>
       </c>
       <c r="L394" t="b">
         <v>0</v>
@@ -15457,10 +15457,10 @@
         <v>21.096208327423</v>
       </c>
       <c r="J395" t="n">
-        <v>0.09928171856846005</v>
+        <v>0.05768809276111465</v>
       </c>
       <c r="K395" t="n">
-        <v>1.160478637476267</v>
+        <v>0.8004894785163239</v>
       </c>
       <c r="L395" t="b">
         <v>0</v>
@@ -15495,10 +15495,10 @@
         <v>106.7208841526199</v>
       </c>
       <c r="J396" t="n">
-        <v>0.09445531911871574</v>
+        <v>0.08521809869900077</v>
       </c>
       <c r="K396" t="n">
-        <v>1.119925820923241</v>
+        <v>1.034396161654227</v>
       </c>
       <c r="L396" t="b">
         <v>0</v>
@@ -15533,10 +15533,10 @@
         <v>27.31988209689151</v>
       </c>
       <c r="J397" t="n">
-        <v>0.0420176007854652</v>
+        <v>0.05042844915195244</v>
       </c>
       <c r="K397" t="n">
-        <v>0.6793288098034447</v>
+        <v>0.738808447236721</v>
       </c>
       <c r="L397" t="b">
         <v>0</v>
@@ -15571,10 +15571,10 @@
         <v>121.4238141117946</v>
       </c>
       <c r="J398" t="n">
-        <v>0.04311870788474587</v>
+        <v>0.05085257378378166</v>
       </c>
       <c r="K398" t="n">
-        <v>0.6885806329621618</v>
+        <v>0.7424119911695515</v>
       </c>
       <c r="L398" t="b">
         <v>0</v>
@@ -15609,10 +15609,10 @@
         <v>34.44329111183458</v>
       </c>
       <c r="J399" t="n">
-        <v>0.06159412615399092</v>
+        <v>0.09734180104459662</v>
       </c>
       <c r="K399" t="n">
-        <v>0.8438164885134084</v>
+        <v>1.137404312448229</v>
       </c>
       <c r="L399" t="b">
         <v>0</v>
@@ -15647,10 +15647,10 @@
         <v>23.19903955717129</v>
       </c>
       <c r="J400" t="n">
-        <v>0.07084323962785452</v>
+        <v>0.06100621641325833</v>
       </c>
       <c r="K400" t="n">
-        <v>0.9215302388751992</v>
+        <v>0.8286816735876029</v>
       </c>
       <c r="L400" t="b">
         <v>0</v>
@@ -15685,10 +15685,10 @@
         <v>59.64627198646539</v>
       </c>
       <c r="J401" t="n">
-        <v>0.05079958977339905</v>
+        <v>0.07764228666207128</v>
       </c>
       <c r="K401" t="n">
-        <v>0.753117643924343</v>
+        <v>0.9700288284385172</v>
       </c>
       <c r="L401" t="b">
         <v>0</v>
@@ -15723,10 +15723,10 @@
         <v>65.30910558387407</v>
       </c>
       <c r="J402" t="n">
-        <v>0.2058451381981441</v>
+        <v>0.1542302925031362</v>
       </c>
       <c r="K402" t="n">
-        <v>2.055855585137462</v>
+        <v>1.6207532218458</v>
       </c>
       <c r="L402" t="b">
         <v>0</v>
@@ -15761,10 +15761,10 @@
         <v>18.39190664309704</v>
       </c>
       <c r="J403" t="n">
-        <v>0.1863241119016438</v>
+        <v>0.1150815513003378</v>
       </c>
       <c r="K403" t="n">
-        <v>1.891834225825664</v>
+        <v>1.288128803804216</v>
       </c>
       <c r="L403" t="b">
         <v>0</v>
@@ -15799,10 +15799,10 @@
         <v>177.694695794369</v>
       </c>
       <c r="J404" t="n">
-        <v>0.04420939472836992</v>
+        <v>0.0954207068082758</v>
       </c>
       <c r="K404" t="n">
-        <v>0.6977449020921502</v>
+        <v>1.12108187569224</v>
       </c>
       <c r="L404" t="b">
         <v>0</v>
@@ -15837,10 +15837,10 @@
         <v>109.1009549042153</v>
       </c>
       <c r="J405" t="n">
-        <v>0.4056528184641447</v>
+        <v>0.3684717906237956</v>
       </c>
       <c r="K405" t="n">
-        <v>3.734698019976151</v>
+        <v>3.441040450586827</v>
       </c>
       <c r="L405" t="b">
         <v>0</v>
@@ -15875,10 +15875,10 @@
         <v>62.9998050958446</v>
       </c>
       <c r="J406" t="n">
-        <v>0.08016669574265435</v>
+        <v>0.1146111335592809</v>
       </c>
       <c r="K406" t="n">
-        <v>0.9998686377998259</v>
+        <v>1.28413193385264</v>
       </c>
       <c r="L406" t="b">
         <v>0</v>
@@ -15913,10 +15913,10 @@
         <v>111.4735650347028</v>
       </c>
       <c r="J407" t="n">
-        <v>0.06845179891697906</v>
+        <v>0.1768884405609376</v>
       </c>
       <c r="K407" t="n">
-        <v>0.901436656183715</v>
+        <v>1.813266520615353</v>
       </c>
       <c r="L407" t="b">
         <v>0</v>
@@ -15951,10 +15951,10 @@
         <v>50.5902303085075</v>
       </c>
       <c r="J408" t="n">
-        <v>0.05503715800569289</v>
+        <v>0.1591850672638399</v>
       </c>
       <c r="K408" t="n">
-        <v>0.7887229287633855</v>
+        <v>1.662851103429497</v>
       </c>
       <c r="L408" t="b">
         <v>0</v>
@@ -15989,10 +15989,10 @@
         <v>57.12164670019577</v>
       </c>
       <c r="J409" t="n">
-        <v>0.06010007083512456</v>
+        <v>0.07773654605296995</v>
       </c>
       <c r="K409" t="n">
-        <v>0.8312629997487621</v>
+        <v>0.9708296964633719</v>
       </c>
       <c r="L409" t="b">
         <v>0</v>
@@ -16027,10 +16027,10 @@
         <v>118.6233953341241</v>
       </c>
       <c r="J410" t="n">
-        <v>0.09113338813836264</v>
+        <v>0.07964426876015082</v>
       </c>
       <c r="K410" t="n">
-        <v>1.092013987464199</v>
+        <v>0.9870385229994187</v>
       </c>
       <c r="L410" t="b">
         <v>0</v>
@@ -16065,10 +16065,10 @@
         <v>110.6772244926049</v>
       </c>
       <c r="J411" t="n">
-        <v>0.1983030666527987</v>
+        <v>0.2865181992758482</v>
       </c>
       <c r="K411" t="n">
-        <v>1.992484899185558</v>
+        <v>2.744727752119263</v>
       </c>
       <c r="L411" t="b">
         <v>0</v>
@@ -16103,10 +16103,10 @@
         <v>109.8286154371832</v>
       </c>
       <c r="J412" t="n">
-        <v>0.158041999429397</v>
+        <v>0.06860020715804861</v>
       </c>
       <c r="K412" t="n">
-        <v>1.654199663920548</v>
+        <v>0.8932034608658739</v>
       </c>
       <c r="L412" t="b">
         <v>0</v>
@@ -16141,10 +16141,10 @@
         <v>34.22526463665388</v>
       </c>
       <c r="J413" t="n">
-        <v>0.09556512446142763</v>
+        <v>0.1279377894611346</v>
       </c>
       <c r="K413" t="n">
-        <v>1.129250729261474</v>
+        <v>1.397360891607166</v>
       </c>
       <c r="L413" t="b">
         <v>0</v>
@@ -16179,10 +16179,10 @@
         <v>112.0140000921148</v>
       </c>
       <c r="J414" t="n">
-        <v>0.08798626717276585</v>
+        <v>0.08853205506051905</v>
       </c>
       <c r="K414" t="n">
-        <v>1.065570958759894</v>
+        <v>1.062552949645316</v>
       </c>
       <c r="L414" t="b">
         <v>0</v>
@@ -16217,10 +16217,10 @@
         <v>70.6433805346871</v>
       </c>
       <c r="J415" t="n">
-        <v>0.1941270537949663</v>
+        <v>0.1563449751757688</v>
       </c>
       <c r="K415" t="n">
-        <v>1.957396820565019</v>
+        <v>1.638720468600512</v>
       </c>
       <c r="L415" t="b">
         <v>0</v>
@@ -16255,10 +16255,10 @@
         <v>21.83007724458759</v>
       </c>
       <c r="J416" t="n">
-        <v>0.07785638122136386</v>
+        <v>0.07549876283790521</v>
       </c>
       <c r="K416" t="n">
-        <v>0.98045670102641</v>
+        <v>0.951816534947953</v>
       </c>
       <c r="L416" t="b">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>21.00719534827816</v>
       </c>
       <c r="J417" t="n">
-        <v>0.02229929510463332</v>
+        <v>0.07831214496528816</v>
       </c>
       <c r="K417" t="n">
-        <v>0.5136498515370225</v>
+        <v>0.9757202305483228</v>
       </c>
       <c r="L417" t="b">
         <v>0</v>
@@ -16331,10 +16331,10 @@
         <v>18.06062429844501</v>
       </c>
       <c r="J418" t="n">
-        <v>0.04934673981013689</v>
+        <v>0.0806240219296271</v>
       </c>
       <c r="K418" t="n">
-        <v>0.7409103745814869</v>
+        <v>0.995362924188547</v>
       </c>
       <c r="L418" t="b">
         <v>0</v>
@@ -16369,10 +16369,10 @@
         <v>169.2865859235861</v>
       </c>
       <c r="J419" t="n">
-        <v>0.07960390261109812</v>
+        <v>0.07645431203608107</v>
       </c>
       <c r="K419" t="n">
-        <v>0.9951398856816166</v>
+        <v>0.9599352888641232</v>
       </c>
       <c r="L419" t="b">
         <v>0</v>
@@ -16407,10 +16407,10 @@
         <v>110.4330950206708</v>
       </c>
       <c r="J420" t="n">
-        <v>0.514632663193816</v>
+        <v>0.4823884456832275</v>
       </c>
       <c r="K420" t="n">
-        <v>4.650378476456763</v>
+        <v>4.408924983530095</v>
       </c>
       <c r="L420" t="b">
         <v>0</v>
@@ -16445,10 +16445,10 @@
         <v>33.90549873962264</v>
       </c>
       <c r="J421" t="n">
-        <v>0.03449912350859644</v>
+        <v>0.05513670830194094</v>
       </c>
       <c r="K421" t="n">
-        <v>0.6161563697802493</v>
+        <v>0.7788118269531024</v>
       </c>
       <c r="L421" t="b">
         <v>0</v>
@@ -16483,10 +16483,10 @@
         <v>89.69141345515386</v>
       </c>
       <c r="J422" t="n">
-        <v>0.004744697710663828</v>
+        <v>0.02719990646787558</v>
       </c>
       <c r="K422" t="n">
-        <v>0.3661510016816522</v>
+        <v>0.5414488322181702</v>
       </c>
       <c r="L422" t="b">
         <v>0</v>
@@ -16521,10 +16521,10 @@
         <v>77.92519024595049</v>
       </c>
       <c r="J423" t="n">
-        <v>0.02933698145363231</v>
+        <v>0.04473113164932827</v>
       </c>
       <c r="K423" t="n">
-        <v>0.5727825458861843</v>
+        <v>0.6904016055226626</v>
       </c>
       <c r="L423" t="b">
         <v>0</v>
@@ -16559,10 +16559,10 @@
         <v>21.61345765035906</v>
       </c>
       <c r="J424" t="n">
-        <v>0.06005450711174819</v>
+        <v>0.06259257405792451</v>
       </c>
       <c r="K424" t="n">
-        <v>0.8308801600491486</v>
+        <v>0.8421600453602611</v>
       </c>
       <c r="L424" t="b">
         <v>0</v>
@@ -16597,10 +16597,10 @@
         <v>121.4319273424702</v>
       </c>
       <c r="J425" t="n">
-        <v>0.05164517066728191</v>
+        <v>0.05890114459735832</v>
       </c>
       <c r="K425" t="n">
-        <v>0.7602224613410183</v>
+        <v>0.8107960847746111</v>
       </c>
       <c r="L425" t="b">
         <v>0</v>
@@ -16635,10 +16635,10 @@
         <v>148.484489831389</v>
       </c>
       <c r="J426" t="n">
-        <v>0.1501033291840559</v>
+        <v>0.1259535967976154</v>
       </c>
       <c r="K426" t="n">
-        <v>1.587496639961075</v>
+        <v>1.380502343676683</v>
       </c>
       <c r="L426" t="b">
         <v>0</v>
@@ -16673,10 +16673,10 @@
         <v>27.07998106582095</v>
       </c>
       <c r="J427" t="n">
-        <v>0.1880764224527174</v>
+        <v>0.2570530376657481</v>
       </c>
       <c r="K427" t="n">
-        <v>1.906557650411953</v>
+        <v>2.494379160263129</v>
       </c>
       <c r="L427" t="b">
         <v>0</v>
@@ -16711,10 +16711,10 @@
         <v>26.95722954595232</v>
       </c>
       <c r="J428" t="n">
-        <v>0.04499951414606724</v>
+        <v>0.04016217679807867</v>
       </c>
       <c r="K428" t="n">
-        <v>0.7043837160018777</v>
+        <v>0.6515818145980303</v>
       </c>
       <c r="L428" t="b">
         <v>0</v>
@@ -16749,10 +16749,10 @@
         <v>36.47561480255364</v>
       </c>
       <c r="J429" t="n">
-        <v>0.02612448324239633</v>
+        <v>0.07082458884570923</v>
       </c>
       <c r="K429" t="n">
-        <v>0.5457901984864929</v>
+        <v>0.9121027572832918</v>
       </c>
       <c r="L429" t="b">
         <v>0</v>
@@ -16787,10 +16787,10 @@
         <v>32.80926707419253</v>
       </c>
       <c r="J430" t="n">
-        <v>0.02837762788363895</v>
+        <v>0.04596501670553559</v>
       </c>
       <c r="K430" t="n">
-        <v>0.5647217772451857</v>
+        <v>0.7008852197115609</v>
       </c>
       <c r="L430" t="b">
         <v>0</v>
@@ -16825,10 +16825,10 @@
         <v>68.66254091461411</v>
       </c>
       <c r="J431" t="n">
-        <v>0.01600263966465743</v>
+        <v>0.02771334111396712</v>
       </c>
       <c r="K431" t="n">
-        <v>0.4607435151233456</v>
+        <v>0.5458111921590405</v>
       </c>
       <c r="L431" t="b">
         <v>0</v>
@@ -16863,10 +16863,10 @@
         <v>119.2432966982582</v>
       </c>
       <c r="J432" t="n">
-        <v>0.006464865715098151</v>
+        <v>0.1001494931675379</v>
       </c>
       <c r="K432" t="n">
-        <v>0.3806043552116643</v>
+        <v>1.161259663341772</v>
       </c>
       <c r="L432" t="b">
         <v>0</v>
@@ -16901,10 +16901,10 @@
         <v>117.3962848607284</v>
       </c>
       <c r="J433" t="n">
-        <v>0.128734708095894</v>
+        <v>0.06954717051376448</v>
       </c>
       <c r="K433" t="n">
-        <v>1.407951250068975</v>
+        <v>0.9012492657991672</v>
       </c>
       <c r="L433" t="b">
         <v>0</v>
@@ -16939,10 +16939,10 @@
         <v>107.5200556285411</v>
       </c>
       <c r="J434" t="n">
-        <v>0.1142077745432111</v>
+        <v>0.08903876844193066</v>
       </c>
       <c r="K434" t="n">
-        <v>1.285891715301051</v>
+        <v>1.066858202852126</v>
       </c>
       <c r="L434" t="b">
         <v>0</v>
@@ -16977,10 +16977,10 @@
         <v>38.16051487094965</v>
       </c>
       <c r="J435" t="n">
-        <v>0.06347517284759176</v>
+        <v>0.05264020486001176</v>
       </c>
       <c r="K435" t="n">
-        <v>0.8596215917352963</v>
+        <v>0.7576004679413559</v>
       </c>
       <c r="L435" t="b">
         <v>0</v>
@@ -17015,10 +17015,10 @@
         <v>51.703436734868</v>
       </c>
       <c r="J436" t="n">
-        <v>0.08904766884676699</v>
+        <v>0.04496462364841552</v>
       </c>
       <c r="K436" t="n">
-        <v>1.074489165349099</v>
+        <v>0.6923854532257456</v>
       </c>
       <c r="L436" t="b">
         <v>0</v>
@@ -17053,10 +17053,10 @@
         <v>39.20783918174072</v>
       </c>
       <c r="J437" t="n">
-        <v>0.1420259415280516</v>
+        <v>0.1789955596718157</v>
       </c>
       <c r="K437" t="n">
-        <v>1.519628071838523</v>
+        <v>1.831169504120479</v>
       </c>
       <c r="L437" t="b">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>83.6350080286978</v>
       </c>
       <c r="J438" t="n">
-        <v>0.08488345077426598</v>
+        <v>0.1285839649384583</v>
       </c>
       <c r="K438" t="n">
-        <v>1.039500189956712</v>
+        <v>1.402851074317872</v>
       </c>
       <c r="L438" t="b">
         <v>0</v>
@@ -17129,10 +17129,10 @@
         <v>91.22407215258015</v>
       </c>
       <c r="J439" t="n">
-        <v>0.09575307278418066</v>
+        <v>0.07153235977639893</v>
       </c>
       <c r="K439" t="n">
-        <v>1.130829925913847</v>
+        <v>0.9181162812611864</v>
       </c>
       <c r="L439" t="b">
         <v>0</v>
@@ -17167,10 +17167,10 @@
         <v>14.89615493382011</v>
       </c>
       <c r="J440" t="n">
-        <v>0.1024705702606236</v>
+        <v>0.1610580225800759</v>
       </c>
       <c r="K440" t="n">
-        <v>1.187272299922496</v>
+        <v>1.678764531369713</v>
       </c>
       <c r="L440" t="b">
         <v>0</v>
@@ -17205,10 +17205,10 @@
         <v>29.14543511076656</v>
       </c>
       <c r="J441" t="n">
-        <v>0.0837304427753687</v>
+        <v>0.09600510660260245</v>
       </c>
       <c r="K441" t="n">
-        <v>1.02981228029438</v>
+        <v>1.126047185827873</v>
       </c>
       <c r="L441" t="b">
         <v>0</v>
@@ -17243,10 +17243,10 @@
         <v>115.4459184195737</v>
       </c>
       <c r="J442" t="n">
-        <v>0.04973149854740927</v>
+        <v>0.03511629528089732</v>
       </c>
       <c r="K442" t="n">
-        <v>0.744143229767273</v>
+        <v>0.6087098511173945</v>
       </c>
       <c r="L442" t="b">
         <v>0</v>
@@ -17281,10 +17281,10 @@
         <v>18.96509308937379</v>
       </c>
       <c r="J443" t="n">
-        <v>0.06995403931069123</v>
+        <v>0.1276757159620138</v>
       </c>
       <c r="K443" t="n">
-        <v>0.9140589183356767</v>
+        <v>1.395134203278221</v>
       </c>
       <c r="L443" t="b">
         <v>0</v>
@@ -17319,10 +17319,10 @@
         <v>32.51831601975699</v>
       </c>
       <c r="J444" t="n">
-        <v>0.0883374029005235</v>
+        <v>0.09022787342256108</v>
       </c>
       <c r="K444" t="n">
-        <v>1.068521303608314</v>
+        <v>1.076961346402098</v>
       </c>
       <c r="L444" t="b">
         <v>0</v>
@@ -17357,10 +17357,10 @@
         <v>63.14476011671022</v>
       </c>
       <c r="J445" t="n">
-        <v>0.02685260435859193</v>
+        <v>0.008488992978136921</v>
       </c>
       <c r="K445" t="n">
-        <v>0.5519080845754757</v>
+        <v>0.382472923431967</v>
       </c>
       <c r="L445" t="b">
         <v>0</v>
@@ -17395,10 +17395,10 @@
         <v>128.7007345228386</v>
       </c>
       <c r="J446" t="n">
-        <v>0.02571232817271913</v>
+        <v>0.03930189168324006</v>
       </c>
       <c r="K446" t="n">
-        <v>0.542327151321405</v>
+        <v>0.6442724650025808</v>
       </c>
       <c r="L446" t="b">
         <v>0</v>
@@ -17433,10 +17433,10 @@
         <v>171.4268816561292</v>
       </c>
       <c r="J447" t="n">
-        <v>0.1032270259732872</v>
+        <v>0.2265729504440888</v>
       </c>
       <c r="K447" t="n">
-        <v>1.193628261559232</v>
+        <v>2.235407327134649</v>
       </c>
       <c r="L447" t="b">
         <v>0</v>
@@ -17471,10 +17471,10 @@
         <v>34.03302231768729</v>
       </c>
       <c r="J448" t="n">
-        <v>0.3780297539097535</v>
+        <v>0.5909447179590464</v>
       </c>
       <c r="K448" t="n">
-        <v>3.502600970991536</v>
+        <v>5.331265415971049</v>
       </c>
       <c r="L448" t="b">
         <v>0</v>
@@ -17509,10 +17509,10 @@
         <v>29.40093435162101</v>
       </c>
       <c r="J449" t="n">
-        <v>0.0257129224584353</v>
+        <v>0.06281945074251805</v>
       </c>
       <c r="K449" t="n">
-        <v>0.5423321446834088</v>
+        <v>0.8440876865272967</v>
       </c>
       <c r="L449" t="b">
         <v>0</v>
@@ -17547,10 +17547,10 @@
         <v>32.41757055345116</v>
       </c>
       <c r="J450" t="n">
-        <v>0.06332035498510727</v>
+        <v>0.05704180129566718</v>
       </c>
       <c r="K450" t="n">
-        <v>0.8583207668777935</v>
+        <v>0.7949983103210017</v>
       </c>
       <c r="L450" t="b">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>100.2904070069606</v>
       </c>
       <c r="J451" t="n">
-        <v>0.05006195799790733</v>
+        <v>0.08716186869444074</v>
       </c>
       <c r="K451" t="n">
-        <v>0.746919846500679</v>
+        <v>1.050911261340081</v>
       </c>
       <c r="L451" t="b">
         <v>0</v>
@@ -17623,10 +17623,10 @@
         <v>31.22431472894692</v>
       </c>
       <c r="J452" t="n">
-        <v>0.1349969446464097</v>
+        <v>0.1263951985717553</v>
       </c>
       <c r="K452" t="n">
-        <v>1.460568388929741</v>
+        <v>1.384254380871659</v>
       </c>
       <c r="L452" t="b">
         <v>0</v>
@@ -17661,10 +17661,10 @@
         <v>48.81819987651181</v>
       </c>
       <c r="J453" t="n">
-        <v>0.08884092380492013</v>
+        <v>0.1010174734603582</v>
       </c>
       <c r="K453" t="n">
-        <v>1.072752033177888</v>
+        <v>1.168634394454462</v>
       </c>
       <c r="L453" t="b">
         <v>0</v>
@@ -17699,10 +17699,10 @@
         <v>16.23229488186946</v>
       </c>
       <c r="J454" t="n">
-        <v>0.07786758198466193</v>
+        <v>0.1275481552418871</v>
       </c>
       <c r="K454" t="n">
-        <v>0.9805508131080996</v>
+        <v>1.39405039294375</v>
       </c>
       <c r="L454" t="b">
         <v>0</v>
@@ -17737,10 +17737,10 @@
         <v>21.75878875797385</v>
       </c>
       <c r="J455" t="n">
-        <v>0.05575471548098133</v>
+        <v>0.09416243551577518</v>
       </c>
       <c r="K455" t="n">
-        <v>0.7947520560589239</v>
+        <v>1.110391065629194</v>
       </c>
       <c r="L455" t="b">
         <v>0</v>
@@ -17775,10 +17775,10 @@
         <v>65.24955909651689</v>
       </c>
       <c r="J456" t="n">
-        <v>0.05477258503027093</v>
+        <v>0.09732784751818123</v>
       </c>
       <c r="K456" t="n">
-        <v>0.7864999094196916</v>
+        <v>1.137285757330977</v>
       </c>
       <c r="L456" t="b">
         <v>0</v>
@@ -17813,10 +17813,10 @@
         <v>32.13319539704933</v>
       </c>
       <c r="J457" t="n">
-        <v>0.0294531812343065</v>
+        <v>0.1590859248896265</v>
       </c>
       <c r="K457" t="n">
-        <v>0.5737588903512972</v>
+        <v>1.662008747493832</v>
       </c>
       <c r="L457" t="b">
         <v>0</v>
@@ -17851,10 +17851,10 @@
         <v>26.04875073011639</v>
       </c>
       <c r="J458" t="n">
-        <v>0.02938718704140904</v>
+        <v>0.01925183686741891</v>
       </c>
       <c r="K458" t="n">
-        <v>0.5732043878850173</v>
+        <v>0.4739186398242209</v>
       </c>
       <c r="L458" t="b">
         <v>0</v>
@@ -17889,10 +17889,10 @@
         <v>107.7198180518485</v>
       </c>
       <c r="J459" t="n">
-        <v>0.04654468916965467</v>
+        <v>0.05793250038720382</v>
       </c>
       <c r="K459" t="n">
-        <v>0.7173667274426689</v>
+        <v>0.8025660700463479</v>
       </c>
       <c r="L459" t="b">
         <v>0</v>
@@ -17927,10 +17927,10 @@
         <v>21.27089676688869</v>
       </c>
       <c r="J460" t="n">
-        <v>0.06177356120331741</v>
+        <v>0.1975677967988107</v>
       </c>
       <c r="K460" t="n">
-        <v>0.8453241541582207</v>
+        <v>1.988967159327217</v>
       </c>
       <c r="L460" t="b">
         <v>0</v>
@@ -17965,10 +17965,10 @@
         <v>65.6670428145887</v>
       </c>
       <c r="J461" t="n">
-        <v>0.05522101534212483</v>
+        <v>0.05511634180814938</v>
       </c>
       <c r="K461" t="n">
-        <v>0.7902677517549113</v>
+        <v>0.7786387845272968</v>
       </c>
       <c r="L461" t="b">
         <v>0</v>
@@ -18003,10 +18003,10 @@
         <v>22.84596851338948</v>
       </c>
       <c r="J462" t="n">
-        <v>0.2569925660363579</v>
+        <v>0.3192375360674627</v>
       </c>
       <c r="K462" t="n">
-        <v>2.485611199002394</v>
+        <v>3.022725205540305</v>
       </c>
       <c r="L462" t="b">
         <v>0</v>
@@ -18041,10 +18041,10 @@
         <v>106.5039748974762</v>
       </c>
       <c r="J463" t="n">
-        <v>0.08172430534815862</v>
+        <v>0.08832668502024395</v>
       </c>
       <c r="K463" t="n">
-        <v>1.012956128226378</v>
+        <v>1.060808038109698</v>
       </c>
       <c r="L463" t="b">
         <v>0</v>
@@ -18079,10 +18079,10 @@
         <v>108.8076078075242</v>
       </c>
       <c r="J464" t="n">
-        <v>0.1902346855427025</v>
+        <v>0.153450218340835</v>
       </c>
       <c r="K464" t="n">
-        <v>1.924692006689897</v>
+        <v>1.614125378745543</v>
       </c>
       <c r="L464" t="b">
         <v>0</v>
@@ -18117,10 +18117,10 @@
         <v>33.00631829005077</v>
       </c>
       <c r="J465" t="n">
-        <v>0.07990084766886103</v>
+        <v>0.0850083802835596</v>
       </c>
       <c r="K465" t="n">
-        <v>0.9976349047075336</v>
+        <v>1.032614304466856</v>
       </c>
       <c r="L465" t="b">
         <v>0</v>
@@ -18155,10 +18155,10 @@
         <v>25.66916356552635</v>
       </c>
       <c r="J466" t="n">
-        <v>0.1040113718840682</v>
+        <v>0.07410650770240559</v>
       </c>
       <c r="K466" t="n">
-        <v>1.200218564779099</v>
+        <v>0.9399873409564521</v>
       </c>
       <c r="L466" t="b">
         <v>0</v>
@@ -18193,10 +18193,10 @@
         <v>105.2254193644207</v>
       </c>
       <c r="J467" t="n">
-        <v>0.05451241643910533</v>
+        <v>0.01734958315532384</v>
       </c>
       <c r="K467" t="n">
-        <v>0.784313896997749</v>
+        <v>0.4577562802051627</v>
       </c>
       <c r="L467" t="b">
         <v>0</v>
@@ -18231,10 +18231,10 @@
         <v>105.0150968272887</v>
       </c>
       <c r="J468" t="n">
-        <v>0.1476220021824662</v>
+        <v>0.07785677324243087</v>
       </c>
       <c r="K468" t="n">
-        <v>1.566647806425577</v>
+        <v>0.9718511979905871</v>
       </c>
       <c r="L468" t="b">
         <v>0</v>
@@ -18269,10 +18269,10 @@
         <v>111.909430537391</v>
       </c>
       <c r="J469" t="n">
-        <v>0.06032553753670859</v>
+        <v>0.03013868796811938</v>
       </c>
       <c r="K469" t="n">
-        <v>0.8331574367681922</v>
+        <v>0.5664179744239506</v>
       </c>
       <c r="L469" t="b">
         <v>0</v>
@@ -18307,10 +18307,10 @@
         <v>36.59643162801245</v>
       </c>
       <c r="J470" t="n">
-        <v>0.06320686255891818</v>
+        <v>0.08771605860601493</v>
       </c>
       <c r="K470" t="n">
-        <v>0.8573671703950888</v>
+        <v>1.055619895415107</v>
       </c>
       <c r="L470" t="b">
         <v>0</v>
@@ -18345,10 +18345,10 @@
         <v>112.8534875182309</v>
       </c>
       <c r="J471" t="n">
-        <v>0.02085661178265439</v>
+        <v>0.1058842610451422</v>
       </c>
       <c r="K471" t="n">
-        <v>0.5015280052809233</v>
+        <v>1.209984699429404</v>
       </c>
       <c r="L471" t="b">
         <v>0</v>
@@ -18383,10 +18383,10 @@
         <v>37.52615629066072</v>
       </c>
       <c r="J472" t="n">
-        <v>0.2406445861710173</v>
+        <v>0.3006632120475224</v>
       </c>
       <c r="K472" t="n">
-        <v>2.348250701721788</v>
+        <v>2.864909819200199</v>
       </c>
       <c r="L472" t="b">
         <v>0</v>
@@ -18421,10 +18421,10 @@
         <v>23.0016980042445</v>
       </c>
       <c r="J473" t="n">
-        <v>0.08981066241424038</v>
+        <v>0.1589177611187168</v>
       </c>
       <c r="K473" t="n">
-        <v>1.080900059949736</v>
+        <v>1.660579956306275</v>
       </c>
       <c r="L473" t="b">
         <v>0</v>
@@ -18459,10 +18459,10 @@
         <v>66.33736534574489</v>
       </c>
       <c r="J474" t="n">
-        <v>0.07701768039884478</v>
+        <v>0.07482191921249687</v>
       </c>
       <c r="K474" t="n">
-        <v>0.9734096919769849</v>
+        <v>0.9460657825587417</v>
       </c>
       <c r="L474" t="b">
         <v>0</v>
@@ -18497,10 +18497,10 @@
         <v>32.10825636304752</v>
       </c>
       <c r="J475" t="n">
-        <v>0.08080751008646492</v>
+        <v>0.03502612259747553</v>
       </c>
       <c r="K475" t="n">
-        <v>1.005252946910518</v>
+        <v>0.6079437055038984</v>
       </c>
       <c r="L475" t="b">
         <v>0</v>
@@ -18535,10 +18535,10 @@
         <v>60.7786924425962</v>
       </c>
       <c r="J476" t="n">
-        <v>0.03392812900184147</v>
+        <v>0.09065871897079229</v>
       </c>
       <c r="K476" t="n">
-        <v>0.611358707314403</v>
+        <v>1.08062199410987</v>
       </c>
       <c r="L476" t="b">
         <v>0</v>
@@ -18573,10 +18573,10 @@
         <v>26.01948629957696</v>
       </c>
       <c r="J477" t="n">
-        <v>0.07937059102767181</v>
+        <v>0.1054624230164757</v>
       </c>
       <c r="K477" t="n">
-        <v>0.9931795336757575</v>
+        <v>1.206400583453205</v>
       </c>
       <c r="L477" t="b">
         <v>0</v>
@@ -18611,10 +18611,10 @@
         <v>68.16226767260881</v>
       </c>
       <c r="J478" t="n">
-        <v>0.06824553912788718</v>
+        <v>0.04405805304183842</v>
       </c>
       <c r="K478" t="n">
-        <v>0.8997036012477519</v>
+        <v>0.6846828423329908</v>
       </c>
       <c r="L478" t="b">
         <v>0</v>
@@ -18649,10 +18649,10 @@
         <v>113.1650583260667</v>
       </c>
       <c r="J479" t="n">
-        <v>0.1412870392480685</v>
+        <v>0.08186642964569843</v>
       </c>
       <c r="K479" t="n">
-        <v>1.513419599265379</v>
+        <v>1.005918950534014</v>
       </c>
       <c r="L479" t="b">
         <v>0</v>
@@ -18687,10 +18687,10 @@
         <v>29.6713629892639</v>
       </c>
       <c r="J480" t="n">
-        <v>0.1471869493010527</v>
+        <v>0.1913071479493404</v>
       </c>
       <c r="K480" t="n">
-        <v>1.562992365164543</v>
+        <v>1.93577401400154</v>
       </c>
       <c r="L480" t="b">
         <v>0</v>
@@ -18725,10 +18725,10 @@
         <v>35.76141077361547</v>
       </c>
       <c r="J481" t="n">
-        <v>0.03051032849347628</v>
+        <v>0.02857031578713433</v>
       </c>
       <c r="K481" t="n">
-        <v>0.5826413501056216</v>
+        <v>0.5530924148288066</v>
       </c>
       <c r="L481" t="b">
         <v>0</v>
@@ -18763,10 +18763,10 @@
         <v>180.7622382130921</v>
       </c>
       <c r="J482" t="n">
-        <v>0.04843589253196012</v>
+        <v>0.1156591775955589</v>
       </c>
       <c r="K482" t="n">
-        <v>0.7332571699587981</v>
+        <v>1.293036563399809</v>
       </c>
       <c r="L482" t="b">
         <v>0</v>
@@ -18801,10 +18801,10 @@
         <v>107.3342802351012</v>
       </c>
       <c r="J483" t="n">
-        <v>0.5315113848846373</v>
+        <v>0.5993268858671351</v>
       </c>
       <c r="K483" t="n">
-        <v>4.792198421429143</v>
+        <v>5.402483892905259</v>
       </c>
       <c r="L483" t="b">
         <v>0</v>
@@ -18839,10 +18839,10 @@
         <v>84.1750803010831</v>
       </c>
       <c r="J484" t="n">
-        <v>0.1409741224042263</v>
+        <v>0.08414922955808216</v>
       </c>
       <c r="K484" t="n">
-        <v>1.510790380632148</v>
+        <v>1.025314593127695</v>
       </c>
       <c r="L484" t="b">
         <v>0</v>
@@ -18877,10 +18877,10 @@
         <v>23.35790148882349</v>
       </c>
       <c r="J485" t="n">
-        <v>0.03823609881386357</v>
+        <v>0.04119834799346658</v>
       </c>
       <c r="K485" t="n">
-        <v>0.6475555267699833</v>
+        <v>0.6603855674204255</v>
       </c>
       <c r="L485" t="b">
         <v>0</v>
@@ -18915,10 +18915,10 @@
         <v>88.15393174999588</v>
       </c>
       <c r="J486" t="n">
-        <v>0.04880309111882454</v>
+        <v>0.06140354170476633</v>
       </c>
       <c r="K486" t="n">
-        <v>0.7363424796366849</v>
+        <v>0.8320575188842991</v>
       </c>
       <c r="L486" t="b">
         <v>0</v>
@@ -18953,10 +18953,10 @@
         <v>112.130190147089</v>
       </c>
       <c r="J487" t="n">
-        <v>0.05182220109333333</v>
+        <v>0.0376100272985385</v>
       </c>
       <c r="K487" t="n">
-        <v>0.761709922639388</v>
+        <v>0.629897662925256</v>
       </c>
       <c r="L487" t="b">
         <v>0</v>
@@ -18991,10 +18991,10 @@
         <v>72.23537045646634</v>
       </c>
       <c r="J488" t="n">
-        <v>0.1102150090126836</v>
+        <v>0.128509816546102</v>
       </c>
       <c r="K488" t="n">
-        <v>1.252343334197348</v>
+        <v>1.402221077922114</v>
       </c>
       <c r="L488" t="b">
         <v>0</v>
@@ -19029,10 +19029,10 @@
         <v>191.2320899311428</v>
       </c>
       <c r="J489" t="n">
-        <v>0.0525577064369807</v>
+        <v>0.0577921413602711</v>
       </c>
       <c r="K489" t="n">
-        <v>0.7678898531621885</v>
+        <v>0.8013735198335957</v>
       </c>
       <c r="L489" t="b">
         <v>0</v>
@@ -19067,10 +19067,10 @@
         <v>102.8457868593067</v>
       </c>
       <c r="J490" t="n">
-        <v>0.7447201762493677</v>
+        <v>0.8172930999405955</v>
       </c>
       <c r="K490" t="n">
-        <v>6.583640902254971</v>
+        <v>7.254417898480123</v>
       </c>
       <c r="L490" t="b">
         <v>0</v>
@@ -19105,10 +19105,10 @@
         <v>36.08685374232218</v>
       </c>
       <c r="J491" t="n">
-        <v>0.1692411490475091</v>
+        <v>0.2896143770444587</v>
       </c>
       <c r="K491" t="n">
-        <v>1.748298187000161</v>
+        <v>2.771034200214298</v>
       </c>
       <c r="L491" t="b">
         <v>0</v>
@@ -19143,10 +19143,10 @@
         <v>23.51379777477309</v>
       </c>
       <c r="J492" t="n">
-        <v>0.08913540938976199</v>
+        <v>0.1058023667682627</v>
       </c>
       <c r="K492" t="n">
-        <v>1.075226386994631</v>
+        <v>1.209288890691982</v>
       </c>
       <c r="L492" t="b">
         <v>0</v>
@@ -19181,10 +19181,10 @@
         <v>62.9675960070216</v>
       </c>
       <c r="J493" t="n">
-        <v>0.04247427815197823</v>
+        <v>0.03082559190159217</v>
       </c>
       <c r="K493" t="n">
-        <v>0.6831659462984572</v>
+        <v>0.5722542034852705</v>
       </c>
       <c r="L493" t="b">
         <v>0</v>
@@ -19219,10 +19219,10 @@
         <v>23.00496465771255</v>
       </c>
       <c r="J494" t="n">
-        <v>0.1656927155932165</v>
+        <v>0.1877719246424107</v>
       </c>
       <c r="K494" t="n">
-        <v>1.718483213660113</v>
+        <v>1.90573724758233</v>
       </c>
       <c r="L494" t="b">
         <v>0</v>
@@ -19257,10 +19257,10 @@
         <v>123.7553397030513</v>
       </c>
       <c r="J495" t="n">
-        <v>0.05371018058261846</v>
+        <v>0.04604645067863952</v>
       </c>
       <c r="K495" t="n">
-        <v>0.7775732772336523</v>
+        <v>0.7015771175115999</v>
       </c>
       <c r="L495" t="b">
         <v>0</v>
@@ -19295,10 +19295,10 @@
         <v>28.05252995446849</v>
       </c>
       <c r="J496" t="n">
-        <v>0.1473806098374094</v>
+        <v>0.1452063159700391</v>
       </c>
       <c r="K496" t="n">
-        <v>1.564619557502477</v>
+        <v>1.544081664842384</v>
       </c>
       <c r="L496" t="b">
         <v>0</v>
@@ -19333,10 +19333,10 @@
         <v>10.03575925202857</v>
       </c>
       <c r="J497" t="n">
-        <v>0.1004297499701479</v>
+        <v>0.05661052326288932</v>
       </c>
       <c r="K497" t="n">
-        <v>1.170124732316641</v>
+        <v>0.7913339880398909</v>
       </c>
       <c r="L497" t="b">
         <v>0</v>
@@ -19371,10 +19371,10 @@
         <v>21.28612946507161</v>
       </c>
       <c r="J498" t="n">
-        <v>0.1599283399960324</v>
+        <v>0.1178266694790487</v>
       </c>
       <c r="K498" t="n">
-        <v>1.670049247808461</v>
+        <v>1.311452499754465</v>
       </c>
       <c r="L498" t="b">
         <v>0</v>
@@ -19409,10 +19409,10 @@
         <v>64.5040466193194</v>
       </c>
       <c r="J499" t="n">
-        <v>0.08471899527354161</v>
+        <v>0.07990525454244687</v>
       </c>
       <c r="K499" t="n">
-        <v>1.03811838685039</v>
+        <v>0.9892559696218697</v>
       </c>
       <c r="L499" t="b">
         <v>0</v>
@@ -19447,10 +19447,10 @@
         <v>58.93185088927868</v>
       </c>
       <c r="J500" t="n">
-        <v>0.1570312910647176</v>
+        <v>0.120170739124764</v>
       </c>
       <c r="K500" t="n">
-        <v>1.645707397308918</v>
+        <v>1.331368716158871</v>
       </c>
       <c r="L500" t="b">
         <v>0</v>
@@ -19485,10 +19485,10 @@
         <v>19.34890285763798</v>
       </c>
       <c r="J501" t="n">
-        <v>0.05349947078577948</v>
+        <v>0.1028243111640211</v>
       </c>
       <c r="K501" t="n">
-        <v>0.7758028320340555</v>
+        <v>1.183986058932335</v>
       </c>
       <c r="L501" t="b">
         <v>0</v>
@@ -19523,10 +19523,10 @@
         <v>32.11741141218442</v>
       </c>
       <c r="J502" t="n">
-        <v>0.08396262427564671</v>
+        <v>0.1025533655093114</v>
       </c>
       <c r="K502" t="n">
-        <v>1.031763137011861</v>
+        <v>1.181683988981941</v>
       </c>
       <c r="L502" t="b">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>197.9463982462871</v>
       </c>
       <c r="J503" t="n">
-        <v>0.06901829138570457</v>
+        <v>0.05049079296674199</v>
       </c>
       <c r="K503" t="n">
-        <v>0.9061964912123126</v>
+        <v>0.7393381469020421</v>
       </c>
       <c r="L503" t="b">
         <v>0</v>
@@ -19599,10 +19599,10 @@
         <v>35.47657079308648</v>
       </c>
       <c r="J504" t="n">
-        <v>0.4369049320139823</v>
+        <v>0.3072504025271042</v>
       </c>
       <c r="K504" t="n">
-        <v>3.997287397601754</v>
+        <v>2.920877401617468</v>
       </c>
       <c r="L504" t="b">
         <v>0</v>
@@ -19637,10 +19637,10 @@
         <v>102.0870426865709</v>
       </c>
       <c r="J505" t="n">
-        <v>0.1707657383157632</v>
+        <v>0.1162601170940918</v>
       </c>
       <c r="K505" t="n">
-        <v>1.761108230917578</v>
+        <v>1.298142401923256</v>
       </c>
       <c r="L505" t="b">
         <v>0</v>
@@ -19675,10 +19675,10 @@
         <v>31.35140164120255</v>
       </c>
       <c r="J506" t="n">
-        <v>0.2918766853741903</v>
+        <v>0.4636383760798014</v>
       </c>
       <c r="K506" t="n">
-        <v>2.778717749102787</v>
+        <v>4.249616387686074</v>
       </c>
       <c r="L506" t="b">
         <v>0</v>
@@ -19713,10 +19713,10 @@
         <v>74.57242336617503</v>
       </c>
       <c r="J507" t="n">
-        <v>0.05936588453448637</v>
+        <v>0.07063819516692019</v>
       </c>
       <c r="K507" t="n">
-        <v>0.8250941522102304</v>
+        <v>0.910519077015958</v>
       </c>
       <c r="L507" t="b">
         <v>0</v>
@@ -19751,10 +19751,10 @@
         <v>122.1648827176944</v>
       </c>
       <c r="J508" t="n">
-        <v>0.09740908597330927</v>
+        <v>0.2853217492063947</v>
       </c>
       <c r="K508" t="n">
-        <v>1.144744231964848</v>
+        <v>2.734562201558998</v>
       </c>
       <c r="L508" t="b">
         <v>0</v>
@@ -19789,10 +19789,10 @@
         <v>30.71397688287655</v>
       </c>
       <c r="J509" t="n">
-        <v>0.04759180993391412</v>
+        <v>0.2197234738324928</v>
       </c>
       <c r="K509" t="n">
-        <v>0.726164941660957</v>
+        <v>2.177211249768598</v>
       </c>
       <c r="L509" t="b">
         <v>0</v>
@@ -19827,10 +19827,10 @@
         <v>33.38310772255179</v>
       </c>
       <c r="J510" t="n">
-        <v>0.06409479966216731</v>
+        <v>0.02307511961812956</v>
       </c>
       <c r="K510" t="n">
-        <v>0.8648278770426904</v>
+        <v>0.506402882251731</v>
       </c>
       <c r="L510" t="b">
         <v>0</v>
@@ -19865,10 +19865,10 @@
         <v>77.18092688478843</v>
       </c>
       <c r="J511" t="n">
-        <v>0.1283088679135468</v>
+        <v>0.06564535229215623</v>
       </c>
       <c r="K511" t="n">
-        <v>1.404373216593824</v>
+        <v>0.8680977524837474</v>
       </c>
       <c r="L511" t="b">
         <v>0</v>
@@ -19903,10 +19903,10 @@
         <v>68.74764705778755</v>
       </c>
       <c r="J512" t="n">
-        <v>0.08263693103991433</v>
+        <v>0.2527076315920819</v>
       </c>
       <c r="K512" t="n">
-        <v>1.020624275598911</v>
+        <v>2.457458735186875</v>
       </c>
       <c r="L512" t="b">
         <v>0</v>
@@ -19941,10 +19941,10 @@
         <v>39.25973160334085</v>
       </c>
       <c r="J513" t="n">
-        <v>0.01738191666656911</v>
+        <v>0.0910859923319232</v>
       </c>
       <c r="K513" t="n">
-        <v>0.4723326029758432</v>
+        <v>1.084252290991055</v>
       </c>
       <c r="L513" t="b">
         <v>0</v>
@@ -19979,10 +19979,10 @@
         <v>167.4548762408798</v>
       </c>
       <c r="J514" t="n">
-        <v>0.1267078162920654</v>
+        <v>0.1216105793286544</v>
       </c>
       <c r="K514" t="n">
-        <v>1.390920713672355</v>
+        <v>1.34360221320571</v>
       </c>
       <c r="L514" t="b">
         <v>0</v>
@@ -20017,10 +20017,10 @@
         <v>90.56998277215375</v>
       </c>
       <c r="J515" t="n">
-        <v>0.2880055574319705</v>
+        <v>0.358662680267523</v>
       </c>
       <c r="K515" t="n">
-        <v>2.746191402510723</v>
+        <v>3.357698061444372</v>
       </c>
       <c r="L515" t="b">
         <v>0</v>
@@ -20055,10 +20055,10 @@
         <v>30.31569049053353</v>
       </c>
       <c r="J516" t="n">
-        <v>0.1023460375691674</v>
+        <v>0.1291859792720434</v>
       </c>
       <c r="K516" t="n">
-        <v>1.186225939909392</v>
+        <v>1.407966045098775</v>
       </c>
       <c r="L516" t="b">
         <v>0</v>
@@ -20093,10 +20093,10 @@
         <v>29.23924703057298</v>
       </c>
       <c r="J517" t="n">
-        <v>0.09226816234966533</v>
+        <v>0.07607465308893091</v>
       </c>
       <c r="K517" t="n">
-        <v>1.101548691522418</v>
+        <v>0.9567095443709369</v>
       </c>
       <c r="L517" t="b">
         <v>0</v>
@@ -20131,10 +20131,10 @@
         <v>29.73800201205247</v>
       </c>
       <c r="J518" t="n">
-        <v>0.06005269213835833</v>
+        <v>0.06649248997421414</v>
       </c>
       <c r="K518" t="n">
-        <v>0.8308649101131054</v>
+        <v>0.875295395877591</v>
       </c>
       <c r="L518" t="b">
         <v>0</v>
@@ -20169,10 +20169,10 @@
         <v>82.32467740121612</v>
       </c>
       <c r="J519" t="n">
-        <v>0.07737856355964483</v>
+        <v>0.04409123153619996</v>
       </c>
       <c r="K519" t="n">
-        <v>0.9764419376021944</v>
+        <v>0.6849647409851425</v>
       </c>
       <c r="L519" t="b">
         <v>0</v>
@@ -20207,10 +20207,10 @@
         <v>110.3127089520582</v>
       </c>
       <c r="J520" t="n">
-        <v>0.1043293952525809</v>
+        <v>0.08685052873028465</v>
       </c>
       <c r="K520" t="n">
-        <v>1.202890689922731</v>
+        <v>1.048265984092109</v>
       </c>
       <c r="L520" t="b">
         <v>0</v>
@@ -20245,10 +20245,10 @@
         <v>36.847810918626</v>
       </c>
       <c r="J521" t="n">
-        <v>0.07081061412561344</v>
+        <v>0.07513669109048769</v>
       </c>
       <c r="K521" t="n">
-        <v>0.9212561098850257</v>
+        <v>0.9487402188117541</v>
       </c>
       <c r="L521" t="b">
         <v>0</v>
@@ -20283,10 +20283,10 @@
         <v>107.7767643535795</v>
       </c>
       <c r="J522" t="n">
-        <v>0.05873961924079202</v>
+        <v>0.09150166505736555</v>
       </c>
       <c r="K522" t="n">
-        <v>0.8198320884641268</v>
+        <v>1.087784023919064</v>
       </c>
       <c r="L522" t="b">
         <v>0</v>
@@ -20321,10 +20321,10 @@
         <v>80.34852903292273</v>
       </c>
       <c r="J523" t="n">
-        <v>0.07822217601696123</v>
+        <v>0.1787793573342376</v>
       </c>
       <c r="K523" t="n">
-        <v>0.9835302156404351</v>
+        <v>1.829332556762615</v>
       </c>
       <c r="L523" t="b">
         <v>0</v>
@@ -20359,10 +20359,10 @@
         <v>109.2869102708129</v>
       </c>
       <c r="J524" t="n">
-        <v>0.03357481916213464</v>
+        <v>0.05728562114922373</v>
       </c>
       <c r="K524" t="n">
-        <v>0.6083900949429655</v>
+        <v>0.7970699078846657</v>
       </c>
       <c r="L524" t="b">
         <v>0</v>
@@ -20397,10 +20397,10 @@
         <v>19.75129116113188</v>
       </c>
       <c r="J525" t="n">
-        <v>0.1947645751039089</v>
+        <v>0.2839180701527603</v>
       </c>
       <c r="K525" t="n">
-        <v>1.96275346063582</v>
+        <v>2.722635945082099</v>
       </c>
       <c r="L525" t="b">
         <v>0</v>
@@ -20435,10 +20435,10 @@
         <v>15.80353130913914</v>
       </c>
       <c r="J526" t="n">
-        <v>0.07198628847367648</v>
+        <v>0.1098442796000836</v>
       </c>
       <c r="K526" t="n">
-        <v>0.931134468827244</v>
+        <v>1.243630707622819</v>
       </c>
       <c r="L526" t="b">
         <v>0</v>
@@ -20473,10 +20473,10 @@
         <v>32.09748658067192</v>
       </c>
       <c r="J527" t="n">
-        <v>0.1229055193056709</v>
+        <v>0.1113790923583534</v>
       </c>
       <c r="K527" t="n">
-        <v>1.358972704856478</v>
+        <v>1.256671132035899</v>
       </c>
       <c r="L527" t="b">
         <v>0</v>
@@ -20511,10 +20511,10 @@
         <v>26.12357195159274</v>
       </c>
       <c r="J528" t="n">
-        <v>0.06051888373530748</v>
+        <v>0.03462917498297585</v>
       </c>
       <c r="K528" t="n">
-        <v>0.8347819879485595</v>
+        <v>0.6045710691122967</v>
       </c>
       <c r="L528" t="b">
         <v>0</v>
@@ -20549,10 +20549,10 @@
         <v>36.7662961966988</v>
       </c>
       <c r="J529" t="n">
-        <v>0.06322294853365397</v>
+        <v>0.05431939210735244</v>
       </c>
       <c r="K529" t="n">
-        <v>0.857502329448816</v>
+        <v>0.7718675596477329</v>
       </c>
       <c r="L529" t="b">
         <v>0</v>
@@ -20587,10 +20587,10 @@
         <v>37.41282177601908</v>
       </c>
       <c r="J530" t="n">
-        <v>0.1231087195509108</v>
+        <v>0.08388084271433748</v>
       </c>
       <c r="K530" t="n">
-        <v>1.360680052612201</v>
+        <v>1.023034263927629</v>
       </c>
       <c r="L530" t="b">
         <v>0</v>
@@ -20625,10 +20625,10 @@
         <v>104.3093832153045</v>
       </c>
       <c r="J531" t="n">
-        <v>0.02442518492686441</v>
+        <v>0.116703095057265</v>
       </c>
       <c r="K531" t="n">
-        <v>0.5315121981725563</v>
+        <v>1.301906131807761</v>
       </c>
       <c r="L531" t="b">
         <v>0</v>
@@ -20663,10 +20663,10 @@
         <v>113.985090203465</v>
       </c>
       <c r="J532" t="n">
-        <v>0.1840798432478286</v>
+        <v>0.1032671929345428</v>
       </c>
       <c r="K532" t="n">
-        <v>1.87297722570341</v>
+        <v>1.187748971523009</v>
       </c>
       <c r="L532" t="b">
         <v>0</v>
@@ -20701,10 +20701,10 @@
         <v>53.16402270022166</v>
       </c>
       <c r="J533" t="n">
-        <v>0.02711803537558052</v>
+        <v>0.05401068199635715</v>
       </c>
       <c r="K533" t="n">
-        <v>0.5541383134347948</v>
+        <v>0.7692446267549118</v>
       </c>
       <c r="L533" t="b">
         <v>0</v>
@@ -20739,10 +20739,10 @@
         <v>118.421866175239</v>
       </c>
       <c r="J534" t="n">
-        <v>0.02501617293904246</v>
+        <v>0.06367292850386676</v>
       </c>
       <c r="K534" t="n">
-        <v>0.5364778519052087</v>
+        <v>0.8513391979414044</v>
       </c>
       <c r="L534" t="b">
         <v>0</v>
@@ -20777,10 +20777,10 @@
         <v>37.5962724829703</v>
       </c>
       <c r="J535" t="n">
-        <v>0.1621417611450527</v>
+        <v>0.06334549052469372</v>
       </c>
       <c r="K535" t="n">
-        <v>1.688647058193916</v>
+        <v>0.8485571450855298</v>
       </c>
       <c r="L535" t="b">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>105.0233979468545</v>
       </c>
       <c r="J536" t="n">
-        <v>0.03557970873361204</v>
+        <v>0.05393658854006137</v>
       </c>
       <c r="K536" t="n">
-        <v>0.6252357621629685</v>
+        <v>0.7686150971193763</v>
       </c>
       <c r="L536" t="b">
         <v>0</v>
@@ -20853,10 +20853,10 @@
         <v>22.15168916874355</v>
       </c>
       <c r="J537" t="n">
-        <v>0.07529475844562802</v>
+        <v>0.01796026674829854</v>
       </c>
       <c r="K537" t="n">
-        <v>0.9589331989656817</v>
+        <v>0.4629449087147873</v>
       </c>
       <c r="L537" t="b">
         <v>0</v>
@@ -20891,10 +20891,10 @@
         <v>156.634181072256</v>
       </c>
       <c r="J538" t="n">
-        <v>0.07977553210942981</v>
+        <v>0.07183757772085909</v>
       </c>
       <c r="K538" t="n">
-        <v>0.9965819668092575</v>
+        <v>0.9207095432163026</v>
       </c>
       <c r="L538" t="b">
         <v>0</v>
@@ -20929,10 +20929,10 @@
         <v>35.89613802985006</v>
       </c>
       <c r="J539" t="n">
-        <v>0.1926362220915088</v>
+        <v>0.1450362276972136</v>
       </c>
       <c r="K539" t="n">
-        <v>1.94487041755771</v>
+        <v>1.542636522264972</v>
       </c>
       <c r="L539" t="b">
         <v>0</v>
@@ -20967,10 +20967,10 @@
         <v>122.5303232713791</v>
       </c>
       <c r="J540" t="n">
-        <v>0.07110730662643099</v>
+        <v>0.06228257200532102</v>
       </c>
       <c r="K540" t="n">
-        <v>0.9237490068537898</v>
+        <v>0.8395261355800009</v>
       </c>
       <c r="L540" t="b">
         <v>0</v>
@@ -21005,10 +21005,10 @@
         <v>19.15164671833609</v>
       </c>
       <c r="J541" t="n">
-        <v>0.0609297387965126</v>
+        <v>0.1034276733797668</v>
       </c>
       <c r="K541" t="n">
-        <v>0.8382341120631137</v>
+        <v>1.189112481895492</v>
       </c>
       <c r="L541" t="b">
         <v>0</v>
@@ -21043,10 +21043,10 @@
         <v>75.98242927724901</v>
       </c>
       <c r="J542" t="n">
-        <v>0.0590204094369645</v>
+        <v>0.103824154038371</v>
       </c>
       <c r="K542" t="n">
-        <v>0.8221913696288622</v>
+        <v>1.19248115083046</v>
       </c>
       <c r="L542" t="b">
         <v>0</v>
@@ -21081,10 +21081,10 @@
         <v>66.52876180755692</v>
       </c>
       <c r="J543" t="n">
-        <v>0.07555221033575125</v>
+        <v>0.1308437392970578</v>
       </c>
       <c r="K543" t="n">
-        <v>0.9610963848727145</v>
+        <v>1.422051081976885</v>
       </c>
       <c r="L543" t="b">
         <v>0</v>
@@ -21119,10 +21119,10 @@
         <v>109.5016221694137</v>
       </c>
       <c r="J544" t="n">
-        <v>0.09811880847358952</v>
+        <v>0.06134713436110744</v>
       </c>
       <c r="K544" t="n">
-        <v>1.150707527514068</v>
+        <v>0.8315782580120117</v>
       </c>
       <c r="L544" t="b">
         <v>0</v>
@@ -21157,10 +21157,10 @@
         <v>31.52740948598641</v>
       </c>
       <c r="J545" t="n">
-        <v>0.0856151367595638</v>
+        <v>0.05629511665671514</v>
       </c>
       <c r="K545" t="n">
-        <v>1.045648029116145</v>
+        <v>0.7886541588652645</v>
       </c>
       <c r="L545" t="b">
         <v>0</v>
@@ -21195,10 +21195,10 @@
         <v>64.33955900571213</v>
       </c>
       <c r="J546" t="n">
-        <v>0.04312697092628188</v>
+        <v>0.01977672913282852</v>
       </c>
       <c r="K546" t="n">
-        <v>0.6886500614483592</v>
+        <v>0.4783783485901293</v>
       </c>
       <c r="L546" t="b">
         <v>0</v>
@@ -21233,10 +21233,10 @@
         <v>87.21586237030168</v>
       </c>
       <c r="J547" t="n">
-        <v>0.02631943419528536</v>
+        <v>0.09820506849683359</v>
       </c>
       <c r="K547" t="n">
-        <v>0.5474282332806841</v>
+        <v>1.144739001255389</v>
       </c>
       <c r="L547" t="b">
         <v>0</v>
@@ -21271,10 +21271,10 @@
         <v>35.78822363629154</v>
       </c>
       <c r="J548" t="n">
-        <v>0.1837321073227859</v>
+        <v>0.04031371945658584</v>
       </c>
       <c r="K548" t="n">
-        <v>1.870055446989486</v>
+        <v>0.6528693857189842</v>
       </c>
       <c r="L548" t="b">
         <v>0</v>
@@ -21309,10 +21309,10 @@
         <v>164.4506104272355</v>
       </c>
       <c r="J549" t="n">
-        <v>0.05267531833171304</v>
+        <v>0.119099897505624</v>
       </c>
       <c r="K549" t="n">
-        <v>0.7688780626216826</v>
+        <v>1.32227038861531</v>
       </c>
       <c r="L549" t="b">
         <v>0</v>
@@ -21347,10 +21347,10 @@
         <v>66.92875839996431</v>
       </c>
       <c r="J550" t="n">
-        <v>0.4665575997176132</v>
+        <v>0.5079005071208909</v>
       </c>
       <c r="K550" t="n">
-        <v>4.246437764498323</v>
+        <v>4.625686348724064</v>
       </c>
       <c r="L550" t="b">
         <v>0</v>
@@ -21385,10 +21385,10 @@
         <v>106.2137689608971</v>
       </c>
       <c r="J551" t="n">
-        <v>0.1015895030866956</v>
+        <v>0.1202288332825067</v>
       </c>
       <c r="K551" t="n">
-        <v>1.179869316425743</v>
+        <v>1.331862308923724</v>
       </c>
       <c r="L551" t="b">
         <v>0</v>
@@ -21423,10 +21423,10 @@
         <v>110.5647459709532</v>
       </c>
       <c r="J552" t="n">
-        <v>0.08205807610163883</v>
+        <v>0.06883846891880947</v>
       </c>
       <c r="K552" t="n">
-        <v>1.015760567493701</v>
+        <v>0.8952278345003697</v>
       </c>
       <c r="L552" t="b">
         <v>0</v>
@@ -21461,10 +21461,10 @@
         <v>16.8966277638494</v>
       </c>
       <c r="J553" t="n">
-        <v>0.2659907798927381</v>
+        <v>0.2760920105176667</v>
       </c>
       <c r="K553" t="n">
-        <v>2.561216817563869</v>
+        <v>2.656142401440506</v>
       </c>
       <c r="L553" t="b">
         <v>0</v>
@@ -21499,10 +21499,10 @@
         <v>23.50385472854057</v>
       </c>
       <c r="J554" t="n">
-        <v>0.04439895086687057</v>
+        <v>0.09129315820966728</v>
       </c>
       <c r="K554" t="n">
-        <v>0.6993376080816067</v>
+        <v>1.086012460728461</v>
       </c>
       <c r="L554" t="b">
         <v>0</v>
@@ -21537,10 +21537,10 @@
         <v>27.26777842911566</v>
       </c>
       <c r="J555" t="n">
-        <v>0.03115200396147299</v>
+        <v>0.04347036660964033</v>
       </c>
       <c r="K555" t="n">
-        <v>0.5880328946330076</v>
+        <v>0.6796896075189209</v>
       </c>
       <c r="L555" t="b">
         <v>0</v>
@@ -21575,10 +21575,10 @@
         <v>64.31035972269635</v>
       </c>
       <c r="J556" t="n">
-        <v>0.02375044919386916</v>
+        <v>0.03265670338203579</v>
       </c>
       <c r="K556" t="n">
-        <v>0.5258428716514418</v>
+        <v>0.587812108333263</v>
       </c>
       <c r="L556" t="b">
         <v>0</v>
@@ -21613,10 +21613,10 @@
         <v>105.2162277874393</v>
       </c>
       <c r="J557" t="n">
-        <v>0.1415471380524675</v>
+        <v>0.05829234935972551</v>
       </c>
       <c r="K557" t="n">
-        <v>1.515605025318545</v>
+        <v>0.805623500538119</v>
       </c>
       <c r="L557" t="b">
         <v>0</v>
@@ -21651,10 +21651,10 @@
         <v>35.17628657583932</v>
       </c>
       <c r="J558" t="n">
-        <v>0.06166757812949387</v>
+        <v>0.05741033556331052</v>
       </c>
       <c r="K558" t="n">
-        <v>0.8444336534453716</v>
+        <v>0.7981295347879198</v>
       </c>
       <c r="L558" t="b">
         <v>0</v>
@@ -21689,10 +21689,10 @@
         <v>120.5449675831407</v>
       </c>
       <c r="J559" t="n">
-        <v>0.0265962570017803</v>
+        <v>0.04228908391102425</v>
       </c>
       <c r="K559" t="n">
-        <v>0.5497541792796374</v>
+        <v>0.6696529254163127</v>
       </c>
       <c r="L559" t="b">
         <v>0</v>
@@ -21727,10 +21727,10 @@
         <v>28.79223786463329</v>
       </c>
       <c r="J560" t="n">
-        <v>0.04503220442579003</v>
+        <v>0.04758448127096806</v>
       </c>
       <c r="K560" t="n">
-        <v>0.7046583892713552</v>
+        <v>0.7146448820165506</v>
       </c>
       <c r="L560" t="b">
         <v>0</v>
@@ -21765,10 +21765,10 @@
         <v>20.01473008672138</v>
       </c>
       <c r="J561" t="n">
-        <v>0.04850366192482005</v>
+        <v>0.04516390774031567</v>
       </c>
       <c r="K561" t="n">
-        <v>0.7338265881731783</v>
+        <v>0.6940786559458498</v>
       </c>
       <c r="L561" t="b">
         <v>0</v>
@@ -21803,10 +21803,10 @@
         <v>110.0100769180797</v>
       </c>
       <c r="J562" t="n">
-        <v>0.1259330826819368</v>
+        <v>0.09366061096747773</v>
       </c>
       <c r="K562" t="n">
-        <v>1.384411175807504</v>
+        <v>1.106127350035588</v>
       </c>
       <c r="L562" t="b">
         <v>0</v>
@@ -21841,10 +21841,10 @@
         <v>119.2457103378272</v>
       </c>
       <c r="J563" t="n">
-        <v>0.1156085440928882</v>
+        <v>0.2222722260554981</v>
       </c>
       <c r="K563" t="n">
-        <v>1.297661389811546</v>
+        <v>2.198866536729619</v>
       </c>
       <c r="L563" t="b">
         <v>0</v>
@@ -21879,10 +21879,10 @@
         <v>16.05094214270119</v>
       </c>
       <c r="J564" t="n">
-        <v>0.08748919246291165</v>
+        <v>0.07774595860019948</v>
       </c>
       <c r="K564" t="n">
-        <v>1.061394391997909</v>
+        <v>0.9709096694828947</v>
       </c>
       <c r="L564" t="b">
         <v>0</v>
@@ -21917,10 +21917,10 @@
         <v>25.47728771939664</v>
       </c>
       <c r="J565" t="n">
-        <v>0.17056831087525</v>
+        <v>0.1571896116794609</v>
       </c>
       <c r="K565" t="n">
-        <v>1.759449387951712</v>
+        <v>1.645896860915194</v>
       </c>
       <c r="L565" t="b">
         <v>0</v>
@@ -21955,10 +21955,10 @@
         <v>84.29527444505138</v>
       </c>
       <c r="J566" t="n">
-        <v>0.08144479012648656</v>
+        <v>0.08612352554622681</v>
       </c>
       <c r="K566" t="n">
-        <v>1.010607559769442</v>
+        <v>1.042089054679259</v>
       </c>
       <c r="L566" t="b">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>77.37938228590966</v>
       </c>
       <c r="J567" t="n">
-        <v>0.4556346364375289</v>
+        <v>0.3758595320352213</v>
       </c>
       <c r="K567" t="n">
-        <v>4.154659839623877</v>
+        <v>3.503809855480017</v>
       </c>
       <c r="L567" t="b">
         <v>0</v>
@@ -22031,10 +22031,10 @@
         <v>30.38084929980743</v>
       </c>
       <c r="J568" t="n">
-        <v>0.3097108864558229</v>
+        <v>0.3471375528595607</v>
       </c>
       <c r="K568" t="n">
-        <v>2.928565910732166</v>
+        <v>3.259775658854974</v>
       </c>
       <c r="L568" t="b">
         <v>0</v>
@@ -22069,10 +22069,10 @@
         <v>105.9225915670005</v>
       </c>
       <c r="J569" t="n">
-        <v>0.08869604746236008</v>
+        <v>0.08427028587812213</v>
       </c>
       <c r="K569" t="n">
-        <v>1.071534739871794</v>
+        <v>1.02634313930227</v>
       </c>
       <c r="L569" t="b">
         <v>0</v>
@@ -22107,10 +22107,10 @@
         <v>77.66472354503343</v>
       </c>
       <c r="J570" t="n">
-        <v>0.1089013439822368</v>
+        <v>0.05452851396058555</v>
       </c>
       <c r="K570" t="n">
-        <v>1.241305537275119</v>
+        <v>0.7736443481879087</v>
       </c>
       <c r="L570" t="b">
         <v>0</v>
@@ -22145,10 +22145,10 @@
         <v>63.091420544408</v>
       </c>
       <c r="J571" t="n">
-        <v>0.217989204041417</v>
+        <v>0.3029180004396023</v>
       </c>
       <c r="K571" t="n">
-        <v>2.157893570073874</v>
+        <v>2.884067463959128</v>
       </c>
       <c r="L571" t="b">
         <v>0</v>
@@ -22183,10 +22183,10 @@
         <v>225.411732694717</v>
       </c>
       <c r="J572" t="n">
-        <v>0.2019619092282155</v>
+        <v>0.1538701036791895</v>
       </c>
       <c r="K572" t="n">
-        <v>2.023227562179426</v>
+        <v>1.617692903831238</v>
       </c>
       <c r="L572" t="b">
         <v>0</v>
@@ -22221,10 +22221,10 @@
         <v>222.1517314720099</v>
       </c>
       <c r="J573" t="n">
-        <v>0.8248806742841497</v>
+        <v>0.9127201505417235</v>
       </c>
       <c r="K573" t="n">
-        <v>7.257172798123215</v>
+        <v>8.06520685864613</v>
       </c>
       <c r="L573" t="b">
         <v>0</v>
@@ -22262,7 +22262,7 @@
         <v>1</v>
       </c>
       <c r="K574" t="n">
-        <v>8.728576473801313</v>
+        <v>8.806773719823804</v>
       </c>
       <c r="L574" t="b">
         <v>0</v>
@@ -22297,10 +22297,10 @@
         <v>22.37892494694004</v>
       </c>
       <c r="J575" t="n">
-        <v>0.07096786651407655</v>
+        <v>0.1108113612129881</v>
       </c>
       <c r="K575" t="n">
-        <v>0.9225773903402121</v>
+        <v>1.251847445857766</v>
       </c>
       <c r="L575" t="b">
         <v>0</v>
@@ -22335,10 +22335,10 @@
         <v>25.13123072370229</v>
       </c>
       <c r="J576" t="n">
-        <v>0.02727832005696075</v>
+        <v>0.04500310018176652</v>
       </c>
       <c r="K576" t="n">
-        <v>0.5554850720999146</v>
+        <v>0.6927123662789096</v>
       </c>
       <c r="L576" t="b">
         <v>0</v>
@@ -22373,10 +22373,10 @@
         <v>107.9720272398016</v>
       </c>
       <c r="J577" t="n">
-        <v>0.03870172187928205</v>
+        <v>0.05222636874970747</v>
       </c>
       <c r="K577" t="n">
-        <v>0.6514678276376153</v>
+        <v>0.7540843396796197</v>
       </c>
       <c r="L577" t="b">
         <v>0</v>
@@ -22411,10 +22411,10 @@
         <v>32.18175992025563</v>
       </c>
       <c r="J578" t="n">
-        <v>0.1297871052880076</v>
+        <v>0.08059168273556228</v>
       </c>
       <c r="K578" t="n">
-        <v>1.416793798373791</v>
+        <v>0.9950881565900174</v>
       </c>
       <c r="L578" t="b">
         <v>0</v>
@@ -22449,10 +22449,10 @@
         <v>87.18874365395749</v>
       </c>
       <c r="J579" t="n">
-        <v>0.02931411951245716</v>
+        <v>0.07647275300332819</v>
       </c>
       <c r="K579" t="n">
-        <v>0.5725904531851603</v>
+        <v>0.9600919711943908</v>
       </c>
       <c r="L579" t="b">
         <v>0</v>
@@ -22487,10 +22487,10 @@
         <v>108.7323158887593</v>
       </c>
       <c r="J580" t="n">
-        <v>0.07186933161416308</v>
+        <v>0.05280803384887114</v>
       </c>
       <c r="K580" t="n">
-        <v>0.9301517631648031</v>
+        <v>0.7590264146776936</v>
       </c>
       <c r="L580" t="b">
         <v>0</v>
@@ -22525,10 +22525,10 @@
         <v>118.059277804328</v>
       </c>
       <c r="J581" t="n">
-        <v>0.1451263525946604</v>
+        <v>0.202458879209488</v>
       </c>
       <c r="K581" t="n">
-        <v>1.545678630341263</v>
+        <v>2.030523883514524</v>
       </c>
       <c r="L581" t="b">
         <v>0</v>
@@ -22563,10 +22563,10 @@
         <v>22.9668952062159</v>
       </c>
       <c r="J582" t="n">
-        <v>0.1895181439755983</v>
+        <v>0.1274463698184485</v>
       </c>
       <c r="K582" t="n">
-        <v>1.918671415351372</v>
+        <v>1.393185580533537</v>
       </c>
       <c r="L582" t="b">
         <v>0</v>
@@ -22601,10 +22601,10 @@
         <v>107.2888713336505</v>
       </c>
       <c r="J583" t="n">
-        <v>0.05056349713574169</v>
+        <v>0.02184744054531307</v>
       </c>
       <c r="K583" t="n">
-        <v>0.7511339246893041</v>
+        <v>0.4959719967470848</v>
       </c>
       <c r="L583" t="b">
         <v>0</v>
@@ -22639,10 +22639,10 @@
         <v>69.25422907386476</v>
       </c>
       <c r="J584" t="n">
-        <v>0.02742986515253264</v>
+        <v>0.08564206154268515</v>
       </c>
       <c r="K584" t="n">
-        <v>0.556758398214802</v>
+        <v>1.037998330965911</v>
       </c>
       <c r="L584" t="b">
         <v>0</v>
@@ -22677,10 +22677,10 @@
         <v>143.7321923452035</v>
       </c>
       <c r="J585" t="n">
-        <v>0.09415722511155485</v>
+        <v>0.2481010874867073</v>
       </c>
       <c r="K585" t="n">
-        <v>1.11742114808921</v>
+        <v>2.418319569912167</v>
       </c>
       <c r="L585" t="b">
         <v>0</v>
@@ -22715,10 +22715,10 @@
         <v>33.31087470882692</v>
       </c>
       <c r="J586" t="n">
-        <v>0.3833203543644332</v>
+        <v>0.4214440926599849</v>
       </c>
       <c r="K586" t="n">
-        <v>3.547054139845048</v>
+        <v>3.891115742812341</v>
       </c>
       <c r="L586" t="b">
         <v>0</v>
@@ -22753,10 +22753,10 @@
         <v>117.1068563835192</v>
       </c>
       <c r="J587" t="n">
-        <v>0.1428444433258107</v>
+        <v>0.1276687289009074</v>
       </c>
       <c r="K587" t="n">
-        <v>1.5265053627877</v>
+        <v>1.395074838224251</v>
       </c>
       <c r="L587" t="b">
         <v>0</v>
@@ -22791,10 +22791,10 @@
         <v>19.32310205211363</v>
       </c>
       <c r="J588" t="n">
-        <v>0.2476596756959777</v>
+        <v>0.1171147187694977</v>
       </c>
       <c r="K588" t="n">
-        <v>2.40719353096147</v>
+        <v>1.305403462590998</v>
       </c>
       <c r="L588" t="b">
         <v>0</v>
@@ -22829,10 +22829,10 @@
         <v>107.6002402781697</v>
       </c>
       <c r="J589" t="n">
-        <v>0.1034875562398892</v>
+        <v>0.1125430768817072</v>
       </c>
       <c r="K589" t="n">
-        <v>1.19581731288373</v>
+        <v>1.266560841456806</v>
       </c>
       <c r="L589" t="b">
         <v>0</v>
@@ -22867,10 +22867,10 @@
         <v>24.61844422229423</v>
       </c>
       <c r="J590" t="n">
-        <v>0.04418778960180206</v>
+        <v>0.0622858974714806</v>
       </c>
       <c r="K590" t="n">
-        <v>0.6975633695142038</v>
+        <v>0.83955439016015</v>
       </c>
       <c r="L590" t="b">
         <v>0</v>
@@ -22905,10 +22905,10 @@
         <v>24.02063297429095</v>
       </c>
       <c r="J591" t="n">
-        <v>0.03082383111012937</v>
+        <v>0.0178561678607548</v>
       </c>
       <c r="K591" t="n">
-        <v>0.5852754905729424</v>
+        <v>0.4620604401259086</v>
       </c>
       <c r="L591" t="b">
         <v>0</v>
@@ -22943,10 +22943,10 @@
         <v>116.6331264234163</v>
       </c>
       <c r="J592" t="n">
-        <v>0.06390298596277053</v>
+        <v>0.05342915628444096</v>
       </c>
       <c r="K592" t="n">
-        <v>0.8632162023678129</v>
+        <v>0.7643037360503976</v>
       </c>
       <c r="L592" t="b">
         <v>0</v>
@@ -22981,10 +22981,10 @@
         <v>29.31885585226721</v>
       </c>
       <c r="J593" t="n">
-        <v>0.08180711589088935</v>
+        <v>0.1173441390344901</v>
       </c>
       <c r="K593" t="n">
-        <v>1.013651926571083</v>
+        <v>1.307352715102968</v>
       </c>
       <c r="L593" t="b">
         <v>0</v>
@@ -23019,10 +23019,10 @@
         <v>83.49585778982015</v>
       </c>
       <c r="J594" t="n">
-        <v>0.03072306119964174</v>
+        <v>0.04409593491388112</v>
       </c>
       <c r="K594" t="n">
-        <v>0.5844287923796782</v>
+        <v>0.6850047028898157</v>
       </c>
       <c r="L594" t="b">
         <v>0</v>
@@ -23057,10 +23057,10 @@
         <v>38.59103886712467</v>
       </c>
       <c r="J595" t="n">
-        <v>0.1194537317625041</v>
+        <v>0.1267167520304024</v>
       </c>
       <c r="K595" t="n">
-        <v>1.329969778663644</v>
+        <v>1.386986436329016</v>
       </c>
       <c r="L595" t="b">
         <v>0</v>
@@ -23095,10 +23095,10 @@
         <v>76.94451010274445</v>
       </c>
       <c r="J596" t="n">
-        <v>0.06596730322572605</v>
+        <v>0.1190825026927952</v>
       </c>
       <c r="K596" t="n">
-        <v>0.8805611983930208</v>
+        <v>1.322122594859589</v>
       </c>
       <c r="L596" t="b">
         <v>0</v>
@@ -23133,10 +23133,10 @@
         <v>22.63615537545256</v>
       </c>
       <c r="J597" t="n">
-        <v>0.172908990759726</v>
+        <v>0.2035827337037437</v>
       </c>
       <c r="K597" t="n">
-        <v>1.779116463367433</v>
+        <v>2.040072631076515</v>
       </c>
       <c r="L597" t="b">
         <v>0</v>
@@ -23171,10 +23171,10 @@
         <v>228.898275247851</v>
       </c>
       <c r="J598" t="n">
-        <v>0.03600202671515497</v>
+        <v>0.04818250758582972</v>
       </c>
       <c r="K598" t="n">
-        <v>0.6287842010791593</v>
+        <v>0.719725968887875</v>
       </c>
       <c r="L598" t="b">
         <v>0</v>
@@ -23209,10 +23209,10 @@
         <v>226.8534719471543</v>
       </c>
       <c r="J599" t="n">
-        <v>0.9336703636294875</v>
+        <v>0.8334998287704721</v>
       </c>
       <c r="K599" t="n">
-        <v>8.171255513576019</v>
+        <v>7.392117185347874</v>
       </c>
       <c r="L599" t="b">
         <v>0</v>

--- a/output/lstm_results/lstm_data_for_cnn.xlsx
+++ b/output/lstm_results/lstm_data_for_cnn.xlsx
@@ -511,16 +511,16 @@
         <v>180</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3331479421579884</v>
+        <v>0.04274593815351099</v>
       </c>
       <c r="G2" t="n">
-        <v>12.22403937878831</v>
+        <v>11.25583982562025</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I2" t="n">
-        <v>121.0268000416056</v>
+        <v>123.1692157433761</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>3.130550111402148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I3" t="n">
-        <v>103.1141331216878</v>
+        <v>105.2558370637407</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5733821862839096</v>
+        <v>0.3331479421580256</v>
       </c>
       <c r="G4" t="n">
-        <v>26.46995551790059</v>
+        <v>24.84224811920275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I4" t="n">
-        <v>31.56419413379803</v>
+        <v>29.88235507177804</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2594549499444109</v>
+        <v>0.5164649610678496</v>
       </c>
       <c r="G5" t="n">
-        <v>21.69703852233483</v>
+        <v>23.2491355768497</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I5" t="n">
-        <v>40.27642527824004</v>
+        <v>39.28942726860058</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         <v>621</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.1195773081201641</v>
       </c>
       <c r="G6" t="n">
-        <v>12.89864333951443</v>
+        <v>13.3613588541968</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I6" t="n">
-        <v>64.51470632775215</v>
+        <v>62.45290031964424</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>502</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4999280372294038</v>
+        <v>0.0426918798665293</v>
       </c>
       <c r="G7" t="n">
-        <v>11.56827388827676</v>
+        <v>10.18839587092663</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I7" t="n">
-        <v>91.92781995271316</v>
+        <v>89.95830214227952</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
         <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3509127758278846</v>
+        <v>0.5556173526140198</v>
       </c>
       <c r="G8" t="n">
-        <v>16.61100187347196</v>
+        <v>17.53394458895654</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I8" t="n">
-        <v>77.39456076767104</v>
+        <v>75.45800338202417</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -783,10 +783,10 @@
         <v>13.96824971139906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I9" t="n">
-        <v>88.78723223269171</v>
+        <v>86.78673227199528</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>406</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1996662958843402</v>
+        <v>0.5556173526140743</v>
       </c>
       <c r="G10" t="n">
-        <v>22.0754042805452</v>
+        <v>24.29950966012491</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I10" t="n">
-        <v>43.07869834413248</v>
+        <v>41.22801978256253</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -853,16 +853,16 @@
         <v>368</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.1676798220245143</v>
       </c>
       <c r="G11" t="n">
-        <v>3.976587858956469</v>
+        <v>4.176625922292869</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I11" t="n">
-        <v>114.4065618609098</v>
+        <v>116.5330098436377</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         <v>379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1665739710790135</v>
+        <v>0.2778086763070295</v>
       </c>
       <c r="G12" t="n">
-        <v>5.758619458586187</v>
+        <v>5.941640973809919</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I12" t="n">
-        <v>100.1913190641316</v>
+        <v>102.3323914321277</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>10.87983322482473</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I13" t="n">
-        <v>36.02931786548452</v>
+        <v>34.6883049897331</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -967,16 +967,16 @@
         <v>662</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005256029964943096</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5.413901311354262</v>
+        <v>5.405378062633547</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I14" t="n">
-        <v>186.9257520393805</v>
+        <v>184.7976516530829</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1005,16 +1005,16 @@
         <v>277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5556173526140004</v>
+        <v>0.5556173526140262</v>
       </c>
       <c r="G15" t="n">
-        <v>18.71282535061893</v>
+        <v>18.71282535061905</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I15" t="n">
-        <v>40.83720822843452</v>
+        <v>39.94033407310379</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         <v>686</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0597886540600792</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>10.30598504068171</v>
+        <v>10.12438798150288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I16" t="n">
-        <v>112.0882345493425</v>
+        <v>114.2301789753145</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1081,22 +1081,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5556173526140011</v>
+        <v>0.8849948832035945</v>
       </c>
       <c r="G17" t="n">
-        <v>23.10576289373351</v>
+        <v>25.06272242830079</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I17" t="n">
-        <v>106.5518709701242</v>
+        <v>108.6797504099136</v>
       </c>
       <c r="J17" t="n">
-        <v>0.08259899431351056</v>
+        <v>0.07065873769014119</v>
       </c>
       <c r="K17" t="n">
-        <v>1.363928572973686</v>
+        <v>1.289904485188784</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1125,16 +1125,16 @@
         <v>5.248200453488796</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I18" t="n">
-        <v>193.3453336789636</v>
+        <v>192.2446076995312</v>
       </c>
       <c r="J18" t="n">
-        <v>0.05758183614082461</v>
+        <v>0.1010218097653444</v>
       </c>
       <c r="K18" t="n">
-        <v>1.05117168119599</v>
+        <v>1.713671199189046</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1163,16 +1163,16 @@
         <v>22.28885569068094</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I19" t="n">
-        <v>33.39024180409309</v>
+        <v>31.95854851596797</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4616034324243376</v>
+        <v>0.5059165470747756</v>
       </c>
       <c r="K19" t="n">
-        <v>6.102126621499981</v>
+        <v>7.364644589518126</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006469251842255576</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>8.93397503665498</v>
+        <v>8.916669781930919</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I20" t="n">
-        <v>69.12137691140141</v>
+        <v>66.99947464678726</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04217161837906352</v>
+        <v>0.01108693935493489</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8585178323648313</v>
+        <v>0.4584818555855918</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         <v>216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3133383436468759</v>
+        <v>0.5769632925472992</v>
       </c>
       <c r="G21" t="n">
-        <v>18.42323844438262</v>
+        <v>19.75508998564958</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I21" t="n">
-        <v>31.86607319519875</v>
+        <v>30.12128391393638</v>
       </c>
       <c r="J21" t="n">
-        <v>0.118703816751164</v>
+        <v>0.1133307230568491</v>
       </c>
       <c r="K21" t="n">
-        <v>1.815300066323992</v>
+        <v>1.885462371226444</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1271,22 +1271,22 @@
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>5.405828698554315e-05</v>
       </c>
       <c r="G22" t="n">
-        <v>6.604105389831389</v>
+        <v>6.604212491818722</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I22" t="n">
-        <v>102.6668204167644</v>
+        <v>104.8029381159723</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04783271473910261</v>
+        <v>0.04608731492791557</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9292911348078305</v>
+        <v>0.9469697829139343</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>435</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.5556173526140915</v>
       </c>
       <c r="G23" t="n">
-        <v>13.21653808680624</v>
+        <v>15.41953945756062</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I23" t="n">
-        <v>26.15123977963556</v>
+        <v>24.52768467624059</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0901937987939639</v>
+        <v>0.06666698793101794</v>
       </c>
       <c r="K23" t="n">
-        <v>1.458876505371512</v>
+        <v>1.23419303825926</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>678</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3331479421580091</v>
+        <v>0.3720916573971721</v>
       </c>
       <c r="G24" t="n">
-        <v>17.22789538798354</v>
+        <v>17.41088234516358</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I24" t="n">
-        <v>109.2935541443511</v>
+        <v>111.4359869865275</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02277742695263215</v>
+        <v>0.02061077018502644</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6160575582120749</v>
+        <v>0.5914026116133818</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1385,22 +1385,22 @@
         <v>120</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5.405828698564195e-05</v>
       </c>
       <c r="G25" t="n">
-        <v>3.556590642736384</v>
+        <v>3.55664832169568</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I25" t="n">
-        <v>102.0803797833086</v>
+        <v>104.2223927646257</v>
       </c>
       <c r="J25" t="n">
-        <v>0.08121693402276901</v>
+        <v>0.04457132087738927</v>
       </c>
       <c r="K25" t="n">
-        <v>1.346650476165167</v>
+        <v>0.9258115873385881</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>674</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>0.5559468992214315</v>
       </c>
       <c r="G26" t="n">
-        <v>19.07863580028719</v>
+        <v>22.26064832465058</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I26" t="n">
-        <v>67.34152279089471</v>
+        <v>65.33773436557786</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1350459408068997</v>
+        <v>0.04428062629448599</v>
       </c>
       <c r="K26" t="n">
-        <v>2.019604323803477</v>
+        <v>0.9217544653230856</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5556173526140191</v>
+        <v>0.555671410901006</v>
       </c>
       <c r="G27" t="n">
-        <v>16.38091541472499</v>
+        <v>16.38114311733634</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I27" t="n">
-        <v>67.57407093593636</v>
+        <v>65.47048678120628</v>
       </c>
       <c r="J27" t="n">
-        <v>0.09762191594226059</v>
+        <v>0.07746728569798508</v>
       </c>
       <c r="K27" t="n">
-        <v>1.551740563512151</v>
+        <v>1.384928994212472</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1499,22 +1499,22 @@
         <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8343241217678299</v>
+        <v>0.7222453819800044</v>
       </c>
       <c r="G28" t="n">
-        <v>25.88631848468244</v>
+        <v>25.19017059230747</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I28" t="n">
-        <v>36.79279032197694</v>
+        <v>35.24708042143696</v>
       </c>
       <c r="J28" t="n">
-        <v>0.1208550685447222</v>
+        <v>0.08178667636430419</v>
       </c>
       <c r="K28" t="n">
-        <v>1.842194361021264</v>
+        <v>1.445213210006443</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1537,22 +1537,22 @@
         <v>373</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0.5080934371524084</v>
       </c>
       <c r="G29" t="n">
-        <v>28.97551239788522</v>
+        <v>25.68630208010256</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I29" t="n">
-        <v>8.47180990041239</v>
+        <v>10.61067327951851</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0539542898655035</v>
+        <v>0.03362784378979535</v>
       </c>
       <c r="K29" t="n">
-        <v>1.005821202535793</v>
+        <v>0.7730773279836476</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -1581,16 +1581,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I30" t="n">
-        <v>39.17350222079536</v>
+        <v>38.23648624117343</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1205761756580851</v>
+        <v>0.0879157370484521</v>
       </c>
       <c r="K30" t="n">
-        <v>1.8387077270974</v>
+        <v>1.530754353524352</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1619,16 +1619,16 @@
         <v>7.790921447428411</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I31" t="n">
-        <v>162.3787553823233</v>
+        <v>160.272998877366</v>
       </c>
       <c r="J31" t="n">
-        <v>0.04596161095211854</v>
+        <v>0.0327061053705026</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9058991651615922</v>
+        <v>0.7602129491703298</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>11.449738512298</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I32" t="n">
-        <v>60.62527993325826</v>
+        <v>58.6306202825246</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1422441920731369</v>
+        <v>0.1158335829929961</v>
       </c>
       <c r="K32" t="n">
-        <v>2.109594668698894</v>
+        <v>1.920393906748177</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1695,16 +1695,16 @@
         <v>16.80179799902379</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I33" t="n">
-        <v>34.48929412896155</v>
+        <v>32.3905445238623</v>
       </c>
       <c r="J33" t="n">
-        <v>0.09049948743386348</v>
+        <v>0.02361856588393054</v>
       </c>
       <c r="K33" t="n">
-        <v>1.462698131641242</v>
+        <v>0.6333813579191503</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1727,22 +1727,22 @@
         <v>193</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03042370505470451</v>
+        <v>0.3331479421579999</v>
       </c>
       <c r="G34" t="n">
-        <v>15.35318315801794</v>
+        <v>16.73490621517591</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I34" t="n">
-        <v>35.95018142275353</v>
+        <v>34.29627342288722</v>
       </c>
       <c r="J34" t="n">
-        <v>0.02493699303060589</v>
+        <v>0.024744126675183</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6430557955607537</v>
+        <v>0.6490904138649788</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -1765,22 +1765,22 @@
         <v>616</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2799194540979267</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>22.66638519535696</v>
+        <v>20.91041556258507</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I35" t="n">
-        <v>20.68198907871965</v>
+        <v>18.64814676732945</v>
       </c>
       <c r="J35" t="n">
-        <v>0.039781966725018</v>
+        <v>0.03860554091598047</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8286431352233028</v>
+        <v>0.8425492954192056</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1803,22 +1803,22 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.5556173526140363</v>
       </c>
       <c r="G36" t="n">
-        <v>15.77523974461244</v>
+        <v>18.40473882773843</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I36" t="n">
-        <v>34.110689030354</v>
+        <v>33.22035544535546</v>
       </c>
       <c r="J36" t="n">
-        <v>0.01360548447540358</v>
+        <v>0.01979204512306645</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5013927269414398</v>
+        <v>0.5799759539841036</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -1841,22 +1841,22 @@
         <v>357</v>
       </c>
       <c r="F37" t="n">
-        <v>0.333147942158018</v>
+        <v>0.4329810901001586</v>
       </c>
       <c r="G37" t="n">
-        <v>19.71998514163917</v>
+        <v>20.25693270693071</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I37" t="n">
-        <v>66.39677468185866</v>
+        <v>64.38123705264955</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02524830844927721</v>
+        <v>0.01889908744670283</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6469477661048908</v>
+        <v>0.5675132578736216</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>285</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5625701729357513</v>
+        <v>0.3331479421579941</v>
       </c>
       <c r="G38" t="n">
-        <v>19.01218311617558</v>
+        <v>17.89259238312755</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I38" t="n">
-        <v>104.1426690809669</v>
+        <v>106.2850349936737</v>
       </c>
       <c r="J38" t="n">
-        <v>0.09451981986204006</v>
+        <v>0.1084872905044423</v>
       </c>
       <c r="K38" t="n">
-        <v>1.512959103150085</v>
+        <v>1.817864287207417</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>21.78421446827955</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I39" t="n">
-        <v>33.88947825465729</v>
+        <v>32.76671958087123</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1630380167748406</v>
+        <v>0.09332872638073257</v>
       </c>
       <c r="K39" t="n">
-        <v>2.369552731760413</v>
+        <v>1.606301541127029</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -1955,22 +1955,22 @@
         <v>296</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>0.5556173526140422</v>
       </c>
       <c r="G40" t="n">
-        <v>14.9179427536105</v>
+        <v>17.40454311137317</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I40" t="n">
-        <v>226.1352548389639</v>
+        <v>224.1061541260364</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03980537058062281</v>
+        <v>0.03917735947588942</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8289357230977548</v>
+        <v>0.850529965871023</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -1999,16 +1999,16 @@
         <v>3.307725502516798</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I41" t="n">
-        <v>188.3168767220277</v>
+        <v>186.6105010565384</v>
       </c>
       <c r="J41" t="n">
-        <v>0.07853455268265705</v>
+        <v>0.1119149160043783</v>
       </c>
       <c r="K41" t="n">
-        <v>1.313116161647706</v>
+        <v>1.865702450333132</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2031,22 +2031,22 @@
         <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.03576195773082118</v>
       </c>
       <c r="G42" t="n">
-        <v>9.292517850399857</v>
+        <v>9.392213439573528</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I42" t="n">
-        <v>67.20219070025054</v>
+        <v>65.0745722593559</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1638732204157168</v>
+        <v>0.1207366229044083</v>
       </c>
       <c r="K42" t="n">
-        <v>2.379994193293285</v>
+        <v>1.988823909704569</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1195773081201493</v>
+        <v>0.5556173526140193</v>
       </c>
       <c r="G43" t="n">
-        <v>9.855441979546789</v>
+        <v>11.10000571301757</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I43" t="n">
-        <v>115.0637846251746</v>
+        <v>117.2016187103962</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04455217537663015</v>
+        <v>0.0264281670771804</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8882788308811007</v>
+        <v>0.672593973242323</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2107,22 +2107,22 @@
         <v>71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3509127758278911</v>
+        <v>0.8334260289210373</v>
       </c>
       <c r="G44" t="n">
-        <v>21.17578026298207</v>
+        <v>23.94910058924098</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I44" t="n">
-        <v>117.3116648161546</v>
+        <v>119.4493209049221</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02655488012718026</v>
+        <v>0.01866406728062848</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6632821272679379</v>
+        <v>0.564233164105295</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2145,22 +2145,22 @@
         <v>620</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>0.1997203541713349</v>
       </c>
       <c r="G45" t="n">
-        <v>18.40132802272705</v>
+        <v>19.50386394770364</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I45" t="n">
-        <v>31.56545478997106</v>
+        <v>30.85318583155741</v>
       </c>
       <c r="J45" t="n">
-        <v>0.06532062138965833</v>
+        <v>0.08253207538397282</v>
       </c>
       <c r="K45" t="n">
-        <v>1.147919617306611</v>
+        <v>1.45561648186252</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2183,22 +2183,22 @@
         <v>496</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5556173526140136</v>
+        <v>0.5639888765295304</v>
       </c>
       <c r="G46" t="n">
-        <v>22.25876213473994</v>
+        <v>22.3066773115032</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I46" t="n">
-        <v>18.51342349872507</v>
+        <v>16.58955756878242</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04136128065745766</v>
+        <v>0.02714303866300337</v>
       </c>
       <c r="K46" t="n">
-        <v>0.8483872369810448</v>
+        <v>0.6825711844449982</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2221,22 +2221,22 @@
         <v>630</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1665739710790135</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>5.842144154763064</v>
+        <v>5.564094176054176</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I47" t="n">
-        <v>34.01156394669319</v>
+        <v>32.15396703199863</v>
       </c>
       <c r="J47" t="n">
-        <v>0.04320285753910592</v>
+        <v>0.06637741472510036</v>
       </c>
       <c r="K47" t="n">
-        <v>0.8714100702500457</v>
+        <v>1.230151566907801</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         <v>12.79325302649799</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I48" t="n">
-        <v>32.49248409342751</v>
+        <v>31.00669874290006</v>
       </c>
       <c r="J48" t="n">
-        <v>0.05520121032056942</v>
+        <v>0.03578366055377311</v>
       </c>
       <c r="K48" t="n">
-        <v>1.021409822279431</v>
+        <v>0.8031653040552</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2303,16 +2303,16 @@
         <v>13.11028664827737</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I49" t="n">
-        <v>23.93283827844492</v>
+        <v>22.99292465625096</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01551579868992332</v>
+        <v>0.01227709936228297</v>
       </c>
       <c r="K49" t="n">
-        <v>0.5252748934100622</v>
+        <v>0.4750925000618573</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         <v>430</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3172642774964361</v>
+        <v>0.8334260289210501</v>
       </c>
       <c r="G50" t="n">
-        <v>22.6747359713291</v>
+        <v>25.88074021494434</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I50" t="n">
-        <v>31.57965849900658</v>
+        <v>29.89635428070724</v>
       </c>
       <c r="J50" t="n">
-        <v>0.02475531192879634</v>
+        <v>0.03333861533723404</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6407844737621514</v>
+        <v>0.769040668233484</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -2373,22 +2373,22 @@
         <v>551</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.1195773081201534</v>
       </c>
       <c r="G51" t="n">
-        <v>5.431724311855306</v>
+        <v>5.626577603354042</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I51" t="n">
-        <v>20.99035760883323</v>
+        <v>19.98262821069968</v>
       </c>
       <c r="J51" t="n">
-        <v>0.04173755244772131</v>
+        <v>0.03354659430277569</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8530912722984925</v>
+        <v>0.7719433574801606</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>5.066791391008713</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I52" t="n">
-        <v>38.47422444999084</v>
+        <v>36.95496758029069</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02526601557465807</v>
+        <v>0.02422132491122961</v>
       </c>
       <c r="K52" t="n">
-        <v>0.6471691351931865</v>
+        <v>0.6417938535882273</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2455,16 +2455,16 @@
         <v>4.862088337329959</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I53" t="n">
-        <v>77.46996081146925</v>
+        <v>75.67134187702</v>
       </c>
       <c r="J53" t="n">
-        <v>0.04234101863360211</v>
+        <v>0.01499288144085234</v>
       </c>
       <c r="K53" t="n">
-        <v>0.8606356227513382</v>
+        <v>0.5129957150107828</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2487,22 +2487,22 @@
         <v>537</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.0002754883203560995</v>
       </c>
       <c r="G54" t="n">
-        <v>6.104072738754019</v>
+        <v>6.104577218977858</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I54" t="n">
-        <v>38.18059332212762</v>
+        <v>37.51344655974254</v>
       </c>
       <c r="J54" t="n">
-        <v>0.07205363074895287</v>
+        <v>0.03988722763043866</v>
       </c>
       <c r="K54" t="n">
-        <v>1.232093649584275</v>
+        <v>0.8604373459438198</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -2531,16 +2531,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I55" t="n">
-        <v>39.45209564029722</v>
+        <v>38.26256329269757</v>
       </c>
       <c r="J55" t="n">
-        <v>0.02403469196042635</v>
+        <v>0.01405734324966357</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6317755024031898</v>
+        <v>0.4999387376364286</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2563,22 +2563,22 @@
         <v>335</v>
       </c>
       <c r="F56" t="n">
-        <v>0.03552966733981126</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3.781204523340663</v>
+        <v>3.741326101798666</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I56" t="n">
-        <v>112.1632538926709</v>
+        <v>114.3018267903333</v>
       </c>
       <c r="J56" t="n">
-        <v>0.005221778894257349</v>
+        <v>0.0002430834568224279</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3965821932653401</v>
+        <v>0.3071379741214916</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>4.362815948444307</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I57" t="n">
-        <v>117.0300017920571</v>
+        <v>119.1724144416496</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1637684283375962</v>
+        <v>0.123652992411889</v>
       </c>
       <c r="K57" t="n">
-        <v>2.378684114650071</v>
+        <v>2.029526652824062</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I58" t="n">
-        <v>39.55191259194645</v>
+        <v>37.5753379440626</v>
       </c>
       <c r="J58" t="n">
-        <v>0.003341741347227731</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3730785364720466</v>
+        <v>0.303745343841185</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3357759571404584</v>
+        <v>0.6486839819726939</v>
       </c>
       <c r="G59" t="n">
-        <v>23.01678000250459</v>
+        <v>24.97969105213751</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I59" t="n">
-        <v>34.14435781244566</v>
+        <v>32.24000229639994</v>
       </c>
       <c r="J59" t="n">
-        <v>0.02834513359208803</v>
+        <v>0.03119078159370639</v>
       </c>
       <c r="K59" t="n">
-        <v>0.6856633308128762</v>
+        <v>0.7390641083696052</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2715,22 +2715,22 @@
         <v>378</v>
       </c>
       <c r="F60" t="n">
-        <v>0.1996662958843589</v>
+        <v>0.8971368186874719</v>
       </c>
       <c r="G60" t="n">
-        <v>23.84802007835967</v>
+        <v>28.55599991914888</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I60" t="n">
-        <v>27.85169128583821</v>
+        <v>26.22489788799395</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04882207204373049</v>
+        <v>0.04198404280613077</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9416597784929799</v>
+        <v>0.8897018576068079</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>4.710418346601499</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I61" t="n">
-        <v>30.24652248389411</v>
+        <v>28.35044261881249</v>
       </c>
       <c r="J61" t="n">
-        <v>0.03535884495641969</v>
+        <v>0.01976734846316553</v>
       </c>
       <c r="K61" t="n">
-        <v>0.773346614061621</v>
+        <v>0.5796312713911475</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2791,22 +2791,22 @@
         <v>232</v>
       </c>
       <c r="F62" t="n">
-        <v>0.3331479421579698</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>14.92928901976279</v>
+        <v>13.57276718285553</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I62" t="n">
-        <v>91.81494381084008</v>
+        <v>89.80197964555539</v>
       </c>
       <c r="J62" t="n">
-        <v>0.05592115140351678</v>
+        <v>0.05815693658718699</v>
       </c>
       <c r="K62" t="n">
-        <v>1.030410306419613</v>
+        <v>1.115421245832698</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -2829,22 +2829,22 @@
         <v>659</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00089809284676518</v>
+        <v>0.09988720622916851</v>
       </c>
       <c r="G63" t="n">
-        <v>4.561587774501019</v>
+        <v>4.697015545311514</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I63" t="n">
-        <v>35.84140144804635</v>
+        <v>34.43419147053508</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1099763108803156</v>
+        <v>0.06822214060695486</v>
       </c>
       <c r="K63" t="n">
-        <v>1.706191446140332</v>
+        <v>1.255897756991878</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -2867,22 +2867,22 @@
         <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>0.3331479421579978</v>
+        <v>0.6156814949944472</v>
       </c>
       <c r="G64" t="n">
-        <v>11.06495370413403</v>
+        <v>11.91760245564876</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I64" t="n">
-        <v>181.1218290282886</v>
+        <v>179.0629132781346</v>
       </c>
       <c r="J64" t="n">
-        <v>0.07482840593505342</v>
+        <v>0.03229328034833517</v>
       </c>
       <c r="K64" t="n">
-        <v>1.266783043823074</v>
+        <v>0.7544512955844316</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -2905,22 +2905,22 @@
         <v>692</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3261957730812335</v>
+        <v>0.0380889877641922</v>
       </c>
       <c r="G65" t="n">
-        <v>12.20086086451897</v>
+        <v>11.24031356469956</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I65" t="n">
-        <v>30.31422308502487</v>
+        <v>28.69860965051859</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2021204486561371</v>
+        <v>0.1095327624348496</v>
       </c>
       <c r="K65" t="n">
-        <v>2.858149391458291</v>
+        <v>1.832455571100921</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -2943,22 +2943,22 @@
         <v>489</v>
       </c>
       <c r="F66" t="n">
-        <v>0.11957730812016</v>
+        <v>0.1071374831981166</v>
       </c>
       <c r="G66" t="n">
-        <v>17.16629727097695</v>
+        <v>17.10445213370436</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I66" t="n">
-        <v>91.45954929602746</v>
+        <v>89.41035276025718</v>
       </c>
       <c r="J66" t="n">
-        <v>0.01191509399842286</v>
+        <v>0.02340004210363482</v>
       </c>
       <c r="K66" t="n">
-        <v>0.4802599800554114</v>
+        <v>0.6303314984030421</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -2981,22 +2981,22 @@
         <v>259</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>0.05978865406008206</v>
       </c>
       <c r="G67" t="n">
-        <v>4.411928036584459</v>
+        <v>4.491063008319657</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I67" t="n">
-        <v>20.62196213552128</v>
+        <v>18.74323521515296</v>
       </c>
       <c r="J67" t="n">
-        <v>0.05213031070504439</v>
+        <v>0.0371850638647615</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9830183706172048</v>
+        <v>0.8227241969964592</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3019,22 +3019,22 @@
         <v>627</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5733821862838934</v>
+        <v>0.5556173526140763</v>
       </c>
       <c r="G68" t="n">
-        <v>21.89233228085997</v>
+        <v>21.79278225228457</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I68" t="n">
-        <v>110.4027361141528</v>
+        <v>112.5446921819305</v>
       </c>
       <c r="J68" t="n">
-        <v>0.02464085443064558</v>
+        <v>0.02641919301260483</v>
       </c>
       <c r="K68" t="n">
-        <v>0.6393535609816036</v>
+        <v>0.6724687253804795</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>0.3776418242492196</v>
       </c>
       <c r="G69" t="n">
-        <v>12.02926119925908</v>
+        <v>13.39208684235665</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I69" t="n">
-        <v>16.50018486318389</v>
+        <v>15.65247452673903</v>
       </c>
       <c r="J69" t="n">
-        <v>0.02776944068322392</v>
+        <v>0.1023407847685687</v>
       </c>
       <c r="K69" t="n">
-        <v>0.6784661934101404</v>
+        <v>1.732079669240445</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1996662958843364</v>
+        <v>0.8334260289210794</v>
       </c>
       <c r="G70" t="n">
-        <v>19.71380764978644</v>
+        <v>23.25012771332207</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I70" t="n">
-        <v>30.0316841130106</v>
+        <v>28.58953588620482</v>
       </c>
       <c r="J70" t="n">
-        <v>0.03990982983412659</v>
+        <v>0.04523462276149988</v>
       </c>
       <c r="K70" t="n">
-        <v>0.8302416408689799</v>
+        <v>0.9350690583587651</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3133,22 +3133,22 @@
         <v>421</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3331479421579884</v>
+        <v>0.5556173526140203</v>
       </c>
       <c r="G71" t="n">
-        <v>14.88994966741949</v>
+        <v>15.79342034552541</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I71" t="n">
-        <v>135.3804565993185</v>
+        <v>134.8465327230052</v>
       </c>
       <c r="J71" t="n">
-        <v>0.04523684934335476</v>
+        <v>0.05060680786484363</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8968384162758836</v>
+        <v>1.010046755694745</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -3171,22 +3171,22 @@
         <v>694</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8334260289210083</v>
+        <v>0.8337015172414023</v>
       </c>
       <c r="G72" t="n">
-        <v>27.44061045606219</v>
+        <v>27.44242471194498</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I72" t="n">
-        <v>25.35226577114653</v>
+        <v>24.1732486796384</v>
       </c>
       <c r="J72" t="n">
-        <v>0.02081947962710545</v>
+        <v>0.01288801785328014</v>
       </c>
       <c r="K72" t="n">
-        <v>0.5915798970976816</v>
+        <v>0.4836188744949403</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>250</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>0.55567141090105</v>
       </c>
       <c r="G73" t="n">
-        <v>17.30370795523318</v>
+        <v>20.18826069922442</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I73" t="n">
-        <v>39.19731183175172</v>
+        <v>41.3279864413372</v>
       </c>
       <c r="J73" t="n">
-        <v>0.02106353729155832</v>
+        <v>0.0273930402486224</v>
       </c>
       <c r="K73" t="n">
-        <v>0.594631031683869</v>
+        <v>0.6860603686148423</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -3247,22 +3247,22 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>0.558245367596471</v>
+        <v>0.4676422691880252</v>
       </c>
       <c r="G74" t="n">
-        <v>24.3159304071615</v>
+        <v>23.74981089503482</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I74" t="n">
-        <v>78.85572116520021</v>
+        <v>76.7997273344141</v>
       </c>
       <c r="J74" t="n">
-        <v>0.03740087817165126</v>
+        <v>0.02879720306608408</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7988754913583211</v>
+        <v>0.7056577750170435</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3285,22 +3285,22 @@
         <v>564</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5556173526140219</v>
+        <v>0.833426028921014</v>
       </c>
       <c r="G75" t="n">
-        <v>23.247951955323</v>
+        <v>24.90867827486581</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I75" t="n">
-        <v>104.9604338120625</v>
+        <v>107.1027669133627</v>
       </c>
       <c r="J75" t="n">
-        <v>0.03042573408260766</v>
+        <v>0.05609992159391964</v>
       </c>
       <c r="K75" t="n">
-        <v>0.7116743644384516</v>
+        <v>1.086712211312503</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3323,22 +3323,22 @@
         <v>521</v>
       </c>
       <c r="F76" t="n">
-        <v>0.7221913236929993</v>
+        <v>0.07152391546164216</v>
       </c>
       <c r="G76" t="n">
-        <v>21.28914136101672</v>
+        <v>17.87351660113654</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I76" t="n">
-        <v>111.4662923908774</v>
+        <v>113.6063264951257</v>
       </c>
       <c r="J76" t="n">
-        <v>0.03903613160703482</v>
+        <v>0.1213975374188765</v>
       </c>
       <c r="K76" t="n">
-        <v>0.8193189317438784</v>
+        <v>1.99804806104662</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>607</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>0.3331479421579999</v>
       </c>
       <c r="G77" t="n">
-        <v>17.53701442663488</v>
+        <v>19.28974050698345</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I77" t="n">
-        <v>110.4782715334348</v>
+        <v>112.6169423981693</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02927508969117054</v>
+        <v>0.05649799147010381</v>
       </c>
       <c r="K77" t="n">
-        <v>0.6972893587186482</v>
+        <v>1.092267932517368</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3399,22 +3399,22 @@
         <v>316</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2778086763070381</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>6.056638501227805</v>
+        <v>5.590695395029137</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I78" t="n">
-        <v>54.47076238682838</v>
+        <v>52.33610320083483</v>
       </c>
       <c r="J78" t="n">
-        <v>0.05267776440273305</v>
+        <v>0.09329097035870559</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9898624700028917</v>
+        <v>1.605774593611689</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>19.31962732559818</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I79" t="n">
-        <v>92.99127867347956</v>
+        <v>92.04725722295079</v>
       </c>
       <c r="J79" t="n">
-        <v>0.02588514881106695</v>
+        <v>0.06356070097207994</v>
       </c>
       <c r="K79" t="n">
-        <v>0.6549093503398822</v>
+        <v>1.190839684090396</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -3475,22 +3475,22 @@
         <v>421</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>5.405828698564195e-05</v>
       </c>
       <c r="G80" t="n">
-        <v>2.935153317971652</v>
+        <v>2.935200918779775</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I80" t="n">
-        <v>31.70242257958273</v>
+        <v>29.97000374106357</v>
       </c>
       <c r="J80" t="n">
-        <v>0.08338828170958193</v>
+        <v>0.0987075789644777</v>
       </c>
       <c r="K80" t="n">
-        <v>1.373796003599124</v>
+        <v>1.681372294141082</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3513,22 +3513,22 @@
         <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>0.5556173526140379</v>
       </c>
       <c r="G81" t="n">
-        <v>10.68101703958944</v>
+        <v>12.46138456281807</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I81" t="n">
-        <v>111.965176657904</v>
+        <v>114.1003375166647</v>
       </c>
       <c r="J81" t="n">
-        <v>0.0218135965085682</v>
+        <v>0.01543389723588296</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6040080435627539</v>
+        <v>0.5191508172948816</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -3557,16 +3557,16 @@
         <v>4.411928036584459</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I82" t="n">
-        <v>32.66492480421002</v>
+        <v>32.17192458987716</v>
       </c>
       <c r="J82" t="n">
-        <v>0.08016547623865404</v>
+        <v>0.03240069049722143</v>
       </c>
       <c r="K82" t="n">
-        <v>1.333505471199962</v>
+        <v>0.7559503812412147</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3589,22 +3589,22 @@
         <v>364</v>
       </c>
       <c r="F83" t="n">
-        <v>0.01390564064347602</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>20.05047639703421</v>
+        <v>19.96717947032079</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I83" t="n">
-        <v>77.5260275179966</v>
+        <v>75.47077855886236</v>
       </c>
       <c r="J83" t="n">
-        <v>0.01645031986415586</v>
+        <v>0.01287114140024358</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5369579924949345</v>
+        <v>0.4833833357777259</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -3627,22 +3627,22 @@
         <v>241</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>0.0001767215277527809</v>
       </c>
       <c r="G84" t="n">
-        <v>7.583696723893961</v>
+        <v>7.584098784635279</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I84" t="n">
-        <v>28.39475105018511</v>
+        <v>26.77165591083007</v>
       </c>
       <c r="J84" t="n">
-        <v>0.06462984904947756</v>
+        <v>0.01462965705323259</v>
       </c>
       <c r="K84" t="n">
-        <v>1.139283791904315</v>
+        <v>0.507926320029763</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3665,22 +3665,22 @@
         <v>126</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9485539488320127</v>
+        <v>0.9999999999999737</v>
       </c>
       <c r="G85" t="n">
-        <v>25.96344656898113</v>
+        <v>26.27539237994347</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I85" t="n">
-        <v>21.96704537329972</v>
+        <v>19.96040547322278</v>
       </c>
       <c r="J85" t="n">
-        <v>0.008510511886172042</v>
+        <v>0.007508499691218278</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4376969314517505</v>
+        <v>0.4085388322384971</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3703,22 +3703,22 @@
         <v>474</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>0.1665739710790094</v>
       </c>
       <c r="G86" t="n">
-        <v>10.254464783693</v>
+        <v>10.76690285978588</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I86" t="n">
-        <v>31.56930834508758</v>
+        <v>29.43489429325481</v>
       </c>
       <c r="J86" t="n">
-        <v>0.03091304700218567</v>
+        <v>0.03144573984514434</v>
       </c>
       <c r="K86" t="n">
-        <v>0.7177666021338081</v>
+        <v>0.7426224709803289</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -3747,16 +3747,16 @@
         <v>10.61501705132875</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I87" t="n">
-        <v>30.02732918080932</v>
+        <v>28.36002813631899</v>
       </c>
       <c r="J87" t="n">
-        <v>0.01765605851808501</v>
+        <v>0.03179058030995022</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5520317699038662</v>
+        <v>0.7474352880188411</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -3779,22 +3779,22 @@
         <v>36</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1195773081201493</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>3.357165614854884</v>
+        <v>3.240904040541774</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I88" t="n">
-        <v>80.59208700967787</v>
+        <v>78.61574729437156</v>
       </c>
       <c r="J88" t="n">
-        <v>0.02147303194123003</v>
+        <v>0.00585049625358451</v>
       </c>
       <c r="K88" t="n">
-        <v>0.5997504090706559</v>
+        <v>0.3853986616119219</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>0.227998016501198</v>
+        <v>0.03576195773081476</v>
       </c>
       <c r="G89" t="n">
-        <v>3.557877017236547</v>
+        <v>3.36582741887074</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I89" t="n">
-        <v>32.82556778667308</v>
+        <v>32.37895504310568</v>
       </c>
       <c r="J89" t="n">
-        <v>0.04931099641676422</v>
+        <v>0.03502011480629487</v>
       </c>
       <c r="K89" t="n">
-        <v>0.947772162088625</v>
+        <v>0.7925087647038351</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -3855,22 +3855,22 @@
         <v>507</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>5.405828698554315e-05</v>
       </c>
       <c r="G90" t="n">
-        <v>5.537535282054643</v>
+        <v>5.537625086956083</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I90" t="n">
-        <v>69.96172010375923</v>
+        <v>67.94669554959272</v>
       </c>
       <c r="J90" t="n">
-        <v>0.0176188837992767</v>
+        <v>0.05659801772982912</v>
       </c>
       <c r="K90" t="n">
-        <v>0.5515670228919576</v>
+        <v>1.093663963831082</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -3893,22 +3893,22 @@
         <v>643</v>
       </c>
       <c r="F91" t="n">
-        <v>0.01220885028668224</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>10.55479058526973</v>
+        <v>10.51627310409919</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I91" t="n">
-        <v>97.29510029733508</v>
+        <v>99.42781128528908</v>
       </c>
       <c r="J91" t="n">
-        <v>0.007539285782878598</v>
+        <v>0.01655047634278601</v>
       </c>
       <c r="K91" t="n">
-        <v>0.4255549585233038</v>
+        <v>0.5347345190323641</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -3931,22 +3931,22 @@
         <v>327</v>
       </c>
       <c r="F92" t="n">
-        <v>0.03552966733981126</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>17.097504502922</v>
+        <v>16.91718590664535</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I92" t="n">
-        <v>92.50648090999269</v>
+        <v>90.47366703256877</v>
       </c>
       <c r="J92" t="n">
-        <v>0.08257200337951115</v>
+        <v>0.05071215743891551</v>
       </c>
       <c r="K92" t="n">
-        <v>1.363591140537693</v>
+        <v>1.011517082633838</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I93" t="n">
-        <v>95.68965337818463</v>
+        <v>95.64008069622601</v>
       </c>
       <c r="J93" t="n">
-        <v>0.0408204355846493</v>
+        <v>0.03108993557757243</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8416257566107641</v>
+        <v>0.7376566360041193</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4013,16 +4013,16 @@
         <v>11.48356342778669</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I94" t="n">
-        <v>22.90491230530777</v>
+        <v>22.49631413769563</v>
       </c>
       <c r="J94" t="n">
-        <v>0.0272047456880012</v>
+        <v>0.04380005086964243</v>
       </c>
       <c r="K94" t="n">
-        <v>0.6714065485740172</v>
+        <v>0.9150472432043608</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -4045,22 +4045,22 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>0.03552966733981096</v>
+        <v>0.5556173526140414</v>
       </c>
       <c r="G95" t="n">
-        <v>11.46942569284369</v>
+        <v>13.24008453495866</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I95" t="n">
-        <v>30.69324316834034</v>
+        <v>29.98675267257744</v>
       </c>
       <c r="J95" t="n">
-        <v>0.01651698469034134</v>
+        <v>0.03440967289417488</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5377914158472094</v>
+        <v>0.7839890417144613</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -4089,16 +4089,16 @@
         <v>24.6460742997744</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I96" t="n">
-        <v>89.96568728032067</v>
+        <v>88.00279922123961</v>
       </c>
       <c r="J96" t="n">
-        <v>0.02715981672293571</v>
+        <v>0.02898430430675722</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6708448603371809</v>
+        <v>0.7082690812033561</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4127,16 +4127,16 @@
         <v>4.685296148590822</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I97" t="n">
-        <v>109.5694087397138</v>
+        <v>111.7106144585304</v>
       </c>
       <c r="J97" t="n">
-        <v>0.05829685620539712</v>
+        <v>0.05255268013256918</v>
       </c>
       <c r="K97" t="n">
-        <v>1.060110644263288</v>
+        <v>1.037204610299047</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -4159,22 +4159,22 @@
         <v>667</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>0.5556173526141032</v>
       </c>
       <c r="G98" t="n">
-        <v>7.554245495084205</v>
+        <v>8.813426459976915</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I98" t="n">
-        <v>29.57445595462799</v>
+        <v>29.09650872009262</v>
       </c>
       <c r="J98" t="n">
-        <v>0.03843287733657647</v>
+        <v>0.01912752336797085</v>
       </c>
       <c r="K98" t="n">
-        <v>0.811777230593099</v>
+        <v>0.570701457653789</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -4197,22 +4197,22 @@
         <v>246</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1996662958843435</v>
+        <v>0.5556173526140675</v>
       </c>
       <c r="G99" t="n">
-        <v>7.635334961789337</v>
+        <v>8.404597863958431</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I99" t="n">
-        <v>107.6788976595723</v>
+        <v>109.8196578563709</v>
       </c>
       <c r="J99" t="n">
-        <v>0.02814409432225154</v>
+        <v>0.04111878077637569</v>
       </c>
       <c r="K99" t="n">
-        <v>0.6831499990936898</v>
+        <v>0.8776256998915958</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -4235,22 +4235,22 @@
         <v>478</v>
       </c>
       <c r="F100" t="n">
-        <v>0.3342521589972344</v>
+        <v>0.6555045588432066</v>
       </c>
       <c r="G100" t="n">
-        <v>23.87651272371126</v>
+        <v>25.96791237301322</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I100" t="n">
-        <v>115.4620289274368</v>
+        <v>117.6041123095149</v>
       </c>
       <c r="J100" t="n">
-        <v>0.08201713780476066</v>
+        <v>0.04015181021872496</v>
       </c>
       <c r="K100" t="n">
-        <v>1.35665438012248</v>
+        <v>0.8641300320377061</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -4279,16 +4279,16 @@
         <v>14.47703643706128</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I101" t="n">
-        <v>18.48126368536625</v>
+        <v>17.32638269460973</v>
       </c>
       <c r="J101" t="n">
-        <v>0.137907389940143</v>
+        <v>0.1261692422551859</v>
       </c>
       <c r="K101" t="n">
-        <v>2.055377289330403</v>
+        <v>2.064645066568778</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4311,22 +4311,22 @@
         <v>130</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3938346890648085</v>
+        <v>0.4497241379310769</v>
       </c>
       <c r="G102" t="n">
-        <v>23.05828416313746</v>
+        <v>23.40404662566535</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I102" t="n">
-        <v>36.28565662927191</v>
+        <v>34.74649648661303</v>
       </c>
       <c r="J102" t="n">
-        <v>0.0658856199569475</v>
+        <v>0.07245085035682697</v>
       </c>
       <c r="K102" t="n">
-        <v>1.154983057308247</v>
+        <v>1.314916371140202</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4349,22 +4349,22 @@
         <v>428</v>
       </c>
       <c r="F103" t="n">
-        <v>0.5760102012663708</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>11.75992413107179</v>
+        <v>10.02719427357424</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I103" t="n">
-        <v>33.73247072472946</v>
+        <v>32.40630702477093</v>
       </c>
       <c r="J103" t="n">
-        <v>0.008623822708241025</v>
+        <v>0.03049771574111161</v>
       </c>
       <c r="K103" t="n">
-        <v>0.4391135088371772</v>
+        <v>0.7293912321134592</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>155</v>
       </c>
       <c r="F104" t="n">
-        <v>0.5556173526140508</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>13.87427427862168</v>
+        <v>11.89204612335489</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I104" t="n">
-        <v>76.36728099023694</v>
+        <v>74.36725170743645</v>
       </c>
       <c r="J104" t="n">
-        <v>0.02045070869627643</v>
+        <v>0.009756284080578784</v>
       </c>
       <c r="K104" t="n">
-        <v>0.5869696352402826</v>
+        <v>0.4399103680995967</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -4431,16 +4431,16 @@
         <v>6.688712506902953</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I105" t="n">
-        <v>23.76653375198363</v>
+        <v>21.74970979379744</v>
       </c>
       <c r="J105" t="n">
-        <v>0.0220676678559542</v>
+        <v>0.02738320339889854</v>
       </c>
       <c r="K105" t="n">
-        <v>0.6071843661630153</v>
+        <v>0.6859230791642469</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4463,22 +4463,22 @@
         <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1996662958843599</v>
+        <v>0.8334260289210814</v>
       </c>
       <c r="G106" t="n">
-        <v>16.32303155199181</v>
+        <v>19.25110435256297</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I106" t="n">
-        <v>112.1475044553201</v>
+        <v>114.2612642159953</v>
       </c>
       <c r="J106" t="n">
-        <v>0.0134401498340233</v>
+        <v>0.03419724820874385</v>
       </c>
       <c r="K106" t="n">
-        <v>0.4993257636123382</v>
+        <v>0.7810243051194722</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -4507,16 +4507,16 @@
         <v>4.560359086738675</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I107" t="n">
-        <v>31.68920212049371</v>
+        <v>29.96750595711618</v>
       </c>
       <c r="J107" t="n">
-        <v>0.07631490487835869</v>
+        <v>0.03305311968435202</v>
       </c>
       <c r="K107" t="n">
-        <v>1.28536680085614</v>
+        <v>0.7650561058550949</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4545,16 +4545,16 @@
         <v>3.08676659305494</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I108" t="n">
-        <v>38.70272745795043</v>
+        <v>37.9803676266304</v>
       </c>
       <c r="J108" t="n">
-        <v>0.04644875606320967</v>
+        <v>0.05036985095449031</v>
       </c>
       <c r="K108" t="n">
-        <v>0.9119893049663566</v>
+        <v>1.006739631467942</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -4577,22 +4577,22 @@
         <v>198</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5556173526139859</v>
+        <v>0.5556173526140396</v>
       </c>
       <c r="G109" t="n">
-        <v>22.77512140307654</v>
+        <v>22.77512140307686</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I109" t="n">
-        <v>118.439399466708</v>
+        <v>120.5775716549919</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01148280969158146</v>
+        <v>0.01273668003488212</v>
       </c>
       <c r="K109" t="n">
-        <v>0.4748556933159366</v>
+        <v>0.4815067058103074</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4615,22 +4615,22 @@
         <v>640</v>
       </c>
       <c r="F110" t="n">
-        <v>0.05978865406007999</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>5.529150957604679</v>
+        <v>5.431724311855306</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I110" t="n">
-        <v>39.82016037470043</v>
+        <v>38.74183761133476</v>
       </c>
       <c r="J110" t="n">
-        <v>0.04160640427932183</v>
+        <v>0.03452883804969824</v>
       </c>
       <c r="K110" t="n">
-        <v>0.8514516978421202</v>
+        <v>0.785652187862993</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4653,22 +4653,22 @@
         <v>124</v>
       </c>
       <c r="F111" t="n">
-        <v>0.5556173526139928</v>
+        <v>0.555617352614012</v>
       </c>
       <c r="G111" t="n">
-        <v>15.41953945756023</v>
+        <v>15.41953945756031</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I111" t="n">
-        <v>110.1888161070285</v>
+        <v>112.3263481695639</v>
       </c>
       <c r="J111" t="n">
-        <v>0.02108024111226559</v>
+        <v>0.02585154497599968</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5948398577627207</v>
+        <v>0.6645462614550549</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -4697,16 +4697,16 @@
         <v>5.144277597486356</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I112" t="n">
-        <v>89.45152006903074</v>
+        <v>87.47532436223625</v>
       </c>
       <c r="J112" t="n">
-        <v>0.04794530646361207</v>
+        <v>0.09700574154659036</v>
       </c>
       <c r="K112" t="n">
-        <v>0.9306987222545899</v>
+        <v>1.657620348074671</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>376</v>
       </c>
       <c r="F113" t="n">
-        <v>0.279057738394296</v>
+        <v>0.5769632925472775</v>
       </c>
       <c r="G113" t="n">
-        <v>12.26201433781094</v>
+        <v>13.27323435906693</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I113" t="n">
-        <v>28.71644008978478</v>
+        <v>28.47488799768441</v>
       </c>
       <c r="J113" t="n">
-        <v>0.02425630193622897</v>
+        <v>0.07597042645028469</v>
       </c>
       <c r="K113" t="n">
-        <v>0.634546002822963</v>
+        <v>1.364037856347772</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4767,22 +4767,22 @@
         <v>366</v>
       </c>
       <c r="F114" t="n">
-        <v>0.3331479421579913</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>15.60332484568304</v>
+        <v>14.18555800805876</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I114" t="n">
-        <v>39.85633703896261</v>
+        <v>37.99274164306352</v>
       </c>
       <c r="J114" t="n">
-        <v>0.00579099415666447</v>
+        <v>0.006655078632036464</v>
       </c>
       <c r="K114" t="n">
-        <v>0.4036983491050248</v>
+        <v>0.396627934783445</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -4811,16 +4811,16 @@
         <v>20.08938572978278</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I115" t="n">
-        <v>53.97269619280505</v>
+        <v>52.14443161388473</v>
       </c>
       <c r="J115" t="n">
-        <v>0.003232608615174005</v>
+        <v>0.03612486376796295</v>
       </c>
       <c r="K115" t="n">
-        <v>0.3717141922954328</v>
+        <v>0.8079273572665955</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -4849,16 +4849,16 @@
         <v>6.463893795538414</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I116" t="n">
-        <v>109.0929473258484</v>
+        <v>111.2347222004942</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0224333681086326</v>
+        <v>0.0234994290003557</v>
       </c>
       <c r="K116" t="n">
-        <v>0.6117562393374389</v>
+        <v>0.6317186063522569</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>388</v>
       </c>
       <c r="F117" t="n">
-        <v>0.5556173526140004</v>
+        <v>0.4329810901001389</v>
       </c>
       <c r="G117" t="n">
-        <v>21.14595613198465</v>
+        <v>20.47912817844968</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I117" t="n">
-        <v>32.07437755633905</v>
+        <v>30.10502168313632</v>
       </c>
       <c r="J117" t="n">
-        <v>0.04599105853165339</v>
+        <v>0.02299869485810145</v>
       </c>
       <c r="K117" t="n">
-        <v>0.906267309831827</v>
+        <v>0.624730036107281</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -4925,16 +4925,16 @@
         <v>8.030018742194814</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I118" t="n">
-        <v>24.56080801932843</v>
+        <v>22.63473056442236</v>
       </c>
       <c r="J118" t="n">
-        <v>0.0415461580087871</v>
+        <v>0.02292305872481806</v>
       </c>
       <c r="K118" t="n">
-        <v>0.8506985173176346</v>
+        <v>0.6236744092068868</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -4957,22 +4957,22 @@
         <v>165</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>0.008371523915462193</v>
       </c>
       <c r="G119" t="n">
-        <v>13.39425787417877</v>
+        <v>13.42789697921584</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I119" t="n">
-        <v>24.17872987986367</v>
+        <v>22.2937981510697</v>
       </c>
       <c r="J119" t="n">
-        <v>0.0111583662967203</v>
+        <v>0.02204339094856612</v>
       </c>
       <c r="K119" t="n">
-        <v>0.4707996008119779</v>
+        <v>0.6113971955563406</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -5001,16 +5001,16 @@
         <v>3.330100148644182</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I120" t="n">
-        <v>102.8229624758939</v>
+        <v>104.9637181944468</v>
       </c>
       <c r="J120" t="n">
-        <v>0.03829221401732969</v>
+        <v>0.0572564195871033</v>
       </c>
       <c r="K120" t="n">
-        <v>0.8100187006189475</v>
+        <v>1.10285304690073</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5033,22 +5033,22 @@
         <v>57</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>0.555671410901072</v>
       </c>
       <c r="G121" t="n">
-        <v>7.701882886671284</v>
+        <v>8.985797725740721</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I121" t="n">
-        <v>30.50491180544313</v>
+        <v>28.58637125554106</v>
       </c>
       <c r="J121" t="n">
-        <v>0.02655526897945019</v>
+        <v>0.04133894910270769</v>
       </c>
       <c r="K121" t="n">
-        <v>0.6632869885805803</v>
+        <v>0.8806985117581145</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -5077,16 +5077,16 @@
         <v>5.670752331040389</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I122" t="n">
-        <v>117.457125890694</v>
+        <v>119.5860631766918</v>
       </c>
       <c r="J122" t="n">
-        <v>0.02287717085443605</v>
+        <v>0.02520629807468851</v>
       </c>
       <c r="K122" t="n">
-        <v>0.6173045260925445</v>
+        <v>0.6555407774773387</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>2.935153317971652</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I123" t="n">
-        <v>38.1937050975917</v>
+        <v>36.08106276858302</v>
       </c>
       <c r="J123" t="n">
-        <v>0.04706777367192203</v>
+        <v>0.0148709053565179</v>
       </c>
       <c r="K123" t="n">
-        <v>0.919728074570808</v>
+        <v>0.5112933377178329</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -5153,16 +5153,16 @@
         <v>20.29361436511495</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I124" t="n">
-        <v>26.5526471562621</v>
+        <v>24.56653125484663</v>
       </c>
       <c r="J124" t="n">
-        <v>0.04139223048854068</v>
+        <v>0.03594706057169879</v>
       </c>
       <c r="K124" t="n">
-        <v>0.8487741623425809</v>
+        <v>0.8054458206146722</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -5191,16 +5191,16 @@
         <v>12.02926119925908</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I125" t="n">
-        <v>63.09836171438233</v>
+        <v>61.08747838338837</v>
       </c>
       <c r="J125" t="n">
-        <v>0.02356197287201956</v>
+        <v>0.0362793677368172</v>
       </c>
       <c r="K125" t="n">
-        <v>0.6258657123401636</v>
+        <v>0.8100837147991666</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -5229,16 +5229,16 @@
         <v>20.00788726977439</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I126" t="n">
-        <v>69.03067443975461</v>
+        <v>66.9284621019665</v>
       </c>
       <c r="J126" t="n">
-        <v>0.07877176392598023</v>
+        <v>0.07013288824031104</v>
       </c>
       <c r="K126" t="n">
-        <v>1.316081704362205</v>
+        <v>1.282565389432549</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -5267,16 +5267,16 @@
         <v>11.24748896420885</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I127" t="n">
-        <v>20.80023579822671</v>
+        <v>19.71586386769579</v>
       </c>
       <c r="J127" t="n">
-        <v>0.06690533086610095</v>
+        <v>0.06464857283242573</v>
       </c>
       <c r="K127" t="n">
-        <v>1.16773117251211</v>
+        <v>1.206022728888046</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>11.07986791437515</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I128" t="n">
-        <v>179.6441411708182</v>
+        <v>178.3092593914622</v>
       </c>
       <c r="J128" t="n">
-        <v>0.01172223610072976</v>
+        <v>0.03287465564440775</v>
       </c>
       <c r="K128" t="n">
-        <v>0.4778489293588887</v>
+        <v>0.7625653460404396</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -5343,16 +5343,16 @@
         <v>5.484544739538552</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I129" t="n">
-        <v>105.1318762908388</v>
+        <v>107.2556686152775</v>
       </c>
       <c r="J129" t="n">
-        <v>0.2417980088304475</v>
+        <v>0.2323274760503178</v>
       </c>
       <c r="K129" t="n">
-        <v>3.354186163811938</v>
+        <v>3.546258184899249</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -5375,22 +5375,22 @@
         <v>575</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2066191162060811</v>
+        <v>0.1996662958843493</v>
       </c>
       <c r="G130" t="n">
-        <v>8.147851124990741</v>
+        <v>8.131847931250766</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I130" t="n">
-        <v>66.43693035394483</v>
+        <v>64.43203187690828</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>0.05551323106844575</v>
       </c>
       <c r="K130" t="n">
-        <v>0.3313011039727364</v>
+        <v>1.078523978069853</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -5413,22 +5413,22 @@
         <v>174</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0002061239924824747</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>3.533937236384185</v>
+        <v>3.533718721120853</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I131" t="n">
-        <v>107.5232864950917</v>
+        <v>109.6627664330125</v>
       </c>
       <c r="J131" t="n">
-        <v>0.0497702452428507</v>
+        <v>0.0110561828042159</v>
       </c>
       <c r="K131" t="n">
-        <v>0.9535135510348798</v>
+        <v>0.4580525972286019</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -5457,16 +5457,16 @@
         <v>6.408090589247315</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I132" t="n">
-        <v>54.31264821633182</v>
+        <v>52.20936080664899</v>
       </c>
       <c r="J132" t="n">
-        <v>0.012502667022566</v>
+        <v>0.007863647123674523</v>
       </c>
       <c r="K132" t="n">
-        <v>0.487605639040934</v>
+        <v>0.4134954999980985</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -5489,22 +5489,22 @@
         <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>0.00089809284676518</v>
+        <v>5.405828698564195e-05</v>
       </c>
       <c r="G133" t="n">
-        <v>11.35152114457479</v>
+        <v>11.3486475959432</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I133" t="n">
-        <v>60.63872986314242</v>
+        <v>58.60376340991579</v>
       </c>
       <c r="J133" t="n">
-        <v>0.06053101918535458</v>
+        <v>0.03497259770907235</v>
       </c>
       <c r="K133" t="n">
-        <v>1.088041469359929</v>
+        <v>0.7918455852963318</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -5533,16 +5533,16 @@
         <v>5.697522180737868</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I134" t="n">
-        <v>114.6627312110546</v>
+        <v>116.7975906726565</v>
       </c>
       <c r="J134" t="n">
-        <v>0.04921469924038625</v>
+        <v>0.06106951321507234</v>
       </c>
       <c r="K134" t="n">
-        <v>0.9465682841196307</v>
+        <v>1.156071053066167</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -5565,22 +5565,22 @@
         <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3331479421579785</v>
+        <v>0.3334234304783526</v>
       </c>
       <c r="G135" t="n">
-        <v>16.20624626952032</v>
+        <v>16.20746395787842</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I135" t="n">
-        <v>106.7159160109704</v>
+        <v>108.8503562615069</v>
       </c>
       <c r="J135" t="n">
-        <v>0.03474857450137577</v>
+        <v>0.07402504767523412</v>
       </c>
       <c r="K135" t="n">
-        <v>0.7657171987081343</v>
+        <v>1.336886889247104</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>97</v>
       </c>
       <c r="F136" t="n">
-        <v>0.5556173526140011</v>
+        <v>1</v>
       </c>
       <c r="G136" t="n">
-        <v>22.49298151702468</v>
+        <v>25.06320970486422</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I136" t="n">
-        <v>105.9235198350917</v>
+        <v>108.0650131451876</v>
       </c>
       <c r="J136" t="n">
-        <v>0.03288985232840752</v>
+        <v>0.03981243965363022</v>
       </c>
       <c r="K136" t="n">
-        <v>0.7424800202291439</v>
+        <v>0.8593935564649311</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -5641,22 +5641,22 @@
         <v>496</v>
       </c>
       <c r="F137" t="n">
-        <v>0.05978865406006932</v>
+        <v>0.2007721468298446</v>
       </c>
       <c r="G137" t="n">
-        <v>13.7434357497768</v>
+        <v>14.31447256538772</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I137" t="n">
-        <v>36.90582284255272</v>
+        <v>35.20358886866349</v>
       </c>
       <c r="J137" t="n">
-        <v>0.05227039634721154</v>
+        <v>0.06322087175549217</v>
       </c>
       <c r="K137" t="n">
-        <v>0.984769678648455</v>
+        <v>1.186096807280105</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -5685,16 +5685,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I138" t="n">
-        <v>108.1014074142814</v>
+        <v>110.2434676749111</v>
       </c>
       <c r="J138" t="n">
-        <v>0.04195324687022794</v>
+        <v>0.03889020661070718</v>
       </c>
       <c r="K138" t="n">
-        <v>0.8557878182727117</v>
+        <v>0.8465222743636338</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -5717,22 +5717,22 @@
         <v>498</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1996662958843395</v>
+        <v>0.2778086763070295</v>
       </c>
       <c r="G139" t="n">
-        <v>8.037959314084993</v>
+        <v>8.215741748407643</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I139" t="n">
-        <v>74.44141948478546</v>
+        <v>72.31849272078884</v>
       </c>
       <c r="J139" t="n">
-        <v>0.09682083976855234</v>
+        <v>0.0819757304222492</v>
       </c>
       <c r="K139" t="n">
-        <v>1.541725753179309</v>
+        <v>1.447851770976339</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -5755,22 +5755,22 @@
         <v>631</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>0.2778086763070762</v>
       </c>
       <c r="G140" t="n">
-        <v>5.222154823442138</v>
+        <v>5.657382799133461</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I140" t="n">
-        <v>24.44294408821018</v>
+        <v>23.25092832022016</v>
       </c>
       <c r="J140" t="n">
-        <v>0.07686217823273767</v>
+        <v>0.05073888684171757</v>
       </c>
       <c r="K140" t="n">
-        <v>1.292208645644698</v>
+        <v>1.011890135504264</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>240</v>
       </c>
       <c r="F141" t="n">
-        <v>0.6326473859844199</v>
+        <v>0.5556173526140057</v>
       </c>
       <c r="G141" t="n">
-        <v>23.56342816914693</v>
+        <v>23.10576289373354</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I141" t="n">
-        <v>23.38279461394301</v>
+        <v>21.79538453295892</v>
       </c>
       <c r="J141" t="n">
-        <v>0.01525511977774123</v>
+        <v>0.02178402797986163</v>
       </c>
       <c r="K141" t="n">
-        <v>0.5220159650472446</v>
+        <v>0.607777357856485</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -5837,16 +5837,16 @@
         <v>13.28753103477091</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I142" t="n">
-        <v>21.12428056504043</v>
+        <v>19.66145414838973</v>
       </c>
       <c r="J142" t="n">
-        <v>0.02833216705338656</v>
+        <v>0.04145905219763923</v>
       </c>
       <c r="K142" t="n">
-        <v>0.685501227095364</v>
+        <v>0.8823747483969613</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -5869,22 +5869,22 @@
         <v>480</v>
       </c>
       <c r="F143" t="n">
-        <v>0.002628014982471252</v>
+        <v>0.07152391546162952</v>
       </c>
       <c r="G143" t="n">
-        <v>5.755722052665244</v>
+        <v>5.874592031157748</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I143" t="n">
-        <v>169.7355751655949</v>
+        <v>169.1573788188489</v>
       </c>
       <c r="J143" t="n">
-        <v>0.01876655297518609</v>
+        <v>0.02534542826637703</v>
       </c>
       <c r="K143" t="n">
-        <v>0.565914833373421</v>
+        <v>0.6574825686111225</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -5907,22 +5907,22 @@
         <v>226</v>
       </c>
       <c r="F144" t="n">
-        <v>0.3929365962180243</v>
+        <v>0.5558928409344037</v>
       </c>
       <c r="G144" t="n">
-        <v>24.86911277719054</v>
+        <v>25.95668219760744</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I144" t="n">
-        <v>106.4884323052565</v>
+        <v>108.6292336416902</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1991196633147025</v>
+        <v>0.1239962702550718</v>
       </c>
       <c r="K144" t="n">
-        <v>2.820634487095419</v>
+        <v>2.034317660902374</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>7.001992287913491</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I145" t="n">
-        <v>37.24166256156995</v>
+        <v>35.26856468239285</v>
       </c>
       <c r="J145" t="n">
-        <v>0.09537343253200714</v>
+        <v>0.07510067823845167</v>
       </c>
       <c r="K145" t="n">
-        <v>1.52363070875765</v>
+        <v>1.351899086567717</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -5989,16 +5989,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I146" t="n">
-        <v>93.58909411372944</v>
+        <v>91.57310119026025</v>
       </c>
       <c r="J146" t="n">
-        <v>0.01666402564775143</v>
+        <v>0.01379230287753385</v>
       </c>
       <c r="K146" t="n">
-        <v>0.5396296771111848</v>
+        <v>0.4962396624145066</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -6021,22 +6021,22 @@
         <v>143</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0.83342602892105</v>
       </c>
       <c r="G147" t="n">
-        <v>27.61445003019253</v>
+        <v>26.55294650695628</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I147" t="n">
-        <v>81.86216132202853</v>
+        <v>79.80545941607964</v>
       </c>
       <c r="J147" t="n">
-        <v>0.04507973365153492</v>
+        <v>0.06254764110937286</v>
       </c>
       <c r="K147" t="n">
-        <v>0.8948742037508683</v>
+        <v>1.176700764021911</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -6059,22 +6059,22 @@
         <v>93</v>
       </c>
       <c r="F148" t="n">
-        <v>0.5556173526140011</v>
+        <v>0.00641757330367245</v>
       </c>
       <c r="G148" t="n">
-        <v>21.05408384692022</v>
+        <v>18.08081441357613</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I148" t="n">
-        <v>22.78207889383847</v>
+        <v>22.39341445150479</v>
       </c>
       <c r="J148" t="n">
-        <v>0.04952028780533011</v>
+        <v>0.03086263098422552</v>
       </c>
       <c r="K148" t="n">
-        <v>0.9503886592827457</v>
+        <v>0.7344842257697</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -6097,22 +6097,22 @@
         <v>499</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5565154454607822</v>
+        <v>0.5556173526140171</v>
       </c>
       <c r="G149" t="n">
-        <v>21.33502609999434</v>
+        <v>21.33010024415377</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I149" t="n">
-        <v>117.4995577163778</v>
+        <v>119.641772479702</v>
       </c>
       <c r="J149" t="n">
-        <v>0.0259089906527061</v>
+        <v>0.0264751840630297</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6552074137823342</v>
+        <v>0.6732501727713497</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>578</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0004122479849647518</v>
+        <v>0.04269187986652515</v>
       </c>
       <c r="G150" t="n">
-        <v>15.77719073785156</v>
+        <v>15.97728213662523</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I150" t="n">
-        <v>152.1546191495728</v>
+        <v>150.0702595585187</v>
       </c>
       <c r="J150" t="n">
-        <v>0.07238428207733777</v>
+        <v>0.03767065476728669</v>
       </c>
       <c r="K150" t="n">
-        <v>1.236227351782342</v>
+        <v>0.8295014183725391</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -6173,22 +6173,22 @@
         <v>421</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>0.4543270300333869</v>
       </c>
       <c r="G151" t="n">
-        <v>21.53334214654102</v>
+        <v>24.46829596178025</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I151" t="n">
-        <v>29.5052140846556</v>
+        <v>28.43038920641624</v>
       </c>
       <c r="J151" t="n">
-        <v>0.2477587346400577</v>
+        <v>0.1649995224296121</v>
       </c>
       <c r="K151" t="n">
-        <v>3.428705342372682</v>
+        <v>2.60658562490459</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -6211,22 +6211,22 @@
         <v>108</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>0.042691879866529</v>
       </c>
       <c r="G152" t="n">
-        <v>16.84023138202085</v>
+        <v>17.05591372254659</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I152" t="n">
-        <v>30.63667124074981</v>
+        <v>28.54263066443623</v>
       </c>
       <c r="J152" t="n">
-        <v>0.0332539528982275</v>
+        <v>0.02952621615574516</v>
       </c>
       <c r="K152" t="n">
-        <v>0.7470318946557012</v>
+        <v>0.7158323542132361</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -6249,22 +6249,22 @@
         <v>79</v>
       </c>
       <c r="F153" t="n">
-        <v>0.01776483366990523</v>
+        <v>0.5556173526140196</v>
       </c>
       <c r="G153" t="n">
-        <v>14.33423083849478</v>
+        <v>16.63488029112043</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I153" t="n">
-        <v>38.97388716672818</v>
+        <v>37.86722477299343</v>
       </c>
       <c r="J153" t="n">
-        <v>0.0296264627514681</v>
+        <v>0.0139128402633241</v>
       </c>
       <c r="K153" t="n">
-        <v>0.7016821176976863</v>
+        <v>0.4979219602980672</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -6293,16 +6293,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I154" t="n">
-        <v>35.11569503810817</v>
+        <v>34.11655722819767</v>
       </c>
       <c r="J154" t="n">
-        <v>0.06329562115928929</v>
+        <v>0.079838980585012</v>
       </c>
       <c r="K154" t="n">
-        <v>1.122603681198775</v>
+        <v>1.418029905292791</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -6325,22 +6325,22 @@
         <v>398</v>
       </c>
       <c r="F155" t="n">
-        <v>0.01520862976525576</v>
+        <v>0.3331479421579995</v>
       </c>
       <c r="G155" t="n">
-        <v>17.11055058970367</v>
+        <v>18.73517311171549</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I155" t="n">
-        <v>72.31699048730442</v>
+        <v>70.23578479127897</v>
       </c>
       <c r="J155" t="n">
-        <v>0.0621659557769953</v>
+        <v>0.02978851144110627</v>
       </c>
       <c r="K155" t="n">
-        <v>1.108480948661517</v>
+        <v>0.7194931172249609</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -6363,22 +6363,22 @@
         <v>369</v>
       </c>
       <c r="F156" t="n">
-        <v>0.3401007624796988</v>
+        <v>0.722191323693021</v>
       </c>
       <c r="G156" t="n">
-        <v>24.88935696132717</v>
+        <v>27.47821200038494</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I156" t="n">
-        <v>115.2863357844628</v>
+        <v>117.4232945545316</v>
       </c>
       <c r="J156" t="n">
-        <v>0.06522269727528598</v>
+        <v>0.07113829149279545</v>
       </c>
       <c r="K156" t="n">
-        <v>1.146695399854342</v>
+        <v>1.29659744888606</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -6401,22 +6401,22 @@
         <v>82</v>
       </c>
       <c r="F157" t="n">
-        <v>0.5556173526140472</v>
+        <v>0.2778086763070295</v>
       </c>
       <c r="G157" t="n">
-        <v>12.1161354524659</v>
+        <v>11.25061469279957</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I157" t="n">
-        <v>113.4313812189094</v>
+        <v>115.5626250666605</v>
       </c>
       <c r="J157" t="n">
-        <v>0.09179887423407228</v>
+        <v>0.1018013114012729</v>
       </c>
       <c r="K157" t="n">
-        <v>1.478942669651718</v>
+        <v>1.724550429261587</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -6439,22 +6439,22 @@
         <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>0.3331479421579749</v>
+        <v>0.6586322580645454</v>
       </c>
       <c r="G158" t="n">
-        <v>20.02303321678843</v>
+        <v>21.80053670835273</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I158" t="n">
-        <v>103.6167029787448</v>
+        <v>105.7580302415108</v>
       </c>
       <c r="J158" t="n">
-        <v>0.07714860013500324</v>
+        <v>0.1505325181426602</v>
       </c>
       <c r="K158" t="n">
-        <v>1.295789405028769</v>
+        <v>2.404674736147188</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -6477,22 +6477,22 @@
         <v>637</v>
       </c>
       <c r="F159" t="n">
-        <v>0.09983314794218011</v>
+        <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>4.903382489061847</v>
+        <v>4.760796887076785</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I159" t="n">
-        <v>40.2183815971469</v>
+        <v>39.36683702149551</v>
       </c>
       <c r="J159" t="n">
-        <v>0.1450133666311872</v>
+        <v>0.1270153590555533</v>
       </c>
       <c r="K159" t="n">
-        <v>2.144214045591641</v>
+        <v>2.076454021053489</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>539</v>
       </c>
       <c r="F160" t="n">
-        <v>0.4997219132369632</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>19.6307379719013</v>
+        <v>22.19287898020444</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I160" t="n">
-        <v>55.37949683734299</v>
+        <v>53.29028302362429</v>
       </c>
       <c r="J160" t="n">
-        <v>0.05965511082725502</v>
+        <v>0.03896900916175289</v>
       </c>
       <c r="K160" t="n">
-        <v>1.077091129850127</v>
+        <v>0.8476220938426631</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
@@ -6553,22 +6553,22 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>0.5625701729357576</v>
+        <v>0.5556714109010127</v>
       </c>
       <c r="G161" t="n">
-        <v>23.62301383883505</v>
+        <v>23.58118283589688</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I161" t="n">
-        <v>42.64336549795016</v>
+        <v>40.63490871157534</v>
       </c>
       <c r="J161" t="n">
-        <v>0.1183137428272863</v>
+        <v>0.1066671524747809</v>
       </c>
       <c r="K161" t="n">
-        <v>1.810423480935941</v>
+        <v>1.7924612611254</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
@@ -6597,16 +6597,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I162" t="n">
-        <v>87.55889695244385</v>
+        <v>85.51667174268432</v>
       </c>
       <c r="J162" t="n">
-        <v>0.0597931769019299</v>
+        <v>0.04617426589159087</v>
       </c>
       <c r="K162" t="n">
-        <v>1.078817189863706</v>
+        <v>0.9481833269210945</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
@@ -6629,22 +6629,22 @@
         <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>0.4461743828673509</v>
+        <v>0.1020448498331738</v>
       </c>
       <c r="G163" t="n">
-        <v>19.88438440337678</v>
+        <v>18.07388302774133</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I163" t="n">
-        <v>95.10524144130524</v>
+        <v>93.1045955081715</v>
       </c>
       <c r="J163" t="n">
-        <v>0.07511774543357587</v>
+        <v>0.05971453313723352</v>
       </c>
       <c r="K163" t="n">
-        <v>1.27040027810691</v>
+        <v>1.137160072856411</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
@@ -6667,22 +6667,22 @@
         <v>624</v>
       </c>
       <c r="F164" t="n">
-        <v>0.5556173526140746</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>13.35824053239593</v>
+        <v>11.449738512298</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I164" t="n">
-        <v>18.70531511010921</v>
+        <v>16.76063733315944</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1455432506212367</v>
+        <v>0.1103454050912997</v>
       </c>
       <c r="K164" t="n">
-        <v>2.150838493843784</v>
+        <v>1.843797338736533</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -6711,16 +6711,16 @@
         <v>4.635186296148192</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I165" t="n">
-        <v>32.60614168986485</v>
+        <v>30.58499220272013</v>
       </c>
       <c r="J165" t="n">
-        <v>0.01937378495350156</v>
+        <v>0.03030417641767487</v>
       </c>
       <c r="K165" t="n">
-        <v>0.5735062626163044</v>
+        <v>0.7266900718711924</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
@@ -6749,16 +6749,16 @@
         <v>15.96371209963397</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I166" t="n">
-        <v>111.5048761915417</v>
+        <v>113.6462632211306</v>
       </c>
       <c r="J166" t="n">
-        <v>0.0696870251246816</v>
+        <v>0.05899170465040631</v>
       </c>
       <c r="K166" t="n">
-        <v>1.202507066887651</v>
+        <v>1.127071809985978</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
@@ -6787,16 +6787,16 @@
         <v>9.514139425087274</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I167" t="n">
-        <v>20.6601594799835</v>
+        <v>19.97388940409684</v>
       </c>
       <c r="J167" t="n">
-        <v>0.09872323122461565</v>
+        <v>0.05488212886523661</v>
       </c>
       <c r="K167" t="n">
-        <v>1.565508871734814</v>
+        <v>1.069715906666872</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -6819,22 +6819,22 @@
         <v>106</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0001396238191203448</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>19.03936614123994</v>
+        <v>19.03856866993945</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I168" t="n">
-        <v>34.40772855833136</v>
+        <v>33.06495335771849</v>
       </c>
       <c r="J168" t="n">
-        <v>0.05373942225808059</v>
+        <v>0.04869408441945994</v>
       </c>
       <c r="K168" t="n">
-        <v>1.00313499315192</v>
+        <v>0.9833515475407766</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
@@ -6857,22 +6857,22 @@
         <v>211</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1996662958843595</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>8.006743959945577</v>
+        <v>7.554245495084205</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I169" t="n">
-        <v>66.97162082788286</v>
+        <v>64.84181881373597</v>
       </c>
       <c r="J169" t="n">
-        <v>0.01507335323866049</v>
+        <v>0.02474350472205482</v>
       </c>
       <c r="K169" t="n">
-        <v>0.5197435751379003</v>
+        <v>0.6490817334839969</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -6901,16 +6901,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I170" t="n">
-        <v>130.681223818928</v>
+        <v>129.3282169229969</v>
       </c>
       <c r="J170" t="n">
-        <v>0.09335733714686609</v>
+        <v>0.06106851050349028</v>
       </c>
       <c r="K170" t="n">
-        <v>1.498426098312627</v>
+        <v>1.156057058573411</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
@@ -6933,22 +6933,22 @@
         <v>255</v>
       </c>
       <c r="F171" t="n">
-        <v>0.3102377814855641</v>
+        <v>0.0002754883203560995</v>
       </c>
       <c r="G171" t="n">
-        <v>11.89243382160549</v>
+        <v>10.88073240491899</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I171" t="n">
-        <v>172.6152698054358</v>
+        <v>171.6568072679967</v>
       </c>
       <c r="J171" t="n">
-        <v>0.1032299815747549</v>
+        <v>0.05974131441074392</v>
       </c>
       <c r="K171" t="n">
-        <v>1.621850891951423</v>
+        <v>1.137533849668063</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>2.82842712474619</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I172" t="n">
-        <v>37.4311333067527</v>
+        <v>35.43481575162259</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2112821458370673</v>
+        <v>0.2472972196780266</v>
       </c>
       <c r="K172" t="n">
-        <v>2.972686139155105</v>
+        <v>3.755185629751618</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>686</v>
       </c>
       <c r="F173" t="n">
-        <v>0.6554505005561951</v>
+        <v>0.5558928409344058</v>
       </c>
       <c r="G173" t="n">
-        <v>19.147952597346</v>
+        <v>18.67003114897264</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I173" t="n">
-        <v>32.96474931318231</v>
+        <v>30.90803994807395</v>
       </c>
       <c r="J173" t="n">
-        <v>0.01506104127036936</v>
+        <v>0.02818474505659737</v>
       </c>
       <c r="K173" t="n">
-        <v>0.5195896546602897</v>
+        <v>0.6971099140660667</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -7047,22 +7047,22 @@
         <v>591</v>
       </c>
       <c r="F174" t="n">
-        <v>0.3331479421579925</v>
+        <v>0.5556714109010233</v>
       </c>
       <c r="G174" t="n">
-        <v>20.50235332772793</v>
+        <v>21.74666754538881</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I174" t="n">
-        <v>34.51291690419441</v>
+        <v>33.63389105679053</v>
       </c>
       <c r="J174" t="n">
-        <v>0.04786805978330853</v>
+        <v>0.03278323028417384</v>
       </c>
       <c r="K174" t="n">
-        <v>0.92973300778514</v>
+        <v>0.7612893544547841</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>105</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>0.2778086763070515</v>
       </c>
       <c r="G175" t="n">
-        <v>8.792540929674423</v>
+        <v>9.525334176788951</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I175" t="n">
-        <v>96.32287938819482</v>
+        <v>98.45051006898224</v>
       </c>
       <c r="J175" t="n">
-        <v>0.06009244641338285</v>
+        <v>0.03546547119666855</v>
       </c>
       <c r="K175" t="n">
-        <v>1.082558566144728</v>
+        <v>0.7987244471499406</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -7123,22 +7123,22 @@
         <v>237</v>
       </c>
       <c r="F176" t="n">
-        <v>0.002567577487512626</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>6.807318479905544</v>
+        <v>6.802079020417213</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I176" t="n">
-        <v>34.58507146887644</v>
+        <v>32.95291393681884</v>
       </c>
       <c r="J176" t="n">
-        <v>0.05636715071325399</v>
+        <v>0.07297371815162612</v>
       </c>
       <c r="K176" t="n">
-        <v>1.035986053947991</v>
+        <v>1.322213852986236</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -7161,22 +7161,22 @@
         <v>389</v>
       </c>
       <c r="F177" t="n">
-        <v>0.3695757023445453</v>
+        <v>0.5935910122358463</v>
       </c>
       <c r="G177" t="n">
-        <v>19.78521892649304</v>
+        <v>20.98216757048645</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I177" t="n">
-        <v>52.65147962623947</v>
+        <v>50.51992698432778</v>
       </c>
       <c r="J177" t="n">
-        <v>0.04851277039300932</v>
+        <v>0.05662153162935981</v>
       </c>
       <c r="K177" t="n">
-        <v>0.9377929834624044</v>
+        <v>1.093992139053694</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -7199,22 +7199,22 @@
         <v>434</v>
       </c>
       <c r="F178" t="n">
-        <v>0.1996662958843516</v>
+        <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>4.164509596786643</v>
+        <v>3.929153725676816</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I178" t="n">
-        <v>18.93367757586399</v>
+        <v>17.67620934095163</v>
       </c>
       <c r="J178" t="n">
-        <v>0.0344739057514559</v>
+        <v>0.02635174359775426</v>
       </c>
       <c r="K178" t="n">
-        <v>0.7622833736549275</v>
+        <v>0.6715273576288346</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -7237,22 +7237,22 @@
         <v>266</v>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>0.007143067854404994</v>
       </c>
       <c r="G179" t="n">
-        <v>3.330100148644182</v>
+        <v>3.3372362880413</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I179" t="n">
-        <v>25.50237808473407</v>
+        <v>23.3890535412473</v>
       </c>
       <c r="J179" t="n">
-        <v>0.04188588821889993</v>
+        <v>0.05119377666582605</v>
       </c>
       <c r="K179" t="n">
-        <v>0.8549457209298292</v>
+        <v>1.018238872730759</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
@@ -7275,22 +7275,22 @@
         <v>137</v>
       </c>
       <c r="F180" t="n">
-        <v>0.5556173526140308</v>
+        <v>0.5187176481845532</v>
       </c>
       <c r="G180" t="n">
-        <v>14.39678690131677</v>
+        <v>14.26018522536537</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I180" t="n">
-        <v>68.87768928795569</v>
+        <v>66.8049253058041</v>
       </c>
       <c r="J180" t="n">
-        <v>0.03601386292547257</v>
+        <v>0.04421688766968496</v>
       </c>
       <c r="K180" t="n">
-        <v>0.7815354492061015</v>
+        <v>0.9208648877625565</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -7313,22 +7313,22 @@
         <v>400</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5558234766065313</v>
+        <v>0.5556173526140029</v>
       </c>
       <c r="G181" t="n">
-        <v>16.67821818751228</v>
+        <v>16.67733424760215</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I181" t="n">
-        <v>35.51398051338204</v>
+        <v>33.52331607343476</v>
       </c>
       <c r="J181" t="n">
-        <v>0.03363041628882302</v>
+        <v>0.02077855868513771</v>
       </c>
       <c r="K181" t="n">
-        <v>0.7517383253021404</v>
+        <v>0.5937443766746734</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>455</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>0.0005509766407120014</v>
       </c>
       <c r="G182" t="n">
-        <v>13.18108918109577</v>
+        <v>13.18326792276715</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I182" t="n">
-        <v>28.89808091454841</v>
+        <v>27.11507121833307</v>
       </c>
       <c r="J182" t="n">
-        <v>0.01121578801305099</v>
+        <v>0.07205484517922305</v>
       </c>
       <c r="K182" t="n">
-        <v>0.471517469620104</v>
+        <v>1.309389466206977</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I183" t="n">
-        <v>103.7986392143959</v>
+        <v>105.9410417546677</v>
       </c>
       <c r="J183" t="n">
-        <v>0.02738884749367671</v>
+        <v>0.04111230773203017</v>
       </c>
       <c r="K183" t="n">
-        <v>0.6737081332750565</v>
+        <v>0.8775353578891434</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -7427,22 +7427,22 @@
         <v>547</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>0.09983314794216577</v>
       </c>
       <c r="G184" t="n">
-        <v>10.22189370909324</v>
+        <v>10.52803885716594</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I184" t="n">
-        <v>24.89108861760429</v>
+        <v>22.81272033570257</v>
       </c>
       <c r="J184" t="n">
-        <v>0.09785423508386254</v>
+        <v>0.06325323914016245</v>
       </c>
       <c r="K184" t="n">
-        <v>1.554644946660962</v>
+        <v>1.186548547479796</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -7465,22 +7465,22 @@
         <v>625</v>
       </c>
       <c r="F185" t="n">
-        <v>0.5556173526140642</v>
+        <v>0.4801446051168408</v>
       </c>
       <c r="G185" t="n">
-        <v>8.472285698004102</v>
+        <v>8.30786430754514</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I185" t="n">
-        <v>69.10325628326945</v>
+        <v>67.09898453728924</v>
       </c>
       <c r="J185" t="n">
-        <v>0.005205587024863732</v>
+        <v>0.00782701330717828</v>
       </c>
       <c r="K185" t="n">
-        <v>0.396379767445882</v>
+        <v>0.4129842147105146</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
@@ -7503,22 +7503,22 @@
         <v>13</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3331479421579884</v>
+        <v>0.3331479421580295</v>
       </c>
       <c r="G186" t="n">
-        <v>13.0429473623322</v>
+        <v>13.04294736233235</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I186" t="n">
-        <v>24.78738334198986</v>
+        <v>23.97765559490883</v>
       </c>
       <c r="J186" t="n">
-        <v>0.06029215667248761</v>
+        <v>0.0603200262343189</v>
       </c>
       <c r="K186" t="n">
-        <v>1.085055282976535</v>
+        <v>1.145610726975539</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -7541,22 +7541,22 @@
         <v>331</v>
       </c>
       <c r="F187" t="n">
-        <v>0.03642776018657633</v>
+        <v>0.01701853615128207</v>
       </c>
       <c r="G187" t="n">
-        <v>20.93039311025401</v>
+        <v>20.80983777183406</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I187" t="n">
-        <v>102.5976910090707</v>
+        <v>104.7392824085638</v>
       </c>
       <c r="J187" t="n">
-        <v>0.0197860082713163</v>
+        <v>0.03548192405491247</v>
       </c>
       <c r="K187" t="n">
-        <v>0.5786597529811208</v>
+        <v>0.7989540739036718</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -7579,22 +7579,22 @@
         <v>180</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>0.55561735261407</v>
       </c>
       <c r="G188" t="n">
-        <v>4.072023452781184</v>
+        <v>4.750769519966189</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I188" t="n">
-        <v>104.8452118577313</v>
+        <v>106.9788372880925</v>
       </c>
       <c r="J188" t="n">
-        <v>0.1779200975072039</v>
+        <v>0.1197638333317601</v>
       </c>
       <c r="K188" t="n">
-        <v>2.555603972309409</v>
+        <v>1.975247027905724</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -7617,22 +7617,22 @@
         <v>414</v>
       </c>
       <c r="F189" t="n">
-        <v>0.6979329882177507</v>
+        <v>0.2007721468298443</v>
       </c>
       <c r="G189" t="n">
-        <v>24.69128246510615</v>
+        <v>21.6461999063891</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I189" t="n">
-        <v>35.57118246076672</v>
+        <v>34.42261139509194</v>
       </c>
       <c r="J189" t="n">
-        <v>0.05137446215069136</v>
+        <v>0.06133944673773306</v>
       </c>
       <c r="K189" t="n">
-        <v>0.9735689822061654</v>
+        <v>1.159838420268443</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -7655,22 +7655,22 @@
         <v>667</v>
       </c>
       <c r="F190" t="n">
-        <v>0.1067859682639175</v>
+        <v>0.5556173526140383</v>
       </c>
       <c r="G190" t="n">
-        <v>18.09882654643683</v>
+        <v>20.4601752851792</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I190" t="n">
-        <v>26.50817696786023</v>
+        <v>26.31116760003824</v>
       </c>
       <c r="J190" t="n">
-        <v>0.06678319220955201</v>
+        <v>0.04940215216676148</v>
       </c>
       <c r="K190" t="n">
-        <v>1.166204232228786</v>
+        <v>0.9932337999630733</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
@@ -7693,22 +7693,22 @@
         <v>294</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>0.03922644482804085</v>
       </c>
       <c r="G191" t="n">
-        <v>14.58684931710751</v>
+        <v>14.75850638909325</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I191" t="n">
-        <v>101.2808746114356</v>
+        <v>103.4217084312932</v>
       </c>
       <c r="J191" t="n">
-        <v>0.03529658570300893</v>
+        <v>0.03279136385233469</v>
       </c>
       <c r="K191" t="n">
-        <v>0.7725682678383314</v>
+        <v>0.7614028718038877</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
@@ -7737,16 +7737,16 @@
         <v>16.38096837796838</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I192" t="n">
-        <v>101.0895396964364</v>
+        <v>103.2319698316377</v>
       </c>
       <c r="J192" t="n">
-        <v>0.07859758702819657</v>
+        <v>0.05717329260355495</v>
       </c>
       <c r="K192" t="n">
-        <v>1.313904197836713</v>
+        <v>1.101692872838771</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -7769,22 +7769,22 @@
         <v>476</v>
       </c>
       <c r="F193" t="n">
-        <v>0.5556173526140394</v>
+        <v>0.833426028921044</v>
       </c>
       <c r="G193" t="n">
-        <v>15.835146673791</v>
+        <v>16.96633641925868</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I193" t="n">
-        <v>107.9458110979606</v>
+        <v>110.0783718206048</v>
       </c>
       <c r="J193" t="n">
-        <v>0.04311037605407018</v>
+        <v>0.03148080661805629</v>
       </c>
       <c r="K193" t="n">
-        <v>0.8702538948920331</v>
+        <v>0.7431118855919561</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         <v>495</v>
       </c>
       <c r="F194" t="n">
-        <v>0.004674704070363457</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>16.17558216422398</v>
+        <v>16.15292911517908</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I194" t="n">
-        <v>40.10738295183334</v>
+        <v>38.07103719493699</v>
       </c>
       <c r="J194" t="n">
-        <v>0.09661372465978796</v>
+        <v>0.1140500065249446</v>
       </c>
       <c r="K194" t="n">
-        <v>1.539136463172418</v>
+        <v>1.895501157517718</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -7851,16 +7851,16 @@
         <v>4.216584043986316</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I195" t="n">
-        <v>108.8995861352868</v>
+        <v>111.0378668078923</v>
       </c>
       <c r="J195" t="n">
-        <v>0.04564778838109967</v>
+        <v>0.0339390399010471</v>
       </c>
       <c r="K195" t="n">
-        <v>0.9019758509624315</v>
+        <v>0.7774205826170453</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -7883,22 +7883,22 @@
         <v>420</v>
       </c>
       <c r="F196" t="n">
-        <v>0.002628014982471252</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>6.864407666429431</v>
+        <v>6.859</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I196" t="n">
-        <v>40.91634157590745</v>
+        <v>38.92421756885921</v>
       </c>
       <c r="J196" t="n">
-        <v>0.1481125005856119</v>
+        <v>0.1993711390883394</v>
       </c>
       <c r="K196" t="n">
-        <v>2.182958474359208</v>
+        <v>3.086298185289444</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -7927,16 +7927,16 @@
         <v>9.010146336214524</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I197" t="n">
-        <v>23.90296308207655</v>
+        <v>23.66411155541576</v>
       </c>
       <c r="J197" t="n">
-        <v>0.06134627484870851</v>
+        <v>0.04472439015833629</v>
       </c>
       <c r="K197" t="n">
-        <v>1.098233547353549</v>
+        <v>0.9279479214368191</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -7965,16 +7965,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I198" t="n">
-        <v>70.05140507918989</v>
+        <v>67.95147626501125</v>
       </c>
       <c r="J198" t="n">
-        <v>0.02778771104480101</v>
+        <v>0.02566253616634559</v>
       </c>
       <c r="K198" t="n">
-        <v>0.6786946039058114</v>
+        <v>0.6619083319996351</v>
       </c>
       <c r="L198" t="b">
         <v>0</v>
@@ -7997,22 +7997,22 @@
         <v>509</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0003409093783001113</v>
+        <v>0.117131934373189</v>
       </c>
       <c r="G199" t="n">
-        <v>22.33336661742296</v>
+        <v>23.11578763067524</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I199" t="n">
-        <v>34.95206885205684</v>
+        <v>33.17756641045589</v>
       </c>
       <c r="J199" t="n">
-        <v>0.03393707542433442</v>
+        <v>0.03340200000519147</v>
       </c>
       <c r="K199" t="n">
-        <v>0.7555720844124175</v>
+        <v>0.7699253057428832</v>
       </c>
       <c r="L199" t="b">
         <v>0</v>
@@ -8035,22 +8035,22 @@
         <v>84</v>
       </c>
       <c r="F200" t="n">
-        <v>0.8334260289210199</v>
+        <v>0.4997219132369523</v>
       </c>
       <c r="G200" t="n">
-        <v>27.1785235982768</v>
+        <v>25.00187157821521</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I200" t="n">
-        <v>64.05928482531222</v>
+        <v>62.11474727984361</v>
       </c>
       <c r="J200" t="n">
-        <v>0.0605256260217527</v>
+        <v>0.02937089870696735</v>
       </c>
       <c r="K200" t="n">
-        <v>1.087974045671222</v>
+        <v>0.7136646432275868</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8073,22 +8073,22 @@
         <v>526</v>
       </c>
       <c r="F201" t="n">
-        <v>0.2778086763070693</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>13.18102944938843</v>
+        <v>12.167</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I201" t="n">
-        <v>28.6098713236826</v>
+        <v>26.93785812927021</v>
       </c>
       <c r="J201" t="n">
-        <v>0.01456180072013058</v>
+        <v>0.01784268746916433</v>
       </c>
       <c r="K201" t="n">
-        <v>0.5133483013593163</v>
+        <v>0.5527694550712352</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -8117,16 +8117,16 @@
         <v>5.379074548656115</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I202" t="n">
-        <v>71.63420816632923</v>
+        <v>69.61682426067625</v>
       </c>
       <c r="J202" t="n">
-        <v>0.03416695361118551</v>
+        <v>0.03740158147013197</v>
       </c>
       <c r="K202" t="n">
-        <v>0.7584459514883966</v>
+        <v>0.8257460570349888</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -8155,16 +8155,16 @@
         <v>8.546030189509043</v>
       </c>
       <c r="H203" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I203" t="n">
-        <v>109.1989371113102</v>
+        <v>111.3287131069042</v>
       </c>
       <c r="J203" t="n">
-        <v>0.0619805962262447</v>
+        <v>0.06231809127159339</v>
       </c>
       <c r="K203" t="n">
-        <v>1.106163640014632</v>
+        <v>1.173497017700914</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -8187,22 +8187,22 @@
         <v>632</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7221913236930246</v>
+        <v>0.7337446051167654</v>
       </c>
       <c r="G204" t="n">
-        <v>26.24948907738989</v>
+        <v>26.32426799261978</v>
       </c>
       <c r="H204" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I204" t="n">
-        <v>33.08221121093714</v>
+        <v>31.41716037663829</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1265524002015193</v>
+        <v>0.09868834219656038</v>
       </c>
       <c r="K204" t="n">
-        <v>1.913420666107826</v>
+        <v>1.681103813339531</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>475</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>0.2778086763070619</v>
       </c>
       <c r="G205" t="n">
-        <v>6.745316375085753</v>
+        <v>7.307488599116229</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I205" t="n">
-        <v>39.10480704337522</v>
+        <v>37.12971794680954</v>
       </c>
       <c r="J205" t="n">
-        <v>0.009119970527476116</v>
+        <v>0.01961906182709817</v>
       </c>
       <c r="K205" t="n">
-        <v>0.4453161977571229</v>
+        <v>0.5775616869847746</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -8263,22 +8263,22 @@
         <v>575</v>
       </c>
       <c r="F206" t="n">
-        <v>0.5556173526139999</v>
+        <v>0.5558928409344395</v>
       </c>
       <c r="G206" t="n">
-        <v>23.7717925710035</v>
+        <v>23.77347653455513</v>
       </c>
       <c r="H206" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I206" t="n">
-        <v>182.50476223137</v>
+        <v>181.2708030172869</v>
       </c>
       <c r="J206" t="n">
-        <v>0.03134763445185192</v>
+        <v>0.01559833642620549</v>
       </c>
       <c r="K206" t="n">
-        <v>0.7231996820633906</v>
+        <v>0.5214458372178739</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>75</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>5.405828698554315e-05</v>
       </c>
       <c r="G207" t="n">
-        <v>4.660218771688728</v>
+        <v>4.660294348721861</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I207" t="n">
-        <v>103.3643622278811</v>
+        <v>105.481210047155</v>
       </c>
       <c r="J207" t="n">
-        <v>0.2051823579456479</v>
+        <v>0.1971180848407858</v>
       </c>
       <c r="K207" t="n">
-        <v>2.89642844880295</v>
+        <v>3.054853099871691</v>
       </c>
       <c r="L207" t="b">
         <v>0</v>
@@ -8339,22 +8339,22 @@
         <v>655</v>
       </c>
       <c r="F208" t="n">
-        <v>0.5733821862839614</v>
+        <v>0.1996662958843493</v>
       </c>
       <c r="G208" t="n">
-        <v>18.09341634349597</v>
+        <v>16.36260252681886</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I208" t="n">
-        <v>87.96765201606391</v>
+        <v>86.0413416528815</v>
       </c>
       <c r="J208" t="n">
-        <v>0.04894711839076198</v>
+        <v>0.0463312109869226</v>
       </c>
       <c r="K208" t="n">
-        <v>0.9432230698370951</v>
+        <v>0.950373754397025</v>
       </c>
       <c r="L208" t="b">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>383</v>
       </c>
       <c r="F209" t="n">
-        <v>0.5651981879181953</v>
+        <v>0.6554505005562139</v>
       </c>
       <c r="G209" t="n">
-        <v>25.62506335626049</v>
+        <v>26.21829216992821</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I209" t="n">
-        <v>26.36338278260041</v>
+        <v>24.94383705155951</v>
       </c>
       <c r="J209" t="n">
-        <v>0.02196923524773254</v>
+        <v>0.01642914510546296</v>
       </c>
       <c r="K209" t="n">
-        <v>0.6059537916755187</v>
+        <v>0.5330411416422691</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -8415,22 +8415,22 @@
         <v>360</v>
       </c>
       <c r="F210" t="n">
-        <v>0.556515445460834</v>
+        <v>0.1665739710790193</v>
       </c>
       <c r="G210" t="n">
-        <v>20.64707970079444</v>
+        <v>18.57729417491535</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I210" t="n">
-        <v>91.94244867014864</v>
+        <v>90.01939748706958</v>
       </c>
       <c r="J210" t="n">
-        <v>0.03858242536234258</v>
+        <v>0.01674243744116495</v>
       </c>
       <c r="K210" t="n">
-        <v>0.8136468344620615</v>
+        <v>0.5374136525427826</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8453,22 +8453,22 @@
         <v>360</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>0.0002754883203560995</v>
       </c>
       <c r="G211" t="n">
-        <v>12.3745858516558</v>
+        <v>12.37560856781722</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I211" t="n">
-        <v>108.1616057213641</v>
+        <v>110.2868725384193</v>
       </c>
       <c r="J211" t="n">
-        <v>0.03584517619221695</v>
+        <v>0.02524913644138504</v>
       </c>
       <c r="K211" t="n">
-        <v>0.7794265790453506</v>
+        <v>0.656138657489057</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -8491,22 +8491,22 @@
         <v>268</v>
       </c>
       <c r="F212" t="n">
-        <v>0.3331479421579884</v>
+        <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>10.88734823617382</v>
+        <v>9.898089765202174</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I212" t="n">
-        <v>76.07795043483195</v>
+        <v>74.11080417368561</v>
       </c>
       <c r="J212" t="n">
-        <v>0.05599580694265725</v>
+        <v>0.06497036510656556</v>
       </c>
       <c r="K212" t="n">
-        <v>1.031343627231449</v>
+        <v>1.210513870438715</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -8529,22 +8529,22 @@
         <v>696</v>
       </c>
       <c r="F213" t="n">
-        <v>0.3331479421579872</v>
+        <v>0.3363296996663423</v>
       </c>
       <c r="G213" t="n">
-        <v>17.93441378054755</v>
+        <v>17.94997719173572</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I213" t="n">
-        <v>191.4732048531235</v>
+        <v>191.0055747854792</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1445411916154166</v>
+        <v>0.1139289351744599</v>
       </c>
       <c r="K213" t="n">
-        <v>2.138311057358999</v>
+        <v>1.893811407276787</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -8573,16 +8573,16 @@
         <v>8.792540929674423</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I214" t="n">
-        <v>98.8809059338564</v>
+        <v>101.0122326041219</v>
       </c>
       <c r="J214" t="n">
-        <v>0.6302716300256432</v>
+        <v>0.5397454582804133</v>
       </c>
       <c r="K214" t="n">
-        <v>8.210765055146132</v>
+        <v>7.836782800839874</v>
       </c>
       <c r="L214" t="b">
         <v>0</v>
@@ -8611,16 +8611,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I215" t="n">
-        <v>39.18225672355824</v>
+        <v>37.30536335882159</v>
       </c>
       <c r="J215" t="n">
-        <v>0.1851570101549704</v>
+        <v>0.1751753422787582</v>
       </c>
       <c r="K215" t="n">
-        <v>2.646077650021267</v>
+        <v>2.748605962275291</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -8649,16 +8649,16 @@
         <v>6.352448897866083</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I216" t="n">
-        <v>26.20795141312005</v>
+        <v>24.97203110583696</v>
       </c>
       <c r="J216" t="n">
-        <v>0.06505496521096026</v>
+        <v>0.04353619070234816</v>
       </c>
       <c r="K216" t="n">
-        <v>1.144598464673781</v>
+        <v>0.9113646396860835</v>
       </c>
       <c r="L216" t="b">
         <v>0</v>
@@ -8681,22 +8681,22 @@
         <v>6</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>0.5556173526140604</v>
       </c>
       <c r="G217" t="n">
-        <v>11.92630068378288</v>
+        <v>13.91423856750369</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I217" t="n">
-        <v>66.24799225946842</v>
+        <v>64.30385816459258</v>
       </c>
       <c r="J217" t="n">
-        <v>0.01346326693369838</v>
+        <v>0.0314030777375273</v>
       </c>
       <c r="K217" t="n">
-        <v>0.4996147665514964</v>
+        <v>0.7420270509545681</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -8719,22 +8719,22 @@
         <v>631</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>0.2778086763070781</v>
       </c>
       <c r="G218" t="n">
-        <v>3.375</v>
+        <v>3.656281284760917</v>
       </c>
       <c r="H218" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I218" t="n">
-        <v>25.6149464284499</v>
+        <v>24.42688634969953</v>
       </c>
       <c r="J218" t="n">
-        <v>0.126018587575894</v>
+        <v>0.1181835338352273</v>
       </c>
       <c r="K218" t="n">
-        <v>1.906747103250294</v>
+        <v>1.953191343845715</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -8763,16 +8763,16 @@
         <v>7.378342564560147</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I219" t="n">
-        <v>119.8175601427273</v>
+        <v>121.9593386067266</v>
       </c>
       <c r="J219" t="n">
-        <v>0.04894050120288345</v>
+        <v>0.03283624089504952</v>
       </c>
       <c r="K219" t="n">
-        <v>0.9431403437696931</v>
+        <v>0.762029204899505</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>9.32407137467319</v>
       </c>
       <c r="H220" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I220" t="n">
-        <v>30.55695503166791</v>
+        <v>29.43788003005546</v>
       </c>
       <c r="J220" t="n">
-        <v>0.155565122273273</v>
+        <v>0.08193670001507039</v>
       </c>
       <c r="K220" t="n">
-        <v>2.276128880787417</v>
+        <v>1.447307037315816</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -8833,22 +8833,22 @@
         <v>605</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>0.1999417842047052</v>
       </c>
       <c r="G221" t="n">
-        <v>21.65865722984691</v>
+        <v>22.95779840085103</v>
       </c>
       <c r="H221" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I221" t="n">
-        <v>13.92432455570455</v>
+        <v>11.9146007619889</v>
       </c>
       <c r="J221" t="n">
-        <v>0.06070552256524385</v>
+        <v>0.05441000425790059</v>
       </c>
       <c r="K221" t="n">
-        <v>1.090223057465266</v>
+        <v>1.063126629634761</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -8871,22 +8871,22 @@
         <v>486</v>
       </c>
       <c r="F222" t="n">
-        <v>0.2500674500404018</v>
+        <v>0.0001081165739711851</v>
       </c>
       <c r="G222" t="n">
-        <v>12.19982795512037</v>
+        <v>11.34883163949307</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I222" t="n">
-        <v>24.09433715930138</v>
+        <v>22.78802392263332</v>
       </c>
       <c r="J222" t="n">
-        <v>0.06683233786533503</v>
+        <v>0.09824454349200142</v>
       </c>
       <c r="K222" t="n">
-        <v>1.166818636248658</v>
+        <v>1.674909870966285</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -8915,16 +8915,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H223" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I223" t="n">
-        <v>68.04374792142461</v>
+        <v>66.00141395688607</v>
       </c>
       <c r="J223" t="n">
-        <v>0.03094833979284505</v>
+        <v>0.02798361671404329</v>
       </c>
       <c r="K223" t="n">
-        <v>0.718207821853194</v>
+        <v>0.6943028365541022</v>
       </c>
       <c r="L223" t="b">
         <v>0</v>
@@ -8947,22 +8947,22 @@
         <v>123</v>
       </c>
       <c r="F224" t="n">
-        <v>0.006952820321738752</v>
+        <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>7.511092129174989</v>
+        <v>7.495457757869096</v>
       </c>
       <c r="H224" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I224" t="n">
-        <v>62.32710773914507</v>
+        <v>60.33757171448367</v>
       </c>
       <c r="J224" t="n">
-        <v>0.03475662343345892</v>
+        <v>0.06073171382208507</v>
       </c>
       <c r="K224" t="n">
-        <v>0.7658178240055034</v>
+        <v>1.151356505789694</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -8985,22 +8985,22 @@
         <v>414</v>
       </c>
       <c r="F225" t="n">
-        <v>0.5556173526140041</v>
+        <v>0.3331479421580289</v>
       </c>
       <c r="G225" t="n">
-        <v>13.71480084269585</v>
+        <v>12.93023865500321</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I225" t="n">
-        <v>21.14351275356823</v>
+        <v>20.40406077565711</v>
       </c>
       <c r="J225" t="n">
-        <v>0.0413334186459632</v>
+        <v>0.04354172170674789</v>
       </c>
       <c r="K225" t="n">
-        <v>0.8480389145995204</v>
+        <v>0.9114418339684601</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -9029,16 +9029,16 @@
         <v>5.617338871743453</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I226" t="n">
-        <v>35.07309486971553</v>
+        <v>33.25141161443479</v>
       </c>
       <c r="J226" t="n">
-        <v>0.04783810385518444</v>
+        <v>0.06706632721919009</v>
       </c>
       <c r="K226" t="n">
-        <v>0.9293585078956748</v>
+        <v>1.239766476200611</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -9061,22 +9061,22 @@
         <v>258</v>
       </c>
       <c r="F227" t="n">
-        <v>0.4329810901001223</v>
+        <v>0.4997759715239306</v>
       </c>
       <c r="G227" t="n">
-        <v>20.79155614269814</v>
+        <v>21.16029049969373</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I227" t="n">
-        <v>200.4760800818992</v>
+        <v>198.8673960174862</v>
       </c>
       <c r="J227" t="n">
-        <v>0.06819201702487422</v>
+        <v>0.05307748311759283</v>
       </c>
       <c r="K227" t="n">
-        <v>1.183816930971705</v>
+        <v>1.044529100914166</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -9099,22 +9099,22 @@
         <v>590</v>
       </c>
       <c r="F228" t="n">
-        <v>0.3331479421580178</v>
+        <v>0.6662958843159219</v>
       </c>
       <c r="G228" t="n">
-        <v>24.19219148021484</v>
+        <v>26.39036957041754</v>
       </c>
       <c r="H228" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I228" t="n">
-        <v>37.15931644749521</v>
+        <v>36.51662592740215</v>
       </c>
       <c r="J228" t="n">
-        <v>0.2296463935758931</v>
+        <v>0.2632768631525626</v>
       </c>
       <c r="K228" t="n">
-        <v>3.202270371024478</v>
+        <v>3.978207891442658</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -9143,16 +9143,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H229" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I229" t="n">
-        <v>98.13513015941827</v>
+        <v>100.2741370005823</v>
       </c>
       <c r="J229" t="n">
-        <v>0.03689141470835521</v>
+        <v>0.04542630169175492</v>
       </c>
       <c r="K229" t="n">
-        <v>0.7925063343119889</v>
+        <v>0.9377442537479562</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -9175,22 +9175,22 @@
         <v>276</v>
       </c>
       <c r="F230" t="n">
-        <v>0.07755348772998523</v>
+        <v>0.5556173526140196</v>
       </c>
       <c r="G230" t="n">
-        <v>16.48995922770069</v>
+        <v>18.80116275151541</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I230" t="n">
-        <v>33.03460455971813</v>
+        <v>32.38602204619789</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1021157368422837</v>
+        <v>0.1188917968188966</v>
       </c>
       <c r="K230" t="n">
-        <v>1.607920943681445</v>
+        <v>1.963076321113304</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -9213,22 +9213,22 @@
         <v>583</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>0.003181757508343503</v>
       </c>
       <c r="G231" t="n">
-        <v>10.48342687292662</v>
+        <v>10.49343358957645</v>
       </c>
       <c r="H231" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I231" t="n">
-        <v>78.15185827168906</v>
+        <v>76.09623671352958</v>
       </c>
       <c r="J231" t="n">
-        <v>0.05739514321198606</v>
+        <v>0.05165975595384268</v>
       </c>
       <c r="K231" t="n">
-        <v>1.048837703062368</v>
+        <v>1.0247423817033</v>
       </c>
       <c r="L231" t="b">
         <v>0</v>
@@ -9251,22 +9251,22 @@
         <v>391</v>
       </c>
       <c r="F232" t="n">
-        <v>0.555617352614008</v>
+        <v>0.1195773081201534</v>
       </c>
       <c r="G232" t="n">
-        <v>16.59246241961035</v>
+        <v>14.73206905492897</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I232" t="n">
-        <v>126.096222243921</v>
+        <v>123.9541054365993</v>
       </c>
       <c r="J232" t="n">
-        <v>0.05000909057616259</v>
+        <v>0.04406096044784404</v>
       </c>
       <c r="K232" t="n">
-        <v>0.9564995226447083</v>
+        <v>0.9186886663888082</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -9295,16 +9295,16 @@
         <v>8.241196029703456</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I233" t="n">
-        <v>33.5557705982751</v>
+        <v>31.78090825247116</v>
       </c>
       <c r="J233" t="n">
-        <v>0.04725107956785</v>
+        <v>0.02853181478281312</v>
       </c>
       <c r="K233" t="n">
-        <v>0.922019709050601</v>
+        <v>0.7019538441217325</v>
       </c>
       <c r="L233" t="b">
         <v>0</v>
@@ -9327,22 +9327,22 @@
         <v>458</v>
       </c>
       <c r="F234" t="n">
-        <v>0.7221913236929889</v>
+        <v>0.1997203541713349</v>
       </c>
       <c r="G234" t="n">
-        <v>16.29622292139029</v>
+        <v>14.19678965212672</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I234" t="n">
-        <v>37.21228530732153</v>
+        <v>35.08080972635029</v>
       </c>
       <c r="J234" t="n">
-        <v>0.01162912805147225</v>
+        <v>0.02092950794196375</v>
       </c>
       <c r="K234" t="n">
-        <v>0.4766849208858137</v>
+        <v>0.5958511223421579</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -9365,22 +9365,22 @@
         <v>581</v>
       </c>
       <c r="F235" t="n">
-        <v>0.1996662958843479</v>
+        <v>0.5556173526140203</v>
       </c>
       <c r="G235" t="n">
-        <v>23.00033926306085</v>
+        <v>25.3176321940087</v>
       </c>
       <c r="H235" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I235" t="n">
-        <v>81.1363936139558</v>
+        <v>79.05578019046209</v>
       </c>
       <c r="J235" t="n">
-        <v>0.0887242641166287</v>
+        <v>0.05105181428686449</v>
       </c>
       <c r="K235" t="n">
-        <v>1.440504830424647</v>
+        <v>1.016257553755683</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -9403,22 +9403,22 @@
         <v>162</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
+        <v>0.5556173526140203</v>
       </c>
       <c r="G236" t="n">
-        <v>17.42023099732033</v>
+        <v>20.32392578591707</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I236" t="n">
-        <v>72.46156905997927</v>
+        <v>70.36177885759051</v>
       </c>
       <c r="J236" t="n">
-        <v>0.03074340114298877</v>
+        <v>0.06229244892446249</v>
       </c>
       <c r="K236" t="n">
-        <v>0.7156457412726688</v>
+        <v>1.17313913648402</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9441,22 +9441,22 @@
         <v>226</v>
       </c>
       <c r="F237" t="n">
-        <v>0.5556173526140197</v>
+        <v>0.006363515016686116</v>
       </c>
       <c r="G237" t="n">
-        <v>14.92569903986922</v>
+        <v>12.8176760438219</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I237" t="n">
-        <v>41.34567720191012</v>
+        <v>40.47910280004336</v>
       </c>
       <c r="J237" t="n">
-        <v>0.08831120478245146</v>
+        <v>0.06282481171655484</v>
       </c>
       <c r="K237" t="n">
-        <v>1.435340888437899</v>
+        <v>1.180569136666552</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -9485,16 +9485,16 @@
         <v>7.554245495084205</v>
       </c>
       <c r="H238" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I238" t="n">
-        <v>171.3082527510872</v>
+        <v>169.1737858527792</v>
       </c>
       <c r="J238" t="n">
-        <v>0.07891453944926152</v>
+        <v>0.039225805617476</v>
       </c>
       <c r="K238" t="n">
-        <v>1.317866640467864</v>
+        <v>0.8512061116238405</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -9523,16 +9523,16 @@
         <v>10.91308792230687</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I239" t="n">
-        <v>94.52750174977807</v>
+        <v>92.44367048249364</v>
       </c>
       <c r="J239" t="n">
-        <v>0.2138297834928408</v>
+        <v>0.1997645963243154</v>
       </c>
       <c r="K239" t="n">
-        <v>3.004535929171041</v>
+        <v>3.091789529497835</v>
       </c>
       <c r="L239" t="b">
         <v>0</v>
@@ -9561,16 +9561,16 @@
         <v>5.222154823442138</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I240" t="n">
-        <v>32.74731782277122</v>
+        <v>31.15143234031292</v>
       </c>
       <c r="J240" t="n">
-        <v>0.08237803380496812</v>
+        <v>0.06176188027743777</v>
       </c>
       <c r="K240" t="n">
-        <v>1.361166191995786</v>
+        <v>1.165734176552945</v>
       </c>
       <c r="L240" t="b">
         <v>0</v>
@@ -9593,22 +9593,22 @@
         <v>283</v>
       </c>
       <c r="F241" t="n">
-        <v>0.5556173526140011</v>
+        <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>12.11613545246576</v>
+        <v>10.3850939331332</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I241" t="n">
-        <v>30.44960189584885</v>
+        <v>30.05871263764906</v>
       </c>
       <c r="J241" t="n">
-        <v>0.07386017968986504</v>
+        <v>0.07008308875266525</v>
       </c>
       <c r="K241" t="n">
-        <v>1.254678574206963</v>
+        <v>1.281870355504945</v>
       </c>
       <c r="L241" t="b">
         <v>0</v>
@@ -9637,16 +9637,16 @@
         <v>7.203826552603831</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I242" t="n">
-        <v>30.9231496426303</v>
+        <v>30.5470585105876</v>
       </c>
       <c r="J242" t="n">
-        <v>0.04202061995051234</v>
+        <v>0.03999431688365183</v>
       </c>
       <c r="K242" t="n">
-        <v>0.8566300960020119</v>
+        <v>0.8619319529725977</v>
       </c>
       <c r="L242" t="b">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>384</v>
       </c>
       <c r="F243" t="n">
-        <v>0.5556173526140258</v>
+        <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>19.51283235407782</v>
+        <v>16.7250191031281</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I243" t="n">
-        <v>86.27187692756985</v>
+        <v>84.20265798860038</v>
       </c>
       <c r="J243" t="n">
-        <v>0.04559799561359341</v>
+        <v>0.04237529914940637</v>
       </c>
       <c r="K243" t="n">
-        <v>0.901353356948892</v>
+        <v>0.8951624847301438</v>
       </c>
       <c r="L243" t="b">
         <v>0</v>
@@ -9707,22 +9707,22 @@
         <v>10</v>
       </c>
       <c r="F244" t="n">
-        <v>0.8334260289210474</v>
+        <v>0.3331479421579999</v>
       </c>
       <c r="G244" t="n">
-        <v>21.5331926302267</v>
+        <v>18.94782988801123</v>
       </c>
       <c r="H244" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I244" t="n">
-        <v>106.3541107695691</v>
+        <v>108.4902520494882</v>
       </c>
       <c r="J244" t="n">
-        <v>0.09858293651398309</v>
+        <v>0.1328642536096019</v>
       </c>
       <c r="K244" t="n">
-        <v>1.563754949993287</v>
+        <v>2.158084984467346</v>
       </c>
       <c r="L244" t="b">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         <v>11.2138976720853</v>
       </c>
       <c r="H245" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I245" t="n">
-        <v>40.22115866055959</v>
+        <v>38.23513054360959</v>
       </c>
       <c r="J245" t="n">
-        <v>0.1353280621314404</v>
+        <v>0.1117368094352062</v>
       </c>
       <c r="K245" t="n">
-        <v>2.023131318674696</v>
+        <v>1.863216679612271</v>
       </c>
       <c r="L245" t="b">
         <v>0</v>
@@ -9783,22 +9783,22 @@
         <v>338</v>
       </c>
       <c r="F246" t="n">
-        <v>0.3359820811329404</v>
+        <v>0.3576756395996085</v>
       </c>
       <c r="G246" t="n">
-        <v>23.42869669546441</v>
+        <v>23.5672107625727</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I246" t="n">
-        <v>103.8078612772872</v>
+        <v>105.9322355649909</v>
       </c>
       <c r="J246" t="n">
-        <v>0.08765751110648941</v>
+        <v>0.06210529069666138</v>
       </c>
       <c r="K246" t="n">
-        <v>1.427168609202288</v>
+        <v>1.170527034948413</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -9827,16 +9827,16 @@
         <v>6.547900426854397</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I247" t="n">
-        <v>84.29148125998131</v>
+        <v>82.22762707931079</v>
       </c>
       <c r="J247" t="n">
-        <v>0.188567491017579</v>
+        <v>0.1610861695687091</v>
       </c>
       <c r="K247" t="n">
-        <v>2.688714443005266</v>
+        <v>2.551968335900335</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -9859,22 +9859,22 @@
         <v>94</v>
       </c>
       <c r="F248" t="n">
-        <v>0.1996662958843422</v>
+        <v>0.3331479421579999</v>
       </c>
       <c r="G248" t="n">
-        <v>16.20451043534328</v>
+        <v>16.81673940703079</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I248" t="n">
-        <v>105.3650851160922</v>
+        <v>107.5074990342365</v>
       </c>
       <c r="J248" t="n">
-        <v>0.08607880631254602</v>
+        <v>0.09272094480386031</v>
       </c>
       <c r="K248" t="n">
-        <v>1.407432122708496</v>
+        <v>1.597818947500694</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -9903,16 +9903,16 @@
         <v>9.609651814712121</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I249" t="n">
-        <v>21.58072909501447</v>
+        <v>20.82357404894231</v>
       </c>
       <c r="J249" t="n">
-        <v>0.2094944851869465</v>
+        <v>0.1844083422857973</v>
       </c>
       <c r="K249" t="n">
-        <v>2.950337350190916</v>
+        <v>2.877467694831751</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>387</v>
       </c>
       <c r="F250" t="n">
-        <v>0.9332591768631677</v>
+        <v>0.5556173526140304</v>
       </c>
       <c r="G250" t="n">
-        <v>28.421242376144</v>
+        <v>25.90564010273646</v>
       </c>
       <c r="H250" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I250" t="n">
-        <v>17.52106167692559</v>
+        <v>16.80713945072462</v>
       </c>
       <c r="J250" t="n">
-        <v>0.0319261855985612</v>
+        <v>0.03690416234061489</v>
       </c>
       <c r="K250" t="n">
-        <v>0.7304325522851081</v>
+        <v>0.8188037532564305</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -9979,16 +9979,16 @@
         <v>10.94637643240904</v>
       </c>
       <c r="H251" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I251" t="n">
-        <v>34.18829798263756</v>
+        <v>33.31144383240486</v>
       </c>
       <c r="J251" t="n">
-        <v>0.05357226890849554</v>
+        <v>0.05358998840531627</v>
       </c>
       <c r="K251" t="n">
-        <v>1.001045292886782</v>
+        <v>1.051681956894891</v>
       </c>
       <c r="L251" t="b">
         <v>0</v>
@@ -10011,22 +10011,22 @@
         <v>466</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>0.6313677623911828</v>
       </c>
       <c r="G252" t="n">
-        <v>13.93214050316749</v>
+        <v>16.57103181560881</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I252" t="n">
-        <v>27.41239004270028</v>
+        <v>26.9716095256939</v>
       </c>
       <c r="J252" t="n">
-        <v>0.02747346861899538</v>
+        <v>0.02398993308395259</v>
       </c>
       <c r="K252" t="n">
-        <v>0.6747660408099856</v>
+        <v>0.6385643992678991</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -10055,16 +10055,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I253" t="n">
-        <v>40.05220233968358</v>
+        <v>38.09961404994059</v>
       </c>
       <c r="J253" t="n">
-        <v>0.04288926350590279</v>
+        <v>0.03654313088095757</v>
       </c>
       <c r="K253" t="n">
-        <v>0.8674896131610496</v>
+        <v>0.8137649641994217</v>
       </c>
       <c r="L253" t="b">
         <v>0</v>
@@ -10093,16 +10093,16 @@
         <v>4.964088133786507</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I254" t="n">
-        <v>33.71195067210364</v>
+        <v>35.79819682585769</v>
       </c>
       <c r="J254" t="n">
-        <v>0.08133202035294579</v>
+        <v>0.05434313696925501</v>
       </c>
       <c r="K254" t="n">
-        <v>1.348089250412175</v>
+        <v>1.062193386413744</v>
       </c>
       <c r="L254" t="b">
         <v>0</v>
@@ -10125,22 +10125,22 @@
         <v>644</v>
       </c>
       <c r="F255" t="n">
-        <v>0.03552966733980809</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>6.086205267166696</v>
+        <v>6.022017186956544</v>
       </c>
       <c r="H255" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I255" t="n">
-        <v>100.3735586754845</v>
+        <v>102.5155448175118</v>
       </c>
       <c r="J255" t="n">
-        <v>0.0204574919182964</v>
+        <v>0.03242466014596826</v>
       </c>
       <c r="K255" t="n">
-        <v>0.5870544370159502</v>
+        <v>0.7562849171952851</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -10163,22 +10163,22 @@
         <v>98</v>
       </c>
       <c r="F256" t="n">
-        <v>0.3331479421579884</v>
+        <v>5.405828698564195e-05</v>
       </c>
       <c r="G256" t="n">
-        <v>4.879961238054292</v>
+        <v>4.436624665523826</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I256" t="n">
-        <v>110.0621373184234</v>
+        <v>112.2045652329671</v>
       </c>
       <c r="J256" t="n">
-        <v>0.1308570902805621</v>
+        <v>0.02761423610322786</v>
       </c>
       <c r="K256" t="n">
-        <v>1.967236590358473</v>
+        <v>0.6891475213319478</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -10207,16 +10207,16 @@
         <v>7.970018757819834</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I257" t="n">
-        <v>56.89336281267433</v>
+        <v>54.78824416133097</v>
       </c>
       <c r="J257" t="n">
-        <v>0.03469045128241876</v>
+        <v>0.04423962379605557</v>
       </c>
       <c r="K257" t="n">
-        <v>0.7649905599278368</v>
+        <v>0.9211822078788248</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -10239,22 +10239,22 @@
         <v>609</v>
       </c>
       <c r="F258" t="n">
-        <v>0.2830647062719636</v>
+        <v>0.1195773081201428</v>
       </c>
       <c r="G258" t="n">
-        <v>22.23925355765605</v>
+        <v>21.23387813681973</v>
       </c>
       <c r="H258" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I258" t="n">
-        <v>114.4543026119931</v>
+        <v>116.5817879328188</v>
       </c>
       <c r="J258" t="n">
-        <v>0.06522235270846093</v>
+        <v>0.0556811506474347</v>
       </c>
       <c r="K258" t="n">
-        <v>1.146691092184843</v>
+        <v>1.080867572552922</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>8.150467777986734</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I259" t="n">
-        <v>40.32582622681115</v>
+        <v>38.60471781849141</v>
       </c>
       <c r="J259" t="n">
-        <v>0.04621114341769975</v>
+        <v>0.0522282480638955</v>
       </c>
       <c r="K259" t="n">
-        <v>0.9090187440439774</v>
+        <v>1.032676626064855</v>
       </c>
       <c r="L259" t="b">
         <v>0</v>
@@ -10315,22 +10315,22 @@
         <v>248</v>
       </c>
       <c r="F260" t="n">
-        <v>0.05978865406007999</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>5.262928993280028</v>
+        <v>5.170193323271385</v>
       </c>
       <c r="H260" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I260" t="n">
-        <v>101.0541150507818</v>
+        <v>103.1771614049493</v>
       </c>
       <c r="J260" t="n">
-        <v>0.0249950400007575</v>
+        <v>0.05279967514141497</v>
       </c>
       <c r="K260" t="n">
-        <v>0.6437814811017097</v>
+        <v>1.040651832734702</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -10353,22 +10353,22 @@
         <v>456</v>
       </c>
       <c r="F261" t="n">
-        <v>0.5582453675964744</v>
+        <v>0.3331479421579997</v>
       </c>
       <c r="G261" t="n">
-        <v>24.26776416222462</v>
+        <v>22.86406359392835</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I261" t="n">
-        <v>23.71882442415492</v>
+        <v>23.11424207709796</v>
       </c>
       <c r="J261" t="n">
-        <v>0.05838163314867257</v>
+        <v>0.03461128783181579</v>
       </c>
       <c r="K261" t="n">
-        <v>1.061170499786854</v>
+        <v>0.786802910462849</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -10391,22 +10391,22 @@
         <v>550</v>
       </c>
       <c r="F262" t="n">
-        <v>0.6827961695302749</v>
+        <v>0.9321583982202715</v>
       </c>
       <c r="G262" t="n">
-        <v>24.05723356791836</v>
+        <v>25.55095167993007</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I262" t="n">
-        <v>159.5753620473509</v>
+        <v>157.7801760952995</v>
       </c>
       <c r="J262" t="n">
-        <v>0.02632104454061322</v>
+        <v>0.02269875084260835</v>
       </c>
       <c r="K262" t="n">
-        <v>0.6603587859860504</v>
+        <v>0.6205438230154456</v>
       </c>
       <c r="L262" t="b">
         <v>0</v>
@@ -10435,16 +10435,16 @@
         <v>3.976587858956469</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I263" t="n">
-        <v>37.83155636242855</v>
+        <v>37.04723495833959</v>
       </c>
       <c r="J263" t="n">
-        <v>0.08165346597045257</v>
+        <v>0.09444996630805436</v>
       </c>
       <c r="K263" t="n">
-        <v>1.352107865616709</v>
+        <v>1.621950292295231</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -10473,16 +10473,16 @@
         <v>20.49853041073921</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I264" t="n">
-        <v>118.5903549101081</v>
+        <v>120.7318778476136</v>
       </c>
       <c r="J264" t="n">
-        <v>0.01310269624241378</v>
+        <v>0.01576192081073753</v>
       </c>
       <c r="K264" t="n">
-        <v>0.4951070215912622</v>
+        <v>0.5237289269172035</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -10505,22 +10505,22 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>0.1197834321126421</v>
+        <v>0.06816017797554594</v>
       </c>
       <c r="G265" t="n">
-        <v>13.83869414965683</v>
+        <v>13.63180904453615</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I265" t="n">
-        <v>21.89699910204037</v>
+        <v>20.62265042769602</v>
       </c>
       <c r="J265" t="n">
-        <v>0.06700945858917927</v>
+        <v>0.02919174144891755</v>
       </c>
       <c r="K265" t="n">
-        <v>1.169032945590933</v>
+        <v>0.7111642084117349</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -10543,22 +10543,22 @@
         <v>177</v>
       </c>
       <c r="F266" t="n">
-        <v>0.5556173526140102</v>
+        <v>0.1749454949944831</v>
       </c>
       <c r="G266" t="n">
-        <v>16.50773505447901</v>
+        <v>14.8918672598611</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I266" t="n">
-        <v>79.92107330297716</v>
+        <v>77.86242225726782</v>
       </c>
       <c r="J266" t="n">
-        <v>0.01758036591234482</v>
+        <v>0.0422520341401565</v>
       </c>
       <c r="K266" t="n">
-        <v>0.5510854840012689</v>
+        <v>0.8934421183656451</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -10581,22 +10581,22 @@
         <v>193</v>
       </c>
       <c r="F267" t="n">
-        <v>0.5582453675964771</v>
+        <v>0.01674304783092765</v>
       </c>
       <c r="G267" t="n">
-        <v>10.04895746827176</v>
+        <v>8.650673070478561</v>
       </c>
       <c r="H267" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I267" t="n">
-        <v>70.35052963970764</v>
+        <v>68.2219232953185</v>
       </c>
       <c r="J267" t="n">
-        <v>0.0856803158516076</v>
+        <v>0.08248658929818464</v>
       </c>
       <c r="K267" t="n">
-        <v>1.40245031633761</v>
+        <v>1.454981648567014</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>139</v>
       </c>
       <c r="F268" t="n">
-        <v>0.8027724650845722</v>
+        <v>0.2210122358176252</v>
       </c>
       <c r="G268" t="n">
-        <v>26.35760466692326</v>
+        <v>22.65029956369739</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I268" t="n">
-        <v>105.5851971521514</v>
+        <v>107.7274527798204</v>
       </c>
       <c r="J268" t="n">
-        <v>0.0511457739843527</v>
+        <v>0.03381294725939832</v>
       </c>
       <c r="K268" t="n">
-        <v>0.9707099924041777</v>
+        <v>0.77566075198203</v>
       </c>
       <c r="L268" t="b">
         <v>0</v>
@@ -10657,22 +10657,22 @@
         <v>99</v>
       </c>
       <c r="F269" t="n">
-        <v>0.6751946607341283</v>
+        <v>0.1195773081201632</v>
       </c>
       <c r="G269" t="n">
-        <v>18.52004975689566</v>
+        <v>15.95300743327104</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I269" t="n">
-        <v>35.42799325117263</v>
+        <v>33.2861146432659</v>
       </c>
       <c r="J269" t="n">
-        <v>0.04964627632092319</v>
+        <v>0.05647058612925773</v>
       </c>
       <c r="K269" t="n">
-        <v>0.9519637293312535</v>
+        <v>1.091885445817484</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -10695,22 +10695,22 @@
         <v>8</v>
       </c>
       <c r="F270" t="n">
-        <v>0.01776483366990573</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>4.460197102110989</v>
+        <v>4.436552715791846</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I270" t="n">
-        <v>68.14384892589926</v>
+        <v>66.01924251943154</v>
       </c>
       <c r="J270" t="n">
-        <v>0.03412489507703795</v>
+        <v>0.01745729634351389</v>
       </c>
       <c r="K270" t="n">
-        <v>0.7579201485046235</v>
+        <v>0.5473906867266735</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -10733,22 +10733,22 @@
         <v>591</v>
       </c>
       <c r="F271" t="n">
-        <v>0.7291441440146861</v>
+        <v>0.5556173526140203</v>
       </c>
       <c r="G271" t="n">
-        <v>20.75865471053332</v>
+        <v>19.87195865725091</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I271" t="n">
-        <v>91.14896700561192</v>
+        <v>89.09665919465984</v>
       </c>
       <c r="J271" t="n">
-        <v>0.04534280650882443</v>
+        <v>0.01448917273645538</v>
       </c>
       <c r="K271" t="n">
-        <v>0.8981630604862738</v>
+        <v>0.505965629848552</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -10771,22 +10771,22 @@
         <v>31</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>0.5913793103448362</v>
       </c>
       <c r="G272" t="n">
-        <v>5.940332650618145</v>
+        <v>6.994229598460587</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I272" t="n">
-        <v>38.90776665945441</v>
+        <v>37.02088600893605</v>
       </c>
       <c r="J272" t="n">
-        <v>0.009832485252923731</v>
+        <v>0.05618190385838794</v>
       </c>
       <c r="K272" t="n">
-        <v>0.4542238398377546</v>
+        <v>1.08785640893302</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -10809,22 +10809,22 @@
         <v>39</v>
       </c>
       <c r="F273" t="n">
-        <v>0.8403788492427867</v>
+        <v>0.7819799777530936</v>
       </c>
       <c r="G273" t="n">
-        <v>25.51243979868082</v>
+        <v>25.1554679644917</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I273" t="n">
-        <v>167.9917233903205</v>
+        <v>165.9522544383636</v>
       </c>
       <c r="J273" t="n">
-        <v>0.06861654771614736</v>
+        <v>0.05566831874851079</v>
       </c>
       <c r="K273" t="n">
-        <v>1.189124284370932</v>
+        <v>1.08068848225442</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -10847,22 +10847,22 @@
         <v>330</v>
       </c>
       <c r="F274" t="n">
-        <v>0.05978865406006932</v>
+        <v>0.1996662958843523</v>
       </c>
       <c r="G274" t="n">
-        <v>18.49003780775315</v>
+        <v>19.2522688431829</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I274" t="n">
-        <v>70.75463697875767</v>
+        <v>68.62512976240302</v>
       </c>
       <c r="J274" t="n">
-        <v>0.3411660619227315</v>
+        <v>0.2693335379228121</v>
       </c>
       <c r="K274" t="n">
-        <v>4.596455298164502</v>
+        <v>4.06273877022857</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
@@ -10885,22 +10885,22 @@
         <v>465</v>
       </c>
       <c r="F275" t="n">
-        <v>0.002628014982471252</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>20.84424091622422</v>
+        <v>20.82782016918717</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I275" t="n">
-        <v>102.3064822147385</v>
+        <v>104.4481570566942</v>
       </c>
       <c r="J275" t="n">
-        <v>0.03562913651730623</v>
+        <v>0.06939948267414323</v>
       </c>
       <c r="K275" t="n">
-        <v>0.7767257168307322</v>
+        <v>1.272329505987203</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -10923,22 +10923,22 @@
         <v>170</v>
       </c>
       <c r="F276" t="n">
-        <v>0.01776483366990563</v>
+        <v>0.2778086763070696</v>
       </c>
       <c r="G276" t="n">
-        <v>8.072814326391208</v>
+        <v>8.699261405441845</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I276" t="n">
-        <v>106.6178934222169</v>
+        <v>108.7582449790528</v>
       </c>
       <c r="J276" t="n">
-        <v>0.04777027604434981</v>
+        <v>0.06899653599147518</v>
       </c>
       <c r="K276" t="n">
-        <v>0.9285105452635367</v>
+        <v>1.266705720910099</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>352</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>0.2778086763070297</v>
       </c>
       <c r="G277" t="n">
-        <v>3.043189116699782</v>
+        <v>3.29681641877848</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I277" t="n">
-        <v>20.16921154335633</v>
+        <v>18.20512821720761</v>
       </c>
       <c r="J277" t="n">
-        <v>0.1338336122426783</v>
+        <v>0.09417382793120579</v>
       </c>
       <c r="K277" t="n">
-        <v>2.004448161343218</v>
+        <v>1.618096326126174</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -11005,16 +11005,16 @@
         <v>10.648</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I278" t="n">
-        <v>25.43494888243173</v>
+        <v>24.63265777721897</v>
       </c>
       <c r="J278" t="n">
-        <v>0.05513272886032063</v>
+        <v>0.06334223376003263</v>
       </c>
       <c r="K278" t="n">
-        <v>1.020553687921405</v>
+        <v>1.187790614077428</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11037,22 +11037,22 @@
         <v>537</v>
       </c>
       <c r="F279" t="n">
-        <v>0.001796185693530261</v>
+        <v>0.02134593993326465</v>
       </c>
       <c r="G279" t="n">
-        <v>15.37151494541131</v>
+        <v>15.46161919406517</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I279" t="n">
-        <v>30.56718790259223</v>
+        <v>28.97162108990738</v>
       </c>
       <c r="J279" t="n">
-        <v>0.02048299915712372</v>
+        <v>0.04394345409035558</v>
       </c>
       <c r="K279" t="n">
-        <v>0.5873733207468039</v>
+        <v>0.9170486715008175</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -11081,16 +11081,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I280" t="n">
-        <v>68.02798022607185</v>
+        <v>65.92689209476436</v>
       </c>
       <c r="J280" t="n">
-        <v>0.03221007521148746</v>
+        <v>0.01457306970744695</v>
       </c>
       <c r="K280" t="n">
-        <v>0.7339816537591407</v>
+        <v>0.5071365503543432</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -11113,22 +11113,22 @@
         <v>544</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>0.1195773081201527</v>
       </c>
       <c r="G281" t="n">
-        <v>13.71614074730936</v>
+        <v>14.20818250381747</v>
       </c>
       <c r="H281" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I281" t="n">
-        <v>101.2589557684979</v>
+        <v>103.3958056976741</v>
       </c>
       <c r="J281" t="n">
-        <v>0.0978711905793959</v>
+        <v>0.05973285605745286</v>
       </c>
       <c r="K281" t="n">
-        <v>1.554856919101835</v>
+        <v>1.13741579940717</v>
       </c>
       <c r="L281" t="b">
         <v>0</v>
@@ -11151,22 +11151,22 @@
         <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>0.4445887713784532</v>
+        <v>0.61540600667409</v>
       </c>
       <c r="G282" t="n">
-        <v>14.81882360815336</v>
+        <v>15.4888507841826</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I282" t="n">
-        <v>38.42580969623944</v>
+        <v>36.48673825964631</v>
       </c>
       <c r="J282" t="n">
-        <v>0.1267234318884515</v>
+        <v>0.08570037484337578</v>
       </c>
       <c r="K282" t="n">
-        <v>1.915558852165219</v>
+        <v>1.499835322681875</v>
       </c>
       <c r="L282" t="b">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I283" t="n">
-        <v>116.5987576789788</v>
+        <v>118.739230221862</v>
       </c>
       <c r="J283" t="n">
-        <v>0.02190174823713601</v>
+        <v>0.02865264140678266</v>
       </c>
       <c r="K283" t="n">
-        <v>0.6051100896241568</v>
+        <v>0.7036401788007958</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11227,22 +11227,22 @@
         <v>377</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>0.1665739710790001</v>
       </c>
       <c r="G284" t="n">
-        <v>4.710418346601499</v>
+        <v>4.945808273432537</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I284" t="n">
-        <v>31.14170672177483</v>
+        <v>29.58078561450717</v>
       </c>
       <c r="J284" t="n">
-        <v>0.07315034314068763</v>
+        <v>0.07676608359873818</v>
       </c>
       <c r="K284" t="n">
-        <v>1.245804413870346</v>
+        <v>1.375142563224462</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -11271,16 +11271,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H285" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I285" t="n">
-        <v>23.6084077727554</v>
+        <v>21.53753539877835</v>
       </c>
       <c r="J285" t="n">
-        <v>0.03753965437363211</v>
+        <v>0.04658218937716482</v>
       </c>
       <c r="K285" t="n">
-        <v>0.8006104291671899</v>
+        <v>0.9538765714853157</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -11309,16 +11309,16 @@
         <v>6.380249524901044</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I286" t="n">
-        <v>106.0651174210617</v>
+        <v>108.2058629750189</v>
       </c>
       <c r="J286" t="n">
-        <v>0.04310702129253904</v>
+        <v>0.04841271971121205</v>
       </c>
       <c r="K286" t="n">
-        <v>0.8702119546851601</v>
+        <v>0.9794246393032131</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -11341,22 +11341,22 @@
         <v>191</v>
       </c>
       <c r="F287" t="n">
-        <v>0.1996662958843595</v>
+        <v>0.9699447845990904</v>
       </c>
       <c r="G287" t="n">
-        <v>16.28349252789993</v>
+        <v>19.83368367755643</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I287" t="n">
-        <v>115.2757891945446</v>
+        <v>117.3927459123834</v>
       </c>
       <c r="J287" t="n">
-        <v>0.1476875645120974</v>
+        <v>0.07098158781680787</v>
       </c>
       <c r="K287" t="n">
-        <v>2.177646052994669</v>
+        <v>1.294410390814975</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -11385,16 +11385,16 @@
         <v>4.313887457966422</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I288" t="n">
-        <v>19.340002836549</v>
+        <v>17.36842068262242</v>
       </c>
       <c r="J288" t="n">
-        <v>0.03959371982415701</v>
+        <v>0.06955935538337776</v>
       </c>
       <c r="K288" t="n">
-        <v>0.826289729804763</v>
+        <v>1.274560793140322</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -11417,22 +11417,22 @@
         <v>372</v>
       </c>
       <c r="F289" t="n">
-        <v>0.3331479421579874</v>
+        <v>0.5556173526140629</v>
       </c>
       <c r="G289" t="n">
-        <v>20.67758652673517</v>
+        <v>21.93223100426378</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I289" t="n">
-        <v>28.59954508285776</v>
+        <v>27.11196571164846</v>
       </c>
       <c r="J289" t="n">
-        <v>0.05308946218654047</v>
+        <v>0.06064310297829288</v>
       </c>
       <c r="K289" t="n">
-        <v>0.9950093903016153</v>
+        <v>1.150119795419756</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -11461,16 +11461,16 @@
         <v>5.832000000000001</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I290" t="n">
-        <v>88.24113551835484</v>
+        <v>86.17362526342446</v>
       </c>
       <c r="J290" t="n">
-        <v>0.03143113759210182</v>
+        <v>0.04909855992432709</v>
       </c>
       <c r="K290" t="n">
-        <v>0.7242436128895045</v>
+        <v>0.9889966698514117</v>
       </c>
       <c r="L290" t="b">
         <v>0</v>
@@ -11493,22 +11493,22 @@
         <v>21</v>
       </c>
       <c r="F291" t="n">
-        <v>0.8913933097544339</v>
+        <v>0.9060557953281976</v>
       </c>
       <c r="G291" t="n">
-        <v>28.51723079072255</v>
+        <v>28.61620369959863</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I291" t="n">
-        <v>81.31966425060826</v>
+        <v>79.25906230131363</v>
       </c>
       <c r="J291" t="n">
-        <v>0.196722942651995</v>
+        <v>0.1974711163201805</v>
       </c>
       <c r="K291" t="n">
-        <v>2.790671415360668</v>
+        <v>3.05978023601889</v>
       </c>
       <c r="L291" t="b">
         <v>0</v>
@@ -11531,22 +11531,22 @@
         <v>556</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>0.5567232035595515</v>
       </c>
       <c r="G292" t="n">
-        <v>7.203826552603831</v>
+        <v>8.406987771479722</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I292" t="n">
-        <v>33.95324573875139</v>
+        <v>31.89400325340628</v>
       </c>
       <c r="J292" t="n">
-        <v>0.1380534513865206</v>
+        <v>0.1784430956619517</v>
       </c>
       <c r="K292" t="n">
-        <v>2.057203305045789</v>
+        <v>2.794212846517089</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -11569,22 +11569,22 @@
         <v>240</v>
       </c>
       <c r="F293" t="n">
-        <v>0.000363050977685269</v>
+        <v>0.5556173526140067</v>
       </c>
       <c r="G293" t="n">
-        <v>19.04064226123026</v>
+        <v>22.21201640652497</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I293" t="n">
-        <v>101.960402397553</v>
+        <v>104.094202676142</v>
       </c>
       <c r="J293" t="n">
-        <v>0.03891152176431463</v>
+        <v>0.03230029283384397</v>
       </c>
       <c r="K293" t="n">
-        <v>0.8177610974437129</v>
+        <v>0.7545491663774027</v>
       </c>
       <c r="L293" t="b">
         <v>0</v>
@@ -11607,22 +11607,22 @@
         <v>466</v>
       </c>
       <c r="F294" t="n">
-        <v>0.1674720639257762</v>
+        <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>8.465026153176632</v>
+        <v>8.060074937616895</v>
       </c>
       <c r="H294" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I294" t="n">
-        <v>81.56254860458294</v>
+        <v>79.54639661569981</v>
       </c>
       <c r="J294" t="n">
-        <v>0.07832970575399024</v>
+        <v>0.07632869756914108</v>
       </c>
       <c r="K294" t="n">
-        <v>1.310555227737555</v>
+        <v>1.369038120299421</v>
       </c>
       <c r="L294" t="b">
         <v>0</v>
@@ -11645,22 +11645,22 @@
         <v>572</v>
       </c>
       <c r="F295" t="n">
-        <v>0.1665739710790042</v>
+        <v>0.03576195773082118</v>
       </c>
       <c r="G295" t="n">
-        <v>17.19956126381971</v>
+        <v>16.55671302758523</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I295" t="n">
-        <v>66.85197166492671</v>
+        <v>64.73857825121728</v>
       </c>
       <c r="J295" t="n">
-        <v>0.1451849979148336</v>
+        <v>0.2035617852283293</v>
       </c>
       <c r="K295" t="n">
-        <v>2.146359727624529</v>
+        <v>3.144785559026954</v>
       </c>
       <c r="L295" t="b">
         <v>0</v>
@@ -11689,16 +11689,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I296" t="n">
-        <v>228.7415697407231</v>
+        <v>226.7840880584426</v>
       </c>
       <c r="J296" t="n">
-        <v>0.1243878720911449</v>
+        <v>0.1096360062773973</v>
       </c>
       <c r="K296" t="n">
-        <v>1.886360394941405</v>
+        <v>1.833896509086011</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -11727,16 +11727,16 @@
         <v>20.58068878827917</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I297" t="n">
-        <v>225.3153145859112</v>
+        <v>223.4261821509419</v>
       </c>
       <c r="J297" t="n">
-        <v>0.3675620567289688</v>
+        <v>0.3043440947988226</v>
       </c>
       <c r="K297" t="n">
-        <v>4.926449985570382</v>
+        <v>4.551368794421108</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -11759,22 +11759,22 @@
         <v>260</v>
       </c>
       <c r="F298" t="n">
-        <v>0.003948001763547289</v>
+        <v>0.1195773081201609</v>
       </c>
       <c r="G298" t="n">
-        <v>18.90094102476329</v>
+        <v>19.55581620031309</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I298" t="n">
-        <v>79.26318029714363</v>
+        <v>77.17677365952497</v>
       </c>
       <c r="J298" t="n">
-        <v>0.5658749775041378</v>
+        <v>0.4678445721951654</v>
       </c>
       <c r="K298" t="n">
-        <v>7.405697719180531</v>
+        <v>6.833287431379674</v>
       </c>
       <c r="L298" t="b">
         <v>0</v>
@@ -11797,22 +11797,22 @@
         <v>195</v>
       </c>
       <c r="F299" t="n">
-        <v>0.3333540661504539</v>
+        <v>0.5556173526140231</v>
       </c>
       <c r="G299" t="n">
-        <v>9.132105622152476</v>
+        <v>9.685665712439366</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I299" t="n">
-        <v>24.91640253283065</v>
+        <v>23.26106200707272</v>
       </c>
       <c r="J299" t="n">
-        <v>0.05693354685610527</v>
+        <v>0.06650324737539487</v>
       </c>
       <c r="K299" t="n">
-        <v>1.043066966013633</v>
+        <v>1.23190776893496</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -11841,16 +11841,16 @@
         <v>5.352813839467986</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I300" t="n">
-        <v>27.61552902382556</v>
+        <v>26.50363905425595</v>
       </c>
       <c r="J300" t="n">
-        <v>0.03746253403928872</v>
+        <v>0.04198978613492613</v>
       </c>
       <c r="K300" t="n">
-        <v>0.7996462942364515</v>
+        <v>0.88978201522607</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -11879,16 +11879,16 @@
         <v>11.82363560839051</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I301" t="n">
-        <v>108.5368410139867</v>
+        <v>107.8917655498726</v>
       </c>
       <c r="J301" t="n">
-        <v>0.04880620552443361</v>
+        <v>0.05786758486959177</v>
       </c>
       <c r="K301" t="n">
-        <v>0.9414614201013364</v>
+        <v>1.111382865715826</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -11911,22 +11911,22 @@
         <v>189</v>
       </c>
       <c r="F302" t="n">
-        <v>0.3331479421579872</v>
+        <v>0.266407119021184</v>
       </c>
       <c r="G302" t="n">
-        <v>23.73139564734706</v>
+        <v>23.29941392954138</v>
       </c>
       <c r="H302" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I302" t="n">
-        <v>35.10543060354426</v>
+        <v>33.74379076914816</v>
       </c>
       <c r="J302" t="n">
-        <v>0.1704297810498447</v>
+        <v>0.1086007616252831</v>
       </c>
       <c r="K302" t="n">
-        <v>2.461962317351465</v>
+        <v>1.819447963717275</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -11955,16 +11955,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I303" t="n">
-        <v>91.03962855834533</v>
+        <v>89.06559099605887</v>
       </c>
       <c r="J303" t="n">
-        <v>0.07557002603272685</v>
+        <v>0.06788778203777744</v>
       </c>
       <c r="K303" t="n">
-        <v>1.276054552402392</v>
+        <v>1.251231232082699</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -11993,16 +11993,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I304" t="n">
-        <v>104.7624480071567</v>
+        <v>106.8816418544399</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1623202273875508</v>
+        <v>0.1047433876805372</v>
       </c>
       <c r="K304" t="n">
-        <v>2.360579147463981</v>
+        <v>1.765611952750185</v>
       </c>
       <c r="L304" t="b">
         <v>0</v>
@@ -12025,22 +12025,22 @@
         <v>181</v>
       </c>
       <c r="F305" t="n">
-        <v>0.005256029964943689</v>
+        <v>0.3415194660734606</v>
       </c>
       <c r="G305" t="n">
-        <v>17.60371399479916</v>
+        <v>19.37676384071214</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I305" t="n">
-        <v>114.1121733565839</v>
+        <v>116.2524532691994</v>
       </c>
       <c r="J305" t="n">
-        <v>0.1962980739002321</v>
+        <v>0.09572034130520173</v>
       </c>
       <c r="K305" t="n">
-        <v>2.785359835632164</v>
+        <v>1.639680469161257</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -12063,22 +12063,22 @@
         <v>418</v>
       </c>
       <c r="F306" t="n">
-        <v>0.6554505005561503</v>
+        <v>0.5080934371523994</v>
       </c>
       <c r="G306" t="n">
-        <v>26.06775675151646</v>
+        <v>25.1047393897355</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I306" t="n">
-        <v>25.77571620709468</v>
+        <v>24.00534701675128</v>
       </c>
       <c r="J306" t="n">
-        <v>0.1687288360176647</v>
+        <v>0.1686192273975706</v>
       </c>
       <c r="K306" t="n">
-        <v>2.44069762063103</v>
+        <v>2.65710457358419</v>
       </c>
       <c r="L306" t="b">
         <v>0</v>
@@ -12101,22 +12101,22 @@
         <v>249</v>
       </c>
       <c r="F307" t="n">
-        <v>0.0008980928467648835</v>
+        <v>0.09261232147713751</v>
       </c>
       <c r="G307" t="n">
-        <v>8.887977234638567</v>
+        <v>9.132457557677537</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I307" t="n">
-        <v>103.38017828642</v>
+        <v>105.5219661395455</v>
       </c>
       <c r="J307" t="n">
-        <v>0.04078069703294767</v>
+        <v>0.03888028477763512</v>
       </c>
       <c r="K307" t="n">
-        <v>0.8411289573409126</v>
+        <v>0.8463837988303482</v>
       </c>
       <c r="L307" t="b">
         <v>0</v>
@@ -12145,16 +12145,16 @@
         <v>3.0214779496134</v>
       </c>
       <c r="H308" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I308" t="n">
-        <v>72.71805437171375</v>
+        <v>70.70378139597372</v>
       </c>
       <c r="J308" t="n">
-        <v>0.2196353084150134</v>
+        <v>0.1453441829477243</v>
       </c>
       <c r="K308" t="n">
-        <v>3.077114833507948</v>
+        <v>2.332262967297043</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -12177,22 +12177,22 @@
         <v>361</v>
       </c>
       <c r="F309" t="n">
-        <v>0.2603530427911768</v>
+        <v>0.5558928409343594</v>
       </c>
       <c r="G309" t="n">
-        <v>21.26403694211919</v>
+        <v>23.01276193585674</v>
       </c>
       <c r="H309" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I309" t="n">
-        <v>147.6208016007466</v>
+        <v>145.4806316844993</v>
       </c>
       <c r="J309" t="n">
-        <v>0.252390489117113</v>
+        <v>0.1933138493140569</v>
       </c>
       <c r="K309" t="n">
-        <v>3.486610126110383</v>
+        <v>3.001758723108625</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -12215,22 +12215,22 @@
         <v>503</v>
       </c>
       <c r="F310" t="n">
-        <v>0.3331479421579884</v>
+        <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>9.299141821658049</v>
+        <v>8.454192746797297</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I310" t="n">
-        <v>36.42502270322404</v>
+        <v>34.94838318845575</v>
       </c>
       <c r="J310" t="n">
-        <v>0.3813834155885668</v>
+        <v>0.3394657064714744</v>
       </c>
       <c r="K310" t="n">
-        <v>5.099240404339514</v>
+        <v>5.041548771336809</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>519</v>
       </c>
       <c r="F311" t="n">
-        <v>0.002628014982471844</v>
+        <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>9.809355675630062</v>
+        <v>9.801628028036975</v>
       </c>
       <c r="H311" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I311" t="n">
-        <v>113.1372459930489</v>
+        <v>115.2503574460976</v>
       </c>
       <c r="J311" t="n">
-        <v>0.09677272186314008</v>
+        <v>0.06922847793328751</v>
       </c>
       <c r="K311" t="n">
-        <v>1.541124197781541</v>
+        <v>1.269942852985444</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -12291,22 +12291,22 @@
         <v>9</v>
       </c>
       <c r="F312" t="n">
-        <v>0.09983314794217912</v>
+        <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>6.485563068671011</v>
+        <v>6.296969191603211</v>
       </c>
       <c r="H312" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I312" t="n">
-        <v>20.83380614519403</v>
+        <v>20.24988718935582</v>
       </c>
       <c r="J312" t="n">
-        <v>0.07755205053517548</v>
+        <v>0.09766596559693762</v>
       </c>
       <c r="K312" t="n">
-        <v>1.300833219049264</v>
+        <v>1.666834862851918</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12335,16 +12335,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H313" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I313" t="n">
-        <v>103.6491138805009</v>
+        <v>105.7883522578129</v>
       </c>
       <c r="J313" t="n">
-        <v>0.04901399074109758</v>
+        <v>0.04660998018250238</v>
       </c>
       <c r="K313" t="n">
-        <v>0.9440590875930874</v>
+        <v>0.9542644379774858</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12373,16 +12373,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H314" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I314" t="n">
-        <v>28.06567468757448</v>
+        <v>26.04685637567984</v>
       </c>
       <c r="J314" t="n">
-        <v>0.06002622425728351</v>
+        <v>0.06854248969155763</v>
       </c>
       <c r="K314" t="n">
-        <v>1.081730676919042</v>
+        <v>1.260368756453951</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12411,16 +12411,16 @@
         <v>4.289492277647788</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I315" t="n">
-        <v>27.70867800933029</v>
+        <v>25.61123445369835</v>
       </c>
       <c r="J315" t="n">
-        <v>0.01803232860008041</v>
+        <v>0.01967221260559414</v>
       </c>
       <c r="K315" t="n">
-        <v>0.5567357838650644</v>
+        <v>0.5783034936996553</v>
       </c>
       <c r="L315" t="b">
         <v>0</v>
@@ -12443,22 +12443,22 @@
         <v>542</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>0.3363296996663437</v>
       </c>
       <c r="G316" t="n">
-        <v>9.962572308395055</v>
+        <v>10.96778499411108</v>
       </c>
       <c r="H316" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I316" t="n">
-        <v>112.6635124560465</v>
+        <v>114.7848877730463</v>
       </c>
       <c r="J316" t="n">
-        <v>0.04384766103969768</v>
+        <v>0.02223125619588508</v>
       </c>
       <c r="K316" t="n">
-        <v>0.8794712072209363</v>
+        <v>0.6140191647146005</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -12481,22 +12481,22 @@
         <v>622</v>
       </c>
       <c r="F317" t="n">
-        <v>0.05978865406007999</v>
+        <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>8.481710812878779</v>
+        <v>8.332258457345164</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I317" t="n">
-        <v>32.83735482260811</v>
+        <v>30.79600906652642</v>
       </c>
       <c r="J317" t="n">
-        <v>0.08080074020017938</v>
+        <v>0.06813702339265269</v>
       </c>
       <c r="K317" t="n">
-        <v>1.341447347758986</v>
+        <v>1.254709805979532</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -12519,22 +12519,22 @@
         <v>538</v>
       </c>
       <c r="F318" t="n">
-        <v>0.01390564064347731</v>
+        <v>0.11985279644052</v>
       </c>
       <c r="G318" t="n">
-        <v>9.810299686261155</v>
+        <v>10.12081631126362</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I318" t="n">
-        <v>87.37521969287069</v>
+        <v>85.37618288149029</v>
       </c>
       <c r="J318" t="n">
-        <v>0.07309104004481089</v>
+        <v>0.03801845892555641</v>
       </c>
       <c r="K318" t="n">
-        <v>1.245063024628164</v>
+        <v>0.8343555986379791</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12557,22 +12557,22 @@
         <v>62</v>
       </c>
       <c r="F319" t="n">
-        <v>0.3331479421579884</v>
+        <v>0.07152391546164236</v>
       </c>
       <c r="G319" t="n">
-        <v>21.96278689569177</v>
+        <v>20.39561872725359</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I319" t="n">
-        <v>41.7122283346884</v>
+        <v>39.82603991525067</v>
       </c>
       <c r="J319" t="n">
-        <v>0.1171563922236868</v>
+        <v>0.0592901308837809</v>
       </c>
       <c r="K319" t="n">
-        <v>1.795954636194253</v>
+        <v>1.131236839926802</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -12601,16 +12601,16 @@
         <v>16.00149602380977</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I320" t="n">
-        <v>80.85455890133923</v>
+        <v>78.82653507520037</v>
       </c>
       <c r="J320" t="n">
-        <v>0.07842273553012795</v>
+        <v>0.03683840932490361</v>
       </c>
       <c r="K320" t="n">
-        <v>1.311718257663927</v>
+        <v>0.8178860615507109</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -12633,22 +12633,22 @@
         <v>282</v>
       </c>
       <c r="F321" t="n">
-        <v>1</v>
+        <v>0.3689098998888046</v>
       </c>
       <c r="G321" t="n">
-        <v>27.88491357562365</v>
+        <v>23.82386136792387</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I321" t="n">
-        <v>25.79173901976185</v>
+        <v>24.28081038740774</v>
       </c>
       <c r="J321" t="n">
-        <v>0.07594046108025101</v>
+        <v>0.04436417065269846</v>
       </c>
       <c r="K321" t="n">
-        <v>1.280685618539859</v>
+        <v>0.9229204645363822</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -12671,22 +12671,22 @@
         <v>10</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7221913236930061</v>
+        <v>0.2023359288098402</v>
       </c>
       <c r="G322" t="n">
-        <v>17.65809095551089</v>
+        <v>15.39459741943883</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I322" t="n">
-        <v>231.3106111856645</v>
+        <v>230.2806811174245</v>
       </c>
       <c r="J322" t="n">
-        <v>0.01839065666989803</v>
+        <v>0.00829621249527665</v>
       </c>
       <c r="K322" t="n">
-        <v>0.5612154922547734</v>
+        <v>0.4195326626956056</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -12709,22 +12709,22 @@
         <v>105</v>
       </c>
       <c r="F323" t="n">
-        <v>0.6554505005561541</v>
+        <v>0.3331479421580283</v>
       </c>
       <c r="G323" t="n">
-        <v>16.28448540392015</v>
+        <v>14.96866295616355</v>
       </c>
       <c r="H323" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I323" t="n">
-        <v>230.680474164526</v>
+        <v>228.7269951484766</v>
       </c>
       <c r="J323" t="n">
-        <v>0.3748637842310465</v>
+        <v>0.487478640586293</v>
       </c>
       <c r="K323" t="n">
-        <v>5.017733958849606</v>
+        <v>7.107313215857507</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -12747,22 +12747,22 @@
         <v>10</v>
       </c>
       <c r="F324" t="n">
-        <v>0.09983314794216223</v>
+        <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>11.96718944576948</v>
+        <v>11.61919519588168</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I324" t="n">
-        <v>271.3229569491451</v>
+        <v>269.7897277448292</v>
       </c>
       <c r="J324" t="n">
-        <v>0.6003574298093823</v>
+        <v>0.5455309324776515</v>
       </c>
       <c r="K324" t="n">
-        <v>7.836786835275088</v>
+        <v>7.917528628647568</v>
       </c>
       <c r="L324" t="b">
         <v>0</v>
@@ -12791,16 +12791,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1673138984182182</v>
+        <v>0.1725313205724583</v>
       </c>
       <c r="I325" t="n">
-        <v>271.9504497714821</v>
+        <v>270.3955759886917</v>
       </c>
       <c r="J325" t="n">
         <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>12.83299652512443</v>
+        <v>14.26039350350955</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>

--- a/output/lstm_results/lstm_data_for_cnn.xlsx
+++ b/output/lstm_results/lstm_data_for_cnn.xlsx
@@ -511,16 +511,16 @@
         <v>180</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04274593815351099</v>
+        <v>0.01385228580827646</v>
       </c>
       <c r="G2" t="n">
-        <v>11.25583982562025</v>
+        <v>11.15950846115205</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I2" t="n">
-        <v>123.1692157433761</v>
+        <v>123.2548079002438</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>3.130550111402148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I3" t="n">
-        <v>105.2558370637407</v>
+        <v>105.3436182048155</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3331479421580256</v>
+        <v>0.376161209448902</v>
       </c>
       <c r="G4" t="n">
-        <v>24.84224811920275</v>
+        <v>25.13368456143969</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I4" t="n">
-        <v>29.88235507177804</v>
+        <v>29.75204344599689</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5164649610678496</v>
+        <v>0.2548041240519832</v>
       </c>
       <c r="G5" t="n">
-        <v>23.2491355768497</v>
+        <v>21.66895193871442</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I5" t="n">
-        <v>39.28942726860058</v>
+        <v>39.16078927133193</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         <v>621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1195773081201641</v>
+        <v>0.02350614742421216</v>
       </c>
       <c r="G6" t="n">
-        <v>13.3613588541968</v>
+        <v>12.98960256308772</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I6" t="n">
-        <v>62.45290031964424</v>
+        <v>62.39924737520739</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>502</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0426918798665293</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>10.18839587092663</v>
+        <v>10.05955744553407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I7" t="n">
-        <v>89.95830214227952</v>
+        <v>89.83979710266848</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
         <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5556173526140198</v>
+        <v>0.6278781090048696</v>
       </c>
       <c r="G8" t="n">
-        <v>17.53394458895654</v>
+        <v>17.85974355140973</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I8" t="n">
-        <v>75.45800338202417</v>
+        <v>75.33728505578088</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -783,10 +783,10 @@
         <v>13.96824971139906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I9" t="n">
-        <v>86.78673227199528</v>
+        <v>86.67061821580916</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>406</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5556173526140743</v>
+        <v>0.7572951632405794</v>
       </c>
       <c r="G10" t="n">
-        <v>24.29950966012491</v>
+        <v>25.55966241167819</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I10" t="n">
-        <v>41.22801978256253</v>
+        <v>41.20755171888074</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -853,16 +853,16 @@
         <v>368</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1676798220245143</v>
+        <v>0.1266367420902895</v>
       </c>
       <c r="G11" t="n">
-        <v>4.176625922292869</v>
+        <v>4.127662498284683</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I11" t="n">
-        <v>116.5330098436377</v>
+        <v>116.6298323264942</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         <v>379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2778086763070295</v>
+        <v>0.313939054502457</v>
       </c>
       <c r="G12" t="n">
-        <v>5.941640973809919</v>
+        <v>6.001088576510699</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I12" t="n">
-        <v>102.3323914321277</v>
+        <v>102.4211071272682</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>10.87983322482473</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I13" t="n">
-        <v>34.6883049897331</v>
+        <v>34.71756767674288</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>5.405378062633547</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I14" t="n">
-        <v>184.7976516530829</v>
+        <v>184.7249199096449</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1005,16 +1005,16 @@
         <v>277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5556173526140262</v>
+        <v>0.6278781090048769</v>
       </c>
       <c r="G15" t="n">
-        <v>18.71282535061905</v>
+        <v>19.06052914612661</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I15" t="n">
-        <v>39.94033407310379</v>
+        <v>39.81334125871752</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>10.12438798150288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I16" t="n">
-        <v>114.2301789753145</v>
+        <v>114.3131951323779</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1081,22 +1081,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8849948832035945</v>
+        <v>0.638834236328366</v>
       </c>
       <c r="G17" t="n">
-        <v>25.06272242830079</v>
+        <v>23.60018664428593</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I17" t="n">
-        <v>108.6797504099136</v>
+        <v>108.7760641671631</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07065873769014119</v>
+        <v>0.06653638601018749</v>
       </c>
       <c r="K17" t="n">
-        <v>1.289904485188784</v>
+        <v>1.220526017557314</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1125,16 +1125,16 @@
         <v>5.248200453488796</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I18" t="n">
-        <v>192.2446076995312</v>
+        <v>192.2886507161189</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1010218097653444</v>
+        <v>0.0879538228317804</v>
       </c>
       <c r="K18" t="n">
-        <v>1.713671199189046</v>
+        <v>1.519233082932138</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1157,22 +1157,22 @@
         <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.003061115095886442</v>
       </c>
       <c r="G19" t="n">
-        <v>22.28885569068094</v>
+        <v>22.30932431646837</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I19" t="n">
-        <v>31.95854851596797</v>
+        <v>31.82601438573502</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5059165470747756</v>
+        <v>0.504604700078616</v>
       </c>
       <c r="K19" t="n">
-        <v>7.364644589518126</v>
+        <v>7.33022540031216</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I20" t="n">
-        <v>66.99947464678726</v>
+        <v>66.92952184047854</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01108693935493489</v>
+        <v>0.009393268324614816</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4584818555855918</v>
+        <v>0.4235560938259772</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         <v>216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5769632925472992</v>
+        <v>0.6396311827169987</v>
       </c>
       <c r="G21" t="n">
-        <v>19.75508998564958</v>
+        <v>20.07169251685383</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I21" t="n">
-        <v>30.12128391393638</v>
+        <v>29.99236422303212</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1133307230568491</v>
+        <v>0.1137651861698729</v>
       </c>
       <c r="K21" t="n">
-        <v>1.885462371226444</v>
+        <v>1.879221846306089</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1271,22 +1271,22 @@
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>5.405828698554315e-05</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>6.604212491818722</v>
+        <v>6.604105389831389</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I22" t="n">
-        <v>104.8029381159723</v>
+        <v>104.8955881632196</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04608731492791557</v>
+        <v>0.04660236333850133</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9469697829139343</v>
+        <v>0.9425079959343268</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>435</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5556173526140915</v>
+        <v>0.02350614742421015</v>
       </c>
       <c r="G23" t="n">
-        <v>15.41953945756062</v>
+        <v>13.30973905461809</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I23" t="n">
-        <v>24.52768467624059</v>
+        <v>24.39634485170043</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06666698793101794</v>
+        <v>0.06643455696444564</v>
       </c>
       <c r="K23" t="n">
-        <v>1.23419303825926</v>
+        <v>1.219105817013391</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>678</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3720916573971721</v>
+        <v>0.2548041240519974</v>
       </c>
       <c r="G24" t="n">
-        <v>17.41088234516358</v>
+        <v>16.8597770202047</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I24" t="n">
-        <v>111.4359869865275</v>
+        <v>111.5210831983169</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02061077018502644</v>
+        <v>0.0185669368327863</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5914026116133818</v>
+        <v>0.5515004235617678</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1385,22 +1385,22 @@
         <v>120</v>
       </c>
       <c r="F25" t="n">
-        <v>5.405828698564195e-05</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.55664832169568</v>
+        <v>3.556590642736384</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I25" t="n">
-        <v>104.2223927646257</v>
+        <v>104.3055741312031</v>
       </c>
       <c r="J25" t="n">
-        <v>0.04457132087738927</v>
+        <v>0.05698843913411514</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9258115873385881</v>
+        <v>1.087361661081618</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>674</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5559468992214315</v>
+        <v>0.03975143544917208</v>
       </c>
       <c r="G26" t="n">
-        <v>22.26064832465058</v>
+        <v>19.3061567481292</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I26" t="n">
-        <v>65.33773436557786</v>
+        <v>65.29489495466176</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04428062629448599</v>
+        <v>0.05746968383407251</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9217544653230856</v>
+        <v>1.094073537635704</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.555671410901006</v>
+        <v>0.03959591678410077</v>
       </c>
       <c r="G27" t="n">
-        <v>16.38114311733634</v>
+        <v>14.20734619898275</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I27" t="n">
-        <v>65.47048678120628</v>
+        <v>65.40660834372586</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07746728569798508</v>
+        <v>0.08323226442055204</v>
       </c>
       <c r="K27" t="n">
-        <v>1.384928994212472</v>
+        <v>1.453381932359726</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1499,22 +1499,22 @@
         <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7222453819800044</v>
+        <v>0.941817163507327</v>
       </c>
       <c r="G28" t="n">
-        <v>25.19017059230747</v>
+        <v>26.5539835083398</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I28" t="n">
-        <v>35.24708042143696</v>
+        <v>35.25899087948547</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08178667636430419</v>
+        <v>0.08895753102252792</v>
       </c>
       <c r="K28" t="n">
-        <v>1.445213210006443</v>
+        <v>1.533231710809429</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1537,22 +1537,22 @@
         <v>373</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5080934371524084</v>
+        <v>0.633069990798042</v>
       </c>
       <c r="G29" t="n">
-        <v>25.68630208010256</v>
+        <v>26.52197739078042</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I29" t="n">
-        <v>10.61067327951851</v>
+        <v>10.70137668636294</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03362784378979535</v>
+        <v>0.03967171398975174</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7730773279836476</v>
+        <v>0.8458468527101417</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -1581,16 +1581,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I30" t="n">
-        <v>38.23648624117343</v>
+        <v>38.10876267995729</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0879157370484521</v>
+        <v>0.09025547625160071</v>
       </c>
       <c r="K30" t="n">
-        <v>1.530754353524352</v>
+        <v>1.551334036200799</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1619,16 +1619,16 @@
         <v>7.790921447428411</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I31" t="n">
-        <v>160.272998877366</v>
+        <v>160.1705211393607</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0327061053705026</v>
+        <v>0.03291691199654435</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7602129491703298</v>
+        <v>0.7516382367405241</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>11.449738512298</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I32" t="n">
-        <v>58.6306202825246</v>
+        <v>58.58939270620922</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1158335829929961</v>
+        <v>0.1151028923145186</v>
       </c>
       <c r="K32" t="n">
-        <v>1.920393906748177</v>
+        <v>1.897878713611429</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1689,22 +1689,22 @@
         <v>305</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.6337306638674393</v>
       </c>
       <c r="G33" t="n">
-        <v>16.80179799902379</v>
+        <v>19.99614237905018</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I33" t="n">
-        <v>32.3905445238623</v>
+        <v>32.3285255702457</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02361856588393054</v>
+        <v>0.0235176320929314</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6333813579191503</v>
+        <v>0.6205473251607524</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1727,22 +1727,22 @@
         <v>193</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3331479421579999</v>
+        <v>0.2144734320629172</v>
       </c>
       <c r="G34" t="n">
-        <v>16.73490621517591</v>
+        <v>16.19324061064967</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I34" t="n">
-        <v>34.29627342288722</v>
+        <v>34.29797380660997</v>
       </c>
       <c r="J34" t="n">
-        <v>0.024744126675183</v>
+        <v>0.03114123458367183</v>
       </c>
       <c r="K34" t="n">
-        <v>0.6490904138649788</v>
+        <v>0.7268730235420542</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -1765,22 +1765,22 @@
         <v>616</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.008059968838719183</v>
       </c>
       <c r="G35" t="n">
-        <v>20.91041556258507</v>
+        <v>20.9609767519368</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I35" t="n">
-        <v>18.64814676732945</v>
+        <v>18.60184049043275</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03860554091598047</v>
+        <v>0.03596259253046459</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8425492954192056</v>
+        <v>0.7941160692624496</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1803,22 +1803,22 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5556173526140363</v>
+        <v>0.5653992803814747</v>
       </c>
       <c r="G36" t="n">
-        <v>18.40473882773843</v>
+        <v>18.45103250444718</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I36" t="n">
-        <v>33.22035544535546</v>
+        <v>33.0936853171095</v>
       </c>
       <c r="J36" t="n">
-        <v>0.01979204512306645</v>
+        <v>0.02011400437984332</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5799759539841036</v>
+        <v>0.5730772355195891</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -1841,22 +1841,22 @@
         <v>357</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4329810901001586</v>
+        <v>0.03959591678410065</v>
       </c>
       <c r="G37" t="n">
-        <v>20.25693270693071</v>
+        <v>18.14113033679745</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I37" t="n">
-        <v>64.38123705264955</v>
+        <v>64.33639892132078</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01889908744670283</v>
+        <v>0.01992226750801966</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5675132578736216</v>
+        <v>0.5704030986103186</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>285</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3331479421579941</v>
+        <v>0.01385228580827779</v>
       </c>
       <c r="G38" t="n">
-        <v>17.89259238312755</v>
+        <v>16.33441531920593</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I38" t="n">
-        <v>106.2850349936737</v>
+        <v>106.3694205618118</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1084872905044423</v>
+        <v>0.1103401481014605</v>
       </c>
       <c r="K38" t="n">
-        <v>1.817864287207417</v>
+        <v>1.831453148364556</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>21.78421446827955</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I39" t="n">
-        <v>32.76671958087123</v>
+        <v>32.63617902444754</v>
       </c>
       <c r="J39" t="n">
-        <v>0.09332872638073257</v>
+        <v>0.09101213490968435</v>
       </c>
       <c r="K39" t="n">
-        <v>1.606301541127029</v>
+        <v>1.561887086462106</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -1955,22 +1955,22 @@
         <v>296</v>
       </c>
       <c r="F40" t="n">
-        <v>0.5556173526140422</v>
+        <v>0.02350614742421227</v>
       </c>
       <c r="G40" t="n">
-        <v>17.40454311137317</v>
+        <v>15.0231417621002</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I40" t="n">
-        <v>224.1061541260364</v>
+        <v>224.0583426296516</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03917735947588942</v>
+        <v>0.03966653475457497</v>
       </c>
       <c r="K40" t="n">
-        <v>0.850529965871023</v>
+        <v>0.8457746183828772</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -1999,16 +1999,16 @@
         <v>3.307725502516798</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I41" t="n">
-        <v>186.6105010565384</v>
+        <v>186.6046194189773</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1119149160043783</v>
+        <v>0.1191204986973772</v>
       </c>
       <c r="K41" t="n">
-        <v>1.865702450333132</v>
+        <v>1.953911908547481</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2031,22 +2031,22 @@
         <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>0.03576195773082118</v>
+        <v>0.01087653413193132</v>
       </c>
       <c r="G42" t="n">
-        <v>9.392213439573528</v>
+        <v>9.322838966671295</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I42" t="n">
-        <v>65.0745722593559</v>
+        <v>65.00225491763509</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1207366229044083</v>
+        <v>0.1300991834706158</v>
       </c>
       <c r="K42" t="n">
-        <v>1.988823909704569</v>
+        <v>2.107030637814985</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5556173526140193</v>
+        <v>0.2694533562488602</v>
       </c>
       <c r="G43" t="n">
-        <v>11.10000571301757</v>
+        <v>10.28322446506008</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I43" t="n">
-        <v>117.2016187103962</v>
+        <v>117.2932088824043</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0264281670771804</v>
+        <v>0.02206675687247813</v>
       </c>
       <c r="K43" t="n">
-        <v>0.672593973242323</v>
+        <v>0.6003120989319204</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2107,22 +2107,22 @@
         <v>71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8334260289210373</v>
+        <v>0.7532651788211991</v>
       </c>
       <c r="G44" t="n">
-        <v>23.94910058924098</v>
+        <v>23.48836357626373</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I44" t="n">
-        <v>119.4493209049221</v>
+        <v>119.5410306109095</v>
       </c>
       <c r="J44" t="n">
-        <v>0.01866406728062848</v>
+        <v>0.02258815603281535</v>
       </c>
       <c r="K44" t="n">
-        <v>0.564233164105295</v>
+        <v>0.6075840061340094</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2145,22 +2145,22 @@
         <v>620</v>
       </c>
       <c r="F45" t="n">
-        <v>0.1997203541713349</v>
+        <v>0.02438253704903324</v>
       </c>
       <c r="G45" t="n">
-        <v>19.50386394770364</v>
+        <v>18.53592934140672</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I45" t="n">
-        <v>30.85318583155741</v>
+        <v>30.73070179240706</v>
       </c>
       <c r="J45" t="n">
-        <v>0.08253207538397282</v>
+        <v>0.08856328392098459</v>
       </c>
       <c r="K45" t="n">
-        <v>1.45561648186252</v>
+        <v>1.527733181937113</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2183,22 +2183,22 @@
         <v>496</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5639888765295304</v>
+        <v>0.6278781090048844</v>
       </c>
       <c r="G46" t="n">
-        <v>22.3066773115032</v>
+        <v>22.67235313089035</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I46" t="n">
-        <v>16.58955756878242</v>
+        <v>16.56187712707846</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02714303866300337</v>
+        <v>0.02858563535645692</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6825711844449982</v>
+        <v>0.6912303109338906</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I47" t="n">
-        <v>32.15396703199863</v>
+        <v>32.13316137457676</v>
       </c>
       <c r="J47" t="n">
-        <v>0.06637741472510036</v>
+        <v>0.06469285662256342</v>
       </c>
       <c r="K47" t="n">
-        <v>1.230151566907801</v>
+        <v>1.194814478968614</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         <v>12.79325302649799</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I48" t="n">
-        <v>31.00669874290006</v>
+        <v>31.02435334595575</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03578366055377311</v>
+        <v>0.03950564155998261</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8031653040552</v>
+        <v>0.8435306554663151</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2303,16 +2303,16 @@
         <v>13.11028664827737</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I49" t="n">
-        <v>22.99292465625096</v>
+        <v>22.86575624663618</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01227709936228297</v>
+        <v>0.01406965660426825</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4750925000618573</v>
+        <v>0.4887772606352653</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         <v>430</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8334260289210501</v>
+        <v>0.662971102711519</v>
       </c>
       <c r="G50" t="n">
-        <v>25.88074021494434</v>
+        <v>24.82200384932912</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I50" t="n">
-        <v>29.89635428070724</v>
+        <v>29.76607052847566</v>
       </c>
       <c r="J50" t="n">
-        <v>0.03333861533723404</v>
+        <v>0.03282859553799315</v>
       </c>
       <c r="K50" t="n">
-        <v>0.769040668233484</v>
+        <v>0.7504064950350213</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -2373,22 +2373,22 @@
         <v>551</v>
       </c>
       <c r="F51" t="n">
-        <v>0.1195773081201534</v>
+        <v>0.01979795839205038</v>
       </c>
       <c r="G51" t="n">
-        <v>5.626577603354042</v>
+        <v>5.463985427432266</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I51" t="n">
-        <v>19.98262821069968</v>
+        <v>19.85438891577595</v>
       </c>
       <c r="J51" t="n">
-        <v>0.03354659430277569</v>
+        <v>0.03293370757005129</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7719433574801606</v>
+        <v>0.7518724830938733</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>5.066791391008713</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I52" t="n">
-        <v>36.95496758029069</v>
+        <v>36.9691194491067</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02422132491122961</v>
+        <v>0.02476932865567675</v>
       </c>
       <c r="K52" t="n">
-        <v>0.6417938535882273</v>
+        <v>0.638004624561793</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2455,16 +2455,16 @@
         <v>4.862088337329959</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I53" t="n">
-        <v>75.67134187702</v>
+        <v>75.65617738784616</v>
       </c>
       <c r="J53" t="n">
-        <v>0.01499288144085234</v>
+        <v>0.01499079446298734</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5129957150107828</v>
+        <v>0.5016242875169425</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2487,22 +2487,22 @@
         <v>537</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0002754883203560995</v>
+        <v>0.0001555186650785688</v>
       </c>
       <c r="G54" t="n">
-        <v>6.104577218977858</v>
+        <v>6.104357527927181</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I54" t="n">
-        <v>37.51344655974254</v>
+        <v>37.39181909988626</v>
       </c>
       <c r="J54" t="n">
-        <v>0.03988722763043866</v>
+        <v>0.04300468536225777</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8604373459438198</v>
+        <v>0.8923315047230211</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -2531,16 +2531,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I55" t="n">
-        <v>38.26256329269757</v>
+        <v>38.13118089805458</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01405734324966357</v>
+        <v>0.01457123908905403</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4999387376364286</v>
+        <v>0.4957727864454649</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2569,16 +2569,16 @@
         <v>3.741326101798666</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I56" t="n">
-        <v>114.3018267903333</v>
+        <v>114.392893792664</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0002430834568224279</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3071379741214916</v>
+        <v>0.2925490251978975</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>4.362815948444307</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I57" t="n">
-        <v>119.1724144416496</v>
+        <v>119.2571500007795</v>
       </c>
       <c r="J57" t="n">
-        <v>0.123652992411889</v>
+        <v>0.1246133205504992</v>
       </c>
       <c r="K57" t="n">
-        <v>2.029526652824062</v>
+        <v>2.030519800987652</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I58" t="n">
-        <v>37.5753379440626</v>
+        <v>37.53757036126978</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>0.001464102699613332</v>
       </c>
       <c r="K58" t="n">
-        <v>0.303745343841185</v>
+        <v>0.3129687338890857</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6486839819726939</v>
+        <v>0.3007404155744692</v>
       </c>
       <c r="G59" t="n">
-        <v>24.97969105213751</v>
+        <v>22.79699768242308</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I59" t="n">
-        <v>32.24000229639994</v>
+        <v>32.21306747033</v>
       </c>
       <c r="J59" t="n">
-        <v>0.03119078159370639</v>
+        <v>0.0333966916865259</v>
       </c>
       <c r="K59" t="n">
-        <v>0.7390641083696052</v>
+        <v>0.7583296809322186</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2715,22 +2715,22 @@
         <v>378</v>
       </c>
       <c r="F60" t="n">
-        <v>0.8971368186874719</v>
+        <v>0.2617302669561336</v>
       </c>
       <c r="G60" t="n">
-        <v>28.55599991914888</v>
+        <v>24.26695667150904</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I60" t="n">
-        <v>26.22489788799395</v>
+        <v>26.09363336287619</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04198404280613077</v>
+        <v>0.04558261822018405</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8897018576068079</v>
+        <v>0.9282857024703508</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>4.710418346601499</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I61" t="n">
-        <v>28.35044261881249</v>
+        <v>28.32493008076046</v>
       </c>
       <c r="J61" t="n">
-        <v>0.01976734846316553</v>
+        <v>0.02068443474840413</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5796312713911475</v>
+        <v>0.5810329765736116</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2797,16 +2797,16 @@
         <v>13.57276718285553</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I62" t="n">
-        <v>89.80197964555539</v>
+        <v>89.6869651653345</v>
       </c>
       <c r="J62" t="n">
-        <v>0.05815693658718699</v>
+        <v>0.0595828014318503</v>
       </c>
       <c r="K62" t="n">
-        <v>1.115421245832698</v>
+        <v>1.123544998748535</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -2829,22 +2829,22 @@
         <v>659</v>
       </c>
       <c r="F63" t="n">
-        <v>0.09988720622916851</v>
+        <v>0.04996627594184065</v>
       </c>
       <c r="G63" t="n">
-        <v>4.697015545311514</v>
+        <v>4.628718334895234</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I63" t="n">
-        <v>34.43419147053508</v>
+        <v>34.45814610010484</v>
       </c>
       <c r="J63" t="n">
-        <v>0.06822214060695486</v>
+        <v>0.07380975299933472</v>
       </c>
       <c r="K63" t="n">
-        <v>1.255897756991878</v>
+        <v>1.321967012893035</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -2867,22 +2867,22 @@
         <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6156814949944472</v>
+        <v>0.1220227996042205</v>
       </c>
       <c r="G64" t="n">
-        <v>11.91760245564876</v>
+        <v>10.42780605421914</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I64" t="n">
-        <v>179.0629132781346</v>
+        <v>179.0094197568594</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03229328034833517</v>
+        <v>0.03608863817982474</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7544512955844316</v>
+        <v>0.7958740165993445</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -2905,22 +2905,22 @@
         <v>692</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0380889877641922</v>
+        <v>0.01095612732349916</v>
       </c>
       <c r="G65" t="n">
-        <v>11.24031356469956</v>
+        <v>11.14985267602592</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I65" t="n">
-        <v>28.69860965051859</v>
+        <v>28.70462788006087</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1095327624348496</v>
+        <v>0.0879171320284878</v>
       </c>
       <c r="K65" t="n">
-        <v>1.832455571100921</v>
+        <v>1.518721359598059</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -2943,22 +2943,22 @@
         <v>489</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1071374831981166</v>
+        <v>0.6278781090048652</v>
       </c>
       <c r="G66" t="n">
-        <v>17.10445213370436</v>
+        <v>19.69333708090076</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I66" t="n">
-        <v>89.41035276025718</v>
+        <v>89.29905708681602</v>
       </c>
       <c r="J66" t="n">
-        <v>0.02340004210363482</v>
+        <v>0.02305821406316307</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6303314984030421</v>
+        <v>0.6141398632130171</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -2981,22 +2981,22 @@
         <v>259</v>
       </c>
       <c r="F67" t="n">
-        <v>0.05978865406008206</v>
+        <v>0.03959591678410077</v>
       </c>
       <c r="G67" t="n">
-        <v>4.491063008319657</v>
+        <v>4.464336337202671</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I67" t="n">
-        <v>18.74323521515296</v>
+        <v>18.72135083536519</v>
       </c>
       <c r="J67" t="n">
-        <v>0.0371850638647615</v>
+        <v>0.04535931986248213</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8227241969964592</v>
+        <v>0.9251713803557218</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3019,22 +3019,22 @@
         <v>627</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5556173526140763</v>
+        <v>0.6348042519090717</v>
       </c>
       <c r="G68" t="n">
-        <v>21.79278225228457</v>
+        <v>22.2365273632229</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I68" t="n">
-        <v>112.5446921819305</v>
+        <v>112.6277355166075</v>
       </c>
       <c r="J68" t="n">
-        <v>0.02641919301260483</v>
+        <v>0.02723299971292755</v>
       </c>
       <c r="K68" t="n">
-        <v>0.6724687253804795</v>
+        <v>0.6723652232501631</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3776418242492196</v>
+        <v>0.3639053304443413</v>
       </c>
       <c r="G69" t="n">
-        <v>13.39208684235665</v>
+        <v>13.34251488077438</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I69" t="n">
-        <v>15.65247452673903</v>
+        <v>15.5281666491021</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1023407847685687</v>
+        <v>0.1041968290979895</v>
       </c>
       <c r="K69" t="n">
-        <v>1.732079669240445</v>
+        <v>1.745772830664815</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>0.8334260289210794</v>
+        <v>0.392389048075213</v>
       </c>
       <c r="G70" t="n">
-        <v>23.25012771332207</v>
+        <v>20.78918259039171</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I70" t="n">
-        <v>28.58953588620482</v>
+        <v>28.61123237468256</v>
       </c>
       <c r="J70" t="n">
-        <v>0.04523462276149988</v>
+        <v>0.04581176224268676</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9350690583587651</v>
+        <v>0.9314815535462816</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3133,22 +3133,22 @@
         <v>421</v>
       </c>
       <c r="F71" t="n">
-        <v>0.5556173526140203</v>
+        <v>0.01788227022763862</v>
       </c>
       <c r="G71" t="n">
-        <v>15.79342034552541</v>
+        <v>13.60962402706039</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I71" t="n">
-        <v>134.8465327230052</v>
+        <v>134.9245575123915</v>
       </c>
       <c r="J71" t="n">
-        <v>0.05060680786484363</v>
+        <v>0.04916583620829132</v>
       </c>
       <c r="K71" t="n">
-        <v>1.010046755694745</v>
+        <v>0.9782605215274428</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -3171,22 +3171,22 @@
         <v>694</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8337015172414023</v>
+        <v>0.7534206974862414</v>
       </c>
       <c r="G72" t="n">
-        <v>27.44242471194498</v>
+        <v>26.91372734536539</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I72" t="n">
-        <v>24.1732486796384</v>
+        <v>24.04223284282924</v>
       </c>
       <c r="J72" t="n">
-        <v>0.01288801785328014</v>
+        <v>0.007866550000008332</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4836188744949403</v>
+        <v>0.4022630906437573</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>250</v>
       </c>
       <c r="F73" t="n">
-        <v>0.55567141090105</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>20.18826069922442</v>
+        <v>17.30370795523318</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I73" t="n">
-        <v>41.3279864413372</v>
+        <v>41.40247703874948</v>
       </c>
       <c r="J73" t="n">
-        <v>0.0273930402486224</v>
+        <v>0.027870700778255</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6860603686148423</v>
+        <v>0.6812591826626319</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -3247,22 +3247,22 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4676422691880252</v>
+        <v>0.6517060518162718</v>
       </c>
       <c r="G74" t="n">
-        <v>23.74981089503482</v>
+        <v>24.89990510430726</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I74" t="n">
-        <v>76.7997273344141</v>
+        <v>76.74715597753509</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02879720306608408</v>
+        <v>0.02624566523883781</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7056577750170435</v>
+        <v>0.658594958126682</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3285,22 +3285,22 @@
         <v>564</v>
       </c>
       <c r="F75" t="n">
-        <v>0.833426028921014</v>
+        <v>0.6489257396709005</v>
       </c>
       <c r="G75" t="n">
-        <v>24.90867827486581</v>
+        <v>23.80574480858942</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I75" t="n">
-        <v>107.1027669133627</v>
+        <v>107.1889235213026</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05609992159391964</v>
+        <v>0.05636115635940101</v>
       </c>
       <c r="K75" t="n">
-        <v>1.086712211312503</v>
+        <v>1.078613004631463</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3323,22 +3323,22 @@
         <v>521</v>
       </c>
       <c r="F76" t="n">
-        <v>0.07152391546164216</v>
+        <v>0.6388342363284196</v>
       </c>
       <c r="G76" t="n">
-        <v>17.87351660113654</v>
+        <v>20.85156522317409</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I76" t="n">
-        <v>113.6063264951257</v>
+        <v>113.6961743438249</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1213975374188765</v>
+        <v>0.1222855381731336</v>
       </c>
       <c r="K76" t="n">
-        <v>1.99804806104662</v>
+        <v>1.998054429497769</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>607</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3331479421579999</v>
+        <v>0.02350614742421015</v>
       </c>
       <c r="G77" t="n">
-        <v>19.28974050698345</v>
+        <v>17.66068272058278</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I77" t="n">
-        <v>112.6169423981693</v>
+        <v>112.707936042604</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05649799147010381</v>
+        <v>0.05688250204756373</v>
       </c>
       <c r="K77" t="n">
-        <v>1.092267932517368</v>
+        <v>1.085884166061942</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3405,16 +3405,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I78" t="n">
-        <v>52.33610320083483</v>
+        <v>52.24254979890153</v>
       </c>
       <c r="J78" t="n">
-        <v>0.09329097035870559</v>
+        <v>0.09775400427046829</v>
       </c>
       <c r="K78" t="n">
-        <v>1.605774593611689</v>
+        <v>1.655915332170288</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>19.31962732559818</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I79" t="n">
-        <v>92.04725722295079</v>
+        <v>92.10226766105751</v>
       </c>
       <c r="J79" t="n">
-        <v>0.06356070097207994</v>
+        <v>0.06402089438294183</v>
       </c>
       <c r="K79" t="n">
-        <v>1.190839684090396</v>
+        <v>1.185442682039222</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -3475,22 +3475,22 @@
         <v>421</v>
       </c>
       <c r="F80" t="n">
-        <v>5.405828698564195e-05</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>2.935200918779775</v>
+        <v>2.935153317971652</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I80" t="n">
-        <v>29.97000374106357</v>
+        <v>29.84077436848336</v>
       </c>
       <c r="J80" t="n">
-        <v>0.0987075789644777</v>
+        <v>0.09927476336792763</v>
       </c>
       <c r="K80" t="n">
-        <v>1.681372294141082</v>
+        <v>1.677125222547374</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3513,22 +3513,22 @@
         <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5556173526140379</v>
+        <v>0.6396311827169713</v>
       </c>
       <c r="G81" t="n">
-        <v>12.46138456281807</v>
+        <v>12.73059050808525</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I81" t="n">
-        <v>114.1003375166647</v>
+        <v>114.1935157735869</v>
       </c>
       <c r="J81" t="n">
-        <v>0.01543389723588296</v>
+        <v>0.01478244525448202</v>
       </c>
       <c r="K81" t="n">
-        <v>0.5191508172948816</v>
+        <v>0.4987184598418472</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -3557,16 +3557,16 @@
         <v>4.411928036584459</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I82" t="n">
-        <v>32.17192458987716</v>
+        <v>32.0555241205651</v>
       </c>
       <c r="J82" t="n">
-        <v>0.03240069049722143</v>
+        <v>0.033964432021305</v>
       </c>
       <c r="K82" t="n">
-        <v>0.7559503812412147</v>
+        <v>0.7662479043269905</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3595,16 +3595,16 @@
         <v>19.96717947032079</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I83" t="n">
-        <v>75.47077855886236</v>
+        <v>75.36016557462568</v>
       </c>
       <c r="J83" t="n">
-        <v>0.01287114140024358</v>
+        <v>0.01411743206003747</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4833833357777259</v>
+        <v>0.4894435806206419</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -3627,22 +3627,22 @@
         <v>241</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0001767215277527809</v>
+        <v>0.0001307138095888819</v>
       </c>
       <c r="G84" t="n">
-        <v>7.584098784635279</v>
+        <v>7.583994112060824</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I84" t="n">
-        <v>26.77165591083007</v>
+        <v>26.64035108623135</v>
       </c>
       <c r="J84" t="n">
-        <v>0.01462965705323259</v>
+        <v>0.01656405556847183</v>
       </c>
       <c r="K84" t="n">
-        <v>0.507926320029763</v>
+        <v>0.5235664186786803</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3665,22 +3665,22 @@
         <v>126</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9999999999999737</v>
+        <v>0.9418171635072538</v>
       </c>
       <c r="G85" t="n">
-        <v>26.27539237994347</v>
+        <v>25.92259772026094</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I85" t="n">
-        <v>19.96040547322278</v>
+        <v>19.91894964181764</v>
       </c>
       <c r="J85" t="n">
-        <v>0.007508499691218278</v>
+        <v>0.008787704408395847</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4085388322384971</v>
+        <v>0.4151103483421719</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3703,22 +3703,22 @@
         <v>474</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1665739710790094</v>
+        <v>0.1253870698163189</v>
       </c>
       <c r="G86" t="n">
-        <v>10.76690285978588</v>
+        <v>10.64019797122157</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I86" t="n">
-        <v>29.43489429325481</v>
+        <v>29.35939248861886</v>
       </c>
       <c r="J86" t="n">
-        <v>0.03144573984514434</v>
+        <v>0.03139190959258149</v>
       </c>
       <c r="K86" t="n">
-        <v>0.7426224709803289</v>
+        <v>0.7303691653492157</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -3747,16 +3747,16 @@
         <v>10.61501705132875</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I87" t="n">
-        <v>28.36002813631899</v>
+        <v>28.36096943049547</v>
       </c>
       <c r="J87" t="n">
-        <v>0.03179058030995022</v>
+        <v>0.03391107606012851</v>
       </c>
       <c r="K87" t="n">
-        <v>0.7474352880188411</v>
+        <v>0.765503753534529</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>3.240904040541774</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I88" t="n">
-        <v>78.61574729437156</v>
+        <v>78.4977001288608</v>
       </c>
       <c r="J88" t="n">
-        <v>0.00585049625358451</v>
+        <v>0.006365307707765795</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3853986616119219</v>
+        <v>0.3813253993939698</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>0.03576195773081476</v>
+        <v>0.01175307371210396</v>
       </c>
       <c r="G89" t="n">
-        <v>3.36582741887074</v>
+        <v>3.341841822398893</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I89" t="n">
-        <v>32.37895504310568</v>
+        <v>32.26398979320266</v>
       </c>
       <c r="J89" t="n">
-        <v>0.03502011480629487</v>
+        <v>0.03665892866202262</v>
       </c>
       <c r="K89" t="n">
-        <v>0.7925087647038351</v>
+        <v>0.8038278066708425</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -3855,22 +3855,22 @@
         <v>507</v>
       </c>
       <c r="F90" t="n">
-        <v>5.405828698554315e-05</v>
+        <v>0.0001555186650783455</v>
       </c>
       <c r="G90" t="n">
-        <v>5.537625086956083</v>
+        <v>5.53779363908311</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I90" t="n">
-        <v>67.94669554959272</v>
+        <v>67.90190403148313</v>
       </c>
       <c r="J90" t="n">
-        <v>0.05659801772982912</v>
+        <v>0.05816908955193113</v>
       </c>
       <c r="K90" t="n">
-        <v>1.093663963831082</v>
+        <v>1.103828086288197</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -3899,16 +3899,16 @@
         <v>10.51627310409919</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I91" t="n">
-        <v>99.42781128528908</v>
+        <v>99.52217776627954</v>
       </c>
       <c r="J91" t="n">
-        <v>0.01655047634278601</v>
+        <v>0.01752283293190116</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5347345190323641</v>
+        <v>0.5369384003477962</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -3937,16 +3937,16 @@
         <v>16.91718590664535</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I92" t="n">
-        <v>90.47366703256877</v>
+        <v>90.36057707337689</v>
       </c>
       <c r="J92" t="n">
-        <v>0.05071215743891551</v>
+        <v>0.05270558925860634</v>
       </c>
       <c r="K92" t="n">
-        <v>1.011517082633838</v>
+        <v>1.027629139005757</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I93" t="n">
-        <v>95.64008069622601</v>
+        <v>95.74067450850278</v>
       </c>
       <c r="J93" t="n">
-        <v>0.03108993557757243</v>
+        <v>0.03312370789239446</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7376566360041193</v>
+        <v>0.7545224005036999</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4013,16 +4013,16 @@
         <v>11.48356342778669</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I94" t="n">
-        <v>22.49631413769563</v>
+        <v>22.38358326184152</v>
       </c>
       <c r="J94" t="n">
-        <v>0.04380005086964243</v>
+        <v>0.04358819169264747</v>
       </c>
       <c r="K94" t="n">
-        <v>0.9150472432043608</v>
+        <v>0.9004696150408074</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -4045,22 +4045,22 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5556173526140414</v>
+        <v>0.09993255188368243</v>
       </c>
       <c r="G95" t="n">
-        <v>13.24008453495866</v>
+        <v>11.68868782921822</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I95" t="n">
-        <v>29.98675267257744</v>
+        <v>29.86446507373608</v>
       </c>
       <c r="J95" t="n">
-        <v>0.03440967289417488</v>
+        <v>0.03585694786875768</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7839890417144613</v>
+        <v>0.7926426526657833</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -4089,16 +4089,16 @@
         <v>24.6460742997744</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I96" t="n">
-        <v>88.00279922123961</v>
+        <v>87.88382431618579</v>
       </c>
       <c r="J96" t="n">
-        <v>0.02898430430675722</v>
+        <v>0.02979561411851748</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7082690812033561</v>
+        <v>0.7081057759202788</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4127,16 +4127,16 @@
         <v>4.685296148590822</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I97" t="n">
-        <v>111.7106144585304</v>
+        <v>111.799154532671</v>
       </c>
       <c r="J97" t="n">
-        <v>0.05255268013256918</v>
+        <v>0.05364863844680842</v>
       </c>
       <c r="K97" t="n">
-        <v>1.037204610299047</v>
+        <v>1.040781761229344</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -4159,22 +4159,22 @@
         <v>667</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5556173526141032</v>
+        <v>0.04996627594184144</v>
       </c>
       <c r="G98" t="n">
-        <v>8.813426459976915</v>
+        <v>7.667482749566142</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I98" t="n">
-        <v>29.09650872009262</v>
+        <v>28.98079984560107</v>
       </c>
       <c r="J98" t="n">
-        <v>0.01912752336797085</v>
+        <v>0.01913769729316605</v>
       </c>
       <c r="K98" t="n">
-        <v>0.570701457653789</v>
+        <v>0.5594607683767053</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -4197,22 +4197,22 @@
         <v>246</v>
       </c>
       <c r="F99" t="n">
-        <v>0.5556173526140675</v>
+        <v>0.02381718475436896</v>
       </c>
       <c r="G99" t="n">
-        <v>8.404597863958431</v>
+        <v>7.255299012986369</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I99" t="n">
-        <v>109.8196578563709</v>
+        <v>109.9008066341507</v>
       </c>
       <c r="J99" t="n">
-        <v>0.04111878077637569</v>
+        <v>0.04004873036340489</v>
       </c>
       <c r="K99" t="n">
-        <v>0.8776256998915958</v>
+        <v>0.8511050661700572</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -4235,22 +4235,22 @@
         <v>478</v>
       </c>
       <c r="F100" t="n">
-        <v>0.6555045588432066</v>
+        <v>0.1521911171540122</v>
       </c>
       <c r="G100" t="n">
-        <v>25.96791237301322</v>
+        <v>22.69126897379678</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I100" t="n">
-        <v>117.6041123095149</v>
+        <v>117.691099971433</v>
       </c>
       <c r="J100" t="n">
-        <v>0.04015181021872496</v>
+        <v>0.03818266096596604</v>
       </c>
       <c r="K100" t="n">
-        <v>0.8641300320377061</v>
+        <v>0.8250791640913945</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -4279,16 +4279,16 @@
         <v>14.47703643706128</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I101" t="n">
-        <v>17.32638269460973</v>
+        <v>17.19598872091978</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1261692422551859</v>
+        <v>0.1210433398850784</v>
       </c>
       <c r="K101" t="n">
-        <v>2.064645066568778</v>
+        <v>1.980729601679695</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4311,22 +4311,22 @@
         <v>130</v>
       </c>
       <c r="F102" t="n">
-        <v>0.4497241379310769</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>23.40404662566535</v>
+        <v>20.62180903800634</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I102" t="n">
-        <v>34.74649648661303</v>
+        <v>34.75904379211874</v>
       </c>
       <c r="J102" t="n">
-        <v>0.07245085035682697</v>
+        <v>0.07335889381491932</v>
       </c>
       <c r="K102" t="n">
-        <v>1.314916371140202</v>
+        <v>1.315678920391777</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4355,16 +4355,16 @@
         <v>10.02719427357424</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I103" t="n">
-        <v>32.40630702477093</v>
+        <v>32.43696780351648</v>
       </c>
       <c r="J103" t="n">
-        <v>0.03049771574111161</v>
+        <v>0.03153340987350037</v>
       </c>
       <c r="K103" t="n">
-        <v>0.7293912321134592</v>
+        <v>0.7323426570426932</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>11.89204612335489</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I104" t="n">
-        <v>74.36725170743645</v>
+        <v>74.25105531851601</v>
       </c>
       <c r="J104" t="n">
-        <v>0.009756284080578784</v>
+        <v>0.01136338273415329</v>
       </c>
       <c r="K104" t="n">
-        <v>0.4399103680995967</v>
+        <v>0.451033102332083</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -4431,16 +4431,16 @@
         <v>6.688712506902953</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I105" t="n">
-        <v>21.74970979379744</v>
+        <v>21.70621962362333</v>
       </c>
       <c r="J105" t="n">
-        <v>0.02738320339889854</v>
+        <v>0.02606127987389218</v>
       </c>
       <c r="K105" t="n">
-        <v>0.6859230791642469</v>
+        <v>0.6560233520227505</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4463,22 +4463,22 @@
         <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>0.8334260289210814</v>
+        <v>0.300740415574471</v>
       </c>
       <c r="G106" t="n">
-        <v>19.25110435256297</v>
+        <v>16.79001038526069</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I106" t="n">
-        <v>114.2612642159953</v>
+        <v>114.3617270008397</v>
       </c>
       <c r="J106" t="n">
-        <v>0.03419724820874385</v>
+        <v>0.03454202424980491</v>
       </c>
       <c r="K106" t="n">
-        <v>0.7810243051194722</v>
+        <v>0.774303531197549</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -4507,16 +4507,16 @@
         <v>4.560359086738675</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I107" t="n">
-        <v>29.96750595711618</v>
+        <v>29.96261113293433</v>
       </c>
       <c r="J107" t="n">
-        <v>0.03305311968435202</v>
+        <v>0.02992317039317353</v>
       </c>
       <c r="K107" t="n">
-        <v>0.7650561058550949</v>
+        <v>0.7098847918123319</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4545,16 +4545,16 @@
         <v>3.08676659305494</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I108" t="n">
-        <v>37.9803676266304</v>
+        <v>37.857318973864</v>
       </c>
       <c r="J108" t="n">
-        <v>0.05036985095449031</v>
+        <v>0.05058973627436752</v>
       </c>
       <c r="K108" t="n">
-        <v>1.006739631467942</v>
+        <v>0.9981195277039349</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -4577,22 +4577,22 @@
         <v>198</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5556173526140396</v>
+        <v>0.6278781090048919</v>
       </c>
       <c r="G109" t="n">
-        <v>22.77512140307686</v>
+        <v>23.19830689252693</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I109" t="n">
-        <v>120.5775716549919</v>
+        <v>120.6689290125666</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01273668003488212</v>
+        <v>0.01242670706159285</v>
       </c>
       <c r="K109" t="n">
-        <v>0.4815067058103074</v>
+        <v>0.4658631911068007</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>5.431724311855306</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I110" t="n">
-        <v>38.74183761133476</v>
+        <v>38.61178886226426</v>
       </c>
       <c r="J110" t="n">
-        <v>0.03452883804969824</v>
+        <v>0.03439530009592531</v>
       </c>
       <c r="K110" t="n">
-        <v>0.785652187862993</v>
+        <v>0.7722571826176483</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4653,22 +4653,22 @@
         <v>124</v>
       </c>
       <c r="F111" t="n">
-        <v>0.555617352614012</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>15.41953945756031</v>
+        <v>13.21653808680624</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I111" t="n">
-        <v>112.3263481695639</v>
+        <v>112.4181382471772</v>
       </c>
       <c r="J111" t="n">
-        <v>0.02585154497599968</v>
+        <v>0.02834097285106757</v>
       </c>
       <c r="K111" t="n">
-        <v>0.6645462614550549</v>
+        <v>0.6878180249726489</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -4697,16 +4697,16 @@
         <v>5.144277597486356</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I112" t="n">
-        <v>87.47532436223625</v>
+        <v>87.35729599894373</v>
       </c>
       <c r="J112" t="n">
-        <v>0.09700574154659036</v>
+        <v>0.09512833865869323</v>
       </c>
       <c r="K112" t="n">
-        <v>1.657620348074671</v>
+        <v>1.619295409997426</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>376</v>
       </c>
       <c r="F113" t="n">
-        <v>0.5769632925472775</v>
+        <v>0.6280336276699486</v>
       </c>
       <c r="G113" t="n">
-        <v>13.27323435906693</v>
+        <v>13.44658911747394</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I113" t="n">
-        <v>28.47488799768441</v>
+        <v>28.36726778123007</v>
       </c>
       <c r="J113" t="n">
-        <v>0.07597042645028469</v>
+        <v>0.07793086485757753</v>
       </c>
       <c r="K113" t="n">
-        <v>1.364037856347772</v>
+        <v>1.379443789386476</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4773,16 +4773,16 @@
         <v>14.18555800805876</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I114" t="n">
-        <v>37.99274164306352</v>
+        <v>37.97081292361351</v>
       </c>
       <c r="J114" t="n">
-        <v>0.006655078632036464</v>
+        <v>0.008901543649641774</v>
       </c>
       <c r="K114" t="n">
-        <v>0.396627934783445</v>
+        <v>0.4166980540027663</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -4811,16 +4811,16 @@
         <v>20.08938572978278</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I115" t="n">
-        <v>52.14443161388473</v>
+        <v>52.01839615613393</v>
       </c>
       <c r="J115" t="n">
-        <v>0.03612486376796295</v>
+        <v>0.0376846071448428</v>
       </c>
       <c r="K115" t="n">
-        <v>0.8079273572665955</v>
+        <v>0.818132852235979</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -4849,16 +4849,16 @@
         <v>6.463893795538414</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I116" t="n">
-        <v>111.2347222004942</v>
+        <v>111.3173890387625</v>
       </c>
       <c r="J116" t="n">
-        <v>0.0234994290003557</v>
+        <v>0.023242272593401</v>
       </c>
       <c r="K116" t="n">
-        <v>0.6317186063522569</v>
+        <v>0.6167069109826711</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>388</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4329810901001389</v>
+        <v>0.6278781090048984</v>
       </c>
       <c r="G117" t="n">
-        <v>20.47912817844968</v>
+        <v>21.53887003295733</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I117" t="n">
-        <v>30.10502168313632</v>
+        <v>30.06878174157317</v>
       </c>
       <c r="J117" t="n">
-        <v>0.02299869485810145</v>
+        <v>0.02545860113888262</v>
       </c>
       <c r="K117" t="n">
-        <v>0.624730036107281</v>
+        <v>0.6476178459018211</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -4925,16 +4925,16 @@
         <v>8.030018742194814</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I118" t="n">
-        <v>22.63473056442236</v>
+        <v>22.60566006711137</v>
       </c>
       <c r="J118" t="n">
-        <v>0.02292305872481806</v>
+        <v>0.02545071161866817</v>
       </c>
       <c r="K118" t="n">
-        <v>0.6236744092068868</v>
+        <v>0.6475078114728601</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -4957,22 +4957,22 @@
         <v>165</v>
       </c>
       <c r="F119" t="n">
-        <v>0.008371523915462193</v>
+        <v>0.00402998441935881</v>
       </c>
       <c r="G119" t="n">
-        <v>13.42789697921584</v>
+        <v>13.41045146934131</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I119" t="n">
-        <v>22.2937981510697</v>
+        <v>22.27046939903661</v>
       </c>
       <c r="J119" t="n">
-        <v>0.02204339094856612</v>
+        <v>0.02329472447284213</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6113971955563406</v>
+        <v>0.6174384526284695</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -5001,16 +5001,16 @@
         <v>3.330100148644182</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I120" t="n">
-        <v>104.9637181944468</v>
+        <v>105.0448656904473</v>
       </c>
       <c r="J120" t="n">
-        <v>0.0572564195871033</v>
+        <v>0.05841487720795295</v>
       </c>
       <c r="K120" t="n">
-        <v>1.10285304690073</v>
+        <v>1.10725606462413</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5033,22 +5033,22 @@
         <v>57</v>
       </c>
       <c r="F121" t="n">
-        <v>0.555671410901072</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>8.985797725740721</v>
+        <v>7.701882886671284</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I121" t="n">
-        <v>28.58637125554106</v>
+        <v>28.55775086481542</v>
       </c>
       <c r="J121" t="n">
-        <v>0.04133894910270769</v>
+        <v>0.04197545962109436</v>
       </c>
       <c r="K121" t="n">
-        <v>0.8806985117581145</v>
+        <v>0.8779769858647609</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -5077,16 +5077,16 @@
         <v>5.670752331040389</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I122" t="n">
-        <v>119.5860631766918</v>
+        <v>119.6819922678943</v>
       </c>
       <c r="J122" t="n">
-        <v>0.02520629807468851</v>
+        <v>0.02682005151614773</v>
       </c>
       <c r="K122" t="n">
-        <v>0.6555407774773387</v>
+        <v>0.6666058718842908</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>2.935153317971652</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I123" t="n">
-        <v>36.08106276858302</v>
+        <v>36.01472799534469</v>
       </c>
       <c r="J123" t="n">
-        <v>0.0148709053565179</v>
+        <v>0.01449293313782848</v>
       </c>
       <c r="K123" t="n">
-        <v>0.5112933377178329</v>
+        <v>0.4946806603854321</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -5153,16 +5153,16 @@
         <v>20.29361436511495</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I124" t="n">
-        <v>24.56653125484663</v>
+        <v>24.52804765846969</v>
       </c>
       <c r="J124" t="n">
-        <v>0.03594706057169879</v>
+        <v>0.03964110007937156</v>
       </c>
       <c r="K124" t="n">
-        <v>0.8054458206146722</v>
+        <v>0.8454198832550437</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -5191,16 +5191,16 @@
         <v>12.02926119925908</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I125" t="n">
-        <v>61.08747838338837</v>
+        <v>61.04349062103338</v>
       </c>
       <c r="J125" t="n">
-        <v>0.0362793677368172</v>
+        <v>0.0376068614649033</v>
       </c>
       <c r="K125" t="n">
-        <v>0.8100837147991666</v>
+        <v>0.81704854022919</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -5229,16 +5229,16 @@
         <v>20.00788726977439</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I126" t="n">
-        <v>66.9284621019665</v>
+        <v>66.86496916882906</v>
       </c>
       <c r="J126" t="n">
-        <v>0.07013288824031104</v>
+        <v>0.07119085719139287</v>
       </c>
       <c r="K126" t="n">
-        <v>1.282565389432549</v>
+        <v>1.285441508565456</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -5267,16 +5267,16 @@
         <v>11.24748896420885</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I127" t="n">
-        <v>19.71586386769579</v>
+        <v>19.58634227535515</v>
       </c>
       <c r="J127" t="n">
-        <v>0.06464857283242573</v>
+        <v>0.0665466746447657</v>
       </c>
       <c r="K127" t="n">
-        <v>1.206022728888046</v>
+        <v>1.220669512218565</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>11.07986791437515</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I128" t="n">
-        <v>178.3092593914622</v>
+        <v>178.3363199421134</v>
       </c>
       <c r="J128" t="n">
-        <v>0.03287465564440775</v>
+        <v>0.03436365057973721</v>
       </c>
       <c r="K128" t="n">
-        <v>0.7625653460404396</v>
+        <v>0.7718157696614747</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -5343,16 +5343,16 @@
         <v>5.484544739538552</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I129" t="n">
-        <v>107.2556686152775</v>
+        <v>107.3533565261391</v>
       </c>
       <c r="J129" t="n">
-        <v>0.2323274760503178</v>
+        <v>0.2314306568740783</v>
       </c>
       <c r="K129" t="n">
-        <v>3.546258184899249</v>
+        <v>3.520291585079175</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -5375,22 +5375,22 @@
         <v>575</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1996662958843493</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>8.131847931250766</v>
+        <v>7.672279257169932</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I130" t="n">
-        <v>64.43203187690828</v>
+        <v>64.38901738476238</v>
       </c>
       <c r="J130" t="n">
-        <v>0.05551323106844575</v>
+        <v>0.05846440095959608</v>
       </c>
       <c r="K130" t="n">
-        <v>1.078523978069853</v>
+        <v>1.107946767934843</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -5419,16 +5419,16 @@
         <v>3.533718721120853</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I131" t="n">
-        <v>109.6627664330125</v>
+        <v>109.7531129049286</v>
       </c>
       <c r="J131" t="n">
-        <v>0.0110561828042159</v>
+        <v>0.01665807758425031</v>
       </c>
       <c r="K131" t="n">
-        <v>0.4580525972286019</v>
+        <v>0.5248777352777563</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -5457,16 +5457,16 @@
         <v>6.408090589247315</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I132" t="n">
-        <v>52.20936080664899</v>
+        <v>52.14568502904427</v>
       </c>
       <c r="J132" t="n">
-        <v>0.007863647123674523</v>
+        <v>0.006922352433483121</v>
       </c>
       <c r="K132" t="n">
-        <v>0.4134954999980985</v>
+        <v>0.3890944520909662</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -5489,22 +5489,22 @@
         <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>5.405828698564195e-05</v>
+        <v>0.09993255188367382</v>
       </c>
       <c r="G133" t="n">
-        <v>11.3486475959432</v>
+        <v>11.6886878292182</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I133" t="n">
-        <v>58.60376340991579</v>
+        <v>58.55549166472917</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03497259770907235</v>
+        <v>0.03411184974807228</v>
       </c>
       <c r="K133" t="n">
-        <v>0.7918455852963318</v>
+        <v>0.7683039261055857</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -5533,16 +5533,16 @@
         <v>5.697522180737868</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I134" t="n">
-        <v>116.7975906726565</v>
+        <v>116.8909275060781</v>
       </c>
       <c r="J134" t="n">
-        <v>0.06106951321507234</v>
+        <v>0.06248419448943771</v>
       </c>
       <c r="K134" t="n">
-        <v>1.156071053066167</v>
+        <v>1.164010466813185</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -5565,22 +5565,22 @@
         <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3334234304783526</v>
+        <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>16.20746395787842</v>
+        <v>14.73369610790178</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I135" t="n">
-        <v>108.8503562615069</v>
+        <v>108.9439042816867</v>
       </c>
       <c r="J135" t="n">
-        <v>0.07402504767523412</v>
+        <v>0.07228963411735068</v>
       </c>
       <c r="K135" t="n">
-        <v>1.336886889247104</v>
+        <v>1.300766051543611</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>97</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>0.1197305102757296</v>
       </c>
       <c r="G136" t="n">
-        <v>25.06320970486422</v>
+        <v>19.97189151615194</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I136" t="n">
-        <v>108.0650131451876</v>
+        <v>108.1471860069701</v>
       </c>
       <c r="J136" t="n">
-        <v>0.03981243965363022</v>
+        <v>0.04613933539271293</v>
       </c>
       <c r="K136" t="n">
-        <v>0.8593935564649311</v>
+        <v>0.9360501868124834</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -5641,22 +5641,22 @@
         <v>496</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2007721468298446</v>
+        <v>0.1267922607553682</v>
       </c>
       <c r="G137" t="n">
-        <v>14.31447256538772</v>
+        <v>14.01482586396705</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I137" t="n">
-        <v>35.20358886866349</v>
+        <v>35.2002921968334</v>
       </c>
       <c r="J137" t="n">
-        <v>0.06322087175549217</v>
+        <v>0.05233815901992576</v>
       </c>
       <c r="K137" t="n">
-        <v>1.186096807280105</v>
+        <v>1.022504622508265</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -5685,16 +5685,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I138" t="n">
-        <v>110.2434676749111</v>
+        <v>110.3267621811903</v>
       </c>
       <c r="J138" t="n">
-        <v>0.03889020661070718</v>
+        <v>0.0404202175871902</v>
       </c>
       <c r="K138" t="n">
-        <v>0.8465222743636338</v>
+        <v>0.8562861650739781</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -5717,22 +5717,22 @@
         <v>498</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2778086763070295</v>
+        <v>0.2946865611692421</v>
       </c>
       <c r="G139" t="n">
-        <v>8.215741748407643</v>
+        <v>8.254140776448388</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I139" t="n">
-        <v>72.31849272078884</v>
+        <v>72.24811473681838</v>
       </c>
       <c r="J139" t="n">
-        <v>0.0819757304222492</v>
+        <v>0.08231832410929341</v>
       </c>
       <c r="K139" t="n">
-        <v>1.447851770976339</v>
+        <v>1.440635289025236</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -5755,22 +5755,22 @@
         <v>631</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2778086763070762</v>
+        <v>0.3139390545025098</v>
       </c>
       <c r="G140" t="n">
-        <v>5.657382799133461</v>
+        <v>5.713986327763283</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I140" t="n">
-        <v>23.25092832022016</v>
+        <v>23.11979381019518</v>
       </c>
       <c r="J140" t="n">
-        <v>0.05073888684171757</v>
+        <v>0.05245354887986443</v>
       </c>
       <c r="K140" t="n">
-        <v>1.011890135504264</v>
+        <v>1.024113954508327</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>240</v>
       </c>
       <c r="F141" t="n">
-        <v>0.5556173526140057</v>
+        <v>0.6476760673969228</v>
       </c>
       <c r="G141" t="n">
-        <v>23.10576289373354</v>
+        <v>23.65271938864671</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I141" t="n">
-        <v>21.79538453295892</v>
+        <v>21.80521251427836</v>
       </c>
       <c r="J141" t="n">
-        <v>0.02178402797986163</v>
+        <v>0.02340482010283678</v>
       </c>
       <c r="K141" t="n">
-        <v>0.607777357856485</v>
+        <v>0.6189739464795889</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -5837,16 +5837,16 @@
         <v>13.28753103477091</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I142" t="n">
-        <v>19.66145414838973</v>
+        <v>19.52892865743299</v>
       </c>
       <c r="J142" t="n">
-        <v>0.04145905219763923</v>
+        <v>0.04334635651928458</v>
       </c>
       <c r="K142" t="n">
-        <v>0.8823747483969613</v>
+        <v>0.8970967616250891</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -5869,22 +5869,22 @@
         <v>480</v>
       </c>
       <c r="F143" t="n">
-        <v>0.07152391546162952</v>
+        <v>0.02350614742420792</v>
       </c>
       <c r="G143" t="n">
-        <v>5.874592031157748</v>
+        <v>5.791744270780583</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I143" t="n">
-        <v>169.1573788188489</v>
+        <v>169.2329116352616</v>
       </c>
       <c r="J143" t="n">
-        <v>0.02534542826637703</v>
+        <v>0.02700584867101539</v>
       </c>
       <c r="K143" t="n">
-        <v>0.6574825686111225</v>
+        <v>0.6691971680953088</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -5907,22 +5907,22 @@
         <v>226</v>
       </c>
       <c r="F144" t="n">
-        <v>0.5558928409344037</v>
+        <v>0.6778443849467041</v>
       </c>
       <c r="G144" t="n">
-        <v>25.95668219760744</v>
+        <v>26.77058638563806</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I144" t="n">
-        <v>108.6292336416902</v>
+        <v>108.718278459124</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1239962702550718</v>
+        <v>0.1266286666338256</v>
       </c>
       <c r="K144" t="n">
-        <v>2.034317660902374</v>
+        <v>2.058627651580593</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>7.001992287913491</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I145" t="n">
-        <v>35.26856468239285</v>
+        <v>35.23144746678061</v>
       </c>
       <c r="J145" t="n">
-        <v>0.07510067823845167</v>
+        <v>0.075897605124521</v>
       </c>
       <c r="K145" t="n">
-        <v>1.351899086567717</v>
+        <v>1.351086098731645</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -5989,16 +5989,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I146" t="n">
-        <v>91.57310119026025</v>
+        <v>91.45836915575082</v>
       </c>
       <c r="J146" t="n">
-        <v>0.01379230287753385</v>
+        <v>0.01467643040581456</v>
       </c>
       <c r="K146" t="n">
-        <v>0.4962396624145066</v>
+        <v>0.4972398802809313</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -6021,22 +6021,22 @@
         <v>143</v>
       </c>
       <c r="F147" t="n">
-        <v>0.83342602892105</v>
+        <v>0.6296819076437551</v>
       </c>
       <c r="G147" t="n">
-        <v>26.55294650695628</v>
+        <v>25.25457377096612</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I147" t="n">
-        <v>79.80545941607964</v>
+        <v>79.69503906537861</v>
       </c>
       <c r="J147" t="n">
-        <v>0.06254764110937286</v>
+        <v>0.06267555107959037</v>
       </c>
       <c r="K147" t="n">
-        <v>1.176700764021911</v>
+        <v>1.166679299968187</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -6059,22 +6059,22 @@
         <v>93</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00641757330367245</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>18.08081441357613</v>
+        <v>18.04607081887911</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I148" t="n">
-        <v>22.39341445150479</v>
+        <v>22.28137270291327</v>
       </c>
       <c r="J148" t="n">
-        <v>0.03086263098422552</v>
+        <v>0.03052605034356669</v>
       </c>
       <c r="K148" t="n">
-        <v>0.7344842257697</v>
+        <v>0.7182931042661218</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -6097,22 +6097,22 @@
         <v>499</v>
       </c>
       <c r="F149" t="n">
-        <v>0.5556173526140171</v>
+        <v>0.6476760673969441</v>
       </c>
       <c r="G149" t="n">
-        <v>21.33010024415377</v>
+        <v>21.8350234929271</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I149" t="n">
-        <v>119.641772479702</v>
+        <v>119.7283838297617</v>
       </c>
       <c r="J149" t="n">
-        <v>0.0264751840630297</v>
+        <v>0.02678463717800377</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6732501727713497</v>
+        <v>0.6661119512948528</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>578</v>
       </c>
       <c r="F150" t="n">
-        <v>0.04269187986652515</v>
+        <v>0.01385228580827768</v>
       </c>
       <c r="G150" t="n">
-        <v>15.97728213662523</v>
+        <v>15.84079668350338</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I150" t="n">
-        <v>150.0702595585187</v>
+        <v>150.0111610382202</v>
       </c>
       <c r="J150" t="n">
-        <v>0.03767065476728669</v>
+        <v>0.04042891963680239</v>
       </c>
       <c r="K150" t="n">
-        <v>0.8295014183725391</v>
+        <v>0.8564075317773823</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -6173,22 +6173,22 @@
         <v>421</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4543270300333869</v>
+        <v>0.6396311827169744</v>
       </c>
       <c r="G151" t="n">
-        <v>24.46829596178025</v>
+        <v>25.66536127805342</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I151" t="n">
-        <v>28.43038920641624</v>
+        <v>28.30061886166619</v>
       </c>
       <c r="J151" t="n">
-        <v>0.1649995224296121</v>
+        <v>0.1653921775178588</v>
       </c>
       <c r="K151" t="n">
-        <v>2.60658562490459</v>
+        <v>2.599258852048094</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -6211,22 +6211,22 @@
         <v>108</v>
       </c>
       <c r="F152" t="n">
-        <v>0.042691879866529</v>
+        <v>0.01385228580827891</v>
       </c>
       <c r="G152" t="n">
-        <v>17.05591372254659</v>
+        <v>16.91021409147524</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I152" t="n">
-        <v>28.54263066443623</v>
+        <v>28.48204198635943</v>
       </c>
       <c r="J152" t="n">
-        <v>0.02952621615574516</v>
+        <v>0.03258097936946355</v>
       </c>
       <c r="K152" t="n">
-        <v>0.7158323542132361</v>
+        <v>0.7469530145995725</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -6249,22 +6249,22 @@
         <v>79</v>
       </c>
       <c r="F153" t="n">
-        <v>0.5556173526140196</v>
+        <v>0.06171934965394685</v>
       </c>
       <c r="G153" t="n">
-        <v>16.63488029112043</v>
+        <v>14.52224507953177</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I153" t="n">
-        <v>37.86722477299343</v>
+        <v>37.73680519254422</v>
       </c>
       <c r="J153" t="n">
-        <v>0.0139128402633241</v>
+        <v>0.01435193049962217</v>
       </c>
       <c r="K153" t="n">
-        <v>0.4979219602980672</v>
+        <v>0.4927141092701161</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -6293,16 +6293,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I154" t="n">
-        <v>34.11655722819767</v>
+        <v>33.98782998313704</v>
       </c>
       <c r="J154" t="n">
-        <v>0.079838980585012</v>
+        <v>0.07488569298269221</v>
       </c>
       <c r="K154" t="n">
-        <v>1.418029905292791</v>
+        <v>1.336973051086369</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -6325,22 +6325,22 @@
         <v>398</v>
       </c>
       <c r="F155" t="n">
-        <v>0.3331479421579995</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>18.73517311171549</v>
+        <v>17.03283675727564</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I155" t="n">
-        <v>70.23578479127897</v>
+        <v>70.17771880285164</v>
       </c>
       <c r="J155" t="n">
-        <v>0.02978851144110627</v>
+        <v>0.0307834123904557</v>
       </c>
       <c r="K155" t="n">
-        <v>0.7194931172249609</v>
+        <v>0.7218825095906454</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -6363,22 +6363,22 @@
         <v>369</v>
       </c>
       <c r="F156" t="n">
-        <v>0.722191323693021</v>
+        <v>0.6278781090048795</v>
       </c>
       <c r="G156" t="n">
-        <v>27.47821200038494</v>
+        <v>26.83919270527387</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I156" t="n">
-        <v>117.4232945545316</v>
+        <v>117.5154493780703</v>
       </c>
       <c r="J156" t="n">
-        <v>0.07113829149279545</v>
+        <v>0.07128179378814092</v>
       </c>
       <c r="K156" t="n">
-        <v>1.29659744888606</v>
+        <v>1.286709793102772</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -6401,22 +6401,22 @@
         <v>82</v>
       </c>
       <c r="F157" t="n">
-        <v>0.2778086763070295</v>
+        <v>0.3406631557986861</v>
       </c>
       <c r="G157" t="n">
-        <v>11.25061469279957</v>
+        <v>11.44643959489128</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I157" t="n">
-        <v>115.5626250666605</v>
+        <v>115.6576366623428</v>
       </c>
       <c r="J157" t="n">
-        <v>0.1018013114012729</v>
+        <v>0.1001957808388589</v>
       </c>
       <c r="K157" t="n">
-        <v>1.724550429261587</v>
+        <v>1.6899705703914</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -6439,22 +6439,22 @@
         <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>0.6586322580645454</v>
+        <v>0.9998434082878648</v>
       </c>
       <c r="G158" t="n">
-        <v>21.80053670835273</v>
+        <v>23.6639260676628</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I158" t="n">
-        <v>105.7580302415108</v>
+        <v>105.8399463635183</v>
       </c>
       <c r="J158" t="n">
-        <v>0.1505325181426602</v>
+        <v>0.1539676875614531</v>
       </c>
       <c r="K158" t="n">
-        <v>2.404674736147188</v>
+        <v>2.439922517980257</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         <v>4.760796887076785</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I159" t="n">
-        <v>39.36683702149551</v>
+        <v>39.24078459784157</v>
       </c>
       <c r="J159" t="n">
-        <v>0.1270153590555533</v>
+        <v>0.1328103360400428</v>
       </c>
       <c r="K159" t="n">
-        <v>2.076454021053489</v>
+        <v>2.144842838898752</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>539</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0.6319080934242277</v>
       </c>
       <c r="G160" t="n">
-        <v>22.19287898020444</v>
+        <v>20.30772071799779</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I160" t="n">
-        <v>53.29028302362429</v>
+        <v>53.23041119366396</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03896900916175289</v>
+        <v>0.03914755830675019</v>
       </c>
       <c r="K160" t="n">
-        <v>0.8476220938426631</v>
+        <v>0.8385365005343353</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
@@ -6553,22 +6553,22 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>0.5556714109010127</v>
+        <v>0.6291277812788482</v>
       </c>
       <c r="G161" t="n">
-        <v>23.58118283589688</v>
+        <v>24.02658936385474</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I161" t="n">
-        <v>40.63490871157534</v>
+        <v>40.59177863076635</v>
       </c>
       <c r="J161" t="n">
-        <v>0.1066671524747809</v>
+        <v>0.1015303897652495</v>
       </c>
       <c r="K161" t="n">
-        <v>1.7924612611254</v>
+        <v>1.708584241072256</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
@@ -6597,16 +6597,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I162" t="n">
-        <v>85.51667174268432</v>
+        <v>85.4045747268129</v>
       </c>
       <c r="J162" t="n">
-        <v>0.04617426589159087</v>
+        <v>0.04813288695773268</v>
       </c>
       <c r="K162" t="n">
-        <v>0.9481833269210945</v>
+        <v>0.9638540712184863</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
@@ -6629,22 +6629,22 @@
         <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>0.1020448498331738</v>
+        <v>0.2507741396326219</v>
       </c>
       <c r="G163" t="n">
-        <v>18.07388302774133</v>
+        <v>18.85636333800415</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I163" t="n">
-        <v>93.1045955081715</v>
+        <v>92.98851113494418</v>
       </c>
       <c r="J163" t="n">
-        <v>0.05971453313723352</v>
+        <v>0.06218213898575557</v>
       </c>
       <c r="K163" t="n">
-        <v>1.137160072856411</v>
+        <v>1.159797725865854</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
@@ -6673,16 +6673,16 @@
         <v>11.449738512298</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I164" t="n">
-        <v>16.76063733315944</v>
+        <v>16.6393848220203</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1103454050912997</v>
+        <v>0.1084012725145787</v>
       </c>
       <c r="K164" t="n">
-        <v>1.843797338736533</v>
+        <v>1.804411824908873</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -6711,16 +6711,16 @@
         <v>4.635186296148192</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I165" t="n">
-        <v>30.58499220272013</v>
+        <v>30.54004103806239</v>
       </c>
       <c r="J165" t="n">
-        <v>0.03030417641767487</v>
+        <v>0.0316047531903635</v>
       </c>
       <c r="K165" t="n">
-        <v>0.7266900718711924</v>
+        <v>0.7333376758673924</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
@@ -6749,16 +6749,16 @@
         <v>15.96371209963397</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I166" t="n">
-        <v>113.6462632211306</v>
+        <v>113.7345489340537</v>
       </c>
       <c r="J166" t="n">
-        <v>0.05899170465040631</v>
+        <v>0.05950948632075438</v>
       </c>
       <c r="K166" t="n">
-        <v>1.127071809985978</v>
+        <v>1.122522479486986</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
@@ -6787,16 +6787,16 @@
         <v>9.514139425087274</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I167" t="n">
-        <v>19.97388940409684</v>
+        <v>19.85304556260846</v>
       </c>
       <c r="J167" t="n">
-        <v>0.05488212886523661</v>
+        <v>0.05798342382527882</v>
       </c>
       <c r="K167" t="n">
-        <v>1.069715906666872</v>
+        <v>1.101238623094679</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -6825,16 +6825,16 @@
         <v>19.03856866993945</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I168" t="n">
-        <v>33.06495335771849</v>
+        <v>33.09423862101185</v>
       </c>
       <c r="J168" t="n">
-        <v>0.04869408441945994</v>
+        <v>0.05043714952010661</v>
       </c>
       <c r="K168" t="n">
-        <v>0.9833515475407766</v>
+        <v>0.9959914139637138</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
@@ -6863,16 +6863,16 @@
         <v>7.554245495084205</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I169" t="n">
-        <v>64.84181881373597</v>
+        <v>64.76848615754716</v>
       </c>
       <c r="J169" t="n">
-        <v>0.02474350472205482</v>
+        <v>0.02625820933216533</v>
       </c>
       <c r="K169" t="n">
-        <v>0.6490817334839969</v>
+        <v>0.6587699094682857</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -6901,16 +6901,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I170" t="n">
-        <v>129.3282169229969</v>
+        <v>129.3541074858832</v>
       </c>
       <c r="J170" t="n">
-        <v>0.06106851050349028</v>
+        <v>0.06373145343876083</v>
       </c>
       <c r="K170" t="n">
-        <v>1.156057058573411</v>
+        <v>1.181405875218881</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
@@ -6933,22 +6933,22 @@
         <v>255</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0002754883203560995</v>
+        <v>0.0001045778075126898</v>
       </c>
       <c r="G171" t="n">
-        <v>10.88073240491899</v>
+        <v>10.88017456155615</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I171" t="n">
-        <v>171.6568072679967</v>
+        <v>171.7102852489521</v>
       </c>
       <c r="J171" t="n">
-        <v>0.05974131441074392</v>
+        <v>0.05835494374298656</v>
       </c>
       <c r="K171" t="n">
-        <v>1.137533849668063</v>
+        <v>1.106420177977796</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>2.82842712474619</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I172" t="n">
-        <v>35.43481575162259</v>
+        <v>35.39393973639758</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2472972196780266</v>
+        <v>0.2458711871050682</v>
       </c>
       <c r="K172" t="n">
-        <v>3.755185629751618</v>
+        <v>3.721692361637394</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>686</v>
       </c>
       <c r="F173" t="n">
-        <v>0.5558928409344058</v>
+        <v>0.9418171635073348</v>
       </c>
       <c r="G173" t="n">
-        <v>18.67003114897264</v>
+        <v>20.52264110291529</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I173" t="n">
-        <v>30.90803994807395</v>
+        <v>30.85615624638522</v>
       </c>
       <c r="J173" t="n">
-        <v>0.02818474505659737</v>
+        <v>0.0279675701881313</v>
       </c>
       <c r="K173" t="n">
-        <v>0.6971099140660667</v>
+        <v>0.6826102116111366</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -7047,22 +7047,22 @@
         <v>591</v>
       </c>
       <c r="F174" t="n">
-        <v>0.5556714109010233</v>
+        <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>21.74666754538881</v>
+        <v>18.63944545848937</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I174" t="n">
-        <v>33.63389105679053</v>
+        <v>33.5074381955181</v>
       </c>
       <c r="J174" t="n">
-        <v>0.03278323028417384</v>
+        <v>0.03735598286563548</v>
       </c>
       <c r="K174" t="n">
-        <v>0.7612893544547841</v>
+        <v>0.8135495589656112</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>105</v>
       </c>
       <c r="F175" t="n">
-        <v>0.2778086763070515</v>
+        <v>0.3139390545024818</v>
       </c>
       <c r="G175" t="n">
-        <v>9.525334176788951</v>
+        <v>9.620637525515331</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I175" t="n">
-        <v>98.45051006898224</v>
+        <v>98.54690623078599</v>
       </c>
       <c r="J175" t="n">
-        <v>0.03546547119666855</v>
+        <v>0.02970125448060148</v>
       </c>
       <c r="K175" t="n">
-        <v>0.7987244471499406</v>
+        <v>0.7067897505356118</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -7129,16 +7129,16 @@
         <v>6.802079020417213</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I176" t="n">
-        <v>32.95291393681884</v>
+        <v>32.82182337785275</v>
       </c>
       <c r="J176" t="n">
-        <v>0.07297371815162612</v>
+        <v>0.07554361784697049</v>
       </c>
       <c r="K176" t="n">
-        <v>1.322213852986236</v>
+        <v>1.346149070004168</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -7161,22 +7161,22 @@
         <v>389</v>
       </c>
       <c r="F177" t="n">
-        <v>0.5935910122358463</v>
+        <v>0.639631182716998</v>
       </c>
       <c r="G177" t="n">
-        <v>20.98216757048645</v>
+        <v>21.2281673624354</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I177" t="n">
-        <v>50.51992698432778</v>
+        <v>50.44579644520729</v>
       </c>
       <c r="J177" t="n">
-        <v>0.05662153162935981</v>
+        <v>0.05853222923202563</v>
       </c>
       <c r="K177" t="n">
-        <v>1.093992139053694</v>
+        <v>1.10889276275092</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I178" t="n">
-        <v>17.67620934095163</v>
+        <v>17.5446063207043</v>
       </c>
       <c r="J178" t="n">
-        <v>0.02635174359775426</v>
+        <v>0.02758108612405689</v>
       </c>
       <c r="K178" t="n">
-        <v>0.6715273576288346</v>
+        <v>0.6772199531243034</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -7237,22 +7237,22 @@
         <v>266</v>
       </c>
       <c r="F179" t="n">
-        <v>0.007143067854404994</v>
+        <v>0.00402998441935881</v>
       </c>
       <c r="G179" t="n">
-        <v>3.3372362880413</v>
+        <v>3.334126224158364</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I179" t="n">
-        <v>23.3890535412473</v>
+        <v>23.32288368628004</v>
       </c>
       <c r="J179" t="n">
-        <v>0.05119377666582605</v>
+        <v>0.05283775195035379</v>
       </c>
       <c r="K179" t="n">
-        <v>1.018238872730759</v>
+        <v>1.029472400182749</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
@@ -7275,22 +7275,22 @@
         <v>137</v>
       </c>
       <c r="F180" t="n">
-        <v>0.5187176481845532</v>
+        <v>0.01385228580827913</v>
       </c>
       <c r="G180" t="n">
-        <v>14.26018522536537</v>
+        <v>12.3911877443092</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I180" t="n">
-        <v>66.8049253058041</v>
+        <v>66.74883950717913</v>
       </c>
       <c r="J180" t="n">
-        <v>0.04421688766968496</v>
+        <v>0.04534542054894106</v>
       </c>
       <c r="K180" t="n">
-        <v>0.9208648877625565</v>
+        <v>0.9249775278796686</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -7313,22 +7313,22 @@
         <v>400</v>
       </c>
       <c r="F181" t="n">
-        <v>0.5556173526140029</v>
+        <v>0.01175307371210619</v>
       </c>
       <c r="G181" t="n">
-        <v>16.67733424760215</v>
+        <v>14.34503252998123</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I181" t="n">
-        <v>33.52331607343476</v>
+        <v>33.48346632930491</v>
       </c>
       <c r="J181" t="n">
-        <v>0.02077855868513771</v>
+        <v>0.02085260795150836</v>
       </c>
       <c r="K181" t="n">
-        <v>0.5937443766746734</v>
+        <v>0.5833784731142295</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>455</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0005509766407120014</v>
+        <v>0.0003110373301569142</v>
       </c>
       <c r="G182" t="n">
-        <v>13.18326792276715</v>
+        <v>13.18231912433201</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I182" t="n">
-        <v>27.11507121833307</v>
+        <v>27.10369785857549</v>
       </c>
       <c r="J182" t="n">
-        <v>0.07205484517922305</v>
+        <v>0.07373146247015004</v>
       </c>
       <c r="K182" t="n">
-        <v>1.309389466206977</v>
+        <v>1.320875101922819</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I183" t="n">
-        <v>105.9410417546677</v>
+        <v>106.0256863426085</v>
       </c>
       <c r="J183" t="n">
-        <v>0.04111230773203017</v>
+        <v>0.04251051030028449</v>
       </c>
       <c r="K183" t="n">
-        <v>0.8775353578891434</v>
+        <v>0.8854392895726705</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -7427,22 +7427,22 @@
         <v>547</v>
       </c>
       <c r="F184" t="n">
-        <v>0.09983314794216577</v>
+        <v>0.04996627594183239</v>
       </c>
       <c r="G184" t="n">
-        <v>10.52803885716594</v>
+        <v>10.37511869760823</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I184" t="n">
-        <v>22.81272033570257</v>
+        <v>22.75643070272934</v>
       </c>
       <c r="J184" t="n">
-        <v>0.06325323914016245</v>
+        <v>0.0650212164408004</v>
       </c>
       <c r="K184" t="n">
-        <v>1.186548547479796</v>
+        <v>1.199394083825611</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -7465,22 +7465,22 @@
         <v>625</v>
       </c>
       <c r="F185" t="n">
-        <v>0.4801446051168408</v>
+        <v>0.2507741396326156</v>
       </c>
       <c r="G185" t="n">
-        <v>8.30786430754514</v>
+        <v>7.808168561520751</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I185" t="n">
-        <v>67.09898453728924</v>
+        <v>67.05604191682495</v>
       </c>
       <c r="J185" t="n">
-        <v>0.00782701330717828</v>
+        <v>0.009617645236873543</v>
       </c>
       <c r="K185" t="n">
-        <v>0.4129842147105146</v>
+        <v>0.4266854584440204</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
@@ -7503,22 +7503,22 @@
         <v>13</v>
       </c>
       <c r="F186" t="n">
-        <v>0.3331479421580295</v>
+        <v>0.4261274853907389</v>
       </c>
       <c r="G186" t="n">
-        <v>13.04294736233235</v>
+        <v>13.37370789185269</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I186" t="n">
-        <v>23.97765559490883</v>
+        <v>23.85324114293519</v>
       </c>
       <c r="J186" t="n">
-        <v>0.0603200262343189</v>
+        <v>0.061385395834559</v>
       </c>
       <c r="K186" t="n">
-        <v>1.145610726975539</v>
+        <v>1.148685620783724</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -7541,22 +7541,22 @@
         <v>331</v>
       </c>
       <c r="F187" t="n">
-        <v>0.01701853615128207</v>
+        <v>0.258834108471334</v>
       </c>
       <c r="G187" t="n">
-        <v>20.80983777183406</v>
+        <v>22.31181219921191</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I187" t="n">
-        <v>104.7392824085638</v>
+        <v>104.8216211106881</v>
       </c>
       <c r="J187" t="n">
-        <v>0.03548192405491247</v>
+        <v>0.03774424748576161</v>
       </c>
       <c r="K187" t="n">
-        <v>0.7989540739036718</v>
+        <v>0.8189646507075801</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -7579,22 +7579,22 @@
         <v>180</v>
       </c>
       <c r="F188" t="n">
-        <v>0.55561735261407</v>
+        <v>0.01979795839205038</v>
       </c>
       <c r="G188" t="n">
-        <v>4.750769519966189</v>
+        <v>4.096208778048068</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I188" t="n">
-        <v>106.9788372880925</v>
+        <v>107.0727832917891</v>
       </c>
       <c r="J188" t="n">
-        <v>0.1197638333317601</v>
+        <v>0.1195107828360214</v>
       </c>
       <c r="K188" t="n">
-        <v>1.975247027905724</v>
+        <v>1.959355166332614</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -7617,22 +7617,22 @@
         <v>414</v>
       </c>
       <c r="F189" t="n">
-        <v>0.2007721468298443</v>
+        <v>0.9453591251098454</v>
       </c>
       <c r="G189" t="n">
-        <v>21.6461999063891</v>
+        <v>26.20675382024651</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I189" t="n">
-        <v>34.42261139509194</v>
+        <v>34.29172451398752</v>
       </c>
       <c r="J189" t="n">
-        <v>0.06133944673773306</v>
+        <v>0.06121111153506963</v>
       </c>
       <c r="K189" t="n">
-        <v>1.159838420268443</v>
+        <v>1.146254893331367</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -7655,22 +7655,22 @@
         <v>667</v>
       </c>
       <c r="F190" t="n">
-        <v>0.5556173526140383</v>
+        <v>0.6278781090048906</v>
       </c>
       <c r="G190" t="n">
-        <v>20.4601752851792</v>
+        <v>20.84034666337098</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I190" t="n">
-        <v>26.31116760003824</v>
+        <v>26.20545316108371</v>
       </c>
       <c r="J190" t="n">
-        <v>0.04940215216676148</v>
+        <v>0.05384131767844651</v>
       </c>
       <c r="K190" t="n">
-        <v>0.9932337999630733</v>
+        <v>1.043469041146204</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
@@ -7693,22 +7693,22 @@
         <v>294</v>
       </c>
       <c r="F191" t="n">
-        <v>0.03922644482804085</v>
+        <v>0.05102630472990546</v>
       </c>
       <c r="G191" t="n">
-        <v>14.75850638909325</v>
+        <v>14.8101432225987</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I191" t="n">
-        <v>103.4217084312932</v>
+        <v>103.5107156379267</v>
       </c>
       <c r="J191" t="n">
-        <v>0.03279136385233469</v>
+        <v>0.03612628935735145</v>
       </c>
       <c r="K191" t="n">
-        <v>0.7614028718038877</v>
+        <v>0.7963991341865047</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
@@ -7737,16 +7737,16 @@
         <v>16.38096837796838</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I192" t="n">
-        <v>103.2319698316377</v>
+        <v>103.3173410944955</v>
       </c>
       <c r="J192" t="n">
-        <v>0.05717329260355495</v>
+        <v>0.05874577597436052</v>
       </c>
       <c r="K192" t="n">
-        <v>1.101692872838771</v>
+        <v>1.111871079962945</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -7769,22 +7769,22 @@
         <v>476</v>
       </c>
       <c r="F193" t="n">
-        <v>0.833426028921044</v>
+        <v>0.3639053304442927</v>
       </c>
       <c r="G193" t="n">
-        <v>16.96633641925868</v>
+        <v>15.05452788087168</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I193" t="n">
-        <v>110.0783718206048</v>
+        <v>110.1728110255309</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03148080661805629</v>
+        <v>0.03251112863765326</v>
       </c>
       <c r="K193" t="n">
-        <v>0.7431118855919561</v>
+        <v>0.7459788127243836</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -7813,16 +7813,16 @@
         <v>16.15292911517908</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I194" t="n">
-        <v>38.07103719493699</v>
+        <v>38.02294659214053</v>
       </c>
       <c r="J194" t="n">
-        <v>0.1140500065249446</v>
+        <v>0.1111592744027997</v>
       </c>
       <c r="K194" t="n">
-        <v>1.895501157517718</v>
+        <v>1.842877429228908</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -7851,16 +7851,16 @@
         <v>4.216584043986316</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I195" t="n">
-        <v>111.0378668078923</v>
+        <v>111.1291459124491</v>
       </c>
       <c r="J195" t="n">
-        <v>0.0339390399010471</v>
+        <v>0.03381794514680692</v>
       </c>
       <c r="K195" t="n">
-        <v>0.7774205826170453</v>
+        <v>0.7642048650612864</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -7889,16 +7889,16 @@
         <v>6.859</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I196" t="n">
-        <v>38.92421756885921</v>
+        <v>38.88389366216378</v>
       </c>
       <c r="J196" t="n">
-        <v>0.1993711390883394</v>
+        <v>0.2008047394176002</v>
       </c>
       <c r="K196" t="n">
-        <v>3.086298185289444</v>
+        <v>3.093154668367785</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -7927,16 +7927,16 @@
         <v>9.010146336214524</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I197" t="n">
-        <v>23.66411155541576</v>
+        <v>23.55720321865559</v>
       </c>
       <c r="J197" t="n">
-        <v>0.04472439015833629</v>
+        <v>0.04506068260733724</v>
       </c>
       <c r="K197" t="n">
-        <v>0.9279479214368191</v>
+        <v>0.9210063134133514</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -7965,16 +7965,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I198" t="n">
-        <v>67.95147626501125</v>
+        <v>67.88862164763613</v>
       </c>
       <c r="J198" t="n">
-        <v>0.02566253616634559</v>
+        <v>0.02689004448824579</v>
       </c>
       <c r="K198" t="n">
-        <v>0.6619083319996351</v>
+        <v>0.6675820575719822</v>
       </c>
       <c r="L198" t="b">
         <v>0</v>
@@ -7997,22 +7997,22 @@
         <v>509</v>
       </c>
       <c r="F199" t="n">
-        <v>0.117131934373189</v>
+        <v>0.03256817361512986</v>
       </c>
       <c r="G199" t="n">
-        <v>23.11578763067524</v>
+        <v>22.54926752881262</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I199" t="n">
-        <v>33.17756641045589</v>
+        <v>33.16658667969853</v>
       </c>
       <c r="J199" t="n">
-        <v>0.03340200000519147</v>
+        <v>0.03466483077050447</v>
       </c>
       <c r="K199" t="n">
-        <v>0.7699253057428832</v>
+        <v>0.7760163026982954</v>
       </c>
       <c r="L199" t="b">
         <v>0</v>
@@ -8035,22 +8035,22 @@
         <v>84</v>
       </c>
       <c r="F200" t="n">
-        <v>0.4997219132369523</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>25.00187157821521</v>
+        <v>28.26503573162433</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I200" t="n">
-        <v>62.11474727984361</v>
+        <v>62.08116485610849</v>
       </c>
       <c r="J200" t="n">
-        <v>0.02937089870696735</v>
+        <v>0.03037161416959136</v>
       </c>
       <c r="K200" t="n">
-        <v>0.7136646432275868</v>
+        <v>0.716139196835454</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8079,16 +8079,16 @@
         <v>12.167</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I201" t="n">
-        <v>26.93785812927021</v>
+        <v>26.93849745717281</v>
       </c>
       <c r="J201" t="n">
-        <v>0.01784268746916433</v>
+        <v>0.02067157420898268</v>
       </c>
       <c r="K201" t="n">
-        <v>0.5527694550712352</v>
+        <v>0.5808536117867924</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -8117,16 +8117,16 @@
         <v>5.379074548656115</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I202" t="n">
-        <v>69.61682426067625</v>
+        <v>69.5716022649659</v>
       </c>
       <c r="J202" t="n">
-        <v>0.03740158147013197</v>
+        <v>0.03882676792092587</v>
       </c>
       <c r="K202" t="n">
-        <v>0.8257460570349888</v>
+        <v>0.8340624658705125</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -8149,22 +8149,22 @@
         <v>407</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>0.02350614742421015</v>
       </c>
       <c r="G203" t="n">
-        <v>8.546030189509043</v>
+        <v>8.606295463166949</v>
       </c>
       <c r="H203" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I203" t="n">
-        <v>111.3287131069042</v>
+        <v>111.4243159831747</v>
       </c>
       <c r="J203" t="n">
-        <v>0.06231809127159339</v>
+        <v>0.06124219274494565</v>
       </c>
       <c r="K203" t="n">
-        <v>1.173497017700914</v>
+        <v>1.146688380170511</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -8187,22 +8187,22 @@
         <v>632</v>
       </c>
       <c r="F204" t="n">
-        <v>0.7337446051167654</v>
+        <v>0.8103131163322702</v>
       </c>
       <c r="G204" t="n">
-        <v>26.32426799261978</v>
+        <v>26.81985967774027</v>
       </c>
       <c r="H204" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I204" t="n">
-        <v>31.41716037663829</v>
+        <v>31.28657062784671</v>
       </c>
       <c r="J204" t="n">
-        <v>0.09868834219656038</v>
+        <v>0.1002930052377353</v>
       </c>
       <c r="K204" t="n">
-        <v>1.681103813339531</v>
+        <v>1.691326550339567</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>475</v>
       </c>
       <c r="F205" t="n">
-        <v>0.2778086763070619</v>
+        <v>0.3139390545024937</v>
       </c>
       <c r="G205" t="n">
-        <v>7.307488599116229</v>
+        <v>7.380601848620135</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I205" t="n">
-        <v>37.12971794680954</v>
+        <v>37.09220333840505</v>
       </c>
       <c r="J205" t="n">
-        <v>0.01961906182709817</v>
+        <v>0.02147504814431216</v>
       </c>
       <c r="K205" t="n">
-        <v>0.5775616869847746</v>
+        <v>0.5920595905099542</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -8263,22 +8263,22 @@
         <v>575</v>
       </c>
       <c r="F206" t="n">
-        <v>0.5558928409344395</v>
+        <v>0.03295622304320514</v>
       </c>
       <c r="G206" t="n">
-        <v>23.77347653455513</v>
+        <v>20.57694826454845</v>
       </c>
       <c r="H206" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I206" t="n">
-        <v>181.2708030172869</v>
+        <v>181.3054672777228</v>
       </c>
       <c r="J206" t="n">
-        <v>0.01559833642620549</v>
+        <v>0.01639588954382101</v>
       </c>
       <c r="K206" t="n">
-        <v>0.5214458372178739</v>
+        <v>0.5212210222553066</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>75</v>
       </c>
       <c r="F207" t="n">
-        <v>5.405828698554315e-05</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>4.660294348721861</v>
+        <v>4.660218771688728</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I207" t="n">
-        <v>105.481210047155</v>
+        <v>105.58088276408</v>
       </c>
       <c r="J207" t="n">
-        <v>0.1971180848407858</v>
+        <v>0.2029165830395439</v>
       </c>
       <c r="K207" t="n">
-        <v>3.054853099871691</v>
+        <v>3.122608361454222</v>
       </c>
       <c r="L207" t="b">
         <v>0</v>
@@ -8339,22 +8339,22 @@
         <v>655</v>
       </c>
       <c r="F208" t="n">
-        <v>0.1996662958843493</v>
+        <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>16.36260252681886</v>
+        <v>15.43787550150603</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I208" t="n">
-        <v>86.0413416528815</v>
+        <v>85.92005596352274</v>
       </c>
       <c r="J208" t="n">
-        <v>0.0463312109869226</v>
+        <v>0.05298287696704168</v>
       </c>
       <c r="K208" t="n">
-        <v>0.950373754397025</v>
+        <v>1.03149644574004</v>
       </c>
       <c r="L208" t="b">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>383</v>
       </c>
       <c r="F209" t="n">
-        <v>0.6554505005562139</v>
+        <v>0.2548041240519801</v>
       </c>
       <c r="G209" t="n">
-        <v>26.21829216992821</v>
+        <v>23.5848419270836</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I209" t="n">
-        <v>24.94383705155951</v>
+        <v>24.81129845126135</v>
       </c>
       <c r="J209" t="n">
-        <v>0.01642914510546296</v>
+        <v>0.01444887658671307</v>
       </c>
       <c r="K209" t="n">
-        <v>0.5330411416422691</v>
+        <v>0.4940662076288374</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -8415,22 +8415,22 @@
         <v>360</v>
       </c>
       <c r="F210" t="n">
-        <v>0.1665739710790193</v>
+        <v>0.6278781090049219</v>
       </c>
       <c r="G210" t="n">
-        <v>18.57729417491535</v>
+        <v>21.02586835959482</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I210" t="n">
-        <v>90.01939748706958</v>
+        <v>89.8979372544534</v>
       </c>
       <c r="J210" t="n">
-        <v>0.01674243744116495</v>
+        <v>0.01599714599507289</v>
       </c>
       <c r="K210" t="n">
-        <v>0.5374136525427826</v>
+        <v>0.5156597818381708</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8453,22 +8453,22 @@
         <v>360</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0002754883203560995</v>
+        <v>0.0001555186650784571</v>
       </c>
       <c r="G211" t="n">
-        <v>12.37560856781722</v>
+        <v>12.37516319537757</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I211" t="n">
-        <v>110.2868725384193</v>
+        <v>110.3840882134172</v>
       </c>
       <c r="J211" t="n">
-        <v>0.02524913644138504</v>
+        <v>0.03695308767345355</v>
       </c>
       <c r="K211" t="n">
-        <v>0.656138657489057</v>
+        <v>0.8079304159508431</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -8497,16 +8497,16 @@
         <v>9.898089765202174</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I212" t="n">
-        <v>74.11080417368561</v>
+        <v>73.99207660134769</v>
       </c>
       <c r="J212" t="n">
-        <v>0.06497036510656556</v>
+        <v>0.07034398676498908</v>
       </c>
       <c r="K212" t="n">
-        <v>1.210513870438715</v>
+        <v>1.273630282883736</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -8529,22 +8529,22 @@
         <v>696</v>
       </c>
       <c r="F213" t="n">
-        <v>0.3363296996663423</v>
+        <v>0.6499683567254033</v>
       </c>
       <c r="G213" t="n">
-        <v>17.94997719173572</v>
+        <v>19.48412533831767</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I213" t="n">
-        <v>191.0055747854792</v>
+        <v>191.0867244384225</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1139289351744599</v>
+        <v>0.1222151402157486</v>
       </c>
       <c r="K213" t="n">
-        <v>1.893811407276787</v>
+        <v>1.997072595516699</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -8573,16 +8573,16 @@
         <v>8.792540929674423</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I214" t="n">
-        <v>101.0122326041219</v>
+        <v>101.1072021157126</v>
       </c>
       <c r="J214" t="n">
-        <v>0.5397454582804133</v>
+        <v>0.5456645327594656</v>
       </c>
       <c r="K214" t="n">
-        <v>7.836782800839874</v>
+        <v>7.902883194381735</v>
       </c>
       <c r="L214" t="b">
         <v>0</v>
@@ -8611,16 +8611,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I215" t="n">
-        <v>37.30536335882159</v>
+        <v>37.28176811469245</v>
       </c>
       <c r="J215" t="n">
-        <v>0.1751753422787582</v>
+        <v>0.1781247927038548</v>
       </c>
       <c r="K215" t="n">
-        <v>2.748605962275291</v>
+        <v>2.776839491059073</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -8649,16 +8649,16 @@
         <v>6.352448897866083</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I216" t="n">
-        <v>24.97203110583696</v>
+        <v>24.84040642367567</v>
       </c>
       <c r="J216" t="n">
-        <v>0.04353619070234816</v>
+        <v>0.04395802794727404</v>
       </c>
       <c r="K216" t="n">
-        <v>0.9113646396860835</v>
+        <v>0.9056276880263358</v>
       </c>
       <c r="L216" t="b">
         <v>0</v>
@@ -8681,22 +8681,22 @@
         <v>6</v>
       </c>
       <c r="F217" t="n">
-        <v>0.5556173526140604</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>13.91423856750369</v>
+        <v>11.92630068378288</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I217" t="n">
-        <v>64.30385816459258</v>
+        <v>64.27029847118371</v>
       </c>
       <c r="J217" t="n">
-        <v>0.0314030777375273</v>
+        <v>0.03048758135818962</v>
       </c>
       <c r="K217" t="n">
-        <v>0.7420270509545681</v>
+        <v>0.7177565807864146</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -8719,22 +8719,22 @@
         <v>631</v>
       </c>
       <c r="F218" t="n">
-        <v>0.2778086763070781</v>
+        <v>0.313939054502512</v>
       </c>
       <c r="G218" t="n">
-        <v>3.656281284760917</v>
+        <v>3.692863292683794</v>
       </c>
       <c r="H218" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I218" t="n">
-        <v>24.42688634969953</v>
+        <v>24.29576064748958</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1181835338352273</v>
+        <v>0.1128015569812101</v>
       </c>
       <c r="K218" t="n">
-        <v>1.953191343845715</v>
+        <v>1.865782196666745</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -8763,16 +8763,16 @@
         <v>7.378342564560147</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I219" t="n">
-        <v>121.9593386067266</v>
+        <v>122.0469822278787</v>
       </c>
       <c r="J219" t="n">
-        <v>0.03283624089504952</v>
+        <v>0.03261830913122976</v>
       </c>
       <c r="K219" t="n">
-        <v>0.762029204899505</v>
+        <v>0.7474736494300245</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>9.32407137467319</v>
       </c>
       <c r="H220" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I220" t="n">
-        <v>29.43788003005546</v>
+        <v>29.30746055915692</v>
       </c>
       <c r="J220" t="n">
-        <v>0.08193670001507039</v>
+        <v>0.0795331335146538</v>
       </c>
       <c r="K220" t="n">
-        <v>1.447307037315816</v>
+        <v>1.401790486261743</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -8833,22 +8833,22 @@
         <v>605</v>
       </c>
       <c r="F221" t="n">
-        <v>0.1999417842047052</v>
+        <v>0.639631182716955</v>
       </c>
       <c r="G221" t="n">
-        <v>22.95779840085103</v>
+        <v>25.81472299184334</v>
       </c>
       <c r="H221" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I221" t="n">
-        <v>11.9146007619889</v>
+        <v>11.79778697778781</v>
       </c>
       <c r="J221" t="n">
-        <v>0.05441000425790059</v>
+        <v>0.05363428607755281</v>
       </c>
       <c r="K221" t="n">
-        <v>1.063126629634761</v>
+        <v>1.040581590025982</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -8871,22 +8871,22 @@
         <v>486</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0001081165739711851</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>11.34883163949307</v>
+        <v>11.34846355239334</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I222" t="n">
-        <v>22.78802392263332</v>
+        <v>22.6558952188293</v>
       </c>
       <c r="J222" t="n">
-        <v>0.09824454349200142</v>
+        <v>0.1188102279007542</v>
       </c>
       <c r="K222" t="n">
-        <v>1.674909870966285</v>
+        <v>1.949584589648268</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -8915,16 +8915,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H223" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I223" t="n">
-        <v>66.00141395688607</v>
+        <v>65.95165086438112</v>
       </c>
       <c r="J223" t="n">
-        <v>0.02798361671404329</v>
+        <v>0.03067398540758564</v>
       </c>
       <c r="K223" t="n">
-        <v>0.6943028365541022</v>
+        <v>0.7203563413008441</v>
       </c>
       <c r="L223" t="b">
         <v>0</v>
@@ -8953,16 +8953,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H224" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I224" t="n">
-        <v>60.33757171448367</v>
+        <v>60.29715011553289</v>
       </c>
       <c r="J224" t="n">
-        <v>0.06073171382208507</v>
+        <v>0.05865589506570817</v>
       </c>
       <c r="K224" t="n">
-        <v>1.151356505789694</v>
+        <v>1.110617519012565</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -8985,22 +8985,22 @@
         <v>414</v>
       </c>
       <c r="F225" t="n">
-        <v>0.3331479421580289</v>
+        <v>0.6278781090048703</v>
       </c>
       <c r="G225" t="n">
-        <v>12.93023865500321</v>
+        <v>13.96963613444291</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I225" t="n">
-        <v>20.40406077565711</v>
+        <v>20.28174127581054</v>
       </c>
       <c r="J225" t="n">
-        <v>0.04354172170674789</v>
+        <v>0.04439631392639277</v>
       </c>
       <c r="K225" t="n">
-        <v>0.9114418339684601</v>
+        <v>0.9117404231639734</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -9029,16 +9029,16 @@
         <v>5.617338871743453</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I226" t="n">
-        <v>33.25141161443479</v>
+        <v>33.23493958389385</v>
       </c>
       <c r="J226" t="n">
-        <v>0.06706632721919009</v>
+        <v>0.07119779833604113</v>
       </c>
       <c r="K226" t="n">
-        <v>1.239766476200611</v>
+        <v>1.285538316085678</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -9061,22 +9061,22 @@
         <v>258</v>
       </c>
       <c r="F227" t="n">
-        <v>0.4997759715239306</v>
+        <v>0.3761612094489241</v>
       </c>
       <c r="G227" t="n">
-        <v>21.16029049969373</v>
+        <v>20.47788776407567</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I227" t="n">
-        <v>198.8673960174862</v>
+        <v>198.8710706229827</v>
       </c>
       <c r="J227" t="n">
-        <v>0.05307748311759283</v>
+        <v>0.05308430908265839</v>
       </c>
       <c r="K227" t="n">
-        <v>1.044529100914166</v>
+        <v>1.032911110335202</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -9099,22 +9099,22 @@
         <v>590</v>
       </c>
       <c r="F228" t="n">
-        <v>0.6662958843159219</v>
+        <v>0.3959591678409639</v>
       </c>
       <c r="G228" t="n">
-        <v>26.39036957041754</v>
+        <v>24.60663276182896</v>
       </c>
       <c r="H228" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I228" t="n">
-        <v>36.51662592740215</v>
+        <v>36.39568664884631</v>
       </c>
       <c r="J228" t="n">
-        <v>0.2632768631525626</v>
+        <v>0.2674865486415208</v>
       </c>
       <c r="K228" t="n">
-        <v>3.978207891442658</v>
+        <v>4.023159865211867</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -9143,16 +9143,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H229" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I229" t="n">
-        <v>100.2741370005823</v>
+        <v>100.3648704906266</v>
       </c>
       <c r="J229" t="n">
-        <v>0.04542630169175492</v>
+        <v>0.04375794272649185</v>
       </c>
       <c r="K229" t="n">
-        <v>0.9377442537479562</v>
+        <v>0.9028371174448707</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -9175,22 +9175,22 @@
         <v>276</v>
       </c>
       <c r="F230" t="n">
-        <v>0.5556173526140196</v>
+        <v>0.653276439834432</v>
       </c>
       <c r="G230" t="n">
-        <v>18.80116275151541</v>
+        <v>19.27329637862211</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I230" t="n">
-        <v>32.38602204619789</v>
+        <v>32.26512182901818</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1188917968188966</v>
+        <v>0.1140934236841186</v>
       </c>
       <c r="K230" t="n">
-        <v>1.963076321113304</v>
+        <v>1.883799745400317</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -9213,22 +9213,22 @@
         <v>583</v>
       </c>
       <c r="F231" t="n">
-        <v>0.003181757508343503</v>
+        <v>0.00229228932849165</v>
       </c>
       <c r="G231" t="n">
-        <v>10.49343358957645</v>
+        <v>10.49063618719067</v>
       </c>
       <c r="H231" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I231" t="n">
-        <v>76.09623671352958</v>
+        <v>76.0437467567826</v>
       </c>
       <c r="J231" t="n">
-        <v>0.05165975595384268</v>
+        <v>0.05424449116888616</v>
       </c>
       <c r="K231" t="n">
-        <v>1.0247423817033</v>
+        <v>1.049092065561747</v>
       </c>
       <c r="L231" t="b">
         <v>0</v>
@@ -9251,22 +9251,22 @@
         <v>391</v>
       </c>
       <c r="F232" t="n">
-        <v>0.1195773081201534</v>
+        <v>0.6278781090048781</v>
       </c>
       <c r="G232" t="n">
-        <v>14.73206905492897</v>
+        <v>16.90076766224575</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I232" t="n">
-        <v>123.9541054365993</v>
+        <v>123.8672578517167</v>
       </c>
       <c r="J232" t="n">
-        <v>0.04406096044784404</v>
+        <v>0.05039324601911643</v>
       </c>
       <c r="K232" t="n">
-        <v>0.9186886663888082</v>
+        <v>0.9953790957834526</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -9289,22 +9289,22 @@
         <v>306</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>0.2507741396326156</v>
       </c>
       <c r="G233" t="n">
-        <v>8.241196029703456</v>
+        <v>8.86119968287124</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I233" t="n">
-        <v>31.78090825247116</v>
+        <v>31.77000166377546</v>
       </c>
       <c r="J233" t="n">
-        <v>0.02853181478281312</v>
+        <v>0.02534186478151545</v>
       </c>
       <c r="K233" t="n">
-        <v>0.7019538441217325</v>
+        <v>0.6459897344232086</v>
       </c>
       <c r="L233" t="b">
         <v>0</v>
@@ -9327,22 +9327,22 @@
         <v>458</v>
       </c>
       <c r="F234" t="n">
-        <v>0.1997203541713349</v>
+        <v>0.09993255188367382</v>
       </c>
       <c r="G234" t="n">
-        <v>14.19678965212672</v>
+        <v>13.79581458516517</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I234" t="n">
-        <v>35.08080972635029</v>
+        <v>35.00687314914575</v>
       </c>
       <c r="J234" t="n">
-        <v>0.02092950794196375</v>
+        <v>0.02340984556518048</v>
       </c>
       <c r="K234" t="n">
-        <v>0.5958511223421579</v>
+        <v>0.6190440361509788</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -9365,22 +9365,22 @@
         <v>581</v>
       </c>
       <c r="F235" t="n">
-        <v>0.5556173526140203</v>
+        <v>0.1197305102757296</v>
       </c>
       <c r="G235" t="n">
-        <v>25.3176321940087</v>
+        <v>22.47994572181821</v>
       </c>
       <c r="H235" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I235" t="n">
-        <v>79.05578019046209</v>
+        <v>78.94866000140857</v>
       </c>
       <c r="J235" t="n">
-        <v>0.05105181428686449</v>
+        <v>0.05324936962908895</v>
       </c>
       <c r="K235" t="n">
-        <v>1.016257553755683</v>
+        <v>1.0352131949331</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -9403,22 +9403,22 @@
         <v>162</v>
       </c>
       <c r="F236" t="n">
-        <v>0.5556173526140203</v>
+        <v>0.008059968838718401</v>
       </c>
       <c r="G236" t="n">
-        <v>20.32392578591707</v>
+        <v>17.46235295302083</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I236" t="n">
-        <v>70.36177885759051</v>
+        <v>70.29894713558546</v>
       </c>
       <c r="J236" t="n">
-        <v>0.06229244892446249</v>
+        <v>0.05702220351178149</v>
       </c>
       <c r="K236" t="n">
-        <v>1.17313913648402</v>
+        <v>1.087832569820649</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9441,22 +9441,22 @@
         <v>226</v>
       </c>
       <c r="F237" t="n">
-        <v>0.006363515016686116</v>
+        <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>12.8176760438219</v>
+        <v>12.79325302649799</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I237" t="n">
-        <v>40.47910280004336</v>
+        <v>40.35270886623581</v>
       </c>
       <c r="J237" t="n">
-        <v>0.06282481171655484</v>
+        <v>0.05859899089560778</v>
       </c>
       <c r="K237" t="n">
-        <v>1.180569136666552</v>
+        <v>1.109823881669317</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -9485,16 +9485,16 @@
         <v>7.554245495084205</v>
       </c>
       <c r="H238" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I238" t="n">
-        <v>169.1737858527792</v>
+        <v>169.0978094301229</v>
       </c>
       <c r="J238" t="n">
-        <v>0.039225805617476</v>
+        <v>0.03898384189913912</v>
       </c>
       <c r="K238" t="n">
-        <v>0.8512061116238405</v>
+        <v>0.8362531625196803</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -9517,22 +9517,22 @@
         <v>390</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>0.0003110373301569142</v>
       </c>
       <c r="G239" t="n">
-        <v>10.91308792230687</v>
+        <v>10.9141062356262</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I239" t="n">
-        <v>92.44367048249364</v>
+        <v>92.33708722750951</v>
       </c>
       <c r="J239" t="n">
-        <v>0.1997645963243154</v>
+        <v>0.1959209510653338</v>
       </c>
       <c r="K239" t="n">
-        <v>3.091789529497835</v>
+        <v>3.02504091139634</v>
       </c>
       <c r="L239" t="b">
         <v>0</v>
@@ -9561,16 +9561,16 @@
         <v>5.222154823442138</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I240" t="n">
-        <v>31.15143234031292</v>
+        <v>31.15906593883903</v>
       </c>
       <c r="J240" t="n">
-        <v>0.06176188027743777</v>
+        <v>0.05839412138475507</v>
       </c>
       <c r="K240" t="n">
-        <v>1.165734176552945</v>
+        <v>1.106966585024469</v>
       </c>
       <c r="L240" t="b">
         <v>0</v>
@@ -9593,22 +9593,22 @@
         <v>283</v>
       </c>
       <c r="F241" t="n">
-        <v>0</v>
+        <v>0.6301703983333869</v>
       </c>
       <c r="G241" t="n">
-        <v>10.3850939331332</v>
+        <v>12.34840756730486</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I241" t="n">
-        <v>30.05871263764906</v>
+        <v>29.94573152509017</v>
       </c>
       <c r="J241" t="n">
-        <v>0.07008308875266525</v>
+        <v>0.06971061493582241</v>
       </c>
       <c r="K241" t="n">
-        <v>1.281870355504945</v>
+        <v>1.264796702938693</v>
       </c>
       <c r="L241" t="b">
         <v>0</v>
@@ -9637,16 +9637,16 @@
         <v>7.203826552603831</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I242" t="n">
-        <v>30.5470585105876</v>
+        <v>30.43453058724796</v>
       </c>
       <c r="J242" t="n">
-        <v>0.03999431688365183</v>
+        <v>0.04679215944365228</v>
       </c>
       <c r="K242" t="n">
-        <v>0.8619319529725977</v>
+        <v>0.9451550651453378</v>
       </c>
       <c r="L242" t="b">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>384</v>
       </c>
       <c r="F243" t="n">
-        <v>0</v>
+        <v>0.01208995325807721</v>
       </c>
       <c r="G243" t="n">
-        <v>16.7250191031281</v>
+        <v>16.78568051288729</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I243" t="n">
-        <v>84.20265798860038</v>
+        <v>84.09388584663459</v>
       </c>
       <c r="J243" t="n">
-        <v>0.04237529914940637</v>
+        <v>0.04113158676906406</v>
       </c>
       <c r="K243" t="n">
-        <v>0.8951624847301438</v>
+        <v>0.8662075670832698</v>
       </c>
       <c r="L243" t="b">
         <v>0</v>
@@ -9707,22 +9707,22 @@
         <v>10</v>
       </c>
       <c r="F244" t="n">
-        <v>0.3331479421579999</v>
+        <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>18.94782988801123</v>
+        <v>17.22617087457337</v>
       </c>
       <c r="H244" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I244" t="n">
-        <v>108.4902520494882</v>
+        <v>108.5828897238169</v>
       </c>
       <c r="J244" t="n">
-        <v>0.1328642536096019</v>
+        <v>0.131285659744251</v>
       </c>
       <c r="K244" t="n">
-        <v>2.158084984467346</v>
+        <v>2.12357831570878</v>
       </c>
       <c r="L244" t="b">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         <v>11.2138976720853</v>
       </c>
       <c r="H245" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I245" t="n">
-        <v>38.23513054360959</v>
+        <v>38.19582647183234</v>
       </c>
       <c r="J245" t="n">
-        <v>0.1117368094352062</v>
+        <v>0.1093057264597961</v>
       </c>
       <c r="K245" t="n">
-        <v>1.863216679612271</v>
+        <v>1.817026162749253</v>
       </c>
       <c r="L245" t="b">
         <v>0</v>
@@ -9783,22 +9783,22 @@
         <v>338</v>
       </c>
       <c r="F246" t="n">
-        <v>0.3576756395996085</v>
+        <v>0.2705720980246611</v>
       </c>
       <c r="G246" t="n">
-        <v>23.5672107625727</v>
+        <v>23.01105185385238</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I246" t="n">
-        <v>105.9322355649909</v>
+        <v>106.0297378961514</v>
       </c>
       <c r="J246" t="n">
-        <v>0.06210529069666138</v>
+        <v>0.06075002390880217</v>
       </c>
       <c r="K246" t="n">
-        <v>1.170527034948413</v>
+        <v>1.139824145671397</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -9827,16 +9827,16 @@
         <v>6.547900426854397</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I247" t="n">
-        <v>82.22762707931079</v>
+        <v>82.11812651631533</v>
       </c>
       <c r="J247" t="n">
-        <v>0.1610861695687091</v>
+        <v>0.157554862114631</v>
       </c>
       <c r="K247" t="n">
-        <v>2.551968335900335</v>
+        <v>2.489952518894592</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -9859,22 +9859,22 @@
         <v>94</v>
       </c>
       <c r="F248" t="n">
-        <v>0.3331479421579999</v>
+        <v>0.2507741396326372</v>
       </c>
       <c r="G248" t="n">
-        <v>16.81673940703079</v>
+        <v>16.43892245749527</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I248" t="n">
-        <v>107.5074990342365</v>
+        <v>107.5922534495869</v>
       </c>
       <c r="J248" t="n">
-        <v>0.09272094480386031</v>
+        <v>0.09145694319492477</v>
       </c>
       <c r="K248" t="n">
-        <v>1.597818947500694</v>
+        <v>1.5680907876167</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -9903,16 +9903,16 @@
         <v>9.609651814712121</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I249" t="n">
-        <v>20.82357404894231</v>
+        <v>20.70074945360344</v>
       </c>
       <c r="J249" t="n">
-        <v>0.1844083422857973</v>
+        <v>0.183734941654126</v>
       </c>
       <c r="K249" t="n">
-        <v>2.877467694831751</v>
+        <v>2.855083733972476</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>387</v>
       </c>
       <c r="F250" t="n">
-        <v>0.5556173526140304</v>
+        <v>0.6976423433388433</v>
       </c>
       <c r="G250" t="n">
-        <v>25.90564010273646</v>
+        <v>26.85171748772526</v>
       </c>
       <c r="H250" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I250" t="n">
-        <v>16.80713945072462</v>
+        <v>16.68606215381434</v>
       </c>
       <c r="J250" t="n">
-        <v>0.03690416234061489</v>
+        <v>0.03674578187691373</v>
       </c>
       <c r="K250" t="n">
-        <v>0.8188037532564305</v>
+        <v>0.8050391406486012</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -9979,16 +9979,16 @@
         <v>10.94637643240904</v>
       </c>
       <c r="H251" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I251" t="n">
-        <v>33.31144383240486</v>
+        <v>33.18504717552116</v>
       </c>
       <c r="J251" t="n">
-        <v>0.05358998840531627</v>
+        <v>0.05813661654152807</v>
       </c>
       <c r="K251" t="n">
-        <v>1.051681956894891</v>
+        <v>1.10337518813226</v>
       </c>
       <c r="L251" t="b">
         <v>0</v>
@@ -10011,22 +10011,22 @@
         <v>466</v>
       </c>
       <c r="F252" t="n">
-        <v>0.6313677623911828</v>
+        <v>0.6278781090048703</v>
       </c>
       <c r="G252" t="n">
-        <v>16.57103181560881</v>
+        <v>16.55644631322318</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I252" t="n">
-        <v>26.9716095256939</v>
+        <v>26.85727431402685</v>
       </c>
       <c r="J252" t="n">
-        <v>0.02398993308395259</v>
+        <v>0.02443819854337737</v>
       </c>
       <c r="K252" t="n">
-        <v>0.6385643992678991</v>
+        <v>0.6333863826626286</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -10055,16 +10055,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I253" t="n">
-        <v>38.09961404994059</v>
+        <v>38.06550007279813</v>
       </c>
       <c r="J253" t="n">
-        <v>0.03654313088095757</v>
+        <v>0.03813547541960685</v>
       </c>
       <c r="K253" t="n">
-        <v>0.8137649641994217</v>
+        <v>0.8244210715195115</v>
       </c>
       <c r="L253" t="b">
         <v>0</v>
@@ -10093,16 +10093,16 @@
         <v>4.964088133786507</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I254" t="n">
-        <v>35.79819682585769</v>
+        <v>35.85900142959329</v>
       </c>
       <c r="J254" t="n">
-        <v>0.05434313696925501</v>
+        <v>0.05604738587606124</v>
       </c>
       <c r="K254" t="n">
-        <v>1.062193386413744</v>
+        <v>1.074236875916323</v>
       </c>
       <c r="L254" t="b">
         <v>0</v>
@@ -10131,16 +10131,16 @@
         <v>6.022017186956544</v>
       </c>
       <c r="H255" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I255" t="n">
-        <v>102.5155448175118</v>
+        <v>102.602769117474</v>
       </c>
       <c r="J255" t="n">
-        <v>0.03242466014596826</v>
+        <v>0.03459798756106196</v>
       </c>
       <c r="K255" t="n">
-        <v>0.7562849171952851</v>
+        <v>0.7750840464671165</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -10163,22 +10163,22 @@
         <v>98</v>
       </c>
       <c r="F256" t="n">
-        <v>5.405828698564195e-05</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>4.436624665523826</v>
+        <v>4.436552715791846</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I256" t="n">
-        <v>112.2045652329671</v>
+        <v>112.2895165637794</v>
       </c>
       <c r="J256" t="n">
-        <v>0.02761423610322786</v>
+        <v>0.02935510831380669</v>
       </c>
       <c r="K256" t="n">
-        <v>0.6891475213319478</v>
+        <v>0.7019620810747278</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -10207,16 +10207,16 @@
         <v>7.970018757819834</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I257" t="n">
-        <v>54.78824416133097</v>
+        <v>54.72400336719295</v>
       </c>
       <c r="J257" t="n">
-        <v>0.04423962379605557</v>
+        <v>0.04392594160629722</v>
       </c>
       <c r="K257" t="n">
-        <v>0.9211822078788248</v>
+        <v>0.9051801827141155</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -10239,22 +10239,22 @@
         <v>609</v>
       </c>
       <c r="F258" t="n">
-        <v>0.1195773081201428</v>
+        <v>0.1197305102757206</v>
       </c>
       <c r="G258" t="n">
-        <v>21.23387813681973</v>
+        <v>21.23482026253326</v>
       </c>
       <c r="H258" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I258" t="n">
-        <v>116.5817879328188</v>
+        <v>116.6782477440529</v>
       </c>
       <c r="J258" t="n">
-        <v>0.0556811506474347</v>
+        <v>0.05845973591444154</v>
       </c>
       <c r="K258" t="n">
-        <v>1.080867572552922</v>
+        <v>1.10788170496958</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>8.150467777986734</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I259" t="n">
-        <v>38.60471781849141</v>
+        <v>38.59920485734258</v>
       </c>
       <c r="J259" t="n">
-        <v>0.0522282480638955</v>
+        <v>0.05241424119579166</v>
       </c>
       <c r="K259" t="n">
-        <v>1.032676626064855</v>
+        <v>1.023565733773331</v>
       </c>
       <c r="L259" t="b">
         <v>0</v>
@@ -10321,16 +10321,16 @@
         <v>5.170193323271385</v>
       </c>
       <c r="H260" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I260" t="n">
-        <v>103.1771614049493</v>
+        <v>103.2750778723411</v>
       </c>
       <c r="J260" t="n">
-        <v>0.05279967514141497</v>
+        <v>0.05524374616929474</v>
       </c>
       <c r="K260" t="n">
-        <v>1.040651832734702</v>
+        <v>1.063028585193836</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -10353,22 +10353,22 @@
         <v>456</v>
       </c>
       <c r="F261" t="n">
-        <v>0.3331479421579997</v>
+        <v>0.7533958926307559</v>
       </c>
       <c r="G261" t="n">
-        <v>22.86406359392835</v>
+        <v>25.48471678778368</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I261" t="n">
-        <v>23.11424207709796</v>
+        <v>22.99530010104736</v>
       </c>
       <c r="J261" t="n">
-        <v>0.03461128783181579</v>
+        <v>0.03438271156054848</v>
       </c>
       <c r="K261" t="n">
-        <v>0.786802910462849</v>
+        <v>0.7720816114467793</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -10391,22 +10391,22 @@
         <v>550</v>
       </c>
       <c r="F262" t="n">
-        <v>0.9321583982202715</v>
+        <v>0.6606788133830472</v>
       </c>
       <c r="G262" t="n">
-        <v>25.55095167993007</v>
+        <v>23.92474720203816</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I262" t="n">
-        <v>157.7801760952995</v>
+        <v>157.7648191166797</v>
       </c>
       <c r="J262" t="n">
-        <v>0.02269875084260835</v>
+        <v>0.02697141370590787</v>
       </c>
       <c r="K262" t="n">
-        <v>0.6205438230154456</v>
+        <v>0.6687169067335392</v>
       </c>
       <c r="L262" t="b">
         <v>0</v>
@@ -10435,16 +10435,16 @@
         <v>3.976587858956469</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I263" t="n">
-        <v>37.04723495833959</v>
+        <v>36.92273735321028</v>
       </c>
       <c r="J263" t="n">
-        <v>0.09444996630805436</v>
+        <v>0.09456730506871755</v>
       </c>
       <c r="K263" t="n">
-        <v>1.621950292295231</v>
+        <v>1.611470724969319</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -10473,16 +10473,16 @@
         <v>20.49853041073921</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I264" t="n">
-        <v>120.7318778476136</v>
+        <v>120.8199568757475</v>
       </c>
       <c r="J264" t="n">
-        <v>0.01576192081073753</v>
+        <v>0.01617275754951263</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5237289269172035</v>
+        <v>0.5181090203959668</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -10505,22 +10505,22 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>0.06816017797554594</v>
+        <v>0.1022248412121741</v>
       </c>
       <c r="G265" t="n">
-        <v>13.63180904453615</v>
+        <v>13.76832642517036</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I265" t="n">
-        <v>20.62265042769602</v>
+        <v>20.49079916147871</v>
       </c>
       <c r="J265" t="n">
-        <v>0.02919174144891755</v>
+        <v>0.0325987978530071</v>
       </c>
       <c r="K265" t="n">
-        <v>0.7111642084117349</v>
+        <v>0.7472015273872165</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -10543,22 +10543,22 @@
         <v>177</v>
       </c>
       <c r="F266" t="n">
-        <v>0.1749454949944831</v>
+        <v>0.0002614276191779871</v>
       </c>
       <c r="G266" t="n">
-        <v>14.8918672598611</v>
+        <v>14.1503720506546</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I266" t="n">
-        <v>77.86242225726782</v>
+        <v>77.75223933939445</v>
       </c>
       <c r="J266" t="n">
-        <v>0.0422520341401565</v>
+        <v>0.04363854881734786</v>
       </c>
       <c r="K266" t="n">
-        <v>0.8934421183656451</v>
+        <v>0.9011719413306087</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -10581,22 +10581,22 @@
         <v>193</v>
       </c>
       <c r="F267" t="n">
-        <v>0.01674304783092765</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>8.650673070478561</v>
+        <v>8.607438643406063</v>
       </c>
       <c r="H267" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I267" t="n">
-        <v>68.2219232953185</v>
+        <v>68.14914158312627</v>
       </c>
       <c r="J267" t="n">
-        <v>0.08248658929818464</v>
+        <v>0.08658223534888157</v>
       </c>
       <c r="K267" t="n">
-        <v>1.454981648567014</v>
+        <v>1.500103675648981</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>139</v>
       </c>
       <c r="F268" t="n">
-        <v>0.2210122358176252</v>
+        <v>0.09993255188367305</v>
       </c>
       <c r="G268" t="n">
-        <v>22.65029956369739</v>
+        <v>21.87871136023609</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I268" t="n">
-        <v>107.7274527798204</v>
+        <v>107.8113370356629</v>
       </c>
       <c r="J268" t="n">
-        <v>0.03381294725939832</v>
+        <v>0.04025835379228906</v>
       </c>
       <c r="K268" t="n">
-        <v>0.77566075198203</v>
+        <v>0.8540286652821913</v>
       </c>
       <c r="L268" t="b">
         <v>0</v>
@@ -10657,22 +10657,22 @@
         <v>99</v>
       </c>
       <c r="F269" t="n">
-        <v>0.1195773081201632</v>
+        <v>0.6301703983333615</v>
       </c>
       <c r="G269" t="n">
-        <v>15.95300743327104</v>
+        <v>18.31203035896111</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I269" t="n">
-        <v>33.2861146432659</v>
+        <v>33.20354613928577</v>
       </c>
       <c r="J269" t="n">
-        <v>0.05647058612925773</v>
+        <v>0.06409777803584124</v>
       </c>
       <c r="K269" t="n">
-        <v>1.091885445817484</v>
+        <v>1.186514971432401</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -10701,16 +10701,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I270" t="n">
-        <v>66.01924251943154</v>
+        <v>65.94821543801203</v>
       </c>
       <c r="J270" t="n">
-        <v>0.01745729634351389</v>
+        <v>0.02551457907476174</v>
       </c>
       <c r="K270" t="n">
-        <v>0.5473906867266735</v>
+        <v>0.6483985651396776</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -10733,22 +10733,22 @@
         <v>591</v>
       </c>
       <c r="F271" t="n">
-        <v>0.5556173526140203</v>
+        <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>19.87195865725091</v>
+        <v>17.03283675727564</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I271" t="n">
-        <v>89.09665919465984</v>
+        <v>88.98572970946806</v>
       </c>
       <c r="J271" t="n">
-        <v>0.01448917273645538</v>
+        <v>0.007744949446603921</v>
       </c>
       <c r="K271" t="n">
-        <v>0.505965629848552</v>
+        <v>0.4005671386604291</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -10771,22 +10771,22 @@
         <v>31</v>
       </c>
       <c r="F272" t="n">
-        <v>0.5913793103448362</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>6.994229598460587</v>
+        <v>5.940332650618145</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I272" t="n">
-        <v>37.02088600893605</v>
+        <v>36.99600262867412</v>
       </c>
       <c r="J272" t="n">
-        <v>0.05618190385838794</v>
+        <v>0.05035317625847977</v>
       </c>
       <c r="K272" t="n">
-        <v>1.08785640893302</v>
+        <v>0.9948202464351505</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -10809,22 +10809,22 @@
         <v>39</v>
       </c>
       <c r="F273" t="n">
-        <v>0.7819799777530936</v>
+        <v>0.4510791980308452</v>
       </c>
       <c r="G273" t="n">
-        <v>25.1554679644917</v>
+        <v>23.13278746983676</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I273" t="n">
-        <v>165.9522544383636</v>
+        <v>165.9026069159431</v>
       </c>
       <c r="J273" t="n">
-        <v>0.05566831874851079</v>
+        <v>0.0460990596628863</v>
       </c>
       <c r="K273" t="n">
-        <v>1.08068848225442</v>
+        <v>0.9354884648304107</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -10847,22 +10847,22 @@
         <v>330</v>
       </c>
       <c r="F274" t="n">
-        <v>0.1996662958843523</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>19.2522688431829</v>
+        <v>18.16423328962717</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I274" t="n">
-        <v>68.62512976240302</v>
+        <v>68.55192274715682</v>
       </c>
       <c r="J274" t="n">
-        <v>0.2693335379228121</v>
+        <v>0.2688295519333445</v>
       </c>
       <c r="K274" t="n">
-        <v>4.06273877022857</v>
+        <v>4.041890611352551</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
@@ -10891,16 +10891,16 @@
         <v>20.82782016918717</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I275" t="n">
-        <v>104.4481570566942</v>
+        <v>104.5306423562862</v>
       </c>
       <c r="J275" t="n">
-        <v>0.06939948267414323</v>
+        <v>0.07069573078897871</v>
       </c>
       <c r="K275" t="n">
-        <v>1.272329505987203</v>
+        <v>1.278536025155526</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -10923,22 +10923,22 @@
         <v>170</v>
       </c>
       <c r="F276" t="n">
-        <v>0.2778086763070696</v>
+        <v>0.3139390545025023</v>
       </c>
       <c r="G276" t="n">
-        <v>8.699261405441845</v>
+        <v>8.786299689663418</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I276" t="n">
-        <v>108.7582449790528</v>
+        <v>108.8477795708756</v>
       </c>
       <c r="J276" t="n">
-        <v>0.06899653599147518</v>
+        <v>0.07237274157704994</v>
       </c>
       <c r="K276" t="n">
-        <v>1.266705720910099</v>
+        <v>1.301925143810548</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>352</v>
       </c>
       <c r="F277" t="n">
-        <v>0.2778086763070297</v>
+        <v>0.3139390545024572</v>
       </c>
       <c r="G277" t="n">
-        <v>3.29681641877848</v>
+        <v>3.329801890890452</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I277" t="n">
-        <v>18.20512821720761</v>
+        <v>18.17102505759465</v>
       </c>
       <c r="J277" t="n">
-        <v>0.09417382793120579</v>
+        <v>0.09349205749021704</v>
       </c>
       <c r="K277" t="n">
-        <v>1.618096326126174</v>
+        <v>1.59647434368426</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -11005,16 +11005,16 @@
         <v>10.648</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I278" t="n">
-        <v>24.63265777721897</v>
+        <v>24.50836755579533</v>
       </c>
       <c r="J278" t="n">
-        <v>0.06334223376003263</v>
+        <v>0.06502393603168098</v>
       </c>
       <c r="K278" t="n">
-        <v>1.187790614077428</v>
+        <v>1.199432013715061</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11037,22 +11037,22 @@
         <v>537</v>
       </c>
       <c r="F279" t="n">
-        <v>0.02134593993326465</v>
+        <v>0.6278781090048962</v>
       </c>
       <c r="G279" t="n">
-        <v>15.46161919406517</v>
+        <v>18.25710831932041</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I279" t="n">
-        <v>28.97162108990738</v>
+        <v>28.84001031030273</v>
       </c>
       <c r="J279" t="n">
-        <v>0.04394345409035558</v>
+        <v>0.04573214683132797</v>
       </c>
       <c r="K279" t="n">
-        <v>0.9170486715008175</v>
+        <v>0.9303711645635245</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -11081,16 +11081,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I280" t="n">
-        <v>65.92689209476436</v>
+        <v>65.86372583391929</v>
       </c>
       <c r="J280" t="n">
-        <v>0.01457306970744695</v>
+        <v>0.02278602568216852</v>
       </c>
       <c r="K280" t="n">
-        <v>0.5071365503543432</v>
+        <v>0.6103436763399905</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -11113,22 +11113,22 @@
         <v>544</v>
       </c>
       <c r="F281" t="n">
-        <v>0.1195773081201527</v>
+        <v>0.03959591678410032</v>
       </c>
       <c r="G281" t="n">
-        <v>14.20818250381747</v>
+        <v>13.8790716975982</v>
       </c>
       <c r="H281" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I281" t="n">
-        <v>103.3958056976741</v>
+        <v>103.4880239092246</v>
       </c>
       <c r="J281" t="n">
-        <v>0.05973285605745286</v>
+        <v>0.05843434987054964</v>
       </c>
       <c r="K281" t="n">
-        <v>1.13741579940717</v>
+        <v>1.107527648098275</v>
       </c>
       <c r="L281" t="b">
         <v>0</v>
@@ -11151,22 +11151,22 @@
         <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>0.61540600667409</v>
+        <v>0.631908093424227</v>
       </c>
       <c r="G282" t="n">
-        <v>15.4888507841826</v>
+        <v>15.55357988815532</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I282" t="n">
-        <v>36.48673825964631</v>
+        <v>36.45468511525988</v>
       </c>
       <c r="J282" t="n">
-        <v>0.08570037484337578</v>
+        <v>0.08384568117176068</v>
       </c>
       <c r="K282" t="n">
-        <v>1.499835322681875</v>
+        <v>1.461937200626962</v>
       </c>
       <c r="L282" t="b">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I283" t="n">
-        <v>118.739230221862</v>
+        <v>118.8286387676094</v>
       </c>
       <c r="J283" t="n">
-        <v>0.02865264140678266</v>
+        <v>0.02968581399910793</v>
       </c>
       <c r="K283" t="n">
-        <v>0.7036401788007958</v>
+        <v>0.7065744035287158</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11227,22 +11227,22 @@
         <v>377</v>
       </c>
       <c r="F284" t="n">
-        <v>0.1665739710790001</v>
+        <v>0.1253870698163085</v>
       </c>
       <c r="G284" t="n">
-        <v>4.945808273432537</v>
+        <v>4.887606012828303</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I284" t="n">
-        <v>29.58078561450717</v>
+        <v>29.59186674388968</v>
       </c>
       <c r="J284" t="n">
-        <v>0.07676608359873818</v>
+        <v>0.07312110781639405</v>
       </c>
       <c r="K284" t="n">
-        <v>1.375142563224462</v>
+        <v>1.312362540453395</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -11271,16 +11271,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H285" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I285" t="n">
-        <v>21.53753539877835</v>
+        <v>21.48311288982705</v>
       </c>
       <c r="J285" t="n">
-        <v>0.04658218937716482</v>
+        <v>0.04715391210488935</v>
       </c>
       <c r="K285" t="n">
-        <v>0.9538765714853157</v>
+        <v>0.9502003969807847</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -11309,16 +11309,16 @@
         <v>6.380249524901044</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I286" t="n">
-        <v>108.2058629750189</v>
+        <v>108.2949720690951</v>
       </c>
       <c r="J286" t="n">
-        <v>0.04841271971121205</v>
+        <v>0.04860138976032433</v>
       </c>
       <c r="K286" t="n">
-        <v>0.9794246393032131</v>
+        <v>0.9703882376758347</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -11341,22 +11341,22 @@
         <v>191</v>
       </c>
       <c r="F287" t="n">
-        <v>0.9699447845990904</v>
+        <v>0.3007404155744564</v>
       </c>
       <c r="G287" t="n">
-        <v>19.83368367755643</v>
+        <v>16.74934020564287</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I287" t="n">
-        <v>117.3927459123834</v>
+        <v>117.4924003835356</v>
       </c>
       <c r="J287" t="n">
-        <v>0.07098158781680787</v>
+        <v>0.06979344808666384</v>
       </c>
       <c r="K287" t="n">
-        <v>1.294410390814975</v>
+        <v>1.265951969444657</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -11385,16 +11385,16 @@
         <v>4.313887457966422</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I288" t="n">
-        <v>17.36842068262242</v>
+        <v>17.33328039059763</v>
       </c>
       <c r="J288" t="n">
-        <v>0.06955935538337776</v>
+        <v>0.062753947730667</v>
       </c>
       <c r="K288" t="n">
-        <v>1.274560793140322</v>
+        <v>1.167772691010887</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -11417,22 +11417,22 @@
         <v>372</v>
       </c>
       <c r="F289" t="n">
-        <v>0.5556173526140629</v>
+        <v>0.00402998441935881</v>
       </c>
       <c r="G289" t="n">
-        <v>21.93223100426378</v>
+        <v>18.82148403028074</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I289" t="n">
-        <v>27.11196571164846</v>
+        <v>26.97954215474278</v>
       </c>
       <c r="J289" t="n">
-        <v>0.06064310297829288</v>
+        <v>0.06146746452148399</v>
       </c>
       <c r="K289" t="n">
-        <v>1.150119795419756</v>
+        <v>1.149830225380191</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -11461,16 +11461,16 @@
         <v>5.832000000000001</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I290" t="n">
-        <v>86.17362526342446</v>
+        <v>86.06462386034174</v>
       </c>
       <c r="J290" t="n">
-        <v>0.04909855992432709</v>
+        <v>0.05180002432261666</v>
       </c>
       <c r="K290" t="n">
-        <v>0.9889966698514117</v>
+        <v>1.014999306276982</v>
       </c>
       <c r="L290" t="b">
         <v>0</v>
@@ -11493,22 +11493,22 @@
         <v>21</v>
       </c>
       <c r="F291" t="n">
-        <v>0.9060557953281976</v>
+        <v>1</v>
       </c>
       <c r="G291" t="n">
-        <v>28.61620369959863</v>
+        <v>29.25033432920041</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I291" t="n">
-        <v>79.25906230131363</v>
+        <v>79.14913125003444</v>
       </c>
       <c r="J291" t="n">
-        <v>0.1974711163201805</v>
+        <v>0.1970772785555232</v>
       </c>
       <c r="K291" t="n">
-        <v>3.05978023601889</v>
+        <v>3.041168106918565</v>
       </c>
       <c r="L291" t="b">
         <v>0</v>
@@ -11531,22 +11531,22 @@
         <v>556</v>
       </c>
       <c r="F292" t="n">
-        <v>0.5567232035595515</v>
+        <v>0.3139390545025129</v>
       </c>
       <c r="G292" t="n">
-        <v>8.406987771479722</v>
+        <v>7.882295301621195</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I292" t="n">
-        <v>31.89400325340628</v>
+        <v>31.8415415541979</v>
       </c>
       <c r="J292" t="n">
-        <v>0.1784430956619517</v>
+        <v>0.1801346498712153</v>
       </c>
       <c r="K292" t="n">
-        <v>2.794212846517089</v>
+        <v>2.804870788234632</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -11569,22 +11569,22 @@
         <v>240</v>
       </c>
       <c r="F293" t="n">
-        <v>0.5556173526140067</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>22.21201640652497</v>
+        <v>19.03856866993945</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I293" t="n">
-        <v>104.094202676142</v>
+        <v>104.1880636553184</v>
       </c>
       <c r="J293" t="n">
-        <v>0.03230029283384397</v>
+        <v>0.0325800794217188</v>
       </c>
       <c r="K293" t="n">
-        <v>0.7545491663774027</v>
+        <v>0.7469404631093048</v>
       </c>
       <c r="L293" t="b">
         <v>0</v>
@@ -11613,16 +11613,16 @@
         <v>8.060074937616895</v>
       </c>
       <c r="H294" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I294" t="n">
-        <v>79.54639661569981</v>
+        <v>79.43164369144843</v>
       </c>
       <c r="J294" t="n">
-        <v>0.07632869756914108</v>
+        <v>0.08214498093713463</v>
       </c>
       <c r="K294" t="n">
-        <v>1.369038120299421</v>
+        <v>1.438217687391127</v>
       </c>
       <c r="L294" t="b">
         <v>0</v>
@@ -11645,22 +11645,22 @@
         <v>572</v>
       </c>
       <c r="F295" t="n">
-        <v>0.03576195773082118</v>
+        <v>0.6278781090048654</v>
       </c>
       <c r="G295" t="n">
-        <v>16.55671302758523</v>
+        <v>19.46654381261656</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I295" t="n">
-        <v>64.73857825121728</v>
+        <v>64.67167054717289</v>
       </c>
       <c r="J295" t="n">
-        <v>0.2035617852283293</v>
+        <v>0.2076835830469004</v>
       </c>
       <c r="K295" t="n">
-        <v>3.144785559026954</v>
+        <v>3.18909328188147</v>
       </c>
       <c r="L295" t="b">
         <v>0</v>
@@ -11689,16 +11689,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I296" t="n">
-        <v>226.7840880584426</v>
+        <v>226.7478660520466</v>
       </c>
       <c r="J296" t="n">
-        <v>0.1096360062773973</v>
+        <v>0.1136716517894194</v>
       </c>
       <c r="K296" t="n">
-        <v>1.833896509086011</v>
+        <v>1.87791733071304</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -11727,16 +11727,16 @@
         <v>20.58068878827917</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I297" t="n">
-        <v>223.4261821509419</v>
+        <v>223.3993526565197</v>
       </c>
       <c r="J297" t="n">
-        <v>0.3043440947988226</v>
+        <v>0.3029441201082962</v>
       </c>
       <c r="K297" t="n">
-        <v>4.551368794421108</v>
+        <v>4.517683425915471</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -11759,22 +11759,22 @@
         <v>260</v>
       </c>
       <c r="F298" t="n">
-        <v>0.1195773081201609</v>
+        <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>19.55581620031309</v>
+        <v>18.87858122317459</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I298" t="n">
-        <v>77.17677365952497</v>
+        <v>77.11740147624107</v>
       </c>
       <c r="J298" t="n">
-        <v>0.4678445721951654</v>
+        <v>0.4645950648088458</v>
       </c>
       <c r="K298" t="n">
-        <v>6.833287431379674</v>
+        <v>6.772214615095272</v>
       </c>
       <c r="L298" t="b">
         <v>0</v>
@@ -11797,22 +11797,22 @@
         <v>195</v>
       </c>
       <c r="F299" t="n">
-        <v>0.5556173526140231</v>
+        <v>0.6278781090048555</v>
       </c>
       <c r="G299" t="n">
-        <v>9.685665712439366</v>
+        <v>9.865635474735059</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I299" t="n">
-        <v>23.26106200707272</v>
+        <v>23.26395229330824</v>
       </c>
       <c r="J299" t="n">
-        <v>0.06650324737539487</v>
+        <v>0.07227710918141356</v>
       </c>
       <c r="K299" t="n">
-        <v>1.23190776893496</v>
+        <v>1.300591367388408</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -11841,16 +11841,16 @@
         <v>5.352813839467986</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I300" t="n">
-        <v>26.50363905425595</v>
+        <v>26.37339902099465</v>
       </c>
       <c r="J300" t="n">
-        <v>0.04198978613492613</v>
+        <v>0.0446522326144599</v>
       </c>
       <c r="K300" t="n">
-        <v>0.88978201522607</v>
+        <v>0.9153096980928033</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -11879,16 +11879,16 @@
         <v>11.82363560839051</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I301" t="n">
-        <v>107.8917655498726</v>
+        <v>107.9641064865613</v>
       </c>
       <c r="J301" t="n">
-        <v>0.05786758486959177</v>
+        <v>0.05656224683523835</v>
       </c>
       <c r="K301" t="n">
-        <v>1.111382865715826</v>
+        <v>1.081417595414784</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -11911,22 +11911,22 @@
         <v>189</v>
       </c>
       <c r="F302" t="n">
-        <v>0.266407119021184</v>
+        <v>0.2507741396326144</v>
       </c>
       <c r="G302" t="n">
-        <v>23.29941392954138</v>
+        <v>23.19822906286911</v>
       </c>
       <c r="H302" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I302" t="n">
-        <v>33.74379076914816</v>
+        <v>33.61132342890492</v>
       </c>
       <c r="J302" t="n">
-        <v>0.1086007616252831</v>
+        <v>0.1035781391015762</v>
       </c>
       <c r="K302" t="n">
-        <v>1.819447963717275</v>
+        <v>1.73714401692091</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -11955,16 +11955,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I303" t="n">
-        <v>89.06559099605887</v>
+        <v>88.94740905995013</v>
       </c>
       <c r="J303" t="n">
-        <v>0.06788778203777744</v>
+        <v>0.06585635376416159</v>
       </c>
       <c r="K303" t="n">
-        <v>1.251231232082699</v>
+        <v>1.211041668974301</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -11993,16 +11993,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I304" t="n">
-        <v>106.8816418544399</v>
+        <v>106.9806842660125</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1047433876805372</v>
+        <v>0.09410693505149988</v>
       </c>
       <c r="K304" t="n">
-        <v>1.765611952750185</v>
+        <v>1.605049985738236</v>
       </c>
       <c r="L304" t="b">
         <v>0</v>
@@ -12025,22 +12025,22 @@
         <v>181</v>
       </c>
       <c r="F305" t="n">
-        <v>0.3415194660734606</v>
+        <v>0.2520238119065863</v>
       </c>
       <c r="G305" t="n">
-        <v>19.37676384071214</v>
+        <v>18.90487115542105</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I305" t="n">
-        <v>116.2524532691994</v>
+        <v>116.3420605779878</v>
       </c>
       <c r="J305" t="n">
-        <v>0.09572034130520173</v>
+        <v>0.09258538942265924</v>
       </c>
       <c r="K305" t="n">
-        <v>1.639680469161257</v>
+        <v>1.583829125678705</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -12063,22 +12063,22 @@
         <v>418</v>
       </c>
       <c r="F306" t="n">
-        <v>0.5080934371523994</v>
+        <v>0.3801911938682704</v>
       </c>
       <c r="G306" t="n">
-        <v>25.1047393897355</v>
+        <v>24.26886442013284</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I306" t="n">
-        <v>24.00534701675128</v>
+        <v>23.99582442390082</v>
       </c>
       <c r="J306" t="n">
-        <v>0.1686192273975706</v>
+        <v>0.1655905443254622</v>
       </c>
       <c r="K306" t="n">
-        <v>2.65710457358419</v>
+        <v>2.602025456075483</v>
       </c>
       <c r="L306" t="b">
         <v>0</v>
@@ -12101,22 +12101,22 @@
         <v>249</v>
       </c>
       <c r="F307" t="n">
-        <v>0.09261232147713751</v>
+        <v>0.04996627594184144</v>
       </c>
       <c r="G307" t="n">
-        <v>9.132457557677537</v>
+        <v>9.018777061810063</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I307" t="n">
-        <v>105.5219661395455</v>
+        <v>105.60466210263</v>
       </c>
       <c r="J307" t="n">
-        <v>0.03888028477763512</v>
+        <v>0.03737348730922107</v>
       </c>
       <c r="K307" t="n">
-        <v>0.8463837988303482</v>
+        <v>0.8137936918662018</v>
       </c>
       <c r="L307" t="b">
         <v>0</v>
@@ -12145,16 +12145,16 @@
         <v>3.0214779496134</v>
       </c>
       <c r="H308" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I308" t="n">
-        <v>70.70378139597372</v>
+        <v>70.65909022983629</v>
       </c>
       <c r="J308" t="n">
-        <v>0.1453441829477243</v>
+        <v>0.144721272899043</v>
       </c>
       <c r="K308" t="n">
-        <v>2.332262967297043</v>
+        <v>2.310963604173042</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -12177,22 +12177,22 @@
         <v>361</v>
       </c>
       <c r="F309" t="n">
-        <v>0.5558928409343594</v>
+        <v>0.6278781090048535</v>
       </c>
       <c r="G309" t="n">
-        <v>23.01276193585674</v>
+        <v>23.43870266616334</v>
       </c>
       <c r="H309" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I309" t="n">
-        <v>145.4806316844993</v>
+        <v>145.4003249552997</v>
       </c>
       <c r="J309" t="n">
-        <v>0.1933138493140569</v>
+        <v>0.193011429484494</v>
       </c>
       <c r="K309" t="n">
-        <v>3.001758723108625</v>
+        <v>2.984462075548851</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -12215,22 +12215,22 @@
         <v>503</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>0.1039625363030408</v>
       </c>
       <c r="G310" t="n">
-        <v>8.454192746797297</v>
+        <v>8.717868542902842</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I310" t="n">
-        <v>34.94838318845575</v>
+        <v>34.81595403461037</v>
       </c>
       <c r="J310" t="n">
-        <v>0.3394657064714744</v>
+        <v>0.3383329160582359</v>
       </c>
       <c r="K310" t="n">
-        <v>5.041548771336809</v>
+        <v>5.011247780670446</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -12259,16 +12259,16 @@
         <v>9.801628028036975</v>
       </c>
       <c r="H311" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I311" t="n">
-        <v>115.2503574460976</v>
+        <v>115.3509789345894</v>
       </c>
       <c r="J311" t="n">
-        <v>0.06922847793328751</v>
+        <v>0.0692480409573115</v>
       </c>
       <c r="K311" t="n">
-        <v>1.269942852985444</v>
+        <v>1.258345225257645</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -12297,16 +12297,16 @@
         <v>6.296969191603211</v>
       </c>
       <c r="H312" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I312" t="n">
-        <v>20.24988718935582</v>
+        <v>20.13193444980531</v>
       </c>
       <c r="J312" t="n">
-        <v>0.09766596559693762</v>
+        <v>0.09965208952693654</v>
       </c>
       <c r="K312" t="n">
-        <v>1.666834862851918</v>
+        <v>1.682387756555788</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12335,16 +12335,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H313" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I313" t="n">
-        <v>105.7883522578129</v>
+        <v>105.8789003117746</v>
       </c>
       <c r="J313" t="n">
-        <v>0.04660998018250238</v>
+        <v>0.04846247534394451</v>
       </c>
       <c r="K313" t="n">
-        <v>0.9542644379774858</v>
+        <v>0.968450810802548</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12373,16 +12373,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H314" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I314" t="n">
-        <v>26.04685637567984</v>
+        <v>26.00261731347925</v>
       </c>
       <c r="J314" t="n">
-        <v>0.06854248969155763</v>
+        <v>0.06880518520459246</v>
       </c>
       <c r="K314" t="n">
-        <v>1.260368756453951</v>
+        <v>1.252168755898543</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12411,16 +12411,16 @@
         <v>4.289492277647788</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I315" t="n">
-        <v>25.61123445369835</v>
+        <v>25.54983911278873</v>
       </c>
       <c r="J315" t="n">
-        <v>0.01967221260559414</v>
+        <v>0.01991620109106526</v>
       </c>
       <c r="K315" t="n">
-        <v>0.5783034936996553</v>
+        <v>0.5703184908385817</v>
       </c>
       <c r="L315" t="b">
         <v>0</v>
@@ -12443,22 +12443,22 @@
         <v>542</v>
       </c>
       <c r="F316" t="n">
-        <v>0.3363296996663437</v>
+        <v>0.6278781090049043</v>
       </c>
       <c r="G316" t="n">
-        <v>10.96778499411108</v>
+        <v>11.83915662694097</v>
       </c>
       <c r="H316" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I316" t="n">
-        <v>114.7848877730463</v>
+        <v>114.8833148848792</v>
       </c>
       <c r="J316" t="n">
-        <v>0.02223125619588508</v>
+        <v>0.02362803876379312</v>
       </c>
       <c r="K316" t="n">
-        <v>0.6140191647146005</v>
+        <v>0.6220871570708743</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -12487,16 +12487,16 @@
         <v>8.332258457345164</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I317" t="n">
-        <v>30.79600906652642</v>
+        <v>30.74724484597344</v>
       </c>
       <c r="J317" t="n">
-        <v>0.06813702339265269</v>
+        <v>0.07238442272139119</v>
       </c>
       <c r="K317" t="n">
-        <v>1.254709805979532</v>
+        <v>1.302088059680242</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -12519,22 +12519,22 @@
         <v>538</v>
       </c>
       <c r="F318" t="n">
-        <v>0.11985279644052</v>
+        <v>0.01385228580827913</v>
       </c>
       <c r="G318" t="n">
-        <v>10.12081631126362</v>
+        <v>9.810143310535647</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I318" t="n">
-        <v>85.37618288149029</v>
+        <v>85.25994168740014</v>
       </c>
       <c r="J318" t="n">
-        <v>0.03801845892555641</v>
+        <v>0.03839320758322701</v>
       </c>
       <c r="K318" t="n">
-        <v>0.8343555986379791</v>
+        <v>0.8280156388288016</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12557,22 +12557,22 @@
         <v>62</v>
       </c>
       <c r="F319" t="n">
-        <v>0.07152391546164236</v>
+        <v>0.09993255188368276</v>
       </c>
       <c r="G319" t="n">
-        <v>20.39561872725359</v>
+        <v>20.56579082983738</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I319" t="n">
-        <v>39.82603991525067</v>
+        <v>39.80110853078232</v>
       </c>
       <c r="J319" t="n">
-        <v>0.0592901308837809</v>
+        <v>0.06336243438950796</v>
       </c>
       <c r="K319" t="n">
-        <v>1.131236839926802</v>
+        <v>1.176259199723212</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -12595,22 +12595,22 @@
         <v>17</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>0.6501754119448682</v>
       </c>
       <c r="G320" t="n">
-        <v>16.00149602380977</v>
+        <v>19.12262980451418</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I320" t="n">
-        <v>78.82653507520037</v>
+        <v>78.7129236699044</v>
       </c>
       <c r="J320" t="n">
-        <v>0.03683840932490361</v>
+        <v>0.03685208081070609</v>
       </c>
       <c r="K320" t="n">
-        <v>0.8178860615507109</v>
+        <v>0.8065216823192074</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -12633,22 +12633,22 @@
         <v>282</v>
       </c>
       <c r="F321" t="n">
-        <v>0.3689098998888046</v>
+        <v>0.9430668357812737</v>
       </c>
       <c r="G321" t="n">
-        <v>23.82386136792387</v>
+        <v>27.51854979935612</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I321" t="n">
-        <v>24.28081038740774</v>
+        <v>24.14846705458958</v>
       </c>
       <c r="J321" t="n">
-        <v>0.04436417065269846</v>
+        <v>0.04474753036888981</v>
       </c>
       <c r="K321" t="n">
-        <v>0.9229204645363822</v>
+        <v>0.9166388073041291</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -12671,22 +12671,22 @@
         <v>10</v>
       </c>
       <c r="F322" t="n">
-        <v>0.2023359288098402</v>
+        <v>0.2521254750514736</v>
       </c>
       <c r="G322" t="n">
-        <v>15.39459741943883</v>
+        <v>15.61138523618781</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I322" t="n">
-        <v>230.2806811174245</v>
+        <v>230.1507886006399</v>
       </c>
       <c r="J322" t="n">
-        <v>0.00829621249527665</v>
+        <v>0.01469370644991958</v>
       </c>
       <c r="K322" t="n">
-        <v>0.4195326626956056</v>
+        <v>0.4974808277145054</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -12709,22 +12709,22 @@
         <v>105</v>
       </c>
       <c r="F323" t="n">
-        <v>0.3331479421580283</v>
+        <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>14.96866295616355</v>
+        <v>13.60856348039719</v>
       </c>
       <c r="H323" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I323" t="n">
-        <v>228.7269951484766</v>
+        <v>228.6075510479119</v>
       </c>
       <c r="J323" t="n">
-        <v>0.487478640586293</v>
+        <v>0.487562362229251</v>
       </c>
       <c r="K323" t="n">
-        <v>7.107313215857507</v>
+        <v>7.092537446869582</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -12753,16 +12753,16 @@
         <v>11.61919519588168</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I324" t="n">
-        <v>269.7897277448292</v>
+        <v>269.6578134873851</v>
       </c>
       <c r="J324" t="n">
-        <v>0.5455309324776515</v>
+        <v>0.5431981214476921</v>
       </c>
       <c r="K324" t="n">
-        <v>7.917528628647568</v>
+        <v>7.868484377609954</v>
       </c>
       <c r="L324" t="b">
         <v>0</v>
@@ -12791,16 +12791,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1725313205724583</v>
+        <v>0.1691447774827022</v>
       </c>
       <c r="I325" t="n">
-        <v>270.3955759886917</v>
+        <v>270.2638640101699</v>
       </c>
       <c r="J325" t="n">
         <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>14.26039350350955</v>
+        <v>14.23945909959438</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>

--- a/output/lstm_results/lstm_data_for_cnn.xlsx
+++ b/output/lstm_results/lstm_data_for_cnn.xlsx
@@ -511,16 +511,16 @@
         <v>180</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01385228580827646</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>11.15950846115205</v>
+        <v>11.11332497500186</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I2" t="n">
-        <v>123.2548079002438</v>
+        <v>125.7079298799892</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>3.130550111402148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I3" t="n">
-        <v>105.3436182048155</v>
+        <v>107.8036555658189</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.376161209448902</v>
+        <v>0.6312434555400193</v>
       </c>
       <c r="G4" t="n">
-        <v>25.13368456143969</v>
+        <v>26.86199461461181</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I4" t="n">
-        <v>29.75204344599689</v>
+        <v>27.66233458454895</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2548041240519832</v>
+        <v>0.04505750084577682</v>
       </c>
       <c r="G5" t="n">
-        <v>21.66895193871442</v>
+        <v>20.40228098434277</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I5" t="n">
-        <v>39.16078927133193</v>
+        <v>37.819406791761</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         <v>621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02350614742421216</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>12.98960256308772</v>
+        <v>12.89864333951443</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I6" t="n">
-        <v>62.39924737520739</v>
+        <v>60.15337380754412</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>10.05955744553407</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I7" t="n">
-        <v>89.83979710266848</v>
+        <v>87.45058533168832</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
         <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6278781090048696</v>
+        <v>0.8171607952460306</v>
       </c>
       <c r="G8" t="n">
-        <v>17.85974355140973</v>
+        <v>18.7131542527061</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I8" t="n">
-        <v>75.33728505578088</v>
+        <v>72.97620396885894</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -777,16 +777,16 @@
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.02993655350185815</v>
       </c>
       <c r="G9" t="n">
-        <v>13.96824971139906</v>
+        <v>14.09369808784285</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I9" t="n">
-        <v>86.67061821580916</v>
+        <v>84.2576080725613</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>406</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7572951632405794</v>
+        <v>0.6462117322909167</v>
       </c>
       <c r="G10" t="n">
-        <v>25.55966241167819</v>
+        <v>24.86557469459941</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I10" t="n">
-        <v>41.20755171888074</v>
+        <v>39.32764223625534</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -853,16 +853,16 @@
         <v>368</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1266367420902895</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.127662498284683</v>
+        <v>3.976587858956469</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I11" t="n">
-        <v>116.6298323264942</v>
+        <v>119.1061572061333</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         <v>379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.313939054502457</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>6.001088576510699</v>
+        <v>5.484544739538552</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I12" t="n">
-        <v>102.4211071272682</v>
+        <v>104.8837510654145</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>10.87983322482473</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I13" t="n">
-        <v>34.71756767674288</v>
+        <v>33.59243690118958</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -967,16 +967,16 @@
         <v>662</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.09055894194721084</v>
       </c>
       <c r="G14" t="n">
-        <v>5.405378062633547</v>
+        <v>5.552229658086575</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I14" t="n">
-        <v>184.7249199096449</v>
+        <v>182.3337158301924</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1005,16 +1005,16 @@
         <v>277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6278781090048769</v>
+        <v>0.6312434555399341</v>
       </c>
       <c r="G15" t="n">
-        <v>19.06052914612661</v>
+        <v>19.07672249673463</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I15" t="n">
-        <v>39.81334125871752</v>
+        <v>38.57227985105439</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         <v>686</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.0003841075862772198</v>
       </c>
       <c r="G16" t="n">
-        <v>10.12438798150288</v>
+        <v>10.12555463777191</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I16" t="n">
-        <v>114.3131951323779</v>
+        <v>116.7570671852539</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1081,22 +1081,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.638834236328366</v>
+        <v>0.7266018532988266</v>
       </c>
       <c r="G17" t="n">
-        <v>23.60018664428593</v>
+        <v>24.1216480644051</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I17" t="n">
-        <v>108.7760641671631</v>
+        <v>111.2520380383647</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06653638601018749</v>
+        <v>0.05280281285738973</v>
       </c>
       <c r="K17" t="n">
-        <v>1.220526017557314</v>
+        <v>0.9705048503766227</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1125,16 +1125,16 @@
         <v>5.248200453488796</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I18" t="n">
-        <v>192.2886507161189</v>
+        <v>191.3630010987614</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0879538228317804</v>
+        <v>0.08900078827801797</v>
       </c>
       <c r="K18" t="n">
-        <v>1.519233082932138</v>
+        <v>1.422897481006313</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1157,22 +1157,22 @@
         <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003061115095886442</v>
+        <v>0.6312434555399205</v>
       </c>
       <c r="G19" t="n">
-        <v>22.30932431646837</v>
+        <v>26.50976397654575</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I19" t="n">
-        <v>31.82601438573502</v>
+        <v>30.00547991986788</v>
       </c>
       <c r="J19" t="n">
-        <v>0.504604700078616</v>
+        <v>0.5909377935547293</v>
       </c>
       <c r="K19" t="n">
-        <v>7.33022540031216</v>
+        <v>7.695972137499886</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1201,16 +1201,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I20" t="n">
-        <v>66.92952184047854</v>
+        <v>64.55810277951949</v>
       </c>
       <c r="J20" t="n">
-        <v>0.009393268324614816</v>
+        <v>0.04207557980691856</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4235560938259772</v>
+        <v>0.8364387562736121</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         <v>216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6396311827169987</v>
+        <v>0.001547658636490593</v>
       </c>
       <c r="G21" t="n">
-        <v>20.07169251685383</v>
+        <v>16.84805026088252</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I21" t="n">
-        <v>29.99236422303212</v>
+        <v>27.83536411711505</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1137651861698729</v>
+        <v>0.067471872020909</v>
       </c>
       <c r="K21" t="n">
-        <v>1.879221846306089</v>
+        <v>1.153834834629424</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1277,16 +1277,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I22" t="n">
-        <v>104.8955881632196</v>
+        <v>107.3669355725416</v>
       </c>
       <c r="J22" t="n">
-        <v>0.04660236333850133</v>
+        <v>0.03435292956081123</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9425079959343268</v>
+        <v>0.739923135726542</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>435</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02350614742421015</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>13.30973905461809</v>
+        <v>13.21653808680624</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I23" t="n">
-        <v>24.39634485170043</v>
+        <v>22.38507822521032</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06643455696444564</v>
+        <v>0.09301421999347741</v>
       </c>
       <c r="K23" t="n">
-        <v>1.219105817013391</v>
+        <v>1.473056278853738</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>678</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2548041240519974</v>
+        <v>0.02993655350186084</v>
       </c>
       <c r="G24" t="n">
-        <v>16.8597770202047</v>
+        <v>15.80317951144785</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I24" t="n">
-        <v>111.5210831983169</v>
+        <v>113.9725838494851</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0185669368327863</v>
+        <v>0.03044050270676376</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5515004235617678</v>
+        <v>0.6910266696650691</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1385,22 +1385,22 @@
         <v>120</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.09458456844067069</v>
       </c>
       <c r="G25" t="n">
-        <v>3.556590642736384</v>
+        <v>3.657510220055388</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I25" t="n">
-        <v>104.3055741312031</v>
+        <v>106.7501645888422</v>
       </c>
       <c r="J25" t="n">
-        <v>0.05698843913411514</v>
+        <v>0.052453828970339</v>
       </c>
       <c r="K25" t="n">
-        <v>1.087361661081618</v>
+        <v>0.9661433429476661</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>674</v>
       </c>
       <c r="F26" t="n">
-        <v>0.03975143544917208</v>
+        <v>0.631781731247903</v>
       </c>
       <c r="G26" t="n">
-        <v>19.3061567481292</v>
+        <v>22.69469586701329</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I26" t="n">
-        <v>65.29489495466176</v>
+        <v>63.15046102124055</v>
       </c>
       <c r="J26" t="n">
-        <v>0.05746968383407251</v>
+        <v>0.1210111879500158</v>
       </c>
       <c r="K26" t="n">
-        <v>1.094073537635704</v>
+        <v>1.822954908164806</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.03959591678410077</v>
+        <v>0.07543157732456826</v>
       </c>
       <c r="G27" t="n">
-        <v>14.20734619898275</v>
+        <v>14.35829203798899</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I27" t="n">
-        <v>65.40660834372586</v>
+        <v>63.07748118121708</v>
       </c>
       <c r="J27" t="n">
-        <v>0.08323226442055204</v>
+        <v>0.09340882523201029</v>
       </c>
       <c r="K27" t="n">
-        <v>1.453381932359726</v>
+        <v>1.477987949750956</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1499,22 +1499,22 @@
         <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>0.941817163507327</v>
+        <v>0.2045230187471987</v>
       </c>
       <c r="G28" t="n">
-        <v>26.5539835083398</v>
+        <v>21.97447301503104</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I28" t="n">
-        <v>35.25899087948547</v>
+        <v>33.84603464998446</v>
       </c>
       <c r="J28" t="n">
-        <v>0.08895753102252792</v>
+        <v>0.0804996979294446</v>
       </c>
       <c r="K28" t="n">
-        <v>1.533231710809429</v>
+        <v>1.316653123930471</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1537,22 +1537,22 @@
         <v>373</v>
       </c>
       <c r="F29" t="n">
-        <v>0.633069990798042</v>
+        <v>0.631525807791473</v>
       </c>
       <c r="G29" t="n">
-        <v>26.52197739078042</v>
+        <v>26.51165196912239</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I29" t="n">
-        <v>10.70137668636294</v>
+        <v>13.17117668814933</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03967171398975174</v>
+        <v>0.0371869860087279</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8458468527101417</v>
+        <v>0.7753424164163516</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -1581,16 +1581,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I30" t="n">
-        <v>38.10876267995729</v>
+        <v>36.82715257770452</v>
       </c>
       <c r="J30" t="n">
-        <v>0.09025547625160071</v>
+        <v>0.09819561126554245</v>
       </c>
       <c r="K30" t="n">
-        <v>1.551334036200799</v>
+        <v>1.537811923351895</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1619,16 +1619,16 @@
         <v>7.790921447428411</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I31" t="n">
-        <v>160.1705211393607</v>
+        <v>157.6956344366866</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03291691199654435</v>
+        <v>0.0286732895939513</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7516382367405241</v>
+        <v>0.6689405120913803</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -1657,16 +1657,16 @@
         <v>11.449738512298</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I32" t="n">
-        <v>58.58939270620922</v>
+        <v>56.46291252198176</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1151028923145186</v>
+        <v>0.1825787252880413</v>
       </c>
       <c r="K32" t="n">
-        <v>1.897878713611429</v>
+        <v>2.592409549041449</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1689,22 +1689,22 @@
         <v>305</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6337306638674393</v>
+        <v>0.6235324590003333</v>
       </c>
       <c r="G33" t="n">
-        <v>19.99614237905018</v>
+        <v>19.94473792561125</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I33" t="n">
-        <v>32.3285255702457</v>
+        <v>30.02078356759165</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0235176320929314</v>
+        <v>0.03789056028278788</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6205473251607524</v>
+        <v>0.7841354998136065</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1727,22 +1727,22 @@
         <v>193</v>
       </c>
       <c r="F34" t="n">
-        <v>0.2144734320629172</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>16.19324061064967</v>
+        <v>15.21432035945083</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I34" t="n">
-        <v>34.29797380660997</v>
+        <v>32.73088529106516</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03114123458367183</v>
+        <v>0.01349084418570487</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7268730235420542</v>
+        <v>0.4791943636447978</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -1765,22 +1765,22 @@
         <v>616</v>
       </c>
       <c r="F35" t="n">
-        <v>0.008059968838719183</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>20.9609767519368</v>
+        <v>20.91041556258507</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I35" t="n">
-        <v>18.60184049043275</v>
+        <v>16.45658571791968</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03596259253046459</v>
+        <v>0.0263451882511215</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7941160692624496</v>
+        <v>0.6398445231965126</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1803,22 +1803,22 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5653992803814747</v>
+        <v>0.07543157732456938</v>
       </c>
       <c r="G36" t="n">
-        <v>18.45103250444718</v>
+        <v>16.13222510959525</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I36" t="n">
-        <v>33.0936853171095</v>
+        <v>31.88345706751251</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02011400437984332</v>
+        <v>0.05941122474830111</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5730772355195891</v>
+        <v>1.053095017502661</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -1841,22 +1841,22 @@
         <v>357</v>
       </c>
       <c r="F37" t="n">
-        <v>0.03959591678410065</v>
+        <v>0.0007712102299163989</v>
       </c>
       <c r="G37" t="n">
-        <v>18.14113033679745</v>
+        <v>17.93231360520937</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I37" t="n">
-        <v>64.33639892132078</v>
+        <v>62.17228694537614</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01992226750801966</v>
+        <v>0.03018929413302932</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5704030986103186</v>
+        <v>0.6878871319923712</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>285</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01385228580827779</v>
+        <v>0.6312434555399422</v>
       </c>
       <c r="G38" t="n">
-        <v>16.33441531920593</v>
+        <v>19.34731180248899</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I38" t="n">
-        <v>106.3694205618118</v>
+        <v>108.8184567997529</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1103401481014605</v>
+        <v>0.07609192930485013</v>
       </c>
       <c r="K38" t="n">
-        <v>1.831453148364556</v>
+        <v>1.261566008694989</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>21.78421446827955</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I39" t="n">
-        <v>32.63617902444754</v>
+        <v>31.16165668302462</v>
       </c>
       <c r="J39" t="n">
-        <v>0.09101213490968435</v>
+        <v>0.08862067238135155</v>
       </c>
       <c r="K39" t="n">
-        <v>1.561887086462106</v>
+        <v>1.41814689403456</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -1955,22 +1955,22 @@
         <v>296</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02350614742421227</v>
+        <v>0.09461038820027579</v>
       </c>
       <c r="G40" t="n">
-        <v>15.0231417621002</v>
+        <v>15.34136046013107</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I40" t="n">
-        <v>224.0583426296516</v>
+        <v>221.8573045094599</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03966653475457497</v>
+        <v>0.045776558050654</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8457746183828772</v>
+        <v>0.8826925940678825</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -1999,16 +1999,16 @@
         <v>3.307725502516798</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I41" t="n">
-        <v>186.6046194189773</v>
+        <v>184.8851312329546</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1191204986973772</v>
+        <v>0.1142150664496884</v>
       </c>
       <c r="K41" t="n">
-        <v>1.953911908547481</v>
+        <v>1.738018796465585</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2031,22 +2031,22 @@
         <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01087653413193132</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>9.322838966671295</v>
+        <v>9.292517850399857</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I42" t="n">
-        <v>65.00225491763509</v>
+        <v>62.61609427293096</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1300991834706158</v>
+        <v>0.2204154585622971</v>
       </c>
       <c r="K42" t="n">
-        <v>2.107030637814985</v>
+        <v>3.065282937717766</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2694533562488602</v>
+        <v>0.6312434555399227</v>
       </c>
       <c r="G43" t="n">
-        <v>10.28322446506008</v>
+        <v>11.31586089924149</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I43" t="n">
-        <v>117.2932088824043</v>
+        <v>119.7625441551378</v>
       </c>
       <c r="J43" t="n">
-        <v>0.02206675687247813</v>
+        <v>0.02636915213894598</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6003120989319204</v>
+        <v>0.6401440174673125</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2107,22 +2107,22 @@
         <v>71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7532651788211991</v>
+        <v>0.1891820467611271</v>
       </c>
       <c r="G44" t="n">
-        <v>23.48836357626373</v>
+        <v>20.2462076234199</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I44" t="n">
-        <v>119.5410306109095</v>
+        <v>122.0105998733219</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02258815603281535</v>
+        <v>0.01662753615676698</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6075840061340094</v>
+        <v>0.5183959022881761</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2145,22 +2145,22 @@
         <v>620</v>
       </c>
       <c r="F45" t="n">
-        <v>0.02438253704903324</v>
+        <v>0.0676523421641429</v>
       </c>
       <c r="G45" t="n">
-        <v>18.53592934140672</v>
+        <v>18.7747959046275</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I45" t="n">
-        <v>30.73070179240706</v>
+        <v>29.73733545847884</v>
       </c>
       <c r="J45" t="n">
-        <v>0.08856328392098459</v>
+        <v>0.1184149986231473</v>
       </c>
       <c r="K45" t="n">
-        <v>1.527733181937113</v>
+        <v>1.790508427234675</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2183,22 +2183,22 @@
         <v>496</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6278781090048844</v>
+        <v>0.6312434555399415</v>
       </c>
       <c r="G46" t="n">
-        <v>22.67235313089035</v>
+        <v>22.69161499715559</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I46" t="n">
-        <v>16.56187712707846</v>
+        <v>14.64375472210871</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02858563535645692</v>
+        <v>0.02733403045755977</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6912303109338906</v>
+        <v>0.6522028090357076</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I47" t="n">
-        <v>32.13316137457676</v>
+        <v>30.25915836979654</v>
       </c>
       <c r="J47" t="n">
-        <v>0.06469285662256342</v>
+        <v>0.05369119003244867</v>
       </c>
       <c r="K47" t="n">
-        <v>1.194814478968614</v>
+        <v>0.9816075510814598</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         <v>12.79325302649799</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I48" t="n">
-        <v>31.02435334595575</v>
+        <v>29.71262768997234</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03950564155998261</v>
+        <v>0.03216611121099414</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8435306554663151</v>
+        <v>0.7125928639506445</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2303,16 +2303,16 @@
         <v>13.11028664827737</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I49" t="n">
-        <v>22.86575624663618</v>
+        <v>21.66026148867186</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01406965660426825</v>
+        <v>0.02583787546889912</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4887772606352653</v>
+        <v>0.6335042635152803</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         <v>430</v>
       </c>
       <c r="F50" t="n">
-        <v>0.662971102711519</v>
+        <v>0.9995621586029051</v>
       </c>
       <c r="G50" t="n">
-        <v>24.82200384932912</v>
+        <v>26.91265150110176</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I50" t="n">
-        <v>29.76607052847566</v>
+        <v>27.6747619224327</v>
       </c>
       <c r="J50" t="n">
-        <v>0.03282859553799315</v>
+        <v>0.03664557256422207</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7504064950350213</v>
+        <v>0.7685759757640189</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -2373,22 +2373,22 @@
         <v>551</v>
       </c>
       <c r="F51" t="n">
-        <v>0.01979795839205038</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>5.463985427432266</v>
+        <v>5.431724311855306</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I51" t="n">
-        <v>19.85438891577595</v>
+        <v>18.59836062288836</v>
       </c>
       <c r="J51" t="n">
-        <v>0.03293370757005129</v>
+        <v>0.01542593962894261</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7518724830938733</v>
+        <v>0.5033786697534475</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>5.066791391008713</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I52" t="n">
-        <v>36.9691194491067</v>
+        <v>35.58856070476764</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02476932865567675</v>
+        <v>0.02014427321902604</v>
       </c>
       <c r="K52" t="n">
-        <v>0.638004624561793</v>
+        <v>0.5623471429954581</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2455,16 +2455,16 @@
         <v>4.862088337329959</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I53" t="n">
-        <v>75.65617738784616</v>
+        <v>73.82711576729665</v>
       </c>
       <c r="J53" t="n">
-        <v>0.01499079446298734</v>
+        <v>0.01649662359391261</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5016242875169425</v>
+        <v>0.5167597920360427</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2487,22 +2487,22 @@
         <v>537</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0001555186650785688</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>6.104357527927181</v>
+        <v>6.104072738754019</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I54" t="n">
-        <v>37.39181909988626</v>
+        <v>36.42098714126841</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04300468536225777</v>
+        <v>0.06515170415924339</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8923315047230211</v>
+        <v>1.124837996263618</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -2531,16 +2531,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I55" t="n">
-        <v>38.13118089805458</v>
+        <v>36.56439641453533</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01457123908905403</v>
+        <v>0.009418109434795489</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4957727864454649</v>
+        <v>0.4282944122963896</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2563,22 +2563,22 @@
         <v>335</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>0.07455010804135394</v>
       </c>
       <c r="G56" t="n">
-        <v>3.741326101798666</v>
+        <v>3.825000981330775</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I56" t="n">
-        <v>114.392893792664</v>
+        <v>116.8611519589317</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>0.006748753540265115</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2925490251978975</v>
+        <v>0.3949335151417579</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>4.362815948444307</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I57" t="n">
-        <v>119.2571500007795</v>
+        <v>121.7073455096708</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1246133205504992</v>
+        <v>0.1790477691445056</v>
       </c>
       <c r="K57" t="n">
-        <v>2.030519800987652</v>
+        <v>2.548280602053383</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I58" t="n">
-        <v>37.53757036126978</v>
+        <v>35.45709376883417</v>
       </c>
       <c r="J58" t="n">
-        <v>0.001464102699613332</v>
+        <v>0.045054791907046</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3129687338890857</v>
+        <v>0.8736721535429079</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3007404155744692</v>
+        <v>0.6462375520504614</v>
       </c>
       <c r="G59" t="n">
-        <v>22.79699768242308</v>
+        <v>24.96434429224193</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I59" t="n">
-        <v>32.21306747033</v>
+        <v>30.26266093263617</v>
       </c>
       <c r="J59" t="n">
-        <v>0.0333966916865259</v>
+        <v>0.05087484909012832</v>
       </c>
       <c r="K59" t="n">
-        <v>0.7583296809322186</v>
+        <v>0.9464096740499082</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2715,22 +2715,22 @@
         <v>378</v>
       </c>
       <c r="F60" t="n">
-        <v>0.2617302669561336</v>
+        <v>0.03032215861681859</v>
       </c>
       <c r="G60" t="n">
-        <v>24.26695667150904</v>
+        <v>22.70493408641378</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I60" t="n">
-        <v>26.09363336287619</v>
+        <v>24.07313538594742</v>
       </c>
       <c r="J60" t="n">
-        <v>0.04558261822018405</v>
+        <v>0.06877232187720636</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9282857024703508</v>
+        <v>1.17008750966597</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>4.710418346601499</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I61" t="n">
-        <v>28.32493008076046</v>
+        <v>26.39782369780529</v>
       </c>
       <c r="J61" t="n">
-        <v>0.02068443474840413</v>
+        <v>0.03018006709735797</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5810329765736116</v>
+        <v>0.6877718149645051</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2797,16 +2797,16 @@
         <v>13.57276718285553</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I62" t="n">
-        <v>89.6869651653345</v>
+        <v>87.26464665313321</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0595828014318503</v>
+        <v>0.0645442386648479</v>
       </c>
       <c r="K62" t="n">
-        <v>1.123544998748535</v>
+        <v>1.117246054730066</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -2829,22 +2829,22 @@
         <v>659</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04996627594184065</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>4.628718334895234</v>
+        <v>4.560359086738675</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I63" t="n">
-        <v>34.45814610010484</v>
+        <v>33.24286973707032</v>
       </c>
       <c r="J63" t="n">
-        <v>0.07380975299933472</v>
+        <v>0.1378608822711742</v>
       </c>
       <c r="K63" t="n">
-        <v>1.321967012893035</v>
+        <v>2.033537888308802</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -2867,22 +2867,22 @@
         <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>0.1220227996042205</v>
+        <v>0.075431577324564</v>
       </c>
       <c r="G64" t="n">
-        <v>10.42780605421914</v>
+        <v>10.28719993112518</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I64" t="n">
-        <v>179.0094197568594</v>
+        <v>176.7584856130123</v>
       </c>
       <c r="J64" t="n">
-        <v>0.03608863817982474</v>
+        <v>0.05799678994524692</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7958740165993445</v>
+        <v>1.035417789039679</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -2905,22 +2905,22 @@
         <v>692</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01095612732349916</v>
+        <v>0.3156217277699857</v>
       </c>
       <c r="G65" t="n">
-        <v>11.14985267602592</v>
+        <v>12.16560702396568</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I65" t="n">
-        <v>28.70462788006087</v>
+        <v>27.21472416797106</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0879171320284878</v>
+        <v>0.2134404065358921</v>
       </c>
       <c r="K65" t="n">
-        <v>1.518721359598059</v>
+        <v>2.978110600084593</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -2943,22 +2943,22 @@
         <v>489</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6278781090048652</v>
+        <v>0.6312434555399274</v>
       </c>
       <c r="G66" t="n">
-        <v>19.69333708090076</v>
+        <v>19.71006804936173</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I66" t="n">
-        <v>89.29905708681602</v>
+        <v>86.85206065970853</v>
       </c>
       <c r="J66" t="n">
-        <v>0.02305821406316307</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6141398632130171</v>
+        <v>0.3105893955584261</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -2981,22 +2981,22 @@
         <v>259</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03959591678410077</v>
+        <v>0.001547658636490593</v>
       </c>
       <c r="G67" t="n">
-        <v>4.464336337202671</v>
+        <v>4.413976484143277</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I67" t="n">
-        <v>18.72135083536519</v>
+        <v>16.86802251777535</v>
       </c>
       <c r="J67" t="n">
-        <v>0.04535931986248213</v>
+        <v>0.04893793645695847</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9251713803557218</v>
+        <v>0.9222026571867428</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3019,22 +3019,22 @@
         <v>627</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6348042519090717</v>
+        <v>0.6312434555399909</v>
       </c>
       <c r="G68" t="n">
-        <v>22.2365273632229</v>
+        <v>22.21657348203934</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I68" t="n">
-        <v>112.6277355166075</v>
+        <v>115.0717256223206</v>
       </c>
       <c r="J68" t="n">
-        <v>0.02723299971292755</v>
+        <v>0.05206878247586127</v>
       </c>
       <c r="K68" t="n">
-        <v>0.6723652232501631</v>
+        <v>0.9613311346811162</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>0.3639053304443413</v>
+        <v>0.009446383408605374</v>
       </c>
       <c r="G69" t="n">
-        <v>13.34251488077438</v>
+        <v>12.06335110328222</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I69" t="n">
-        <v>15.5281666491021</v>
+        <v>14.53484343025496</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1041968290979895</v>
+        <v>0.06640070973224391</v>
       </c>
       <c r="K69" t="n">
-        <v>1.745772830664815</v>
+        <v>1.140447734385017</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>0.392389048075213</v>
+        <v>0.02976497305343656</v>
       </c>
       <c r="G70" t="n">
-        <v>20.78918259039171</v>
+        <v>18.76577415155641</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I70" t="n">
-        <v>28.61123237468256</v>
+        <v>27.37316340460314</v>
       </c>
       <c r="J70" t="n">
-        <v>0.04581176224268676</v>
+        <v>0.05413005788255321</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9314815535462816</v>
+        <v>0.9870924042783722</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3133,22 +3133,22 @@
         <v>421</v>
       </c>
       <c r="F71" t="n">
-        <v>0.01788227022763862</v>
+        <v>0.6312563654197627</v>
       </c>
       <c r="G71" t="n">
-        <v>13.60962402706039</v>
+        <v>16.1005979932334</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I71" t="n">
-        <v>134.9245575123915</v>
+        <v>134.7042397844755</v>
       </c>
       <c r="J71" t="n">
-        <v>0.04916583620829132</v>
+        <v>0.0606884503987622</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9782605215274428</v>
+        <v>1.069057442616375</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -3171,22 +3171,22 @@
         <v>694</v>
       </c>
       <c r="F72" t="n">
-        <v>0.7534206974862414</v>
+        <v>0.2063670837128264</v>
       </c>
       <c r="G72" t="n">
-        <v>26.91372734536539</v>
+        <v>23.31105106649919</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I72" t="n">
-        <v>24.04223284282924</v>
+        <v>22.5455495730006</v>
       </c>
       <c r="J72" t="n">
-        <v>0.007866550000008332</v>
+        <v>0.07804509625251528</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4022630906437573</v>
+        <v>1.285976167640223</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>250</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>0.1891691368813207</v>
       </c>
       <c r="G73" t="n">
-        <v>17.30370795523318</v>
+        <v>18.28570620485455</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I73" t="n">
-        <v>41.40247703874948</v>
+        <v>43.80983571802437</v>
       </c>
       <c r="J73" t="n">
-        <v>0.027870700778255</v>
+        <v>0.03760779108758551</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6812591826626319</v>
+        <v>0.7806015259216375</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -3247,22 +3247,22 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6517060518162718</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>24.89990510430726</v>
+        <v>27.07616621994333</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I74" t="n">
-        <v>76.74715597753509</v>
+        <v>74.50890895960447</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02624566523883781</v>
+        <v>0.01472370166717854</v>
       </c>
       <c r="K74" t="n">
-        <v>0.658594958126682</v>
+        <v>0.4946022872304228</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3285,22 +3285,22 @@
         <v>564</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6489257396709005</v>
+        <v>0.6543106743578074</v>
       </c>
       <c r="G75" t="n">
-        <v>23.80574480858942</v>
+        <v>23.83793567779642</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I75" t="n">
-        <v>107.1889235213026</v>
+        <v>109.6439904846215</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05636115635940101</v>
+        <v>0.0693436007569946</v>
       </c>
       <c r="K75" t="n">
-        <v>1.078613004631463</v>
+        <v>1.177227200553304</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3323,22 +3323,22 @@
         <v>521</v>
       </c>
       <c r="F76" t="n">
-        <v>0.6388342363284196</v>
+        <v>0.00445934016114399</v>
       </c>
       <c r="G76" t="n">
-        <v>20.85156522317409</v>
+        <v>17.52146665824808</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I76" t="n">
-        <v>113.6961743438249</v>
+        <v>116.1616580623895</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1222855381731336</v>
+        <v>0.1029304058911647</v>
       </c>
       <c r="K76" t="n">
-        <v>1.998054429497769</v>
+        <v>1.596986122220374</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>607</v>
       </c>
       <c r="F77" t="n">
-        <v>0.02350614742421015</v>
+        <v>0.09458456844065385</v>
       </c>
       <c r="G77" t="n">
-        <v>17.66068272058278</v>
+        <v>18.03463370901911</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I77" t="n">
-        <v>112.707936042604</v>
+        <v>115.1760411915495</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05688250204756373</v>
+        <v>0.1045702434882503</v>
       </c>
       <c r="K77" t="n">
-        <v>1.085884166061942</v>
+        <v>1.617480374612408</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3405,16 +3405,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I78" t="n">
-        <v>52.24254979890153</v>
+        <v>49.77025100071132</v>
       </c>
       <c r="J78" t="n">
-        <v>0.09775400427046829</v>
+        <v>0.06489944498710261</v>
       </c>
       <c r="K78" t="n">
-        <v>1.655915332170288</v>
+        <v>1.121685328492585</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3443,16 +3443,16 @@
         <v>19.31962732559818</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I79" t="n">
-        <v>92.10226766105751</v>
+        <v>91.40235674066331</v>
       </c>
       <c r="J79" t="n">
-        <v>0.06402089438294183</v>
+        <v>0.07339447061342587</v>
       </c>
       <c r="K79" t="n">
-        <v>1.185442682039222</v>
+        <v>1.227853890289247</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -3475,22 +3475,22 @@
         <v>421</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>0.03771578866228487</v>
       </c>
       <c r="G80" t="n">
-        <v>2.935153317971652</v>
+        <v>2.968363804641259</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I80" t="n">
-        <v>29.84077436848336</v>
+        <v>27.69706104912006</v>
       </c>
       <c r="J80" t="n">
-        <v>0.09927476336792763</v>
+        <v>0.1291293308948217</v>
       </c>
       <c r="K80" t="n">
-        <v>1.677125222547374</v>
+        <v>1.924413290849261</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3513,22 +3513,22 @@
         <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6396311827169713</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>12.73059050808525</v>
+        <v>10.68101703958944</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I81" t="n">
-        <v>114.1935157735869</v>
+        <v>116.6657330243738</v>
       </c>
       <c r="J81" t="n">
-        <v>0.01478244525448202</v>
+        <v>0.041574142364369</v>
       </c>
       <c r="K81" t="n">
-        <v>0.4987184598418472</v>
+        <v>0.830171925018681</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -3551,22 +3551,22 @@
         <v>340</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>0.005869271986388712</v>
       </c>
       <c r="G82" t="n">
-        <v>4.411928036584459</v>
+        <v>4.419696478273785</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I82" t="n">
-        <v>32.0555241205651</v>
+        <v>31.30922545993537</v>
       </c>
       <c r="J82" t="n">
-        <v>0.033964432021305</v>
+        <v>0.02488523194201968</v>
       </c>
       <c r="K82" t="n">
-        <v>0.7662479043269905</v>
+        <v>0.6215983791068462</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3589,22 +3589,22 @@
         <v>364</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>0.631243455539904</v>
       </c>
       <c r="G83" t="n">
-        <v>19.96717947032079</v>
+        <v>23.74842488019001</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I83" t="n">
-        <v>75.36016557462568</v>
+        <v>72.90972109658848</v>
       </c>
       <c r="J83" t="n">
-        <v>0.01411743206003747</v>
+        <v>0.03234371530215913</v>
       </c>
       <c r="K83" t="n">
-        <v>0.4894435806206419</v>
+        <v>0.7148125124552659</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -3627,22 +3627,22 @@
         <v>241</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0001307138095888819</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>7.583994112060824</v>
+        <v>7.583696723893961</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I84" t="n">
-        <v>26.64035108623135</v>
+        <v>24.62229984380533</v>
       </c>
       <c r="J84" t="n">
-        <v>0.01656405556847183</v>
+        <v>0.03052300254622423</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5235664186786803</v>
+        <v>0.6920577306281853</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3665,22 +3665,22 @@
         <v>126</v>
       </c>
       <c r="F85" t="n">
-        <v>0.9418171635072538</v>
+        <v>0.8171607952459812</v>
       </c>
       <c r="G85" t="n">
-        <v>25.92259772026094</v>
+        <v>25.16673733824778</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I85" t="n">
-        <v>19.91894964181764</v>
+        <v>17.82274990983389</v>
       </c>
       <c r="J85" t="n">
-        <v>0.008787704408395847</v>
+        <v>0.0201327640972012</v>
       </c>
       <c r="K85" t="n">
-        <v>0.4151103483421719</v>
+        <v>0.5622033050642458</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3703,22 +3703,22 @@
         <v>474</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1253870698163189</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G86" t="n">
-        <v>10.64019797122157</v>
+        <v>10.48651791966895</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I86" t="n">
-        <v>29.35939248861886</v>
+        <v>26.95889411917921</v>
       </c>
       <c r="J86" t="n">
-        <v>0.03139190959258149</v>
+        <v>0.05704510055548651</v>
       </c>
       <c r="K86" t="n">
-        <v>0.7303691653492157</v>
+        <v>1.023523829182169</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -3747,16 +3747,16 @@
         <v>10.61501705132875</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I87" t="n">
-        <v>28.36096943049547</v>
+        <v>26.79523771556672</v>
       </c>
       <c r="J87" t="n">
-        <v>0.03391107606012851</v>
+        <v>0.04449431440052245</v>
       </c>
       <c r="K87" t="n">
-        <v>0.765503753534529</v>
+        <v>0.8666674553342765</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>3.240904040541774</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I88" t="n">
-        <v>78.4977001288608</v>
+        <v>76.10378933863043</v>
       </c>
       <c r="J88" t="n">
-        <v>0.006365307707765795</v>
+        <v>0.003743268412839851</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3813253993939698</v>
+        <v>0.3573717645931487</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>0.01175307371210396</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>3.341841822398893</v>
+        <v>3.330100148644182</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I89" t="n">
-        <v>32.26398979320266</v>
+        <v>31.57034842915032</v>
       </c>
       <c r="J89" t="n">
-        <v>0.03665892866202262</v>
+        <v>0.02403588599167712</v>
       </c>
       <c r="K89" t="n">
-        <v>0.8038278066708425</v>
+        <v>0.6109834802257564</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -3855,22 +3855,22 @@
         <v>507</v>
       </c>
       <c r="F90" t="n">
-        <v>0.0001555186650783455</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>5.53779363908311</v>
+        <v>5.537535282054643</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I90" t="n">
-        <v>67.90190403148313</v>
+        <v>65.73757519951349</v>
       </c>
       <c r="J90" t="n">
-        <v>0.05816908955193113</v>
+        <v>0.05186784461347131</v>
       </c>
       <c r="K90" t="n">
-        <v>1.103828086288197</v>
+        <v>0.9588198669346915</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -3893,22 +3893,22 @@
         <v>643</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>0.6312434555399501</v>
       </c>
       <c r="G91" t="n">
-        <v>10.51627310409919</v>
+        <v>12.50777167618921</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I91" t="n">
-        <v>99.52217776627954</v>
+        <v>101.9961438580741</v>
       </c>
       <c r="J91" t="n">
-        <v>0.01752283293190116</v>
+        <v>0.006518371940374905</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5369384003477962</v>
+        <v>0.3920542674266049</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -3931,22 +3931,22 @@
         <v>327</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>2.581975960509618e-05</v>
       </c>
       <c r="G92" t="n">
-        <v>16.91718590664535</v>
+        <v>16.91731694594734</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I92" t="n">
-        <v>90.36057707337689</v>
+        <v>87.92429791115475</v>
       </c>
       <c r="J92" t="n">
-        <v>0.05270558925860634</v>
+        <v>0.1123175579396413</v>
       </c>
       <c r="K92" t="n">
-        <v>1.027629139005757</v>
+        <v>1.714304241810873</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I93" t="n">
-        <v>95.74067450850278</v>
+        <v>96.10328747417087</v>
       </c>
       <c r="J93" t="n">
-        <v>0.03312370789239446</v>
+        <v>0.02720717487894838</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7545224005036999</v>
+        <v>0.6506174018892805</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4013,16 +4013,16 @@
         <v>11.48356342778669</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I94" t="n">
-        <v>22.38358326184152</v>
+        <v>21.81114993983779</v>
       </c>
       <c r="J94" t="n">
-        <v>0.04358819169264747</v>
+        <v>0.01115619346139485</v>
       </c>
       <c r="K94" t="n">
-        <v>0.9004696150408074</v>
+        <v>0.4500165223291137</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -4045,22 +4045,22 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>0.09993255188368243</v>
+        <v>0.07543157732456927</v>
       </c>
       <c r="G95" t="n">
-        <v>11.68868782921822</v>
+        <v>11.60527330418356</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I95" t="n">
-        <v>29.86446507373608</v>
+        <v>28.8825999298514</v>
       </c>
       <c r="J95" t="n">
-        <v>0.03585694786875768</v>
+        <v>0.04130077482271573</v>
       </c>
       <c r="K95" t="n">
-        <v>0.7926426526657833</v>
+        <v>0.8267554504821847</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -4083,22 +4083,22 @@
         <v>640</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0.8823550343346107</v>
       </c>
       <c r="G96" t="n">
-        <v>24.6460742997744</v>
+        <v>23.97696201559357</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I96" t="n">
-        <v>87.88382431618579</v>
+        <v>85.50003233637676</v>
       </c>
       <c r="J96" t="n">
-        <v>0.02979561411851748</v>
+        <v>0.0370673771684086</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7081057759202788</v>
+        <v>0.773847577069956</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4121,22 +4121,22 @@
         <v>33</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>0.2467977957428397</v>
       </c>
       <c r="G97" t="n">
-        <v>4.685296148590822</v>
+        <v>5.032192377153212</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I97" t="n">
-        <v>111.799154532671</v>
+        <v>114.261286048223</v>
       </c>
       <c r="J97" t="n">
-        <v>0.05364863844680842</v>
+        <v>0.0871409368736942</v>
       </c>
       <c r="K97" t="n">
-        <v>1.040781761229344</v>
+        <v>1.399653554803112</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -4159,22 +4159,22 @@
         <v>667</v>
       </c>
       <c r="F98" t="n">
-        <v>0.04996627594184144</v>
+        <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>7.667482749566142</v>
+        <v>7.554245495084205</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I98" t="n">
-        <v>28.98079984560107</v>
+        <v>28.27017442628089</v>
       </c>
       <c r="J98" t="n">
-        <v>0.01913769729316605</v>
+        <v>0.02955218549538835</v>
       </c>
       <c r="K98" t="n">
-        <v>0.5594607683767053</v>
+        <v>0.6799247183703363</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -4197,22 +4197,22 @@
         <v>246</v>
       </c>
       <c r="F99" t="n">
-        <v>0.02381718475436896</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>7.255299012986369</v>
+        <v>7.203826552603831</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I99" t="n">
-        <v>109.9008066341507</v>
+        <v>112.3371716389262</v>
       </c>
       <c r="J99" t="n">
-        <v>0.04004873036340489</v>
+        <v>0.06016662922727597</v>
       </c>
       <c r="K99" t="n">
-        <v>0.8511050661700572</v>
+        <v>1.062535860960391</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -4235,22 +4235,22 @@
         <v>478</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1521911171540122</v>
+        <v>0.07543157732456197</v>
       </c>
       <c r="G100" t="n">
-        <v>22.69126897379678</v>
+        <v>22.19155325258548</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I100" t="n">
-        <v>117.691099971433</v>
+        <v>120.1487238224961</v>
       </c>
       <c r="J100" t="n">
-        <v>0.03818266096596604</v>
+        <v>0.02850576900076543</v>
       </c>
       <c r="K100" t="n">
-        <v>0.8250791640913945</v>
+        <v>0.6668468844518407</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -4279,16 +4279,16 @@
         <v>14.47703643706128</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I101" t="n">
-        <v>17.19598872091978</v>
+        <v>15.79500210769504</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1210433398850784</v>
+        <v>0.1510799650706089</v>
       </c>
       <c r="K101" t="n">
-        <v>1.980729601679695</v>
+        <v>2.198746455159752</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4311,22 +4311,22 @@
         <v>130</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>0.6312434555399306</v>
       </c>
       <c r="G102" t="n">
-        <v>20.62180903800634</v>
+        <v>24.52702363699705</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I102" t="n">
-        <v>34.75904379211874</v>
+        <v>33.35705974101977</v>
       </c>
       <c r="J102" t="n">
-        <v>0.07335889381491932</v>
+        <v>0.08375560123379357</v>
       </c>
       <c r="K102" t="n">
-        <v>1.315678920391777</v>
+        <v>1.357344533983503</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4355,16 +4355,16 @@
         <v>10.02719427357424</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I103" t="n">
-        <v>32.43696780351648</v>
+        <v>31.3416252250965</v>
       </c>
       <c r="J103" t="n">
-        <v>0.03153340987350037</v>
+        <v>0.0283235820892883</v>
       </c>
       <c r="K103" t="n">
-        <v>0.7323426570426932</v>
+        <v>0.6645699610827378</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>155</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>0.2268849255436165</v>
       </c>
       <c r="G104" t="n">
-        <v>11.89204612335489</v>
+        <v>12.70148392313247</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I104" t="n">
-        <v>74.25105531851601</v>
+        <v>71.83905967424685</v>
       </c>
       <c r="J104" t="n">
-        <v>0.01136338273415329</v>
+        <v>0.01422955966229241</v>
       </c>
       <c r="K104" t="n">
-        <v>0.451033102332083</v>
+        <v>0.4884266324072617</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -4431,16 +4431,16 @@
         <v>6.688712506902953</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I105" t="n">
-        <v>21.70621962362333</v>
+        <v>19.58358541648231</v>
       </c>
       <c r="J105" t="n">
-        <v>0.02606127987389218</v>
+        <v>0.02286123399355125</v>
       </c>
       <c r="K105" t="n">
-        <v>0.6560233520227505</v>
+        <v>0.5963029932280292</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4463,22 +4463,22 @@
         <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>0.300740415574471</v>
+        <v>0.6689592442022074</v>
       </c>
       <c r="G106" t="n">
-        <v>16.79001038526069</v>
+        <v>18.49124112075864</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I106" t="n">
-        <v>114.3617270008397</v>
+        <v>116.8383245040687</v>
       </c>
       <c r="J106" t="n">
-        <v>0.03454202424980491</v>
+        <v>0.03075560019297903</v>
       </c>
       <c r="K106" t="n">
-        <v>0.774303531197549</v>
+        <v>0.6949646739052868</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -4507,16 +4507,16 @@
         <v>4.560359086738675</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I107" t="n">
-        <v>29.96261113293433</v>
+        <v>28.30789211632625</v>
       </c>
       <c r="J107" t="n">
-        <v>0.02992317039317353</v>
+        <v>0.06756024431723888</v>
       </c>
       <c r="K107" t="n">
-        <v>0.7098847918123319</v>
+        <v>1.154939287990334</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4545,16 +4545,16 @@
         <v>3.08676659305494</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I108" t="n">
-        <v>37.857318973864</v>
+        <v>36.82151706568144</v>
       </c>
       <c r="J108" t="n">
-        <v>0.05058973627436752</v>
+        <v>0.07802484997133013</v>
       </c>
       <c r="K108" t="n">
-        <v>0.9981195277039349</v>
+        <v>1.285723135024465</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -4577,22 +4577,22 @@
         <v>198</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6278781090048919</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>23.19830689252693</v>
+        <v>19.52122242586258</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I109" t="n">
-        <v>120.6689290125666</v>
+        <v>123.1377831718758</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01242670706159285</v>
+        <v>0.01826396447491734</v>
       </c>
       <c r="K109" t="n">
-        <v>0.4658631911068007</v>
+        <v>0.5388475464224798</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>5.431724311855306</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I110" t="n">
-        <v>38.61178886226426</v>
+        <v>37.16874595536945</v>
       </c>
       <c r="J110" t="n">
-        <v>0.03439530009592531</v>
+        <v>0.02502410914857784</v>
       </c>
       <c r="K110" t="n">
-        <v>0.7722571826176483</v>
+        <v>0.6233340293491398</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>13.21653808680624</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I111" t="n">
-        <v>112.4181382471772</v>
+        <v>114.8878799244959</v>
       </c>
       <c r="J111" t="n">
-        <v>0.02834097285106757</v>
+        <v>0.01960457304054154</v>
       </c>
       <c r="K111" t="n">
-        <v>0.6878180249726489</v>
+        <v>0.5556021142843557</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -4691,22 +4691,22 @@
         <v>254</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1.290987980249197e-05</v>
       </c>
       <c r="G112" t="n">
-        <v>5.144277597486356</v>
+        <v>5.144297521087992</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I112" t="n">
-        <v>87.35729599894373</v>
+        <v>84.96294058987614</v>
       </c>
       <c r="J112" t="n">
-        <v>0.09512833865869323</v>
+        <v>0.06427391363261695</v>
       </c>
       <c r="K112" t="n">
-        <v>1.619295409997426</v>
+        <v>1.113867604663869</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>376</v>
       </c>
       <c r="F113" t="n">
-        <v>0.6280336276699486</v>
+        <v>0.6336257962135482</v>
       </c>
       <c r="G113" t="n">
-        <v>13.44658911747394</v>
+        <v>13.46557135098619</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I113" t="n">
-        <v>28.36726778123007</v>
+        <v>27.9360886974725</v>
       </c>
       <c r="J113" t="n">
-        <v>0.07793086485757753</v>
+        <v>0.03476251882118998</v>
       </c>
       <c r="K113" t="n">
-        <v>1.379443789386476</v>
+        <v>0.7450420729275109</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4767,22 +4767,22 @@
         <v>366</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>0.004472250040946481</v>
       </c>
       <c r="G114" t="n">
-        <v>14.18555800805876</v>
+        <v>14.20459041677348</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I114" t="n">
-        <v>37.97081292361351</v>
+        <v>36.07556935275215</v>
       </c>
       <c r="J114" t="n">
-        <v>0.008901543649641774</v>
+        <v>0.03210949831980147</v>
       </c>
       <c r="K114" t="n">
-        <v>0.4166980540027663</v>
+        <v>0.7118853311542215</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -4811,16 +4811,16 @@
         <v>20.08938572978278</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I115" t="n">
-        <v>52.01839615613393</v>
+        <v>49.759661154374</v>
       </c>
       <c r="J115" t="n">
-        <v>0.0376846071448428</v>
+        <v>0.0335570604949422</v>
       </c>
       <c r="K115" t="n">
-        <v>0.818132852235979</v>
+        <v>0.7299765766673272</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -4843,22 +4843,22 @@
         <v>447</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>0.3156217277700383</v>
       </c>
       <c r="G116" t="n">
-        <v>6.463893795538414</v>
+        <v>7.075937393899374</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I116" t="n">
-        <v>111.3173890387625</v>
+        <v>113.7599239359851</v>
       </c>
       <c r="J116" t="n">
-        <v>0.023242272593401</v>
+        <v>0.01976436379563859</v>
       </c>
       <c r="K116" t="n">
-        <v>0.6167069109826711</v>
+        <v>0.5575991364716094</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>388</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6278781090048984</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>21.53887003295733</v>
+        <v>23.56226241259528</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I117" t="n">
-        <v>30.06878174157317</v>
+        <v>28.01233718918579</v>
       </c>
       <c r="J117" t="n">
-        <v>0.02545860113888262</v>
+        <v>0.04150741498182098</v>
       </c>
       <c r="K117" t="n">
-        <v>0.6476178459018211</v>
+        <v>0.8293379840102363</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -4925,16 +4925,16 @@
         <v>8.030018742194814</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I118" t="n">
-        <v>22.60566006711137</v>
+        <v>20.64702568718556</v>
       </c>
       <c r="J118" t="n">
-        <v>0.02545071161866817</v>
+        <v>0.04071063071710519</v>
       </c>
       <c r="K118" t="n">
-        <v>0.6475078114728601</v>
+        <v>0.8193799870402261</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -4957,22 +4957,22 @@
         <v>165</v>
       </c>
       <c r="F119" t="n">
-        <v>0.00402998441935881</v>
+        <v>0.6312434555399813</v>
       </c>
       <c r="G119" t="n">
-        <v>13.41045146934131</v>
+        <v>15.93076916164583</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I119" t="n">
-        <v>22.27046939903661</v>
+        <v>20.38496747809766</v>
       </c>
       <c r="J119" t="n">
-        <v>0.02329472447284213</v>
+        <v>0.02946873963826681</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6174384526284695</v>
+        <v>0.6788818343311132</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -5001,16 +5001,16 @@
         <v>3.330100148644182</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I120" t="n">
-        <v>105.0448656904473</v>
+        <v>107.4812760562148</v>
       </c>
       <c r="J120" t="n">
-        <v>0.05841487720795295</v>
+        <v>0.07055885507153563</v>
       </c>
       <c r="K120" t="n">
-        <v>1.10725606462413</v>
+        <v>1.192415124459291</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5033,22 +5033,22 @@
         <v>57</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>0.1891691368813245</v>
       </c>
       <c r="G121" t="n">
-        <v>7.701882886671284</v>
+        <v>8.138970448081079</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I121" t="n">
-        <v>28.55775086481542</v>
+        <v>26.59223122164555</v>
       </c>
       <c r="J121" t="n">
-        <v>0.04197545962109436</v>
+        <v>0.06125104359159268</v>
       </c>
       <c r="K121" t="n">
-        <v>0.8779769858647609</v>
+        <v>1.076088582107505</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -5071,22 +5071,22 @@
         <v>137</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>0.000773829318245072</v>
       </c>
       <c r="G122" t="n">
-        <v>5.670752331040389</v>
+        <v>5.672068789363469</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I122" t="n">
-        <v>119.6819922678943</v>
+        <v>122.1576443448918</v>
       </c>
       <c r="J122" t="n">
-        <v>0.02682005151614773</v>
+        <v>0.04406069310967198</v>
       </c>
       <c r="K122" t="n">
-        <v>0.6666058718842908</v>
+        <v>0.8612481722338992</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>2.935153317971652</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I123" t="n">
-        <v>36.01472799534469</v>
+        <v>33.67265981416313</v>
       </c>
       <c r="J123" t="n">
-        <v>0.01449293313782848</v>
+        <v>0.04382919116351536</v>
       </c>
       <c r="K123" t="n">
-        <v>0.4946806603854321</v>
+        <v>0.8583549227302818</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -5153,16 +5153,16 @@
         <v>20.29361436511495</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I124" t="n">
-        <v>24.52804765846969</v>
+        <v>22.45476873880682</v>
       </c>
       <c r="J124" t="n">
-        <v>0.03964110007937156</v>
+        <v>0.03655108665643</v>
       </c>
       <c r="K124" t="n">
-        <v>0.8454198832550437</v>
+        <v>0.7673951161196112</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -5191,16 +5191,16 @@
         <v>12.02926119925908</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I125" t="n">
-        <v>61.04349062103338</v>
+        <v>58.88849202640949</v>
       </c>
       <c r="J125" t="n">
-        <v>0.0376068614649033</v>
+        <v>0.04754116054361431</v>
       </c>
       <c r="K125" t="n">
-        <v>0.81704854022919</v>
+        <v>0.9047461248117897</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -5229,16 +5229,16 @@
         <v>20.00788726977439</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I126" t="n">
-        <v>66.86496916882906</v>
+        <v>64.53856166061541</v>
       </c>
       <c r="J126" t="n">
-        <v>0.07119085719139287</v>
+        <v>0.1042154661721067</v>
       </c>
       <c r="K126" t="n">
-        <v>1.285441508565456</v>
+        <v>1.613046462453706</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -5267,16 +5267,16 @@
         <v>11.24748896420885</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I127" t="n">
-        <v>19.58634227535515</v>
+        <v>18.24106175676632</v>
       </c>
       <c r="J127" t="n">
-        <v>0.0665466746447657</v>
+        <v>0.1308686962521367</v>
       </c>
       <c r="K127" t="n">
-        <v>1.220669512218565</v>
+        <v>1.946151414611108</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>11.07986791437515</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I128" t="n">
-        <v>178.3363199421134</v>
+        <v>177.114136893939</v>
       </c>
       <c r="J128" t="n">
-        <v>0.03436365057973721</v>
+        <v>0.04708702744975365</v>
       </c>
       <c r="K128" t="n">
-        <v>0.7718157696614747</v>
+        <v>0.8990704906747893</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -5343,16 +5343,16 @@
         <v>5.484544739538552</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I129" t="n">
-        <v>107.3533565261391</v>
+        <v>109.8301137596924</v>
       </c>
       <c r="J129" t="n">
-        <v>0.2314306568740783</v>
+        <v>0.1683423269112377</v>
       </c>
       <c r="K129" t="n">
-        <v>3.520291585079175</v>
+        <v>2.414486843764838</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -5375,22 +5375,22 @@
         <v>575</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>0.631243455539969</v>
       </c>
       <c r="G130" t="n">
-        <v>7.672279257169932</v>
+        <v>9.125202078219003</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I130" t="n">
-        <v>64.38901738476238</v>
+        <v>62.24301249667668</v>
       </c>
       <c r="J130" t="n">
-        <v>0.05846440095959608</v>
+        <v>0.0009098020923751557</v>
       </c>
       <c r="K130" t="n">
-        <v>1.107946767934843</v>
+        <v>0.3219598591586484</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -5419,16 +5419,16 @@
         <v>3.533718721120853</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I131" t="n">
-        <v>109.7531129049286</v>
+        <v>112.2197855381751</v>
       </c>
       <c r="J131" t="n">
-        <v>0.01665807758425031</v>
+        <v>0.02594674615074104</v>
       </c>
       <c r="K131" t="n">
-        <v>0.5248777352777563</v>
+        <v>0.6348649002245048</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -5457,16 +5457,16 @@
         <v>6.408090589247315</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I132" t="n">
-        <v>52.14568502904427</v>
+        <v>49.8197164717041</v>
       </c>
       <c r="J132" t="n">
-        <v>0.006922352433483121</v>
+        <v>0.0502133434292877</v>
       </c>
       <c r="K132" t="n">
-        <v>0.3890944520909662</v>
+        <v>0.9381423529468174</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -5489,22 +5489,22 @@
         <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>0.09993255188367382</v>
+        <v>0.001547658636490593</v>
       </c>
       <c r="G133" t="n">
-        <v>11.6886878292182</v>
+        <v>11.35373261668167</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I133" t="n">
-        <v>58.55549166472917</v>
+        <v>56.35946125940621</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03411184974807228</v>
+        <v>0.03309718421798928</v>
       </c>
       <c r="K133" t="n">
-        <v>0.7683039261055857</v>
+        <v>0.7242291657616786</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -5533,16 +5533,16 @@
         <v>5.697522180737868</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I134" t="n">
-        <v>116.8909275060781</v>
+        <v>119.3633934402498</v>
       </c>
       <c r="J134" t="n">
-        <v>0.06248419448943771</v>
+        <v>0.06807002443881705</v>
       </c>
       <c r="K134" t="n">
-        <v>1.164010466813185</v>
+        <v>1.161310383819965</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -5565,22 +5565,22 @@
         <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135" t="n">
-        <v>14.73369610790178</v>
+        <v>19.15380494027231</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I135" t="n">
-        <v>108.9439042816867</v>
+        <v>111.4167069146978</v>
       </c>
       <c r="J135" t="n">
-        <v>0.07228963411735068</v>
+        <v>0.1347645521804704</v>
       </c>
       <c r="K135" t="n">
-        <v>1.300766051543611</v>
+        <v>1.99484078166805</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>97</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1197305102757296</v>
+        <v>0.1891691368813415</v>
       </c>
       <c r="G136" t="n">
-        <v>19.97189151615194</v>
+        <v>20.37351186851368</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I136" t="n">
-        <v>108.1471860069701</v>
+        <v>110.5877853747244</v>
       </c>
       <c r="J136" t="n">
-        <v>0.04613933539271293</v>
+        <v>0.1102715753031118</v>
       </c>
       <c r="K136" t="n">
-        <v>0.9360501868124834</v>
+        <v>1.68873409717138</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -5641,22 +5641,22 @@
         <v>496</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1267922607553682</v>
+        <v>2.581975960509618e-05</v>
       </c>
       <c r="G137" t="n">
-        <v>14.01482586396705</v>
+        <v>13.50137352021813</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I137" t="n">
-        <v>35.2002921968334</v>
+        <v>33.55889291631487</v>
       </c>
       <c r="J137" t="n">
-        <v>0.05233815901992576</v>
+        <v>0.05281953057414808</v>
       </c>
       <c r="K137" t="n">
-        <v>1.022504622508265</v>
+        <v>0.9707137839364295</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -5685,16 +5685,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I138" t="n">
-        <v>110.3267621811903</v>
+        <v>112.7717331017953</v>
       </c>
       <c r="J138" t="n">
-        <v>0.0404202175871902</v>
+        <v>0.04267430051765795</v>
       </c>
       <c r="K138" t="n">
-        <v>0.8562861650739781</v>
+        <v>0.8439214078362052</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -5717,22 +5717,22 @@
         <v>498</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2946865611692421</v>
+        <v>0.6334731256205066</v>
       </c>
       <c r="G139" t="n">
-        <v>8.254140776448388</v>
+        <v>9.024917144126892</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I139" t="n">
-        <v>72.24811473681838</v>
+        <v>69.87362953542686</v>
       </c>
       <c r="J139" t="n">
-        <v>0.08231832410929341</v>
+        <v>0.06979810608123287</v>
       </c>
       <c r="K139" t="n">
-        <v>1.440635289025236</v>
+        <v>1.182907486726164</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -5755,22 +5755,22 @@
         <v>631</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3139390545025098</v>
+        <v>0.005869271986388712</v>
       </c>
       <c r="G140" t="n">
-        <v>5.713986327763283</v>
+        <v>5.231349897546282</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I140" t="n">
-        <v>23.11979381019518</v>
+        <v>21.614263051162</v>
       </c>
       <c r="J140" t="n">
-        <v>0.05245354887986443</v>
+        <v>0.08155696938117458</v>
       </c>
       <c r="K140" t="n">
-        <v>1.024113954508327</v>
+        <v>1.329866620204222</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>240</v>
       </c>
       <c r="F141" t="n">
-        <v>0.6476760673969228</v>
+        <v>0.4105919013255929</v>
       </c>
       <c r="G141" t="n">
-        <v>23.65271938864671</v>
+        <v>22.24411049399104</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I141" t="n">
-        <v>21.80521251427836</v>
+        <v>20.40002956880289</v>
       </c>
       <c r="J141" t="n">
-        <v>0.02340482010283678</v>
+        <v>0.03677649015282731</v>
       </c>
       <c r="K141" t="n">
-        <v>0.6189739464795889</v>
+        <v>0.7702121488266447</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -5837,16 +5837,16 @@
         <v>13.28753103477091</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I142" t="n">
-        <v>19.52892865743299</v>
+        <v>17.72959932853104</v>
       </c>
       <c r="J142" t="n">
-        <v>0.04334635651928458</v>
+        <v>0.04328992062183881</v>
       </c>
       <c r="K142" t="n">
-        <v>0.8970967616250891</v>
+        <v>0.8516152635052764</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -5869,22 +5869,22 @@
         <v>480</v>
       </c>
       <c r="F143" t="n">
-        <v>0.02350614742420792</v>
+        <v>0.01496827675093042</v>
       </c>
       <c r="G143" t="n">
-        <v>5.791744270780583</v>
+        <v>5.777013401509032</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I143" t="n">
-        <v>169.2329116352616</v>
+        <v>168.9509513487269</v>
       </c>
       <c r="J143" t="n">
-        <v>0.02700584867101539</v>
+        <v>0.06507134157311195</v>
       </c>
       <c r="K143" t="n">
-        <v>0.6691971680953088</v>
+        <v>1.123833646121883</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -5907,22 +5907,22 @@
         <v>226</v>
       </c>
       <c r="F144" t="n">
-        <v>0.6778443849467041</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G144" t="n">
-        <v>26.77058638563806</v>
+        <v>22.75008536600774</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I144" t="n">
-        <v>108.718278459124</v>
+        <v>111.1817634008267</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1266286666338256</v>
+        <v>0.2246910541853423</v>
       </c>
       <c r="K144" t="n">
-        <v>2.058627651580593</v>
+        <v>3.118718190074889</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>7.001992287913491</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I145" t="n">
-        <v>35.23144746678061</v>
+        <v>33.15993339716324</v>
       </c>
       <c r="J145" t="n">
-        <v>0.075897605124521</v>
+        <v>0.08472299945593015</v>
       </c>
       <c r="K145" t="n">
-        <v>1.351086098731645</v>
+        <v>1.369434818633219</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -5989,16 +5989,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I146" t="n">
-        <v>91.45836915575082</v>
+        <v>89.0338057750707</v>
       </c>
       <c r="J146" t="n">
-        <v>0.01467643040581456</v>
+        <v>0.01974938331484347</v>
       </c>
       <c r="K146" t="n">
-        <v>0.4972398802809313</v>
+        <v>0.5574119144229657</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -6021,22 +6021,22 @@
         <v>143</v>
       </c>
       <c r="F147" t="n">
-        <v>0.6296819076437551</v>
+        <v>0.1917059732767608</v>
       </c>
       <c r="G147" t="n">
-        <v>25.25457377096612</v>
+        <v>22.46354348927283</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I147" t="n">
-        <v>79.69503906537861</v>
+        <v>77.24359729109156</v>
       </c>
       <c r="J147" t="n">
-        <v>0.06267555107959037</v>
+        <v>0.07848356790227373</v>
       </c>
       <c r="K147" t="n">
-        <v>1.166679299968187</v>
+        <v>1.29145606923101</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -6065,16 +6065,16 @@
         <v>18.04607081887911</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I148" t="n">
-        <v>22.28137270291327</v>
+        <v>21.73356234285896</v>
       </c>
       <c r="J148" t="n">
-        <v>0.03052605034356669</v>
+        <v>0.07547355599849995</v>
       </c>
       <c r="K148" t="n">
-        <v>0.7182931042661218</v>
+        <v>1.253837744240411</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -6097,22 +6097,22 @@
         <v>499</v>
       </c>
       <c r="F149" t="n">
-        <v>0.6476760673969441</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>21.8350234929271</v>
+        <v>18.28265254277946</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I149" t="n">
-        <v>119.7283838297617</v>
+        <v>122.184832405044</v>
       </c>
       <c r="J149" t="n">
-        <v>0.02678463717800377</v>
+        <v>0.02787124995961653</v>
       </c>
       <c r="K149" t="n">
-        <v>0.6661119512948528</v>
+        <v>0.658916834915247</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>578</v>
       </c>
       <c r="F150" t="n">
-        <v>0.01385228580827768</v>
+        <v>0.6312434555399631</v>
       </c>
       <c r="G150" t="n">
-        <v>15.84079668350338</v>
+        <v>18.7626447991206</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I150" t="n">
-        <v>150.0111610382202</v>
+        <v>147.7146489603284</v>
       </c>
       <c r="J150" t="n">
-        <v>0.04042891963680239</v>
+        <v>0.03476525399641924</v>
       </c>
       <c r="K150" t="n">
-        <v>0.8564075317773823</v>
+        <v>0.7450762564171349</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -6173,22 +6173,22 @@
         <v>421</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6396311827169744</v>
+        <v>0.6312434555399277</v>
       </c>
       <c r="G151" t="n">
-        <v>25.66536127805342</v>
+        <v>25.61117653831286</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I151" t="n">
-        <v>28.30061886166619</v>
+        <v>26.90013679222753</v>
       </c>
       <c r="J151" t="n">
-        <v>0.1653921775178588</v>
+        <v>0.2254956736287785</v>
       </c>
       <c r="K151" t="n">
-        <v>2.599258852048094</v>
+        <v>3.128774109016269</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -6211,22 +6211,22 @@
         <v>108</v>
       </c>
       <c r="F152" t="n">
-        <v>0.01385228580827891</v>
+        <v>0.6312434555399918</v>
       </c>
       <c r="G152" t="n">
-        <v>16.91021409147524</v>
+        <v>20.02931713692481</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I152" t="n">
-        <v>28.48204198635943</v>
+        <v>26.1880586797866</v>
       </c>
       <c r="J152" t="n">
-        <v>0.03258097936946355</v>
+        <v>0.04723279415833727</v>
       </c>
       <c r="K152" t="n">
-        <v>0.7469530145995725</v>
+        <v>0.9008922440736491</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -6249,22 +6249,22 @@
         <v>79</v>
       </c>
       <c r="F153" t="n">
-        <v>0.06171934965394685</v>
+        <v>0.07543157732456883</v>
       </c>
       <c r="G153" t="n">
-        <v>14.52224507953177</v>
+        <v>14.58089875869763</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I153" t="n">
-        <v>37.73680519254422</v>
+        <v>36.26420390626544</v>
       </c>
       <c r="J153" t="n">
-        <v>0.01435193049962217</v>
+        <v>0.03404700164942884</v>
       </c>
       <c r="K153" t="n">
-        <v>0.4927141092701161</v>
+        <v>0.7360997303839755</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -6293,16 +6293,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I154" t="n">
-        <v>33.98782998313704</v>
+        <v>32.64935854815148</v>
       </c>
       <c r="J154" t="n">
-        <v>0.07488569298269221</v>
+        <v>0.01386704588867773</v>
       </c>
       <c r="K154" t="n">
-        <v>1.336973051086369</v>
+        <v>0.4838960320690013</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -6331,16 +6331,16 @@
         <v>17.03283675727564</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I155" t="n">
-        <v>70.17771880285164</v>
+        <v>67.89338313006266</v>
       </c>
       <c r="J155" t="n">
-        <v>0.0307834123904557</v>
+        <v>0.03522715880383775</v>
       </c>
       <c r="K155" t="n">
-        <v>0.7218825095906454</v>
+        <v>0.7508490193548509</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -6363,22 +6363,22 @@
         <v>369</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6278781090048795</v>
+        <v>0.6312434555399365</v>
       </c>
       <c r="G156" t="n">
-        <v>26.83919270527387</v>
+        <v>26.86199461461126</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I156" t="n">
-        <v>117.5154493780703</v>
+        <v>119.9858792593487</v>
       </c>
       <c r="J156" t="n">
-        <v>0.07128179378814092</v>
+        <v>0.08292097369575829</v>
       </c>
       <c r="K156" t="n">
-        <v>1.286709793102772</v>
+        <v>1.346913581889077</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -6401,22 +6401,22 @@
         <v>82</v>
       </c>
       <c r="F157" t="n">
-        <v>0.3406631557986861</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>11.44643959489128</v>
+        <v>10.3850939331332</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I157" t="n">
-        <v>115.6576366623428</v>
+        <v>118.1323694003545</v>
       </c>
       <c r="J157" t="n">
-        <v>0.1001957808388589</v>
+        <v>0.08931725443417961</v>
       </c>
       <c r="K157" t="n">
-        <v>1.6899705703914</v>
+        <v>1.426852590518036</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -6439,22 +6439,22 @@
         <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>0.9998434082878648</v>
+        <v>0.03216622358243008</v>
       </c>
       <c r="G158" t="n">
-        <v>23.6639260676628</v>
+        <v>18.37934094186289</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I158" t="n">
-        <v>105.8399463635183</v>
+        <v>108.2795297604204</v>
       </c>
       <c r="J158" t="n">
-        <v>0.1539676875614531</v>
+        <v>0.1758700100198796</v>
       </c>
       <c r="K158" t="n">
-        <v>2.439922517980257</v>
+        <v>2.508565817091189</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         <v>4.760796887076785</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I159" t="n">
-        <v>39.24078459784157</v>
+        <v>38.0529462745222</v>
       </c>
       <c r="J159" t="n">
-        <v>0.1328103360400428</v>
+        <v>0.1554647142968545</v>
       </c>
       <c r="K159" t="n">
-        <v>2.144842838898752</v>
+        <v>2.253545880101689</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>539</v>
       </c>
       <c r="F160" t="n">
-        <v>0.6319080934242277</v>
+        <v>0.1917844120768706</v>
       </c>
       <c r="G160" t="n">
-        <v>20.30772071799779</v>
+        <v>18.05365650342918</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I160" t="n">
-        <v>53.23041119366396</v>
+        <v>50.93379983479113</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03914755830675019</v>
+        <v>0.02636155748742742</v>
       </c>
       <c r="K160" t="n">
-        <v>0.8385365005343353</v>
+        <v>0.640049101540682</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
@@ -6553,22 +6553,22 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>0.6291277812788482</v>
+        <v>0.0125123732910225</v>
       </c>
       <c r="G161" t="n">
-        <v>24.02658936385474</v>
+        <v>20.28770971945494</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I161" t="n">
-        <v>40.59177863076635</v>
+        <v>38.45267583225674</v>
       </c>
       <c r="J161" t="n">
-        <v>0.1015303897652495</v>
+        <v>0.09140913524596746</v>
       </c>
       <c r="K161" t="n">
-        <v>1.708584241072256</v>
+        <v>1.452996358295423</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
@@ -6597,16 +6597,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I162" t="n">
-        <v>85.4045747268129</v>
+        <v>82.96215303648229</v>
       </c>
       <c r="J162" t="n">
-        <v>0.04813288695773268</v>
+        <v>0.05561727708891365</v>
       </c>
       <c r="K162" t="n">
-        <v>0.9638540712184863</v>
+        <v>1.005679272777791</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
@@ -6629,22 +6629,22 @@
         <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>0.2507741396326219</v>
+        <v>0.4124359662912174</v>
       </c>
       <c r="G163" t="n">
-        <v>18.85636333800415</v>
+        <v>19.70688307390854</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I163" t="n">
-        <v>92.98851113494418</v>
+        <v>90.57512650932068</v>
       </c>
       <c r="J163" t="n">
-        <v>0.06218213898575557</v>
+        <v>0.08984775292735193</v>
       </c>
       <c r="K163" t="n">
-        <v>1.159797725865854</v>
+        <v>1.433482619023292</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
@@ -6667,22 +6667,22 @@
         <v>624</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>0.1891691368813188</v>
       </c>
       <c r="G164" t="n">
-        <v>11.449738512298</v>
+        <v>12.09951965786446</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I164" t="n">
-        <v>16.6393848220203</v>
+        <v>14.30109739303513</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1084012725145787</v>
+        <v>0.0966716815551097</v>
       </c>
       <c r="K164" t="n">
-        <v>1.804411824908873</v>
+        <v>1.518766256775621</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -6711,16 +6711,16 @@
         <v>4.635186296148192</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I165" t="n">
-        <v>30.54004103806239</v>
+        <v>28.38957703245651</v>
       </c>
       <c r="J165" t="n">
-        <v>0.0316047531903635</v>
+        <v>0.04619919308337005</v>
       </c>
       <c r="K165" t="n">
-        <v>0.7333376758673924</v>
+        <v>0.8879745738478269</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
@@ -6749,16 +6749,16 @@
         <v>15.96371209963397</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I166" t="n">
-        <v>113.7345489340537</v>
+        <v>116.1959748294505</v>
       </c>
       <c r="J166" t="n">
-        <v>0.05950948632075438</v>
+        <v>0.1235406531765352</v>
       </c>
       <c r="K166" t="n">
-        <v>1.122522479486986</v>
+        <v>1.854567489106538</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
@@ -6781,22 +6781,22 @@
         <v>623</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>0.000773829318245072</v>
       </c>
       <c r="G167" t="n">
-        <v>9.514139425087274</v>
+        <v>9.516348121094776</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I167" t="n">
-        <v>19.85304556260846</v>
+        <v>18.98272842273284</v>
       </c>
       <c r="J167" t="n">
-        <v>0.05798342382527882</v>
+        <v>0.1037428329085284</v>
       </c>
       <c r="K167" t="n">
-        <v>1.101238623094679</v>
+        <v>1.607139618135792</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -6819,22 +6819,22 @@
         <v>106</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1.330559724956681e-05</v>
       </c>
       <c r="G168" t="n">
-        <v>19.03856866993945</v>
+        <v>19.03864466579753</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I168" t="n">
-        <v>33.09423862101185</v>
+        <v>31.97326599568843</v>
       </c>
       <c r="J168" t="n">
-        <v>0.05043714952010661</v>
+        <v>0.05805496670809546</v>
       </c>
       <c r="K168" t="n">
-        <v>0.9959914139637138</v>
+        <v>1.036144866686446</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
@@ -6857,22 +6857,22 @@
         <v>211</v>
       </c>
       <c r="F169" t="n">
-        <v>0</v>
+        <v>0.0003856051149581994</v>
       </c>
       <c r="G169" t="n">
-        <v>7.554245495084205</v>
+        <v>7.55511938179497</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I169" t="n">
-        <v>64.76848615754716</v>
+        <v>62.37623187108682</v>
       </c>
       <c r="J169" t="n">
-        <v>0.02625820933216533</v>
+        <v>0.05574890483760114</v>
       </c>
       <c r="K169" t="n">
-        <v>0.6587699094682857</v>
+        <v>1.007324321231486</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -6901,16 +6901,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I170" t="n">
-        <v>129.3541074858832</v>
+        <v>128.1177224039265</v>
       </c>
       <c r="J170" t="n">
-        <v>0.06373145343876083</v>
+        <v>0.06012746675224112</v>
       </c>
       <c r="K170" t="n">
-        <v>1.181405875218881</v>
+        <v>1.062046418805212</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
@@ -6933,22 +6933,22 @@
         <v>255</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0001045778075126898</v>
+        <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>10.88017456155615</v>
+        <v>10.87983322482473</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I171" t="n">
-        <v>171.7102852489521</v>
+        <v>170.9653298060792</v>
       </c>
       <c r="J171" t="n">
-        <v>0.05835494374298656</v>
+        <v>0.08952016557169432</v>
       </c>
       <c r="K171" t="n">
-        <v>1.106420177977796</v>
+        <v>1.429388519730034</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>2.82842712474619</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I172" t="n">
-        <v>35.39393973639758</v>
+        <v>33.2817085402124</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2458711871050682</v>
+        <v>0.3041749153686934</v>
       </c>
       <c r="K172" t="n">
-        <v>3.721692361637394</v>
+        <v>4.112086262059653</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>686</v>
       </c>
       <c r="F173" t="n">
-        <v>0.9418171635073348</v>
+        <v>0.6316290606548958</v>
       </c>
       <c r="G173" t="n">
-        <v>20.52264110291529</v>
+        <v>19.03359899458738</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I173" t="n">
-        <v>30.85615624638522</v>
+        <v>28.63741558226205</v>
       </c>
       <c r="J173" t="n">
-        <v>0.0279675701881313</v>
+        <v>0.02494973775659836</v>
       </c>
       <c r="K173" t="n">
-        <v>0.6826102116111366</v>
+        <v>0.6224045555520497</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -7047,22 +7047,22 @@
         <v>591</v>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>0.03071038282010412</v>
       </c>
       <c r="G174" t="n">
-        <v>18.63944545848937</v>
+        <v>18.81117281016477</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I174" t="n">
-        <v>33.5074381955181</v>
+        <v>32.3084736348904</v>
       </c>
       <c r="J174" t="n">
-        <v>0.03735598286563548</v>
+        <v>0.06015242066977085</v>
       </c>
       <c r="K174" t="n">
-        <v>0.8135495589656112</v>
+        <v>1.062358286202894</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>105</v>
       </c>
       <c r="F175" t="n">
-        <v>0.3139390545024818</v>
+        <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>9.620637525515331</v>
+        <v>8.792540929674423</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I175" t="n">
-        <v>98.54690623078599</v>
+        <v>101.0229474917047</v>
       </c>
       <c r="J175" t="n">
-        <v>0.02970125448060148</v>
+        <v>0.04153267975460911</v>
       </c>
       <c r="K175" t="n">
-        <v>0.7067897505356118</v>
+        <v>0.8296537363939283</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -7129,16 +7129,16 @@
         <v>6.802079020417213</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I176" t="n">
-        <v>32.82182337785275</v>
+        <v>30.77943517363615</v>
       </c>
       <c r="J176" t="n">
-        <v>0.07554361784697049</v>
+        <v>0.133609084500859</v>
       </c>
       <c r="K176" t="n">
-        <v>1.346149070004168</v>
+        <v>1.980400055160205</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -7161,22 +7161,22 @@
         <v>389</v>
       </c>
       <c r="F177" t="n">
-        <v>0.639631182716998</v>
+        <v>0.6334731256205226</v>
       </c>
       <c r="G177" t="n">
-        <v>21.2281673624354</v>
+        <v>21.1952639055474</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I177" t="n">
-        <v>50.44579644520729</v>
+        <v>48.04991597291333</v>
       </c>
       <c r="J177" t="n">
-        <v>0.05853222923202563</v>
+        <v>0.07325786484172693</v>
       </c>
       <c r="K177" t="n">
-        <v>1.10889276275092</v>
+        <v>1.226146627833268</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I178" t="n">
-        <v>17.5446063207043</v>
+        <v>16.01317503579472</v>
       </c>
       <c r="J178" t="n">
-        <v>0.02758108612405689</v>
+        <v>0.05160790838777836</v>
       </c>
       <c r="K178" t="n">
-        <v>0.6772199531243034</v>
+        <v>0.9555712533984169</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -7237,22 +7237,22 @@
         <v>266</v>
       </c>
       <c r="F179" t="n">
-        <v>0.00402998441935881</v>
+        <v>0.00222967008057149</v>
       </c>
       <c r="G179" t="n">
-        <v>3.334126224158364</v>
+        <v>3.332327656044203</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I179" t="n">
-        <v>23.32288368628004</v>
+        <v>20.98827866477739</v>
       </c>
       <c r="J179" t="n">
-        <v>0.05283775195035379</v>
+        <v>0.05714736503311457</v>
       </c>
       <c r="K179" t="n">
-        <v>1.029472400182749</v>
+        <v>1.024801903315226</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
@@ -7275,22 +7275,22 @@
         <v>137</v>
       </c>
       <c r="F180" t="n">
-        <v>0.01385228580827913</v>
+        <v>0.08100972335851891</v>
       </c>
       <c r="G180" t="n">
-        <v>12.3911877443092</v>
+        <v>12.6398027038002</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I180" t="n">
-        <v>66.74883950717913</v>
+        <v>64.48137141519184</v>
       </c>
       <c r="J180" t="n">
-        <v>0.04534542054894106</v>
+        <v>0.06200296499245927</v>
       </c>
       <c r="K180" t="n">
-        <v>0.9249775278796686</v>
+        <v>1.085485894985146</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -7313,22 +7313,22 @@
         <v>400</v>
       </c>
       <c r="F181" t="n">
-        <v>0.01175307371210619</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G181" t="n">
-        <v>14.34503252998123</v>
+        <v>14.61811073921889</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I181" t="n">
-        <v>33.48346632930491</v>
+        <v>31.38377618840136</v>
       </c>
       <c r="J181" t="n">
-        <v>0.02085260795150836</v>
+        <v>0.0524058132626113</v>
       </c>
       <c r="K181" t="n">
-        <v>0.5833784731142295</v>
+        <v>0.9655432554544274</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>455</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0003110373301569142</v>
+        <v>0.0002946042980451566</v>
       </c>
       <c r="G182" t="n">
-        <v>13.18231912433201</v>
+        <v>13.18225414275347</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I182" t="n">
-        <v>27.10369785857549</v>
+        <v>25.36443568900793</v>
       </c>
       <c r="J182" t="n">
-        <v>0.07373146247015004</v>
+        <v>0.01788724438241677</v>
       </c>
       <c r="K182" t="n">
-        <v>1.320875101922819</v>
+        <v>0.5341393993043879</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I183" t="n">
-        <v>106.0256863426085</v>
+        <v>108.4756476986584</v>
       </c>
       <c r="J183" t="n">
-        <v>0.04251051030028449</v>
+        <v>0.05187780944263005</v>
       </c>
       <c r="K183" t="n">
-        <v>0.8854392895726705</v>
+        <v>0.9589444047085453</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -7427,22 +7427,22 @@
         <v>547</v>
       </c>
       <c r="F184" t="n">
-        <v>0.04996627594183239</v>
+        <v>0.0003794847494315991</v>
       </c>
       <c r="G184" t="n">
-        <v>10.37511869760823</v>
+        <v>10.22305742492512</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I184" t="n">
-        <v>22.75643070272934</v>
+        <v>20.50498496772092</v>
       </c>
       <c r="J184" t="n">
-        <v>0.0650212164408004</v>
+        <v>0.1011520301329528</v>
       </c>
       <c r="K184" t="n">
-        <v>1.199394083825611</v>
+        <v>1.574760456885315</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -7465,22 +7465,22 @@
         <v>625</v>
       </c>
       <c r="F185" t="n">
-        <v>0.2507741396326156</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>7.808168561520751</v>
+        <v>7.261843774138907</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I185" t="n">
-        <v>67.05604191682495</v>
+        <v>64.91022091244798</v>
       </c>
       <c r="J185" t="n">
-        <v>0.009617645236873543</v>
+        <v>0.03038741316820152</v>
       </c>
       <c r="K185" t="n">
-        <v>0.4266854584440204</v>
+        <v>0.6903631707889579</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
@@ -7503,22 +7503,22 @@
         <v>13</v>
       </c>
       <c r="F186" t="n">
-        <v>0.4261274853907389</v>
+        <v>0.631243455539946</v>
       </c>
       <c r="G186" t="n">
-        <v>13.37370789185269</v>
+        <v>14.10337663984631</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I186" t="n">
-        <v>23.85324114293519</v>
+        <v>22.79294747556716</v>
       </c>
       <c r="J186" t="n">
-        <v>0.061385395834559</v>
+        <v>0.1023182876490163</v>
       </c>
       <c r="K186" t="n">
-        <v>1.148685620783724</v>
+        <v>1.58933603188786</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -7541,22 +7541,22 @@
         <v>331</v>
       </c>
       <c r="F187" t="n">
-        <v>0.258834108471334</v>
+        <v>0.0004580117789578011</v>
       </c>
       <c r="G187" t="n">
-        <v>22.31181219921191</v>
+        <v>20.70697638920036</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I187" t="n">
-        <v>104.8216211106881</v>
+        <v>107.262916169774</v>
       </c>
       <c r="J187" t="n">
-        <v>0.03774424748576161</v>
+        <v>0.04776688128583111</v>
       </c>
       <c r="K187" t="n">
-        <v>0.8189646507075801</v>
+        <v>0.9075671223723591</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -7579,22 +7579,22 @@
         <v>180</v>
       </c>
       <c r="F188" t="n">
-        <v>0.01979795839205038</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>4.096208778048068</v>
+        <v>4.072023452781184</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I188" t="n">
-        <v>107.0727832917891</v>
+        <v>109.5461704544331</v>
       </c>
       <c r="J188" t="n">
-        <v>0.1195107828360214</v>
+        <v>0.125992286016634</v>
       </c>
       <c r="K188" t="n">
-        <v>1.959355166332614</v>
+        <v>1.885207341666866</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -7617,22 +7617,22 @@
         <v>414</v>
       </c>
       <c r="F189" t="n">
-        <v>0.9453591251098454</v>
+        <v>0.7993496381311703</v>
       </c>
       <c r="G189" t="n">
-        <v>26.20675382024651</v>
+        <v>25.31245381672093</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I189" t="n">
-        <v>34.29172451398752</v>
+        <v>32.78211371308092</v>
       </c>
       <c r="J189" t="n">
-        <v>0.06121111153506963</v>
+        <v>0.05775623245508746</v>
       </c>
       <c r="K189" t="n">
-        <v>1.146254893331367</v>
+        <v>1.032411365765274</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -7655,22 +7655,22 @@
         <v>667</v>
       </c>
       <c r="F190" t="n">
-        <v>0.6278781090048906</v>
+        <v>0.2837537053219952</v>
       </c>
       <c r="G190" t="n">
-        <v>20.84034666337098</v>
+        <v>19.02987227378776</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I190" t="n">
-        <v>26.20545316108371</v>
+        <v>25.84310341602255</v>
       </c>
       <c r="J190" t="n">
-        <v>0.05384131767844651</v>
+        <v>0.06158166267091819</v>
       </c>
       <c r="K190" t="n">
-        <v>1.043469041146204</v>
+        <v>1.080220571073584</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
@@ -7693,22 +7693,22 @@
         <v>294</v>
       </c>
       <c r="F191" t="n">
-        <v>0.05102630472990546</v>
+        <v>0.00445934016114399</v>
       </c>
       <c r="G191" t="n">
-        <v>14.8101432225987</v>
+        <v>14.60636363400281</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I191" t="n">
-        <v>103.5107156379267</v>
+        <v>105.9741236304569</v>
       </c>
       <c r="J191" t="n">
-        <v>0.03612628935735145</v>
+        <v>0.04283316941684356</v>
       </c>
       <c r="K191" t="n">
-        <v>0.7963991341865047</v>
+        <v>0.8459069089144468</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
@@ -7737,16 +7737,16 @@
         <v>16.38096837796838</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I192" t="n">
-        <v>103.3173410944955</v>
+        <v>105.7698370100968</v>
       </c>
       <c r="J192" t="n">
-        <v>0.05874577597436052</v>
+        <v>0.03300980370442965</v>
       </c>
       <c r="K192" t="n">
-        <v>1.111871079962945</v>
+        <v>0.7231371074369888</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -7769,22 +7769,22 @@
         <v>476</v>
       </c>
       <c r="F193" t="n">
-        <v>0.3639053304442927</v>
+        <v>0.4102062962106391</v>
       </c>
       <c r="G193" t="n">
-        <v>15.05452788087168</v>
+        <v>15.24305754947807</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I193" t="n">
-        <v>110.1728110255309</v>
+        <v>112.646858444203</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03251112863765326</v>
+        <v>0.04887199094332657</v>
       </c>
       <c r="K193" t="n">
-        <v>0.7459788127243836</v>
+        <v>0.9213784877672244</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -7813,16 +7813,16 @@
         <v>16.15292911517908</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I194" t="n">
-        <v>38.02294659214053</v>
+        <v>35.83577489227513</v>
       </c>
       <c r="J194" t="n">
-        <v>0.1111592744027997</v>
+        <v>0.1803835647868803</v>
       </c>
       <c r="K194" t="n">
-        <v>1.842877429228908</v>
+        <v>2.564975019285713</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -7845,22 +7845,22 @@
         <v>628</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>0.3156217277700418</v>
       </c>
       <c r="G195" t="n">
-        <v>4.216584043986316</v>
+        <v>4.615837706361481</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I195" t="n">
-        <v>111.1291459124491</v>
+        <v>113.5978587531956</v>
       </c>
       <c r="J195" t="n">
-        <v>0.03381794514680692</v>
+        <v>0.07181801387694549</v>
       </c>
       <c r="K195" t="n">
-        <v>0.7642048650612864</v>
+        <v>1.208151754968059</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -7883,22 +7883,22 @@
         <v>420</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>0.6312434555399646</v>
       </c>
       <c r="G196" t="n">
-        <v>6.859</v>
+        <v>8.157909658464586</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I196" t="n">
-        <v>38.88389366216378</v>
+        <v>36.77503357662145</v>
       </c>
       <c r="J196" t="n">
-        <v>0.2008047394176002</v>
+        <v>0.1597380647220451</v>
       </c>
       <c r="K196" t="n">
-        <v>3.093154668367785</v>
+        <v>2.306953072575575</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -7927,16 +7927,16 @@
         <v>9.010146336214524</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I197" t="n">
-        <v>23.55720321865559</v>
+        <v>23.17107648052712</v>
       </c>
       <c r="J197" t="n">
-        <v>0.04506068260733724</v>
+        <v>0.0318490317578702</v>
       </c>
       <c r="K197" t="n">
-        <v>0.9210063134133514</v>
+        <v>0.7086300896172595</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -7959,22 +7959,22 @@
         <v>517</v>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G198" t="n">
-        <v>9.292517850399857</v>
+        <v>9.502802634031552</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I198" t="n">
-        <v>67.88862164763613</v>
+        <v>65.56689610313644</v>
       </c>
       <c r="J198" t="n">
-        <v>0.02689004448824579</v>
+        <v>0.03815870789660654</v>
       </c>
       <c r="K198" t="n">
-        <v>0.6675820575719822</v>
+        <v>0.7874867370859366</v>
       </c>
       <c r="L198" t="b">
         <v>0</v>
@@ -7997,22 +7997,22 @@
         <v>509</v>
       </c>
       <c r="F199" t="n">
-        <v>0.03256817361512986</v>
+        <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>22.54926752881262</v>
+        <v>22.33108275476135</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I199" t="n">
-        <v>33.16658667969853</v>
+        <v>31.42082342327583</v>
       </c>
       <c r="J199" t="n">
-        <v>0.03466483077050447</v>
+        <v>0.01811756418448567</v>
       </c>
       <c r="K199" t="n">
-        <v>0.7760163026982954</v>
+        <v>0.5370178746868725</v>
       </c>
       <c r="L199" t="b">
         <v>0</v>
@@ -8035,22 +8035,22 @@
         <v>84</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0.8760076994998224</v>
       </c>
       <c r="G200" t="n">
-        <v>28.26503573162433</v>
+        <v>27.45627108452806</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I200" t="n">
-        <v>62.08116485610849</v>
+        <v>60.03537259399403</v>
       </c>
       <c r="J200" t="n">
-        <v>0.03037161416959136</v>
+        <v>0.02929139449782417</v>
       </c>
       <c r="K200" t="n">
-        <v>0.716139196835454</v>
+        <v>0.6766654221234703</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8073,22 +8073,22 @@
         <v>526</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>0.1891691368813246</v>
       </c>
       <c r="G201" t="n">
-        <v>12.167</v>
+        <v>12.85748626653052</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I201" t="n">
-        <v>26.93849745717281</v>
+        <v>25.37214512884822</v>
       </c>
       <c r="J201" t="n">
-        <v>0.02067157420898268</v>
+        <v>0.02668554625719914</v>
       </c>
       <c r="K201" t="n">
-        <v>0.5808536117867924</v>
+        <v>0.6440982266684918</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -8111,22 +8111,22 @@
         <v>497</v>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>0.03771578866227802</v>
       </c>
       <c r="G202" t="n">
-        <v>5.379074548656115</v>
+        <v>5.439937360318841</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I202" t="n">
-        <v>69.5716022649659</v>
+        <v>67.40276975216564</v>
       </c>
       <c r="J202" t="n">
-        <v>0.03882676792092587</v>
+        <v>0.05025362371035521</v>
       </c>
       <c r="K202" t="n">
-        <v>0.8340624658705125</v>
+        <v>0.9386457651432976</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -8149,22 +8149,22 @@
         <v>407</v>
       </c>
       <c r="F203" t="n">
-        <v>0.02350614742421015</v>
+        <v>0.03771578866228487</v>
       </c>
       <c r="G203" t="n">
-        <v>8.606295463166949</v>
+        <v>8.642726270067751</v>
       </c>
       <c r="H203" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I203" t="n">
-        <v>111.4243159831747</v>
+        <v>113.8996716948806</v>
       </c>
       <c r="J203" t="n">
-        <v>0.06124219274494565</v>
+        <v>0.04574415590891035</v>
       </c>
       <c r="K203" t="n">
-        <v>1.146688380170511</v>
+        <v>0.8822876407529219</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -8187,22 +8187,22 @@
         <v>632</v>
       </c>
       <c r="F204" t="n">
-        <v>0.8103131163322702</v>
+        <v>0.9640631301414659</v>
       </c>
       <c r="G204" t="n">
-        <v>26.81985967774027</v>
+        <v>27.81501065065835</v>
       </c>
       <c r="H204" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I204" t="n">
-        <v>31.28657062784671</v>
+        <v>29.21182499750316</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1002930052377353</v>
+        <v>0.1028308476522743</v>
       </c>
       <c r="K204" t="n">
-        <v>1.691326550339567</v>
+        <v>1.595741869936396</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>475</v>
       </c>
       <c r="F205" t="n">
-        <v>0.3139390545024937</v>
+        <v>2.581975960520842e-05</v>
       </c>
       <c r="G205" t="n">
-        <v>7.380601848620135</v>
+        <v>6.745368623819933</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I205" t="n">
-        <v>37.09220333840505</v>
+        <v>35.01482160969051</v>
       </c>
       <c r="J205" t="n">
-        <v>0.02147504814431216</v>
+        <v>0.01882929628647361</v>
       </c>
       <c r="K205" t="n">
-        <v>0.5920595905099542</v>
+        <v>0.545912912439134</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -8263,22 +8263,22 @@
         <v>575</v>
       </c>
       <c r="F206" t="n">
-        <v>0.03295622304320514</v>
+        <v>0</v>
       </c>
       <c r="G206" t="n">
-        <v>20.57694826454845</v>
+        <v>20.37549842335151</v>
       </c>
       <c r="H206" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I206" t="n">
-        <v>181.3054672777228</v>
+        <v>180.2126241682663</v>
       </c>
       <c r="J206" t="n">
-        <v>0.01639588954382101</v>
+        <v>0.01202629068450122</v>
       </c>
       <c r="K206" t="n">
-        <v>0.5212210222553066</v>
+        <v>0.4608907650758604</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>75</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>0.0001526705929857841</v>
       </c>
       <c r="G207" t="n">
-        <v>4.660218771688728</v>
+        <v>4.660432215197723</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I207" t="n">
-        <v>105.58088276408</v>
+        <v>108.0577724873036</v>
       </c>
       <c r="J207" t="n">
-        <v>0.2029165830395439</v>
+        <v>0.2213189858586616</v>
       </c>
       <c r="K207" t="n">
-        <v>3.122608361454222</v>
+        <v>3.076574980593046</v>
       </c>
       <c r="L207" t="b">
         <v>0</v>
@@ -8339,22 +8339,22 @@
         <v>655</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>0.3918271344128271</v>
       </c>
       <c r="G208" t="n">
-        <v>15.43787550150603</v>
+        <v>17.25256905725916</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I208" t="n">
-        <v>85.92005596352274</v>
+        <v>83.56662747849063</v>
       </c>
       <c r="J208" t="n">
-        <v>0.05298287696704168</v>
+        <v>0.03203092159487781</v>
       </c>
       <c r="K208" t="n">
-        <v>1.03149644574004</v>
+        <v>0.710903300228972</v>
       </c>
       <c r="L208" t="b">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>383</v>
       </c>
       <c r="F209" t="n">
-        <v>0.2548041240519801</v>
+        <v>0.6689592442022723</v>
       </c>
       <c r="G209" t="n">
-        <v>23.5848419270836</v>
+        <v>26.30708519620149</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I209" t="n">
-        <v>24.81129845126135</v>
+        <v>23.03037319598706</v>
       </c>
       <c r="J209" t="n">
-        <v>0.01444887658671307</v>
+        <v>0.02687693996657087</v>
       </c>
       <c r="K209" t="n">
-        <v>0.4940662076288374</v>
+        <v>0.646490214139131</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -8415,22 +8415,22 @@
         <v>360</v>
       </c>
       <c r="F210" t="n">
-        <v>0.6278781090049219</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
-        <v>21.02586835959482</v>
+        <v>17.69312971184013</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I210" t="n">
-        <v>89.8979372544534</v>
+        <v>87.54694098545153</v>
       </c>
       <c r="J210" t="n">
-        <v>0.01599714599507289</v>
+        <v>0.02414155433664077</v>
       </c>
       <c r="K210" t="n">
-        <v>0.5156597818381708</v>
+        <v>0.6123040949838169</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8453,22 +8453,22 @@
         <v>360</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0001555186650784571</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G211" t="n">
-        <v>12.37516319537757</v>
+        <v>12.65461621051439</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I211" t="n">
-        <v>110.3840882134172</v>
+        <v>112.8606375326945</v>
       </c>
       <c r="J211" t="n">
-        <v>0.03695308767345355</v>
+        <v>0.02553791053223156</v>
       </c>
       <c r="K211" t="n">
-        <v>0.8079304159508431</v>
+        <v>0.6297553818383683</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -8491,22 +8491,22 @@
         <v>268</v>
       </c>
       <c r="F212" t="n">
-        <v>0</v>
+        <v>0.6312434555399117</v>
       </c>
       <c r="G212" t="n">
-        <v>9.898089765202174</v>
+        <v>11.77252108119131</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I212" t="n">
-        <v>73.99207660134769</v>
+        <v>71.60587000799686</v>
       </c>
       <c r="J212" t="n">
-        <v>0.07034398676498908</v>
+        <v>0.1125463525988247</v>
       </c>
       <c r="K212" t="n">
-        <v>1.273630282883736</v>
+        <v>1.717163656364843</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -8529,22 +8529,22 @@
         <v>696</v>
       </c>
       <c r="F213" t="n">
-        <v>0.6499683567254033</v>
+        <v>0.6312434555399155</v>
       </c>
       <c r="G213" t="n">
-        <v>19.48412533831767</v>
+        <v>19.39253340026383</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I213" t="n">
-        <v>191.0867244384225</v>
+        <v>190.9323183108731</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1222151402157486</v>
+        <v>0.1231029863584751</v>
       </c>
       <c r="K213" t="n">
-        <v>1.997072595516699</v>
+        <v>1.849097646087397</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -8573,16 +8573,16 @@
         <v>8.792540929674423</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I214" t="n">
-        <v>101.1072021157126</v>
+        <v>103.58190003143</v>
       </c>
       <c r="J214" t="n">
-        <v>0.5456645327594656</v>
+        <v>0.5447755558329787</v>
       </c>
       <c r="K214" t="n">
-        <v>7.902883194381735</v>
+        <v>7.119048817451578</v>
       </c>
       <c r="L214" t="b">
         <v>0</v>
@@ -8605,22 +8605,22 @@
         <v>572</v>
       </c>
       <c r="F215" t="n">
-        <v>0</v>
+        <v>0.005233169479388724</v>
       </c>
       <c r="G215" t="n">
-        <v>12.89864333951443</v>
+        <v>12.91889357550939</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I215" t="n">
-        <v>37.28176811469245</v>
+        <v>35.36648320141236</v>
       </c>
       <c r="J215" t="n">
-        <v>0.1781247927038548</v>
+        <v>0.2132598519206622</v>
       </c>
       <c r="K215" t="n">
-        <v>2.776839491059073</v>
+        <v>2.975854076718105</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -8649,16 +8649,16 @@
         <v>6.352448897866083</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I216" t="n">
-        <v>24.84040642367567</v>
+        <v>23.27213168035812</v>
       </c>
       <c r="J216" t="n">
-        <v>0.04395802794727404</v>
+        <v>0.02153681839389956</v>
       </c>
       <c r="K216" t="n">
-        <v>0.9056276880263358</v>
+        <v>0.5797508007307663</v>
       </c>
       <c r="L216" t="b">
         <v>0</v>
@@ -8687,16 +8687,16 @@
         <v>11.92630068378288</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I217" t="n">
-        <v>64.27029847118371</v>
+        <v>62.2241552631687</v>
       </c>
       <c r="J217" t="n">
-        <v>0.03048758135818962</v>
+        <v>0.02194297137316929</v>
       </c>
       <c r="K217" t="n">
-        <v>0.7177565807864146</v>
+        <v>0.5848267922080468</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -8719,22 +8719,22 @@
         <v>631</v>
       </c>
       <c r="F218" t="n">
-        <v>0.313939054502512</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>3.692863292683794</v>
+        <v>3.375</v>
       </c>
       <c r="H218" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I218" t="n">
-        <v>24.29576064748958</v>
+        <v>22.78679945649736</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1128015569812101</v>
+        <v>0.1138403971162385</v>
       </c>
       <c r="K218" t="n">
-        <v>1.865782196666745</v>
+        <v>1.733336279186481</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -8763,16 +8763,16 @@
         <v>7.378342564560147</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I219" t="n">
-        <v>122.0469822278787</v>
+        <v>124.506548463585</v>
       </c>
       <c r="J219" t="n">
-        <v>0.03261830913122976</v>
+        <v>0.03227679672788973</v>
       </c>
       <c r="K219" t="n">
-        <v>0.7474736494300245</v>
+        <v>0.7139761819837427</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>9.32407137467319</v>
       </c>
       <c r="H220" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I220" t="n">
-        <v>29.30746055915692</v>
+        <v>27.850965833472</v>
       </c>
       <c r="J220" t="n">
-        <v>0.0795331335146538</v>
+        <v>0.1055362962802856</v>
       </c>
       <c r="K220" t="n">
-        <v>1.401790486261743</v>
+        <v>1.629553844435998</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -8833,22 +8833,22 @@
         <v>605</v>
       </c>
       <c r="F221" t="n">
-        <v>0.639631182716955</v>
+        <v>0.6312434555399326</v>
       </c>
       <c r="G221" t="n">
-        <v>25.81472299184334</v>
+        <v>25.76022291948397</v>
       </c>
       <c r="H221" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I221" t="n">
-        <v>11.79778697778781</v>
+        <v>9.405356952988271</v>
       </c>
       <c r="J221" t="n">
-        <v>0.05363428607755281</v>
+        <v>0.05060439055764315</v>
       </c>
       <c r="K221" t="n">
-        <v>1.040581590025982</v>
+        <v>0.9430295555331835</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -8871,22 +8871,22 @@
         <v>486</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>0.0003856051149581994</v>
       </c>
       <c r="G222" t="n">
-        <v>11.34846355239334</v>
+        <v>11.34977636007115</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I222" t="n">
-        <v>22.6558952188293</v>
+        <v>21.01910019300469</v>
       </c>
       <c r="J222" t="n">
-        <v>0.1188102279007542</v>
+        <v>0.1337905187388285</v>
       </c>
       <c r="K222" t="n">
-        <v>1.949584589648268</v>
+        <v>1.9826675718168</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -8909,22 +8909,22 @@
         <v>620</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>0.005869271986387589</v>
       </c>
       <c r="G223" t="n">
-        <v>2.870959421517483</v>
+        <v>2.876014554029513</v>
       </c>
       <c r="H223" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I223" t="n">
-        <v>65.95165086438112</v>
+        <v>63.74026434718448</v>
       </c>
       <c r="J223" t="n">
-        <v>0.03067398540758564</v>
+        <v>0.05209643239989119</v>
       </c>
       <c r="K223" t="n">
-        <v>0.7203563413008441</v>
+        <v>0.9616766960481057</v>
       </c>
       <c r="L223" t="b">
         <v>0</v>
@@ -8953,16 +8953,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H224" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I224" t="n">
-        <v>60.29715011553289</v>
+        <v>58.1785347482576</v>
       </c>
       <c r="J224" t="n">
-        <v>0.05865589506570817</v>
+        <v>0.0962910284769382</v>
       </c>
       <c r="K224" t="n">
-        <v>1.110617519012565</v>
+        <v>1.514008956252864</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -8985,22 +8985,22 @@
         <v>414</v>
       </c>
       <c r="F225" t="n">
-        <v>0.6278781090048703</v>
+        <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>13.96963613444291</v>
+        <v>11.75535677893274</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I225" t="n">
-        <v>20.28174127581054</v>
+        <v>19.34229465780666</v>
       </c>
       <c r="J225" t="n">
-        <v>0.04439631392639277</v>
+        <v>0.0469431418072388</v>
       </c>
       <c r="K225" t="n">
-        <v>0.9117404231639734</v>
+        <v>0.8972722463373437</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -9023,22 +9023,22 @@
         <v>209</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>0.0001526705929860085</v>
       </c>
       <c r="G226" t="n">
-        <v>5.617338871743453</v>
+        <v>5.617596152480419</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I226" t="n">
-        <v>33.23493958389385</v>
+        <v>31.41544522447941</v>
       </c>
       <c r="J226" t="n">
-        <v>0.07119779833604113</v>
+        <v>0.06567374467155952</v>
       </c>
       <c r="K226" t="n">
-        <v>1.285538316085678</v>
+        <v>1.131362319182722</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -9061,22 +9061,22 @@
         <v>258</v>
       </c>
       <c r="F227" t="n">
-        <v>0.3761612094489241</v>
+        <v>0.6315487967258989</v>
       </c>
       <c r="G227" t="n">
-        <v>20.47788776407567</v>
+        <v>21.8877289940006</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I227" t="n">
-        <v>198.8710706229827</v>
+        <v>197.284488081846</v>
       </c>
       <c r="J227" t="n">
-        <v>0.05308430908265839</v>
+        <v>0.03278257744544419</v>
       </c>
       <c r="K227" t="n">
-        <v>1.032911110335202</v>
+        <v>0.7202972943298724</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -9099,22 +9099,22 @@
         <v>590</v>
       </c>
       <c r="F228" t="n">
-        <v>0.3959591678409639</v>
+        <v>0.6312434555399485</v>
       </c>
       <c r="G228" t="n">
-        <v>24.60663276182896</v>
+        <v>26.15908649406219</v>
       </c>
       <c r="H228" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I228" t="n">
-        <v>36.39568664884631</v>
+        <v>35.45671280172216</v>
       </c>
       <c r="J228" t="n">
-        <v>0.2674865486415208</v>
+        <v>0.2041640149065889</v>
       </c>
       <c r="K228" t="n">
-        <v>4.023159865211867</v>
+        <v>2.862176734635859</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -9143,16 +9143,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H229" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I229" t="n">
-        <v>100.3648704906266</v>
+        <v>102.8324443812095</v>
       </c>
       <c r="J229" t="n">
-        <v>0.04375794272649185</v>
+        <v>0.03001483335798935</v>
       </c>
       <c r="K229" t="n">
-        <v>0.9028371174448707</v>
+        <v>0.6857067678133003</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -9175,22 +9175,22 @@
         <v>276</v>
       </c>
       <c r="F230" t="n">
-        <v>0.653276439834432</v>
+        <v>0.6316290606548846</v>
       </c>
       <c r="G230" t="n">
-        <v>19.27329637862211</v>
+        <v>19.16864195331167</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I230" t="n">
-        <v>32.26512182901818</v>
+        <v>31.33756433923772</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1140934236841186</v>
+        <v>0.167779967621922</v>
       </c>
       <c r="K230" t="n">
-        <v>1.883799745400317</v>
+        <v>2.407458627537374</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -9213,22 +9213,22 @@
         <v>583</v>
       </c>
       <c r="F231" t="n">
-        <v>0.00229228932849165</v>
+        <v>0.3156217277700418</v>
       </c>
       <c r="G231" t="n">
-        <v>10.49063618719067</v>
+        <v>11.47606606370182</v>
       </c>
       <c r="H231" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I231" t="n">
-        <v>76.0437467567826</v>
+        <v>73.80629880294171</v>
       </c>
       <c r="J231" t="n">
-        <v>0.05424449116888616</v>
+        <v>0.03984152784135851</v>
       </c>
       <c r="K231" t="n">
-        <v>1.049092065561747</v>
+        <v>0.8085181713812539</v>
       </c>
       <c r="L231" t="b">
         <v>0</v>
@@ -9251,22 +9251,22 @@
         <v>391</v>
       </c>
       <c r="F232" t="n">
-        <v>0.6278781090048781</v>
+        <v>0.07544448720436538</v>
       </c>
       <c r="G232" t="n">
-        <v>16.90076766224575</v>
+        <v>14.54377348842496</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I232" t="n">
-        <v>123.8672578517167</v>
+        <v>121.411157719852</v>
       </c>
       <c r="J232" t="n">
-        <v>0.05039324601911643</v>
+        <v>0.083445134370388</v>
       </c>
       <c r="K232" t="n">
-        <v>0.9953790957834526</v>
+        <v>1.353464402030616</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -9289,22 +9289,22 @@
         <v>306</v>
       </c>
       <c r="F233" t="n">
-        <v>0.2507741396326156</v>
+        <v>0.09235724689858751</v>
       </c>
       <c r="G233" t="n">
-        <v>8.86119968287124</v>
+        <v>8.46953628263995</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I233" t="n">
-        <v>31.77000166377546</v>
+        <v>30.02756415553403</v>
       </c>
       <c r="J233" t="n">
-        <v>0.02534186478151545</v>
+        <v>0.08193155662613687</v>
       </c>
       <c r="K233" t="n">
-        <v>0.6459897344232086</v>
+        <v>1.334548111563329</v>
       </c>
       <c r="L233" t="b">
         <v>0</v>
@@ -9327,22 +9327,22 @@
         <v>458</v>
       </c>
       <c r="F234" t="n">
-        <v>0.09993255188367382</v>
+        <v>0.6312434555399332</v>
       </c>
       <c r="G234" t="n">
-        <v>13.79581458516517</v>
+        <v>15.93076916164564</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I234" t="n">
-        <v>35.00687314914575</v>
+        <v>32.61433272656713</v>
       </c>
       <c r="J234" t="n">
-        <v>0.02340984556518048</v>
+        <v>0.02250987359924241</v>
       </c>
       <c r="K234" t="n">
-        <v>0.6190440361509788</v>
+        <v>0.5919117848459747</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -9365,22 +9365,22 @@
         <v>581</v>
       </c>
       <c r="F235" t="n">
-        <v>0.1197305102757296</v>
+        <v>0.6689592442021973</v>
       </c>
       <c r="G235" t="n">
-        <v>22.47994572181821</v>
+        <v>26.05550432331384</v>
       </c>
       <c r="H235" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I235" t="n">
-        <v>78.94866000140857</v>
+        <v>76.48390928331555</v>
       </c>
       <c r="J235" t="n">
-        <v>0.05324936962908895</v>
+        <v>0.07100466044849593</v>
       </c>
       <c r="K235" t="n">
-        <v>1.0352131949331</v>
+        <v>1.197986681014274</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -9403,22 +9403,22 @@
         <v>162</v>
       </c>
       <c r="F236" t="n">
-        <v>0.008059968838718401</v>
+        <v>0.6312434555400217</v>
       </c>
       <c r="G236" t="n">
-        <v>17.46235295302083</v>
+        <v>20.71915304063649</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I236" t="n">
-        <v>70.29894713558546</v>
+        <v>67.97717340195084</v>
       </c>
       <c r="J236" t="n">
-        <v>0.05702220351178149</v>
+        <v>0.0695497344319627</v>
       </c>
       <c r="K236" t="n">
-        <v>1.087832569820649</v>
+        <v>1.179803404177859</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9441,22 +9441,22 @@
         <v>226</v>
       </c>
       <c r="F237" t="n">
-        <v>0</v>
+        <v>0.03771578866228487</v>
       </c>
       <c r="G237" t="n">
-        <v>12.79325302649799</v>
+        <v>12.93800531473315</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I237" t="n">
-        <v>40.35270886623581</v>
+        <v>39.14451926509778</v>
       </c>
       <c r="J237" t="n">
-        <v>0.05859899089560778</v>
+        <v>0.01473187885041933</v>
       </c>
       <c r="K237" t="n">
-        <v>1.109823881669317</v>
+        <v>0.4947044834829604</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -9485,16 +9485,16 @@
         <v>7.554245495084205</v>
       </c>
       <c r="H238" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I238" t="n">
-        <v>169.0978094301229</v>
+        <v>166.6885267686902</v>
       </c>
       <c r="J238" t="n">
-        <v>0.03898384189913912</v>
+        <v>0.02711035782319661</v>
       </c>
       <c r="K238" t="n">
-        <v>0.8362531625196803</v>
+        <v>0.6494074081801736</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -9517,22 +9517,22 @@
         <v>390</v>
       </c>
       <c r="F239" t="n">
-        <v>0.0003110373301569142</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>10.9141062356262</v>
+        <v>10.91308792230687</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I239" t="n">
-        <v>92.33708722750951</v>
+        <v>89.87065212241453</v>
       </c>
       <c r="J239" t="n">
-        <v>0.1959209510653338</v>
+        <v>0.1244919012509154</v>
       </c>
       <c r="K239" t="n">
-        <v>3.02504091139634</v>
+        <v>1.866455933522272</v>
       </c>
       <c r="L239" t="b">
         <v>0</v>
@@ -9561,16 +9561,16 @@
         <v>5.222154823442138</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I240" t="n">
-        <v>31.15906593883903</v>
+        <v>29.68794091335738</v>
       </c>
       <c r="J240" t="n">
-        <v>0.05839412138475507</v>
+        <v>0.07562257013078373</v>
       </c>
       <c r="K240" t="n">
-        <v>1.106966585024469</v>
+        <v>1.255700083073495</v>
       </c>
       <c r="L240" t="b">
         <v>0</v>
@@ -9593,22 +9593,22 @@
         <v>283</v>
       </c>
       <c r="F241" t="n">
-        <v>0.6301703983333869</v>
+        <v>0.07543157732456592</v>
       </c>
       <c r="G241" t="n">
-        <v>12.34840756730486</v>
+        <v>10.6201031379452</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I241" t="n">
-        <v>29.94573152509017</v>
+        <v>29.33018682506201</v>
       </c>
       <c r="J241" t="n">
-        <v>0.06971061493582241</v>
+        <v>0.05954180912537812</v>
       </c>
       <c r="K241" t="n">
-        <v>1.264796702938693</v>
+        <v>1.054727026176587</v>
       </c>
       <c r="L241" t="b">
         <v>0</v>
@@ -9631,22 +9631,22 @@
         <v>616</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>0.01163730388596001</v>
       </c>
       <c r="G242" t="n">
-        <v>7.203826552603831</v>
+        <v>7.228976488224151</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I242" t="n">
-        <v>30.43453058724796</v>
+        <v>29.83315909944809</v>
       </c>
       <c r="J242" t="n">
-        <v>0.04679215944365228</v>
+        <v>0.03770657463115364</v>
       </c>
       <c r="K242" t="n">
-        <v>0.9451550651453378</v>
+        <v>0.7818360962703493</v>
       </c>
       <c r="L242" t="b">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>384</v>
       </c>
       <c r="F243" t="n">
-        <v>0.01208995325807721</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G243" t="n">
-        <v>16.78568051288729</v>
+        <v>17.10349747464782</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I243" t="n">
-        <v>84.09388584663459</v>
+        <v>81.63506546186058</v>
       </c>
       <c r="J243" t="n">
-        <v>0.04113158676906406</v>
+        <v>0.02929311701672032</v>
       </c>
       <c r="K243" t="n">
-        <v>0.8662075670832698</v>
+        <v>0.676686949704659</v>
       </c>
       <c r="L243" t="b">
         <v>0</v>
@@ -9707,22 +9707,22 @@
         <v>10</v>
       </c>
       <c r="F244" t="n">
-        <v>0</v>
+        <v>0.6312434555400103</v>
       </c>
       <c r="G244" t="n">
-        <v>17.22617087457337</v>
+        <v>20.48834316314989</v>
       </c>
       <c r="H244" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I244" t="n">
-        <v>108.5828897238169</v>
+        <v>111.0542086038588</v>
       </c>
       <c r="J244" t="n">
-        <v>0.131285659744251</v>
+        <v>0.1419834696856976</v>
       </c>
       <c r="K244" t="n">
-        <v>2.12357831570878</v>
+        <v>2.085060884934582</v>
       </c>
       <c r="L244" t="b">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         <v>11.2138976720853</v>
       </c>
       <c r="H245" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I245" t="n">
-        <v>38.19582647183234</v>
+        <v>36.09828453310744</v>
       </c>
       <c r="J245" t="n">
-        <v>0.1093057264597961</v>
+        <v>0.1361817063538488</v>
       </c>
       <c r="K245" t="n">
-        <v>1.817026162749253</v>
+        <v>2.012551996095173</v>
       </c>
       <c r="L245" t="b">
         <v>0</v>
@@ -9783,22 +9783,22 @@
         <v>338</v>
       </c>
       <c r="F246" t="n">
-        <v>0.2705720980246611</v>
+        <v>0.6312563654197155</v>
       </c>
       <c r="G246" t="n">
-        <v>23.01105185385238</v>
+        <v>25.31403247806064</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I246" t="n">
-        <v>106.0297378961514</v>
+        <v>108.506421855006</v>
       </c>
       <c r="J246" t="n">
-        <v>0.06075002390880217</v>
+        <v>0.0440068059878537</v>
       </c>
       <c r="K246" t="n">
-        <v>1.139824145671397</v>
+        <v>0.8605747053752377</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -9827,16 +9827,16 @@
         <v>6.547900426854397</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I247" t="n">
-        <v>82.11812651631533</v>
+        <v>79.66238221620721</v>
       </c>
       <c r="J247" t="n">
-        <v>0.157554862114631</v>
+        <v>0.1307113727872923</v>
       </c>
       <c r="K247" t="n">
-        <v>2.489952518894592</v>
+        <v>1.944185227958575</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -9859,22 +9859,22 @@
         <v>94</v>
       </c>
       <c r="F248" t="n">
-        <v>0.2507741396326372</v>
+        <v>0.6312434555399736</v>
       </c>
       <c r="G248" t="n">
-        <v>16.43892245749527</v>
+        <v>18.18398887328586</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I248" t="n">
-        <v>107.5922534495869</v>
+        <v>110.042590562249</v>
       </c>
       <c r="J248" t="n">
-        <v>0.09145694319492477</v>
+        <v>0.1112421833150802</v>
       </c>
       <c r="K248" t="n">
-        <v>1.5680907876167</v>
+        <v>1.700864496917285</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -9903,16 +9903,16 @@
         <v>9.609651814712121</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I249" t="n">
-        <v>20.70074945360344</v>
+        <v>19.73502163275336</v>
       </c>
       <c r="J249" t="n">
-        <v>0.183734941654126</v>
+        <v>0.2293972715648486</v>
       </c>
       <c r="K249" t="n">
-        <v>2.855083733972476</v>
+        <v>3.177535238152576</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>387</v>
       </c>
       <c r="F250" t="n">
-        <v>0.6976423433388433</v>
+        <v>0.01251237329102261</v>
       </c>
       <c r="G250" t="n">
-        <v>26.85171748772526</v>
+        <v>22.28783075812694</v>
       </c>
       <c r="H250" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I250" t="n">
-        <v>16.68606215381434</v>
+        <v>15.83315784229396</v>
       </c>
       <c r="J250" t="n">
-        <v>0.03674578187691373</v>
+        <v>0.02997857390008206</v>
       </c>
       <c r="K250" t="n">
-        <v>0.8050391406486012</v>
+        <v>0.6852536067909704</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -9979,16 +9979,16 @@
         <v>10.94637643240904</v>
       </c>
       <c r="H251" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I251" t="n">
-        <v>33.18504717552116</v>
+        <v>31.98992578272659</v>
       </c>
       <c r="J251" t="n">
-        <v>0.05813661654152807</v>
+        <v>0.0594042038673525</v>
       </c>
       <c r="K251" t="n">
-        <v>1.10337518813226</v>
+        <v>1.053007272407396</v>
       </c>
       <c r="L251" t="b">
         <v>0</v>
@@ -10011,22 +10011,22 @@
         <v>466</v>
       </c>
       <c r="F252" t="n">
-        <v>0.6278781090048703</v>
+        <v>0.07543157732456961</v>
       </c>
       <c r="G252" t="n">
-        <v>16.55644631322318</v>
+        <v>14.24741750326592</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I252" t="n">
-        <v>26.85727431402685</v>
+        <v>26.20515053567233</v>
       </c>
       <c r="J252" t="n">
-        <v>0.02443819854337737</v>
+        <v>0.01571867693238567</v>
       </c>
       <c r="K252" t="n">
-        <v>0.6333863826626286</v>
+        <v>0.5070372224003609</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -10055,16 +10055,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I253" t="n">
-        <v>38.06550007279813</v>
+        <v>36.02511600539317</v>
       </c>
       <c r="J253" t="n">
-        <v>0.03813547541960685</v>
+        <v>0.04698404768848962</v>
       </c>
       <c r="K253" t="n">
-        <v>0.8244210715195115</v>
+        <v>0.8977834771178569</v>
       </c>
       <c r="L253" t="b">
         <v>0</v>
@@ -10093,16 +10093,16 @@
         <v>4.964088133786507</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I254" t="n">
-        <v>35.85900142959329</v>
+        <v>38.18345393616875</v>
       </c>
       <c r="J254" t="n">
-        <v>0.05604738587606124</v>
+        <v>0.04516962250182115</v>
       </c>
       <c r="K254" t="n">
-        <v>1.074236875916323</v>
+        <v>0.8751072756524583</v>
       </c>
       <c r="L254" t="b">
         <v>0</v>
@@ -10131,16 +10131,16 @@
         <v>6.022017186956544</v>
       </c>
       <c r="H255" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I255" t="n">
-        <v>102.602769117474</v>
+        <v>105.0611853762308</v>
       </c>
       <c r="J255" t="n">
-        <v>0.03459798756106196</v>
+        <v>0.02330084186883719</v>
       </c>
       <c r="K255" t="n">
-        <v>0.7750840464671165</v>
+        <v>0.601797095062045</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -10163,22 +10163,22 @@
         <v>98</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>0.3156217277700418</v>
       </c>
       <c r="G256" t="n">
-        <v>4.436552715791846</v>
+        <v>4.856634445842174</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I256" t="n">
-        <v>112.2895165637794</v>
+        <v>114.7405105044512</v>
       </c>
       <c r="J256" t="n">
-        <v>0.02935510831380669</v>
+        <v>0.05984199216884175</v>
       </c>
       <c r="K256" t="n">
-        <v>0.7019620810747278</v>
+        <v>1.058478633693994</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -10207,16 +10207,16 @@
         <v>7.970018757819834</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I257" t="n">
-        <v>54.72400336719295</v>
+        <v>52.39344246626491</v>
       </c>
       <c r="J257" t="n">
-        <v>0.04392594160629722</v>
+        <v>0.02718963449301625</v>
       </c>
       <c r="K257" t="n">
-        <v>0.9051801827141155</v>
+        <v>0.6503981868298223</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -10239,22 +10239,22 @@
         <v>609</v>
       </c>
       <c r="F258" t="n">
-        <v>0.1197305102757206</v>
+        <v>0.6320172848582126</v>
       </c>
       <c r="G258" t="n">
-        <v>21.23482026253326</v>
+        <v>24.38515807087288</v>
       </c>
       <c r="H258" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I258" t="n">
-        <v>116.6782477440529</v>
+        <v>119.1543274422245</v>
       </c>
       <c r="J258" t="n">
-        <v>0.05845973591444154</v>
+        <v>0.06947011682472622</v>
       </c>
       <c r="K258" t="n">
-        <v>1.10788170496958</v>
+        <v>1.178808364583417</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>8.150467777986734</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I259" t="n">
-        <v>38.59920485734258</v>
+        <v>36.92159136459008</v>
       </c>
       <c r="J259" t="n">
-        <v>0.05241424119579166</v>
+        <v>0.09473708020792547</v>
       </c>
       <c r="K259" t="n">
-        <v>1.023565733773331</v>
+        <v>1.494588125747507</v>
       </c>
       <c r="L259" t="b">
         <v>0</v>
@@ -10321,16 +10321,16 @@
         <v>5.170193323271385</v>
       </c>
       <c r="H260" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I260" t="n">
-        <v>103.2750778723411</v>
+        <v>105.7519122109659</v>
       </c>
       <c r="J260" t="n">
-        <v>0.05524374616929474</v>
+        <v>0.03330837618976785</v>
       </c>
       <c r="K260" t="n">
-        <v>1.063028585193836</v>
+        <v>0.7268685866290218</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -10353,22 +10353,22 @@
         <v>456</v>
       </c>
       <c r="F261" t="n">
-        <v>0.7533958926307559</v>
+        <v>0.6342469549387438</v>
       </c>
       <c r="G261" t="n">
-        <v>25.48471678778368</v>
+        <v>24.74170770527471</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I261" t="n">
-        <v>22.99530010104736</v>
+        <v>22.18524881187164</v>
       </c>
       <c r="J261" t="n">
-        <v>0.03438271156054848</v>
+        <v>0.01899728862120417</v>
       </c>
       <c r="K261" t="n">
-        <v>0.7720816114467793</v>
+        <v>0.548012435778527</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -10391,22 +10391,22 @@
         <v>550</v>
       </c>
       <c r="F262" t="n">
-        <v>0.6606788133830472</v>
+        <v>0.7262136290955139</v>
       </c>
       <c r="G262" t="n">
-        <v>23.92474720203816</v>
+        <v>24.31731083010372</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I262" t="n">
-        <v>157.7648191166797</v>
+        <v>155.9228539462806</v>
       </c>
       <c r="J262" t="n">
-        <v>0.02697141370590787</v>
+        <v>0.04453453832656704</v>
       </c>
       <c r="K262" t="n">
-        <v>0.6687169067335392</v>
+        <v>0.867170163220729</v>
       </c>
       <c r="L262" t="b">
         <v>0</v>
@@ -10435,16 +10435,16 @@
         <v>3.976587858956469</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I263" t="n">
-        <v>36.92273735321028</v>
+        <v>35.8192655025677</v>
       </c>
       <c r="J263" t="n">
-        <v>0.09456730506871755</v>
+        <v>0.06247323690787367</v>
       </c>
       <c r="K263" t="n">
-        <v>1.611470724969319</v>
+        <v>1.091363227804272</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -10473,16 +10473,16 @@
         <v>20.49853041073921</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I264" t="n">
-        <v>120.8199568757475</v>
+        <v>123.2807776588541</v>
       </c>
       <c r="J264" t="n">
-        <v>0.01617275754951263</v>
+        <v>0.01769928818453461</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5181090203959668</v>
+        <v>0.5317903729344046</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -10505,22 +10505,22 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>0.1022248412121741</v>
+        <v>0.07543157732456288</v>
       </c>
       <c r="G265" t="n">
-        <v>13.76832642517036</v>
+        <v>13.66094986961278</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I265" t="n">
-        <v>20.49079916147871</v>
+        <v>18.90845325847148</v>
       </c>
       <c r="J265" t="n">
-        <v>0.0325987978530071</v>
+        <v>0.03823644769066924</v>
       </c>
       <c r="K265" t="n">
-        <v>0.7472015273872165</v>
+        <v>0.7884583082727769</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -10543,22 +10543,22 @@
         <v>177</v>
       </c>
       <c r="F266" t="n">
-        <v>0.0002614276191779871</v>
+        <v>0.6312434555399274</v>
       </c>
       <c r="G266" t="n">
-        <v>14.1503720506546</v>
+        <v>16.82875112568169</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I266" t="n">
-        <v>77.75223933939445</v>
+        <v>75.2996610220434</v>
       </c>
       <c r="J266" t="n">
-        <v>0.04363854881734786</v>
+        <v>0.05355932634621149</v>
       </c>
       <c r="K266" t="n">
-        <v>0.9011719413306087</v>
+        <v>0.9799595539432727</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -10581,22 +10581,22 @@
         <v>193</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>0.6320172848581825</v>
       </c>
       <c r="G267" t="n">
-        <v>8.607438643406063</v>
+        <v>10.23945364370273</v>
       </c>
       <c r="H267" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I267" t="n">
-        <v>68.14914158312627</v>
+        <v>65.75998246291847</v>
       </c>
       <c r="J267" t="n">
-        <v>0.08658223534888157</v>
+        <v>0.06168670016393277</v>
       </c>
       <c r="K267" t="n">
-        <v>1.500103675648981</v>
+        <v>1.081533301612445</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>139</v>
       </c>
       <c r="F268" t="n">
-        <v>0.09993255188367305</v>
+        <v>0.632017284858201</v>
       </c>
       <c r="G268" t="n">
-        <v>21.87871136023609</v>
+        <v>25.26945611497919</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I268" t="n">
-        <v>107.8113370356629</v>
+        <v>110.2585381903155</v>
       </c>
       <c r="J268" t="n">
-        <v>0.04025835379228906</v>
+        <v>0.04181266359591997</v>
       </c>
       <c r="K268" t="n">
-        <v>0.8540286652821913</v>
+        <v>0.8331528996767521</v>
       </c>
       <c r="L268" t="b">
         <v>0</v>
@@ -10657,22 +10657,22 @@
         <v>99</v>
       </c>
       <c r="F269" t="n">
-        <v>0.6301703983333615</v>
+        <v>0.6312434555399266</v>
       </c>
       <c r="G269" t="n">
-        <v>18.31203035896111</v>
+        <v>18.31698805736985</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I269" t="n">
-        <v>33.20354613928577</v>
+        <v>30.76593474216654</v>
       </c>
       <c r="J269" t="n">
-        <v>0.06409777803584124</v>
+        <v>0.07780436541626286</v>
       </c>
       <c r="K269" t="n">
-        <v>1.186514971432401</v>
+        <v>1.282967577932637</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -10695,22 +10695,22 @@
         <v>8</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>0.0001526705929860085</v>
       </c>
       <c r="G270" t="n">
-        <v>4.436552715791846</v>
+        <v>4.436755915132027</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I270" t="n">
-        <v>65.94821543801203</v>
+        <v>63.56999750248387</v>
       </c>
       <c r="J270" t="n">
-        <v>0.02551457907476174</v>
+        <v>0.03037471571787101</v>
       </c>
       <c r="K270" t="n">
-        <v>0.6483985651396776</v>
+        <v>0.6902044814454087</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -10739,16 +10739,16 @@
         <v>17.03283675727564</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I271" t="n">
-        <v>88.98572970946806</v>
+        <v>86.53679202614136</v>
       </c>
       <c r="J271" t="n">
-        <v>0.007744949446603921</v>
+        <v>0.008261854103272735</v>
       </c>
       <c r="K271" t="n">
-        <v>0.4005671386604291</v>
+        <v>0.4138438419252883</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -10777,16 +10777,16 @@
         <v>5.940332650618145</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I272" t="n">
-        <v>36.99600262867412</v>
+        <v>35.06515555098649</v>
       </c>
       <c r="J272" t="n">
-        <v>0.05035317625847977</v>
+        <v>0.02818393523934563</v>
       </c>
       <c r="K272" t="n">
-        <v>0.9948202464351505</v>
+        <v>0.6628246920429475</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -10809,22 +10809,22 @@
         <v>39</v>
       </c>
       <c r="F273" t="n">
-        <v>0.4510791980308452</v>
+        <v>0.726601853298862</v>
       </c>
       <c r="G273" t="n">
-        <v>23.13278746983676</v>
+        <v>24.81696089824009</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I273" t="n">
-        <v>165.9026069159431</v>
+        <v>163.6858778477157</v>
       </c>
       <c r="J273" t="n">
-        <v>0.0460990596628863</v>
+        <v>0.05017080453588997</v>
       </c>
       <c r="K273" t="n">
-        <v>0.9354884648304107</v>
+        <v>0.9376107132165659</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -10847,22 +10847,22 @@
         <v>330</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>0.9468651833099453</v>
       </c>
       <c r="G274" t="n">
-        <v>18.16423328962717</v>
+        <v>23.32395731466741</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I274" t="n">
-        <v>68.55192274715682</v>
+        <v>66.16020045843086</v>
       </c>
       <c r="J274" t="n">
-        <v>0.2688295519333445</v>
+        <v>0.2905464826834747</v>
       </c>
       <c r="K274" t="n">
-        <v>4.041890611352551</v>
+        <v>3.941761749647497</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
@@ -10891,16 +10891,16 @@
         <v>20.82782016918717</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I275" t="n">
-        <v>104.5306423562862</v>
+        <v>106.9725225134952</v>
       </c>
       <c r="J275" t="n">
-        <v>0.07069573078897871</v>
+        <v>0.03681509965212897</v>
       </c>
       <c r="K275" t="n">
-        <v>1.278536025155526</v>
+        <v>0.7706946800387748</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -10923,22 +10923,22 @@
         <v>170</v>
       </c>
       <c r="F276" t="n">
-        <v>0.3139390545025023</v>
+        <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>8.786299689663418</v>
+        <v>8.030018742194814</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I276" t="n">
-        <v>108.8477795708756</v>
+        <v>111.3125103002659</v>
       </c>
       <c r="J276" t="n">
-        <v>0.07237274157704994</v>
+        <v>0.06307693742549564</v>
       </c>
       <c r="K276" t="n">
-        <v>1.301925143810548</v>
+        <v>1.098908115663494</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>352</v>
       </c>
       <c r="F277" t="n">
-        <v>0.3139390545024572</v>
+        <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>3.329801890890452</v>
+        <v>3.043189116699782</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I277" t="n">
-        <v>18.17102505759465</v>
+        <v>16.16552129253147</v>
       </c>
       <c r="J277" t="n">
-        <v>0.09349205749021704</v>
+        <v>0.1093930815208273</v>
       </c>
       <c r="K277" t="n">
-        <v>1.59647434368426</v>
+        <v>1.677754916470212</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -10999,22 +10999,22 @@
         <v>429</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.005869271986388712</v>
       </c>
       <c r="G278" t="n">
-        <v>10.648</v>
+        <v>10.66674880243332</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I278" t="n">
-        <v>24.50836755579533</v>
+        <v>23.45128887231625</v>
       </c>
       <c r="J278" t="n">
-        <v>0.06502393603168098</v>
+        <v>0.09973608086852448</v>
       </c>
       <c r="K278" t="n">
-        <v>1.199432013715061</v>
+        <v>1.557064301088495</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11037,22 +11037,22 @@
         <v>537</v>
       </c>
       <c r="F279" t="n">
-        <v>0.6278781090048962</v>
+        <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>18.25710831932041</v>
+        <v>15.36323637779488</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I279" t="n">
-        <v>28.84001031030273</v>
+        <v>26.84616567360449</v>
       </c>
       <c r="J279" t="n">
-        <v>0.04573214683132797</v>
+        <v>0.03486211029670912</v>
       </c>
       <c r="K279" t="n">
-        <v>0.9303711645635245</v>
+        <v>0.7462867405939992</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -11081,16 +11081,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I280" t="n">
-        <v>65.86372583391929</v>
+        <v>63.53985576360109</v>
       </c>
       <c r="J280" t="n">
-        <v>0.02278602568216852</v>
+        <v>0.01489300689685219</v>
       </c>
       <c r="K280" t="n">
-        <v>0.6103436763399905</v>
+        <v>0.4967182187802237</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -11113,22 +11113,22 @@
         <v>544</v>
       </c>
       <c r="F281" t="n">
-        <v>0.03959591678410032</v>
+        <v>0.0007738293182452965</v>
       </c>
       <c r="G281" t="n">
-        <v>13.8790716975982</v>
+        <v>13.71932493286239</v>
       </c>
       <c r="H281" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I281" t="n">
-        <v>103.4880239092246</v>
+        <v>105.9585994252374</v>
       </c>
       <c r="J281" t="n">
-        <v>0.05843434987054964</v>
+        <v>0.1002873238914751</v>
       </c>
       <c r="K281" t="n">
-        <v>1.107527648098275</v>
+        <v>1.563953589187375</v>
       </c>
       <c r="L281" t="b">
         <v>0</v>
@@ -11151,22 +11151,22 @@
         <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>0.631908093424227</v>
+        <v>0.6312434555399251</v>
       </c>
       <c r="G282" t="n">
-        <v>15.55357988815532</v>
+        <v>15.55097285939777</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I282" t="n">
-        <v>36.45468511525988</v>
+        <v>34.43914095773528</v>
       </c>
       <c r="J282" t="n">
-        <v>0.08384568117176068</v>
+        <v>0.118279480469321</v>
       </c>
       <c r="K282" t="n">
-        <v>1.461937200626962</v>
+        <v>1.788814757536435</v>
       </c>
       <c r="L282" t="b">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I283" t="n">
-        <v>118.8286387676094</v>
+        <v>121.2930211727403</v>
       </c>
       <c r="J283" t="n">
-        <v>0.02968581399910793</v>
+        <v>0.0521358502941222</v>
       </c>
       <c r="K283" t="n">
-        <v>0.7065744035287158</v>
+        <v>0.9621693303641921</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11227,22 +11227,22 @@
         <v>377</v>
       </c>
       <c r="F284" t="n">
-        <v>0.1253870698163085</v>
+        <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>4.887606012828303</v>
+        <v>4.710418346601499</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I284" t="n">
-        <v>29.59186674388968</v>
+        <v>28.17835312057534</v>
       </c>
       <c r="J284" t="n">
-        <v>0.07312110781639405</v>
+        <v>0.1309062201057508</v>
       </c>
       <c r="K284" t="n">
-        <v>1.312362540453395</v>
+        <v>1.946620377713341</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -11271,16 +11271,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H285" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I285" t="n">
-        <v>21.48311288982705</v>
+        <v>19.25068659894232</v>
       </c>
       <c r="J285" t="n">
-        <v>0.04715391210488935</v>
+        <v>0.09336101109847106</v>
       </c>
       <c r="K285" t="n">
-        <v>0.9502003969807847</v>
+        <v>1.477390381478097</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -11309,16 +11309,16 @@
         <v>6.380249524901044</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I286" t="n">
-        <v>108.2949720690951</v>
+        <v>110.7586252727911</v>
       </c>
       <c r="J286" t="n">
-        <v>0.04860138976032433</v>
+        <v>0.07884647848665349</v>
       </c>
       <c r="K286" t="n">
-        <v>0.9703882376758347</v>
+        <v>1.295991628804249</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -11341,22 +11341,22 @@
         <v>191</v>
       </c>
       <c r="F287" t="n">
-        <v>0.3007404155744564</v>
+        <v>0.6312434555399357</v>
       </c>
       <c r="G287" t="n">
-        <v>16.74934020564287</v>
+        <v>18.27261910361371</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I287" t="n">
-        <v>117.4924003835356</v>
+        <v>119.9692951507314</v>
       </c>
       <c r="J287" t="n">
-        <v>0.06979344808666384</v>
+        <v>0.1295275831732211</v>
       </c>
       <c r="K287" t="n">
-        <v>1.265951969444657</v>
+        <v>1.929390541476839</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -11379,22 +11379,22 @@
         <v>268</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>0.01496827675093042</v>
       </c>
       <c r="G288" t="n">
-        <v>4.313887457966422</v>
+        <v>4.333258896369386</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I288" t="n">
-        <v>17.33328039059763</v>
+        <v>15.31871851676592</v>
       </c>
       <c r="J288" t="n">
-        <v>0.062753947730667</v>
+        <v>0.09027497699661007</v>
       </c>
       <c r="K288" t="n">
-        <v>1.167772691010887</v>
+        <v>1.438821951356499</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -11417,22 +11417,22 @@
         <v>372</v>
       </c>
       <c r="F289" t="n">
-        <v>0.00402998441935881</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>18.82148403028074</v>
+        <v>18.79875642163598</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I289" t="n">
-        <v>26.97954215474278</v>
+        <v>25.11189274963553</v>
       </c>
       <c r="J289" t="n">
-        <v>0.06146746452148399</v>
+        <v>0.08812903304921438</v>
       </c>
       <c r="K289" t="n">
-        <v>1.149830225380191</v>
+        <v>1.412002516947111</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -11461,16 +11461,16 @@
         <v>5.832000000000001</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I290" t="n">
-        <v>86.06462386034174</v>
+        <v>83.60672766171015</v>
       </c>
       <c r="J290" t="n">
-        <v>0.05180002432261666</v>
+        <v>0.06350490335350305</v>
       </c>
       <c r="K290" t="n">
-        <v>1.014999306276982</v>
+        <v>1.104256719549246</v>
       </c>
       <c r="L290" t="b">
         <v>0</v>
@@ -11499,16 +11499,16 @@
         <v>29.25033432920041</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I291" t="n">
-        <v>79.14913125003444</v>
+        <v>76.69535432337047</v>
       </c>
       <c r="J291" t="n">
-        <v>0.1970772785555232</v>
+        <v>0.2592643895365634</v>
       </c>
       <c r="K291" t="n">
-        <v>3.041168106918565</v>
+        <v>3.550806502955177</v>
       </c>
       <c r="L291" t="b">
         <v>0</v>
@@ -11531,22 +11531,22 @@
         <v>556</v>
       </c>
       <c r="F292" t="n">
-        <v>0.3139390545025129</v>
+        <v>0.3592067884186558</v>
       </c>
       <c r="G292" t="n">
-        <v>7.882295301621195</v>
+        <v>7.980125572689588</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I292" t="n">
-        <v>31.8415415541979</v>
+        <v>29.61669166068819</v>
       </c>
       <c r="J292" t="n">
-        <v>0.1801346498712153</v>
+        <v>0.2002679563616882</v>
       </c>
       <c r="K292" t="n">
-        <v>2.804870788234632</v>
+        <v>2.813484835331167</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -11569,22 +11569,22 @@
         <v>240</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>0.6689592442021899</v>
       </c>
       <c r="G293" t="n">
-        <v>19.03856866993945</v>
+        <v>22.85937662237971</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I293" t="n">
-        <v>104.1880636553184</v>
+        <v>106.6613339185951</v>
       </c>
       <c r="J293" t="n">
-        <v>0.0325800794217188</v>
+        <v>0.06583193558812039</v>
       </c>
       <c r="K293" t="n">
-        <v>0.7469404631093048</v>
+        <v>1.133339347015165</v>
       </c>
       <c r="L293" t="b">
         <v>0</v>
@@ -11607,22 +11607,22 @@
         <v>466</v>
       </c>
       <c r="F294" t="n">
-        <v>0</v>
+        <v>0.001547658636490593</v>
       </c>
       <c r="G294" t="n">
-        <v>8.060074937616895</v>
+        <v>8.063817210993284</v>
       </c>
       <c r="H294" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I294" t="n">
-        <v>79.43164369144843</v>
+        <v>77.00743402227098</v>
       </c>
       <c r="J294" t="n">
-        <v>0.08214498093713463</v>
+        <v>0.1317480076914624</v>
       </c>
       <c r="K294" t="n">
-        <v>1.438217687391127</v>
+        <v>1.957140814171631</v>
       </c>
       <c r="L294" t="b">
         <v>0</v>
@@ -11645,22 +11645,22 @@
         <v>572</v>
       </c>
       <c r="F295" t="n">
-        <v>0.6278781090048654</v>
+        <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>19.46654381261656</v>
+        <v>16.38096837796838</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I295" t="n">
-        <v>64.67167054717289</v>
+        <v>62.32087399783248</v>
       </c>
       <c r="J295" t="n">
-        <v>0.2076835830469004</v>
+        <v>0.2380901705465084</v>
       </c>
       <c r="K295" t="n">
-        <v>3.18909328188147</v>
+        <v>3.286176768304844</v>
       </c>
       <c r="L295" t="b">
         <v>0</v>
@@ -11689,16 +11689,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I296" t="n">
-        <v>226.7478660520466</v>
+        <v>224.6613889065725</v>
       </c>
       <c r="J296" t="n">
-        <v>0.1136716517894194</v>
+        <v>0.1773517274016451</v>
       </c>
       <c r="K296" t="n">
-        <v>1.87791733071304</v>
+        <v>2.527083925256008</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -11727,16 +11727,16 @@
         <v>20.58068878827917</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I297" t="n">
-        <v>223.3993526565197</v>
+        <v>221.4163403853632</v>
       </c>
       <c r="J297" t="n">
-        <v>0.3029441201082962</v>
+        <v>0.3768182539473801</v>
       </c>
       <c r="K297" t="n">
-        <v>4.517683425915471</v>
+        <v>5.019963309199904</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -11765,16 +11765,16 @@
         <v>18.87858122317459</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I298" t="n">
-        <v>77.11740147624107</v>
+        <v>74.82185436263431</v>
       </c>
       <c r="J298" t="n">
-        <v>0.4645950648088458</v>
+        <v>0.476394513193428</v>
       </c>
       <c r="K298" t="n">
-        <v>6.772214615095272</v>
+        <v>6.264440806770453</v>
       </c>
       <c r="L298" t="b">
         <v>0</v>
@@ -11797,22 +11797,22 @@
         <v>195</v>
       </c>
       <c r="F299" t="n">
-        <v>0.6278781090048555</v>
+        <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>9.865635474735059</v>
+        <v>8.301867259839799</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I299" t="n">
-        <v>23.26395229330824</v>
+        <v>21.74405116195978</v>
       </c>
       <c r="J299" t="n">
-        <v>0.07227710918141356</v>
+        <v>0.04693541000075607</v>
       </c>
       <c r="K299" t="n">
-        <v>1.300591367388408</v>
+        <v>0.8971756162845964</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -11841,16 +11841,16 @@
         <v>5.352813839467986</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I300" t="n">
-        <v>26.37339902099465</v>
+        <v>24.94051482215637</v>
       </c>
       <c r="J300" t="n">
-        <v>0.0446522326144599</v>
+        <v>0.06681553141515277</v>
       </c>
       <c r="K300" t="n">
-        <v>0.9153096980928033</v>
+        <v>1.14563206500552</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -11879,16 +11879,16 @@
         <v>11.82363560839051</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I301" t="n">
-        <v>107.9641064865613</v>
+        <v>107.6213823426911</v>
       </c>
       <c r="J301" t="n">
-        <v>0.05656224683523835</v>
+        <v>0.02645691778173915</v>
       </c>
       <c r="K301" t="n">
-        <v>1.081417595414784</v>
+        <v>0.6412408890343195</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -11911,22 +11911,22 @@
         <v>189</v>
       </c>
       <c r="F302" t="n">
-        <v>0.2507741396326144</v>
+        <v>0.02993655350185781</v>
       </c>
       <c r="G302" t="n">
-        <v>23.19822906286911</v>
+        <v>21.76885202900664</v>
       </c>
       <c r="H302" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I302" t="n">
-        <v>33.61132342890492</v>
+        <v>31.86396102487339</v>
       </c>
       <c r="J302" t="n">
-        <v>0.1035781391015762</v>
+        <v>0.1018673624093364</v>
       </c>
       <c r="K302" t="n">
-        <v>1.73714401692091</v>
+        <v>1.583700488655796</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -11955,16 +11955,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I303" t="n">
-        <v>88.94740905995013</v>
+        <v>86.55466606625306</v>
       </c>
       <c r="J303" t="n">
-        <v>0.06585635376416159</v>
+        <v>0.052766500545495</v>
       </c>
       <c r="K303" t="n">
-        <v>1.211041668974301</v>
+        <v>0.9700510287992716</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -11987,22 +11987,22 @@
         <v>584</v>
       </c>
       <c r="F304" t="n">
-        <v>0</v>
+        <v>0.05289263828635841</v>
       </c>
       <c r="G304" t="n">
-        <v>5.092576558089235</v>
+        <v>5.173384501039015</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I304" t="n">
-        <v>106.9806842660125</v>
+        <v>109.4576641369723</v>
       </c>
       <c r="J304" t="n">
-        <v>0.09410693505149988</v>
+        <v>0.1359231582538181</v>
       </c>
       <c r="K304" t="n">
-        <v>1.605049985738236</v>
+        <v>2.009320730982746</v>
       </c>
       <c r="L304" t="b">
         <v>0</v>
@@ -12025,22 +12025,22 @@
         <v>181</v>
       </c>
       <c r="F305" t="n">
-        <v>0.2520238119065863</v>
+        <v>0.02993655350186084</v>
       </c>
       <c r="G305" t="n">
-        <v>18.90487115542105</v>
+        <v>17.73384945930461</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I305" t="n">
-        <v>116.3420605779878</v>
+        <v>118.8069473985389</v>
       </c>
       <c r="J305" t="n">
-        <v>0.09258538942265924</v>
+        <v>0.1451190837743335</v>
       </c>
       <c r="K305" t="n">
-        <v>1.583829125678705</v>
+        <v>2.12424895249123</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -12063,22 +12063,22 @@
         <v>418</v>
       </c>
       <c r="F306" t="n">
-        <v>0.3801911938682704</v>
+        <v>0.6371127275263401</v>
       </c>
       <c r="G306" t="n">
-        <v>24.26886442013284</v>
+        <v>25.94791455735085</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I306" t="n">
-        <v>23.99582442390082</v>
+        <v>22.29108278956808</v>
       </c>
       <c r="J306" t="n">
-        <v>0.1655905443254622</v>
+        <v>0.2194640914241477</v>
       </c>
       <c r="K306" t="n">
-        <v>2.602025456075483</v>
+        <v>3.053393005274838</v>
       </c>
       <c r="L306" t="b">
         <v>0</v>
@@ -12101,22 +12101,22 @@
         <v>249</v>
       </c>
       <c r="F307" t="n">
-        <v>0.04996627594184144</v>
+        <v>0.3156217277700418</v>
       </c>
       <c r="G307" t="n">
-        <v>9.018777061810063</v>
+        <v>9.726928148614416</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I307" t="n">
-        <v>105.60466210263</v>
+        <v>108.0473616971713</v>
       </c>
       <c r="J307" t="n">
-        <v>0.03737348730922107</v>
+        <v>0.02074549093407682</v>
       </c>
       <c r="K307" t="n">
-        <v>0.8137936918662018</v>
+        <v>0.5698610014511438</v>
       </c>
       <c r="L307" t="b">
         <v>0</v>
@@ -12145,16 +12145,16 @@
         <v>3.0214779496134</v>
       </c>
       <c r="H308" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I308" t="n">
-        <v>70.65909022983629</v>
+        <v>68.49527187931382</v>
       </c>
       <c r="J308" t="n">
-        <v>0.144721272899043</v>
+        <v>0.1913485704453476</v>
       </c>
       <c r="K308" t="n">
-        <v>2.310963604173042</v>
+        <v>2.702012731949516</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -12177,22 +12177,22 @@
         <v>361</v>
       </c>
       <c r="F309" t="n">
-        <v>0.6278781090048535</v>
+        <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>23.43870266616334</v>
+        <v>25.64056805142975</v>
       </c>
       <c r="H309" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I309" t="n">
-        <v>145.4003249552997</v>
+        <v>142.9697431236751</v>
       </c>
       <c r="J309" t="n">
-        <v>0.193011429484494</v>
+        <v>0.1707905299660034</v>
       </c>
       <c r="K309" t="n">
-        <v>2.984462075548851</v>
+        <v>2.445083831783951</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -12215,22 +12215,22 @@
         <v>503</v>
       </c>
       <c r="F310" t="n">
-        <v>0.1039625363030408</v>
+        <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>8.717868542902842</v>
+        <v>8.454192746797297</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I310" t="n">
-        <v>34.81595403461037</v>
+        <v>32.93836585854968</v>
       </c>
       <c r="J310" t="n">
-        <v>0.3383329160582359</v>
+        <v>0.3334714677895974</v>
       </c>
       <c r="K310" t="n">
-        <v>5.011247780670446</v>
+        <v>4.478226750969995</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>519</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>0.3156217277699938</v>
       </c>
       <c r="G311" t="n">
-        <v>9.801628028036975</v>
+        <v>10.72971005998732</v>
       </c>
       <c r="H311" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I311" t="n">
-        <v>115.3509789345894</v>
+        <v>117.8274930109075</v>
       </c>
       <c r="J311" t="n">
-        <v>0.0692480409573115</v>
+        <v>0.06514838595253097</v>
       </c>
       <c r="K311" t="n">
-        <v>1.258345225257645</v>
+        <v>1.124796526202208</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -12291,22 +12291,22 @@
         <v>9</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>0.09458456844065385</v>
       </c>
       <c r="G312" t="n">
-        <v>6.296969191603211</v>
+        <v>6.475648025644776</v>
       </c>
       <c r="H312" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I312" t="n">
-        <v>20.13193444980531</v>
+        <v>19.37993393889387</v>
       </c>
       <c r="J312" t="n">
-        <v>0.09965208952693654</v>
+        <v>0.08222395483121217</v>
       </c>
       <c r="K312" t="n">
-        <v>1.682387756555788</v>
+        <v>1.338202426249393</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12335,16 +12335,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H313" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I313" t="n">
-        <v>105.8789003117746</v>
+        <v>108.346043548387</v>
       </c>
       <c r="J313" t="n">
-        <v>0.04846247534394451</v>
+        <v>0.04519274494093514</v>
       </c>
       <c r="K313" t="n">
-        <v>0.968450810802548</v>
+        <v>0.8753962537219717</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12373,16 +12373,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H314" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I314" t="n">
-        <v>26.00261731347925</v>
+        <v>23.86473516311424</v>
       </c>
       <c r="J314" t="n">
-        <v>0.06880518520459246</v>
+        <v>0.0698687720146067</v>
       </c>
       <c r="K314" t="n">
-        <v>1.252168755898543</v>
+        <v>1.183790650691094</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12411,16 +12411,16 @@
         <v>4.289492277647788</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I315" t="n">
-        <v>25.54983911278873</v>
+        <v>23.25132212997007</v>
       </c>
       <c r="J315" t="n">
-        <v>0.01991620109106526</v>
+        <v>0.01937396992747339</v>
       </c>
       <c r="K315" t="n">
-        <v>0.5703184908385817</v>
+        <v>0.5527200981566569</v>
       </c>
       <c r="L315" t="b">
         <v>0</v>
@@ -12443,22 +12443,22 @@
         <v>542</v>
       </c>
       <c r="F316" t="n">
-        <v>0.6278781090049043</v>
+        <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>11.83915662694097</v>
+        <v>9.962572308395055</v>
       </c>
       <c r="H316" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I316" t="n">
-        <v>114.8833148848792</v>
+        <v>117.3602625184094</v>
       </c>
       <c r="J316" t="n">
-        <v>0.02362803876379312</v>
+        <v>0.04174175447274171</v>
       </c>
       <c r="K316" t="n">
-        <v>0.6220871570708743</v>
+        <v>0.8322666963905877</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -12487,16 +12487,16 @@
         <v>8.332258457345164</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I317" t="n">
-        <v>30.74724484597344</v>
+        <v>28.55845971489516</v>
       </c>
       <c r="J317" t="n">
-        <v>0.07238442272139119</v>
+        <v>0.1340024044243991</v>
       </c>
       <c r="K317" t="n">
-        <v>1.302088059680242</v>
+        <v>1.985315662533869</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -12519,22 +12519,22 @@
         <v>538</v>
       </c>
       <c r="F318" t="n">
-        <v>0.01385228580827913</v>
+        <v>0.07543157732456444</v>
       </c>
       <c r="G318" t="n">
-        <v>9.810143310535647</v>
+        <v>9.990623792789549</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I318" t="n">
-        <v>85.25994168740014</v>
+        <v>82.84809553799803</v>
       </c>
       <c r="J318" t="n">
-        <v>0.03839320758322701</v>
+        <v>0.02446680286096781</v>
       </c>
       <c r="K318" t="n">
-        <v>0.8280156388288016</v>
+        <v>0.6163689641876586</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12557,22 +12557,22 @@
         <v>62</v>
       </c>
       <c r="F319" t="n">
-        <v>0.09993255188368276</v>
+        <v>0.1899429661995712</v>
       </c>
       <c r="G319" t="n">
-        <v>20.56579082983738</v>
+        <v>21.10496705889037</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I319" t="n">
-        <v>39.80110853078232</v>
+        <v>37.86706947869204</v>
       </c>
       <c r="J319" t="n">
-        <v>0.06336243438950796</v>
+        <v>0.08072807027480121</v>
       </c>
       <c r="K319" t="n">
-        <v>1.176259199723212</v>
+        <v>1.319507260519007</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -12595,22 +12595,22 @@
         <v>17</v>
       </c>
       <c r="F320" t="n">
-        <v>0.6501754119448682</v>
+        <v>0.6312434555399274</v>
       </c>
       <c r="G320" t="n">
-        <v>19.12262980451418</v>
+        <v>19.0317479169732</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I320" t="n">
-        <v>78.7129236699044</v>
+        <v>76.28031730831748</v>
       </c>
       <c r="J320" t="n">
-        <v>0.03685208081070609</v>
+        <v>0.06202283514034478</v>
       </c>
       <c r="K320" t="n">
-        <v>0.8065216823192074</v>
+        <v>1.085734226787366</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -12633,22 +12633,22 @@
         <v>282</v>
       </c>
       <c r="F321" t="n">
-        <v>0.9430668357812737</v>
+        <v>0.7302873641417358</v>
       </c>
       <c r="G321" t="n">
-        <v>27.51854979935612</v>
+        <v>26.14931814304795</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I321" t="n">
-        <v>24.14846705458958</v>
+        <v>22.26579170095671</v>
       </c>
       <c r="J321" t="n">
-        <v>0.04474753036888981</v>
+        <v>0.1035625077169918</v>
       </c>
       <c r="K321" t="n">
-        <v>0.9166388073041291</v>
+        <v>1.604885962045359</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -12671,22 +12671,22 @@
         <v>10</v>
       </c>
       <c r="F322" t="n">
-        <v>0.2521254750514736</v>
+        <v>0.2837537053219952</v>
       </c>
       <c r="G322" t="n">
-        <v>15.61138523618781</v>
+        <v>15.7490971758529</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I322" t="n">
-        <v>230.1507886006399</v>
+        <v>228.675219788383</v>
       </c>
       <c r="J322" t="n">
-        <v>0.01469370644991958</v>
+        <v>0.01708222537759991</v>
       </c>
       <c r="K322" t="n">
-        <v>0.4974808277145054</v>
+        <v>0.52407848675157</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -12709,22 +12709,22 @@
         <v>105</v>
       </c>
       <c r="F323" t="n">
-        <v>0</v>
+        <v>0.01173854397277731</v>
       </c>
       <c r="G323" t="n">
-        <v>13.60856348039719</v>
+        <v>13.65648689664348</v>
       </c>
       <c r="H323" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I323" t="n">
-        <v>228.6075510479119</v>
+        <v>226.2278107914438</v>
       </c>
       <c r="J323" t="n">
-        <v>0.487562362229251</v>
+        <v>0.5032956930437169</v>
       </c>
       <c r="K323" t="n">
-        <v>7.092537446869582</v>
+        <v>6.600644568944935</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -12753,16 +12753,16 @@
         <v>11.61919519588168</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I324" t="n">
-        <v>269.6578134873851</v>
+        <v>267.6614719824601</v>
       </c>
       <c r="J324" t="n">
-        <v>0.5431981214476921</v>
+        <v>0.5972520611410271</v>
       </c>
       <c r="K324" t="n">
-        <v>7.868484377609954</v>
+        <v>7.774886167654103</v>
       </c>
       <c r="L324" t="b">
         <v>0</v>
@@ -12785,22 +12785,22 @@
         <v>10</v>
       </c>
       <c r="F325" t="n">
-        <v>0</v>
+        <v>0.0003856051149581994</v>
       </c>
       <c r="G325" t="n">
-        <v>5.564094176054176</v>
+        <v>5.564737839006495</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1691447774827022</v>
+        <v>0.1750952620997123</v>
       </c>
       <c r="I325" t="n">
-        <v>270.2638640101699</v>
+        <v>268.2461997551408</v>
       </c>
       <c r="J325" t="n">
         <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>14.23945909959438</v>
+        <v>12.80832235915076</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>

--- a/output/lstm_results/lstm_data_for_cnn.xlsx
+++ b/output/lstm_results/lstm_data_for_cnn.xlsx
@@ -517,10 +517,10 @@
         <v>11.11332497500186</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I2" t="n">
-        <v>125.7079298799892</v>
+        <v>124.3262143814385</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>3.130550111402148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I3" t="n">
-        <v>107.8036555658189</v>
+        <v>106.4305605231818</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6312434555400193</v>
+        <v>0.3833534905282807</v>
       </c>
       <c r="G4" t="n">
-        <v>26.86199461461181</v>
+        <v>25.18241587020466</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I4" t="n">
-        <v>27.66233458454895</v>
+        <v>28.47316595812926</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04505750084577682</v>
+        <v>0.5951892006378684</v>
       </c>
       <c r="G5" t="n">
-        <v>20.40228098434277</v>
+        <v>23.7245554245881</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I5" t="n">
-        <v>37.819406791761</v>
+        <v>38.05362038487433</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         <v>621</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.03731312714916836</v>
       </c>
       <c r="G6" t="n">
-        <v>12.89864333951443</v>
+        <v>13.04302995520815</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I6" t="n">
-        <v>60.15337380754412</v>
+        <v>61.58294078210703</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>502</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.01489622401923269</v>
       </c>
       <c r="G7" t="n">
-        <v>10.05955744553407</v>
+        <v>10.10451227190698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I7" t="n">
-        <v>87.45058533168832</v>
+        <v>88.57674629989116</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
         <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8171607952460306</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18.7131542527061</v>
+        <v>15.02885654333023</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I8" t="n">
-        <v>72.97620396885894</v>
+        <v>74.06598031578348</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -777,16 +777,16 @@
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02993655350185815</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>14.09369808784285</v>
+        <v>13.96824971139906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I9" t="n">
-        <v>84.2576080725613</v>
+        <v>85.41781853610156</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>406</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6462117322909167</v>
+        <v>0.773626803832149</v>
       </c>
       <c r="G10" t="n">
-        <v>24.86557469459941</v>
+        <v>25.66170815367089</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I10" t="n">
-        <v>39.32764223625534</v>
+        <v>40.68396813840372</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -853,16 +853,16 @@
         <v>368</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.1786585096886898</v>
       </c>
       <c r="G11" t="n">
-        <v>3.976587858956469</v>
+        <v>4.189723237114659</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I11" t="n">
-        <v>119.1061572061333</v>
+        <v>117.7765291818234</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         <v>379</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2975946003189555</v>
       </c>
       <c r="G12" t="n">
-        <v>5.484544739538552</v>
+        <v>5.974196009446874</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I12" t="n">
-        <v>104.8837510654145</v>
+        <v>103.5145149524218</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>10.87983322482473</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I13" t="n">
-        <v>33.59243690118958</v>
+        <v>34.66942230515379</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -967,16 +967,16 @@
         <v>662</v>
       </c>
       <c r="F14" t="n">
-        <v>0.09055894194721084</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5.552229658086575</v>
+        <v>5.405378062633547</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I14" t="n">
-        <v>182.3337158301924</v>
+        <v>183.7520546554697</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1005,16 +1005,16 @@
         <v>277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6312434555399341</v>
+        <v>0.5961513589799912</v>
       </c>
       <c r="G15" t="n">
-        <v>19.07672249673463</v>
+        <v>18.90786659519642</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I15" t="n">
-        <v>38.57227985105439</v>
+        <v>38.73852153989588</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1043,16 +1043,16 @@
         <v>686</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003841075862772198</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>10.12555463777191</v>
+        <v>10.12438798150288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I16" t="n">
-        <v>116.7570671852539</v>
+        <v>115.3666681299147</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1081,22 +1081,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7266018532988266</v>
+        <v>0.5381280975441328</v>
       </c>
       <c r="G17" t="n">
-        <v>24.1216480644051</v>
+        <v>23.00185245272622</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I17" t="n">
-        <v>111.2520380383647</v>
+        <v>109.9196310786236</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05280281285738973</v>
+        <v>0.07117533912770208</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9705048503766227</v>
+        <v>1.257611532524588</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1125,16 +1125,16 @@
         <v>5.248200453488796</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I18" t="n">
-        <v>191.3630010987614</v>
+        <v>192.3682051821898</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08900078827801797</v>
+        <v>0.09562359332823858</v>
       </c>
       <c r="K18" t="n">
-        <v>1.422897481006313</v>
+        <v>1.598741014765982</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1157,22 +1157,22 @@
         <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6312434555399205</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>26.50976397654575</v>
+        <v>22.28885569068094</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I19" t="n">
-        <v>30.00547991986788</v>
+        <v>30.58966353184178</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5909377935547293</v>
+        <v>0.5157709914462432</v>
       </c>
       <c r="K19" t="n">
-        <v>7.695972137499886</v>
+        <v>7.461109068102017</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.5951892006378768</v>
       </c>
       <c r="G20" t="n">
-        <v>8.916669781930919</v>
+        <v>10.50880144988873</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I20" t="n">
-        <v>64.55810277951949</v>
+        <v>65.98198029495637</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04207557980691856</v>
+        <v>0.0104592280209364</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8364387562736121</v>
+        <v>0.4104322052944498</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         <v>216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.001547658636490593</v>
+        <v>0.364323318398138</v>
       </c>
       <c r="G21" t="n">
-        <v>16.84805026088252</v>
+        <v>18.68081807592794</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I21" t="n">
-        <v>27.83536411711505</v>
+        <v>28.7086504990966</v>
       </c>
       <c r="J21" t="n">
-        <v>0.067471872020909</v>
+        <v>0.1104656187959975</v>
       </c>
       <c r="K21" t="n">
-        <v>1.153834834629424</v>
+        <v>1.805833612122856</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1277,16 +1277,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I22" t="n">
-        <v>107.3669355725416</v>
+        <v>106.0153727067974</v>
       </c>
       <c r="J22" t="n">
-        <v>0.03435292956081123</v>
+        <v>0.03697540924515345</v>
       </c>
       <c r="K22" t="n">
-        <v>0.739923135726542</v>
+        <v>0.7804157263197521</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>435</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.2138868098388862</v>
       </c>
       <c r="G23" t="n">
-        <v>13.21653808680624</v>
+        <v>14.06459103735658</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I23" t="n">
-        <v>22.38507822521032</v>
+        <v>23.12554096159242</v>
       </c>
       <c r="J23" t="n">
-        <v>0.09301421999347741</v>
+        <v>0.06962635540779759</v>
       </c>
       <c r="K23" t="n">
-        <v>1.473056278853738</v>
+        <v>1.235998373153897</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>678</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02993655350186084</v>
+        <v>0.4060274677024713</v>
       </c>
       <c r="G24" t="n">
-        <v>15.80317951144785</v>
+        <v>17.57033838650605</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I24" t="n">
-        <v>113.9725838494851</v>
+        <v>112.5892694242007</v>
       </c>
       <c r="J24" t="n">
-        <v>0.03044050270676376</v>
+        <v>0.02957647779124048</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6910266696650691</v>
+        <v>0.6771775304424568</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1385,22 +1385,22 @@
         <v>120</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09458456844067069</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>3.657510220055388</v>
+        <v>3.556590642736384</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I25" t="n">
-        <v>106.7501645888422</v>
+        <v>105.3604732968598</v>
       </c>
       <c r="J25" t="n">
-        <v>0.052453828970339</v>
+        <v>0.04957708895887434</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9661433429476661</v>
+        <v>0.9562485052516378</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>674</v>
       </c>
       <c r="F26" t="n">
-        <v>0.631781731247903</v>
+        <v>0.5961513589800258</v>
       </c>
       <c r="G26" t="n">
-        <v>22.69469586701329</v>
+        <v>22.49076219823504</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I26" t="n">
-        <v>63.15046102124055</v>
+        <v>64.56875548284938</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1210111879500158</v>
+        <v>0.04873444836510492</v>
       </c>
       <c r="K26" t="n">
-        <v>1.822954908164806</v>
+        <v>0.9444910379449606</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07543157732456826</v>
+        <v>0.03806034426027984</v>
       </c>
       <c r="G27" t="n">
-        <v>14.35829203798899</v>
+        <v>14.20087810883268</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I27" t="n">
-        <v>63.07748118121708</v>
+        <v>64.50701566469179</v>
       </c>
       <c r="J27" t="n">
-        <v>0.09340882523201029</v>
+        <v>0.07719098250288987</v>
       </c>
       <c r="K27" t="n">
-        <v>1.477987949750956</v>
+        <v>1.34154854058636</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1499,22 +1499,22 @@
         <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2045230187471987</v>
+        <v>0.5951892006379008</v>
       </c>
       <c r="G28" t="n">
-        <v>21.97447301503104</v>
+        <v>24.40099422378334</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I28" t="n">
-        <v>33.84603464998446</v>
+        <v>35.04079928524294</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0804996979294446</v>
+        <v>0.07690373752842843</v>
       </c>
       <c r="K28" t="n">
-        <v>1.316653123930471</v>
+        <v>1.337540576311663</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1537,22 +1537,22 @@
         <v>373</v>
       </c>
       <c r="F29" t="n">
-        <v>0.631525807791473</v>
+        <v>0.008619644781409842</v>
       </c>
       <c r="G29" t="n">
-        <v>26.51165196912239</v>
+        <v>22.34649229627227</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I29" t="n">
-        <v>13.17117668814933</v>
+        <v>11.82679437469452</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0371869860087279</v>
+        <v>0.03056447323122934</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7753424164163516</v>
+        <v>0.6909631517034162</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -1581,16 +1581,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I30" t="n">
-        <v>36.82715257770452</v>
+        <v>37.02019426331515</v>
       </c>
       <c r="J30" t="n">
-        <v>0.09819561126554245</v>
+        <v>0.07382933078240987</v>
       </c>
       <c r="K30" t="n">
-        <v>1.537811923351895</v>
+        <v>1.294643002813521</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1619,16 +1619,16 @@
         <v>7.790921447428411</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I31" t="n">
-        <v>157.6956344366866</v>
+        <v>158.9910764511143</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0286732895939513</v>
+        <v>0.02635594974707148</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6689405120913803</v>
+        <v>0.6322411085924601</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -1651,22 +1651,22 @@
         <v>469</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.5961513589799898</v>
       </c>
       <c r="G32" t="n">
-        <v>11.449738512298</v>
+        <v>13.49747166451959</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I32" t="n">
-        <v>56.46291252198176</v>
+        <v>57.87812290221395</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1825787252880413</v>
+        <v>0.1222728294615628</v>
       </c>
       <c r="K32" t="n">
-        <v>2.592409549041449</v>
+        <v>1.970581067218072</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1689,22 +1689,22 @@
         <v>305</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6235324590003333</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>19.94473792561125</v>
+        <v>16.80179799902379</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I33" t="n">
-        <v>30.02078356759165</v>
+        <v>31.45164435315388</v>
       </c>
       <c r="J33" t="n">
-        <v>0.03789056028278788</v>
+        <v>0.0291656377942774</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7841354998136065</v>
+        <v>0.6714450296962482</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1727,22 +1727,22 @@
         <v>193</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>0.7253779204408797</v>
       </c>
       <c r="G34" t="n">
-        <v>15.21432035945083</v>
+        <v>18.52515997842876</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I34" t="n">
-        <v>32.73088529106516</v>
+        <v>33.98316204155502</v>
       </c>
       <c r="J34" t="n">
-        <v>0.01349084418570487</v>
+        <v>0.02040937807656706</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4791943636447978</v>
+        <v>0.5492678664774465</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -1771,16 +1771,16 @@
         <v>20.91041556258507</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I35" t="n">
-        <v>16.45658571791968</v>
+        <v>17.87056869735334</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0263451882511215</v>
+        <v>0.04281570600990994</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6398445231965126</v>
+        <v>0.8619061016715328</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1803,22 +1803,22 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>0.07543157732456938</v>
+        <v>0.3570043753498616</v>
       </c>
       <c r="G36" t="n">
-        <v>16.13222510959525</v>
+        <v>17.46478862791835</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I36" t="n">
-        <v>31.88345706751251</v>
+        <v>32.02631717944388</v>
       </c>
       <c r="J36" t="n">
-        <v>0.05941122474830111</v>
+        <v>0.02883047339277337</v>
       </c>
       <c r="K36" t="n">
-        <v>1.053095017502661</v>
+        <v>0.6667684397928142</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -1841,22 +1841,22 @@
         <v>357</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0007712102299163989</v>
+        <v>0.1290559302512047</v>
       </c>
       <c r="G37" t="n">
-        <v>17.93231360520937</v>
+        <v>18.62228652001175</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I37" t="n">
-        <v>62.17228694537614</v>
+        <v>63.59345128450408</v>
       </c>
       <c r="J37" t="n">
-        <v>0.03018929413302932</v>
+        <v>0.02451037746208378</v>
       </c>
       <c r="K37" t="n">
-        <v>0.6878871319923712</v>
+        <v>0.606489612683885</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>285</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6312434555399422</v>
+        <v>0.4760653467354941</v>
       </c>
       <c r="G38" t="n">
-        <v>19.34731180248899</v>
+        <v>18.59003570069012</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I38" t="n">
-        <v>108.8184567997529</v>
+        <v>107.4327523783848</v>
       </c>
       <c r="J38" t="n">
-        <v>0.07609192930485013</v>
+        <v>0.09830492424141522</v>
       </c>
       <c r="K38" t="n">
-        <v>1.261566008694989</v>
+        <v>1.636153953073443</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>21.78421446827955</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I39" t="n">
-        <v>31.16165668302462</v>
+        <v>31.48672224991659</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08862067238135155</v>
+        <v>0.08092816860159326</v>
       </c>
       <c r="K39" t="n">
-        <v>1.41814689403456</v>
+        <v>1.393693955487292</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -1955,22 +1955,22 @@
         <v>296</v>
       </c>
       <c r="F40" t="n">
-        <v>0.09461038820027579</v>
+        <v>0.03806034426027984</v>
       </c>
       <c r="G40" t="n">
-        <v>15.34136046013107</v>
+        <v>15.08827736466777</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I40" t="n">
-        <v>221.8573045094599</v>
+        <v>223.2837414757134</v>
       </c>
       <c r="J40" t="n">
-        <v>0.045776558050654</v>
+        <v>0.04322337500139405</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8826925940678825</v>
+        <v>0.867594356990303</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -1999,16 +1999,16 @@
         <v>3.307725502516798</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I41" t="n">
-        <v>184.8851312329546</v>
+        <v>186.1988743998944</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1142150664496884</v>
+        <v>0.117011084186937</v>
       </c>
       <c r="K41" t="n">
-        <v>1.738018796465585</v>
+        <v>1.897163291597112</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2031,22 +2031,22 @@
         <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>0.01903017213013992</v>
       </c>
       <c r="G42" t="n">
-        <v>9.292517850399857</v>
+        <v>9.345569314664509</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I42" t="n">
-        <v>62.61609427293096</v>
+        <v>64.03661408127596</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2204154585622971</v>
+        <v>0.1302543276600578</v>
       </c>
       <c r="K42" t="n">
-        <v>3.065282937717766</v>
+        <v>2.081947888162836</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6312434555399227</v>
+        <v>0.4950623756433119</v>
       </c>
       <c r="G43" t="n">
-        <v>11.31586089924149</v>
+        <v>10.92716716488289</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I43" t="n">
-        <v>119.7625441551378</v>
+        <v>118.4057146636658</v>
       </c>
       <c r="J43" t="n">
-        <v>0.02636915213894598</v>
+        <v>0.02850515019238923</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6401440174673125</v>
+        <v>0.6622291653727324</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2107,22 +2107,22 @@
         <v>71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1891820467611271</v>
+        <v>0.3568752063885261</v>
       </c>
       <c r="G44" t="n">
-        <v>20.2462076234199</v>
+        <v>21.21005026440009</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I44" t="n">
-        <v>122.0105998733219</v>
+        <v>120.6542969456362</v>
       </c>
       <c r="J44" t="n">
-        <v>0.01662753615676698</v>
+        <v>0.02682423662967152</v>
       </c>
       <c r="K44" t="n">
-        <v>0.5183959022881761</v>
+        <v>0.6387751727629105</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2145,22 +2145,22 @@
         <v>620</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0676523421641429</v>
+        <v>0.3570961128829306</v>
       </c>
       <c r="G45" t="n">
-        <v>18.7747959046275</v>
+        <v>20.37264083536693</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I45" t="n">
-        <v>29.73733545847884</v>
+        <v>29.73686546975663</v>
       </c>
       <c r="J45" t="n">
-        <v>0.1184149986231473</v>
+        <v>0.08112386973333242</v>
       </c>
       <c r="K45" t="n">
-        <v>1.790508427234675</v>
+        <v>1.396424597323582</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2183,22 +2183,22 @@
         <v>496</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6312434555399415</v>
+        <v>0.5951892006378828</v>
       </c>
       <c r="G46" t="n">
-        <v>22.69161499715559</v>
+        <v>22.48525519765746</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I46" t="n">
-        <v>14.64375472210871</v>
+        <v>16.00090322117087</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02733403045755977</v>
+        <v>0.02457609320427136</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6522028090357076</v>
+        <v>0.6074065524753187</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I47" t="n">
-        <v>30.25915836979654</v>
+        <v>31.61185113963246</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05369119003244867</v>
+        <v>0.07366936984565307</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9816075510814598</v>
+        <v>1.292411048290834</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         <v>12.79325302649799</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I48" t="n">
-        <v>29.71262768997234</v>
+        <v>30.86520467093996</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03216611121099414</v>
+        <v>0.03584021938597341</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7125928639506445</v>
+        <v>0.7645762833177536</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2303,16 +2303,16 @@
         <v>13.11028664827737</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I49" t="n">
-        <v>21.66026148867186</v>
+        <v>21.79264110153531</v>
       </c>
       <c r="J49" t="n">
-        <v>0.02583787546889912</v>
+        <v>0.0124047633535027</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6335042635152803</v>
+        <v>0.4375784978369297</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         <v>430</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9995621586029051</v>
+        <v>0.3778296952028944</v>
       </c>
       <c r="G50" t="n">
-        <v>26.91265150110176</v>
+        <v>23.05092228433527</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I50" t="n">
-        <v>27.6747619224327</v>
+        <v>28.48704509831741</v>
       </c>
       <c r="J50" t="n">
-        <v>0.03664557256422207</v>
+        <v>0.04087174102814416</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7685759757640189</v>
+        <v>0.8347817204259136</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -2373,22 +2373,22 @@
         <v>551</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>0.5951892006378862</v>
       </c>
       <c r="G51" t="n">
-        <v>5.431724311855306</v>
+        <v>6.401595407232866</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I51" t="n">
-        <v>18.59836062288836</v>
+        <v>18.76150444288304</v>
       </c>
       <c r="J51" t="n">
-        <v>0.01542593962894261</v>
+        <v>0.02452316651819899</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5033786697534475</v>
+        <v>0.6066680599486733</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>5.066791391008713</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I52" t="n">
-        <v>35.58856070476764</v>
+        <v>36.77136260216994</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02014427321902604</v>
+        <v>0.03985540235201662</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5623471429954581</v>
+        <v>0.8206006225231569</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2455,16 +2455,16 @@
         <v>4.862088337329959</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I53" t="n">
-        <v>73.82711576729665</v>
+        <v>75.17190931593855</v>
       </c>
       <c r="J53" t="n">
-        <v>0.01649662359391261</v>
+        <v>0.02044907895341146</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5167597920360427</v>
+        <v>0.5498218176696819</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2487,22 +2487,22 @@
         <v>537</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>0.003777446303530025</v>
       </c>
       <c r="G54" t="n">
-        <v>6.104072738754019</v>
+        <v>6.110990080855065</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I54" t="n">
-        <v>36.42098714126841</v>
+        <v>36.40969723893878</v>
       </c>
       <c r="J54" t="n">
-        <v>0.06515170415924339</v>
+        <v>0.04257711143576667</v>
       </c>
       <c r="K54" t="n">
-        <v>1.124837996263618</v>
+        <v>0.8585769623851246</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -2531,16 +2531,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I55" t="n">
-        <v>36.56439641453533</v>
+        <v>36.95769840833051</v>
       </c>
       <c r="J55" t="n">
-        <v>0.009418109434795489</v>
+        <v>0.009816980564778357</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4282944122963896</v>
+        <v>0.4014708479560907</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2563,22 +2563,22 @@
         <v>335</v>
       </c>
       <c r="F56" t="n">
-        <v>0.07455010804135394</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3.825000981330775</v>
+        <v>3.741326101798666</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I56" t="n">
-        <v>116.8611519589317</v>
+        <v>115.5019490161087</v>
       </c>
       <c r="J56" t="n">
-        <v>0.006748753540265115</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.3949335151417579</v>
+        <v>0.2644933169729917</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>4.362815948444307</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I57" t="n">
-        <v>121.7073455096708</v>
+        <v>120.3226405281799</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1790477691445056</v>
+        <v>0.1224474511474744</v>
       </c>
       <c r="K57" t="n">
-        <v>2.548280602053383</v>
+        <v>1.973017584967542</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I58" t="n">
-        <v>35.45709376883417</v>
+        <v>36.86247906006698</v>
       </c>
       <c r="J58" t="n">
-        <v>0.045054791907046</v>
+        <v>0.009429943128561859</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8736721535429079</v>
+        <v>0.3960704672523563</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6462375520504614</v>
+        <v>0.6783175077595754</v>
       </c>
       <c r="G59" t="n">
-        <v>24.96434429224193</v>
+        <v>25.16558585377399</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I59" t="n">
-        <v>30.26266093263617</v>
+        <v>31.63658954004927</v>
       </c>
       <c r="J59" t="n">
-        <v>0.05087484909012832</v>
+        <v>0.03975892685893766</v>
       </c>
       <c r="K59" t="n">
-        <v>0.9464096740499082</v>
+        <v>0.8192544881639074</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2715,22 +2715,22 @@
         <v>378</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03032215861681859</v>
+        <v>0.5951892006378728</v>
       </c>
       <c r="G60" t="n">
-        <v>22.70493408641378</v>
+        <v>26.517830201182</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I60" t="n">
-        <v>24.07313538594742</v>
+        <v>24.82197678875015</v>
       </c>
       <c r="J60" t="n">
-        <v>0.06877232187720636</v>
+        <v>0.05115901572137915</v>
       </c>
       <c r="K60" t="n">
-        <v>1.17008750966597</v>
+        <v>0.9783213229264979</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>4.710418346601499</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I61" t="n">
-        <v>26.39782369780529</v>
+        <v>27.76439945401208</v>
       </c>
       <c r="J61" t="n">
-        <v>0.03018006709735797</v>
+        <v>0.0258531300616107</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6877718149645051</v>
+        <v>0.6252252039984114</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2797,16 +2797,16 @@
         <v>13.57276718285553</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I62" t="n">
-        <v>87.26464665313321</v>
+        <v>88.43921665496805</v>
       </c>
       <c r="J62" t="n">
-        <v>0.0645442386648479</v>
+        <v>0.06634879302686382</v>
       </c>
       <c r="K62" t="n">
-        <v>1.117246054730066</v>
+        <v>1.19026614422455</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -2829,22 +2829,22 @@
         <v>659</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>0.1069434049194428</v>
       </c>
       <c r="G63" t="n">
-        <v>4.560359086738675</v>
+        <v>4.706669185256021</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I63" t="n">
-        <v>33.24286973707032</v>
+        <v>34.35772109356829</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1378608822711742</v>
+        <v>0.08370465832416041</v>
       </c>
       <c r="K63" t="n">
-        <v>2.033537888308802</v>
+        <v>1.432434656305394</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -2867,22 +2867,22 @@
         <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>0.075431577324564</v>
+        <v>0.192140657863612</v>
       </c>
       <c r="G64" t="n">
-        <v>10.28719993112518</v>
+        <v>10.63941244115459</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I64" t="n">
-        <v>176.7584856130123</v>
+        <v>178.1886232491165</v>
       </c>
       <c r="J64" t="n">
-        <v>0.05799678994524692</v>
+        <v>0.04240653799683514</v>
       </c>
       <c r="K64" t="n">
-        <v>1.035417789039679</v>
+        <v>0.8561969303210941</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -2905,22 +2905,22 @@
         <v>692</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3156217277699857</v>
+        <v>0.01026339997102327</v>
       </c>
       <c r="G65" t="n">
-        <v>12.16560702396568</v>
+        <v>11.14754312476978</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I65" t="n">
-        <v>27.21472416797106</v>
+        <v>28.43574905151868</v>
       </c>
       <c r="J65" t="n">
-        <v>0.2134404065358921</v>
+        <v>0.08354331737309077</v>
       </c>
       <c r="K65" t="n">
-        <v>2.978110600084593</v>
+        <v>1.430183446274147</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -2943,22 +2943,22 @@
         <v>489</v>
       </c>
       <c r="F66" t="n">
-        <v>0.6312434555399274</v>
+        <v>0.5951892006378646</v>
       </c>
       <c r="G66" t="n">
-        <v>19.71006804936173</v>
+        <v>19.53082273380041</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I66" t="n">
-        <v>86.85206065970853</v>
+        <v>88.06986888223165</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>0.01751897000178738</v>
       </c>
       <c r="K66" t="n">
-        <v>0.3105893955584261</v>
+        <v>0.5089376489523727</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -2981,22 +2981,22 @@
         <v>259</v>
       </c>
       <c r="F67" t="n">
-        <v>0.001547658636490593</v>
+        <v>0.06404688595454136</v>
       </c>
       <c r="G67" t="n">
-        <v>4.413976484143277</v>
+        <v>4.496699112124089</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I67" t="n">
-        <v>16.86802251777535</v>
+        <v>18.20773370358911</v>
       </c>
       <c r="J67" t="n">
-        <v>0.04893793645695847</v>
+        <v>0.04145116055714369</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9222026571867428</v>
+        <v>0.8428664320092799</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3019,22 +3019,22 @@
         <v>627</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6312434555399909</v>
+        <v>0.5951892006379293</v>
       </c>
       <c r="G68" t="n">
-        <v>22.21657348203934</v>
+        <v>22.01453375723949</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I68" t="n">
-        <v>115.0717256223206</v>
+        <v>113.6814412022847</v>
       </c>
       <c r="J68" t="n">
-        <v>0.05206878247586127</v>
+        <v>0.03366746126235582</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9613311346811162</v>
+        <v>0.7342595233697493</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>0.009446383408605374</v>
+        <v>0.2975946003189912</v>
       </c>
       <c r="G69" t="n">
-        <v>12.06335110328222</v>
+        <v>13.10321415287696</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I69" t="n">
-        <v>14.53484343025496</v>
+        <v>14.51460204666816</v>
       </c>
       <c r="J69" t="n">
-        <v>0.06640070973224391</v>
+        <v>0.1020090995145471</v>
       </c>
       <c r="K69" t="n">
-        <v>1.140447734385017</v>
+        <v>1.687838763886115</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>0.02976497305343656</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G70" t="n">
-        <v>18.76577415155641</v>
+        <v>20.59101867377917</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I70" t="n">
-        <v>27.37316340460314</v>
+        <v>28.4940097654383</v>
       </c>
       <c r="J70" t="n">
-        <v>0.05413005788255321</v>
+        <v>0.05328615671300892</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9870924042783722</v>
+        <v>1.008001581450364</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3133,22 +3133,22 @@
         <v>421</v>
       </c>
       <c r="F71" t="n">
-        <v>0.6312563654197627</v>
+        <v>0.7021326055573247</v>
       </c>
       <c r="G71" t="n">
-        <v>16.1005979932334</v>
+        <v>16.38843354153381</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I71" t="n">
-        <v>134.7042397844755</v>
+        <v>135.3698516483658</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0606884503987622</v>
+        <v>0.05598102072613393</v>
       </c>
       <c r="K71" t="n">
-        <v>1.069057442616375</v>
+        <v>1.045603348757255</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -3171,22 +3171,22 @@
         <v>694</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2063670837128264</v>
+        <v>0.892783800956821</v>
       </c>
       <c r="G72" t="n">
-        <v>23.31105106649919</v>
+        <v>27.83151699958124</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I72" t="n">
-        <v>22.5455495730006</v>
+        <v>22.8818978209353</v>
       </c>
       <c r="J72" t="n">
-        <v>0.07804509625251528</v>
+        <v>0.01474056606293384</v>
       </c>
       <c r="K72" t="n">
-        <v>1.285976167640223</v>
+        <v>0.4701702388402119</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>250</v>
       </c>
       <c r="F73" t="n">
-        <v>0.1891691368813207</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>18.28570620485455</v>
+        <v>17.30370795523318</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I73" t="n">
-        <v>43.80983571802437</v>
+        <v>42.39975683390819</v>
       </c>
       <c r="J73" t="n">
-        <v>0.03760779108758551</v>
+        <v>0.03660892665848817</v>
       </c>
       <c r="K73" t="n">
-        <v>0.7806015259216375</v>
+        <v>0.7753021499468071</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -3247,22 +3247,22 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0.6592360865923952</v>
       </c>
       <c r="G74" t="n">
-        <v>27.07616621994333</v>
+        <v>24.9469553673627</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I74" t="n">
-        <v>74.50890895960447</v>
+        <v>75.93808782829193</v>
       </c>
       <c r="J74" t="n">
-        <v>0.01472370166717854</v>
+        <v>0.02578941513991383</v>
       </c>
       <c r="K74" t="n">
-        <v>0.4946022872304228</v>
+        <v>0.6243361819000962</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3285,22 +3285,22 @@
         <v>564</v>
       </c>
       <c r="F75" t="n">
-        <v>0.6543106743578074</v>
+        <v>0.7023535120516848</v>
       </c>
       <c r="G75" t="n">
-        <v>23.83793567779642</v>
+        <v>24.12513334953356</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I75" t="n">
-        <v>109.6439904846215</v>
+        <v>108.2646034605665</v>
       </c>
       <c r="J75" t="n">
-        <v>0.0693436007569946</v>
+        <v>0.05807055728311725</v>
       </c>
       <c r="K75" t="n">
-        <v>1.177227200553304</v>
+        <v>1.074758908003385</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3323,22 +3323,22 @@
         <v>521</v>
       </c>
       <c r="F76" t="n">
-        <v>0.00445934016114399</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>17.52146665824808</v>
+        <v>17.49805772078718</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I76" t="n">
-        <v>116.1616580623895</v>
+        <v>114.7970277367613</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1029304058911647</v>
+        <v>0.1166115144834716</v>
       </c>
       <c r="K76" t="n">
-        <v>1.596986122220374</v>
+        <v>1.89158804663506</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>607</v>
       </c>
       <c r="F77" t="n">
-        <v>0.09458456844065385</v>
+        <v>0.2329169819690044</v>
       </c>
       <c r="G77" t="n">
-        <v>18.03463370901911</v>
+        <v>18.76241496853449</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I77" t="n">
-        <v>115.1760411915495</v>
+        <v>113.8165305589208</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1045702434882503</v>
+        <v>0.05040346690741452</v>
       </c>
       <c r="K77" t="n">
-        <v>1.617480374612408</v>
+        <v>0.9677790578796055</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3399,22 +3399,22 @@
         <v>316</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>0.1876591470898412</v>
       </c>
       <c r="G78" t="n">
-        <v>5.590695395029137</v>
+        <v>5.905438933870218</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I78" t="n">
-        <v>49.77025100071132</v>
+        <v>51.12330019301063</v>
       </c>
       <c r="J78" t="n">
-        <v>0.06489944498710261</v>
+        <v>0.08432075995561805</v>
       </c>
       <c r="K78" t="n">
-        <v>1.121685328492585</v>
+        <v>1.441031197752619</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3437,22 +3437,22 @@
         <v>438</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>0.000441812988819266</v>
       </c>
       <c r="G79" t="n">
-        <v>19.31962732559818</v>
+        <v>19.32218802428566</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I79" t="n">
-        <v>91.40235674066331</v>
+        <v>92.30076899316654</v>
       </c>
       <c r="J79" t="n">
-        <v>0.07339447061342587</v>
+        <v>0.06563548997055982</v>
       </c>
       <c r="K79" t="n">
-        <v>1.227853890289247</v>
+        <v>1.180313339403302</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -3475,22 +3475,22 @@
         <v>421</v>
       </c>
       <c r="F80" t="n">
-        <v>0.03771578866228487</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>2.968363804641259</v>
+        <v>2.935153317971652</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I80" t="n">
-        <v>27.69706104912006</v>
+        <v>28.55776405149015</v>
       </c>
       <c r="J80" t="n">
-        <v>0.1291293308948217</v>
+        <v>0.09973742284354106</v>
       </c>
       <c r="K80" t="n">
-        <v>1.924413290849261</v>
+        <v>1.65614178134316</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3513,22 +3513,22 @@
         <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>0.5951892006378883</v>
       </c>
       <c r="G81" t="n">
-        <v>10.68101703958944</v>
+        <v>12.58818483772731</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I81" t="n">
-        <v>116.6657330243738</v>
+        <v>115.3166139883762</v>
       </c>
       <c r="J81" t="n">
-        <v>0.041574142364369</v>
+        <v>0.02523071726945565</v>
       </c>
       <c r="K81" t="n">
-        <v>0.830171925018681</v>
+        <v>0.6165406021537686</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -3551,22 +3551,22 @@
         <v>340</v>
       </c>
       <c r="F82" t="n">
-        <v>0.005869271986388712</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>4.419696478273785</v>
+        <v>4.411928036584459</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I82" t="n">
-        <v>31.30922545993537</v>
+        <v>31.15512129592505</v>
       </c>
       <c r="J82" t="n">
-        <v>0.02488523194201968</v>
+        <v>0.04211492978310331</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6215983791068462</v>
+        <v>0.8521280852349898</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3589,22 +3589,22 @@
         <v>364</v>
       </c>
       <c r="F83" t="n">
-        <v>0.631243455539904</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>23.74842488019001</v>
+        <v>19.96717947032079</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I83" t="n">
-        <v>72.90972109658848</v>
+        <v>74.13477741184354</v>
       </c>
       <c r="J83" t="n">
-        <v>0.03234371530215913</v>
+        <v>0.01784680031872117</v>
       </c>
       <c r="K83" t="n">
-        <v>0.7148125124552659</v>
+        <v>0.5135119054764317</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -3633,16 +3633,16 @@
         <v>7.583696723893961</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I84" t="n">
-        <v>24.62229984380533</v>
+        <v>25.36910668034387</v>
       </c>
       <c r="J84" t="n">
-        <v>0.03052300254622423</v>
+        <v>0.02114838353087327</v>
       </c>
       <c r="K84" t="n">
-        <v>0.6920577306281853</v>
+        <v>0.5595793000028518</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3665,22 +3665,22 @@
         <v>126</v>
       </c>
       <c r="F85" t="n">
-        <v>0.8171607952459812</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>25.16673733824778</v>
+        <v>26.27539237994364</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I85" t="n">
-        <v>17.82274990983389</v>
+        <v>19.22765176316778</v>
       </c>
       <c r="J85" t="n">
-        <v>0.0201327640972012</v>
+        <v>0.009590700929010199</v>
       </c>
       <c r="K85" t="n">
-        <v>0.5622033050642458</v>
+        <v>0.3983135405116324</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3703,22 +3703,22 @@
         <v>474</v>
       </c>
       <c r="F86" t="n">
-        <v>0.07543157732456288</v>
+        <v>0.1784376031942697</v>
       </c>
       <c r="G86" t="n">
-        <v>10.48651791966895</v>
+        <v>10.80339941910567</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I86" t="n">
-        <v>26.95889411917921</v>
+        <v>28.37676406093437</v>
       </c>
       <c r="J86" t="n">
-        <v>0.05704510055548651</v>
+        <v>0.04104277419760721</v>
       </c>
       <c r="K86" t="n">
-        <v>1.023523829182169</v>
+        <v>0.837168167166301</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -3747,16 +3747,16 @@
         <v>10.61501705132875</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I87" t="n">
-        <v>26.79523771556672</v>
+        <v>28.04427858735315</v>
       </c>
       <c r="J87" t="n">
-        <v>0.04449431440052245</v>
+        <v>0.04145284809972126</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8666674553342765</v>
+        <v>0.8428899784973451</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>3.240904040541774</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I88" t="n">
-        <v>76.10378933863043</v>
+        <v>77.23657795004371</v>
       </c>
       <c r="J88" t="n">
-        <v>0.003743268412839851</v>
+        <v>0.006405490195938278</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3573717645931487</v>
+        <v>0.3538699054246448</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>0.01903017213013642</v>
       </c>
       <c r="G89" t="n">
-        <v>3.330100148644182</v>
+        <v>3.349111862355969</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I89" t="n">
-        <v>31.57034842915032</v>
+        <v>31.38438911698386</v>
       </c>
       <c r="J89" t="n">
-        <v>0.02403588599167712</v>
+        <v>0.03986693367006636</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6109834802257564</v>
+        <v>0.8207615204148264</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -3861,16 +3861,16 @@
         <v>5.537535282054643</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I90" t="n">
-        <v>65.73757519951349</v>
+        <v>67.15884312996096</v>
       </c>
       <c r="J90" t="n">
-        <v>0.05186784461347131</v>
+        <v>0.06563371653183789</v>
       </c>
       <c r="K90" t="n">
-        <v>0.9588198669346915</v>
+        <v>1.180288594395825</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -3893,22 +3893,22 @@
         <v>643</v>
       </c>
       <c r="F91" t="n">
-        <v>0.6312434555399501</v>
+        <v>0.1999768503251298</v>
       </c>
       <c r="G91" t="n">
-        <v>12.50777167618921</v>
+        <v>11.14717645585418</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I91" t="n">
-        <v>101.9961438580741</v>
+        <v>100.6533425672609</v>
       </c>
       <c r="J91" t="n">
-        <v>0.006518371940374905</v>
+        <v>0.02064318352719496</v>
       </c>
       <c r="K91" t="n">
-        <v>0.3920542674266049</v>
+        <v>0.5525301825374686</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -3931,22 +3931,22 @@
         <v>327</v>
       </c>
       <c r="F92" t="n">
-        <v>2.581975960509618e-05</v>
+        <v>0.3518891294774103</v>
       </c>
       <c r="G92" t="n">
-        <v>16.91731694594734</v>
+        <v>18.70307805321443</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I92" t="n">
-        <v>87.92429791115475</v>
+        <v>89.12217466696183</v>
       </c>
       <c r="J92" t="n">
-        <v>0.1123175579396413</v>
+        <v>0.06060238684240486</v>
       </c>
       <c r="K92" t="n">
-        <v>1.714304241810873</v>
+        <v>1.110085835627701</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I93" t="n">
-        <v>96.10328747417087</v>
+        <v>96.45277424442565</v>
       </c>
       <c r="J93" t="n">
-        <v>0.02720717487894838</v>
+        <v>0.04085151869700926</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6506174018892805</v>
+        <v>0.8344995557652725</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4013,16 +4013,16 @@
         <v>11.48356342778669</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I94" t="n">
-        <v>21.81114993983779</v>
+        <v>21.54290463660477</v>
       </c>
       <c r="J94" t="n">
-        <v>0.01115619346139485</v>
+        <v>0.039650262468175</v>
       </c>
       <c r="K94" t="n">
-        <v>0.4500165223291137</v>
+        <v>0.8177382806238971</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -4045,22 +4045,22 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>0.07543157732456927</v>
+        <v>0.2138868098388857</v>
       </c>
       <c r="G95" t="n">
-        <v>11.60527330418356</v>
+        <v>12.07664955213162</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I95" t="n">
-        <v>28.8825999298514</v>
+        <v>28.87418744907121</v>
       </c>
       <c r="J95" t="n">
-        <v>0.04130077482271573</v>
+        <v>0.04235445329601931</v>
       </c>
       <c r="K95" t="n">
-        <v>0.8267554504821847</v>
+        <v>0.8554701861177549</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -4083,22 +4083,22 @@
         <v>640</v>
       </c>
       <c r="F96" t="n">
-        <v>0.8823550343346107</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>23.97696201559357</v>
+        <v>24.6460742997744</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I96" t="n">
-        <v>85.50003233637676</v>
+        <v>86.61891584467858</v>
       </c>
       <c r="J96" t="n">
-        <v>0.0370673771684086</v>
+        <v>0.03568468592417719</v>
       </c>
       <c r="K96" t="n">
-        <v>0.773847577069956</v>
+        <v>0.7624061058949176</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4121,22 +4121,22 @@
         <v>33</v>
       </c>
       <c r="F97" t="n">
-        <v>0.2467977957428397</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>5.032192377153212</v>
+        <v>4.685296148590822</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I97" t="n">
-        <v>114.261286048223</v>
+        <v>112.8911509417079</v>
       </c>
       <c r="J97" t="n">
-        <v>0.0871409368736942</v>
+        <v>0.06040624124670921</v>
       </c>
       <c r="K97" t="n">
-        <v>1.399653554803112</v>
+        <v>1.107348992131443</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -4159,22 +4159,22 @@
         <v>667</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>0.5951892006378902</v>
       </c>
       <c r="G98" t="n">
-        <v>7.554245495084205</v>
+        <v>8.903107096376671</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I98" t="n">
-        <v>28.27017442628089</v>
+        <v>28.09208303351382</v>
       </c>
       <c r="J98" t="n">
-        <v>0.02955218549538835</v>
+        <v>0.02411252330269363</v>
       </c>
       <c r="K98" t="n">
-        <v>0.6799247183703363</v>
+        <v>0.6009383049182218</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -4197,22 +4197,22 @@
         <v>246</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>0.6142193727680159</v>
       </c>
       <c r="G99" t="n">
-        <v>7.203826552603831</v>
+        <v>8.531245500604802</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I99" t="n">
-        <v>112.3371716389262</v>
+        <v>110.9410823223517</v>
       </c>
       <c r="J99" t="n">
-        <v>0.06016662922727597</v>
+        <v>0.05121296786759101</v>
       </c>
       <c r="K99" t="n">
-        <v>1.062535860960391</v>
+        <v>0.9790741238239402</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -4235,22 +4235,22 @@
         <v>478</v>
       </c>
       <c r="F100" t="n">
-        <v>0.07543157732456197</v>
+        <v>0.1280937719090819</v>
       </c>
       <c r="G100" t="n">
-        <v>22.19155325258548</v>
+        <v>22.53439176628481</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I100" t="n">
-        <v>120.1487238224961</v>
+        <v>118.7723069765904</v>
       </c>
       <c r="J100" t="n">
-        <v>0.02850576900076543</v>
+        <v>0.04556655777820207</v>
       </c>
       <c r="K100" t="n">
-        <v>0.6668468844518407</v>
+        <v>0.9002890729766873</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -4279,16 +4279,16 @@
         <v>14.47703643706128</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I101" t="n">
-        <v>15.79500210769504</v>
+        <v>16.05542771999552</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1510799650706089</v>
+        <v>0.1262474730449963</v>
       </c>
       <c r="K101" t="n">
-        <v>2.198746455159752</v>
+        <v>2.026039755457702</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4311,22 +4311,22 @@
         <v>130</v>
       </c>
       <c r="F102" t="n">
-        <v>0.6312434555399306</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>24.52702363699705</v>
+        <v>20.62180903800634</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I102" t="n">
-        <v>33.35705974101977</v>
+        <v>34.54734663011796</v>
       </c>
       <c r="J102" t="n">
-        <v>0.08375560123379357</v>
+        <v>0.08017584252750347</v>
       </c>
       <c r="K102" t="n">
-        <v>1.357344533983503</v>
+        <v>1.383196657724194</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4355,16 +4355,16 @@
         <v>10.02719427357424</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I103" t="n">
-        <v>31.3416252250965</v>
+        <v>32.40457206220999</v>
       </c>
       <c r="J103" t="n">
-        <v>0.0283235820892883</v>
+        <v>0.03824643686239805</v>
       </c>
       <c r="K103" t="n">
-        <v>0.6645699610827378</v>
+        <v>0.7981505301805385</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>155</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2268849255436165</v>
+        <v>0.213886809838868</v>
       </c>
       <c r="G104" t="n">
-        <v>12.70148392313247</v>
+        <v>12.6551116656892</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I104" t="n">
-        <v>71.83905967424685</v>
+        <v>72.99798165687919</v>
       </c>
       <c r="J104" t="n">
-        <v>0.01422955966229241</v>
+        <v>0.009478467725839015</v>
       </c>
       <c r="K104" t="n">
-        <v>0.4884266324072617</v>
+        <v>0.3967475368954216</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -4431,16 +4431,16 @@
         <v>6.688712506902953</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I105" t="n">
-        <v>19.58358541648231</v>
+        <v>20.99439779113741</v>
       </c>
       <c r="J105" t="n">
-        <v>0.02286123399355125</v>
+        <v>0.0318905254518025</v>
       </c>
       <c r="K105" t="n">
-        <v>0.5963029932280292</v>
+        <v>0.7094657205870155</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4463,22 +4463,22 @@
         <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>0.6689592442022074</v>
+        <v>0.2222970801906261</v>
       </c>
       <c r="G106" t="n">
-        <v>18.49124112075864</v>
+        <v>16.42758944756093</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I106" t="n">
-        <v>116.8383245040687</v>
+        <v>115.5312235343863</v>
       </c>
       <c r="J106" t="n">
-        <v>0.03075560019297903</v>
+        <v>0.04198541141829493</v>
       </c>
       <c r="K106" t="n">
-        <v>0.6949646739052868</v>
+        <v>0.8503208996435186</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -4507,16 +4507,16 @@
         <v>4.560359086738675</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I107" t="n">
-        <v>28.30789211632625</v>
+        <v>29.58947318993439</v>
       </c>
       <c r="J107" t="n">
-        <v>0.06756024431723888</v>
+        <v>0.03382618379878579</v>
       </c>
       <c r="K107" t="n">
-        <v>1.154939287990334</v>
+        <v>0.7364741983411511</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4545,16 +4545,16 @@
         <v>3.08676659305494</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I108" t="n">
-        <v>36.82151706568144</v>
+        <v>36.8520154738767</v>
       </c>
       <c r="J108" t="n">
-        <v>0.07802484997133013</v>
+        <v>0.05749417413112488</v>
       </c>
       <c r="K108" t="n">
-        <v>1.285723135024465</v>
+        <v>1.066716563359917</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -4577,22 +4577,22 @@
         <v>198</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>0.5951892006378899</v>
       </c>
       <c r="G109" t="n">
-        <v>19.52122242586258</v>
+        <v>23.00686865719966</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I109" t="n">
-        <v>123.1377831718758</v>
+        <v>121.7798212998546</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01826396447491734</v>
+        <v>0.01914708473393399</v>
       </c>
       <c r="K109" t="n">
-        <v>0.5388475464224798</v>
+        <v>0.5316549330190024</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>5.431724311855306</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I110" t="n">
-        <v>37.16874595536945</v>
+        <v>37.47354957790519</v>
       </c>
       <c r="J110" t="n">
-        <v>0.02502410914857784</v>
+        <v>0.03675098763622488</v>
       </c>
       <c r="K110" t="n">
-        <v>0.6233340293491398</v>
+        <v>0.7772843441511266</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>13.21653808680624</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I111" t="n">
-        <v>114.8878799244959</v>
+        <v>113.5320649587213</v>
       </c>
       <c r="J111" t="n">
-        <v>0.01960457304054154</v>
+        <v>0.03518496796026094</v>
       </c>
       <c r="K111" t="n">
-        <v>0.5556021142843557</v>
+        <v>0.7554334800010929</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -4691,22 +4691,22 @@
         <v>254</v>
       </c>
       <c r="F112" t="n">
-        <v>1.290987980249197e-05</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>5.144297521087992</v>
+        <v>5.144277597486356</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I112" t="n">
-        <v>84.96294058987614</v>
+        <v>86.096201787232</v>
       </c>
       <c r="J112" t="n">
-        <v>0.06427391363261695</v>
+        <v>0.1002151090352374</v>
       </c>
       <c r="K112" t="n">
-        <v>1.113867604663869</v>
+        <v>1.662806995223489</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>376</v>
       </c>
       <c r="F113" t="n">
-        <v>0.6336257962135482</v>
+        <v>0.3759053785186572</v>
       </c>
       <c r="G113" t="n">
-        <v>13.46557135098619</v>
+        <v>12.59075702602164</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I113" t="n">
-        <v>27.9360886974725</v>
+        <v>27.59206476803213</v>
       </c>
       <c r="J113" t="n">
-        <v>0.03476251882118998</v>
+        <v>0.0866989259574545</v>
       </c>
       <c r="K113" t="n">
-        <v>0.7450420729275109</v>
+        <v>1.47421403895822</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4767,22 +4767,22 @@
         <v>366</v>
       </c>
       <c r="F114" t="n">
-        <v>0.004472250040946481</v>
+        <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>14.20459041677348</v>
+        <v>14.18555800805876</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I114" t="n">
-        <v>36.07556935275215</v>
+        <v>37.43566240841635</v>
       </c>
       <c r="J114" t="n">
-        <v>0.03210949831980147</v>
+        <v>0.01323544886924865</v>
       </c>
       <c r="K114" t="n">
-        <v>0.7118853311542215</v>
+        <v>0.4491691544771745</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -4811,16 +4811,16 @@
         <v>20.08938572978278</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I115" t="n">
-        <v>49.759661154374</v>
+        <v>50.73406826350784</v>
       </c>
       <c r="J115" t="n">
-        <v>0.0335570604949422</v>
+        <v>0.04529719387308753</v>
       </c>
       <c r="K115" t="n">
-        <v>0.7299765766673272</v>
+        <v>0.8965306054504365</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -4843,22 +4843,22 @@
         <v>447</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3156217277700383</v>
+        <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>7.075937393899374</v>
+        <v>6.463893795538414</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I116" t="n">
-        <v>113.7599239359851</v>
+        <v>112.3684561107601</v>
       </c>
       <c r="J116" t="n">
-        <v>0.01976436379563859</v>
+        <v>0.02174038076035456</v>
       </c>
       <c r="K116" t="n">
-        <v>0.5575991364716094</v>
+        <v>0.5678395097799925</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>388</v>
       </c>
       <c r="F117" t="n">
-        <v>1</v>
+        <v>0.6592360865923985</v>
       </c>
       <c r="G117" t="n">
-        <v>23.56226241259528</v>
+        <v>21.70937731679848</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I117" t="n">
-        <v>28.01233718918579</v>
+        <v>29.41156471541793</v>
       </c>
       <c r="J117" t="n">
-        <v>0.04150741498182098</v>
+        <v>0.02727492951955807</v>
       </c>
       <c r="K117" t="n">
-        <v>0.8293379840102363</v>
+        <v>0.6450637458003056</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -4925,16 +4925,16 @@
         <v>8.030018742194814</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I118" t="n">
-        <v>20.64702568718556</v>
+        <v>22.01992062528602</v>
       </c>
       <c r="J118" t="n">
-        <v>0.04071063071710519</v>
+        <v>0.02223415526142057</v>
       </c>
       <c r="K118" t="n">
-        <v>0.8193799870402261</v>
+        <v>0.5747292058094519</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -4957,22 +4957,22 @@
         <v>165</v>
       </c>
       <c r="F119" t="n">
-        <v>0.6312434555399813</v>
+        <v>0.5980044885993355</v>
       </c>
       <c r="G119" t="n">
-        <v>15.93076916164583</v>
+        <v>15.79720577324354</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I119" t="n">
-        <v>20.38496747809766</v>
+        <v>21.7370229037786</v>
       </c>
       <c r="J119" t="n">
-        <v>0.02946873963826681</v>
+        <v>0.02962550899872316</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6788818343311132</v>
+        <v>0.6778616688797063</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -5001,16 +5001,16 @@
         <v>3.330100148644182</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I120" t="n">
-        <v>107.4812760562148</v>
+        <v>106.0852673306042</v>
       </c>
       <c r="J120" t="n">
-        <v>0.07055885507153563</v>
+        <v>0.06437305271057844</v>
       </c>
       <c r="K120" t="n">
-        <v>1.192415124459291</v>
+        <v>1.162698397848488</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5033,22 +5033,22 @@
         <v>57</v>
       </c>
       <c r="F121" t="n">
-        <v>0.1891691368813245</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>8.138970448081079</v>
+        <v>7.701882886671284</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I121" t="n">
-        <v>26.59223122164555</v>
+        <v>27.96918029625179</v>
       </c>
       <c r="J121" t="n">
-        <v>0.06125104359159268</v>
+        <v>0.04156004041195172</v>
       </c>
       <c r="K121" t="n">
-        <v>1.076088582107505</v>
+        <v>0.8443856459454786</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -5071,22 +5071,22 @@
         <v>137</v>
       </c>
       <c r="F122" t="n">
-        <v>0.000773829318245072</v>
+        <v>0</v>
       </c>
       <c r="G122" t="n">
-        <v>5.672068789363469</v>
+        <v>5.670752331040389</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I122" t="n">
-        <v>122.1576443448918</v>
+        <v>120.8229240654558</v>
       </c>
       <c r="J122" t="n">
-        <v>0.04406069310967198</v>
+        <v>0.03424136106151673</v>
       </c>
       <c r="K122" t="n">
-        <v>0.8612481722338992</v>
+        <v>0.7422672174873075</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>2.935153317971652</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I123" t="n">
-        <v>33.67265981416313</v>
+        <v>35.10148992551561</v>
       </c>
       <c r="J123" t="n">
-        <v>0.04382919116351536</v>
+        <v>0.02346594428305947</v>
       </c>
       <c r="K123" t="n">
-        <v>0.8583549227302818</v>
+        <v>0.5919165087446894</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -5153,16 +5153,16 @@
         <v>20.29361436511495</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I124" t="n">
-        <v>22.45476873880682</v>
+        <v>23.85636101303718</v>
       </c>
       <c r="J124" t="n">
-        <v>0.03655108665643</v>
+        <v>0.04521826786553125</v>
       </c>
       <c r="K124" t="n">
-        <v>0.7673951161196112</v>
+        <v>0.8954293412099631</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -5191,16 +5191,16 @@
         <v>12.02926119925908</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I125" t="n">
-        <v>58.88849202640949</v>
+        <v>60.30827120306865</v>
       </c>
       <c r="J125" t="n">
-        <v>0.04754116054361431</v>
+        <v>0.04530766383207459</v>
       </c>
       <c r="K125" t="n">
-        <v>0.9047461248117897</v>
+        <v>0.8966766940692413</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -5229,16 +5229,16 @@
         <v>20.00788726977439</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I126" t="n">
-        <v>64.53856166061541</v>
+        <v>65.96828651400513</v>
       </c>
       <c r="J126" t="n">
-        <v>0.1042154661721067</v>
+        <v>0.0820389482767252</v>
       </c>
       <c r="K126" t="n">
-        <v>1.613046462453706</v>
+        <v>1.409192800204544</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -5267,16 +5267,16 @@
         <v>11.24748896420885</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I127" t="n">
-        <v>18.24106175676632</v>
+        <v>18.46558051146141</v>
       </c>
       <c r="J127" t="n">
-        <v>0.1308686962521367</v>
+        <v>0.07682211868953247</v>
       </c>
       <c r="K127" t="n">
-        <v>1.946151414611108</v>
+        <v>1.336401738666024</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>11.07986791437515</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I128" t="n">
-        <v>177.114136893939</v>
+        <v>178.2453031415336</v>
       </c>
       <c r="J128" t="n">
-        <v>0.04708702744975365</v>
+        <v>0.04205146067695802</v>
       </c>
       <c r="K128" t="n">
-        <v>0.8990704906747893</v>
+        <v>0.8512424930311429</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -5343,16 +5343,16 @@
         <v>5.484544739538552</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I129" t="n">
-        <v>109.8301137596924</v>
+        <v>108.5056849424009</v>
       </c>
       <c r="J129" t="n">
-        <v>0.1683423269112377</v>
+        <v>0.2276647445315529</v>
       </c>
       <c r="K129" t="n">
-        <v>2.414486843764838</v>
+        <v>3.441127353482788</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -5375,22 +5375,22 @@
         <v>575</v>
       </c>
       <c r="F130" t="n">
-        <v>0.631243455539969</v>
+        <v>0.2138868098388678</v>
       </c>
       <c r="G130" t="n">
-        <v>9.125202078219003</v>
+        <v>8.164579057522632</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I130" t="n">
-        <v>62.24301249667668</v>
+        <v>63.66152611624592</v>
       </c>
       <c r="J130" t="n">
-        <v>0.0009098020923751557</v>
+        <v>0.06464646812175677</v>
       </c>
       <c r="K130" t="n">
-        <v>0.3219598591586484</v>
+        <v>1.166513396534572</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -5419,16 +5419,16 @@
         <v>3.533718721120853</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I131" t="n">
-        <v>112.2197855381751</v>
+        <v>110.8574129646511</v>
       </c>
       <c r="J131" t="n">
-        <v>0.02594674615074104</v>
+        <v>0.02334646227040829</v>
       </c>
       <c r="K131" t="n">
-        <v>0.6348649002245048</v>
+        <v>0.5902493616028717</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -5457,16 +5457,16 @@
         <v>6.408090589247315</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I132" t="n">
-        <v>49.8197164717041</v>
+        <v>51.24958801802928</v>
       </c>
       <c r="J132" t="n">
-        <v>0.0502133434292877</v>
+        <v>0.005854972367227541</v>
       </c>
       <c r="K132" t="n">
-        <v>0.9381423529468174</v>
+        <v>0.3461884628016935</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -5489,22 +5489,22 @@
         <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>0.001547658636490593</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>11.35373261668167</v>
+        <v>11.34846355239334</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I133" t="n">
-        <v>56.35946125940621</v>
+        <v>57.78455765085248</v>
       </c>
       <c r="J133" t="n">
-        <v>0.03309718421798928</v>
+        <v>0.0282193595453896</v>
       </c>
       <c r="K133" t="n">
-        <v>0.7242291657616786</v>
+        <v>0.6582414935070546</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -5533,16 +5533,16 @@
         <v>5.697522180737868</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I134" t="n">
-        <v>119.3633934402498</v>
+        <v>118.0150255933915</v>
       </c>
       <c r="J134" t="n">
-        <v>0.06807002443881705</v>
+        <v>0.07400236167211645</v>
       </c>
       <c r="K134" t="n">
-        <v>1.161310383819965</v>
+        <v>1.297057323988899</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -5565,22 +5565,22 @@
         <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>1</v>
+        <v>0.2141077163332778</v>
       </c>
       <c r="G135" t="n">
-        <v>19.15380494027231</v>
+        <v>15.68007551594518</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I135" t="n">
-        <v>111.4167069146978</v>
+        <v>110.0695285913</v>
       </c>
       <c r="J135" t="n">
-        <v>0.1347645521804704</v>
+        <v>0.07007192809279915</v>
       </c>
       <c r="K135" t="n">
-        <v>1.99484078166805</v>
+        <v>1.242215503346046</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>97</v>
       </c>
       <c r="F136" t="n">
-        <v>0.1891691368813415</v>
+        <v>0.7736268038321662</v>
       </c>
       <c r="G136" t="n">
-        <v>20.37351186851368</v>
+        <v>23.75390842322235</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I136" t="n">
-        <v>110.5877853747244</v>
+        <v>109.1948224615794</v>
       </c>
       <c r="J136" t="n">
-        <v>0.1102715753031118</v>
+        <v>0.04829186905689345</v>
       </c>
       <c r="K136" t="n">
-        <v>1.68873409717138</v>
+        <v>0.9383156747054202</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -5641,22 +5641,22 @@
         <v>496</v>
       </c>
       <c r="F137" t="n">
-        <v>2.581975960509618e-05</v>
+        <v>0.3570961128829266</v>
       </c>
       <c r="G137" t="n">
-        <v>13.50137352021813</v>
+        <v>14.94764413763975</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I137" t="n">
-        <v>33.55889291631487</v>
+        <v>34.83787690051925</v>
       </c>
       <c r="J137" t="n">
-        <v>0.05281953057414808</v>
+        <v>0.059076903799179</v>
       </c>
       <c r="K137" t="n">
-        <v>0.9707137839364295</v>
+        <v>1.088800584074146</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -5685,16 +5685,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I138" t="n">
-        <v>112.7717331017953</v>
+        <v>111.3823025980306</v>
       </c>
       <c r="J138" t="n">
-        <v>0.04267430051765795</v>
+        <v>0.05125944225578121</v>
       </c>
       <c r="K138" t="n">
-        <v>0.8439214078362052</v>
+        <v>0.9797225866487607</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -5717,22 +5717,22 @@
         <v>498</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6334731256205066</v>
+        <v>0.2701375862540557</v>
       </c>
       <c r="G139" t="n">
-        <v>9.024917144126892</v>
+        <v>8.198289182256612</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I139" t="n">
-        <v>69.87362953542686</v>
+        <v>71.29680198100472</v>
       </c>
       <c r="J139" t="n">
-        <v>0.06979810608123287</v>
+        <v>0.08055242908679464</v>
       </c>
       <c r="K139" t="n">
-        <v>1.182907486726164</v>
+        <v>1.388451216063465</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -5755,22 +5755,22 @@
         <v>631</v>
       </c>
       <c r="F140" t="n">
-        <v>0.005869271986388712</v>
+        <v>0.2975946003190054</v>
       </c>
       <c r="G140" t="n">
-        <v>5.231349897546282</v>
+        <v>5.688380346688007</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I140" t="n">
-        <v>21.614263051162</v>
+        <v>21.95632069995601</v>
       </c>
       <c r="J140" t="n">
-        <v>0.08155696938117458</v>
+        <v>0.06314189424032648</v>
       </c>
       <c r="K140" t="n">
-        <v>1.329866620204222</v>
+        <v>1.145519893073904</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>240</v>
       </c>
       <c r="F141" t="n">
-        <v>0.4105919013255929</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G141" t="n">
-        <v>22.24411049399104</v>
+        <v>21.92495879553007</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I141" t="n">
-        <v>20.40002956880289</v>
+        <v>21.58259830850937</v>
       </c>
       <c r="J141" t="n">
-        <v>0.03677649015282731</v>
+        <v>0.03243618204395738</v>
       </c>
       <c r="K141" t="n">
-        <v>0.7702121488266447</v>
+        <v>0.7170793337815033</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -5837,16 +5837,16 @@
         <v>13.28753103477091</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I142" t="n">
-        <v>17.72959932853104</v>
+        <v>18.29193779128371</v>
       </c>
       <c r="J142" t="n">
-        <v>0.04328992062183881</v>
+        <v>0.04739342070273656</v>
       </c>
       <c r="K142" t="n">
-        <v>0.8516152635052764</v>
+        <v>0.9257795148896634</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -5869,22 +5869,22 @@
         <v>480</v>
       </c>
       <c r="F143" t="n">
-        <v>0.01496827675093042</v>
+        <v>0.02739142753116069</v>
       </c>
       <c r="G143" t="n">
-        <v>5.777013401509032</v>
+        <v>5.798447763434555</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I143" t="n">
-        <v>168.9509513487269</v>
+        <v>169.6491284361976</v>
       </c>
       <c r="J143" t="n">
-        <v>0.06507134157311195</v>
+        <v>0.03742994058885556</v>
       </c>
       <c r="K143" t="n">
-        <v>1.123833646121883</v>
+        <v>0.7867578577728921</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -5907,22 +5907,22 @@
         <v>226</v>
       </c>
       <c r="F144" t="n">
-        <v>0.07543157732456288</v>
+        <v>0.7021326055573245</v>
       </c>
       <c r="G144" t="n">
-        <v>22.75008536600774</v>
+        <v>26.93268588700068</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I144" t="n">
-        <v>111.1817634008267</v>
+        <v>109.8137827669214</v>
       </c>
       <c r="J144" t="n">
-        <v>0.2246910541853423</v>
+        <v>0.1285403258150606</v>
       </c>
       <c r="K144" t="n">
-        <v>3.118718190074889</v>
+        <v>2.058032210701832</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>7.001992287913491</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I145" t="n">
-        <v>33.15993339716324</v>
+        <v>34.56320414530052</v>
       </c>
       <c r="J145" t="n">
-        <v>0.08472299945593015</v>
+        <v>0.07861296280032957</v>
       </c>
       <c r="K145" t="n">
-        <v>1.369434818633219</v>
+        <v>1.361389605663818</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -5989,16 +5989,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I146" t="n">
-        <v>89.0338057750707</v>
+        <v>90.21194356471943</v>
       </c>
       <c r="J146" t="n">
-        <v>0.01974938331484347</v>
+        <v>0.02231289156679477</v>
       </c>
       <c r="K146" t="n">
-        <v>0.5574119144229657</v>
+        <v>0.5758278231121676</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -6021,22 +6021,22 @@
         <v>143</v>
       </c>
       <c r="F147" t="n">
-        <v>0.1917059732767608</v>
+        <v>0.7736268038321321</v>
       </c>
       <c r="G147" t="n">
-        <v>22.46354348927283</v>
+        <v>26.17187203471116</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I147" t="n">
-        <v>77.24359729109156</v>
+        <v>78.47061759355985</v>
       </c>
       <c r="J147" t="n">
-        <v>0.07848356790227373</v>
+        <v>0.06886315513967547</v>
       </c>
       <c r="K147" t="n">
-        <v>1.29145606923101</v>
+        <v>1.225349346430947</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -6065,16 +6065,16 @@
         <v>18.04607081887911</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I148" t="n">
-        <v>21.73356234285896</v>
+        <v>21.45058488238239</v>
       </c>
       <c r="J148" t="n">
-        <v>0.07547355599849995</v>
+        <v>0.03790815691624677</v>
       </c>
       <c r="K148" t="n">
-        <v>1.253837744240411</v>
+        <v>0.7934304687014371</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -6097,22 +6097,22 @@
         <v>499</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>0.7661794915118011</v>
       </c>
       <c r="G149" t="n">
-        <v>18.28265254277946</v>
+        <v>22.48499057139357</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I149" t="n">
-        <v>122.184832405044</v>
+        <v>120.8069464208056</v>
       </c>
       <c r="J149" t="n">
-        <v>0.02787124995961653</v>
+        <v>0.02197426467552615</v>
       </c>
       <c r="K149" t="n">
-        <v>0.658916834915247</v>
+        <v>0.5711029206653931</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>578</v>
       </c>
       <c r="F150" t="n">
-        <v>0.6312434555399631</v>
+        <v>0.4760322035132072</v>
       </c>
       <c r="G150" t="n">
-        <v>18.7626447991206</v>
+        <v>18.02809638558554</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I150" t="n">
-        <v>147.7146489603284</v>
+        <v>149.1455179304894</v>
       </c>
       <c r="J150" t="n">
-        <v>0.03476525399641924</v>
+        <v>0.04324311038105409</v>
       </c>
       <c r="K150" t="n">
-        <v>0.7450762564171349</v>
+        <v>0.867869727157434</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -6173,22 +6173,22 @@
         <v>421</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6312434555399277</v>
+        <v>0.6026373126474847</v>
       </c>
       <c r="G151" t="n">
-        <v>25.61117653831286</v>
+        <v>25.42638077959412</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I151" t="n">
-        <v>26.90013679222753</v>
+        <v>27.17077545253045</v>
       </c>
       <c r="J151" t="n">
-        <v>0.2254956736287785</v>
+        <v>0.1625344628414699</v>
       </c>
       <c r="K151" t="n">
-        <v>3.128774109016269</v>
+        <v>2.532356564005043</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -6211,22 +6211,22 @@
         <v>108</v>
       </c>
       <c r="F152" t="n">
-        <v>0.6312434555399918</v>
+        <v>0.5951892006379031</v>
       </c>
       <c r="G152" t="n">
-        <v>20.02931713692481</v>
+        <v>19.84716853846755</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I152" t="n">
-        <v>26.1880586797866</v>
+        <v>27.61901184876957</v>
       </c>
       <c r="J152" t="n">
-        <v>0.04723279415833727</v>
+        <v>0.02701304932254462</v>
       </c>
       <c r="K152" t="n">
-        <v>0.9008922440736491</v>
+        <v>0.6414096993688629</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -6249,22 +6249,22 @@
         <v>79</v>
       </c>
       <c r="F153" t="n">
-        <v>0.07543157732456883</v>
+        <v>0.1259735770495792</v>
       </c>
       <c r="G153" t="n">
-        <v>14.58089875869763</v>
+        <v>14.79709078142948</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I153" t="n">
-        <v>36.26420390626544</v>
+        <v>36.58966232633272</v>
       </c>
       <c r="J153" t="n">
-        <v>0.03404700164942884</v>
+        <v>0.02413461412593173</v>
       </c>
       <c r="K153" t="n">
-        <v>0.7360997303839755</v>
+        <v>0.6012465408777993</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -6293,16 +6293,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I154" t="n">
-        <v>32.64935854815148</v>
+        <v>32.87968912169009</v>
       </c>
       <c r="J154" t="n">
-        <v>0.01386704588867773</v>
+        <v>0.06868951412633864</v>
       </c>
       <c r="K154" t="n">
-        <v>0.4838960320690013</v>
+        <v>1.222926512125904</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -6331,16 +6331,16 @@
         <v>17.03283675727564</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I155" t="n">
-        <v>67.89338313006266</v>
+        <v>69.32433762117935</v>
       </c>
       <c r="J155" t="n">
-        <v>0.03522715880383775</v>
+        <v>0.02570774773948593</v>
       </c>
       <c r="K155" t="n">
-        <v>0.7508490193548509</v>
+        <v>0.6231966666694602</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -6363,22 +6363,22 @@
         <v>369</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6312434555399365</v>
+        <v>0.7711337653765813</v>
       </c>
       <c r="G156" t="n">
-        <v>26.86199461461126</v>
+        <v>27.80982157057147</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I156" t="n">
-        <v>119.9858792593487</v>
+        <v>118.6317151155459</v>
       </c>
       <c r="J156" t="n">
-        <v>0.08292097369575829</v>
+        <v>0.06910029041081561</v>
       </c>
       <c r="K156" t="n">
-        <v>1.346913581889077</v>
+        <v>1.228658123883998</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -6401,22 +6401,22 @@
         <v>82</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>0.4045380052384032</v>
       </c>
       <c r="G157" t="n">
-        <v>10.3850939331332</v>
+        <v>11.64544348831014</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I157" t="n">
-        <v>118.1323694003545</v>
+        <v>116.7927005161663</v>
       </c>
       <c r="J157" t="n">
-        <v>0.08931725443417961</v>
+        <v>0.1021147885733841</v>
       </c>
       <c r="K157" t="n">
-        <v>1.426852590518036</v>
+        <v>1.689313456255718</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -6439,22 +6439,22 @@
         <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>0.03216622358243008</v>
+        <v>0.3217923731004134</v>
       </c>
       <c r="G158" t="n">
-        <v>18.37934094186289</v>
+        <v>19.96101928044163</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I158" t="n">
-        <v>108.2795297604204</v>
+        <v>106.8858169294864</v>
       </c>
       <c r="J158" t="n">
-        <v>0.1758700100198796</v>
+        <v>0.1585777953619021</v>
       </c>
       <c r="K158" t="n">
-        <v>2.508565817091189</v>
+        <v>2.477148698542129</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         <v>4.760796887076785</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I159" t="n">
-        <v>38.0529462745222</v>
+        <v>38.18343082909047</v>
       </c>
       <c r="J159" t="n">
-        <v>0.1554647142968545</v>
+        <v>0.1242915947134856</v>
       </c>
       <c r="K159" t="n">
-        <v>2.253545880101689</v>
+        <v>1.998749145785426</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>539</v>
       </c>
       <c r="F160" t="n">
-        <v>0.1917844120768706</v>
+        <v>0.3643233183981304</v>
       </c>
       <c r="G160" t="n">
-        <v>18.05365650342918</v>
+        <v>18.93730305743638</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I160" t="n">
-        <v>50.93379983479113</v>
+        <v>52.36474367311432</v>
       </c>
       <c r="J160" t="n">
-        <v>0.02636155748742742</v>
+        <v>0.03128772523621363</v>
       </c>
       <c r="K160" t="n">
-        <v>0.640049101540682</v>
+        <v>0.7010547754229097</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
@@ -6553,22 +6553,22 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0125123732910225</v>
+        <v>0.3208302147583296</v>
       </c>
       <c r="G161" t="n">
-        <v>20.28770971945494</v>
+        <v>22.1572110107528</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I161" t="n">
-        <v>38.45267583225674</v>
+        <v>39.86911187028896</v>
       </c>
       <c r="J161" t="n">
-        <v>0.09140913524596746</v>
+        <v>0.08975307605639128</v>
       </c>
       <c r="K161" t="n">
-        <v>1.452996358295423</v>
+        <v>1.516828968981115</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
@@ -6597,16 +6597,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I162" t="n">
-        <v>82.96215303648229</v>
+        <v>84.17126200775139</v>
       </c>
       <c r="J162" t="n">
-        <v>0.05561727708891365</v>
+        <v>0.03893779469059028</v>
       </c>
       <c r="K162" t="n">
-        <v>1.005679272777791</v>
+        <v>0.8077971305488205</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
@@ -6629,22 +6629,22 @@
         <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>0.4124359662912174</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G163" t="n">
-        <v>19.70688307390854</v>
+        <v>19.41457211951801</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I163" t="n">
-        <v>90.57512650932068</v>
+        <v>91.73580564939417</v>
       </c>
       <c r="J163" t="n">
-        <v>0.08984775292735193</v>
+        <v>0.0558499425420699</v>
       </c>
       <c r="K163" t="n">
-        <v>1.433482619023292</v>
+        <v>1.043774398816857</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
@@ -6667,22 +6667,22 @@
         <v>624</v>
       </c>
       <c r="F164" t="n">
-        <v>0.1891691368813188</v>
+        <v>0.001924316684246317</v>
       </c>
       <c r="G164" t="n">
-        <v>12.09951965786446</v>
+        <v>11.45634838915284</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I164" t="n">
-        <v>14.30109739303513</v>
+        <v>15.36728592076906</v>
       </c>
       <c r="J164" t="n">
-        <v>0.0966716815551097</v>
+        <v>0.1017287711275299</v>
       </c>
       <c r="K164" t="n">
-        <v>1.518766256775621</v>
+        <v>1.68392730760231</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -6711,16 +6711,16 @@
         <v>4.635186296148192</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I165" t="n">
-        <v>28.38957703245651</v>
+        <v>29.80696048120351</v>
       </c>
       <c r="J165" t="n">
-        <v>0.04619919308337005</v>
+        <v>0.04339517240541264</v>
       </c>
       <c r="K165" t="n">
-        <v>0.8879745738478269</v>
+        <v>0.8699914671889522</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
@@ -6749,16 +6749,16 @@
         <v>15.96371209963397</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I166" t="n">
-        <v>116.1959748294505</v>
+        <v>114.824765569008</v>
       </c>
       <c r="J166" t="n">
-        <v>0.1235406531765352</v>
+        <v>0.06724631472435257</v>
       </c>
       <c r="K166" t="n">
-        <v>1.854567489106538</v>
+        <v>1.202789374286434</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
@@ -6781,22 +6781,22 @@
         <v>623</v>
       </c>
       <c r="F167" t="n">
-        <v>0.000773829318245072</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>9.516348121094776</v>
+        <v>9.514139425087274</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I167" t="n">
-        <v>18.98272842273284</v>
+        <v>18.89273191491552</v>
       </c>
       <c r="J167" t="n">
-        <v>0.1037428329085284</v>
+        <v>0.06077057432420193</v>
       </c>
       <c r="K167" t="n">
-        <v>1.607139618135792</v>
+        <v>1.112432576139899</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -6819,22 +6819,22 @@
         <v>106</v>
       </c>
       <c r="F168" t="n">
-        <v>1.330559724956681e-05</v>
+        <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>19.03864466579753</v>
+        <v>19.03856866993945</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I168" t="n">
-        <v>31.97326599568843</v>
+        <v>33.04760170095802</v>
       </c>
       <c r="J168" t="n">
-        <v>0.05805496670809546</v>
+        <v>0.05795825191453557</v>
       </c>
       <c r="K168" t="n">
-        <v>1.036144866686446</v>
+        <v>1.073191897454371</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
@@ -6857,22 +6857,22 @@
         <v>211</v>
       </c>
       <c r="F169" t="n">
-        <v>0.0003856051149581994</v>
+        <v>0.2138868098388862</v>
       </c>
       <c r="G169" t="n">
-        <v>7.55511938179497</v>
+        <v>8.038971535989207</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I169" t="n">
-        <v>62.37623187108682</v>
+        <v>63.79507164034288</v>
       </c>
       <c r="J169" t="n">
-        <v>0.05574890483760114</v>
+        <v>0.03391606430482601</v>
       </c>
       <c r="K169" t="n">
-        <v>1.007324321231486</v>
+        <v>0.7377283120393154</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -6901,16 +6901,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I170" t="n">
-        <v>128.1177224039265</v>
+        <v>129.2534646138466</v>
       </c>
       <c r="J170" t="n">
-        <v>0.06012746675224112</v>
+        <v>0.06893006680978271</v>
       </c>
       <c r="K170" t="n">
-        <v>1.062046418805212</v>
+        <v>1.226282973150972</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
@@ -6939,16 +6939,16 @@
         <v>10.87983322482473</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I171" t="n">
-        <v>170.9653298060792</v>
+        <v>171.8882454960283</v>
       </c>
       <c r="J171" t="n">
-        <v>0.08952016557169432</v>
+        <v>0.05685485280137732</v>
       </c>
       <c r="K171" t="n">
-        <v>1.429388519730034</v>
+        <v>1.057796034621391</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>2.82842712474619</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I172" t="n">
-        <v>33.2817085402124</v>
+        <v>34.69300613334362</v>
       </c>
       <c r="J172" t="n">
-        <v>0.3041749153686934</v>
+        <v>0.2470540049634271</v>
       </c>
       <c r="K172" t="n">
-        <v>4.112086262059653</v>
+        <v>3.711668076673717</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>686</v>
       </c>
       <c r="F173" t="n">
-        <v>0.6316290606548958</v>
+        <v>0.3568752063884874</v>
       </c>
       <c r="G173" t="n">
-        <v>19.03359899458738</v>
+        <v>17.71465718261627</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I173" t="n">
-        <v>28.63741558226205</v>
+        <v>30.06398657653316</v>
       </c>
       <c r="J173" t="n">
-        <v>0.02494973775659836</v>
+        <v>0.02353984531373826</v>
       </c>
       <c r="K173" t="n">
-        <v>0.6224045555520497</v>
+        <v>0.592947658867957</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -7047,22 +7047,22 @@
         <v>591</v>
       </c>
       <c r="F174" t="n">
-        <v>0.03071038282010412</v>
+        <v>0.595189200637853</v>
       </c>
       <c r="G174" t="n">
-        <v>18.81117281016477</v>
+        <v>21.96764445132071</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I174" t="n">
-        <v>32.3084736348904</v>
+        <v>32.44400472476183</v>
       </c>
       <c r="J174" t="n">
-        <v>0.06015242066977085</v>
+        <v>0.03102647924353538</v>
       </c>
       <c r="K174" t="n">
-        <v>1.062358286202894</v>
+        <v>0.6974095781221546</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>105</v>
       </c>
       <c r="F175" t="n">
-        <v>0</v>
+        <v>0.2975946003189789</v>
       </c>
       <c r="G175" t="n">
-        <v>8.792540929674423</v>
+        <v>9.577524740800841</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I175" t="n">
-        <v>101.0229474917047</v>
+        <v>99.69118740114735</v>
       </c>
       <c r="J175" t="n">
-        <v>0.04153267975460911</v>
+        <v>0.0307675874401792</v>
       </c>
       <c r="K175" t="n">
-        <v>0.8296537363939283</v>
+        <v>0.6937972291130586</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -7123,22 +7123,22 @@
         <v>237</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>0.4613255728523793</v>
       </c>
       <c r="G176" t="n">
-        <v>6.802079020417213</v>
+        <v>7.74347092062155</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I176" t="n">
-        <v>30.77943517363615</v>
+        <v>31.54836343024143</v>
       </c>
       <c r="J176" t="n">
-        <v>0.133609084500859</v>
+        <v>0.08775208452231183</v>
       </c>
       <c r="K176" t="n">
-        <v>1.980400055160205</v>
+        <v>1.488908889273543</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -7161,22 +7161,22 @@
         <v>389</v>
       </c>
       <c r="F177" t="n">
-        <v>0.6334731256205226</v>
+        <v>0.7211627776874531</v>
       </c>
       <c r="G177" t="n">
-        <v>21.1952639055474</v>
+        <v>21.66380335575148</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I177" t="n">
-        <v>48.04991597291333</v>
+        <v>49.46802954117463</v>
       </c>
       <c r="J177" t="n">
-        <v>0.07325786484172693</v>
+        <v>0.06489053493473027</v>
       </c>
       <c r="K177" t="n">
-        <v>1.226146627833268</v>
+        <v>1.169918890638937</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I178" t="n">
-        <v>16.01317503579472</v>
+        <v>16.36853542214117</v>
       </c>
       <c r="J178" t="n">
-        <v>0.05160790838777836</v>
+        <v>0.03181047408823484</v>
       </c>
       <c r="K178" t="n">
-        <v>0.9555712533984169</v>
+        <v>0.7083487541164217</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -7237,22 +7237,22 @@
         <v>266</v>
       </c>
       <c r="F179" t="n">
-        <v>0.00222967008057149</v>
+        <v>0.002815287961406337</v>
       </c>
       <c r="G179" t="n">
-        <v>3.332327656044203</v>
+        <v>3.332912705901808</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I179" t="n">
-        <v>20.98827866477739</v>
+        <v>22.41821534977743</v>
       </c>
       <c r="J179" t="n">
-        <v>0.05714736503311457</v>
+        <v>0.06211832247304657</v>
       </c>
       <c r="K179" t="n">
-        <v>1.024801903315226</v>
+        <v>1.131237870965289</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
@@ -7275,22 +7275,22 @@
         <v>137</v>
       </c>
       <c r="F180" t="n">
-        <v>0.08100972335851891</v>
+        <v>0.01489622401923269</v>
       </c>
       <c r="G180" t="n">
-        <v>12.6398027038002</v>
+        <v>12.39505237443052</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I180" t="n">
-        <v>64.48137141519184</v>
+        <v>65.91198051634814</v>
       </c>
       <c r="J180" t="n">
-        <v>0.06200296499245927</v>
+        <v>0.05043180377384307</v>
       </c>
       <c r="K180" t="n">
-        <v>1.085485894985146</v>
+        <v>0.968174445644058</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -7313,22 +7313,22 @@
         <v>400</v>
       </c>
       <c r="F181" t="n">
-        <v>0.07543157732456288</v>
+        <v>0.197467775324399</v>
       </c>
       <c r="G181" t="n">
-        <v>14.61811073921889</v>
+        <v>15.14144945670485</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I181" t="n">
-        <v>31.38377618840136</v>
+        <v>32.79248051459653</v>
       </c>
       <c r="J181" t="n">
-        <v>0.0524058132626113</v>
+        <v>0.02498515995065889</v>
       </c>
       <c r="K181" t="n">
-        <v>0.9655432554544274</v>
+        <v>0.6131143108392794</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>455</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0002946042980451566</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>13.18225414275347</v>
+        <v>13.18108918109577</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I182" t="n">
-        <v>25.36443568900793</v>
+        <v>26.67330524017127</v>
       </c>
       <c r="J182" t="n">
-        <v>0.01788724438241677</v>
+        <v>0.07673483952672022</v>
       </c>
       <c r="K182" t="n">
-        <v>0.5341393993043879</v>
+        <v>1.335183921828208</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I183" t="n">
-        <v>108.4756476986584</v>
+        <v>107.0908447689045</v>
       </c>
       <c r="J183" t="n">
-        <v>0.05187780944263005</v>
+        <v>0.04839255197473234</v>
       </c>
       <c r="K183" t="n">
-        <v>0.9589444047085453</v>
+        <v>0.9397205157771471</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -7427,22 +7427,22 @@
         <v>547</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0003794847494315991</v>
+        <v>0.1069434049194244</v>
       </c>
       <c r="G184" t="n">
-        <v>10.22305742492512</v>
+        <v>10.54984294448571</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I184" t="n">
-        <v>20.50498496772092</v>
+        <v>21.93390490578757</v>
       </c>
       <c r="J184" t="n">
-        <v>0.1011520301329528</v>
+        <v>0.073503219610451</v>
       </c>
       <c r="K184" t="n">
-        <v>1.574760456885315</v>
+        <v>1.290092733729644</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -7465,22 +7465,22 @@
         <v>625</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G185" t="n">
-        <v>7.261843774138907</v>
+        <v>8.039315372836008</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I185" t="n">
-        <v>64.91022091244798</v>
+        <v>66.32876973711292</v>
       </c>
       <c r="J185" t="n">
-        <v>0.03038741316820152</v>
+        <v>0.01652186388401744</v>
       </c>
       <c r="K185" t="n">
-        <v>0.6903631707889579</v>
+        <v>0.4950249052895912</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
@@ -7503,22 +7503,22 @@
         <v>13</v>
       </c>
       <c r="F186" t="n">
-        <v>0.631243455539946</v>
+        <v>0.5951892006379289</v>
       </c>
       <c r="G186" t="n">
-        <v>14.10337663984631</v>
+        <v>13.97511913256855</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I186" t="n">
-        <v>22.79294747556716</v>
+        <v>22.83008308976832</v>
       </c>
       <c r="J186" t="n">
-        <v>0.1023182876490163</v>
+        <v>0.07119131539883053</v>
       </c>
       <c r="K186" t="n">
-        <v>1.58933603188786</v>
+        <v>1.25783445139043</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -7541,22 +7541,22 @@
         <v>331</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0004580117789578011</v>
+        <v>0.3208302147582923</v>
       </c>
       <c r="G187" t="n">
-        <v>20.70697638920036</v>
+        <v>22.69688486159929</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I187" t="n">
-        <v>107.262916169774</v>
+        <v>105.8705291305261</v>
       </c>
       <c r="J187" t="n">
-        <v>0.04776688128583111</v>
+        <v>0.0447686277673402</v>
       </c>
       <c r="K187" t="n">
-        <v>0.9075671223723591</v>
+        <v>0.8891554579039103</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -7579,22 +7579,22 @@
         <v>180</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>0.5951892006379226</v>
       </c>
       <c r="G188" t="n">
-        <v>4.072023452781184</v>
+        <v>4.799110767933096</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I188" t="n">
-        <v>109.5461704544331</v>
+        <v>108.2010514368915</v>
       </c>
       <c r="J188" t="n">
-        <v>0.125992286016634</v>
+        <v>0.1256277264496282</v>
       </c>
       <c r="K188" t="n">
-        <v>1.885207341666866</v>
+        <v>2.017392355383052</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -7617,22 +7617,22 @@
         <v>414</v>
       </c>
       <c r="F189" t="n">
-        <v>0.7993496381311703</v>
+        <v>0.4666504708804904</v>
       </c>
       <c r="G189" t="n">
-        <v>25.31245381672093</v>
+        <v>23.27468988369172</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I189" t="n">
-        <v>32.78211371308092</v>
+        <v>33.13290255498572</v>
       </c>
       <c r="J189" t="n">
-        <v>0.05775623245508746</v>
+        <v>0.06224079665568052</v>
       </c>
       <c r="K189" t="n">
-        <v>1.032411365765274</v>
+        <v>1.132946768220985</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -7655,22 +7655,22 @@
         <v>667</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2837537053219952</v>
+        <v>0.5951892006378887</v>
       </c>
       <c r="G190" t="n">
-        <v>19.02987227378776</v>
+        <v>20.66836690608407</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I190" t="n">
-        <v>25.84310341602255</v>
+        <v>25.45745337313942</v>
       </c>
       <c r="J190" t="n">
-        <v>0.06158166267091819</v>
+        <v>0.06011109066764364</v>
       </c>
       <c r="K190" t="n">
-        <v>1.080220571073584</v>
+        <v>1.103230719988409</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
@@ -7693,22 +7693,22 @@
         <v>294</v>
       </c>
       <c r="F191" t="n">
-        <v>0.00445934016114399</v>
+        <v>0.03494634924224297</v>
       </c>
       <c r="G191" t="n">
-        <v>14.60636363400281</v>
+        <v>14.7397764562814</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I191" t="n">
-        <v>105.9741236304569</v>
+        <v>104.6060825951789</v>
       </c>
       <c r="J191" t="n">
-        <v>0.04283316941684356</v>
+        <v>0.0427202265027613</v>
       </c>
       <c r="K191" t="n">
-        <v>0.8459069089144468</v>
+        <v>0.8605738644258334</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
@@ -7737,16 +7737,16 @@
         <v>16.38096837796838</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I192" t="n">
-        <v>105.7698370100968</v>
+        <v>104.3876536530662</v>
       </c>
       <c r="J192" t="n">
-        <v>0.03300980370442965</v>
+        <v>0.06306765017023516</v>
       </c>
       <c r="K192" t="n">
-        <v>0.7231371074369888</v>
+        <v>1.144483956479741</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -7769,22 +7769,22 @@
         <v>476</v>
       </c>
       <c r="F193" t="n">
-        <v>0.4102062962106391</v>
+        <v>0.5951892006379221</v>
       </c>
       <c r="G193" t="n">
-        <v>15.24305754947807</v>
+        <v>15.99627651785805</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I193" t="n">
-        <v>112.646858444203</v>
+        <v>111.3042436089622</v>
       </c>
       <c r="J193" t="n">
-        <v>0.04887199094332657</v>
+        <v>0.03491275956122911</v>
       </c>
       <c r="K193" t="n">
-        <v>0.9213784877672244</v>
+        <v>0.7516353229031743</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -7813,16 +7813,16 @@
         <v>16.15292911517908</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I194" t="n">
-        <v>35.83577489227513</v>
+        <v>37.25911266396184</v>
       </c>
       <c r="J194" t="n">
-        <v>0.1803835647868803</v>
+        <v>0.1149364972551594</v>
       </c>
       <c r="K194" t="n">
-        <v>2.564975019285713</v>
+        <v>1.868216326300649</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -7845,22 +7845,22 @@
         <v>628</v>
       </c>
       <c r="F195" t="n">
-        <v>0.3156217277700418</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>4.615837706361481</v>
+        <v>4.216584043986316</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I195" t="n">
-        <v>113.5978587531956</v>
+        <v>112.2396835746597</v>
       </c>
       <c r="J195" t="n">
-        <v>0.07181801387694549</v>
+        <v>0.04364022693902917</v>
       </c>
       <c r="K195" t="n">
-        <v>1.208151754968059</v>
+        <v>0.8734107430803031</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -7883,22 +7883,22 @@
         <v>420</v>
       </c>
       <c r="F196" t="n">
-        <v>0.6312434555399646</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>8.157909658464586</v>
+        <v>6.859</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I196" t="n">
-        <v>36.77503357662145</v>
+        <v>38.18604901577585</v>
       </c>
       <c r="J196" t="n">
-        <v>0.1597380647220451</v>
+        <v>0.2008303783503962</v>
       </c>
       <c r="K196" t="n">
-        <v>2.306953072575575</v>
+        <v>3.066704158821589</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -7927,16 +7927,16 @@
         <v>9.010146336214524</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I197" t="n">
-        <v>23.17107648052712</v>
+        <v>22.79581057132287</v>
       </c>
       <c r="J197" t="n">
-        <v>0.0318490317578702</v>
+        <v>0.04042731089430789</v>
       </c>
       <c r="K197" t="n">
-        <v>0.7086300896172595</v>
+        <v>0.8285805323899715</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -7959,22 +7959,22 @@
         <v>517</v>
       </c>
       <c r="F198" t="n">
-        <v>0.07543157732456288</v>
+        <v>0</v>
       </c>
       <c r="G198" t="n">
-        <v>9.502802634031552</v>
+        <v>9.292517850399857</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I198" t="n">
-        <v>65.56689610313644</v>
+        <v>66.99692213101615</v>
       </c>
       <c r="J198" t="n">
-        <v>0.03815870789660654</v>
+        <v>0.03345944576780337</v>
       </c>
       <c r="K198" t="n">
-        <v>0.7874867370859366</v>
+        <v>0.7313570577223942</v>
       </c>
       <c r="L198" t="b">
         <v>0</v>
@@ -7997,22 +7997,22 @@
         <v>509</v>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>0.1280937719090827</v>
       </c>
       <c r="G199" t="n">
-        <v>22.33108275476135</v>
+        <v>23.18922454102273</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I199" t="n">
-        <v>31.42082342327583</v>
+        <v>32.73427114087708</v>
       </c>
       <c r="J199" t="n">
-        <v>0.01811756418448567</v>
+        <v>0.03143600944600945</v>
       </c>
       <c r="K199" t="n">
-        <v>0.5370178746868725</v>
+        <v>0.7031238031455973</v>
       </c>
       <c r="L199" t="b">
         <v>0</v>
@@ -8035,22 +8035,22 @@
         <v>84</v>
       </c>
       <c r="F200" t="n">
-        <v>0.8760076994998224</v>
+        <v>0.3568752063885352</v>
       </c>
       <c r="G200" t="n">
-        <v>27.45627108452806</v>
+        <v>24.07012528439627</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I200" t="n">
-        <v>60.03537259399403</v>
+        <v>61.43524986452373</v>
       </c>
       <c r="J200" t="n">
-        <v>0.02929139449782417</v>
+        <v>0.02683394273711947</v>
       </c>
       <c r="K200" t="n">
-        <v>0.6766654221234703</v>
+        <v>0.6389106032677285</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8073,22 +8073,22 @@
         <v>526</v>
       </c>
       <c r="F201" t="n">
-        <v>0.1891691368813246</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>12.85748626653052</v>
+        <v>12.167</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I201" t="n">
-        <v>25.37214512884822</v>
+        <v>26.62056868824821</v>
       </c>
       <c r="J201" t="n">
-        <v>0.02668554625719914</v>
+        <v>0.02348755763740584</v>
       </c>
       <c r="K201" t="n">
-        <v>0.6440982266684918</v>
+        <v>0.5922180825223996</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -8111,22 +8111,22 @@
         <v>497</v>
       </c>
       <c r="F202" t="n">
-        <v>0.03771578866227802</v>
+        <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>5.439937360318841</v>
+        <v>5.379074548656115</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I202" t="n">
-        <v>67.40276975216564</v>
+        <v>68.8246855576138</v>
       </c>
       <c r="J202" t="n">
-        <v>0.05025362371035521</v>
+        <v>0.04484320250466523</v>
       </c>
       <c r="K202" t="n">
-        <v>0.9386457651432976</v>
+        <v>0.8901960083384446</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -8149,22 +8149,22 @@
         <v>407</v>
       </c>
       <c r="F203" t="n">
-        <v>0.03771578866228487</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
-        <v>8.642726270067751</v>
+        <v>8.546030189509043</v>
       </c>
       <c r="H203" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I203" t="n">
-        <v>113.8996716948806</v>
+        <v>112.56327134266</v>
       </c>
       <c r="J203" t="n">
-        <v>0.04574415590891035</v>
+        <v>0.06693094091371253</v>
       </c>
       <c r="K203" t="n">
-        <v>0.8822876407529219</v>
+        <v>1.198388924918816</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -8187,22 +8187,22 @@
         <v>632</v>
       </c>
       <c r="F204" t="n">
-        <v>0.9640631301414659</v>
+        <v>0.8967821537548112</v>
       </c>
       <c r="G204" t="n">
-        <v>27.81501065065835</v>
+        <v>27.37953277686025</v>
       </c>
       <c r="H204" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I204" t="n">
-        <v>29.21182499750316</v>
+        <v>30.00931073048559</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1028308476522743</v>
+        <v>0.1064598380015814</v>
       </c>
       <c r="K204" t="n">
-        <v>1.595741869936396</v>
+        <v>1.749940462568574</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>475</v>
       </c>
       <c r="F205" t="n">
-        <v>2.581975960520842e-05</v>
+        <v>0.2975946003189902</v>
       </c>
       <c r="G205" t="n">
-        <v>6.745368623819933</v>
+        <v>7.347527294286389</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I205" t="n">
-        <v>35.01482160969051</v>
+        <v>36.41952856072783</v>
       </c>
       <c r="J205" t="n">
-        <v>0.01882929628647361</v>
+        <v>0.0310365066839129</v>
       </c>
       <c r="K205" t="n">
-        <v>0.545912912439134</v>
+        <v>0.6975494922246558</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -8263,22 +8263,22 @@
         <v>575</v>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>0.7021326055572705</v>
       </c>
       <c r="G206" t="n">
-        <v>20.37549842335151</v>
+        <v>24.66738896260627</v>
       </c>
       <c r="H206" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I206" t="n">
-        <v>180.2126241682663</v>
+        <v>181.2901179123892</v>
       </c>
       <c r="J206" t="n">
-        <v>0.01202629068450122</v>
+        <v>0.01194338684723754</v>
       </c>
       <c r="K206" t="n">
-        <v>0.4608907650758604</v>
+        <v>0.4311408549930034</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>75</v>
       </c>
       <c r="F207" t="n">
-        <v>0.0001526705929857841</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>4.660432215197723</v>
+        <v>4.660218771688728</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I207" t="n">
-        <v>108.0577724873036</v>
+        <v>106.7456386579016</v>
       </c>
       <c r="J207" t="n">
-        <v>0.2213189858586616</v>
+        <v>0.2041365205869367</v>
       </c>
       <c r="K207" t="n">
-        <v>3.076574980593046</v>
+        <v>3.112835165973123</v>
       </c>
       <c r="L207" t="b">
         <v>0</v>
@@ -8339,22 +8339,22 @@
         <v>655</v>
       </c>
       <c r="F208" t="n">
-        <v>0.3918271344128271</v>
+        <v>0.4045380052383922</v>
       </c>
       <c r="G208" t="n">
-        <v>17.25256905725916</v>
+        <v>17.3114377096554</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I208" t="n">
-        <v>83.56662747849063</v>
+        <v>84.64680015456598</v>
       </c>
       <c r="J208" t="n">
-        <v>0.03203092159487781</v>
+        <v>0.05010414405541489</v>
       </c>
       <c r="K208" t="n">
-        <v>0.710903300228972</v>
+        <v>0.9636025695018214</v>
       </c>
       <c r="L208" t="b">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>383</v>
       </c>
       <c r="F209" t="n">
-        <v>0.6689592442022723</v>
+        <v>0.595276734759264</v>
       </c>
       <c r="G209" t="n">
-        <v>26.30708519620149</v>
+        <v>25.82276976552384</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I209" t="n">
-        <v>23.03037319598706</v>
+        <v>23.58098937592436</v>
       </c>
       <c r="J209" t="n">
-        <v>0.02687693996657087</v>
+        <v>0.02539824640223518</v>
       </c>
       <c r="K209" t="n">
-        <v>0.646490214139131</v>
+        <v>0.6188781566415723</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -8415,22 +8415,22 @@
         <v>360</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>0.8334130855072851</v>
       </c>
       <c r="G210" t="n">
-        <v>17.69312971184013</v>
+        <v>22.11683545946772</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I210" t="n">
-        <v>87.54694098545153</v>
+        <v>88.62410291821563</v>
       </c>
       <c r="J210" t="n">
-        <v>0.02414155433664077</v>
+        <v>0.02298926152426626</v>
       </c>
       <c r="K210" t="n">
-        <v>0.6123040949838169</v>
+        <v>0.5852652958864331</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8453,22 +8453,22 @@
         <v>360</v>
       </c>
       <c r="F211" t="n">
-        <v>0.07543157732456288</v>
+        <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>12.65461621051439</v>
+        <v>12.3745858516558</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I211" t="n">
-        <v>112.8606375326945</v>
+        <v>111.5333790947743</v>
       </c>
       <c r="J211" t="n">
-        <v>0.02553791053223156</v>
+        <v>0.02669758172322314</v>
       </c>
       <c r="K211" t="n">
-        <v>0.6297553818383683</v>
+        <v>0.6370079413562966</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -8491,22 +8491,22 @@
         <v>268</v>
       </c>
       <c r="F212" t="n">
-        <v>0.6312434555399117</v>
+        <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>11.77252108119131</v>
+        <v>9.898089765202174</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I212" t="n">
-        <v>71.60587000799686</v>
+        <v>72.72821762777428</v>
       </c>
       <c r="J212" t="n">
-        <v>0.1125463525988247</v>
+        <v>0.06481867921080828</v>
       </c>
       <c r="K212" t="n">
-        <v>1.717163656364843</v>
+        <v>1.168916278931102</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -8529,22 +8529,22 @@
         <v>696</v>
       </c>
       <c r="F213" t="n">
-        <v>0.6312434555399155</v>
+        <v>0.1793997615363759</v>
       </c>
       <c r="G213" t="n">
-        <v>19.39253340026383</v>
+        <v>17.18236207699566</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I213" t="n">
-        <v>190.9323183108731</v>
+        <v>191.5656158165872</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1231029863584751</v>
+        <v>0.1087000701567234</v>
       </c>
       <c r="K213" t="n">
-        <v>1.849097646087397</v>
+        <v>1.781198695934265</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -8573,16 +8573,16 @@
         <v>8.792540929674423</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I214" t="n">
-        <v>103.58190003143</v>
+        <v>102.2422512481748</v>
       </c>
       <c r="J214" t="n">
-        <v>0.5447755558329787</v>
+        <v>0.5438297996003815</v>
       </c>
       <c r="K214" t="n">
-        <v>7.119048817451578</v>
+        <v>7.852617051429585</v>
       </c>
       <c r="L214" t="b">
         <v>0</v>
@@ -8605,22 +8605,22 @@
         <v>572</v>
       </c>
       <c r="F215" t="n">
-        <v>0.005233169479388724</v>
+        <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>12.91889357550939</v>
+        <v>12.89864333951443</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I215" t="n">
-        <v>35.36648320141236</v>
+        <v>36.7320094797958</v>
       </c>
       <c r="J215" t="n">
-        <v>0.2132598519206622</v>
+        <v>0.175352800573726</v>
       </c>
       <c r="K215" t="n">
-        <v>2.975854076718105</v>
+        <v>2.711212398778878</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -8649,16 +8649,16 @@
         <v>6.352448897866083</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I216" t="n">
-        <v>23.27213168035812</v>
+        <v>23.66118060948362</v>
       </c>
       <c r="J216" t="n">
-        <v>0.02153681839389956</v>
+        <v>0.03921184188513715</v>
       </c>
       <c r="K216" t="n">
-        <v>0.5797508007307663</v>
+        <v>0.8116209445855476</v>
       </c>
       <c r="L216" t="b">
         <v>0</v>
@@ -8687,16 +8687,16 @@
         <v>11.92630068378288</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I217" t="n">
-        <v>62.2241552631687</v>
+        <v>63.62420013359195</v>
       </c>
       <c r="J217" t="n">
-        <v>0.02194297137316929</v>
+        <v>0.02637026903215837</v>
       </c>
       <c r="K217" t="n">
-        <v>0.5848267922080468</v>
+        <v>0.6324409073293225</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -8719,22 +8719,22 @@
         <v>631</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>0.2975946003190075</v>
       </c>
       <c r="G218" t="n">
-        <v>3.375</v>
+        <v>3.676314532822995</v>
       </c>
       <c r="H218" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I218" t="n">
-        <v>22.78679945649736</v>
+        <v>23.1322047890503</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1138403971162385</v>
+        <v>0.1102956944533754</v>
       </c>
       <c r="K218" t="n">
-        <v>1.733336279186481</v>
+        <v>1.803462636979051</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -8763,16 +8763,16 @@
         <v>7.378342564560147</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I219" t="n">
-        <v>124.506548463585</v>
+        <v>123.1326316327044</v>
       </c>
       <c r="J219" t="n">
-        <v>0.03227679672788973</v>
+        <v>0.02717202169629166</v>
       </c>
       <c r="K219" t="n">
-        <v>0.7139761819837427</v>
+        <v>0.6436278603509188</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>9.32407137467319</v>
       </c>
       <c r="H220" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I220" t="n">
-        <v>27.850965833472</v>
+        <v>28.16170469023544</v>
       </c>
       <c r="J220" t="n">
-        <v>0.1055362962802856</v>
+        <v>0.08386089611856004</v>
       </c>
       <c r="K220" t="n">
-        <v>1.629553844435998</v>
+        <v>1.434614661367224</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -8833,22 +8833,22 @@
         <v>605</v>
       </c>
       <c r="F221" t="n">
-        <v>0.6312434555399326</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G221" t="n">
-        <v>25.76022291948397</v>
+        <v>23.97748856054686</v>
       </c>
       <c r="H221" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I221" t="n">
-        <v>9.405356952988271</v>
+        <v>10.54560760806768</v>
       </c>
       <c r="J221" t="n">
-        <v>0.05060439055764315</v>
+        <v>0.04880300256150973</v>
       </c>
       <c r="K221" t="n">
-        <v>0.9430295555331835</v>
+        <v>0.9454475830353881</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -8871,22 +8871,22 @@
         <v>486</v>
       </c>
       <c r="F222" t="n">
-        <v>0.0003856051149581994</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>11.34977636007115</v>
+        <v>11.34846355239334</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I222" t="n">
-        <v>21.01910019300469</v>
+        <v>21.45770517375902</v>
       </c>
       <c r="J222" t="n">
-        <v>0.1337905187388285</v>
+        <v>0.129675242829506</v>
       </c>
       <c r="K222" t="n">
-        <v>1.9826675718168</v>
+        <v>2.073867846667864</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -8909,22 +8909,22 @@
         <v>620</v>
       </c>
       <c r="F223" t="n">
-        <v>0.005869271986387589</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>2.876014554029513</v>
+        <v>2.870959421517483</v>
       </c>
       <c r="H223" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I223" t="n">
-        <v>63.74026434718448</v>
+        <v>65.16710788664736</v>
       </c>
       <c r="J223" t="n">
-        <v>0.05209643239989119</v>
+        <v>0.03771236793398703</v>
       </c>
       <c r="K223" t="n">
-        <v>0.9616766960481057</v>
+        <v>0.7906986010760845</v>
       </c>
       <c r="L223" t="b">
         <v>0</v>
@@ -8953,16 +8953,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H224" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I224" t="n">
-        <v>58.1785347482576</v>
+        <v>59.59246457978199</v>
       </c>
       <c r="J224" t="n">
-        <v>0.0962910284769382</v>
+        <v>0.06256883412528132</v>
       </c>
       <c r="K224" t="n">
-        <v>1.514008956252864</v>
+        <v>1.137523915171553</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -8985,22 +8985,22 @@
         <v>414</v>
       </c>
       <c r="F225" t="n">
-        <v>0</v>
+        <v>0.7021326055572941</v>
       </c>
       <c r="G225" t="n">
-        <v>11.75535677893274</v>
+        <v>14.23150256426704</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I225" t="n">
-        <v>19.34229465780666</v>
+        <v>19.29685327936522</v>
       </c>
       <c r="J225" t="n">
-        <v>0.0469431418072388</v>
+        <v>0.04650138621225038</v>
       </c>
       <c r="K225" t="n">
-        <v>0.8972722463373437</v>
+        <v>0.9133328484984764</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -9023,22 +9023,22 @@
         <v>209</v>
       </c>
       <c r="F226" t="n">
-        <v>0.0001526705929860085</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>5.617596152480419</v>
+        <v>5.617338871743453</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I226" t="n">
-        <v>31.41544522447941</v>
+        <v>32.75219164270666</v>
       </c>
       <c r="J226" t="n">
-        <v>0.06567374467155952</v>
+        <v>0.08172966261775096</v>
       </c>
       <c r="K226" t="n">
-        <v>1.131362319182722</v>
+        <v>1.404877299562038</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -9061,22 +9061,22 @@
         <v>258</v>
       </c>
       <c r="F227" t="n">
-        <v>0.6315487967258989</v>
+        <v>0.5951892006378695</v>
       </c>
       <c r="G227" t="n">
-        <v>21.8877289940006</v>
+        <v>21.6870095376837</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I227" t="n">
-        <v>197.284488081846</v>
+        <v>198.5540470285124</v>
       </c>
       <c r="J227" t="n">
-        <v>0.03278257744544419</v>
+        <v>0.05244496390246932</v>
       </c>
       <c r="K227" t="n">
-        <v>0.7202972943298724</v>
+        <v>0.9962643152402363</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -9099,22 +9099,22 @@
         <v>590</v>
       </c>
       <c r="F228" t="n">
-        <v>0.6312434555399485</v>
+        <v>0.5951892006378894</v>
       </c>
       <c r="G228" t="n">
-        <v>26.15908649406219</v>
+        <v>25.92119316453736</v>
       </c>
       <c r="H228" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I228" t="n">
-        <v>35.45671280172216</v>
+        <v>35.42476242100042</v>
       </c>
       <c r="J228" t="n">
-        <v>0.2041640149065889</v>
+        <v>0.2757651752042349</v>
       </c>
       <c r="K228" t="n">
-        <v>2.862176734635859</v>
+        <v>4.112278548016752</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -9143,16 +9143,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H229" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I229" t="n">
-        <v>102.8324443812095</v>
+        <v>101.4719820777812</v>
       </c>
       <c r="J229" t="n">
-        <v>0.03001483335798935</v>
+        <v>0.04327850465781699</v>
       </c>
       <c r="K229" t="n">
-        <v>0.6857067678133003</v>
+        <v>0.8683635878317955</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -9175,22 +9175,22 @@
         <v>276</v>
       </c>
       <c r="F230" t="n">
-        <v>0.6316290606548846</v>
+        <v>0.5951892006378686</v>
       </c>
       <c r="G230" t="n">
-        <v>19.16864195331167</v>
+        <v>18.99247316276928</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I230" t="n">
-        <v>31.33756433923772</v>
+        <v>31.29618219787185</v>
       </c>
       <c r="J230" t="n">
-        <v>0.167779967621922</v>
+        <v>0.1216474875526688</v>
       </c>
       <c r="K230" t="n">
-        <v>2.407458627537374</v>
+        <v>1.961855595049177</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -9213,22 +9213,22 @@
         <v>583</v>
       </c>
       <c r="F231" t="n">
-        <v>0.3156217277700418</v>
+        <v>0.0009621583421231584</v>
       </c>
       <c r="G231" t="n">
-        <v>11.47606606370182</v>
+        <v>10.48645288791257</v>
       </c>
       <c r="H231" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I231" t="n">
-        <v>73.80629880294171</v>
+        <v>75.235418617203</v>
       </c>
       <c r="J231" t="n">
-        <v>0.03984152784135851</v>
+        <v>0.05101741931453972</v>
       </c>
       <c r="K231" t="n">
-        <v>0.8085181713812539</v>
+        <v>0.976345610936751</v>
       </c>
       <c r="L231" t="b">
         <v>0</v>
@@ -9251,22 +9251,22 @@
         <v>391</v>
       </c>
       <c r="F232" t="n">
-        <v>0.07544448720436538</v>
+        <v>0.5951892006378768</v>
       </c>
       <c r="G232" t="n">
-        <v>14.54377348842496</v>
+        <v>16.76129829700606</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I232" t="n">
-        <v>121.411157719852</v>
+        <v>122.7916546889391</v>
       </c>
       <c r="J232" t="n">
-        <v>0.083445134370388</v>
+        <v>0.04711683253628815</v>
       </c>
       <c r="K232" t="n">
-        <v>1.353464402030616</v>
+        <v>0.921920246361092</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -9289,22 +9289,22 @@
         <v>306</v>
       </c>
       <c r="F233" t="n">
-        <v>0.09235724689858751</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>8.46953628263995</v>
+        <v>8.241196029703456</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I233" t="n">
-        <v>30.02756415553403</v>
+        <v>31.33945178415587</v>
       </c>
       <c r="J233" t="n">
-        <v>0.08193155662613687</v>
+        <v>0.03291091723652307</v>
       </c>
       <c r="K233" t="n">
-        <v>1.334548111563329</v>
+        <v>0.7237033720098914</v>
       </c>
       <c r="L233" t="b">
         <v>0</v>
@@ -9327,22 +9327,22 @@
         <v>458</v>
       </c>
       <c r="F234" t="n">
-        <v>0.6312434555399332</v>
+        <v>0.01489622401923269</v>
       </c>
       <c r="G234" t="n">
-        <v>15.93076916164564</v>
+        <v>13.45411503393831</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I234" t="n">
-        <v>32.61433272656713</v>
+        <v>34.03414409076662</v>
       </c>
       <c r="J234" t="n">
-        <v>0.02250987359924241</v>
+        <v>0.02071798449934107</v>
       </c>
       <c r="K234" t="n">
-        <v>0.5919117848459747</v>
+        <v>0.5535738896541426</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -9365,22 +9365,22 @@
         <v>581</v>
       </c>
       <c r="F235" t="n">
-        <v>0.6689592442021973</v>
+        <v>0.8927838009568149</v>
       </c>
       <c r="G235" t="n">
-        <v>26.05550432331384</v>
+        <v>27.51263460382292</v>
       </c>
       <c r="H235" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I235" t="n">
-        <v>76.48390928331555</v>
+        <v>77.74258841302183</v>
       </c>
       <c r="J235" t="n">
-        <v>0.07100466044849593</v>
+        <v>0.05192785208938826</v>
       </c>
       <c r="K235" t="n">
-        <v>1.197986681014274</v>
+        <v>0.9890489908407796</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -9403,22 +9403,22 @@
         <v>162</v>
       </c>
       <c r="F236" t="n">
-        <v>0.6312434555400217</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>20.71915304063649</v>
+        <v>17.42023099732033</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I236" t="n">
-        <v>67.97717340195084</v>
+        <v>69.40718392562836</v>
       </c>
       <c r="J236" t="n">
-        <v>0.0695497344319627</v>
+        <v>0.06510344638555284</v>
       </c>
       <c r="K236" t="n">
-        <v>1.179803404177859</v>
+        <v>1.172889670163177</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9441,22 +9441,22 @@
         <v>226</v>
       </c>
       <c r="F237" t="n">
-        <v>0.03771578866228487</v>
+        <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>12.93800531473315</v>
+        <v>12.79325302649799</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I237" t="n">
-        <v>39.14451926509778</v>
+        <v>39.28893102475666</v>
       </c>
       <c r="J237" t="n">
-        <v>0.01473187885041933</v>
+        <v>0.0543571848261528</v>
       </c>
       <c r="K237" t="n">
-        <v>0.4947044834829604</v>
+        <v>1.022945767759369</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -9485,16 +9485,16 @@
         <v>7.554245495084205</v>
       </c>
       <c r="H238" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I238" t="n">
-        <v>166.6885267686902</v>
+        <v>168.1006583785138</v>
       </c>
       <c r="J238" t="n">
-        <v>0.02711035782319661</v>
+        <v>0.03413531561391447</v>
       </c>
       <c r="K238" t="n">
-        <v>0.6494074081801736</v>
+        <v>0.7407875523816565</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -9523,16 +9523,16 @@
         <v>10.91308792230687</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I239" t="n">
-        <v>89.87065212241453</v>
+        <v>91.13388517800792</v>
       </c>
       <c r="J239" t="n">
-        <v>0.1244919012509154</v>
+        <v>0.1919963081534496</v>
       </c>
       <c r="K239" t="n">
-        <v>1.866455933522272</v>
+        <v>2.943441296465454</v>
       </c>
       <c r="L239" t="b">
         <v>0</v>
@@ -9561,16 +9561,16 @@
         <v>5.222154823442138</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I240" t="n">
-        <v>29.68794091335738</v>
+        <v>30.90318264775372</v>
       </c>
       <c r="J240" t="n">
-        <v>0.07562257013078373</v>
+        <v>0.05585307743273919</v>
       </c>
       <c r="K240" t="n">
-        <v>1.255700083073495</v>
+        <v>1.043818140329937</v>
       </c>
       <c r="L240" t="b">
         <v>0</v>
@@ -9593,22 +9593,22 @@
         <v>283</v>
       </c>
       <c r="F241" t="n">
-        <v>0.07543157732456592</v>
+        <v>0.0009621583421231584</v>
       </c>
       <c r="G241" t="n">
-        <v>10.6201031379452</v>
+        <v>10.38809156456165</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I241" t="n">
-        <v>29.33018682506201</v>
+        <v>29.09565202367103</v>
       </c>
       <c r="J241" t="n">
-        <v>0.05954180912537812</v>
+        <v>0.06640835207869075</v>
       </c>
       <c r="K241" t="n">
-        <v>1.054727026176587</v>
+        <v>1.191097178962076</v>
       </c>
       <c r="L241" t="b">
         <v>0</v>
@@ -9631,22 +9631,22 @@
         <v>616</v>
       </c>
       <c r="F242" t="n">
-        <v>0.01163730388596001</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>7.228976488224151</v>
+        <v>7.203826552603831</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I242" t="n">
-        <v>29.83315909944809</v>
+        <v>29.5905633922513</v>
       </c>
       <c r="J242" t="n">
-        <v>0.03770657463115364</v>
+        <v>0.03405388914306758</v>
       </c>
       <c r="K242" t="n">
-        <v>0.7818360962703493</v>
+        <v>0.7396513988709436</v>
       </c>
       <c r="L242" t="b">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>384</v>
       </c>
       <c r="F243" t="n">
-        <v>0.07543157732456288</v>
+        <v>0.1283146784034923</v>
       </c>
       <c r="G243" t="n">
-        <v>17.10349747464782</v>
+        <v>17.36883873738115</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I243" t="n">
-        <v>81.63506546186058</v>
+        <v>82.87840375755239</v>
       </c>
       <c r="J243" t="n">
-        <v>0.02929311701672032</v>
+        <v>0.03750467642591655</v>
       </c>
       <c r="K243" t="n">
-        <v>0.676686949704659</v>
+        <v>0.7878006560517539</v>
       </c>
       <c r="L243" t="b">
         <v>0</v>
@@ -9707,22 +9707,22 @@
         <v>10</v>
       </c>
       <c r="F244" t="n">
-        <v>0.6312434555400103</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G244" t="n">
-        <v>20.48834316314989</v>
+        <v>19.07044886041755</v>
       </c>
       <c r="H244" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I244" t="n">
-        <v>111.0542086038588</v>
+        <v>109.7025190475378</v>
       </c>
       <c r="J244" t="n">
-        <v>0.1419834696856976</v>
+        <v>0.1249579991317163</v>
       </c>
       <c r="K244" t="n">
-        <v>2.085060884934582</v>
+        <v>2.008047568171325</v>
       </c>
       <c r="L244" t="b">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         <v>11.2138976720853</v>
       </c>
       <c r="H245" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I245" t="n">
-        <v>36.09828453310744</v>
+        <v>37.50710237297542</v>
       </c>
       <c r="J245" t="n">
-        <v>0.1361817063538488</v>
+        <v>0.1069651103411932</v>
       </c>
       <c r="K245" t="n">
-        <v>2.012551996095173</v>
+        <v>1.756990589346088</v>
       </c>
       <c r="L245" t="b">
         <v>0</v>
@@ -9783,22 +9783,22 @@
         <v>338</v>
       </c>
       <c r="F246" t="n">
-        <v>0.6312563654197155</v>
+        <v>0.2138868098388667</v>
       </c>
       <c r="G246" t="n">
-        <v>25.31403247806064</v>
+        <v>22.64911446935715</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I246" t="n">
-        <v>108.506421855006</v>
+        <v>107.1809151148391</v>
       </c>
       <c r="J246" t="n">
-        <v>0.0440068059878537</v>
+        <v>0.0562390143281821</v>
       </c>
       <c r="K246" t="n">
-        <v>0.8605747053752377</v>
+        <v>1.0492031650536</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -9827,16 +9827,16 @@
         <v>6.547900426854397</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I247" t="n">
-        <v>79.66238221620721</v>
+        <v>80.89865680021674</v>
       </c>
       <c r="J247" t="n">
-        <v>0.1307113727872923</v>
+        <v>0.1541675173141192</v>
       </c>
       <c r="K247" t="n">
-        <v>1.944185227958575</v>
+        <v>2.415611549319109</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -9859,22 +9859,22 @@
         <v>94</v>
       </c>
       <c r="F248" t="n">
-        <v>0.6312434555399736</v>
+        <v>0.213886809838868</v>
       </c>
       <c r="G248" t="n">
-        <v>18.18398887328586</v>
+        <v>16.26973446335233</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I248" t="n">
-        <v>110.042590562249</v>
+        <v>108.6581416320909</v>
       </c>
       <c r="J248" t="n">
-        <v>0.1112421833150802</v>
+        <v>0.08618028872765238</v>
       </c>
       <c r="K248" t="n">
-        <v>1.700864496917285</v>
+        <v>1.466977430232611</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -9903,16 +9903,16 @@
         <v>9.609651814712121</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I249" t="n">
-        <v>19.73502163275336</v>
+        <v>19.70704228825455</v>
       </c>
       <c r="J249" t="n">
-        <v>0.2293972715648486</v>
+        <v>0.1848023313770253</v>
       </c>
       <c r="K249" t="n">
-        <v>3.177535238152576</v>
+        <v>2.843062858280516</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>387</v>
       </c>
       <c r="F250" t="n">
-        <v>0.01251237329102261</v>
+        <v>0.6592360865924102</v>
       </c>
       <c r="G250" t="n">
-        <v>22.28783075812694</v>
+        <v>26.59588018216066</v>
       </c>
       <c r="H250" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I250" t="n">
-        <v>15.83315784229396</v>
+        <v>15.72586358695627</v>
       </c>
       <c r="J250" t="n">
-        <v>0.02997857390008206</v>
+        <v>0.03034082125402233</v>
       </c>
       <c r="K250" t="n">
-        <v>0.6852536067909704</v>
+        <v>0.6878425083003704</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -9979,16 +9979,16 @@
         <v>10.94637643240904</v>
       </c>
       <c r="H251" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I251" t="n">
-        <v>31.98992578272659</v>
+        <v>32.12273484698847</v>
       </c>
       <c r="J251" t="n">
-        <v>0.0594042038673525</v>
+        <v>0.07012747956567604</v>
       </c>
       <c r="K251" t="n">
-        <v>1.053007272407396</v>
+        <v>1.242990619844132</v>
       </c>
       <c r="L251" t="b">
         <v>0</v>
@@ -10011,22 +10011,22 @@
         <v>466</v>
       </c>
       <c r="F252" t="n">
-        <v>0.07543157732456961</v>
+        <v>0.2138868098388869</v>
       </c>
       <c r="G252" t="n">
-        <v>14.24741750326592</v>
+        <v>14.82611082910238</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I252" t="n">
-        <v>26.20515053567233</v>
+        <v>25.98981150047861</v>
       </c>
       <c r="J252" t="n">
-        <v>0.01571867693238567</v>
+        <v>0.01983519917212461</v>
       </c>
       <c r="K252" t="n">
-        <v>0.5070372224003609</v>
+        <v>0.5412562779697451</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -10055,16 +10055,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I253" t="n">
-        <v>36.02511600539317</v>
+        <v>37.42203608768811</v>
       </c>
       <c r="J253" t="n">
-        <v>0.04698404768848962</v>
+        <v>0.04469525637236679</v>
       </c>
       <c r="K253" t="n">
-        <v>0.8977834771178569</v>
+        <v>0.8881316978524436</v>
       </c>
       <c r="L253" t="b">
         <v>0</v>
@@ -10093,16 +10093,16 @@
         <v>4.964088133786507</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I254" t="n">
-        <v>38.18345393616875</v>
+        <v>36.75496687846424</v>
       </c>
       <c r="J254" t="n">
-        <v>0.04516962250182115</v>
+        <v>0.06225462350267034</v>
       </c>
       <c r="K254" t="n">
-        <v>0.8751072756524583</v>
+        <v>1.133139695908826</v>
       </c>
       <c r="L254" t="b">
         <v>0</v>
@@ -10131,16 +10131,16 @@
         <v>6.022017186956544</v>
       </c>
       <c r="H255" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I255" t="n">
-        <v>105.0611853762308</v>
+        <v>103.6859494942262</v>
       </c>
       <c r="J255" t="n">
-        <v>0.02330084186883719</v>
+        <v>0.04094310252005835</v>
       </c>
       <c r="K255" t="n">
-        <v>0.601797095062045</v>
+        <v>0.835777436054072</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -10163,22 +10163,22 @@
         <v>98</v>
       </c>
       <c r="F256" t="n">
-        <v>0.3156217277700418</v>
+        <v>0.1280937719090827</v>
       </c>
       <c r="G256" t="n">
-        <v>4.856634445842174</v>
+        <v>4.607041147283625</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I256" t="n">
-        <v>114.7405105044512</v>
+        <v>113.3566710358595</v>
       </c>
       <c r="J256" t="n">
-        <v>0.05984199216884175</v>
+        <v>0.03102087414622694</v>
       </c>
       <c r="K256" t="n">
-        <v>1.058478633693994</v>
+        <v>0.6973313695135948</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -10207,16 +10207,16 @@
         <v>7.970018757819834</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I257" t="n">
-        <v>52.39344246626491</v>
+        <v>53.82295764512868</v>
       </c>
       <c r="J257" t="n">
-        <v>0.02718963449301625</v>
+        <v>0.04599134765031042</v>
       </c>
       <c r="K257" t="n">
-        <v>0.6503981868298223</v>
+        <v>0.9062162180376434</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -10239,22 +10239,22 @@
         <v>609</v>
       </c>
       <c r="F258" t="n">
-        <v>0.6320172848582126</v>
+        <v>0.1280937719090599</v>
       </c>
       <c r="G258" t="n">
-        <v>24.38515807087288</v>
+        <v>21.28625063441045</v>
       </c>
       <c r="H258" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I258" t="n">
-        <v>119.1543274422245</v>
+        <v>117.8226273556703</v>
       </c>
       <c r="J258" t="n">
-        <v>0.06947011682472622</v>
+        <v>0.06531691350390043</v>
       </c>
       <c r="K258" t="n">
-        <v>1.178808364583417</v>
+        <v>1.175868202984383</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>8.150467777986734</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I259" t="n">
-        <v>36.92159136459008</v>
+        <v>38.21399982058071</v>
       </c>
       <c r="J259" t="n">
-        <v>0.09473708020792547</v>
+        <v>0.05627874788898988</v>
       </c>
       <c r="K259" t="n">
-        <v>1.494588125747507</v>
+        <v>1.049757572289175</v>
       </c>
       <c r="L259" t="b">
         <v>0</v>
@@ -10321,16 +10321,16 @@
         <v>5.170193323271385</v>
       </c>
       <c r="H260" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I260" t="n">
-        <v>105.7519122109659</v>
+        <v>104.4289152865013</v>
       </c>
       <c r="J260" t="n">
-        <v>0.03330837618976785</v>
+        <v>0.06248807626433864</v>
       </c>
       <c r="K260" t="n">
-        <v>0.7268685866290218</v>
+        <v>1.136397090856642</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -10353,22 +10353,22 @@
         <v>456</v>
       </c>
       <c r="F261" t="n">
-        <v>0.6342469549387438</v>
+        <v>0.77362680383212</v>
       </c>
       <c r="G261" t="n">
-        <v>24.74170770527471</v>
+        <v>25.61087612299238</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I261" t="n">
-        <v>22.18524881187164</v>
+        <v>22.06211102029395</v>
       </c>
       <c r="J261" t="n">
-        <v>0.01899728862120417</v>
+        <v>0.03787835940829505</v>
       </c>
       <c r="K261" t="n">
-        <v>0.548012435778527</v>
+        <v>0.7930147004270941</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -10391,22 +10391,22 @@
         <v>550</v>
       </c>
       <c r="F262" t="n">
-        <v>0.7262136290955139</v>
+        <v>0.616364595946658</v>
       </c>
       <c r="G262" t="n">
-        <v>24.31731083010372</v>
+        <v>23.6592982222464</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I262" t="n">
-        <v>155.9228539462806</v>
+        <v>157.2733832363579</v>
       </c>
       <c r="J262" t="n">
-        <v>0.04453453832656704</v>
+        <v>0.03508224269586363</v>
       </c>
       <c r="K262" t="n">
-        <v>0.867170163220729</v>
+        <v>0.7540001418179437</v>
       </c>
       <c r="L262" t="b">
         <v>0</v>
@@ -10435,16 +10435,16 @@
         <v>3.976587858956469</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I263" t="n">
-        <v>35.8192655025677</v>
+        <v>35.89327265622588</v>
       </c>
       <c r="J263" t="n">
-        <v>0.06247323690787367</v>
+        <v>0.0971587323445857</v>
       </c>
       <c r="K263" t="n">
-        <v>1.091363227804272</v>
+        <v>1.62016099729396</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -10467,22 +10467,22 @@
         <v>136</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>0.5951892006378579</v>
       </c>
       <c r="G264" t="n">
-        <v>20.49853041073921</v>
+        <v>24.15868158956481</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I264" t="n">
-        <v>123.2807776588541</v>
+        <v>121.9086207852389</v>
       </c>
       <c r="J264" t="n">
-        <v>0.01769928818453461</v>
+        <v>0.02376599781947106</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5317903729344046</v>
+        <v>0.5961031924514768</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -10505,22 +10505,22 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>0.07543157732456288</v>
+        <v>0.06686217391594833</v>
       </c>
       <c r="G265" t="n">
-        <v>13.66094986961278</v>
+        <v>13.62660716970657</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I265" t="n">
-        <v>18.90845325847148</v>
+        <v>19.30466492675331</v>
       </c>
       <c r="J265" t="n">
-        <v>0.03823644769066924</v>
+        <v>0.04273664096578794</v>
       </c>
       <c r="K265" t="n">
-        <v>0.7884583082727769</v>
+        <v>0.8608028974368459</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -10543,22 +10543,22 @@
         <v>177</v>
       </c>
       <c r="F266" t="n">
-        <v>0.6312434555399274</v>
+        <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>16.82875112568169</v>
+        <v>14.14926234826395</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I266" t="n">
-        <v>75.2996610220434</v>
+        <v>76.52912530227201</v>
       </c>
       <c r="J266" t="n">
-        <v>0.05355932634621149</v>
+        <v>0.05560764775778137</v>
       </c>
       <c r="K266" t="n">
-        <v>0.9799595539432727</v>
+        <v>1.04039363004555</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -10581,22 +10581,22 @@
         <v>193</v>
       </c>
       <c r="F267" t="n">
-        <v>0.6320172848581825</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>10.23945364370273</v>
+        <v>8.607438643406063</v>
       </c>
       <c r="H267" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I267" t="n">
-        <v>65.75998246291847</v>
+        <v>67.17964067390784</v>
       </c>
       <c r="J267" t="n">
-        <v>0.06168670016393277</v>
+        <v>0.101614393263648</v>
       </c>
       <c r="K267" t="n">
-        <v>1.081533301612445</v>
+        <v>1.682331379272793</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>139</v>
       </c>
       <c r="F268" t="n">
-        <v>0.632017284858201</v>
+        <v>0.6026373126474955</v>
       </c>
       <c r="G268" t="n">
-        <v>25.26945611497919</v>
+        <v>25.08223032086358</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I268" t="n">
-        <v>110.2585381903155</v>
+        <v>108.871104867552</v>
       </c>
       <c r="J268" t="n">
-        <v>0.04181266359591997</v>
+        <v>0.04080637078755128</v>
       </c>
       <c r="K268" t="n">
-        <v>0.8331528996767521</v>
+        <v>0.8338696014605049</v>
       </c>
       <c r="L268" t="b">
         <v>0</v>
@@ -10657,22 +10657,22 @@
         <v>99</v>
       </c>
       <c r="F269" t="n">
-        <v>0.6312434555399266</v>
+        <v>0.5951892006378695</v>
       </c>
       <c r="G269" t="n">
-        <v>18.31698805736985</v>
+        <v>18.15041154955398</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I269" t="n">
-        <v>30.76593474216654</v>
+        <v>32.16580183945761</v>
       </c>
       <c r="J269" t="n">
-        <v>0.07780436541626286</v>
+        <v>0.07319660577874641</v>
       </c>
       <c r="K269" t="n">
-        <v>1.282967577932637</v>
+        <v>1.285814513419945</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -10695,22 +10695,22 @@
         <v>8</v>
       </c>
       <c r="F270" t="n">
-        <v>0.0001526705929860085</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>4.436755915132027</v>
+        <v>4.436552715791846</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I270" t="n">
-        <v>63.56999750248387</v>
+        <v>64.99243890703715</v>
       </c>
       <c r="J270" t="n">
-        <v>0.03037471571787101</v>
+        <v>0.01921404503805324</v>
       </c>
       <c r="K270" t="n">
-        <v>0.6902044814454087</v>
+        <v>0.5325892383353478</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -10739,16 +10739,16 @@
         <v>17.03283675727564</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I271" t="n">
-        <v>86.53679202614136</v>
+        <v>87.75847577800965</v>
       </c>
       <c r="J271" t="n">
-        <v>0.008261854103272735</v>
+        <v>0.01588184017901685</v>
       </c>
       <c r="K271" t="n">
-        <v>0.4138438419252883</v>
+        <v>0.4860945762232206</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -10777,16 +10777,16 @@
         <v>5.940332650618145</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I272" t="n">
-        <v>35.06515555098649</v>
+        <v>36.43485590217651</v>
       </c>
       <c r="J272" t="n">
-        <v>0.02818393523934563</v>
+        <v>0.05941412310869225</v>
       </c>
       <c r="K272" t="n">
-        <v>0.6628246920429475</v>
+        <v>1.093505846360463</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -10809,22 +10809,22 @@
         <v>39</v>
       </c>
       <c r="F273" t="n">
-        <v>0.726601853298862</v>
+        <v>0.9118139730869906</v>
       </c>
       <c r="G273" t="n">
-        <v>24.81696089824009</v>
+        <v>25.94909767465867</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I273" t="n">
-        <v>163.6858778477157</v>
+        <v>165.1136951119933</v>
       </c>
       <c r="J273" t="n">
-        <v>0.05017080453588997</v>
+        <v>0.04146505421591763</v>
       </c>
       <c r="K273" t="n">
-        <v>0.9376107132165659</v>
+        <v>0.84306029193012</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -10847,22 +10847,22 @@
         <v>330</v>
       </c>
       <c r="F274" t="n">
-        <v>0.9468651833099453</v>
+        <v>0.7661794915118137</v>
       </c>
       <c r="G274" t="n">
-        <v>23.32395731466741</v>
+        <v>22.33935219729172</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I274" t="n">
-        <v>66.16020045843086</v>
+        <v>67.57912623523882</v>
       </c>
       <c r="J274" t="n">
-        <v>0.2905464826834747</v>
+        <v>0.2698756124593771</v>
       </c>
       <c r="K274" t="n">
-        <v>3.941761749647497</v>
+        <v>4.030100758416648</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
@@ -10891,16 +10891,16 @@
         <v>20.82782016918717</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I275" t="n">
-        <v>106.9725225134952</v>
+        <v>105.580600554595</v>
       </c>
       <c r="J275" t="n">
-        <v>0.03681509965212897</v>
+        <v>0.07037904282112063</v>
       </c>
       <c r="K275" t="n">
-        <v>0.7706946800387748</v>
+        <v>1.246500712727529</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -10923,22 +10923,22 @@
         <v>170</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>0.2957404881141228</v>
       </c>
       <c r="G276" t="n">
-        <v>8.030018742194814</v>
+        <v>8.74245924090949</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I276" t="n">
-        <v>111.3125103002659</v>
+        <v>109.9466087803887</v>
       </c>
       <c r="J276" t="n">
-        <v>0.06307693742549564</v>
+        <v>0.06939984957788799</v>
       </c>
       <c r="K276" t="n">
-        <v>1.098908115663494</v>
+        <v>1.232837909594907</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>352</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>0.2493457169276791</v>
       </c>
       <c r="G277" t="n">
-        <v>3.043189116699782</v>
+        <v>3.270830968314787</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I277" t="n">
-        <v>16.16552129253147</v>
+        <v>17.54820087315366</v>
       </c>
       <c r="J277" t="n">
-        <v>0.1093930815208273</v>
+        <v>0.0918239839906527</v>
       </c>
       <c r="K277" t="n">
-        <v>1.677754916470212</v>
+        <v>1.545724600775089</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -10999,22 +10999,22 @@
         <v>429</v>
       </c>
       <c r="F278" t="n">
-        <v>0.005869271986388712</v>
+        <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>10.66674880243332</v>
+        <v>10.648</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I278" t="n">
-        <v>23.45128887231625</v>
+        <v>23.48699508612173</v>
       </c>
       <c r="J278" t="n">
-        <v>0.09973608086852448</v>
+        <v>0.07571106376810288</v>
       </c>
       <c r="K278" t="n">
-        <v>1.557064301088495</v>
+        <v>1.320899053403503</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11037,22 +11037,22 @@
         <v>537</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>0.01026339997102189</v>
       </c>
       <c r="G279" t="n">
-        <v>15.36323637779488</v>
+        <v>15.41054008973328</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I279" t="n">
-        <v>26.84616567360449</v>
+        <v>27.57243351437813</v>
       </c>
       <c r="J279" t="n">
-        <v>0.03486211029670912</v>
+        <v>0.05544735628235414</v>
       </c>
       <c r="K279" t="n">
-        <v>0.7462867405939992</v>
+        <v>1.038157063476351</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -11081,16 +11081,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I280" t="n">
-        <v>63.53985576360109</v>
+        <v>64.96975879538874</v>
       </c>
       <c r="J280" t="n">
-        <v>0.01489300689685219</v>
+        <v>0.01278257604134545</v>
       </c>
       <c r="K280" t="n">
-        <v>0.4967182187802237</v>
+        <v>0.4428501644979054</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -11113,22 +11113,22 @@
         <v>544</v>
       </c>
       <c r="F281" t="n">
-        <v>0.0007738293182452965</v>
+        <v>0.1280937719090704</v>
       </c>
       <c r="G281" t="n">
-        <v>13.71932493286239</v>
+        <v>14.24322640861692</v>
       </c>
       <c r="H281" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I281" t="n">
-        <v>105.9585994252374</v>
+        <v>104.6049766457641</v>
       </c>
       <c r="J281" t="n">
-        <v>0.1002873238914751</v>
+        <v>0.06856049990274385</v>
       </c>
       <c r="K281" t="n">
-        <v>1.563953589187375</v>
+        <v>1.221126360878471</v>
       </c>
       <c r="L281" t="b">
         <v>0</v>
@@ -11151,22 +11151,22 @@
         <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>0.6312434555399251</v>
+        <v>0.6142193727680187</v>
       </c>
       <c r="G282" t="n">
-        <v>15.55097285939777</v>
+        <v>15.48419623650953</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I282" t="n">
-        <v>34.43914095773528</v>
+        <v>35.83015251778446</v>
       </c>
       <c r="J282" t="n">
-        <v>0.118279480469321</v>
+        <v>0.08880919564033243</v>
       </c>
       <c r="K282" t="n">
-        <v>1.788814757536435</v>
+        <v>1.503658890046772</v>
       </c>
       <c r="L282" t="b">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I283" t="n">
-        <v>121.2930211727403</v>
+        <v>119.9264170939405</v>
       </c>
       <c r="J283" t="n">
-        <v>0.0521358502941222</v>
+        <v>0.03942149004406699</v>
       </c>
       <c r="K283" t="n">
-        <v>0.9621693303641921</v>
+        <v>0.8145461909987262</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11227,22 +11227,22 @@
         <v>377</v>
       </c>
       <c r="F284" t="n">
-        <v>0</v>
+        <v>0.1759445647387021</v>
       </c>
       <c r="G284" t="n">
-        <v>4.710418346601499</v>
+        <v>4.959050098320499</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I284" t="n">
-        <v>28.17835312057534</v>
+        <v>29.37053762411161</v>
       </c>
       <c r="J284" t="n">
-        <v>0.1309062201057508</v>
+        <v>0.07871214314105981</v>
       </c>
       <c r="K284" t="n">
-        <v>1.946620377713341</v>
+        <v>1.362773481093299</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -11271,16 +11271,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H285" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I285" t="n">
-        <v>19.25068659894232</v>
+        <v>20.67780935287059</v>
       </c>
       <c r="J285" t="n">
-        <v>0.09336101109847106</v>
+        <v>0.05682554923635216</v>
       </c>
       <c r="K285" t="n">
-        <v>1.477390381478097</v>
+        <v>1.057387158393139</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -11309,16 +11309,16 @@
         <v>6.380249524901044</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I286" t="n">
-        <v>110.7586252727911</v>
+        <v>109.3909229698417</v>
       </c>
       <c r="J286" t="n">
-        <v>0.07884647848665349</v>
+        <v>0.05698279651525851</v>
       </c>
       <c r="K286" t="n">
-        <v>1.295991628804249</v>
+        <v>1.059581248915808</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -11341,22 +11341,22 @@
         <v>191</v>
       </c>
       <c r="F287" t="n">
-        <v>0.6312434555399357</v>
+        <v>0.04550845626989476</v>
       </c>
       <c r="G287" t="n">
-        <v>18.27261910361371</v>
+        <v>15.57298352905376</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I287" t="n">
-        <v>119.9692951507314</v>
+        <v>118.6568805104413</v>
       </c>
       <c r="J287" t="n">
-        <v>0.1295275831732211</v>
+        <v>0.07418057453598051</v>
       </c>
       <c r="K287" t="n">
-        <v>1.929390541476839</v>
+        <v>1.29954394988374</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -11379,22 +11379,22 @@
         <v>268</v>
       </c>
       <c r="F288" t="n">
-        <v>0.01496827675093042</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>4.333258896369386</v>
+        <v>4.313887457966422</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I288" t="n">
-        <v>15.31871851676592</v>
+        <v>16.70312070433718</v>
       </c>
       <c r="J288" t="n">
-        <v>0.09027497699661007</v>
+        <v>0.06600335300352803</v>
       </c>
       <c r="K288" t="n">
-        <v>1.438821951356499</v>
+        <v>1.185446177312417</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -11417,22 +11417,22 @@
         <v>372</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>0.1280937719090713</v>
       </c>
       <c r="G289" t="n">
-        <v>18.79875642163598</v>
+        <v>19.52115750681015</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I289" t="n">
-        <v>25.11189274963553</v>
+        <v>25.73255828216863</v>
       </c>
       <c r="J289" t="n">
-        <v>0.08812903304921438</v>
+        <v>0.06923647514180371</v>
       </c>
       <c r="K289" t="n">
-        <v>1.412002516947111</v>
+        <v>1.230558326098443</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -11461,16 +11461,16 @@
         <v>5.832000000000001</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I290" t="n">
-        <v>83.60672766171015</v>
+        <v>84.84784354193106</v>
       </c>
       <c r="J290" t="n">
-        <v>0.06350490335350305</v>
+        <v>0.05500546302009557</v>
       </c>
       <c r="K290" t="n">
-        <v>1.104256719549246</v>
+        <v>1.031991272719933</v>
       </c>
       <c r="L290" t="b">
         <v>0</v>
@@ -11493,22 +11493,22 @@
         <v>21</v>
       </c>
       <c r="F291" t="n">
-        <v>1</v>
+        <v>0.9327684619013404</v>
       </c>
       <c r="G291" t="n">
-        <v>29.25033432920041</v>
+        <v>28.79651625992683</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I291" t="n">
-        <v>76.69535432337047</v>
+        <v>77.92735927414485</v>
       </c>
       <c r="J291" t="n">
-        <v>0.2592643895365634</v>
+        <v>0.2028350967431129</v>
       </c>
       <c r="K291" t="n">
-        <v>3.550806502955177</v>
+        <v>3.094676239843728</v>
       </c>
       <c r="L291" t="b">
         <v>0</v>
@@ -11531,22 +11531,22 @@
         <v>556</v>
       </c>
       <c r="F292" t="n">
-        <v>0.3592067884186558</v>
+        <v>0.5951892006378834</v>
       </c>
       <c r="G292" t="n">
-        <v>7.980125572689588</v>
+        <v>8.490118482817302</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I292" t="n">
-        <v>29.61669166068819</v>
+        <v>31.04392917087046</v>
       </c>
       <c r="J292" t="n">
-        <v>0.2002679563616882</v>
+        <v>0.1848435084485238</v>
       </c>
       <c r="K292" t="n">
-        <v>2.813484835331167</v>
+        <v>2.84363740699738</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -11569,22 +11569,22 @@
         <v>240</v>
       </c>
       <c r="F293" t="n">
-        <v>0.6689592442021899</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>22.85937662237971</v>
+        <v>19.03856866993945</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I293" t="n">
-        <v>106.6613339185951</v>
+        <v>105.3158312513815</v>
       </c>
       <c r="J293" t="n">
-        <v>0.06583193558812039</v>
+        <v>0.04170940643728721</v>
       </c>
       <c r="K293" t="n">
-        <v>1.133339347015165</v>
+        <v>0.8464697683727573</v>
       </c>
       <c r="L293" t="b">
         <v>0</v>
@@ -11607,22 +11607,22 @@
         <v>466</v>
       </c>
       <c r="F294" t="n">
-        <v>0.001547658636490593</v>
+        <v>0.6547545758186289</v>
       </c>
       <c r="G294" t="n">
-        <v>8.063817210993284</v>
+        <v>9.643286221670607</v>
       </c>
       <c r="H294" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I294" t="n">
-        <v>77.00743402227098</v>
+        <v>78.18521834202453</v>
       </c>
       <c r="J294" t="n">
-        <v>0.1317480076914624</v>
+        <v>0.08480899472864541</v>
       </c>
       <c r="K294" t="n">
-        <v>1.957140814171631</v>
+        <v>1.447843597278939</v>
       </c>
       <c r="L294" t="b">
         <v>0</v>
@@ -11645,22 +11645,22 @@
         <v>572</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>0.1280937719090756</v>
       </c>
       <c r="G295" t="n">
-        <v>16.38096837796838</v>
+        <v>17.01045838608556</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I295" t="n">
-        <v>62.32087399783248</v>
+        <v>63.74817769250181</v>
       </c>
       <c r="J295" t="n">
-        <v>0.2380901705465084</v>
+        <v>0.2112766607422832</v>
       </c>
       <c r="K295" t="n">
-        <v>3.286176768304844</v>
+        <v>3.212462415196951</v>
       </c>
       <c r="L295" t="b">
         <v>0</v>
@@ -11689,16 +11689,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I296" t="n">
-        <v>224.6613889065725</v>
+        <v>226.0711472404213</v>
       </c>
       <c r="J296" t="n">
-        <v>0.1773517274016451</v>
+        <v>0.118454017081057</v>
       </c>
       <c r="K296" t="n">
-        <v>2.527083925256008</v>
+        <v>1.917296710819717</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -11727,16 +11727,16 @@
         <v>20.58068878827917</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I297" t="n">
-        <v>221.4163403853632</v>
+        <v>222.8042638753087</v>
       </c>
       <c r="J297" t="n">
-        <v>0.3768182539473801</v>
+        <v>0.3069900951694882</v>
       </c>
       <c r="K297" t="n">
-        <v>5.019963309199904</v>
+        <v>4.547963676836382</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -11765,16 +11765,16 @@
         <v>18.87858122317459</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I298" t="n">
-        <v>74.82185436263431</v>
+        <v>76.2527812117013</v>
       </c>
       <c r="J298" t="n">
-        <v>0.476394513193428</v>
+        <v>0.4675406497337666</v>
       </c>
       <c r="K298" t="n">
-        <v>6.264440806770453</v>
+        <v>6.788145208934453</v>
       </c>
       <c r="L298" t="b">
         <v>0</v>
@@ -11797,22 +11797,22 @@
         <v>195</v>
       </c>
       <c r="F299" t="n">
-        <v>0</v>
+        <v>0.5951892006378724</v>
       </c>
       <c r="G299" t="n">
-        <v>8.301867259839799</v>
+        <v>9.784221781295532</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I299" t="n">
-        <v>21.74405116195978</v>
+        <v>22.97246480537063</v>
       </c>
       <c r="J299" t="n">
-        <v>0.04693541000075607</v>
+        <v>0.07930454160670507</v>
       </c>
       <c r="K299" t="n">
-        <v>0.8971756162845964</v>
+        <v>1.371039289367729</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -11841,16 +11841,16 @@
         <v>5.352813839467986</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I300" t="n">
-        <v>24.94051482215637</v>
+        <v>25.23282686066488</v>
       </c>
       <c r="J300" t="n">
-        <v>0.06681553141515277</v>
+        <v>0.05153358503856067</v>
       </c>
       <c r="K300" t="n">
-        <v>1.14563206500552</v>
+        <v>0.9835477344397927</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -11879,16 +11879,16 @@
         <v>11.82363560839051</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I301" t="n">
-        <v>107.6213823426911</v>
+        <v>108.3476654740087</v>
       </c>
       <c r="J301" t="n">
-        <v>0.02645691778173915</v>
+        <v>0.04918326515755557</v>
       </c>
       <c r="K301" t="n">
-        <v>0.6412408890343195</v>
+        <v>0.9507534335652815</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -11911,22 +11911,22 @@
         <v>189</v>
       </c>
       <c r="F302" t="n">
-        <v>0.02993655350185781</v>
+        <v>0.3951397009945179</v>
       </c>
       <c r="G302" t="n">
-        <v>21.76885202900664</v>
+        <v>24.13263892265262</v>
       </c>
       <c r="H302" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I302" t="n">
-        <v>31.86396102487339</v>
+        <v>32.3913530405488</v>
       </c>
       <c r="J302" t="n">
-        <v>0.1018673624093364</v>
+        <v>0.1021607352561664</v>
       </c>
       <c r="K302" t="n">
-        <v>1.583700488655796</v>
+        <v>1.689954555942415</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -11955,16 +11955,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I303" t="n">
-        <v>86.55466606625306</v>
+        <v>87.68567489980217</v>
       </c>
       <c r="J303" t="n">
-        <v>0.052766500545495</v>
+        <v>0.06213111957168835</v>
       </c>
       <c r="K303" t="n">
-        <v>0.9700510287992716</v>
+        <v>1.131416430448435</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -11987,22 +11987,22 @@
         <v>584</v>
       </c>
       <c r="F304" t="n">
-        <v>0.05289263828635841</v>
+        <v>0</v>
       </c>
       <c r="G304" t="n">
-        <v>5.173384501039015</v>
+        <v>5.092576558089235</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I304" t="n">
-        <v>109.4576641369723</v>
+        <v>108.1415102488429</v>
       </c>
       <c r="J304" t="n">
-        <v>0.1359231582538181</v>
+        <v>0.09674420827715187</v>
       </c>
       <c r="K304" t="n">
-        <v>2.009320730982746</v>
+        <v>1.614377092261706</v>
       </c>
       <c r="L304" t="b">
         <v>0</v>
@@ -12025,22 +12025,22 @@
         <v>181</v>
       </c>
       <c r="F305" t="n">
-        <v>0.02993655350186084</v>
+        <v>0.3568752063885191</v>
       </c>
       <c r="G305" t="n">
-        <v>17.73384945930461</v>
+        <v>19.45773158824538</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I305" t="n">
-        <v>118.8069473985389</v>
+        <v>117.4412337930304</v>
       </c>
       <c r="J305" t="n">
-        <v>0.1451190837743335</v>
+        <v>0.1001543474829619</v>
       </c>
       <c r="K305" t="n">
-        <v>2.12424895249123</v>
+        <v>1.661959181850072</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -12063,22 +12063,22 @@
         <v>418</v>
       </c>
       <c r="F306" t="n">
-        <v>0.6371127275263401</v>
+        <v>0.9548796949877907</v>
       </c>
       <c r="G306" t="n">
-        <v>25.94791455735085</v>
+        <v>28.02460568838536</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I306" t="n">
-        <v>22.29108278956808</v>
+        <v>23.58655590268409</v>
       </c>
       <c r="J306" t="n">
-        <v>0.2194640914241477</v>
+        <v>0.1739754044360187</v>
       </c>
       <c r="K306" t="n">
-        <v>3.053393005274838</v>
+        <v>2.691993421937289</v>
       </c>
       <c r="L306" t="b">
         <v>0</v>
@@ -12101,22 +12101,22 @@
         <v>249</v>
       </c>
       <c r="F307" t="n">
-        <v>0.3156217277700418</v>
+        <v>0.1069434049194435</v>
       </c>
       <c r="G307" t="n">
-        <v>9.726928148614416</v>
+        <v>9.17065956800675</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I307" t="n">
-        <v>108.0473616971713</v>
+        <v>106.6560859473089</v>
       </c>
       <c r="J307" t="n">
-        <v>0.02074549093407682</v>
+        <v>0.03953180843893027</v>
       </c>
       <c r="K307" t="n">
-        <v>0.5698610014511438</v>
+        <v>0.8160854770603291</v>
       </c>
       <c r="L307" t="b">
         <v>0</v>
@@ -12145,16 +12145,16 @@
         <v>3.0214779496134</v>
       </c>
       <c r="H308" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I308" t="n">
-        <v>68.49527187931382</v>
+        <v>69.91652044153162</v>
       </c>
       <c r="J308" t="n">
-        <v>0.1913485704453476</v>
+        <v>0.149528910676004</v>
       </c>
       <c r="K308" t="n">
-        <v>2.702012731949516</v>
+        <v>2.350888503337894</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -12177,22 +12177,22 @@
         <v>361</v>
       </c>
       <c r="F309" t="n">
-        <v>1</v>
+        <v>0.7926569759622206</v>
       </c>
       <c r="G309" t="n">
-        <v>25.64056805142975</v>
+        <v>24.41370814731515</v>
       </c>
       <c r="H309" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I309" t="n">
-        <v>142.9697431236751</v>
+        <v>144.3714273525547</v>
       </c>
       <c r="J309" t="n">
-        <v>0.1707905299660034</v>
+        <v>0.1904504988786427</v>
       </c>
       <c r="K309" t="n">
-        <v>2.445083831783951</v>
+        <v>2.921872430515621</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -12221,16 +12221,16 @@
         <v>8.454192746797297</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I310" t="n">
-        <v>32.93836585854968</v>
+        <v>33.56888168405879</v>
       </c>
       <c r="J310" t="n">
-        <v>0.3334714677895974</v>
+        <v>0.344116664101211</v>
       </c>
       <c r="K310" t="n">
-        <v>4.478226750969995</v>
+        <v>5.065995235785082</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>519</v>
       </c>
       <c r="F311" t="n">
-        <v>0.3156217277699938</v>
+        <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>10.72971005998732</v>
+        <v>9.801628028036975</v>
       </c>
       <c r="H311" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I311" t="n">
-        <v>117.8274930109075</v>
+        <v>116.521434931452</v>
       </c>
       <c r="J311" t="n">
-        <v>0.06514838595253097</v>
+        <v>0.06345150869753131</v>
       </c>
       <c r="K311" t="n">
-        <v>1.124796526202208</v>
+        <v>1.149839981478352</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -12291,22 +12291,22 @@
         <v>9</v>
       </c>
       <c r="F312" t="n">
-        <v>0.09458456844065385</v>
+        <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>6.475648025644776</v>
+        <v>6.296969191603211</v>
       </c>
       <c r="H312" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I312" t="n">
-        <v>19.37993393889387</v>
+        <v>19.21671164859784</v>
       </c>
       <c r="J312" t="n">
-        <v>0.08222395483121217</v>
+        <v>0.09812125995937439</v>
       </c>
       <c r="K312" t="n">
-        <v>1.338202426249393</v>
+        <v>1.63359126287377</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12335,16 +12335,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H313" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I313" t="n">
-        <v>108.346043548387</v>
+        <v>106.9846395378498</v>
       </c>
       <c r="J313" t="n">
-        <v>0.04519274494093514</v>
+        <v>0.06275063461857189</v>
       </c>
       <c r="K313" t="n">
-        <v>0.8753962537219717</v>
+        <v>1.140060599698749</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12373,16 +12373,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H314" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I314" t="n">
-        <v>23.86473516311424</v>
+        <v>25.27933245754436</v>
       </c>
       <c r="J314" t="n">
-        <v>0.0698687720146067</v>
+        <v>0.0699078135047175</v>
       </c>
       <c r="K314" t="n">
-        <v>1.183790650691094</v>
+        <v>1.239925592418201</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12411,16 +12411,16 @@
         <v>4.289492277647788</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I315" t="n">
-        <v>23.25132212997007</v>
+        <v>24.68228976091389</v>
       </c>
       <c r="J315" t="n">
-        <v>0.01937396992747339</v>
+        <v>0.01584318531735677</v>
       </c>
       <c r="K315" t="n">
-        <v>0.5527200981566569</v>
+        <v>0.4855552202088378</v>
       </c>
       <c r="L315" t="b">
         <v>0</v>
@@ -12443,22 +12443,22 @@
         <v>542</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>0.215811126523114</v>
       </c>
       <c r="G316" t="n">
-        <v>9.962572308395055</v>
+        <v>10.60758249427787</v>
       </c>
       <c r="H316" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I316" t="n">
-        <v>117.3602625184094</v>
+        <v>116.040183199774</v>
       </c>
       <c r="J316" t="n">
-        <v>0.04174175447274171</v>
+        <v>0.02945005895888352</v>
       </c>
       <c r="K316" t="n">
-        <v>0.8322666963905877</v>
+        <v>0.6754135930065254</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -12487,16 +12487,16 @@
         <v>8.332258457345164</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I317" t="n">
-        <v>28.55845971489516</v>
+        <v>29.9815002674252</v>
       </c>
       <c r="J317" t="n">
-        <v>0.1340024044243991</v>
+        <v>0.06931937799975402</v>
       </c>
       <c r="K317" t="n">
-        <v>1.985315662533869</v>
+        <v>1.231715079819054</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -12519,22 +12519,22 @@
         <v>538</v>
       </c>
       <c r="F318" t="n">
-        <v>0.07543157732456444</v>
+        <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>9.990623792789549</v>
+        <v>9.769544155179402</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I318" t="n">
-        <v>82.84809553799803</v>
+        <v>84.00657879762412</v>
       </c>
       <c r="J318" t="n">
-        <v>0.02446680286096781</v>
+        <v>0.03333514302705234</v>
       </c>
       <c r="K318" t="n">
-        <v>0.6163689641876586</v>
+        <v>0.729622646371556</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12557,22 +12557,22 @@
         <v>62</v>
       </c>
       <c r="F319" t="n">
-        <v>0.1899429661995712</v>
+        <v>0.5951892006378646</v>
       </c>
       <c r="G319" t="n">
-        <v>21.10496705889037</v>
+        <v>23.53245434670069</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I319" t="n">
-        <v>37.86706947869204</v>
+        <v>39.23809699938215</v>
       </c>
       <c r="J319" t="n">
-        <v>0.08072807027480121</v>
+        <v>0.07140758531934494</v>
       </c>
       <c r="K319" t="n">
-        <v>1.319507260519007</v>
+        <v>1.260852092053208</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -12595,22 +12595,22 @@
         <v>17</v>
       </c>
       <c r="F320" t="n">
-        <v>0.6312434555399274</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>19.0317479169732</v>
+        <v>16.00149602380977</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I320" t="n">
-        <v>76.28031730831748</v>
+        <v>77.47204303414661</v>
       </c>
       <c r="J320" t="n">
-        <v>0.06202283514034478</v>
+        <v>0.03805076796810314</v>
       </c>
       <c r="K320" t="n">
-        <v>1.085734226787366</v>
+        <v>0.7954203381572527</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -12633,22 +12633,22 @@
         <v>282</v>
       </c>
       <c r="F321" t="n">
-        <v>0.7302873641417358</v>
+        <v>0.4209220923430291</v>
       </c>
       <c r="G321" t="n">
-        <v>26.14931814304795</v>
+        <v>24.15855878903113</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I321" t="n">
-        <v>22.26579170095671</v>
+        <v>22.89777808116138</v>
       </c>
       <c r="J321" t="n">
-        <v>0.1035625077169918</v>
+        <v>0.05303853768316191</v>
       </c>
       <c r="K321" t="n">
-        <v>1.604885962045359</v>
+        <v>1.004546522829328</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -12671,22 +12671,22 @@
         <v>10</v>
       </c>
       <c r="F322" t="n">
-        <v>0.2837537053219952</v>
+        <v>0.7736268038321459</v>
       </c>
       <c r="G322" t="n">
-        <v>15.7490971758529</v>
+        <v>17.88204530505818</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I322" t="n">
-        <v>228.675219788383</v>
+        <v>229.012104723199</v>
       </c>
       <c r="J322" t="n">
-        <v>0.01708222537759991</v>
+        <v>0.005130738211116231</v>
       </c>
       <c r="K322" t="n">
-        <v>0.52407848675157</v>
+        <v>0.3360831350073529</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -12709,22 +12709,22 @@
         <v>105</v>
       </c>
       <c r="F323" t="n">
-        <v>0.01173854397277731</v>
+        <v>0.005630575922813203</v>
       </c>
       <c r="G323" t="n">
-        <v>13.65648689664348</v>
+        <v>13.63155069536023</v>
       </c>
       <c r="H323" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I323" t="n">
-        <v>226.2278107914438</v>
+        <v>227.3406228240788</v>
       </c>
       <c r="J323" t="n">
-        <v>0.5032956930437169</v>
+        <v>0.4907647669557456</v>
       </c>
       <c r="K323" t="n">
-        <v>6.600644568944935</v>
+        <v>7.112194158133995</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -12753,16 +12753,16 @@
         <v>11.61919519588168</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I324" t="n">
-        <v>267.6614719824601</v>
+        <v>268.3943070793736</v>
       </c>
       <c r="J324" t="n">
-        <v>0.5972520611410271</v>
+        <v>0.5419204802923576</v>
       </c>
       <c r="K324" t="n">
-        <v>7.774886167654103</v>
+        <v>7.825976085508779</v>
       </c>
       <c r="L324" t="b">
         <v>0</v>
@@ -12785,22 +12785,22 @@
         <v>10</v>
       </c>
       <c r="F325" t="n">
-        <v>0.0003856051149581994</v>
+        <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>5.564737839006495</v>
+        <v>5.564094176054176</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1750952620997123</v>
+        <v>0.1715803741141795</v>
       </c>
       <c r="I325" t="n">
-        <v>268.2461997551408</v>
+        <v>268.9970524603122</v>
       </c>
       <c r="J325" t="n">
         <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>12.80832235915076</v>
+        <v>14.2176156725933</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>

--- a/output/lstm_results/lstm_data_for_cnn.xlsx
+++ b/output/lstm_results/lstm_data_for_cnn.xlsx
@@ -511,16 +511,16 @@
         <v>180</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.001125376523017444</v>
       </c>
       <c r="G2" t="n">
-        <v>11.11332497500186</v>
+        <v>11.11707697750772</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I2" t="n">
-        <v>124.3262143814385</v>
+        <v>123.9801760535763</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -555,10 +555,10 @@
         <v>3.130550111402148</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I3" t="n">
-        <v>106.4305605231818</v>
+        <v>106.087331717162</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>122</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3833534905282807</v>
+        <v>0.7233058175376885</v>
       </c>
       <c r="G4" t="n">
-        <v>25.18241587020466</v>
+        <v>27.48576325471744</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I4" t="n">
-        <v>28.47316595812926</v>
+        <v>28.6680047599389</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -625,16 +625,16 @@
         <v>272</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5951892006378684</v>
+        <v>0.9332434347061007</v>
       </c>
       <c r="G5" t="n">
-        <v>23.7245554245881</v>
+        <v>25.7660828291824</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I5" t="n">
-        <v>38.05362038487433</v>
+        <v>38.09754107350119</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -663,16 +663,16 @@
         <v>621</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03731312714916836</v>
+        <v>0.0715227090007348</v>
       </c>
       <c r="G6" t="n">
-        <v>13.04302995520815</v>
+        <v>13.17540711373734</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I6" t="n">
-        <v>61.58294078210703</v>
+        <v>61.94894254417791</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -701,16 +701,16 @@
         <v>502</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01489622401923269</v>
+        <v>0.05611812376378129</v>
       </c>
       <c r="G7" t="n">
-        <v>10.10451227190698</v>
+        <v>10.22891449245528</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I7" t="n">
-        <v>88.57674629989116</v>
+        <v>88.85052760492121</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -739,16 +739,16 @@
         <v>118</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.3342481549315355</v>
       </c>
       <c r="G8" t="n">
-        <v>15.02885654333023</v>
+        <v>16.53586681443189</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I8" t="n">
-        <v>74.06598031578348</v>
+        <v>74.33018561764962</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -783,10 +783,10 @@
         <v>13.96824971139906</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I9" t="n">
-        <v>85.41781853610156</v>
+        <v>85.7009805737882</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -815,16 +815,16 @@
         <v>406</v>
       </c>
       <c r="F10" t="n">
-        <v>0.773626803832149</v>
+        <v>0.6554394444584196</v>
       </c>
       <c r="G10" t="n">
-        <v>25.66170815367089</v>
+        <v>24.92323263347875</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I10" t="n">
-        <v>40.68396813840372</v>
+        <v>41.03867798004076</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -853,16 +853,16 @@
         <v>368</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1786585096886898</v>
+        <v>0.1676180539756941</v>
       </c>
       <c r="G11" t="n">
-        <v>4.189723237114659</v>
+        <v>4.176552234470966</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I11" t="n">
-        <v>117.7765291818234</v>
+        <v>117.4467179728609</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -891,16 +891,16 @@
         <v>379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2975946003189555</v>
+        <v>0.2778039902477502</v>
       </c>
       <c r="G12" t="n">
-        <v>5.974196009446874</v>
+        <v>5.941633263539386</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I12" t="n">
-        <v>103.5145149524218</v>
+        <v>103.1725216447958</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -935,10 +935,10 @@
         <v>10.87983322482473</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I13" t="n">
-        <v>34.66942230515379</v>
+        <v>34.96428678718871</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         <v>5.405378062633547</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I14" t="n">
-        <v>183.7520546554697</v>
+        <v>184.1108783166889</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1005,16 +1005,16 @@
         <v>277</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5961513589799912</v>
+        <v>0.5556079804954677</v>
       </c>
       <c r="G15" t="n">
-        <v>18.90786659519642</v>
+        <v>18.71278025392539</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I15" t="n">
-        <v>38.73852153989588</v>
+        <v>38.76486015077398</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>10.12438798150288</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I16" t="n">
-        <v>115.3666681299147</v>
+        <v>115.0178084115471</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1081,22 +1081,22 @@
         <v>212</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5381280975441328</v>
+        <v>0.2080343106309664</v>
       </c>
       <c r="G17" t="n">
-        <v>23.00185245272622</v>
+        <v>21.04063736180966</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I17" t="n">
-        <v>109.9196310786236</v>
+        <v>109.5890103764476</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07117533912770208</v>
+        <v>0.06752472552838458</v>
       </c>
       <c r="K17" t="n">
-        <v>1.257611532524588</v>
+        <v>1.268345857398801</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1125,16 +1125,16 @@
         <v>5.248200453488796</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I18" t="n">
-        <v>192.3682051821898</v>
+        <v>192.6431649330305</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09562359332823858</v>
+        <v>0.08978410643517858</v>
       </c>
       <c r="K18" t="n">
-        <v>1.598741014765982</v>
+        <v>1.576774331427376</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1157,22 +1157,22 @@
         <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.006363407677315835</v>
       </c>
       <c r="G19" t="n">
-        <v>22.28885569068094</v>
+        <v>22.33140561330714</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I19" t="n">
-        <v>30.58966353184178</v>
+        <v>30.72546812524225</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5157709914462432</v>
+        <v>0.5162807819833414</v>
       </c>
       <c r="K19" t="n">
-        <v>7.461109068102017</v>
+        <v>7.486360018845595</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -1195,22 +1195,22 @@
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5951892006378768</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>10.50880144988873</v>
+        <v>8.916669781930919</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I20" t="n">
-        <v>65.98198029495637</v>
+        <v>66.34307745706205</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0104592280209364</v>
+        <v>0.004435000154890434</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4104322052944498</v>
+        <v>0.394167559030695</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1233,22 +1233,22 @@
         <v>216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.364323318398138</v>
+        <v>0.1195961345280388</v>
       </c>
       <c r="G21" t="n">
-        <v>18.68081807592794</v>
+        <v>17.44443935537509</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I21" t="n">
-        <v>28.7086504990966</v>
+        <v>28.91957774721743</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1104656187959975</v>
+        <v>0.1055980215456138</v>
       </c>
       <c r="K21" t="n">
-        <v>1.805833612122856</v>
+        <v>1.795893709740377</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -1271,22 +1271,22 @@
         <v>16</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>0.0002201270988605955</v>
       </c>
       <c r="G22" t="n">
-        <v>6.604105389831389</v>
+        <v>6.6045415125994</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I22" t="n">
-        <v>106.0153727067974</v>
+        <v>105.6789003401442</v>
       </c>
       <c r="J22" t="n">
-        <v>0.03697540924515345</v>
+        <v>0.03262702369201181</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7804157263197521</v>
+        <v>0.7847993935700854</v>
       </c>
       <c r="L22" t="b">
         <v>0</v>
@@ -1309,22 +1309,22 @@
         <v>435</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2138868098388862</v>
+        <v>0.006008028808968237</v>
       </c>
       <c r="G23" t="n">
-        <v>14.06459103735658</v>
+        <v>13.24035968928035</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I23" t="n">
-        <v>23.12554096159242</v>
+        <v>23.30424984737047</v>
       </c>
       <c r="J23" t="n">
-        <v>0.06962635540779759</v>
+        <v>0.06967777148904498</v>
       </c>
       <c r="K23" t="n">
-        <v>1.235998373153897</v>
+        <v>1.298178703287034</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1347,22 +1347,22 @@
         <v>678</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4060274677024713</v>
+        <v>0.5915894620946763</v>
       </c>
       <c r="G24" t="n">
-        <v>17.57033838650605</v>
+        <v>18.44224864246285</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I24" t="n">
-        <v>112.5892694242007</v>
+        <v>112.2427370236233</v>
       </c>
       <c r="J24" t="n">
-        <v>0.02957647779124048</v>
+        <v>0.02422818139642693</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6771775304424568</v>
+        <v>0.6684240943791163</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -1385,22 +1385,22 @@
         <v>120</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.0002201270988607931</v>
       </c>
       <c r="G25" t="n">
-        <v>3.556590642736384</v>
+        <v>3.55682551333039</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I25" t="n">
-        <v>105.3604732968598</v>
+        <v>105.0118681725144</v>
       </c>
       <c r="J25" t="n">
-        <v>0.04957708895887434</v>
+        <v>0.05009294533522403</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9562485052516378</v>
+        <v>1.026809159361658</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>674</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5961513589800258</v>
+        <v>0.1195752910976399</v>
       </c>
       <c r="G26" t="n">
-        <v>22.49076219823504</v>
+        <v>19.76303582915675</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I26" t="n">
-        <v>64.56875548284938</v>
+        <v>64.93410941150916</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04873444836510492</v>
+        <v>0.04612079301367206</v>
       </c>
       <c r="K26" t="n">
-        <v>0.9444910379449606</v>
+        <v>0.9717705720678214</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1461,22 +1461,22 @@
         <v>576</v>
       </c>
       <c r="F27" t="n">
-        <v>0.03806034426027984</v>
+        <v>0.01674276541024988</v>
       </c>
       <c r="G27" t="n">
-        <v>14.20087810883268</v>
+        <v>14.11108487559604</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I27" t="n">
-        <v>64.50701566469179</v>
+        <v>64.87084648785653</v>
       </c>
       <c r="J27" t="n">
-        <v>0.07719098250288987</v>
+        <v>0.07173491780083813</v>
       </c>
       <c r="K27" t="n">
-        <v>1.34154854058636</v>
+        <v>1.326682752903536</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -1499,22 +1499,22 @@
         <v>70</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5951892006379008</v>
+        <v>0.1261588258738101</v>
       </c>
       <c r="G28" t="n">
-        <v>24.40099422378334</v>
+        <v>21.48773424718133</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I28" t="n">
-        <v>35.04079928524294</v>
+        <v>35.36183364569316</v>
       </c>
       <c r="J28" t="n">
-        <v>0.07690373752842843</v>
+        <v>0.07660281009965791</v>
       </c>
       <c r="K28" t="n">
-        <v>1.337540576311663</v>
+        <v>1.394132813610399</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -1537,22 +1537,22 @@
         <v>373</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008619644781409842</v>
+        <v>0.4841231118242003</v>
       </c>
       <c r="G29" t="n">
-        <v>22.34649229627227</v>
+        <v>25.52602074347283</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I29" t="n">
-        <v>11.82679437469452</v>
+        <v>11.49619242734502</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03056447323122934</v>
+        <v>0.02205576380014211</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6909631517034162</v>
+        <v>0.6383228329388018</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -1581,16 +1581,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I30" t="n">
-        <v>37.02019426331515</v>
+        <v>37.05379367224545</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07382933078240987</v>
+        <v>0.08145734203609174</v>
       </c>
       <c r="K30" t="n">
-        <v>1.294643002813521</v>
+        <v>1.461397751640202</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
@@ -1619,16 +1619,16 @@
         <v>7.790921447428411</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I31" t="n">
-        <v>158.9910764511143</v>
+        <v>159.311698206782</v>
       </c>
       <c r="J31" t="n">
-        <v>0.02635594974707148</v>
+        <v>0.02440297659210422</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6322411085924601</v>
+        <v>0.6708460761806774</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
@@ -1651,22 +1651,22 @@
         <v>469</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5961513589799898</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>13.49747166451959</v>
+        <v>11.449738512298</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I32" t="n">
-        <v>57.87812290221395</v>
+        <v>58.24308663919517</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1222728294615628</v>
+        <v>0.1172059203003309</v>
       </c>
       <c r="K32" t="n">
-        <v>1.970581067218072</v>
+        <v>1.956734054518467</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1695,16 +1695,16 @@
         <v>16.80179799902379</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I33" t="n">
-        <v>31.45164435315388</v>
+        <v>31.81660223219713</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0291656377942774</v>
+        <v>0.02028582891838809</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6714450296962482</v>
+        <v>0.6137984170534201</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1727,22 +1727,22 @@
         <v>193</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7253779204408797</v>
+        <v>0.5383036065805676</v>
       </c>
       <c r="G34" t="n">
-        <v>18.52515997842876</v>
+        <v>17.67129741580019</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I34" t="n">
-        <v>33.98316204155502</v>
+        <v>34.31668278173959</v>
       </c>
       <c r="J34" t="n">
-        <v>0.02040937807656706</v>
+        <v>0.0175790155089342</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5492678664774465</v>
+        <v>0.5762925073943094</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
@@ -1765,22 +1765,22 @@
         <v>616</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.1996629279258337</v>
       </c>
       <c r="G35" t="n">
-        <v>20.91041556258507</v>
+        <v>22.16292600119657</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I35" t="n">
-        <v>17.87056869735334</v>
+        <v>18.23551245922807</v>
       </c>
       <c r="J35" t="n">
-        <v>0.04281570600990994</v>
+        <v>0.03658539665511644</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8619061016715328</v>
+        <v>0.8396470525305239</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1803,22 +1803,22 @@
         <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>0.3570043753498616</v>
+        <v>0.1996629279258283</v>
       </c>
       <c r="G36" t="n">
-        <v>17.46478862791835</v>
+        <v>16.72015891145481</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I36" t="n">
-        <v>32.02631717944388</v>
+        <v>32.04843524662011</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02883047339277337</v>
+        <v>0.0194750570674192</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6667684397928142</v>
+        <v>0.6025642715115136</v>
       </c>
       <c r="L36" t="b">
         <v>0</v>
@@ -1841,22 +1841,22 @@
         <v>357</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1290559302512047</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>18.62228652001175</v>
+        <v>17.92816568977429</v>
       </c>
       <c r="H37" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I37" t="n">
-        <v>63.59345128450408</v>
+        <v>63.95913087275729</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02451037746208378</v>
+        <v>0.01820432960755358</v>
       </c>
       <c r="K37" t="n">
-        <v>0.606489612683885</v>
+        <v>0.5849569295556132</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
@@ -1879,22 +1879,22 @@
         <v>285</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4760653467354941</v>
+        <v>0.5556079804954748</v>
       </c>
       <c r="G38" t="n">
-        <v>18.59003570069012</v>
+        <v>18.97820730610955</v>
       </c>
       <c r="H38" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I38" t="n">
-        <v>107.4327523783848</v>
+        <v>107.0854528338689</v>
       </c>
       <c r="J38" t="n">
-        <v>0.09830492424141522</v>
+        <v>0.1033708429427106</v>
       </c>
       <c r="K38" t="n">
-        <v>1.636153953073443</v>
+        <v>1.765033673661257</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1923,16 +1923,16 @@
         <v>21.78421446827955</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I39" t="n">
-        <v>31.48672224991659</v>
+        <v>31.555702688621</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08092816860159326</v>
+        <v>0.08197809829037678</v>
       </c>
       <c r="K39" t="n">
-        <v>1.393693955487292</v>
+        <v>1.468613408604001</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
@@ -1955,22 +1955,22 @@
         <v>296</v>
       </c>
       <c r="F40" t="n">
-        <v>0.03806034426027984</v>
+        <v>0.3689036771398187</v>
       </c>
       <c r="G40" t="n">
-        <v>15.08827736466777</v>
+        <v>16.56892793476097</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I40" t="n">
-        <v>223.2837414757134</v>
+        <v>223.649820006219</v>
       </c>
       <c r="J40" t="n">
-        <v>0.04322337500139405</v>
+        <v>0.03915474465860454</v>
       </c>
       <c r="K40" t="n">
-        <v>0.867594356990303</v>
+        <v>0.875248226133799</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -1999,16 +1999,16 @@
         <v>3.307725502516798</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I41" t="n">
-        <v>186.1988743998944</v>
+        <v>186.5442363668793</v>
       </c>
       <c r="J41" t="n">
-        <v>0.117011084186937</v>
+        <v>0.1175975269656386</v>
       </c>
       <c r="K41" t="n">
-        <v>1.897163291597112</v>
+        <v>1.962160200317671</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
@@ -2031,22 +2031,22 @@
         <v>68</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01903017213013992</v>
+        <v>0.03274050562477036</v>
       </c>
       <c r="G42" t="n">
-        <v>9.345569314664509</v>
+        <v>9.383790370284645</v>
       </c>
       <c r="H42" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I42" t="n">
-        <v>64.03661408127596</v>
+        <v>64.39636598436697</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1302543276600578</v>
+        <v>0.129698314139604</v>
       </c>
       <c r="K42" t="n">
-        <v>2.081947888162836</v>
+        <v>2.129830062217178</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>109</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4950623756433119</v>
+        <v>0.6554394444583629</v>
       </c>
       <c r="G43" t="n">
-        <v>10.92716716488289</v>
+        <v>11.38492210287086</v>
       </c>
       <c r="H43" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I43" t="n">
-        <v>118.4057146636658</v>
+        <v>118.0675667311436</v>
       </c>
       <c r="J43" t="n">
-        <v>0.02850515019238923</v>
+        <v>0.02194364233334995</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6622291653727324</v>
+        <v>0.6367692653416905</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
@@ -2107,22 +2107,22 @@
         <v>71</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3568752063885261</v>
+        <v>0.6153956260442651</v>
       </c>
       <c r="G44" t="n">
-        <v>21.21005026440009</v>
+        <v>22.6959367763004</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I44" t="n">
-        <v>120.6542969456362</v>
+        <v>120.316306044816</v>
       </c>
       <c r="J44" t="n">
-        <v>0.02682423662967152</v>
+        <v>0.02490807665304837</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6387751727629105</v>
+        <v>0.6778447991766613</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2145,22 +2145,22 @@
         <v>620</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3570961128829306</v>
+        <v>0.3331423226394665</v>
       </c>
       <c r="G45" t="n">
-        <v>20.37264083536693</v>
+        <v>20.24040636986965</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I45" t="n">
-        <v>29.73686546975663</v>
+        <v>29.72309480130389</v>
       </c>
       <c r="J45" t="n">
-        <v>0.08112386973333242</v>
+        <v>0.07866702063590655</v>
       </c>
       <c r="K45" t="n">
-        <v>1.396424597323582</v>
+        <v>1.422734745911875</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
@@ -2183,22 +2183,22 @@
         <v>496</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5951892006378828</v>
+        <v>0.3331423226394647</v>
       </c>
       <c r="G46" t="n">
-        <v>22.48525519765746</v>
+        <v>20.98540611327722</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I46" t="n">
-        <v>16.00090322117087</v>
+        <v>16.35669369979437</v>
       </c>
       <c r="J46" t="n">
-        <v>0.02457609320427136</v>
+        <v>0.02030298795274825</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6074065524753187</v>
+        <v>0.6140361745546582</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2227,16 +2227,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I47" t="n">
-        <v>31.61185113963246</v>
+        <v>31.96603750993888</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07366936984565307</v>
+        <v>0.06592508982159091</v>
       </c>
       <c r="K47" t="n">
-        <v>1.292411048290834</v>
+        <v>1.246181125948547</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         <v>12.79325302649799</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I48" t="n">
-        <v>30.86520467093996</v>
+        <v>31.1773386021069</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03584021938597341</v>
+        <v>0.03207094151605213</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7645762833177536</v>
+        <v>0.7770942566804344</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2303,16 +2303,16 @@
         <v>13.11028664827737</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I49" t="n">
-        <v>21.79264110153531</v>
+        <v>21.81688102916607</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0124047633535027</v>
+        <v>0.008632123305801454</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4375784978369297</v>
+        <v>0.4523233673241045</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2335,22 +2335,22 @@
         <v>430</v>
       </c>
       <c r="F50" t="n">
-        <v>0.3778296952028944</v>
+        <v>0.5041627971162882</v>
       </c>
       <c r="G50" t="n">
-        <v>23.05092228433527</v>
+        <v>23.83560743337149</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I50" t="n">
-        <v>28.48704509831741</v>
+        <v>28.68225490547623</v>
       </c>
       <c r="J50" t="n">
-        <v>0.04087174102814416</v>
+        <v>0.03639271808758275</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8347817204259136</v>
+        <v>0.8369772767262791</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
@@ -2373,22 +2373,22 @@
         <v>551</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5951892006378862</v>
+        <v>0.06089347784089657</v>
       </c>
       <c r="G51" t="n">
-        <v>6.401595407232866</v>
+        <v>5.530951287061852</v>
       </c>
       <c r="H51" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I51" t="n">
-        <v>18.76150444288304</v>
+        <v>18.79602663289732</v>
       </c>
       <c r="J51" t="n">
-        <v>0.02452316651819899</v>
+        <v>0.0231705025220404</v>
       </c>
       <c r="K51" t="n">
-        <v>0.6066680599486733</v>
+        <v>0.6537687774767612</v>
       </c>
       <c r="L51" t="b">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>5.066791391008713</v>
       </c>
       <c r="H52" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I52" t="n">
-        <v>36.77136260216994</v>
+        <v>37.08965531300392</v>
       </c>
       <c r="J52" t="n">
-        <v>0.03985540235201662</v>
+        <v>0.02920940382954866</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8206006225231569</v>
+        <v>0.7374444701154297</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2455,16 +2455,16 @@
         <v>4.862088337329959</v>
       </c>
       <c r="H53" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I53" t="n">
-        <v>75.17190931593855</v>
+        <v>75.52402008117728</v>
       </c>
       <c r="J53" t="n">
-        <v>0.02044907895341146</v>
+        <v>0.01279216703866535</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5498218176696819</v>
+        <v>0.5099653990496018</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
@@ -2487,22 +2487,22 @@
         <v>537</v>
       </c>
       <c r="F54" t="n">
-        <v>0.003777446303530025</v>
+        <v>0.006363407677315835</v>
       </c>
       <c r="G54" t="n">
-        <v>6.110990080855065</v>
+        <v>6.115725549752624</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I54" t="n">
-        <v>36.40969723893878</v>
+        <v>36.39113369846598</v>
       </c>
       <c r="J54" t="n">
-        <v>0.04257711143576667</v>
+        <v>0.04353250280782109</v>
       </c>
       <c r="K54" t="n">
-        <v>0.8585769623851246</v>
+        <v>0.935906933187817</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
@@ -2525,22 +2525,22 @@
         <v>528</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.655439444458367</v>
       </c>
       <c r="G55" t="n">
-        <v>9.292517850399857</v>
+        <v>11.11972267164552</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I55" t="n">
-        <v>36.95769840833051</v>
+        <v>37.04273089348604</v>
       </c>
       <c r="J55" t="n">
-        <v>0.009816980564778357</v>
+        <v>0.007185648988070501</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4014708479560907</v>
+        <v>0.4322808572288164</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2569,16 +2569,16 @@
         <v>3.741326101798666</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I56" t="n">
-        <v>115.5019490161087</v>
+        <v>115.1630708182802</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.2644933169729917</v>
+        <v>0.3327157003371836</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>4.362815948444307</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I57" t="n">
-        <v>120.3226405281799</v>
+        <v>119.9756396626877</v>
       </c>
       <c r="J57" t="n">
-        <v>0.1224474511474744</v>
+        <v>0.1067987052088964</v>
       </c>
       <c r="K57" t="n">
-        <v>1.973017584967542</v>
+        <v>1.812530517008645</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I58" t="n">
-        <v>36.86247906006698</v>
+        <v>37.2260544377146</v>
       </c>
       <c r="J58" t="n">
-        <v>0.009429943128561859</v>
+        <v>0.01464240786221142</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3960704672523563</v>
+        <v>0.5356025430555931</v>
       </c>
       <c r="L58" t="b">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>551</v>
       </c>
       <c r="F59" t="n">
-        <v>0.6783175077595754</v>
+        <v>0.6452832321038344</v>
       </c>
       <c r="G59" t="n">
-        <v>25.16558585377399</v>
+        <v>24.95835772424283</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I59" t="n">
-        <v>31.63658954004927</v>
+        <v>31.99478692223615</v>
       </c>
       <c r="J59" t="n">
-        <v>0.03975892685893766</v>
+        <v>0.03104354869996067</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8192544881639074</v>
+        <v>0.7628585867926752</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
@@ -2715,22 +2715,22 @@
         <v>378</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5951892006378728</v>
+        <v>0.8334119707432152</v>
       </c>
       <c r="G60" t="n">
-        <v>26.517830201182</v>
+        <v>28.12585227896881</v>
       </c>
       <c r="H60" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I60" t="n">
-        <v>24.82197678875015</v>
+        <v>25.00209944356101</v>
       </c>
       <c r="J60" t="n">
-        <v>0.05115901572137915</v>
+        <v>0.04224996180320375</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9783213229264979</v>
+        <v>0.9181359014331798</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2759,16 +2759,16 @@
         <v>4.710418346601499</v>
       </c>
       <c r="H61" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I61" t="n">
-        <v>27.76439945401208</v>
+        <v>28.12132239769239</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0258531300616107</v>
+        <v>0.02008668735844665</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6252252039984114</v>
+        <v>0.61103908930277</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
@@ -2797,16 +2797,16 @@
         <v>13.57276718285553</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I62" t="n">
-        <v>88.43921665496805</v>
+        <v>88.72628164755132</v>
       </c>
       <c r="J62" t="n">
-        <v>0.06634879302686382</v>
+        <v>0.06094391724158663</v>
       </c>
       <c r="K62" t="n">
-        <v>1.19026614422455</v>
+        <v>1.177161440982611</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
@@ -2829,22 +2829,22 @@
         <v>659</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1069434049194428</v>
+        <v>0.100051591061783</v>
       </c>
       <c r="G63" t="n">
-        <v>4.706669185256021</v>
+        <v>4.697240441471054</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I63" t="n">
-        <v>34.35772109356829</v>
+        <v>34.66112711767342</v>
       </c>
       <c r="J63" t="n">
-        <v>0.08370465832416041</v>
+        <v>0.0764390715912122</v>
       </c>
       <c r="K63" t="n">
-        <v>1.432434656305394</v>
+        <v>1.391864034505037</v>
       </c>
       <c r="L63" t="b">
         <v>0</v>
@@ -2867,22 +2867,22 @@
         <v>46</v>
       </c>
       <c r="F64" t="n">
-        <v>0.192140657863612</v>
+        <v>0.3929299681882875</v>
       </c>
       <c r="G64" t="n">
-        <v>10.63941244115459</v>
+        <v>11.24536792165266</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I64" t="n">
-        <v>178.1886232491165</v>
+        <v>178.5545222002372</v>
       </c>
       <c r="J64" t="n">
-        <v>0.04240653799683514</v>
+        <v>0.03614216191861186</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8561969303210941</v>
+        <v>0.8335055423964823</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -2905,22 +2905,22 @@
         <v>692</v>
       </c>
       <c r="F65" t="n">
-        <v>0.01026339997102327</v>
+        <v>0.4331939137012132</v>
       </c>
       <c r="G65" t="n">
-        <v>11.14754312476978</v>
+        <v>12.55759239704821</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I65" t="n">
-        <v>28.43574905151868</v>
+        <v>28.76299847980758</v>
       </c>
       <c r="J65" t="n">
-        <v>0.08354331737309077</v>
+        <v>0.0907613936639983</v>
       </c>
       <c r="K65" t="n">
-        <v>1.430183446274147</v>
+        <v>1.590315732688023</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
@@ -2943,22 +2943,22 @@
         <v>489</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5951892006378646</v>
+        <v>0.5556079804954617</v>
       </c>
       <c r="G66" t="n">
-        <v>19.53082273380041</v>
+        <v>19.33404295526943</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I66" t="n">
-        <v>88.06986888223165</v>
+        <v>88.36892033840955</v>
       </c>
       <c r="J66" t="n">
-        <v>0.01751897000178738</v>
+        <v>0.019630895462323</v>
       </c>
       <c r="K66" t="n">
-        <v>0.5089376489523727</v>
+        <v>0.6047235857591337</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
@@ -2981,22 +2981,22 @@
         <v>259</v>
       </c>
       <c r="F67" t="n">
-        <v>0.06404688595454136</v>
+        <v>0.05978764554882575</v>
       </c>
       <c r="G67" t="n">
-        <v>4.496699112124089</v>
+        <v>4.491061673475929</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I67" t="n">
-        <v>18.20773370358911</v>
+        <v>18.56010457189323</v>
       </c>
       <c r="J67" t="n">
-        <v>0.04145116055714369</v>
+        <v>0.0371665918637124</v>
       </c>
       <c r="K67" t="n">
-        <v>0.8428664320092799</v>
+        <v>0.8477001584120651</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
@@ -3019,22 +3019,22 @@
         <v>627</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5951892006379293</v>
+        <v>0.5556079804955176</v>
       </c>
       <c r="G68" t="n">
-        <v>22.01453375723949</v>
+        <v>21.79272973309482</v>
       </c>
       <c r="H68" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I68" t="n">
-        <v>113.6814412022847</v>
+        <v>113.3326225889613</v>
       </c>
       <c r="J68" t="n">
-        <v>0.03366746126235582</v>
+        <v>0.02752928411082462</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7342595233697493</v>
+        <v>0.7141645431847929</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
@@ -3057,22 +3057,22 @@
         <v>12</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2975946003189912</v>
+        <v>0.2778039902477835</v>
       </c>
       <c r="G69" t="n">
-        <v>13.10321415287696</v>
+        <v>13.03179422752518</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I69" t="n">
-        <v>14.51460204666816</v>
+        <v>14.50737125346635</v>
       </c>
       <c r="J69" t="n">
-        <v>0.1020090995145471</v>
+        <v>0.09557250754730418</v>
       </c>
       <c r="K69" t="n">
-        <v>1.687838763886115</v>
+        <v>1.656979065312553</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
@@ -3095,22 +3095,22 @@
         <v>69</v>
       </c>
       <c r="F70" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.3331423226394647</v>
       </c>
       <c r="G70" t="n">
-        <v>20.59101867377917</v>
+        <v>20.45859140111987</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I70" t="n">
-        <v>28.4940097654383</v>
+        <v>28.79942375731314</v>
       </c>
       <c r="J70" t="n">
-        <v>0.05328615671300892</v>
+        <v>0.04828294028670889</v>
       </c>
       <c r="K70" t="n">
-        <v>1.008001581450364</v>
+        <v>1.001729526759335</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3133,22 +3133,22 @@
         <v>421</v>
       </c>
       <c r="F71" t="n">
-        <v>0.7021326055573247</v>
+        <v>0.3331423226394647</v>
       </c>
       <c r="G71" t="n">
-        <v>16.38843354153381</v>
+        <v>14.88992684598889</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I71" t="n">
-        <v>135.3698516483658</v>
+        <v>135.563433563711</v>
       </c>
       <c r="J71" t="n">
-        <v>0.05598102072613393</v>
+        <v>0.05031401226382509</v>
       </c>
       <c r="K71" t="n">
-        <v>1.045603348757255</v>
+        <v>1.029872287475243</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
@@ -3171,22 +3171,22 @@
         <v>694</v>
       </c>
       <c r="F72" t="n">
-        <v>0.892783800956821</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>27.83151699958124</v>
+        <v>28.5376</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I72" t="n">
-        <v>22.8818978209353</v>
+        <v>22.95753198808722</v>
       </c>
       <c r="J72" t="n">
-        <v>0.01474056606293384</v>
+        <v>0.006948588387803812</v>
       </c>
       <c r="K72" t="n">
-        <v>0.4701702388402119</v>
+        <v>0.4289961190099634</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>250</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>0.006363407677315243</v>
       </c>
       <c r="G73" t="n">
-        <v>17.30370795523318</v>
+        <v>17.33674111964768</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I73" t="n">
-        <v>42.39975683390819</v>
+        <v>42.04436319093445</v>
       </c>
       <c r="J73" t="n">
-        <v>0.03660892665848817</v>
+        <v>0.03180426458368495</v>
       </c>
       <c r="K73" t="n">
-        <v>0.7753021499468071</v>
+        <v>0.7733991512481209</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
@@ -3247,22 +3247,22 @@
         <v>350</v>
       </c>
       <c r="F74" t="n">
-        <v>0.6592360865923952</v>
+        <v>0.7819667873639948</v>
       </c>
       <c r="G74" t="n">
-        <v>24.9469553673627</v>
+        <v>25.71381925683546</v>
       </c>
       <c r="H74" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I74" t="n">
-        <v>75.93808782829193</v>
+        <v>76.30413346312223</v>
       </c>
       <c r="J74" t="n">
-        <v>0.02578941513991383</v>
+        <v>0.02273853422239137</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6243361819000962</v>
+        <v>0.6477833763531925</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
@@ -3285,22 +3285,22 @@
         <v>564</v>
       </c>
       <c r="F75" t="n">
-        <v>0.7023535120516848</v>
+        <v>0.6165014583363441</v>
       </c>
       <c r="G75" t="n">
-        <v>24.12513334953356</v>
+        <v>23.61191408263667</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I75" t="n">
-        <v>108.2646034605665</v>
+        <v>107.9193527142928</v>
       </c>
       <c r="J75" t="n">
-        <v>0.05807055728311725</v>
+        <v>0.04878295314332639</v>
       </c>
       <c r="K75" t="n">
-        <v>1.074758908003385</v>
+        <v>1.0086577608826</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
@@ -3329,16 +3329,16 @@
         <v>17.49805772078718</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I76" t="n">
-        <v>114.7970277367613</v>
+        <v>114.4564527493285</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1166115144834716</v>
+        <v>0.1061321169699709</v>
       </c>
       <c r="K76" t="n">
-        <v>1.89158804663506</v>
+        <v>1.803294195738161</v>
       </c>
       <c r="L76" t="b">
         <v>0</v>
@@ -3361,22 +3361,22 @@
         <v>607</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2329169819690044</v>
+        <v>0.1996629279258283</v>
       </c>
       <c r="G77" t="n">
-        <v>18.76241496853449</v>
+        <v>18.58746192088471</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I77" t="n">
-        <v>113.8165305589208</v>
+        <v>113.4775615538107</v>
       </c>
       <c r="J77" t="n">
-        <v>0.05040346690741452</v>
+        <v>0.04017824110757598</v>
       </c>
       <c r="K77" t="n">
-        <v>0.9677790578796055</v>
+        <v>0.8894299075225018</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3399,22 +3399,22 @@
         <v>316</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1876591470898412</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>5.905438933870218</v>
+        <v>5.590695395029137</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I78" t="n">
-        <v>51.12330019301063</v>
+        <v>51.46148284146233</v>
       </c>
       <c r="J78" t="n">
-        <v>0.08432075995561805</v>
+        <v>0.07675651614748659</v>
       </c>
       <c r="K78" t="n">
-        <v>1.441031197752619</v>
+        <v>1.396262581818207</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
@@ -3437,22 +3437,22 @@
         <v>438</v>
       </c>
       <c r="F79" t="n">
-        <v>0.000441812988819266</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>19.32218802428566</v>
+        <v>19.31962732559818</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I79" t="n">
-        <v>92.30076899316654</v>
+        <v>92.55132778260048</v>
       </c>
       <c r="J79" t="n">
-        <v>0.06563548997055982</v>
+        <v>0.05910069686940132</v>
       </c>
       <c r="K79" t="n">
-        <v>1.180313339403302</v>
+        <v>1.151621573136691</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
@@ -3475,22 +3475,22 @@
         <v>421</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>0.0002201270988607931</v>
       </c>
       <c r="G80" t="n">
-        <v>2.935153317971652</v>
+        <v>2.935347150007031</v>
       </c>
       <c r="H80" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I80" t="n">
-        <v>28.55776405149015</v>
+        <v>28.76547326001593</v>
       </c>
       <c r="J80" t="n">
-        <v>0.09973742284354106</v>
+        <v>0.08626057189507862</v>
       </c>
       <c r="K80" t="n">
-        <v>1.65614178134316</v>
+        <v>1.527951842341064</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3513,22 +3513,22 @@
         <v>17</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5951892006378883</v>
+        <v>0.5639793632006124</v>
       </c>
       <c r="G81" t="n">
-        <v>12.58818483772731</v>
+        <v>12.4881789960862</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I81" t="n">
-        <v>115.3166139883762</v>
+        <v>114.9808622044124</v>
       </c>
       <c r="J81" t="n">
-        <v>0.02523071726945565</v>
+        <v>0.0160626855974438</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6165406021537686</v>
+        <v>0.5552820703707836</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
@@ -3557,16 +3557,16 @@
         <v>4.411928036584459</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I82" t="n">
-        <v>31.15512129592505</v>
+        <v>31.101573511657</v>
       </c>
       <c r="J82" t="n">
-        <v>0.04211492978310331</v>
+        <v>0.04149844387980364</v>
       </c>
       <c r="K82" t="n">
-        <v>0.8521280852349898</v>
+        <v>0.9077227849457993</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
@@ -3595,16 +3595,16 @@
         <v>19.96717947032079</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I83" t="n">
-        <v>74.13477741184354</v>
+        <v>74.43606183224631</v>
       </c>
       <c r="J83" t="n">
-        <v>0.01784680031872117</v>
+        <v>0.009287636344232689</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5135119054764317</v>
+        <v>0.4614062293765469</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
@@ -3627,22 +3627,22 @@
         <v>241</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>0.0005522665463144676</v>
       </c>
       <c r="G84" t="n">
-        <v>7.583696723893961</v>
+        <v>7.58495319049336</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I84" t="n">
-        <v>25.36910668034387</v>
+        <v>25.54849223054578</v>
       </c>
       <c r="J84" t="n">
-        <v>0.02114838353087327</v>
+        <v>0.01123645041926108</v>
       </c>
       <c r="K84" t="n">
-        <v>0.5595793000028518</v>
+        <v>0.4884092153914435</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3665,22 +3665,22 @@
         <v>126</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0.6153956260442643</v>
       </c>
       <c r="G85" t="n">
-        <v>26.27539237994364</v>
+        <v>23.94332372531375</v>
       </c>
       <c r="H85" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I85" t="n">
-        <v>19.22765176316778</v>
+        <v>19.59132238529054</v>
       </c>
       <c r="J85" t="n">
-        <v>0.009590700929010199</v>
+        <v>0.002350834869385132</v>
       </c>
       <c r="K85" t="n">
-        <v>0.3983135405116324</v>
+        <v>0.3652891314893643</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3703,22 +3703,22 @@
         <v>474</v>
       </c>
       <c r="F86" t="n">
-        <v>0.1784376031942697</v>
+        <v>0.1665711613197418</v>
       </c>
       <c r="G86" t="n">
-        <v>10.80339941910567</v>
+        <v>10.76689421601264</v>
       </c>
       <c r="H86" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I86" t="n">
-        <v>28.37676406093437</v>
+        <v>28.7356999090658</v>
       </c>
       <c r="J86" t="n">
-        <v>0.04104277419760721</v>
+        <v>0.03096843882937501</v>
       </c>
       <c r="K86" t="n">
-        <v>0.837168167166301</v>
+        <v>0.761817856016459</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
@@ -3747,16 +3747,16 @@
         <v>10.61501705132875</v>
       </c>
       <c r="H87" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I87" t="n">
-        <v>28.04427858735315</v>
+        <v>28.37751686324468</v>
       </c>
       <c r="J87" t="n">
-        <v>0.04145284809972126</v>
+        <v>0.03508177892580801</v>
       </c>
       <c r="K87" t="n">
-        <v>0.8428899784973451</v>
+        <v>0.8188127569265808</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
@@ -3785,16 +3785,16 @@
         <v>3.240904040541774</v>
       </c>
       <c r="H88" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I88" t="n">
-        <v>77.23657795004371</v>
+        <v>77.51239391945548</v>
       </c>
       <c r="J88" t="n">
-        <v>0.006405490195938278</v>
+        <v>0.002854183808912798</v>
       </c>
       <c r="K88" t="n">
-        <v>0.3538699054246448</v>
+        <v>0.372263590750944</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
@@ -3817,22 +3817,22 @@
         <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>0.01903017213013642</v>
+        <v>0.1996629279258283</v>
       </c>
       <c r="G89" t="n">
-        <v>3.349111862355969</v>
+        <v>3.529569412433542</v>
       </c>
       <c r="H89" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I89" t="n">
-        <v>31.38438911698386</v>
+        <v>31.32262874478228</v>
       </c>
       <c r="J89" t="n">
-        <v>0.03986693367006636</v>
+        <v>0.05735811714564721</v>
       </c>
       <c r="K89" t="n">
-        <v>0.8207615204148264</v>
+        <v>1.127476193383269</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
@@ -3855,22 +3855,22 @@
         <v>507</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>0.0002201270988605955</v>
       </c>
       <c r="G90" t="n">
-        <v>5.537535282054643</v>
+        <v>5.537900970527586</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I90" t="n">
-        <v>67.15884312996096</v>
+        <v>67.52453209825443</v>
       </c>
       <c r="J90" t="n">
-        <v>0.06563371653183789</v>
+        <v>0.05523532506917526</v>
       </c>
       <c r="K90" t="n">
-        <v>1.180288594395825</v>
+        <v>1.098062548701608</v>
       </c>
       <c r="L90" t="b">
         <v>0</v>
@@ -3893,22 +3893,22 @@
         <v>643</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1999768503251298</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>11.14717645585418</v>
+        <v>10.51627310409919</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I91" t="n">
-        <v>100.6533425672609</v>
+        <v>100.3195926502358</v>
       </c>
       <c r="J91" t="n">
-        <v>0.02064318352719496</v>
+        <v>0.03809811311663408</v>
       </c>
       <c r="K91" t="n">
-        <v>0.5525301825374686</v>
+        <v>0.8606074211866614</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
@@ -3931,22 +3931,22 @@
         <v>327</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3518891294774103</v>
+        <v>0.499713483959131</v>
       </c>
       <c r="G92" t="n">
-        <v>18.70307805321443</v>
+        <v>19.45330967910356</v>
       </c>
       <c r="H92" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I92" t="n">
-        <v>89.12217466696183</v>
+        <v>89.41567267166317</v>
       </c>
       <c r="J92" t="n">
-        <v>0.06060238684240486</v>
+        <v>0.08203506662211275</v>
       </c>
       <c r="K92" t="n">
-        <v>1.110085835627701</v>
+        <v>1.46940276818677</v>
       </c>
       <c r="L92" t="b">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I93" t="n">
-        <v>96.45277424442565</v>
+        <v>96.5690615278435</v>
       </c>
       <c r="J93" t="n">
-        <v>0.04085151869700926</v>
+        <v>0.06170633296027273</v>
       </c>
       <c r="K93" t="n">
-        <v>0.8344995557652725</v>
+        <v>1.187725558541603</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4007,22 +4007,22 @@
         <v>547</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>2.084343038850936e-05</v>
       </c>
       <c r="G94" t="n">
-        <v>11.48356342778669</v>
+        <v>11.48363523484316</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I94" t="n">
-        <v>21.54290463660477</v>
+        <v>21.4647095987396</v>
       </c>
       <c r="J94" t="n">
-        <v>0.039650262468175</v>
+        <v>0.008426269081474905</v>
       </c>
       <c r="K94" t="n">
-        <v>0.8177382806238971</v>
+        <v>0.4494710281441772</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
@@ -4045,22 +4045,22 @@
         <v>8</v>
       </c>
       <c r="F95" t="n">
-        <v>0.2138868098388857</v>
+        <v>0.1996629279258279</v>
       </c>
       <c r="G95" t="n">
-        <v>12.07664955213162</v>
+        <v>12.02822379049246</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I95" t="n">
-        <v>28.87418744907121</v>
+        <v>28.85871547584147</v>
       </c>
       <c r="J95" t="n">
-        <v>0.04235445329601931</v>
+        <v>0.0365531484227057</v>
       </c>
       <c r="K95" t="n">
-        <v>0.8554701861177549</v>
+        <v>0.8392002174116941</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
@@ -4089,16 +4089,16 @@
         <v>24.6460742997744</v>
       </c>
       <c r="H96" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I96" t="n">
-        <v>86.61891584467858</v>
+        <v>86.89074637933992</v>
       </c>
       <c r="J96" t="n">
-        <v>0.03568468592417719</v>
+        <v>0.02913190660586206</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7624061058949176</v>
+        <v>0.7363706599073563</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
@@ -4127,16 +4127,16 @@
         <v>4.685296148590822</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I97" t="n">
-        <v>112.8911509417079</v>
+        <v>112.5488443754669</v>
       </c>
       <c r="J97" t="n">
-        <v>0.06040624124670921</v>
+        <v>0.04360935945168738</v>
       </c>
       <c r="K97" t="n">
-        <v>1.107348992131443</v>
+        <v>0.9369718674501802</v>
       </c>
       <c r="L97" t="b">
         <v>0</v>
@@ -4159,22 +4159,22 @@
         <v>667</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5951892006378902</v>
+        <v>0.09983146396292303</v>
       </c>
       <c r="G98" t="n">
-        <v>8.903107096376671</v>
+        <v>7.780490911157075</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I98" t="n">
-        <v>28.09208303351382</v>
+        <v>28.03353254097128</v>
       </c>
       <c r="J98" t="n">
-        <v>0.02411252330269363</v>
+        <v>0.02435284560449164</v>
       </c>
       <c r="K98" t="n">
-        <v>0.6009383049182218</v>
+        <v>0.6701514556035986</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
@@ -4197,22 +4197,22 @@
         <v>246</v>
       </c>
       <c r="F99" t="n">
-        <v>0.6142193727680159</v>
+        <v>0.558789684334119</v>
       </c>
       <c r="G99" t="n">
-        <v>8.531245500604802</v>
+        <v>8.411453742202005</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I99" t="n">
-        <v>110.9410823223517</v>
+        <v>110.5903325239081</v>
       </c>
       <c r="J99" t="n">
-        <v>0.05121296786759101</v>
+        <v>0.04068181734217143</v>
       </c>
       <c r="K99" t="n">
-        <v>0.9790741238239402</v>
+        <v>0.8964075162099888</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
@@ -4235,22 +4235,22 @@
         <v>478</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1280937719090819</v>
+        <v>0.7223492366494063</v>
       </c>
       <c r="G100" t="n">
-        <v>22.53439176628481</v>
+        <v>26.4030809065047</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I100" t="n">
-        <v>118.7723069765904</v>
+        <v>118.4279849665371</v>
       </c>
       <c r="J100" t="n">
-        <v>0.04556655777820207</v>
+        <v>0.0476450983226594</v>
       </c>
       <c r="K100" t="n">
-        <v>0.9002890729766873</v>
+        <v>0.9928915170919989</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
@@ -4279,16 +4279,16 @@
         <v>14.47703643706128</v>
       </c>
       <c r="H101" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I101" t="n">
-        <v>16.05542771999552</v>
+        <v>16.11763324445985</v>
       </c>
       <c r="J101" t="n">
-        <v>0.1262474730449963</v>
+        <v>0.1223503304742738</v>
       </c>
       <c r="K101" t="n">
-        <v>2.026039755457702</v>
+        <v>2.028015577862272</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4311,22 +4311,22 @@
         <v>130</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>0.6586211482970057</v>
       </c>
       <c r="G102" t="n">
-        <v>20.62180903800634</v>
+        <v>24.69639690257833</v>
       </c>
       <c r="H102" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I102" t="n">
-        <v>34.54734663011796</v>
+        <v>34.86743676924045</v>
       </c>
       <c r="J102" t="n">
-        <v>0.08017584252750347</v>
+        <v>0.07668472989674305</v>
       </c>
       <c r="K102" t="n">
-        <v>1.383196657724194</v>
+        <v>1.395267903490639</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
@@ -4355,16 +4355,16 @@
         <v>10.02719427357424</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I103" t="n">
-        <v>32.40457206220999</v>
+        <v>32.69652726945044</v>
       </c>
       <c r="J103" t="n">
-        <v>0.03824643686239805</v>
+        <v>0.03609467793224348</v>
       </c>
       <c r="K103" t="n">
-        <v>0.7981505301805385</v>
+        <v>0.8328475989650044</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
@@ -4387,22 +4387,22 @@
         <v>155</v>
       </c>
       <c r="F104" t="n">
-        <v>0.213886809838868</v>
+        <v>0.299494391888751</v>
       </c>
       <c r="G104" t="n">
-        <v>12.6551116656892</v>
+        <v>12.96052645996303</v>
       </c>
       <c r="H104" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I104" t="n">
-        <v>72.99798165687919</v>
+        <v>73.28103868943279</v>
       </c>
       <c r="J104" t="n">
-        <v>0.009478467725839015</v>
+        <v>0.003506977447594539</v>
       </c>
       <c r="K104" t="n">
-        <v>0.3967475368954216</v>
+        <v>0.3813087724959905</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
@@ -4431,16 +4431,16 @@
         <v>6.688712506902953</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I105" t="n">
-        <v>20.99439779113741</v>
+        <v>21.35888827785711</v>
       </c>
       <c r="J105" t="n">
-        <v>0.0318905254518025</v>
+        <v>0.03397722648995531</v>
       </c>
       <c r="K105" t="n">
-        <v>0.7094657205870155</v>
+        <v>0.8035079547085366</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
@@ -4463,22 +4463,22 @@
         <v>15</v>
       </c>
       <c r="F106" t="n">
-        <v>0.2222970801906261</v>
+        <v>0.3331423226394752</v>
       </c>
       <c r="G106" t="n">
-        <v>16.42758944756093</v>
+        <v>16.93971245343891</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I106" t="n">
-        <v>115.5312235343863</v>
+        <v>115.2081830634903</v>
       </c>
       <c r="J106" t="n">
-        <v>0.04198541141829493</v>
+        <v>0.03728431743851911</v>
       </c>
       <c r="K106" t="n">
-        <v>0.8503208996435186</v>
+        <v>0.8493313771572679</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
@@ -4507,16 +4507,16 @@
         <v>4.560359086738675</v>
       </c>
       <c r="H107" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I107" t="n">
-        <v>29.58947318993439</v>
+        <v>29.92941544538215</v>
       </c>
       <c r="J107" t="n">
-        <v>0.03382618379878579</v>
+        <v>0.03443248082123485</v>
       </c>
       <c r="K107" t="n">
-        <v>0.7364741983411511</v>
+        <v>0.8098160096935065</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4545,16 +4545,16 @@
         <v>3.08676659305494</v>
       </c>
       <c r="H108" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I108" t="n">
-        <v>36.8520154738767</v>
+        <v>36.84403045977039</v>
       </c>
       <c r="J108" t="n">
-        <v>0.05749417413112488</v>
+        <v>0.05412720565878654</v>
       </c>
       <c r="K108" t="n">
-        <v>1.066716563359917</v>
+        <v>1.08270832208503</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
@@ -4577,22 +4577,22 @@
         <v>198</v>
       </c>
       <c r="F109" t="n">
-        <v>0.5951892006378899</v>
+        <v>0.5556079804954809</v>
       </c>
       <c r="G109" t="n">
-        <v>23.00686865719966</v>
+        <v>22.77506651651356</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I109" t="n">
-        <v>121.7798212998546</v>
+        <v>121.4413115151095</v>
       </c>
       <c r="J109" t="n">
-        <v>0.01914708473393399</v>
+        <v>0.01810097657899717</v>
       </c>
       <c r="K109" t="n">
-        <v>0.5316549330190024</v>
+        <v>0.5835248584204202</v>
       </c>
       <c r="L109" t="b">
         <v>0</v>
@@ -4621,16 +4621,16 @@
         <v>5.431724311855306</v>
       </c>
       <c r="H110" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I110" t="n">
-        <v>37.47354957790519</v>
+        <v>37.53572098473737</v>
       </c>
       <c r="J110" t="n">
-        <v>0.03675098763622488</v>
+        <v>0.02967287441741327</v>
       </c>
       <c r="K110" t="n">
-        <v>0.7772843441511266</v>
+        <v>0.7438663704715431</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4659,16 +4659,16 @@
         <v>13.21653808680624</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I111" t="n">
-        <v>113.5320649587213</v>
+        <v>113.1942474619081</v>
       </c>
       <c r="J111" t="n">
-        <v>0.03518496796026094</v>
+        <v>0.02984364169012838</v>
       </c>
       <c r="K111" t="n">
-        <v>0.7554334800010929</v>
+        <v>0.7462325409215698</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
@@ -4697,16 +4697,16 @@
         <v>5.144277597486356</v>
       </c>
       <c r="H112" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I112" t="n">
-        <v>86.096201787232</v>
+        <v>86.37196738056875</v>
       </c>
       <c r="J112" t="n">
-        <v>0.1002151090352374</v>
+        <v>0.09375759983937609</v>
       </c>
       <c r="K112" t="n">
-        <v>1.662806995223489</v>
+        <v>1.631831500912498</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
@@ -4729,22 +4729,22 @@
         <v>376</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3759053785186572</v>
+        <v>0.1996837713562344</v>
       </c>
       <c r="G113" t="n">
-        <v>12.59075702602164</v>
+        <v>11.99258483736536</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I113" t="n">
-        <v>27.59206476803213</v>
+        <v>27.4913044018852</v>
       </c>
       <c r="J113" t="n">
-        <v>0.0866989259574545</v>
+        <v>0.08198726054670794</v>
       </c>
       <c r="K113" t="n">
-        <v>1.47421403895822</v>
+        <v>1.468740361853542</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4767,22 +4767,22 @@
         <v>366</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>0.555607980495524</v>
       </c>
       <c r="G114" t="n">
-        <v>14.18555800805876</v>
+        <v>16.55004077917665</v>
       </c>
       <c r="H114" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I114" t="n">
-        <v>37.43566240841635</v>
+        <v>37.79115251291416</v>
       </c>
       <c r="J114" t="n">
-        <v>0.01323544886924865</v>
+        <v>0.007129835696621932</v>
       </c>
       <c r="K114" t="n">
-        <v>0.4491691544771745</v>
+        <v>0.4315075020135893</v>
       </c>
       <c r="L114" t="b">
         <v>0</v>
@@ -4811,16 +4811,16 @@
         <v>20.08938572978278</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I115" t="n">
-        <v>50.73406826350784</v>
+        <v>50.9684274257136</v>
       </c>
       <c r="J115" t="n">
-        <v>0.04529719387308753</v>
+        <v>0.03893952859869226</v>
       </c>
       <c r="K115" t="n">
-        <v>0.8965306054504365</v>
+        <v>0.8722661683118347</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -4843,22 +4843,22 @@
         <v>447</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>2.719597194161805e-05</v>
       </c>
       <c r="G116" t="n">
-        <v>6.463893795538414</v>
+        <v>6.463946533100704</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I116" t="n">
-        <v>112.3684561107601</v>
+        <v>112.0192480824186</v>
       </c>
       <c r="J116" t="n">
-        <v>0.02174038076035456</v>
+        <v>0.01772994738260566</v>
       </c>
       <c r="K116" t="n">
-        <v>0.5678395097799925</v>
+        <v>0.5783838363343948</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -4881,22 +4881,22 @@
         <v>388</v>
       </c>
       <c r="F117" t="n">
-        <v>0.6592360865923985</v>
+        <v>0.5561602470417755</v>
       </c>
       <c r="G117" t="n">
-        <v>21.70937731679848</v>
+        <v>21.14890809066993</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I117" t="n">
-        <v>29.41156471541793</v>
+        <v>29.77421325989814</v>
       </c>
       <c r="J117" t="n">
-        <v>0.02727492951955807</v>
+        <v>0.01852844082029126</v>
       </c>
       <c r="K117" t="n">
-        <v>0.6450637458003056</v>
+        <v>0.5894478508071437</v>
       </c>
       <c r="L117" t="b">
         <v>0</v>
@@ -4925,16 +4925,16 @@
         <v>8.030018742194814</v>
       </c>
       <c r="H118" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I118" t="n">
-        <v>22.01992062528602</v>
+        <v>22.378182767952</v>
       </c>
       <c r="J118" t="n">
-        <v>0.02223415526142057</v>
+        <v>0.01874361263097217</v>
       </c>
       <c r="K118" t="n">
-        <v>0.5747292058094519</v>
+        <v>0.5924292955068039</v>
       </c>
       <c r="L118" t="b">
         <v>0</v>
@@ -4957,22 +4957,22 @@
         <v>165</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5980044885993355</v>
+        <v>0.008371382705123311</v>
       </c>
       <c r="G119" t="n">
-        <v>15.79720577324354</v>
+        <v>13.42789641179353</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I119" t="n">
-        <v>21.7370229037786</v>
+        <v>22.09146411070306</v>
       </c>
       <c r="J119" t="n">
-        <v>0.02962550899872316</v>
+        <v>0.02291860235552781</v>
       </c>
       <c r="K119" t="n">
-        <v>0.6778616688797063</v>
+        <v>0.6502784205665513</v>
       </c>
       <c r="L119" t="b">
         <v>0</v>
@@ -4995,22 +4995,22 @@
         <v>437</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>2.084343038841057e-05</v>
       </c>
       <c r="G120" t="n">
-        <v>3.330100148644182</v>
+        <v>3.330120971857372</v>
       </c>
       <c r="H120" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I120" t="n">
-        <v>106.0852673306042</v>
+        <v>105.7345537272479</v>
       </c>
       <c r="J120" t="n">
-        <v>0.06437305271057844</v>
+        <v>0.05798394099333827</v>
       </c>
       <c r="K120" t="n">
-        <v>1.162698397848488</v>
+        <v>1.136147678684782</v>
       </c>
       <c r="L120" t="b">
         <v>0</v>
@@ -5033,22 +5033,22 @@
         <v>57</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>0.3331423226394647</v>
       </c>
       <c r="G121" t="n">
-        <v>7.701882886671284</v>
+        <v>8.471629832740129</v>
       </c>
       <c r="H121" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I121" t="n">
-        <v>27.96918029625179</v>
+        <v>28.32800162588812</v>
       </c>
       <c r="J121" t="n">
-        <v>0.04156004041195172</v>
+        <v>0.03413154263974233</v>
       </c>
       <c r="K121" t="n">
-        <v>0.8443856459454786</v>
+        <v>0.8056461765573864</v>
       </c>
       <c r="L121" t="b">
         <v>0</v>
@@ -5077,16 +5077,16 @@
         <v>5.670752331040389</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I122" t="n">
-        <v>120.8229240654558</v>
+        <v>120.4915576373548</v>
       </c>
       <c r="J122" t="n">
-        <v>0.03424136106151673</v>
+        <v>0.02521476029894242</v>
       </c>
       <c r="K122" t="n">
-        <v>0.7422672174873075</v>
+        <v>0.6820942421107975</v>
       </c>
       <c r="L122" t="b">
         <v>0</v>
@@ -5115,16 +5115,16 @@
         <v>2.935153317971652</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I123" t="n">
-        <v>35.10148992551561</v>
+        <v>35.46494110471002</v>
       </c>
       <c r="J123" t="n">
-        <v>0.02346594428305947</v>
+        <v>0.02021033201682453</v>
       </c>
       <c r="K123" t="n">
-        <v>0.5919165087446894</v>
+        <v>0.6127523235326416</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
@@ -5153,16 +5153,16 @@
         <v>20.29361436511495</v>
       </c>
       <c r="H124" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I124" t="n">
-        <v>23.85636101303718</v>
+        <v>24.2194534750497</v>
       </c>
       <c r="J124" t="n">
-        <v>0.04521826786553125</v>
+        <v>0.0370252768123957</v>
       </c>
       <c r="K124" t="n">
-        <v>0.8954293412099631</v>
+        <v>0.8457420812392371</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
@@ -5191,16 +5191,16 @@
         <v>12.02926119925908</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I125" t="n">
-        <v>60.30827120306865</v>
+        <v>60.6738019350187</v>
       </c>
       <c r="J125" t="n">
-        <v>0.04530766383207459</v>
+        <v>0.03790470146291579</v>
       </c>
       <c r="K125" t="n">
-        <v>0.8966766940692413</v>
+        <v>0.8579274876581656</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
@@ -5229,16 +5229,16 @@
         <v>20.00788726977439</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I126" t="n">
-        <v>65.96828651400513</v>
+        <v>66.33223853133558</v>
       </c>
       <c r="J126" t="n">
-        <v>0.0820389482767252</v>
+        <v>0.0683430307644161</v>
       </c>
       <c r="K126" t="n">
-        <v>1.409192800204544</v>
+        <v>1.279684386367581</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
@@ -5267,16 +5267,16 @@
         <v>11.24748896420885</v>
       </c>
       <c r="H127" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I127" t="n">
-        <v>18.46558051146141</v>
+        <v>18.51603222208767</v>
       </c>
       <c r="J127" t="n">
-        <v>0.07682211868953247</v>
+        <v>0.06316568803915033</v>
       </c>
       <c r="K127" t="n">
-        <v>1.336401738666024</v>
+        <v>1.207946545905483</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
@@ -5305,16 +5305,16 @@
         <v>11.07986791437515</v>
       </c>
       <c r="H128" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I128" t="n">
-        <v>178.2453031415336</v>
+        <v>178.5497889623871</v>
       </c>
       <c r="J128" t="n">
-        <v>0.04205146067695802</v>
+        <v>0.03651615878648024</v>
       </c>
       <c r="K128" t="n">
-        <v>0.8512424930311429</v>
+        <v>0.8386876848707551</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
@@ -5343,16 +5343,16 @@
         <v>5.484544739538552</v>
       </c>
       <c r="H129" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I129" t="n">
-        <v>108.5056849424009</v>
+        <v>108.1774849927473</v>
       </c>
       <c r="J129" t="n">
-        <v>0.2276647445315529</v>
+        <v>0.2207988683630142</v>
       </c>
       <c r="K129" t="n">
-        <v>3.441127353482788</v>
+        <v>3.392129541252008</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
@@ -5375,22 +5375,22 @@
         <v>575</v>
       </c>
       <c r="F130" t="n">
-        <v>0.2138868098388678</v>
+        <v>0.1844063775521226</v>
       </c>
       <c r="G130" t="n">
-        <v>8.164579057522632</v>
+        <v>8.096724424784831</v>
       </c>
       <c r="H130" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I130" t="n">
-        <v>63.66152611624592</v>
+        <v>64.02690710431625</v>
       </c>
       <c r="J130" t="n">
-        <v>0.06464646812175677</v>
+        <v>0.06220106288047179</v>
       </c>
       <c r="K130" t="n">
-        <v>1.166513396534572</v>
+        <v>1.194580591706371</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
@@ -5413,22 +5413,22 @@
         <v>174</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>2.084343038841057e-05</v>
       </c>
       <c r="G131" t="n">
-        <v>3.533718721120853</v>
+        <v>3.533740817566906</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I131" t="n">
-        <v>110.8574129646511</v>
+        <v>110.5175583083802</v>
       </c>
       <c r="J131" t="n">
-        <v>0.02334646227040829</v>
+        <v>0.01714484802762499</v>
       </c>
       <c r="K131" t="n">
-        <v>0.5902493616028717</v>
+        <v>0.5702766341634345</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
@@ -5451,22 +5451,22 @@
         <v>442</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>0.1195961345280291</v>
       </c>
       <c r="G132" t="n">
-        <v>6.408090589247315</v>
+        <v>6.638005448501141</v>
       </c>
       <c r="H132" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I132" t="n">
-        <v>51.24958801802928</v>
+        <v>51.61364598797163</v>
       </c>
       <c r="J132" t="n">
-        <v>0.005854972367227541</v>
+        <v>0.001843253912438717</v>
       </c>
       <c r="K132" t="n">
-        <v>0.3461884628016935</v>
+        <v>0.3582560329206093</v>
       </c>
       <c r="L132" t="b">
         <v>0</v>
@@ -5489,22 +5489,22 @@
         <v>55</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>0.02156570697015319</v>
       </c>
       <c r="G133" t="n">
-        <v>11.34846355239334</v>
+        <v>11.42188484425305</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I133" t="n">
-        <v>57.78455765085248</v>
+        <v>58.15057381362641</v>
       </c>
       <c r="J133" t="n">
-        <v>0.0282193595453896</v>
+        <v>0.02438686221916285</v>
       </c>
       <c r="K133" t="n">
-        <v>0.6582414935070546</v>
+        <v>0.6706227936250193</v>
       </c>
       <c r="L133" t="b">
         <v>0</v>
@@ -5533,16 +5533,16 @@
         <v>5.697522180737868</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I134" t="n">
-        <v>118.0150255933915</v>
+        <v>117.6794961727823</v>
       </c>
       <c r="J134" t="n">
-        <v>0.07400236167211645</v>
+        <v>0.06902151554830471</v>
       </c>
       <c r="K134" t="n">
-        <v>1.297057323988899</v>
+        <v>1.289085547497022</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
@@ -5565,22 +5565,22 @@
         <v>8</v>
       </c>
       <c r="F135" t="n">
-        <v>0.2141077163332778</v>
+        <v>0.3331423226394548</v>
       </c>
       <c r="G135" t="n">
-        <v>15.68007551594518</v>
+        <v>16.20622143063687</v>
       </c>
       <c r="H135" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I135" t="n">
-        <v>110.0695285913</v>
+        <v>109.7343934548947</v>
       </c>
       <c r="J135" t="n">
-        <v>0.07007192809279915</v>
+        <v>0.06226559429164285</v>
       </c>
       <c r="K135" t="n">
-        <v>1.242215503346046</v>
+        <v>1.195474746164563</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
@@ -5603,22 +5603,22 @@
         <v>97</v>
       </c>
       <c r="F136" t="n">
-        <v>0.7736268038321662</v>
+        <v>0.5561602470418389</v>
       </c>
       <c r="G136" t="n">
-        <v>23.75390842322235</v>
+        <v>22.49612151938448</v>
       </c>
       <c r="H136" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I136" t="n">
-        <v>109.1948224615794</v>
+        <v>108.8451233741888</v>
       </c>
       <c r="J136" t="n">
-        <v>0.04829186905689345</v>
+        <v>0.0472438437306539</v>
       </c>
       <c r="K136" t="n">
-        <v>0.9383156747054202</v>
+        <v>0.9873316885402783</v>
       </c>
       <c r="L136" t="b">
         <v>0</v>
@@ -5641,22 +5641,22 @@
         <v>496</v>
       </c>
       <c r="F137" t="n">
-        <v>0.3570961128829266</v>
+        <v>0.3426195376366536</v>
       </c>
       <c r="G137" t="n">
-        <v>14.94764413763975</v>
+        <v>14.88900849691915</v>
       </c>
       <c r="H137" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I137" t="n">
-        <v>34.83787690051925</v>
+        <v>35.17700347287872</v>
       </c>
       <c r="J137" t="n">
-        <v>0.059076903799179</v>
+        <v>0.04660429524326926</v>
       </c>
       <c r="K137" t="n">
-        <v>1.088800584074146</v>
+        <v>0.9784700330945457</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
@@ -5685,16 +5685,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I138" t="n">
-        <v>111.3823025980306</v>
+        <v>111.0337705876007</v>
       </c>
       <c r="J138" t="n">
-        <v>0.05125944225578121</v>
+        <v>0.04640410195835692</v>
       </c>
       <c r="K138" t="n">
-        <v>0.9797225866487607</v>
+        <v>0.9756961325249465</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
@@ -5717,22 +5717,22 @@
         <v>498</v>
       </c>
       <c r="F139" t="n">
-        <v>0.2701375862540557</v>
+        <v>0.2778039902477502</v>
       </c>
       <c r="G139" t="n">
-        <v>8.198289182256612</v>
+        <v>8.215731087111919</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I139" t="n">
-        <v>71.29680198100472</v>
+        <v>71.65759962973476</v>
       </c>
       <c r="J139" t="n">
-        <v>0.08055242908679464</v>
+        <v>0.07273261810822634</v>
       </c>
       <c r="K139" t="n">
-        <v>1.388451216063465</v>
+        <v>1.340507000066299</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
@@ -5755,22 +5755,22 @@
         <v>631</v>
       </c>
       <c r="F140" t="n">
-        <v>0.2975946003190054</v>
+        <v>0.2778039902477968</v>
       </c>
       <c r="G140" t="n">
-        <v>5.688380346688007</v>
+        <v>5.657375457735339</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I140" t="n">
-        <v>21.95632069995601</v>
+        <v>22.03399112663278</v>
       </c>
       <c r="J140" t="n">
-        <v>0.06314189424032648</v>
+        <v>0.05821858780669491</v>
       </c>
       <c r="K140" t="n">
-        <v>1.145519893073904</v>
+        <v>1.13939897120196</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>240</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.3555937348028165</v>
       </c>
       <c r="G141" t="n">
-        <v>21.92495879553007</v>
+        <v>21.91734507630208</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I141" t="n">
-        <v>21.58259830850937</v>
+        <v>21.90255111146006</v>
       </c>
       <c r="J141" t="n">
-        <v>0.03243618204395738</v>
+        <v>0.02663052693037509</v>
       </c>
       <c r="K141" t="n">
-        <v>0.7170793337815033</v>
+        <v>0.7017112630666713</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
@@ -5837,16 +5837,16 @@
         <v>13.28753103477091</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I142" t="n">
-        <v>18.29193779128371</v>
+        <v>18.42837345552771</v>
       </c>
       <c r="J142" t="n">
-        <v>0.04739342070273656</v>
+        <v>0.04114150571222441</v>
       </c>
       <c r="K142" t="n">
-        <v>0.9257795148896634</v>
+        <v>0.9027770097326434</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
@@ -5869,22 +5869,22 @@
         <v>480</v>
       </c>
       <c r="F143" t="n">
-        <v>0.02739142753116069</v>
+        <v>0.07152270900072197</v>
       </c>
       <c r="G143" t="n">
-        <v>5.798447763434555</v>
+        <v>5.874589949582776</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I143" t="n">
-        <v>169.6491284361976</v>
+        <v>169.8503077329442</v>
       </c>
       <c r="J143" t="n">
-        <v>0.03742994058885556</v>
+        <v>0.03141345429256028</v>
       </c>
       <c r="K143" t="n">
-        <v>0.7867578577728921</v>
+        <v>0.7679840400987603</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
@@ -5907,22 +5907,22 @@
         <v>226</v>
       </c>
       <c r="F144" t="n">
-        <v>0.7021326055573245</v>
+        <v>0.5556079804954629</v>
       </c>
       <c r="G144" t="n">
-        <v>26.93268588700068</v>
+        <v>25.95478104001131</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I144" t="n">
-        <v>109.8137827669214</v>
+        <v>109.4721668119197</v>
       </c>
       <c r="J144" t="n">
-        <v>0.1285403258150606</v>
+        <v>0.1249573407154713</v>
       </c>
       <c r="K144" t="n">
-        <v>2.058032210701832</v>
+        <v>2.064138603647953</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
@@ -5951,16 +5951,16 @@
         <v>7.001992287913491</v>
       </c>
       <c r="H145" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I145" t="n">
-        <v>34.56320414530052</v>
+        <v>34.92646023213352</v>
       </c>
       <c r="J145" t="n">
-        <v>0.07861296280032957</v>
+        <v>0.0734813157554785</v>
       </c>
       <c r="K145" t="n">
-        <v>1.361389605663818</v>
+        <v>1.350881038491612</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
@@ -5989,16 +5989,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H146" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I146" t="n">
-        <v>90.21194356471943</v>
+        <v>90.49996639995184</v>
       </c>
       <c r="J146" t="n">
-        <v>0.02231289156679477</v>
+        <v>0.01579725580373862</v>
       </c>
       <c r="K146" t="n">
-        <v>0.5758278231121676</v>
+        <v>0.5516042454314016</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
@@ -6021,22 +6021,22 @@
         <v>143</v>
       </c>
       <c r="F147" t="n">
-        <v>0.7736268038321321</v>
+        <v>0.03529989789632428</v>
       </c>
       <c r="G147" t="n">
-        <v>26.17187203471116</v>
+        <v>21.46683554627016</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I147" t="n">
-        <v>78.47061759355985</v>
+        <v>78.77237568327845</v>
       </c>
       <c r="J147" t="n">
-        <v>0.06886315513967547</v>
+        <v>0.06290681954822033</v>
       </c>
       <c r="K147" t="n">
-        <v>1.225349346430947</v>
+        <v>1.204359635111964</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
@@ -6059,22 +6059,22 @@
         <v>93</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>0.6554394444583669</v>
       </c>
       <c r="G148" t="n">
-        <v>18.04607081887911</v>
+        <v>21.59450280853385</v>
       </c>
       <c r="H148" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I148" t="n">
-        <v>21.45058488238239</v>
+        <v>21.36867160429097</v>
       </c>
       <c r="J148" t="n">
-        <v>0.03790815691624677</v>
+        <v>0.03381818610944464</v>
       </c>
       <c r="K148" t="n">
-        <v>0.7934304687014371</v>
+        <v>0.8013042733898501</v>
       </c>
       <c r="L148" t="b">
         <v>0</v>
@@ -6097,22 +6097,22 @@
         <v>499</v>
       </c>
       <c r="F149" t="n">
-        <v>0.7661794915118011</v>
+        <v>0.6565452767504513</v>
       </c>
       <c r="G149" t="n">
-        <v>22.48499057139357</v>
+        <v>21.8836692948089</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I149" t="n">
-        <v>120.8069464208056</v>
+        <v>120.4621489507427</v>
       </c>
       <c r="J149" t="n">
-        <v>0.02197426467552615</v>
+        <v>0.02092523265920851</v>
       </c>
       <c r="K149" t="n">
-        <v>0.5711029206653931</v>
+        <v>0.6226580668745529</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
@@ -6135,22 +6135,22 @@
         <v>578</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4760322035132072</v>
+        <v>0.04269115974258064</v>
       </c>
       <c r="G150" t="n">
-        <v>18.02809638558554</v>
+        <v>15.97727872858687</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I150" t="n">
-        <v>149.1455179304894</v>
+        <v>149.5104723599268</v>
       </c>
       <c r="J150" t="n">
-        <v>0.04324311038105409</v>
+        <v>0.03886524342784958</v>
       </c>
       <c r="K150" t="n">
-        <v>0.867869727157434</v>
+        <v>0.8712368646675916</v>
       </c>
       <c r="L150" t="b">
         <v>0</v>
@@ -6173,22 +6173,22 @@
         <v>421</v>
       </c>
       <c r="F151" t="n">
-        <v>0.6026373126474847</v>
+        <v>0.5765390456978614</v>
       </c>
       <c r="G151" t="n">
-        <v>25.42638077959412</v>
+        <v>25.25778590609671</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I151" t="n">
-        <v>27.17077545253045</v>
+        <v>27.2274190694097</v>
       </c>
       <c r="J151" t="n">
-        <v>0.1625344628414699</v>
+        <v>0.1596996985260555</v>
       </c>
       <c r="K151" t="n">
-        <v>2.532356564005043</v>
+        <v>2.545532603262859</v>
       </c>
       <c r="L151" t="b">
         <v>0</v>
@@ -6211,22 +6211,22 @@
         <v>108</v>
       </c>
       <c r="F152" t="n">
-        <v>0.5951892006379031</v>
+        <v>0.0426911597425845</v>
       </c>
       <c r="G152" t="n">
-        <v>19.84716853846755</v>
+        <v>17.05591008443043</v>
       </c>
       <c r="H152" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I152" t="n">
-        <v>27.61901184876957</v>
+        <v>27.9844061417769</v>
       </c>
       <c r="J152" t="n">
-        <v>0.02701304932254462</v>
+        <v>0.02335891227748426</v>
       </c>
       <c r="K152" t="n">
-        <v>0.6414096993688629</v>
+        <v>0.6563794041427485</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
@@ -6249,22 +6249,22 @@
         <v>79</v>
       </c>
       <c r="F153" t="n">
-        <v>0.1259735770495792</v>
+        <v>0.1355928184632897</v>
       </c>
       <c r="G153" t="n">
-        <v>14.79709078142948</v>
+        <v>14.83823682372481</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I153" t="n">
-        <v>36.58966232633272</v>
+        <v>36.65734319615311</v>
       </c>
       <c r="J153" t="n">
-        <v>0.02413461412593173</v>
+        <v>0.0155512229944599</v>
       </c>
       <c r="K153" t="n">
-        <v>0.6012465408777993</v>
+        <v>0.5481951872799399</v>
       </c>
       <c r="L153" t="b">
         <v>0</v>
@@ -6293,16 +6293,16 @@
         <v>5.590695395029137</v>
       </c>
       <c r="H154" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I154" t="n">
-        <v>32.87968912169009</v>
+        <v>32.92395093557022</v>
       </c>
       <c r="J154" t="n">
-        <v>0.06868951412633864</v>
+        <v>0.06593206656512968</v>
       </c>
       <c r="K154" t="n">
-        <v>1.222926512125904</v>
+        <v>1.246277796488144</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
@@ -6331,16 +6331,16 @@
         <v>17.03283675727564</v>
       </c>
       <c r="H155" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I155" t="n">
-        <v>69.32433762117935</v>
+        <v>69.68972377019222</v>
       </c>
       <c r="J155" t="n">
-        <v>0.02570774773948593</v>
+        <v>0.02197083891060323</v>
       </c>
       <c r="K155" t="n">
-        <v>0.6231966666694602</v>
+        <v>0.6371461041610698</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
@@ -6363,22 +6363,22 @@
         <v>369</v>
       </c>
       <c r="F156" t="n">
-        <v>0.7711337653765813</v>
+        <v>0.7221791418152028</v>
       </c>
       <c r="G156" t="n">
-        <v>27.80982157057147</v>
+        <v>27.47812946205771</v>
       </c>
       <c r="H156" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I156" t="n">
-        <v>118.6317151155459</v>
+        <v>118.294393656733</v>
       </c>
       <c r="J156" t="n">
-        <v>0.06910029041081561</v>
+        <v>0.0656059152679344</v>
       </c>
       <c r="K156" t="n">
-        <v>1.228658123883998</v>
+        <v>1.241758607597959</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
@@ -6401,22 +6401,22 @@
         <v>82</v>
       </c>
       <c r="F157" t="n">
-        <v>0.4045380052384032</v>
+        <v>0.3375916357965652</v>
       </c>
       <c r="G157" t="n">
-        <v>11.64544348831014</v>
+        <v>11.43687018776942</v>
       </c>
       <c r="H157" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I157" t="n">
-        <v>116.7927005161663</v>
+        <v>116.4598417866512</v>
       </c>
       <c r="J157" t="n">
-        <v>0.1021147885733841</v>
+        <v>0.09718688044436741</v>
       </c>
       <c r="K157" t="n">
-        <v>1.689313456255718</v>
+        <v>1.679347996921174</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
@@ -6439,22 +6439,22 @@
         <v>23</v>
       </c>
       <c r="F158" t="n">
-        <v>0.3217923731004134</v>
+        <v>0.6554394444583832</v>
       </c>
       <c r="G158" t="n">
-        <v>19.96101928044163</v>
+        <v>21.78310042323694</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I158" t="n">
-        <v>106.8858169294864</v>
+        <v>106.5358721097394</v>
       </c>
       <c r="J158" t="n">
-        <v>0.1585777953619021</v>
+        <v>0.1328311786659585</v>
       </c>
       <c r="K158" t="n">
-        <v>2.477148698542129</v>
+        <v>2.173239383853202</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
@@ -6483,16 +6483,16 @@
         <v>4.760796887076785</v>
       </c>
       <c r="H159" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I159" t="n">
-        <v>38.18343082909047</v>
+        <v>38.20072964526668</v>
       </c>
       <c r="J159" t="n">
-        <v>0.1242915947134856</v>
+        <v>0.1083662257989432</v>
       </c>
       <c r="K159" t="n">
-        <v>1.998749145785426</v>
+        <v>1.83425025780561</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
@@ -6515,22 +6515,22 @@
         <v>539</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3643233183981304</v>
+        <v>0.7963603154272592</v>
       </c>
       <c r="G160" t="n">
-        <v>18.93730305743638</v>
+        <v>21.14995185513755</v>
       </c>
       <c r="H160" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I160" t="n">
-        <v>52.36474367311432</v>
+        <v>52.72986510062912</v>
       </c>
       <c r="J160" t="n">
-        <v>0.03128772523621363</v>
+        <v>0.02500499588630333</v>
       </c>
       <c r="K160" t="n">
-        <v>0.7010547754229097</v>
+        <v>0.6791877229238228</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
@@ -6553,22 +6553,22 @@
         <v>60</v>
       </c>
       <c r="F161" t="n">
-        <v>0.3208302147583296</v>
+        <v>0.001105832292071119</v>
       </c>
       <c r="G161" t="n">
-        <v>22.1572110107528</v>
+        <v>20.21854556396755</v>
       </c>
       <c r="H161" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I161" t="n">
-        <v>39.86911187028896</v>
+        <v>40.23426136641109</v>
       </c>
       <c r="J161" t="n">
-        <v>0.08975307605639128</v>
+        <v>0.08981830663089144</v>
       </c>
       <c r="K161" t="n">
-        <v>1.516828968981115</v>
+        <v>1.577248213168264</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
@@ -6597,16 +6597,16 @@
         <v>6.604105389831389</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I162" t="n">
-        <v>84.17126200775139</v>
+        <v>84.46794792650101</v>
       </c>
       <c r="J162" t="n">
-        <v>0.03893779469059028</v>
+        <v>0.03289927029084826</v>
       </c>
       <c r="K162" t="n">
-        <v>0.8077971305488205</v>
+        <v>0.788571672924583</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
@@ -6629,22 +6629,22 @@
         <v>69</v>
       </c>
       <c r="F163" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.1003837305092376</v>
       </c>
       <c r="G163" t="n">
-        <v>19.41457211951801</v>
+        <v>18.06514370567686</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I163" t="n">
-        <v>91.73580564939417</v>
+        <v>92.01899615236768</v>
       </c>
       <c r="J163" t="n">
-        <v>0.0558499425420699</v>
+        <v>0.03827613397899608</v>
       </c>
       <c r="K163" t="n">
-        <v>1.043774398816857</v>
+        <v>0.8630740981869549</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
@@ -6667,22 +6667,22 @@
         <v>624</v>
       </c>
       <c r="F164" t="n">
-        <v>0.001924316684246317</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>11.45634838915284</v>
+        <v>11.449738512298</v>
       </c>
       <c r="H164" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I164" t="n">
-        <v>15.36728592076906</v>
+        <v>15.63318564062918</v>
       </c>
       <c r="J164" t="n">
-        <v>0.1017287711275299</v>
+        <v>0.1000941215364188</v>
       </c>
       <c r="K164" t="n">
-        <v>1.68392730760231</v>
+        <v>1.719631054990453</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
@@ -6711,16 +6711,16 @@
         <v>4.635186296148192</v>
       </c>
       <c r="H165" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I165" t="n">
-        <v>29.80696048120351</v>
+        <v>30.17225168549809</v>
       </c>
       <c r="J165" t="n">
-        <v>0.04339517240541264</v>
+        <v>0.03542059614012801</v>
       </c>
       <c r="K165" t="n">
-        <v>0.8699914671889522</v>
+        <v>0.8235074461825357</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
@@ -6749,16 +6749,16 @@
         <v>15.96371209963397</v>
       </c>
       <c r="H166" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I166" t="n">
-        <v>114.824765569008</v>
+        <v>114.4821131261623</v>
       </c>
       <c r="J166" t="n">
-        <v>0.06724631472435257</v>
+        <v>0.06163372815088555</v>
       </c>
       <c r="K166" t="n">
-        <v>1.202789374286434</v>
+        <v>1.186719538173822</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
@@ -6787,16 +6787,16 @@
         <v>9.514139425087274</v>
       </c>
       <c r="H167" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I167" t="n">
-        <v>18.89273191491552</v>
+        <v>18.86237171536617</v>
       </c>
       <c r="J167" t="n">
-        <v>0.06077057432420193</v>
+        <v>0.0569312244464208</v>
       </c>
       <c r="K167" t="n">
-        <v>1.112432576139899</v>
+        <v>1.121561120347426</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
@@ -6825,16 +6825,16 @@
         <v>19.03856866993945</v>
       </c>
       <c r="H168" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I168" t="n">
-        <v>33.04760170095802</v>
+        <v>33.34204843965681</v>
       </c>
       <c r="J168" t="n">
-        <v>0.05795825191453557</v>
+        <v>0.0526207182872673</v>
       </c>
       <c r="K168" t="n">
-        <v>1.073191897454371</v>
+        <v>1.061834264397326</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
@@ -6857,22 +6857,22 @@
         <v>211</v>
       </c>
       <c r="F169" t="n">
-        <v>0.2138868098388862</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>8.038971535989207</v>
+        <v>7.554245495084205</v>
       </c>
       <c r="H169" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I169" t="n">
-        <v>63.79507164034288</v>
+        <v>64.15418126697598</v>
       </c>
       <c r="J169" t="n">
-        <v>0.03391606430482601</v>
+        <v>0.02779391253173094</v>
       </c>
       <c r="K169" t="n">
-        <v>0.7377283120393154</v>
+        <v>0.7178312642129512</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
@@ -6901,16 +6901,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H170" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I170" t="n">
-        <v>129.2534646138466</v>
+        <v>129.5592370729899</v>
       </c>
       <c r="J170" t="n">
-        <v>0.06893006680978271</v>
+        <v>0.0648221506179687</v>
       </c>
       <c r="K170" t="n">
-        <v>1.226282973150972</v>
+        <v>1.230898676856908</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
@@ -6933,22 +6933,22 @@
         <v>255</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>0.0005522665463146651</v>
       </c>
       <c r="G171" t="n">
-        <v>10.87983322482473</v>
+        <v>10.88163579520059</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I171" t="n">
-        <v>171.8882454960283</v>
+        <v>172.1437399303423</v>
       </c>
       <c r="J171" t="n">
-        <v>0.05685485280137732</v>
+        <v>0.05660614015410899</v>
       </c>
       <c r="K171" t="n">
-        <v>1.057796034621391</v>
+        <v>1.117056715996369</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>2.82842712474619</v>
       </c>
       <c r="H172" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I172" t="n">
-        <v>34.69300613334362</v>
+        <v>35.05747478498868</v>
       </c>
       <c r="J172" t="n">
-        <v>0.2470540049634271</v>
+        <v>0.2478217734049579</v>
       </c>
       <c r="K172" t="n">
-        <v>3.711668076673717</v>
+        <v>3.766561939026462</v>
       </c>
       <c r="L172" t="b">
         <v>0</v>
@@ -7009,22 +7009,22 @@
         <v>686</v>
       </c>
       <c r="F173" t="n">
-        <v>0.3568752063884874</v>
+        <v>0.5556496673562658</v>
       </c>
       <c r="G173" t="n">
-        <v>17.71465718261627</v>
+        <v>18.66886380665953</v>
       </c>
       <c r="H173" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I173" t="n">
-        <v>30.06398657653316</v>
+        <v>30.43007602768878</v>
       </c>
       <c r="J173" t="n">
-        <v>0.02353984531373826</v>
+        <v>0.02088820825456031</v>
       </c>
       <c r="K173" t="n">
-        <v>0.592947658867957</v>
+        <v>0.6221450525784555</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
@@ -7047,22 +7047,22 @@
         <v>591</v>
       </c>
       <c r="F174" t="n">
-        <v>0.595189200637853</v>
+        <v>0.7221791418151724</v>
       </c>
       <c r="G174" t="n">
-        <v>21.96764445132071</v>
+        <v>22.67775107602614</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I174" t="n">
-        <v>32.44400472476183</v>
+        <v>32.4641144900037</v>
       </c>
       <c r="J174" t="n">
-        <v>0.03102647924353538</v>
+        <v>0.02574861300700042</v>
       </c>
       <c r="K174" t="n">
-        <v>0.6974095781221546</v>
+        <v>0.689491365004368</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>105</v>
       </c>
       <c r="F175" t="n">
-        <v>0.2975946003189789</v>
+        <v>0.2778039902477721</v>
       </c>
       <c r="G175" t="n">
-        <v>9.577524740800841</v>
+        <v>9.525321816078547</v>
       </c>
       <c r="H175" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I175" t="n">
-        <v>99.69118740114735</v>
+        <v>99.36081300332583</v>
       </c>
       <c r="J175" t="n">
-        <v>0.0307675874401792</v>
+        <v>0.02942479748934099</v>
       </c>
       <c r="K175" t="n">
-        <v>0.6937972291130586</v>
+        <v>0.7404289887812161</v>
       </c>
       <c r="L175" t="b">
         <v>0</v>
@@ -7123,22 +7123,22 @@
         <v>237</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4613255728523793</v>
+        <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>7.74347092062155</v>
+        <v>6.802079020417213</v>
       </c>
       <c r="H176" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I176" t="n">
-        <v>31.54836343024143</v>
+        <v>31.73155585338033</v>
       </c>
       <c r="J176" t="n">
-        <v>0.08775208452231183</v>
+        <v>0.07772243624429306</v>
       </c>
       <c r="K176" t="n">
-        <v>1.488908889273543</v>
+        <v>1.409646478825002</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
@@ -7161,22 +7161,22 @@
         <v>389</v>
       </c>
       <c r="F177" t="n">
-        <v>0.7211627776874531</v>
+        <v>0.5945510388345008</v>
       </c>
       <c r="G177" t="n">
-        <v>21.66380335575148</v>
+        <v>20.98729714192518</v>
       </c>
       <c r="H177" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I177" t="n">
-        <v>49.46802954117463</v>
+        <v>49.82690989904415</v>
       </c>
       <c r="J177" t="n">
-        <v>0.06489053493473027</v>
+        <v>0.06160440936067566</v>
       </c>
       <c r="K177" t="n">
-        <v>1.169918890638937</v>
+        <v>1.186313293734111</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
@@ -7205,16 +7205,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H178" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I178" t="n">
-        <v>16.36853542214117</v>
+        <v>16.45445506024886</v>
       </c>
       <c r="J178" t="n">
-        <v>0.03181047408823484</v>
+        <v>0.02821692574375623</v>
       </c>
       <c r="K178" t="n">
-        <v>0.7083487541164217</v>
+        <v>0.7236925826397842</v>
       </c>
       <c r="L178" t="b">
         <v>0</v>
@@ -7237,22 +7237,22 @@
         <v>266</v>
       </c>
       <c r="F179" t="n">
-        <v>0.002815287961406337</v>
+        <v>0.008371382705123311</v>
       </c>
       <c r="G179" t="n">
-        <v>3.332912705901808</v>
+        <v>3.338463411481388</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I179" t="n">
-        <v>22.41821534977743</v>
+        <v>22.7823621997474</v>
       </c>
       <c r="J179" t="n">
-        <v>0.06211832247304657</v>
+        <v>0.0574877103667597</v>
       </c>
       <c r="K179" t="n">
-        <v>1.131237870965289</v>
+        <v>1.129271851564399</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
@@ -7275,22 +7275,22 @@
         <v>137</v>
       </c>
       <c r="F180" t="n">
-        <v>0.01489622401923269</v>
+        <v>0.3516446462069153</v>
       </c>
       <c r="G180" t="n">
-        <v>12.39505237443052</v>
+        <v>13.64168563494195</v>
       </c>
       <c r="H180" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I180" t="n">
-        <v>65.91198051634814</v>
+        <v>66.2777116565302</v>
       </c>
       <c r="J180" t="n">
-        <v>0.05043180377384307</v>
+        <v>0.04532750327872063</v>
       </c>
       <c r="K180" t="n">
-        <v>0.968174445644058</v>
+        <v>0.9607786606827691</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
@@ -7313,22 +7313,22 @@
         <v>400</v>
       </c>
       <c r="F181" t="n">
-        <v>0.197467775324399</v>
+        <v>0.5556288239258327</v>
       </c>
       <c r="G181" t="n">
-        <v>15.14144945670485</v>
+        <v>16.67738344105229</v>
       </c>
       <c r="H181" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I181" t="n">
-        <v>32.79248051459653</v>
+        <v>33.15658098034373</v>
       </c>
       <c r="J181" t="n">
-        <v>0.02498515995065889</v>
+        <v>0.02297918149052067</v>
       </c>
       <c r="K181" t="n">
-        <v>0.6131143108392794</v>
+        <v>0.6511178118435169</v>
       </c>
       <c r="L181" t="b">
         <v>0</v>
@@ -7351,22 +7351,22 @@
         <v>455</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>0.001087075840509128</v>
       </c>
       <c r="G182" t="n">
-        <v>13.18108918109577</v>
+        <v>13.18538783417588</v>
       </c>
       <c r="H182" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I182" t="n">
-        <v>26.67330524017127</v>
+        <v>27.01901448286991</v>
       </c>
       <c r="J182" t="n">
-        <v>0.07673483952672022</v>
+        <v>0.07451155410039169</v>
       </c>
       <c r="K182" t="n">
-        <v>1.335183921828208</v>
+        <v>1.365156136345313</v>
       </c>
       <c r="L182" t="b">
         <v>0</v>
@@ -7395,16 +7395,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I183" t="n">
-        <v>107.0908447689045</v>
+        <v>106.7438405094656</v>
       </c>
       <c r="J183" t="n">
-        <v>0.04839255197473234</v>
+        <v>0.0431612678002198</v>
       </c>
       <c r="K183" t="n">
-        <v>0.9397205157771471</v>
+        <v>0.930763059358626</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
@@ -7427,22 +7427,22 @@
         <v>547</v>
       </c>
       <c r="F184" t="n">
-        <v>0.1069434049194244</v>
+        <v>0.09983146396290524</v>
       </c>
       <c r="G184" t="n">
-        <v>10.54984294448571</v>
+        <v>10.52803369312884</v>
       </c>
       <c r="H184" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I184" t="n">
-        <v>21.93390490578757</v>
+        <v>22.29996452392944</v>
       </c>
       <c r="J184" t="n">
-        <v>0.073503219610451</v>
+        <v>0.06908479615091929</v>
       </c>
       <c r="K184" t="n">
-        <v>1.290092733729644</v>
+        <v>1.289962370611813</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
@@ -7465,22 +7465,22 @@
         <v>625</v>
       </c>
       <c r="F185" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.1195752910976404</v>
       </c>
       <c r="G185" t="n">
-        <v>8.039315372836008</v>
+        <v>7.522344899098382</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I185" t="n">
-        <v>66.32876973711292</v>
+        <v>66.69415341948341</v>
       </c>
       <c r="J185" t="n">
-        <v>0.01652186388401744</v>
+        <v>0.01022714249078745</v>
       </c>
       <c r="K185" t="n">
-        <v>0.4950249052895912</v>
+        <v>0.4744241317313203</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
@@ -7503,22 +7503,22 @@
         <v>13</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5951892006379289</v>
+        <v>0.5556079804954781</v>
       </c>
       <c r="G186" t="n">
-        <v>13.97511913256855</v>
+        <v>13.83431498492274</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I186" t="n">
-        <v>22.83008308976832</v>
+        <v>22.82928131736363</v>
       </c>
       <c r="J186" t="n">
-        <v>0.07119131539883053</v>
+        <v>0.06650547053256065</v>
       </c>
       <c r="K186" t="n">
-        <v>1.25783445139043</v>
+        <v>1.254222946059788</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
@@ -7541,22 +7541,22 @@
         <v>331</v>
       </c>
       <c r="F187" t="n">
-        <v>0.3208302147582923</v>
+        <v>0.2694800550181519</v>
       </c>
       <c r="G187" t="n">
-        <v>22.69688486159929</v>
+        <v>22.37793672260443</v>
       </c>
       <c r="H187" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I187" t="n">
-        <v>105.8705291305261</v>
+        <v>105.521028736643</v>
       </c>
       <c r="J187" t="n">
-        <v>0.0447686277673402</v>
+        <v>0.03984648460308035</v>
       </c>
       <c r="K187" t="n">
-        <v>0.8891554579039103</v>
+        <v>0.8848330522523982</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
@@ -7579,22 +7579,22 @@
         <v>180</v>
       </c>
       <c r="F188" t="n">
-        <v>0.5951892006379226</v>
+        <v>0.05978764554882575</v>
       </c>
       <c r="G188" t="n">
-        <v>4.799110767933096</v>
+        <v>4.145060461239599</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I188" t="n">
-        <v>108.2010514368915</v>
+        <v>107.8665568292082</v>
       </c>
       <c r="J188" t="n">
-        <v>0.1256277264496282</v>
+        <v>0.1216085690659777</v>
       </c>
       <c r="K188" t="n">
-        <v>2.017392355383052</v>
+        <v>2.017737648740522</v>
       </c>
       <c r="L188" t="b">
         <v>0</v>
@@ -7617,22 +7617,22 @@
         <v>414</v>
       </c>
       <c r="F189" t="n">
-        <v>0.4666504708804904</v>
+        <v>0.4342997459932854</v>
       </c>
       <c r="G189" t="n">
-        <v>23.27468988369172</v>
+        <v>23.0765434893762</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I189" t="n">
-        <v>33.13290255498572</v>
+        <v>33.20798565323336</v>
       </c>
       <c r="J189" t="n">
-        <v>0.06224079665568052</v>
+        <v>0.05780608347844864</v>
       </c>
       <c r="K189" t="n">
-        <v>1.132946768220985</v>
+        <v>1.133683265045355</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
@@ -7655,22 +7655,22 @@
         <v>667</v>
       </c>
       <c r="F190" t="n">
-        <v>0.5951892006378887</v>
+        <v>0.5556079804954797</v>
       </c>
       <c r="G190" t="n">
-        <v>20.66836690608407</v>
+        <v>20.46012597748569</v>
       </c>
       <c r="H190" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I190" t="n">
-        <v>25.45745337313942</v>
+        <v>25.34697150093866</v>
       </c>
       <c r="J190" t="n">
-        <v>0.06011109066764364</v>
+        <v>0.05544440376006007</v>
       </c>
       <c r="K190" t="n">
-        <v>1.103230719988409</v>
+        <v>1.100959566451181</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
@@ -7693,22 +7693,22 @@
         <v>294</v>
       </c>
       <c r="F191" t="n">
-        <v>0.03494634924224297</v>
+        <v>0.2012933958275406</v>
       </c>
       <c r="G191" t="n">
-        <v>14.7397764562814</v>
+        <v>15.46772024714708</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I191" t="n">
-        <v>104.6060825951789</v>
+        <v>104.2644639573409</v>
       </c>
       <c r="J191" t="n">
-        <v>0.0427202265027613</v>
+        <v>0.03793653154841775</v>
       </c>
       <c r="K191" t="n">
-        <v>0.8605738644258334</v>
+        <v>0.8583685288866112</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
@@ -7737,16 +7737,16 @@
         <v>16.38096837796838</v>
       </c>
       <c r="H192" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I192" t="n">
-        <v>104.3876536530662</v>
+        <v>104.0415086516282</v>
       </c>
       <c r="J192" t="n">
-        <v>0.06306765017023516</v>
+        <v>0.05846094361190878</v>
       </c>
       <c r="K192" t="n">
-        <v>1.144483956479741</v>
+        <v>1.142757080373417</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
@@ -7769,22 +7769,22 @@
         <v>476</v>
       </c>
       <c r="F193" t="n">
-        <v>0.5951892006379221</v>
+        <v>0.5769535603667887</v>
       </c>
       <c r="G193" t="n">
-        <v>15.99627651785805</v>
+        <v>15.92202408790893</v>
       </c>
       <c r="H193" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I193" t="n">
-        <v>111.3042436089622</v>
+        <v>110.9705048205496</v>
       </c>
       <c r="J193" t="n">
-        <v>0.03491275956122911</v>
+        <v>0.0312363532280319</v>
       </c>
       <c r="K193" t="n">
-        <v>0.7516353229031743</v>
+        <v>0.7655301079202308</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
@@ -7813,16 +7813,16 @@
         <v>16.15292911517908</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I194" t="n">
-        <v>37.25911266396184</v>
+        <v>37.62500953797321</v>
       </c>
       <c r="J194" t="n">
-        <v>0.1149364972551594</v>
+        <v>0.1084780215516304</v>
       </c>
       <c r="K194" t="n">
-        <v>1.868216326300649</v>
+        <v>1.835799312271616</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
@@ -7851,16 +7851,16 @@
         <v>4.216584043986316</v>
       </c>
       <c r="H195" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I195" t="n">
-        <v>112.2396835746597</v>
+        <v>111.9011360156052</v>
       </c>
       <c r="J195" t="n">
-        <v>0.04364022693902917</v>
+        <v>0.03801765555202913</v>
       </c>
       <c r="K195" t="n">
-        <v>0.8734107430803031</v>
+        <v>0.8594925921633805</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
@@ -7889,16 +7889,16 @@
         <v>6.859</v>
       </c>
       <c r="H196" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I196" t="n">
-        <v>38.18604901577585</v>
+        <v>38.55046460200905</v>
       </c>
       <c r="J196" t="n">
-        <v>0.2008303783503962</v>
+        <v>0.1957335446714338</v>
       </c>
       <c r="K196" t="n">
-        <v>3.066704158821589</v>
+        <v>3.044821609841083</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
@@ -7927,16 +7927,16 @@
         <v>9.010146336214524</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I197" t="n">
-        <v>22.79581057132287</v>
+        <v>22.6893706782187</v>
       </c>
       <c r="J197" t="n">
-        <v>0.04042731089430789</v>
+        <v>0.03729746972925155</v>
       </c>
       <c r="K197" t="n">
-        <v>0.8285805323899715</v>
+        <v>0.8495136167702011</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
@@ -7965,16 +7965,16 @@
         <v>9.292517850399857</v>
       </c>
       <c r="H198" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I198" t="n">
-        <v>66.99692213101615</v>
+        <v>67.36107947788858</v>
       </c>
       <c r="J198" t="n">
-        <v>0.03345944576780337</v>
+        <v>0.02848837157843066</v>
       </c>
       <c r="K198" t="n">
-        <v>0.7313570577223942</v>
+        <v>0.7274537665163985</v>
       </c>
       <c r="L198" t="b">
         <v>0</v>
@@ -7997,22 +7997,22 @@
         <v>509</v>
       </c>
       <c r="F199" t="n">
-        <v>0.1280937719090827</v>
+        <v>0.09510596445829443</v>
       </c>
       <c r="G199" t="n">
-        <v>23.18922454102273</v>
+        <v>22.96822850359822</v>
       </c>
       <c r="H199" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I199" t="n">
-        <v>32.73427114087708</v>
+        <v>33.08061750547459</v>
       </c>
       <c r="J199" t="n">
-        <v>0.03143600944600945</v>
+        <v>0.02601180658989631</v>
       </c>
       <c r="K199" t="n">
-        <v>0.7031238031455973</v>
+        <v>0.6931382047564079</v>
       </c>
       <c r="L199" t="b">
         <v>0</v>
@@ -8035,22 +8035,22 @@
         <v>84</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3568752063885352</v>
+        <v>0.5995449479220395</v>
       </c>
       <c r="G200" t="n">
-        <v>24.07012528439627</v>
+        <v>25.65298734180286</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I200" t="n">
-        <v>61.43524986452373</v>
+        <v>61.79784854718401</v>
       </c>
       <c r="J200" t="n">
-        <v>0.02683394273711947</v>
+        <v>0.02323068401909079</v>
       </c>
       <c r="K200" t="n">
-        <v>0.6389106032677285</v>
+        <v>0.654602659037876</v>
       </c>
       <c r="L200" t="b">
         <v>0</v>
@@ -8079,16 +8079,16 @@
         <v>12.167</v>
       </c>
       <c r="H201" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I201" t="n">
-        <v>26.62056868824821</v>
+        <v>26.9538013662656</v>
       </c>
       <c r="J201" t="n">
-        <v>0.02348755763740584</v>
+        <v>0.02090750052551303</v>
       </c>
       <c r="K201" t="n">
-        <v>0.5922180825223996</v>
+        <v>0.6224123684447598</v>
       </c>
       <c r="L201" t="b">
         <v>0</v>
@@ -8117,16 +8117,16 @@
         <v>5.379074548656115</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I202" t="n">
-        <v>68.8246855576138</v>
+        <v>69.19043935795727</v>
       </c>
       <c r="J202" t="n">
-        <v>0.04484320250466523</v>
+        <v>0.03940829396085267</v>
       </c>
       <c r="K202" t="n">
-        <v>0.8901960083384446</v>
+        <v>0.8787614336533995</v>
       </c>
       <c r="L202" t="b">
         <v>0</v>
@@ -8149,22 +8149,22 @@
         <v>407</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>4.168686077682113e-05</v>
       </c>
       <c r="G203" t="n">
-        <v>8.546030189509043</v>
+        <v>8.546137066660254</v>
       </c>
       <c r="H203" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I203" t="n">
-        <v>112.56327134266</v>
+        <v>112.2314253815471</v>
       </c>
       <c r="J203" t="n">
-        <v>0.06693094091371253</v>
+        <v>0.06412482526245931</v>
       </c>
       <c r="K203" t="n">
-        <v>1.198388924918816</v>
+        <v>1.221236458657679</v>
       </c>
       <c r="L203" t="b">
         <v>0</v>
@@ -8187,22 +8187,22 @@
         <v>632</v>
       </c>
       <c r="F204" t="n">
-        <v>0.8967821537548112</v>
+        <v>0.6586211482970756</v>
       </c>
       <c r="G204" t="n">
-        <v>27.37953277686025</v>
+        <v>25.83802945975136</v>
       </c>
       <c r="H204" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I204" t="n">
-        <v>30.00931073048559</v>
+        <v>30.20027935357011</v>
       </c>
       <c r="J204" t="n">
-        <v>0.1064598380015814</v>
+        <v>0.09863253170504496</v>
       </c>
       <c r="K204" t="n">
-        <v>1.749940462568574</v>
+        <v>1.699379102645779</v>
       </c>
       <c r="L204" t="b">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>475</v>
       </c>
       <c r="F205" t="n">
-        <v>0.2975946003189902</v>
+        <v>0.2778039902477826</v>
       </c>
       <c r="G205" t="n">
-        <v>7.347527294286389</v>
+        <v>7.307479116430511</v>
       </c>
       <c r="H205" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I205" t="n">
-        <v>36.41952856072783</v>
+        <v>36.78300028732573</v>
       </c>
       <c r="J205" t="n">
-        <v>0.0310365066839129</v>
+        <v>0.02472967253166859</v>
       </c>
       <c r="K205" t="n">
-        <v>0.6975494922246558</v>
+        <v>0.6753728116965073</v>
       </c>
       <c r="L205" t="b">
         <v>0</v>
@@ -8263,22 +8263,22 @@
         <v>575</v>
       </c>
       <c r="F206" t="n">
-        <v>0.7021326055572705</v>
+        <v>0.561971388172774</v>
       </c>
       <c r="G206" t="n">
-        <v>24.66738896260627</v>
+        <v>23.81063256345642</v>
       </c>
       <c r="H206" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I206" t="n">
-        <v>181.2901179123892</v>
+        <v>181.5821210559195</v>
       </c>
       <c r="J206" t="n">
-        <v>0.01194338684723754</v>
+        <v>0.00787700053513485</v>
       </c>
       <c r="K206" t="n">
-        <v>0.4311408549930034</v>
+        <v>0.4418603016693969</v>
       </c>
       <c r="L206" t="b">
         <v>0</v>
@@ -8301,22 +8301,22 @@
         <v>75</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>0.0002201270988605955</v>
       </c>
       <c r="G207" t="n">
-        <v>4.660218771688728</v>
+        <v>4.660526523820208</v>
       </c>
       <c r="H207" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I207" t="n">
-        <v>106.7456386579016</v>
+        <v>106.4211411450678</v>
       </c>
       <c r="J207" t="n">
-        <v>0.2041365205869367</v>
+        <v>0.1971455032121993</v>
       </c>
       <c r="K207" t="n">
-        <v>3.112835165973123</v>
+        <v>3.064385865466316</v>
       </c>
       <c r="L207" t="b">
         <v>0</v>
@@ -8339,22 +8339,22 @@
         <v>655</v>
       </c>
       <c r="F208" t="n">
-        <v>0.4045380052383922</v>
+        <v>0.2009888873167598</v>
       </c>
       <c r="G208" t="n">
-        <v>17.3114377096554</v>
+        <v>16.36872792738074</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I208" t="n">
-        <v>84.64680015456598</v>
+        <v>84.90814752653405</v>
       </c>
       <c r="J208" t="n">
-        <v>0.05010414405541489</v>
+        <v>0.04337124486360127</v>
       </c>
       <c r="K208" t="n">
-        <v>0.9636025695018214</v>
+        <v>0.9336725250580957</v>
       </c>
       <c r="L208" t="b">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>383</v>
       </c>
       <c r="F209" t="n">
-        <v>0.595276734759264</v>
+        <v>0.1996629279258353</v>
       </c>
       <c r="G209" t="n">
-        <v>25.82276976552384</v>
+        <v>23.22239862334988</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I209" t="n">
-        <v>23.58098937592436</v>
+        <v>23.710947310279</v>
       </c>
       <c r="J209" t="n">
-        <v>0.02539824640223518</v>
+        <v>0.0206888148224128</v>
       </c>
       <c r="K209" t="n">
-        <v>0.6188781566415723</v>
+        <v>0.6193822348583182</v>
       </c>
       <c r="L209" t="b">
         <v>0</v>
@@ -8415,22 +8415,22 @@
         <v>360</v>
       </c>
       <c r="F210" t="n">
-        <v>0.8334130855072851</v>
+        <v>0.1760692197473361</v>
       </c>
       <c r="G210" t="n">
-        <v>22.11683545946772</v>
+        <v>18.62769437481576</v>
       </c>
       <c r="H210" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I210" t="n">
-        <v>88.62410291821563</v>
+        <v>88.88455251571462</v>
       </c>
       <c r="J210" t="n">
-        <v>0.02298926152426626</v>
+        <v>0.01433061543627181</v>
       </c>
       <c r="K210" t="n">
-        <v>0.5852652958864331</v>
+        <v>0.531282312293161</v>
       </c>
       <c r="L210" t="b">
         <v>0</v>
@@ -8453,22 +8453,22 @@
         <v>360</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>0.1996629279258283</v>
       </c>
       <c r="G211" t="n">
-        <v>12.3745858516558</v>
+        <v>13.11580966455914</v>
       </c>
       <c r="H211" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I211" t="n">
-        <v>111.5333790947743</v>
+        <v>111.2043106350381</v>
       </c>
       <c r="J211" t="n">
-        <v>0.02669758172322314</v>
+        <v>0.01659938995100512</v>
       </c>
       <c r="K211" t="n">
-        <v>0.6370079413562966</v>
+        <v>0.5627187059837213</v>
       </c>
       <c r="L211" t="b">
         <v>0</v>
@@ -8497,16 +8497,16 @@
         <v>9.898089765202174</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I212" t="n">
-        <v>72.72821762777428</v>
+        <v>73.00129866017464</v>
       </c>
       <c r="J212" t="n">
-        <v>0.06481867921080828</v>
+        <v>0.05736449551168305</v>
       </c>
       <c r="K212" t="n">
-        <v>1.168916278931102</v>
+        <v>1.127564572737191</v>
       </c>
       <c r="L212" t="b">
         <v>0</v>
@@ -8529,22 +8529,22 @@
         <v>696</v>
       </c>
       <c r="F213" t="n">
-        <v>0.1793997615363759</v>
+        <v>0.1911401318904522</v>
       </c>
       <c r="G213" t="n">
-        <v>17.18236207699566</v>
+        <v>17.23978952419807</v>
       </c>
       <c r="H213" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I213" t="n">
-        <v>191.5656158165872</v>
+        <v>191.7507383033395</v>
       </c>
       <c r="J213" t="n">
-        <v>0.1087000701567234</v>
+        <v>0.1083213787420934</v>
       </c>
       <c r="K213" t="n">
-        <v>1.781198695934265</v>
+        <v>1.833628851964775</v>
       </c>
       <c r="L213" t="b">
         <v>0</v>
@@ -8573,16 +8573,16 @@
         <v>8.792540929674423</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I214" t="n">
-        <v>102.2422512481748</v>
+        <v>101.9094594036892</v>
       </c>
       <c r="J214" t="n">
-        <v>0.5438297996003815</v>
+        <v>0.5437802316679784</v>
       </c>
       <c r="K214" t="n">
-        <v>7.852617051429585</v>
+        <v>7.867395472543654</v>
       </c>
       <c r="L214" t="b">
         <v>0</v>
@@ -8605,22 +8605,22 @@
         <v>572</v>
       </c>
       <c r="F215" t="n">
-        <v>0</v>
+        <v>0.000440254197721191</v>
       </c>
       <c r="G215" t="n">
-        <v>12.89864333951443</v>
+        <v>12.90034694407697</v>
       </c>
       <c r="H215" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I215" t="n">
-        <v>36.7320094797958</v>
+        <v>37.0885490265103</v>
       </c>
       <c r="J215" t="n">
-        <v>0.175352800573726</v>
+        <v>0.1738629823106587</v>
       </c>
       <c r="K215" t="n">
-        <v>2.711212398778878</v>
+        <v>2.741780649118685</v>
       </c>
       <c r="L215" t="b">
         <v>0</v>
@@ -8649,16 +8649,16 @@
         <v>6.352448897866083</v>
       </c>
       <c r="H216" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I216" t="n">
-        <v>23.66118060948362</v>
+        <v>23.74982453776133</v>
       </c>
       <c r="J216" t="n">
-        <v>0.03921184188513715</v>
+        <v>0.03720480554044111</v>
       </c>
       <c r="K216" t="n">
-        <v>0.8116209445855476</v>
+        <v>0.8482296513952622</v>
       </c>
       <c r="L216" t="b">
         <v>0</v>
@@ -8687,16 +8687,16 @@
         <v>11.92630068378288</v>
       </c>
       <c r="H217" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I217" t="n">
-        <v>63.62420013359195</v>
+        <v>63.9868220257185</v>
       </c>
       <c r="J217" t="n">
-        <v>0.02637026903215837</v>
+        <v>0.02229500574513994</v>
       </c>
       <c r="K217" t="n">
-        <v>0.6324409073293225</v>
+        <v>0.641637796114475</v>
       </c>
       <c r="L217" t="b">
         <v>0</v>
@@ -8719,22 +8719,22 @@
         <v>631</v>
       </c>
       <c r="F218" t="n">
-        <v>0.2975946003190075</v>
+        <v>0.2778039902477988</v>
       </c>
       <c r="G218" t="n">
-        <v>3.676314532822995</v>
+        <v>3.656276540125896</v>
       </c>
       <c r="H218" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I218" t="n">
-        <v>23.1322047890503</v>
+        <v>23.21000309857262</v>
       </c>
       <c r="J218" t="n">
-        <v>0.1102956944533754</v>
+        <v>0.1065852627211665</v>
       </c>
       <c r="K218" t="n">
-        <v>1.803462636979051</v>
+        <v>1.80957303400141</v>
       </c>
       <c r="L218" t="b">
         <v>0</v>
@@ -8763,16 +8763,16 @@
         <v>7.378342564560147</v>
       </c>
       <c r="H219" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I219" t="n">
-        <v>123.1326316327044</v>
+        <v>122.789098308766</v>
       </c>
       <c r="J219" t="n">
-        <v>0.02717202169629166</v>
+        <v>0.02309029087164947</v>
       </c>
       <c r="K219" t="n">
-        <v>0.6436278603509188</v>
+        <v>0.6526573558683625</v>
       </c>
       <c r="L219" t="b">
         <v>0</v>
@@ -8801,16 +8801,16 @@
         <v>9.32407137467319</v>
       </c>
       <c r="H220" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I220" t="n">
-        <v>28.16170469023544</v>
+        <v>28.22820124178438</v>
       </c>
       <c r="J220" t="n">
-        <v>0.08386089611856004</v>
+        <v>0.07798385540057613</v>
       </c>
       <c r="K220" t="n">
-        <v>1.434614661367224</v>
+        <v>1.413268731923228</v>
       </c>
       <c r="L220" t="b">
         <v>0</v>
@@ -8833,22 +8833,22 @@
         <v>605</v>
       </c>
       <c r="F221" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.1030131678015809</v>
       </c>
       <c r="G221" t="n">
-        <v>23.97748856054686</v>
+        <v>22.32799529731945</v>
       </c>
       <c r="H221" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I221" t="n">
-        <v>10.54560760806768</v>
+        <v>10.83404712752934</v>
       </c>
       <c r="J221" t="n">
-        <v>0.04880300256150973</v>
+        <v>0.04547839530843906</v>
       </c>
       <c r="K221" t="n">
-        <v>0.9454475830353881</v>
+        <v>0.9628694375405803</v>
       </c>
       <c r="L221" t="b">
         <v>0</v>
@@ -8877,16 +8877,16 @@
         <v>11.34846355239334</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I222" t="n">
-        <v>21.45770517375902</v>
+        <v>21.56032231405796</v>
       </c>
       <c r="J222" t="n">
-        <v>0.129675242829506</v>
+        <v>0.1155595135206235</v>
       </c>
       <c r="K222" t="n">
-        <v>2.073867846667864</v>
+        <v>1.933921257845381</v>
       </c>
       <c r="L222" t="b">
         <v>0</v>
@@ -8915,16 +8915,16 @@
         <v>2.870959421517483</v>
       </c>
       <c r="H223" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I223" t="n">
-        <v>65.16710788664736</v>
+        <v>65.5332015475182</v>
       </c>
       <c r="J223" t="n">
-        <v>0.03771236793398703</v>
+        <v>0.03306682361612143</v>
       </c>
       <c r="K223" t="n">
-        <v>0.7906986010760845</v>
+        <v>0.7908933105590171</v>
       </c>
       <c r="L223" t="b">
         <v>0</v>
@@ -8953,16 +8953,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H224" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I224" t="n">
-        <v>59.59246457978199</v>
+        <v>59.95725158847284</v>
       </c>
       <c r="J224" t="n">
-        <v>0.06256883412528132</v>
+        <v>0.05707718139434922</v>
       </c>
       <c r="K224" t="n">
-        <v>1.137523915171553</v>
+        <v>1.123583516159418</v>
       </c>
       <c r="L224" t="b">
         <v>0</v>
@@ -8985,22 +8985,22 @@
         <v>414</v>
       </c>
       <c r="F225" t="n">
-        <v>0.7021326055572941</v>
+        <v>0.3342481549315383</v>
       </c>
       <c r="G225" t="n">
-        <v>14.23150256426704</v>
+        <v>12.93411867310881</v>
       </c>
       <c r="H225" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I225" t="n">
-        <v>19.29685327936522</v>
+        <v>19.27755057678108</v>
       </c>
       <c r="J225" t="n">
-        <v>0.04650138621225038</v>
+        <v>0.041951657785348</v>
       </c>
       <c r="K225" t="n">
-        <v>0.9133328484984764</v>
+        <v>0.9140025675633344</v>
       </c>
       <c r="L225" t="b">
         <v>0</v>
@@ -9029,16 +9029,16 @@
         <v>5.617338871743453</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I226" t="n">
-        <v>32.75219164270666</v>
+        <v>33.10322296997024</v>
       </c>
       <c r="J226" t="n">
-        <v>0.08172966261775096</v>
+        <v>0.07245986782915644</v>
       </c>
       <c r="K226" t="n">
-        <v>1.404877299562038</v>
+        <v>1.336727741662094</v>
       </c>
       <c r="L226" t="b">
         <v>0</v>
@@ -9061,22 +9061,22 @@
         <v>258</v>
       </c>
       <c r="F227" t="n">
-        <v>0.5951892006378695</v>
+        <v>0.5556079804954617</v>
       </c>
       <c r="G227" t="n">
-        <v>21.6870095376837</v>
+        <v>21.46850543306963</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I227" t="n">
-        <v>198.5540470285124</v>
+        <v>198.8898071097533</v>
       </c>
       <c r="J227" t="n">
-        <v>0.05244496390246932</v>
+        <v>0.04969941108699671</v>
       </c>
       <c r="K227" t="n">
-        <v>0.9962643152402363</v>
+        <v>1.021356304757706</v>
       </c>
       <c r="L227" t="b">
         <v>0</v>
@@ -9099,22 +9099,22 @@
         <v>590</v>
       </c>
       <c r="F228" t="n">
-        <v>0.5951892006378894</v>
+        <v>0.5556079804954802</v>
       </c>
       <c r="G228" t="n">
-        <v>25.92119316453736</v>
+        <v>25.66002819879582</v>
       </c>
       <c r="H228" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I228" t="n">
-        <v>35.42476242100042</v>
+        <v>35.40116781865143</v>
       </c>
       <c r="J228" t="n">
-        <v>0.2757651752042349</v>
+        <v>0.2691325604650545</v>
       </c>
       <c r="K228" t="n">
-        <v>4.112278548016752</v>
+        <v>4.061846590509618</v>
       </c>
       <c r="L228" t="b">
         <v>0</v>
@@ -9143,16 +9143,16 @@
         <v>7.672279257169932</v>
       </c>
       <c r="H229" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I229" t="n">
-        <v>101.4719820777812</v>
+        <v>101.1327585515637</v>
       </c>
       <c r="J229" t="n">
-        <v>0.04327850465781699</v>
+        <v>0.03850201809182462</v>
       </c>
       <c r="K229" t="n">
-        <v>0.8683635878317955</v>
+        <v>0.8662039737445335</v>
       </c>
       <c r="L229" t="b">
         <v>0</v>
@@ -9175,22 +9175,22 @@
         <v>276</v>
       </c>
       <c r="F230" t="n">
-        <v>0.5951892006378686</v>
+        <v>0.5556288239258491</v>
       </c>
       <c r="G230" t="n">
-        <v>18.99247316276928</v>
+        <v>18.80121820966289</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I230" t="n">
-        <v>31.29618219787185</v>
+        <v>31.27139798662175</v>
       </c>
       <c r="J230" t="n">
-        <v>0.1216474875526688</v>
+        <v>0.1201579126638204</v>
       </c>
       <c r="K230" t="n">
-        <v>1.961855595049177</v>
+        <v>1.997637191215192</v>
       </c>
       <c r="L230" t="b">
         <v>0</v>
@@ -9213,22 +9213,22 @@
         <v>583</v>
       </c>
       <c r="F231" t="n">
-        <v>0.0009621583421231584</v>
+        <v>0.1996629279258459</v>
       </c>
       <c r="G231" t="n">
-        <v>10.48645288791257</v>
+        <v>11.11137238417013</v>
       </c>
       <c r="H231" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I231" t="n">
-        <v>75.235418617203</v>
+        <v>75.60146940259757</v>
       </c>
       <c r="J231" t="n">
-        <v>0.05101741931453972</v>
+        <v>0.04612784292709375</v>
       </c>
       <c r="K231" t="n">
-        <v>0.976345610936751</v>
+        <v>0.9718682564575081</v>
       </c>
       <c r="L231" t="b">
         <v>0</v>
@@ -9251,22 +9251,22 @@
         <v>391</v>
       </c>
       <c r="F232" t="n">
-        <v>0.5951892006378768</v>
+        <v>0.5556079804954686</v>
       </c>
       <c r="G232" t="n">
-        <v>16.76129829700606</v>
+        <v>16.59242243285371</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I232" t="n">
-        <v>122.7916546889391</v>
+        <v>123.1377817201257</v>
       </c>
       <c r="J232" t="n">
-        <v>0.04711683253628815</v>
+        <v>0.03906938619940457</v>
       </c>
       <c r="K232" t="n">
-        <v>0.921920246361092</v>
+        <v>0.8740654897663001</v>
       </c>
       <c r="L232" t="b">
         <v>0</v>
@@ -9295,16 +9295,16 @@
         <v>8.241196029703456</v>
       </c>
       <c r="H233" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I233" t="n">
-        <v>31.33945178415587</v>
+        <v>31.68553701822883</v>
       </c>
       <c r="J233" t="n">
-        <v>0.03291091723652307</v>
+        <v>0.03186880604415999</v>
       </c>
       <c r="K233" t="n">
-        <v>0.7237033720098914</v>
+        <v>0.7742934449505938</v>
       </c>
       <c r="L233" t="b">
         <v>0</v>
@@ -9327,22 +9327,22 @@
         <v>458</v>
       </c>
       <c r="F234" t="n">
-        <v>0.01489622401923269</v>
+        <v>0.2080343106309516</v>
       </c>
       <c r="G234" t="n">
-        <v>13.45411503393831</v>
+        <v>14.23019743515916</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I234" t="n">
-        <v>34.03414409076662</v>
+        <v>34.39374116263873</v>
       </c>
       <c r="J234" t="n">
-        <v>0.02071798449934107</v>
+        <v>0.01605066740040504</v>
       </c>
       <c r="K234" t="n">
-        <v>0.5535738896541426</v>
+        <v>0.5551155448870444</v>
       </c>
       <c r="L234" t="b">
         <v>0</v>
@@ -9365,22 +9365,22 @@
         <v>581</v>
       </c>
       <c r="F235" t="n">
-        <v>0.8927838009568149</v>
+        <v>0.2946108127397306</v>
       </c>
       <c r="G235" t="n">
-        <v>27.51263460382292</v>
+        <v>23.61844181840269</v>
       </c>
       <c r="H235" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I235" t="n">
-        <v>77.74258841302183</v>
+        <v>78.05322860006304</v>
       </c>
       <c r="J235" t="n">
-        <v>0.05192785208938826</v>
+        <v>0.04709687302835378</v>
       </c>
       <c r="K235" t="n">
-        <v>0.9890489908407796</v>
+        <v>0.9852952460342113</v>
       </c>
       <c r="L235" t="b">
         <v>0</v>
@@ -9409,16 +9409,16 @@
         <v>17.42023099732033</v>
       </c>
       <c r="H236" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I236" t="n">
-        <v>69.40718392562836</v>
+        <v>69.77132932094929</v>
       </c>
       <c r="J236" t="n">
-        <v>0.06510344638555284</v>
+        <v>0.06279213725005192</v>
       </c>
       <c r="K236" t="n">
-        <v>1.172889670163177</v>
+        <v>1.20277058434859</v>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -9441,22 +9441,22 @@
         <v>226</v>
       </c>
       <c r="F237" t="n">
-        <v>0</v>
+        <v>0.00221166458414194</v>
       </c>
       <c r="G237" t="n">
-        <v>12.79325302649799</v>
+        <v>12.80174134188839</v>
       </c>
       <c r="H237" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I237" t="n">
-        <v>39.28893102475666</v>
+        <v>39.30955668568047</v>
       </c>
       <c r="J237" t="n">
-        <v>0.0543571848261528</v>
+        <v>0.04854579739402579</v>
       </c>
       <c r="K237" t="n">
-        <v>1.022945767759369</v>
+        <v>1.005371704268081</v>
       </c>
       <c r="L237" t="b">
         <v>0</v>
@@ -9485,16 +9485,16 @@
         <v>7.554245495084205</v>
       </c>
       <c r="H238" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I238" t="n">
-        <v>168.1006583785138</v>
+        <v>168.4572035921299</v>
       </c>
       <c r="J238" t="n">
-        <v>0.03413531561391447</v>
+        <v>0.02946831946086508</v>
       </c>
       <c r="K238" t="n">
-        <v>0.7407875523816565</v>
+        <v>0.7410320340914203</v>
       </c>
       <c r="L238" t="b">
         <v>0</v>
@@ -9517,22 +9517,22 @@
         <v>390</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>0.001104533092629232</v>
       </c>
       <c r="G239" t="n">
-        <v>10.91308792230687</v>
+        <v>10.91670408233276</v>
       </c>
       <c r="H239" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I239" t="n">
-        <v>91.13388517800792</v>
+        <v>91.4456522604136</v>
       </c>
       <c r="J239" t="n">
-        <v>0.1919963081534496</v>
+        <v>0.1860612378168399</v>
       </c>
       <c r="K239" t="n">
-        <v>2.943441296465454</v>
+        <v>2.910801043142034</v>
       </c>
       <c r="L239" t="b">
         <v>0</v>
@@ -9561,16 +9561,16 @@
         <v>5.222154823442138</v>
       </c>
       <c r="H240" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I240" t="n">
-        <v>30.90318264775372</v>
+        <v>31.22897471775214</v>
       </c>
       <c r="J240" t="n">
-        <v>0.05585307743273919</v>
+        <v>0.05034057862950782</v>
       </c>
       <c r="K240" t="n">
-        <v>1.043818140329937</v>
+        <v>1.030240394012542</v>
       </c>
       <c r="L240" t="b">
         <v>0</v>
@@ -9593,22 +9593,22 @@
         <v>283</v>
       </c>
       <c r="F241" t="n">
-        <v>0.0009621583421231584</v>
+        <v>0.3333624497383254</v>
       </c>
       <c r="G241" t="n">
-        <v>10.38809156456165</v>
+        <v>11.42369403942677</v>
       </c>
       <c r="H241" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I241" t="n">
-        <v>29.09565202367103</v>
+        <v>29.02228276037576</v>
       </c>
       <c r="J241" t="n">
-        <v>0.06640835207869075</v>
+        <v>0.06390330604779985</v>
       </c>
       <c r="K241" t="n">
-        <v>1.191097178962076</v>
+        <v>1.21816706361783</v>
       </c>
       <c r="L241" t="b">
         <v>0</v>
@@ -9637,16 +9637,16 @@
         <v>7.203826552603831</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I242" t="n">
-        <v>29.5905633922513</v>
+        <v>29.51495278586153</v>
       </c>
       <c r="J242" t="n">
-        <v>0.03405388914306758</v>
+        <v>0.03400453143894145</v>
       </c>
       <c r="K242" t="n">
-        <v>0.7396513988709436</v>
+        <v>0.8038862951387797</v>
       </c>
       <c r="L242" t="b">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>384</v>
       </c>
       <c r="F243" t="n">
-        <v>0.1283146784034923</v>
+        <v>0.7221791418151987</v>
       </c>
       <c r="G243" t="n">
-        <v>17.36883873738115</v>
+        <v>20.34855708595006</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I243" t="n">
-        <v>82.87840375755239</v>
+        <v>83.18466101719089</v>
       </c>
       <c r="J243" t="n">
-        <v>0.03750467642591655</v>
+        <v>0.03285066209608641</v>
       </c>
       <c r="K243" t="n">
-        <v>0.7878006560517539</v>
+        <v>0.7878981523357376</v>
       </c>
       <c r="L243" t="b">
         <v>0</v>
@@ -9707,22 +9707,22 @@
         <v>10</v>
       </c>
       <c r="F244" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.5639793632006114</v>
       </c>
       <c r="G244" t="n">
-        <v>19.07044886041755</v>
+        <v>20.14073233864142</v>
       </c>
       <c r="H244" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I244" t="n">
-        <v>109.7025190475378</v>
+        <v>109.3659934887598</v>
       </c>
       <c r="J244" t="n">
-        <v>0.1249579991317163</v>
+        <v>0.1285956709610433</v>
       </c>
       <c r="K244" t="n">
-        <v>2.008047568171325</v>
+        <v>2.114551714881935</v>
       </c>
       <c r="L244" t="b">
         <v>0</v>
@@ -9751,16 +9751,16 @@
         <v>11.2138976720853</v>
       </c>
       <c r="H245" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I245" t="n">
-        <v>37.50710237297542</v>
+        <v>37.87119821296901</v>
       </c>
       <c r="J245" t="n">
-        <v>0.1069651103411932</v>
+        <v>0.1008944002622727</v>
       </c>
       <c r="K245" t="n">
-        <v>1.756990589346088</v>
+        <v>1.730719806615943</v>
       </c>
       <c r="L245" t="b">
         <v>0</v>
@@ -9783,22 +9783,22 @@
         <v>338</v>
       </c>
       <c r="F246" t="n">
-        <v>0.2138868098388667</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>22.64911446935715</v>
+        <v>21.28344032340636</v>
       </c>
       <c r="H246" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I246" t="n">
-        <v>107.1809151148391</v>
+        <v>106.8523962655682</v>
       </c>
       <c r="J246" t="n">
-        <v>0.0562390143281821</v>
+        <v>0.05323201081637501</v>
       </c>
       <c r="K246" t="n">
-        <v>1.0492031650536</v>
+        <v>1.070304402121606</v>
       </c>
       <c r="L246" t="b">
         <v>0</v>
@@ -9827,16 +9827,16 @@
         <v>6.547900426854397</v>
       </c>
       <c r="H247" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I247" t="n">
-        <v>80.89865680021674</v>
+        <v>81.20296263863577</v>
       </c>
       <c r="J247" t="n">
-        <v>0.1541675173141192</v>
+        <v>0.1486796900458862</v>
       </c>
       <c r="K247" t="n">
-        <v>2.415611549319109</v>
+        <v>2.392838131949724</v>
       </c>
       <c r="L247" t="b">
         <v>0</v>
@@ -9859,22 +9859,22 @@
         <v>94</v>
       </c>
       <c r="F248" t="n">
-        <v>0.213886809838868</v>
+        <v>0.1996629279258283</v>
       </c>
       <c r="G248" t="n">
-        <v>16.26973446335233</v>
+        <v>16.20449498781296</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I248" t="n">
-        <v>108.6581416320909</v>
+        <v>108.3112490709763</v>
       </c>
       <c r="J248" t="n">
-        <v>0.08618028872765238</v>
+        <v>0.0813322705286305</v>
       </c>
       <c r="K248" t="n">
-        <v>1.466977430232611</v>
+        <v>1.45966474682968</v>
       </c>
       <c r="L248" t="b">
         <v>0</v>
@@ -9903,16 +9903,16 @@
         <v>9.609651814712121</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I249" t="n">
-        <v>19.70704228825455</v>
+        <v>19.69185827617169</v>
       </c>
       <c r="J249" t="n">
-        <v>0.1848023313770253</v>
+        <v>0.1782875998421726</v>
       </c>
       <c r="K249" t="n">
-        <v>2.843062858280516</v>
+        <v>2.803088645020242</v>
       </c>
       <c r="L249" t="b">
         <v>0</v>
@@ -9935,22 +9935,22 @@
         <v>387</v>
       </c>
       <c r="F250" t="n">
-        <v>0.6592360865924102</v>
+        <v>0.7152270900071567</v>
       </c>
       <c r="G250" t="n">
-        <v>26.59588018216066</v>
+        <v>26.96885554250523</v>
       </c>
       <c r="H250" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I250" t="n">
-        <v>15.72586358695627</v>
+        <v>15.69454559756121</v>
       </c>
       <c r="J250" t="n">
-        <v>0.03034082125402233</v>
+        <v>0.02577403323993261</v>
       </c>
       <c r="K250" t="n">
-        <v>0.6878425083003704</v>
+        <v>0.6898435905979527</v>
       </c>
       <c r="L250" t="b">
         <v>0</v>
@@ -9979,16 +9979,16 @@
         <v>10.94637643240904</v>
       </c>
       <c r="H251" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I251" t="n">
-        <v>32.12273484698847</v>
+        <v>32.14224867246167</v>
       </c>
       <c r="J251" t="n">
-        <v>0.07012747956567604</v>
+        <v>0.06648830961779398</v>
       </c>
       <c r="K251" t="n">
-        <v>1.242990619844132</v>
+        <v>1.253985162503426</v>
       </c>
       <c r="L251" t="b">
         <v>0</v>
@@ -10011,22 +10011,22 @@
         <v>466</v>
       </c>
       <c r="F252" t="n">
-        <v>0.2138868098388869</v>
+        <v>0.0715227090007348</v>
       </c>
       <c r="G252" t="n">
-        <v>14.82611082910238</v>
+        <v>14.23107983245711</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I252" t="n">
-        <v>25.98981150047861</v>
+        <v>25.92265632619799</v>
       </c>
       <c r="J252" t="n">
-        <v>0.01983519917212461</v>
+        <v>0.01568062378433104</v>
       </c>
       <c r="K252" t="n">
-        <v>0.5412562779697451</v>
+        <v>0.549988179112245</v>
       </c>
       <c r="L252" t="b">
         <v>0</v>
@@ -10055,16 +10055,16 @@
         <v>3.929153725676816</v>
       </c>
       <c r="H253" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I253" t="n">
-        <v>37.42203608768811</v>
+        <v>37.78423556568735</v>
       </c>
       <c r="J253" t="n">
-        <v>0.04469525637236679</v>
+        <v>0.04090034354176771</v>
       </c>
       <c r="K253" t="n">
-        <v>0.8881316978524436</v>
+        <v>0.8994354396980214</v>
       </c>
       <c r="L253" t="b">
         <v>0</v>
@@ -10093,16 +10093,16 @@
         <v>4.964088133786507</v>
       </c>
       <c r="H254" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I254" t="n">
-        <v>36.75496687846424</v>
+        <v>36.39186742144362</v>
       </c>
       <c r="J254" t="n">
-        <v>0.06225462350267034</v>
+        <v>0.05884027727865989</v>
       </c>
       <c r="K254" t="n">
-        <v>1.133139695908826</v>
+        <v>1.148013170130523</v>
       </c>
       <c r="L254" t="b">
         <v>0</v>
@@ -10131,16 +10131,16 @@
         <v>6.022017186956544</v>
       </c>
       <c r="H255" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I255" t="n">
-        <v>103.6859494942262</v>
+        <v>103.342045118843</v>
       </c>
       <c r="J255" t="n">
-        <v>0.04094310252005835</v>
+        <v>0.03699097291564366</v>
       </c>
       <c r="K255" t="n">
-        <v>0.835777436054072</v>
+        <v>0.84526676260514</v>
       </c>
       <c r="L255" t="b">
         <v>0</v>
@@ -10163,22 +10163,22 @@
         <v>98</v>
       </c>
       <c r="F256" t="n">
-        <v>0.1280937719090827</v>
+        <v>0.0002201270988607931</v>
       </c>
       <c r="G256" t="n">
-        <v>4.607041147283625</v>
+        <v>4.436845697435327</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I256" t="n">
-        <v>113.3566710358595</v>
+        <v>113.009966218039</v>
       </c>
       <c r="J256" t="n">
-        <v>0.03102087414622694</v>
+        <v>0.03050015663176892</v>
       </c>
       <c r="K256" t="n">
-        <v>0.6973313695135948</v>
+        <v>0.7553292854570546</v>
       </c>
       <c r="L256" t="b">
         <v>0</v>
@@ -10207,16 +10207,16 @@
         <v>7.970018757819834</v>
       </c>
       <c r="H257" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I257" t="n">
-        <v>53.82295764512868</v>
+        <v>54.18678303121391</v>
       </c>
       <c r="J257" t="n">
-        <v>0.04599134765031042</v>
+        <v>0.03826023798304883</v>
       </c>
       <c r="K257" t="n">
-        <v>0.9062162180376434</v>
+        <v>0.8628538414873772</v>
       </c>
       <c r="L257" t="b">
         <v>0</v>
@@ -10239,22 +10239,22 @@
         <v>609</v>
       </c>
       <c r="F258" t="n">
-        <v>0.1280937719090599</v>
+        <v>0.1195752910976302</v>
       </c>
       <c r="G258" t="n">
-        <v>21.28625063441045</v>
+        <v>21.23386573302054</v>
       </c>
       <c r="H258" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I258" t="n">
-        <v>117.8226273556703</v>
+        <v>117.4921884760412</v>
       </c>
       <c r="J258" t="n">
-        <v>0.06531691350390043</v>
+        <v>0.06346105346854732</v>
       </c>
       <c r="K258" t="n">
-        <v>1.175868202984383</v>
+        <v>1.212039162364636</v>
       </c>
       <c r="L258" t="b">
         <v>0</v>
@@ -10283,16 +10283,16 @@
         <v>8.150467777986734</v>
       </c>
       <c r="H259" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I259" t="n">
-        <v>38.21399982058071</v>
+        <v>38.55580674511089</v>
       </c>
       <c r="J259" t="n">
-        <v>0.05627874788898988</v>
+        <v>0.04932139491511824</v>
       </c>
       <c r="K259" t="n">
-        <v>1.049757572289175</v>
+        <v>1.016118470357064</v>
       </c>
       <c r="L259" t="b">
         <v>0</v>
@@ -10321,16 +10321,16 @@
         <v>5.170193323271385</v>
       </c>
       <c r="H260" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I260" t="n">
-        <v>104.4289152865013</v>
+        <v>104.1011678217864</v>
       </c>
       <c r="J260" t="n">
-        <v>0.06248807626433864</v>
+        <v>0.05915999044825661</v>
       </c>
       <c r="K260" t="n">
-        <v>1.136397090856642</v>
+        <v>1.152443151603883</v>
       </c>
       <c r="L260" t="b">
         <v>0</v>
@@ -10353,22 +10353,22 @@
         <v>456</v>
       </c>
       <c r="F261" t="n">
-        <v>0.77362680383212</v>
+        <v>0.5567138127875345</v>
       </c>
       <c r="G261" t="n">
-        <v>25.61087612299238</v>
+        <v>24.25821343390555</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I261" t="n">
-        <v>22.06211102029395</v>
+        <v>22.02077503751684</v>
       </c>
       <c r="J261" t="n">
-        <v>0.03787835940829505</v>
+        <v>0.03058244464010039</v>
       </c>
       <c r="K261" t="n">
-        <v>0.7930147004270941</v>
+        <v>0.7564694773135486</v>
       </c>
       <c r="L261" t="b">
         <v>0</v>
@@ -10391,22 +10391,22 @@
         <v>550</v>
       </c>
       <c r="F262" t="n">
-        <v>0.616364595946658</v>
+        <v>0.6763099473155368</v>
       </c>
       <c r="G262" t="n">
-        <v>23.6592982222464</v>
+        <v>24.01838009900455</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I262" t="n">
-        <v>157.2733832363579</v>
+        <v>157.6264598993876</v>
       </c>
       <c r="J262" t="n">
-        <v>0.03508224269586363</v>
+        <v>0.02865654177421886</v>
       </c>
       <c r="K262" t="n">
-        <v>0.7540001418179437</v>
+        <v>0.7297839515777543</v>
       </c>
       <c r="L262" t="b">
         <v>0</v>
@@ -10435,16 +10435,16 @@
         <v>3.976587858956469</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I263" t="n">
-        <v>35.89327265622588</v>
+        <v>35.89665906257355</v>
       </c>
       <c r="J263" t="n">
-        <v>0.0971587323445857</v>
+        <v>0.08859944201941712</v>
       </c>
       <c r="K263" t="n">
-        <v>1.62016099729396</v>
+        <v>1.560359488646293</v>
       </c>
       <c r="L263" t="b">
         <v>0</v>
@@ -10467,22 +10467,22 @@
         <v>136</v>
       </c>
       <c r="F264" t="n">
-        <v>0.5951892006378579</v>
+        <v>0.4997134839591869</v>
       </c>
       <c r="G264" t="n">
-        <v>24.15868158956481</v>
+        <v>23.57154802501736</v>
       </c>
       <c r="H264" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I264" t="n">
-        <v>121.9086207852389</v>
+        <v>121.5656500640314</v>
       </c>
       <c r="J264" t="n">
-        <v>0.02376599781947106</v>
+        <v>0.01892704754638402</v>
       </c>
       <c r="K264" t="n">
-        <v>0.5961031924514768</v>
+        <v>0.5949709902323194</v>
       </c>
       <c r="L264" t="b">
         <v>0</v>
@@ -10505,22 +10505,22 @@
         <v>1</v>
       </c>
       <c r="F265" t="n">
-        <v>0.06686217391594833</v>
+        <v>0.3333624497383244</v>
       </c>
       <c r="G265" t="n">
-        <v>13.62660716970657</v>
+        <v>14.69463239399368</v>
       </c>
       <c r="H265" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I265" t="n">
-        <v>19.30466492675331</v>
+        <v>19.39807656504409</v>
       </c>
       <c r="J265" t="n">
-        <v>0.04273664096578794</v>
+        <v>0.03086256071279006</v>
       </c>
       <c r="K265" t="n">
-        <v>0.8608028974368459</v>
+        <v>0.7603507969788311</v>
       </c>
       <c r="L265" t="b">
         <v>0</v>
@@ -10549,16 +10549,16 @@
         <v>14.14926234826395</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I266" t="n">
-        <v>76.52912530227201</v>
+        <v>76.83159647340524</v>
       </c>
       <c r="J266" t="n">
-        <v>0.05560764775778137</v>
+        <v>0.05360873369188705</v>
       </c>
       <c r="K266" t="n">
-        <v>1.04039363004555</v>
+        <v>1.075524316462996</v>
       </c>
       <c r="L266" t="b">
         <v>0</v>
@@ -10587,16 +10587,16 @@
         <v>8.607438643406063</v>
       </c>
       <c r="H267" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I267" t="n">
-        <v>67.17964067390784</v>
+        <v>67.53905442013119</v>
       </c>
       <c r="J267" t="n">
-        <v>0.101614393263648</v>
+        <v>0.1089859808805799</v>
       </c>
       <c r="K267" t="n">
-        <v>1.682331379272793</v>
+        <v>1.842837653605208</v>
       </c>
       <c r="L267" t="b">
         <v>0</v>
@@ -10619,22 +10619,22 @@
         <v>139</v>
       </c>
       <c r="F268" t="n">
-        <v>0.6026373126474955</v>
+        <v>0.2080343106309692</v>
       </c>
       <c r="G268" t="n">
-        <v>25.08223032086358</v>
+        <v>22.56759688679835</v>
       </c>
       <c r="H268" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I268" t="n">
-        <v>108.871104867552</v>
+        <v>108.5232355439619</v>
       </c>
       <c r="J268" t="n">
-        <v>0.04080637078755128</v>
+        <v>0.02971484563791155</v>
       </c>
       <c r="K268" t="n">
-        <v>0.8338696014605049</v>
+        <v>0.74444792840191</v>
       </c>
       <c r="L268" t="b">
         <v>0</v>
@@ -10657,22 +10657,22 @@
         <v>99</v>
       </c>
       <c r="F269" t="n">
-        <v>0.5951892006378695</v>
+        <v>0.5893156726907743</v>
       </c>
       <c r="G269" t="n">
-        <v>18.15041154955398</v>
+        <v>18.12327489739895</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I269" t="n">
-        <v>32.16580183945761</v>
+        <v>32.51862200158574</v>
       </c>
       <c r="J269" t="n">
-        <v>0.07319660577874641</v>
+        <v>0.05674140151116017</v>
       </c>
       <c r="K269" t="n">
-        <v>1.285814513419945</v>
+        <v>1.118930912503676</v>
       </c>
       <c r="L269" t="b">
         <v>0</v>
@@ -10701,16 +10701,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H270" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I270" t="n">
-        <v>64.99243890703715</v>
+        <v>65.35294828455255</v>
       </c>
       <c r="J270" t="n">
-        <v>0.01921404503805324</v>
+        <v>0.01482071490558914</v>
       </c>
       <c r="K270" t="n">
-        <v>0.5325892383353478</v>
+        <v>0.5380731854120815</v>
       </c>
       <c r="L270" t="b">
         <v>0</v>
@@ -10739,16 +10739,16 @@
         <v>17.03283675727564</v>
       </c>
       <c r="H271" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I271" t="n">
-        <v>87.75847577800965</v>
+        <v>88.05861173312994</v>
       </c>
       <c r="J271" t="n">
-        <v>0.01588184017901685</v>
+        <v>0.0155626138651398</v>
       </c>
       <c r="K271" t="n">
-        <v>0.4860945762232206</v>
+        <v>0.5483530204594147</v>
       </c>
       <c r="L271" t="b">
         <v>0</v>
@@ -10777,16 +10777,16 @@
         <v>5.940332650618145</v>
       </c>
       <c r="H272" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I272" t="n">
-        <v>36.43485590217651</v>
+        <v>36.79218799525311</v>
       </c>
       <c r="J272" t="n">
-        <v>0.05941412310869225</v>
+        <v>0.06025196671695134</v>
       </c>
       <c r="K272" t="n">
-        <v>1.093505846360463</v>
+        <v>1.167573697041745</v>
       </c>
       <c r="L272" t="b">
         <v>0</v>
@@ -10809,22 +10809,22 @@
         <v>39</v>
       </c>
       <c r="F273" t="n">
-        <v>0.9118139730869906</v>
+        <v>0.7438695434561791</v>
       </c>
       <c r="G273" t="n">
-        <v>25.94909767465867</v>
+        <v>24.92251223631269</v>
       </c>
       <c r="H273" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I273" t="n">
-        <v>165.1136951119933</v>
+        <v>165.479798986277</v>
       </c>
       <c r="J273" t="n">
-        <v>0.04146505421591763</v>
+        <v>0.03632697870334912</v>
       </c>
       <c r="K273" t="n">
-        <v>0.84306029193012</v>
+        <v>0.8360663844580862</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
@@ -10847,22 +10847,22 @@
         <v>330</v>
       </c>
       <c r="F274" t="n">
-        <v>0.7661794915118137</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>22.33935219729172</v>
+        <v>18.16423328962717</v>
       </c>
       <c r="H274" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I274" t="n">
-        <v>67.57912623523882</v>
+        <v>67.9382603354593</v>
       </c>
       <c r="J274" t="n">
-        <v>0.2698756124593771</v>
+        <v>0.2619492663876723</v>
       </c>
       <c r="K274" t="n">
-        <v>4.030100758416648</v>
+        <v>3.962314063524141</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
@@ -10891,16 +10891,16 @@
         <v>20.82782016918717</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I275" t="n">
-        <v>105.580600554595</v>
+        <v>105.2312555390271</v>
       </c>
       <c r="J275" t="n">
-        <v>0.07037904282112063</v>
+        <v>0.0544906833528224</v>
       </c>
       <c r="K275" t="n">
-        <v>1.246500712727529</v>
+        <v>1.087744709708942</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
@@ -10923,22 +10923,22 @@
         <v>170</v>
       </c>
       <c r="F276" t="n">
-        <v>0.2957404881141228</v>
+        <v>0.2778039902477902</v>
       </c>
       <c r="G276" t="n">
-        <v>8.74245924090949</v>
+        <v>8.699250116698693</v>
       </c>
       <c r="H276" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I276" t="n">
-        <v>109.9466087803887</v>
+        <v>109.6056483141055</v>
       </c>
       <c r="J276" t="n">
-        <v>0.06939984957788799</v>
+        <v>0.06104423095218368</v>
       </c>
       <c r="K276" t="n">
-        <v>1.232837909594907</v>
+        <v>1.178551398987874</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>352</v>
       </c>
       <c r="F277" t="n">
-        <v>0.2493457169276791</v>
+        <v>0.260499616332828</v>
       </c>
       <c r="G277" t="n">
-        <v>3.270830968314787</v>
+        <v>3.281013995898341</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I277" t="n">
-        <v>17.54820087315366</v>
+        <v>17.90836118415923</v>
       </c>
       <c r="J277" t="n">
-        <v>0.0918239839906527</v>
+        <v>0.08692972124274952</v>
       </c>
       <c r="K277" t="n">
-        <v>1.545724600775089</v>
+        <v>1.537223650621067</v>
       </c>
       <c r="L277" t="b">
         <v>0</v>
@@ -10999,22 +10999,22 @@
         <v>429</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>0.5192209235756093</v>
       </c>
       <c r="G278" t="n">
-        <v>10.648</v>
+        <v>12.30659931826993</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I278" t="n">
-        <v>23.48699508612173</v>
+        <v>23.48542429853708</v>
       </c>
       <c r="J278" t="n">
-        <v>0.07571106376810288</v>
+        <v>0.06796053565396191</v>
       </c>
       <c r="K278" t="n">
-        <v>1.320899053403503</v>
+        <v>1.274384491292567</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
@@ -11037,22 +11037,22 @@
         <v>537</v>
       </c>
       <c r="F279" t="n">
-        <v>0.01026339997102189</v>
+        <v>0.02245141216336351</v>
       </c>
       <c r="G279" t="n">
-        <v>15.41054008973328</v>
+        <v>15.4667142834192</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I279" t="n">
-        <v>27.57243351437813</v>
+        <v>27.74575182460348</v>
       </c>
       <c r="J279" t="n">
-        <v>0.05544735628235414</v>
+        <v>0.0502661135847207</v>
       </c>
       <c r="K279" t="n">
-        <v>1.038157063476351</v>
+        <v>1.029208598014786</v>
       </c>
       <c r="L279" t="b">
         <v>0</v>
@@ -11081,16 +11081,16 @@
         <v>9.387285283829399</v>
       </c>
       <c r="H280" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I280" t="n">
-        <v>64.96975879538874</v>
+        <v>65.33383073074842</v>
       </c>
       <c r="J280" t="n">
-        <v>0.01278257604134545</v>
+        <v>0.006269192729047403</v>
       </c>
       <c r="K280" t="n">
-        <v>0.4428501644979054</v>
+        <v>0.4195823366963717</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
@@ -11113,22 +11113,22 @@
         <v>544</v>
       </c>
       <c r="F281" t="n">
-        <v>0.1280937719090704</v>
+        <v>0.11957529109764</v>
       </c>
       <c r="G281" t="n">
-        <v>14.24322640861692</v>
+        <v>14.20817420408807</v>
       </c>
       <c r="H281" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I281" t="n">
-        <v>104.6049766457641</v>
+        <v>104.2678716967407</v>
       </c>
       <c r="J281" t="n">
-        <v>0.06856049990274385</v>
+        <v>0.05969027312944552</v>
       </c>
       <c r="K281" t="n">
-        <v>1.221126360878471</v>
+        <v>1.159790807805451</v>
       </c>
       <c r="L281" t="b">
         <v>0</v>
@@ -11151,22 +11151,22 @@
         <v>2</v>
       </c>
       <c r="F282" t="n">
-        <v>0.6142193727680187</v>
+        <v>0.5556079804954597</v>
       </c>
       <c r="G282" t="n">
-        <v>15.48419623650953</v>
+        <v>15.25429422703398</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I282" t="n">
-        <v>35.83015251778446</v>
+        <v>36.19135607862867</v>
       </c>
       <c r="J282" t="n">
-        <v>0.08880919564033243</v>
+        <v>0.08131368602426263</v>
       </c>
       <c r="K282" t="n">
-        <v>1.503658890046772</v>
+        <v>1.459407237856417</v>
       </c>
       <c r="L282" t="b">
         <v>0</v>
@@ -11195,16 +11195,16 @@
         <v>12.89864333951443</v>
       </c>
       <c r="H283" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I283" t="n">
-        <v>119.9264170939405</v>
+        <v>119.5852073126348</v>
       </c>
       <c r="J283" t="n">
-        <v>0.03942149004406699</v>
+        <v>0.03173675390030887</v>
       </c>
       <c r="K283" t="n">
-        <v>0.8145461909987262</v>
+        <v>0.7724637156606937</v>
       </c>
       <c r="L283" t="b">
         <v>0</v>
@@ -11227,22 +11227,22 @@
         <v>377</v>
       </c>
       <c r="F284" t="n">
-        <v>0.1759445647387021</v>
+        <v>0.1665711613197325</v>
       </c>
       <c r="G284" t="n">
-        <v>4.959050098320499</v>
+        <v>4.945804302890054</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I284" t="n">
-        <v>29.37053762411161</v>
+        <v>29.69148311353445</v>
       </c>
       <c r="J284" t="n">
-        <v>0.07871214314105981</v>
+        <v>0.0711364547114766</v>
       </c>
       <c r="K284" t="n">
-        <v>1.362773481093299</v>
+        <v>1.318390381332777</v>
       </c>
       <c r="L284" t="b">
         <v>0</v>
@@ -11271,16 +11271,16 @@
         <v>8.916669781930919</v>
       </c>
       <c r="H285" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I285" t="n">
-        <v>20.67780935287059</v>
+        <v>21.04391167104258</v>
       </c>
       <c r="J285" t="n">
-        <v>0.05682554923635216</v>
+        <v>0.04979902731015715</v>
       </c>
       <c r="K285" t="n">
-        <v>1.057387158393139</v>
+        <v>1.022736598298955</v>
       </c>
       <c r="L285" t="b">
         <v>0</v>
@@ -11309,16 +11309,16 @@
         <v>6.380249524901044</v>
       </c>
       <c r="H286" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I286" t="n">
-        <v>109.3909229698417</v>
+        <v>109.0493962188312</v>
       </c>
       <c r="J286" t="n">
-        <v>0.05698279651525851</v>
+        <v>0.05021466087415751</v>
       </c>
       <c r="K286" t="n">
-        <v>1.059581248915808</v>
+        <v>1.028495663496522</v>
       </c>
       <c r="L286" t="b">
         <v>0</v>
@@ -11341,22 +11341,22 @@
         <v>191</v>
       </c>
       <c r="F287" t="n">
-        <v>0.04550845626989476</v>
+        <v>0.4329737866023448</v>
       </c>
       <c r="G287" t="n">
-        <v>15.57298352905376</v>
+        <v>17.3587999664831</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I287" t="n">
-        <v>118.6568805104413</v>
+        <v>118.3322402595562</v>
       </c>
       <c r="J287" t="n">
-        <v>0.07418057453598051</v>
+        <v>0.06732511436370536</v>
       </c>
       <c r="K287" t="n">
-        <v>1.29954394988374</v>
+        <v>1.265580022752327</v>
       </c>
       <c r="L287" t="b">
         <v>0</v>
@@ -11385,16 +11385,16 @@
         <v>4.313887457966422</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I288" t="n">
-        <v>16.70312070433718</v>
+        <v>17.06361198525787</v>
       </c>
       <c r="J288" t="n">
-        <v>0.06600335300352803</v>
+        <v>0.05931554970815239</v>
       </c>
       <c r="K288" t="n">
-        <v>1.185446177312417</v>
+        <v>1.154598598125579</v>
       </c>
       <c r="L288" t="b">
         <v>0</v>
@@ -11417,22 +11417,22 @@
         <v>372</v>
       </c>
       <c r="F289" t="n">
-        <v>0.1280937719090713</v>
+        <v>0.01155308654378118</v>
       </c>
       <c r="G289" t="n">
-        <v>19.52115750681015</v>
+        <v>18.86391151959237</v>
       </c>
       <c r="H289" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I289" t="n">
-        <v>25.73255828216863</v>
+        <v>25.87944471852555</v>
       </c>
       <c r="J289" t="n">
-        <v>0.06923647514180371</v>
+        <v>0.06259142532558874</v>
       </c>
       <c r="K289" t="n">
-        <v>1.230558326098443</v>
+        <v>1.199989497451307</v>
       </c>
       <c r="L289" t="b">
         <v>0</v>
@@ -11461,16 +11461,16 @@
         <v>5.832000000000001</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I290" t="n">
-        <v>84.84784354193106</v>
+        <v>85.15345168414174</v>
       </c>
       <c r="J290" t="n">
-        <v>0.05500546302009557</v>
+        <v>0.05048501527324719</v>
       </c>
       <c r="K290" t="n">
-        <v>1.031991272719933</v>
+        <v>1.032241724319475</v>
       </c>
       <c r="L290" t="b">
         <v>0</v>
@@ -11493,22 +11493,22 @@
         <v>21</v>
       </c>
       <c r="F291" t="n">
-        <v>0.9327684619013404</v>
+        <v>0.8723550290822299</v>
       </c>
       <c r="G291" t="n">
-        <v>28.79651625992683</v>
+        <v>28.38872092732676</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I291" t="n">
-        <v>77.92735927414485</v>
+        <v>78.23051673795405</v>
       </c>
       <c r="J291" t="n">
-        <v>0.2028350967431129</v>
+        <v>0.1965988309738812</v>
       </c>
       <c r="K291" t="n">
-        <v>3.094676239843728</v>
+        <v>3.056811113726173</v>
       </c>
       <c r="L291" t="b">
         <v>0</v>
@@ -11531,22 +11531,22 @@
         <v>556</v>
       </c>
       <c r="F292" t="n">
-        <v>0.5951892006378834</v>
+        <v>0.5913693349958532</v>
       </c>
       <c r="G292" t="n">
-        <v>8.490118482817302</v>
+        <v>8.48186318795547</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I292" t="n">
-        <v>31.04392917087046</v>
+        <v>31.41003171181515</v>
       </c>
       <c r="J292" t="n">
-        <v>0.1848435084485238</v>
+        <v>0.178150317623215</v>
       </c>
       <c r="K292" t="n">
-        <v>2.84363740699738</v>
+        <v>2.801186447224103</v>
       </c>
       <c r="L292" t="b">
         <v>0</v>
@@ -11569,22 +11569,22 @@
         <v>240</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>0.5556079804955215</v>
       </c>
       <c r="G293" t="n">
-        <v>19.03856866993945</v>
+        <v>22.21196287700856</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I293" t="n">
-        <v>105.3158312513815</v>
+        <v>104.9812306898206</v>
       </c>
       <c r="J293" t="n">
-        <v>0.04170940643728721</v>
+        <v>0.03453596938243972</v>
       </c>
       <c r="K293" t="n">
-        <v>0.8464697683727573</v>
+        <v>0.811249958784251</v>
       </c>
       <c r="L293" t="b">
         <v>0</v>
@@ -11607,22 +11607,22 @@
         <v>466</v>
       </c>
       <c r="F294" t="n">
-        <v>0.6547545758186289</v>
+        <v>0.00114751915284794</v>
       </c>
       <c r="G294" t="n">
-        <v>9.643286221670607</v>
+        <v>8.062849664726187</v>
       </c>
       <c r="H294" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I294" t="n">
-        <v>78.18521834202453</v>
+        <v>78.47334446509352</v>
       </c>
       <c r="J294" t="n">
-        <v>0.08480899472864541</v>
+        <v>0.07488949624176468</v>
       </c>
       <c r="K294" t="n">
-        <v>1.447843597278939</v>
+        <v>1.370392944970983</v>
       </c>
       <c r="L294" t="b">
         <v>0</v>
@@ -11645,22 +11645,22 @@
         <v>572</v>
       </c>
       <c r="F295" t="n">
-        <v>0.1280937719090756</v>
+        <v>0.0357613545003674</v>
       </c>
       <c r="G295" t="n">
-        <v>17.01045838608556</v>
+        <v>16.55671006313553</v>
       </c>
       <c r="H295" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I295" t="n">
-        <v>63.74817769250181</v>
+        <v>64.11080580346466</v>
       </c>
       <c r="J295" t="n">
-        <v>0.2112766607422832</v>
+        <v>0.2073186226593192</v>
       </c>
       <c r="K295" t="n">
-        <v>3.212462415196951</v>
+        <v>3.205345747518916</v>
       </c>
       <c r="L295" t="b">
         <v>0</v>
@@ -11689,16 +11689,16 @@
         <v>4.120023422263519</v>
       </c>
       <c r="H296" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I296" t="n">
-        <v>226.0711472404213</v>
+        <v>226.4352634391044</v>
       </c>
       <c r="J296" t="n">
-        <v>0.118454017081057</v>
+        <v>0.1134772162390941</v>
       </c>
       <c r="K296" t="n">
-        <v>1.917296710819717</v>
+        <v>1.905068713576284</v>
       </c>
       <c r="L296" t="b">
         <v>0</v>
@@ -11727,16 +11727,16 @@
         <v>20.58068878827917</v>
       </c>
       <c r="H297" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I297" t="n">
-        <v>222.8042638753087</v>
+        <v>223.1646180257878</v>
       </c>
       <c r="J297" t="n">
-        <v>0.3069900951694882</v>
+        <v>0.3071518363785487</v>
       </c>
       <c r="K297" t="n">
-        <v>4.547963676836382</v>
+        <v>4.588645934245693</v>
       </c>
       <c r="L297" t="b">
         <v>0</v>
@@ -11765,16 +11765,16 @@
         <v>18.87858122317459</v>
       </c>
       <c r="H298" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I298" t="n">
-        <v>76.2527812117013</v>
+        <v>76.61785409348556</v>
       </c>
       <c r="J298" t="n">
-        <v>0.4675406497337666</v>
+        <v>0.4691518786589061</v>
       </c>
       <c r="K298" t="n">
-        <v>6.788145208934453</v>
+        <v>6.833336657779916</v>
       </c>
       <c r="L298" t="b">
         <v>0</v>
@@ -11797,22 +11797,22 @@
         <v>195</v>
       </c>
       <c r="F299" t="n">
-        <v>0.5951892006378724</v>
+        <v>0.1211770438342067</v>
       </c>
       <c r="G299" t="n">
-        <v>9.784221781295532</v>
+        <v>8.603665979695212</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I299" t="n">
-        <v>22.97246480537063</v>
+        <v>23.30190010905856</v>
       </c>
       <c r="J299" t="n">
-        <v>0.07930454160670507</v>
+        <v>0.07284581273767239</v>
       </c>
       <c r="K299" t="n">
-        <v>1.371039289367729</v>
+        <v>1.342075437525294</v>
       </c>
       <c r="L299" t="b">
         <v>0</v>
@@ -11841,16 +11841,16 @@
         <v>5.352813839467986</v>
       </c>
       <c r="H300" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I300" t="n">
-        <v>25.23282686066488</v>
+        <v>25.29591866447656</v>
       </c>
       <c r="J300" t="n">
-        <v>0.05153358503856067</v>
+        <v>0.04081564039787116</v>
       </c>
       <c r="K300" t="n">
-        <v>0.9835477344397927</v>
+        <v>0.8982617834527364</v>
       </c>
       <c r="L300" t="b">
         <v>0</v>
@@ -11879,16 +11879,16 @@
         <v>11.82363560839051</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I301" t="n">
-        <v>108.3476654740087</v>
+        <v>108.5564721704733</v>
       </c>
       <c r="J301" t="n">
-        <v>0.04918326515755557</v>
+        <v>0.04764348055510992</v>
       </c>
       <c r="K301" t="n">
-        <v>0.9507534335652815</v>
+        <v>0.9928691011237062</v>
       </c>
       <c r="L301" t="b">
         <v>0</v>
@@ -11911,22 +11911,22 @@
         <v>189</v>
       </c>
       <c r="F302" t="n">
-        <v>0.3951397009945179</v>
+        <v>0.555607980495504</v>
       </c>
       <c r="G302" t="n">
-        <v>24.13263892265262</v>
+        <v>25.17127404541802</v>
       </c>
       <c r="H302" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I302" t="n">
-        <v>32.3913530405488</v>
+        <v>32.5120263276317</v>
       </c>
       <c r="J302" t="n">
-        <v>0.1021607352561664</v>
+        <v>0.1011169679664066</v>
       </c>
       <c r="K302" t="n">
-        <v>1.689954555942415</v>
+        <v>1.733803729643341</v>
       </c>
       <c r="L302" t="b">
         <v>0</v>
@@ -11955,16 +11955,16 @@
         <v>4.8366988742323</v>
       </c>
       <c r="H303" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I303" t="n">
-        <v>87.68567489980217</v>
+        <v>87.96079640843733</v>
       </c>
       <c r="J303" t="n">
-        <v>0.06213111957168835</v>
+        <v>0.06083816750684155</v>
       </c>
       <c r="K303" t="n">
-        <v>1.131416430448435</v>
+        <v>1.17569616081813</v>
       </c>
       <c r="L303" t="b">
         <v>0</v>
@@ -11993,16 +11993,16 @@
         <v>5.092576558089235</v>
       </c>
       <c r="H304" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I304" t="n">
-        <v>108.1415102488429</v>
+        <v>107.8158011165014</v>
       </c>
       <c r="J304" t="n">
-        <v>0.09674420827715187</v>
+        <v>0.101679807636147</v>
       </c>
       <c r="K304" t="n">
-        <v>1.614377092261706</v>
+        <v>1.741602499123393</v>
       </c>
       <c r="L304" t="b">
         <v>0</v>
@@ -12025,22 +12025,22 @@
         <v>181</v>
       </c>
       <c r="F305" t="n">
-        <v>0.3568752063885191</v>
+        <v>0.3415137053445865</v>
       </c>
       <c r="G305" t="n">
-        <v>19.45773158824538</v>
+        <v>19.37673346554094</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I305" t="n">
-        <v>117.4412337930304</v>
+        <v>117.1003108476595</v>
       </c>
       <c r="J305" t="n">
-        <v>0.1001543474829619</v>
+        <v>0.1079576752164343</v>
       </c>
       <c r="K305" t="n">
-        <v>1.661959181850072</v>
+        <v>1.828589335192608</v>
       </c>
       <c r="L305" t="b">
         <v>0</v>
@@ -12063,22 +12063,22 @@
         <v>418</v>
       </c>
       <c r="F306" t="n">
-        <v>0.9548796949877907</v>
+        <v>0.6180286073545052</v>
       </c>
       <c r="G306" t="n">
-        <v>28.02460568838536</v>
+        <v>25.82319478732235</v>
       </c>
       <c r="H306" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I306" t="n">
-        <v>23.58655590268409</v>
+        <v>23.92977894360567</v>
       </c>
       <c r="J306" t="n">
-        <v>0.1739754044360187</v>
+        <v>0.180073575819808</v>
       </c>
       <c r="K306" t="n">
-        <v>2.691993421937289</v>
+        <v>2.827835328126135</v>
       </c>
       <c r="L306" t="b">
         <v>0</v>
@@ -12101,22 +12101,22 @@
         <v>249</v>
       </c>
       <c r="F307" t="n">
-        <v>0.1069434049194435</v>
+        <v>0.09516891274740057</v>
       </c>
       <c r="G307" t="n">
-        <v>9.17065956800675</v>
+        <v>9.139272599018085</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I307" t="n">
-        <v>106.6560859473089</v>
+        <v>106.3069532779422</v>
       </c>
       <c r="J307" t="n">
-        <v>0.03953180843893027</v>
+        <v>0.03499546266927289</v>
       </c>
       <c r="K307" t="n">
-        <v>0.8160854770603291</v>
+        <v>0.81761674921197</v>
       </c>
       <c r="L307" t="b">
         <v>0</v>
@@ -12145,16 +12145,16 @@
         <v>3.0214779496134</v>
       </c>
       <c r="H308" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I308" t="n">
-        <v>69.91652044153162</v>
+        <v>70.28220645485493</v>
       </c>
       <c r="J308" t="n">
-        <v>0.149528910676004</v>
+        <v>0.1467071045198777</v>
       </c>
       <c r="K308" t="n">
-        <v>2.350888503337894</v>
+        <v>2.365505766048571</v>
       </c>
       <c r="L308" t="b">
         <v>0</v>
@@ -12177,22 +12177,22 @@
         <v>361</v>
       </c>
       <c r="F309" t="n">
-        <v>0.7926569759622206</v>
+        <v>0.5913693349958079</v>
       </c>
       <c r="G309" t="n">
-        <v>24.41370814731515</v>
+        <v>23.22267827282799</v>
       </c>
       <c r="H309" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I309" t="n">
-        <v>144.3714273525547</v>
+        <v>144.7243813146909</v>
       </c>
       <c r="J309" t="n">
-        <v>0.1904504988786427</v>
+        <v>0.1893286922698079</v>
       </c>
       <c r="K309" t="n">
-        <v>2.921872430515621</v>
+        <v>2.956075257870046</v>
       </c>
       <c r="L309" t="b">
         <v>0</v>
@@ -12221,16 +12221,16 @@
         <v>8.454192746797297</v>
       </c>
       <c r="H310" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I310" t="n">
-        <v>33.56888168405879</v>
+        <v>33.71581933347247</v>
       </c>
       <c r="J310" t="n">
-        <v>0.344116664101211</v>
+        <v>0.3411248801319116</v>
       </c>
       <c r="K310" t="n">
-        <v>5.065995235785082</v>
+        <v>5.059380232150517</v>
       </c>
       <c r="L310" t="b">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>519</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>0.0167427654102483</v>
       </c>
       <c r="G311" t="n">
-        <v>9.801628028036975</v>
+        <v>9.850859935650556</v>
       </c>
       <c r="H311" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I311" t="n">
-        <v>116.521434931452</v>
+        <v>116.1987002253622</v>
       </c>
       <c r="J311" t="n">
-        <v>0.06345150869753131</v>
+        <v>0.062078963597188</v>
       </c>
       <c r="K311" t="n">
-        <v>1.149839981478352</v>
+        <v>1.192888770366825</v>
       </c>
       <c r="L311" t="b">
         <v>0</v>
@@ -12297,16 +12297,16 @@
         <v>6.296969191603211</v>
       </c>
       <c r="H312" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I312" t="n">
-        <v>19.21671164859784</v>
+        <v>19.16727144745277</v>
       </c>
       <c r="J312" t="n">
-        <v>0.09812125995937439</v>
+        <v>0.1005404546840603</v>
       </c>
       <c r="K312" t="n">
-        <v>1.63359126287377</v>
+        <v>1.725815497056109</v>
       </c>
       <c r="L312" t="b">
         <v>0</v>
@@ -12335,16 +12335,16 @@
         <v>4.436552715791846</v>
       </c>
       <c r="H313" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I313" t="n">
-        <v>106.9846395378498</v>
+        <v>106.6451010731672</v>
       </c>
       <c r="J313" t="n">
-        <v>0.06275063461857189</v>
+        <v>0.05773688931451138</v>
       </c>
       <c r="K313" t="n">
-        <v>1.140060599698749</v>
+        <v>1.132724502962787</v>
       </c>
       <c r="L313" t="b">
         <v>0</v>
@@ -12373,16 +12373,16 @@
         <v>7.495457757869096</v>
       </c>
       <c r="H314" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I314" t="n">
-        <v>25.27933245754436</v>
+        <v>25.64429454798278</v>
       </c>
       <c r="J314" t="n">
-        <v>0.0699078135047175</v>
+        <v>0.06426630163102193</v>
       </c>
       <c r="K314" t="n">
-        <v>1.239925592418201</v>
+        <v>1.223196771060328</v>
       </c>
       <c r="L314" t="b">
         <v>0</v>
@@ -12411,16 +12411,16 @@
         <v>4.289492277647788</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I315" t="n">
-        <v>24.68228976091389</v>
+        <v>25.04761994277485</v>
       </c>
       <c r="J315" t="n">
-        <v>0.01584318531735677</v>
+        <v>0.0130968379918141</v>
       </c>
       <c r="K315" t="n">
-        <v>0.4855552202088378</v>
+        <v>0.514186953887716</v>
       </c>
       <c r="L315" t="b">
         <v>0</v>
@@ -12443,22 +12443,22 @@
         <v>542</v>
       </c>
       <c r="F316" t="n">
-        <v>0.215811126523114</v>
+        <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>10.60758249427787</v>
+        <v>9.962572308395055</v>
       </c>
       <c r="H316" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I316" t="n">
-        <v>116.040183199774</v>
+        <v>115.7132580605942</v>
       </c>
       <c r="J316" t="n">
-        <v>0.02945005895888352</v>
+        <v>0.02317055492743147</v>
       </c>
       <c r="K316" t="n">
-        <v>0.6754135930065254</v>
+        <v>0.6537695036117273</v>
       </c>
       <c r="L316" t="b">
         <v>0</v>
@@ -12487,16 +12487,16 @@
         <v>8.332258457345164</v>
       </c>
       <c r="H317" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I317" t="n">
-        <v>29.9815002674252</v>
+        <v>30.34737944951276</v>
       </c>
       <c r="J317" t="n">
-        <v>0.06931937799975402</v>
+        <v>0.06185759665358005</v>
       </c>
       <c r="K317" t="n">
-        <v>1.231715079819054</v>
+        <v>1.189821485211713</v>
       </c>
       <c r="L317" t="b">
         <v>0</v>
@@ -12519,22 +12519,22 @@
         <v>538</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>0.2210085077971383</v>
       </c>
       <c r="G318" t="n">
-        <v>9.769544155179402</v>
+        <v>10.41728986785774</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I318" t="n">
-        <v>84.00657879762412</v>
+        <v>84.28929105786695</v>
       </c>
       <c r="J318" t="n">
-        <v>0.03333514302705234</v>
+        <v>0.03077210270048482</v>
       </c>
       <c r="K318" t="n">
-        <v>0.729622646371556</v>
+        <v>0.759097400632554</v>
       </c>
       <c r="L318" t="b">
         <v>0</v>
@@ -12557,22 +12557,22 @@
         <v>62</v>
       </c>
       <c r="F319" t="n">
-        <v>0.5951892006378646</v>
+        <v>0.5556079804954613</v>
       </c>
       <c r="G319" t="n">
-        <v>23.53245434670069</v>
+        <v>23.2953567488294</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I319" t="n">
-        <v>39.23809699938215</v>
+        <v>39.59563978969698</v>
       </c>
       <c r="J319" t="n">
-        <v>0.07140758531934494</v>
+        <v>0.06727810131957619</v>
       </c>
       <c r="K319" t="n">
-        <v>1.260852092053208</v>
+        <v>1.264928604749242</v>
       </c>
       <c r="L319" t="b">
         <v>0</v>
@@ -12601,16 +12601,16 @@
         <v>16.00149602380977</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I320" t="n">
-        <v>77.47204303414661</v>
+        <v>77.76402666918767</v>
       </c>
       <c r="J320" t="n">
-        <v>0.03805076796810314</v>
+        <v>0.03538740799623811</v>
       </c>
       <c r="K320" t="n">
-        <v>0.7954203381572527</v>
+        <v>0.8230475875450172</v>
       </c>
       <c r="L320" t="b">
         <v>0</v>
@@ -12633,22 +12633,22 @@
         <v>282</v>
       </c>
       <c r="F321" t="n">
-        <v>0.4209220923430291</v>
+        <v>0.5769535603667504</v>
       </c>
       <c r="G321" t="n">
-        <v>24.15855878903113</v>
+        <v>25.16261817385862</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I321" t="n">
-        <v>22.89777808116138</v>
+        <v>23.04887397476644</v>
       </c>
       <c r="J321" t="n">
-        <v>0.05303853768316191</v>
+        <v>0.04823233642922739</v>
       </c>
       <c r="K321" t="n">
-        <v>1.004546522829328</v>
+        <v>1.00102835404441</v>
       </c>
       <c r="L321" t="b">
         <v>0</v>
@@ -12671,22 +12671,22 @@
         <v>10</v>
       </c>
       <c r="F322" t="n">
-        <v>0.7736268038321459</v>
+        <v>0.3689036771398159</v>
       </c>
       <c r="G322" t="n">
-        <v>17.88204530505818</v>
+        <v>16.1198472203911</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I322" t="n">
-        <v>229.012104723199</v>
+        <v>229.075474647693</v>
       </c>
       <c r="J322" t="n">
-        <v>0.005130738211116231</v>
+        <v>0.002981317864523067</v>
       </c>
       <c r="K322" t="n">
-        <v>0.3360831350073529</v>
+        <v>0.3740251744595444</v>
       </c>
       <c r="L322" t="b">
         <v>0</v>
@@ -12709,22 +12709,22 @@
         <v>105</v>
       </c>
       <c r="F323" t="n">
-        <v>0.005630575922813203</v>
+        <v>0.4973185634292778</v>
       </c>
       <c r="G323" t="n">
-        <v>13.63155069536023</v>
+        <v>15.63890085251937</v>
       </c>
       <c r="H323" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I323" t="n">
-        <v>227.3406228240788</v>
+        <v>227.6097810791039</v>
       </c>
       <c r="J323" t="n">
-        <v>0.4907647669557456</v>
+        <v>0.481706556524077</v>
       </c>
       <c r="K323" t="n">
-        <v>7.112194158133995</v>
+        <v>7.007295679914854</v>
       </c>
       <c r="L323" t="b">
         <v>0</v>
@@ -12753,16 +12753,16 @@
         <v>11.61919519588168</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I324" t="n">
-        <v>268.3943070793736</v>
+        <v>268.5611034208869</v>
       </c>
       <c r="J324" t="n">
-        <v>0.5419204802923576</v>
+        <v>0.5412726641973885</v>
       </c>
       <c r="K324" t="n">
-        <v>7.825976085508779</v>
+        <v>7.832650336921232</v>
       </c>
       <c r="L324" t="b">
         <v>0</v>
@@ -12791,16 +12791,16 @@
         <v>5.564094176054176</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1715803741141795</v>
+        <v>0.1703073780451764</v>
       </c>
       <c r="I325" t="n">
-        <v>268.9970524603122</v>
+        <v>269.1686191641557</v>
       </c>
       <c r="J325" t="n">
         <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>14.2176156725933</v>
+        <v>14.18882766140421</v>
       </c>
       <c r="L325" t="b">
         <v>0</v>
